--- a/telegram_research_dashboard/static/valuation_full.xlsx
+++ b/telegram_research_dashboard/static/valuation_full.xlsx
@@ -802,7 +802,7 @@
         </is>
       </c>
       <c r="B5" s="8" t="n">
-        <v>37480</v>
+        <v>33297</v>
       </c>
       <c r="C5" s="9" t="n"/>
       <c r="D5" s="9" t="n">
@@ -815,10 +815,10 @@
         <v>37.73</v>
       </c>
       <c r="G5" s="10" t="n">
-        <v>15.36</v>
+        <v>13.72</v>
       </c>
       <c r="H5" s="10" t="n">
-        <v>13.42</v>
+        <v>11.82</v>
       </c>
       <c r="I5" s="10" t="n"/>
       <c r="J5" s="9" t="n"/>
@@ -847,10 +847,10 @@
         <v>5.72</v>
       </c>
       <c r="U5" s="10" t="n">
-        <v>4.15</v>
+        <v>3.7</v>
       </c>
       <c r="V5" s="10" t="n">
-        <v>3.3</v>
+        <v>2.93</v>
       </c>
       <c r="W5" s="10" t="n"/>
       <c r="X5" s="11" t="n">
@@ -866,10 +866,10 @@
         <v>18.82</v>
       </c>
       <c r="AB5" s="12" t="n">
-        <v>30.52</v>
+        <v>30.41</v>
       </c>
       <c r="AC5" s="12" t="n">
-        <v>27.39</v>
+        <v>27.65</v>
       </c>
       <c r="AD5" s="12" t="n"/>
       <c r="AE5" s="9" t="n">
@@ -885,10 +885,10 @@
         <v>3.04</v>
       </c>
       <c r="AI5" s="10" t="n">
-        <v>2.01</v>
+        <v>1.79</v>
       </c>
       <c r="AJ5" s="10" t="n">
-        <v>1.88</v>
+        <v>1.68</v>
       </c>
       <c r="AK5" s="10" t="n"/>
     </row>
@@ -899,7 +899,7 @@
         </is>
       </c>
       <c r="B6" s="8" t="n">
-        <v>19558</v>
+        <v>17984</v>
       </c>
       <c r="C6" s="9" t="n"/>
       <c r="D6" s="9" t="n">
@@ -912,10 +912,10 @@
         <v>27.94</v>
       </c>
       <c r="G6" s="10" t="n">
-        <v>13.87</v>
+        <v>12.59</v>
       </c>
       <c r="H6" s="10" t="n">
-        <v>13.31</v>
+        <v>12.36</v>
       </c>
       <c r="I6" s="10" t="n"/>
       <c r="J6" s="9" t="n"/>
@@ -944,10 +944,10 @@
         <v>5.64</v>
       </c>
       <c r="U6" s="10" t="n">
-        <v>3.25</v>
+        <v>2.99</v>
       </c>
       <c r="V6" s="10" t="n">
-        <v>2.61</v>
+        <v>2.4</v>
       </c>
       <c r="W6" s="10" t="n"/>
       <c r="X6" s="11" t="n">
@@ -963,10 +963,10 @@
         <v>22.59</v>
       </c>
       <c r="AB6" s="12" t="n">
-        <v>26.58</v>
+        <v>26.9</v>
       </c>
       <c r="AC6" s="12" t="n">
-        <v>21.78</v>
+        <v>21.54</v>
       </c>
       <c r="AD6" s="12" t="n"/>
       <c r="AE6" s="9" t="n">
@@ -982,10 +982,10 @@
         <v>2.72</v>
       </c>
       <c r="AI6" s="10" t="n">
-        <v>1.65</v>
+        <v>1.52</v>
       </c>
       <c r="AJ6" s="10" t="n">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="AK6" s="10" t="n"/>
     </row>
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>13630</v>
+        <v>12699</v>
       </c>
       <c r="C7" s="9" t="n"/>
       <c r="D7" s="9" t="n"/>
@@ -1007,10 +1007,10 @@
         <v>37.73</v>
       </c>
       <c r="G7" s="10" t="n">
-        <v>18.07</v>
+        <v>17.04</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>12.56</v>
+        <v>11.74</v>
       </c>
       <c r="I7" s="10" t="n"/>
       <c r="J7" s="9" t="n"/>
@@ -1039,10 +1039,10 @@
         <v>4.96</v>
       </c>
       <c r="U7" s="10" t="n">
-        <v>3.54</v>
+        <v>3.31</v>
       </c>
       <c r="V7" s="10" t="n">
-        <v>2.76</v>
+        <v>2.58</v>
       </c>
       <c r="W7" s="10" t="n"/>
       <c r="X7" s="11" t="n">
@@ -1058,7 +1058,7 @@
         <v>13.74</v>
       </c>
       <c r="AB7" s="12" t="n">
-        <v>21.73</v>
+        <v>21.52</v>
       </c>
       <c r="AC7" s="12" t="n">
         <v>24.71</v>
@@ -1077,10 +1077,10 @@
         <v>1.93</v>
       </c>
       <c r="AI7" s="10" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="AJ7" s="10" t="n">
-        <v>1.24</v>
+        <v>1.15</v>
       </c>
       <c r="AK7" s="10" t="n"/>
     </row>
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="B8" s="8" t="n">
-        <v>19273</v>
+        <v>17172</v>
       </c>
       <c r="C8" s="9" t="n"/>
       <c r="D8" s="9" t="n">
@@ -1104,10 +1104,10 @@
         <v>13.27</v>
       </c>
       <c r="G8" s="10" t="n">
-        <v>7.06</v>
+        <v>6.23</v>
       </c>
       <c r="H8" s="10" t="n">
-        <v>6.08</v>
+        <v>5.28</v>
       </c>
       <c r="I8" s="10" t="n"/>
       <c r="J8" s="9" t="n">
@@ -1138,10 +1138,10 @@
         <v>2.17</v>
       </c>
       <c r="U8" s="10" t="n">
-        <v>1.59</v>
+        <v>1.41</v>
       </c>
       <c r="V8" s="10" t="n">
-        <v>1.31</v>
+        <v>1.16</v>
       </c>
       <c r="W8" s="10" t="n"/>
       <c r="X8" s="11" t="n">
@@ -1157,10 +1157,10 @@
         <v>17.78</v>
       </c>
       <c r="AB8" s="12" t="n">
-        <v>24.77</v>
+        <v>25</v>
       </c>
       <c r="AC8" s="12" t="n">
-        <v>23.63</v>
+        <v>24.17</v>
       </c>
       <c r="AD8" s="12" t="n"/>
       <c r="AE8" s="9" t="n">
@@ -1176,10 +1176,10 @@
         <v>0.96</v>
       </c>
       <c r="AI8" s="10" t="n">
-        <v>0.74</v>
+        <v>0.66</v>
       </c>
       <c r="AJ8" s="10" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.62</v>
       </c>
       <c r="AK8" s="10" t="n"/>
     </row>
@@ -1190,7 +1190,7 @@
         </is>
       </c>
       <c r="B9" s="8" t="n">
-        <v>1349</v>
+        <v>1306</v>
       </c>
       <c r="C9" s="9" t="n"/>
       <c r="D9" s="9" t="n"/>
@@ -1199,10 +1199,10 @@
         <v>10.3</v>
       </c>
       <c r="G9" s="10" t="n">
-        <v>6.46</v>
+        <v>5.99</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>6.17</v>
+        <v>5.87</v>
       </c>
       <c r="I9" s="10" t="n"/>
       <c r="J9" s="9" t="n"/>
@@ -1221,10 +1221,10 @@
         <v>2.35</v>
       </c>
       <c r="U9" s="10" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="V9" s="10" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="W9" s="10" t="n"/>
       <c r="X9" s="11" t="n">
@@ -1240,10 +1240,10 @@
         <v>32.19</v>
       </c>
       <c r="AB9" s="12" t="n">
-        <v>22.79</v>
+        <v>23.73</v>
       </c>
       <c r="AC9" s="12" t="n">
-        <v>19.48</v>
+        <v>19.63</v>
       </c>
       <c r="AD9" s="12" t="n"/>
       <c r="AE9" s="9" t="n"/>
@@ -1253,10 +1253,10 @@
         <v>2.09</v>
       </c>
       <c r="AI9" s="10" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="AJ9" s="10" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AK9" s="10" t="n"/>
     </row>
@@ -1267,7 +1267,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>1077</v>
+        <v>1030</v>
       </c>
       <c r="C10" s="9" t="n"/>
       <c r="D10" s="9" t="n"/>
@@ -1346,7 +1346,7 @@
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>8257</v>
+        <v>7797</v>
       </c>
       <c r="C11" s="9" t="n"/>
       <c r="D11" s="9" t="n"/>
@@ -1357,10 +1357,10 @@
         <v>32.18</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>31.91</v>
+        <v>30.11</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>26.15</v>
+        <v>25.02</v>
       </c>
       <c r="I11" s="10" t="n"/>
       <c r="J11" s="9" t="n"/>
@@ -1383,10 +1383,10 @@
         <v>10.52</v>
       </c>
       <c r="U11" s="10" t="n">
-        <v>10.95</v>
+        <v>10.35</v>
       </c>
       <c r="V11" s="10" t="n">
-        <v>8.94</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="W11" s="10" t="n"/>
       <c r="X11" s="11" t="n">
@@ -1402,10 +1402,10 @@
         <v>33.73</v>
       </c>
       <c r="AB11" s="12" t="n">
-        <v>37.81</v>
+        <v>37.86</v>
       </c>
       <c r="AC11" s="12" t="n">
-        <v>37.64</v>
+        <v>37.22</v>
       </c>
       <c r="AD11" s="12" t="n"/>
       <c r="AE11" s="9" t="n"/>
@@ -1417,10 +1417,10 @@
         <v>4.38</v>
       </c>
       <c r="AI11" s="10" t="n">
-        <v>4.77</v>
+        <v>4.47</v>
       </c>
       <c r="AJ11" s="10" t="n">
-        <v>4.14</v>
+        <v>3.93</v>
       </c>
       <c r="AK11" s="10" t="n"/>
     </row>
@@ -1431,7 +1431,7 @@
         </is>
       </c>
       <c r="B12" s="8" t="n">
-        <v>1328</v>
+        <v>1241</v>
       </c>
       <c r="C12" s="9" t="n">
         <v>14.21</v>
@@ -1446,10 +1446,10 @@
         <v>18.39</v>
       </c>
       <c r="G12" s="10" t="n">
-        <v>13.36</v>
+        <v>13.06</v>
       </c>
       <c r="H12" s="10" t="n">
-        <v>9.640000000000001</v>
+        <v>9.17</v>
       </c>
       <c r="I12" s="10" t="n"/>
       <c r="J12" s="9" t="n">
@@ -1480,10 +1480,10 @@
         <v>6.21</v>
       </c>
       <c r="U12" s="10" t="n">
-        <v>2.86</v>
+        <v>2.7</v>
       </c>
       <c r="V12" s="10" t="n">
-        <v>2.21</v>
+        <v>2.09</v>
       </c>
       <c r="W12" s="10" t="n"/>
       <c r="X12" s="11" t="n">
@@ -1499,10 +1499,10 @@
         <v>41.36</v>
       </c>
       <c r="AB12" s="12" t="n">
-        <v>24</v>
+        <v>23.08</v>
       </c>
       <c r="AC12" s="12" t="n">
-        <v>25.85</v>
+        <v>25.69</v>
       </c>
       <c r="AD12" s="12" t="n"/>
       <c r="AE12" s="9" t="n">
@@ -1518,10 +1518,10 @@
         <v>7.54</v>
       </c>
       <c r="AI12" s="10" t="n">
-        <v>2.93</v>
+        <v>2.74</v>
       </c>
       <c r="AJ12" s="10" t="n">
-        <v>2.34</v>
+        <v>2.2</v>
       </c>
       <c r="AK12" s="10" t="n"/>
     </row>
@@ -1532,7 +1532,7 @@
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>3129</v>
+        <v>3020</v>
       </c>
       <c r="C13" s="9" t="n"/>
       <c r="D13" s="9" t="n"/>
@@ -1543,10 +1543,10 @@
         <v>20.62</v>
       </c>
       <c r="G13" s="10" t="n">
-        <v>22.04</v>
+        <v>20.57</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>14.44</v>
+        <v>14.01</v>
       </c>
       <c r="I13" s="10" t="n"/>
       <c r="J13" s="9" t="n"/>
@@ -1575,10 +1575,10 @@
         <v>6.44</v>
       </c>
       <c r="U13" s="10" t="n">
-        <v>5.62</v>
+        <v>5.38</v>
       </c>
       <c r="V13" s="10" t="n">
-        <v>4.05</v>
+        <v>3.89</v>
       </c>
       <c r="W13" s="10" t="n"/>
       <c r="X13" s="11" t="n">
@@ -1594,10 +1594,10 @@
         <v>36.6</v>
       </c>
       <c r="AB13" s="12" t="n">
-        <v>29.23</v>
+        <v>30.11</v>
       </c>
       <c r="AC13" s="12" t="n">
-        <v>32.59</v>
+        <v>32.22</v>
       </c>
       <c r="AD13" s="12" t="n"/>
       <c r="AE13" s="9" t="n">
@@ -1613,10 +1613,10 @@
         <v>2.61</v>
       </c>
       <c r="AI13" s="10" t="n">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="AJ13" s="10" t="n">
-        <v>1.92</v>
+        <v>1.84</v>
       </c>
       <c r="AK13" s="10" t="n"/>
     </row>
@@ -1627,7 +1627,7 @@
         </is>
       </c>
       <c r="B14" s="8" t="n">
-        <v>815</v>
+        <v>771</v>
       </c>
       <c r="C14" s="9" t="n">
         <v>23.46</v>
@@ -1640,10 +1640,10 @@
         <v>14.78</v>
       </c>
       <c r="G14" s="10" t="n">
-        <v>9.07</v>
+        <v>8.67</v>
       </c>
       <c r="H14" s="10" t="n">
-        <v>7.7</v>
+        <v>7.3</v>
       </c>
       <c r="I14" s="10" t="n"/>
       <c r="J14" s="9" t="n">
@@ -1674,10 +1674,10 @@
         <v>2.59</v>
       </c>
       <c r="U14" s="10" t="n">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
       <c r="V14" s="10" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="W14" s="10" t="n"/>
       <c r="X14" s="11" t="n">
@@ -1693,10 +1693,10 @@
         <v>19.3</v>
       </c>
       <c r="AB14" s="12" t="n">
-        <v>19.11</v>
+        <v>18.94</v>
       </c>
       <c r="AC14" s="12" t="n">
-        <v>19.15</v>
+        <v>19.16</v>
       </c>
       <c r="AD14" s="12" t="n"/>
       <c r="AE14" s="9" t="n">
@@ -1712,10 +1712,10 @@
         <v>1.65</v>
       </c>
       <c r="AI14" s="10" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="AJ14" s="10" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AK14" s="10" t="n"/>
     </row>
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="B15" s="8" t="n">
-        <v>375</v>
+        <v>365</v>
       </c>
       <c r="C15" s="9" t="n">
         <v>37.11</v>
@@ -1741,10 +1741,10 @@
         <v>13.58</v>
       </c>
       <c r="G15" s="10" t="n">
-        <v>6.88</v>
+        <v>6.7</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>5.79</v>
+        <v>5.64</v>
       </c>
       <c r="I15" s="10" t="n"/>
       <c r="J15" s="9" t="n">
@@ -1775,10 +1775,10 @@
         <v>2.93</v>
       </c>
       <c r="U15" s="10" t="n">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="V15" s="10" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="W15" s="10" t="n"/>
       <c r="X15" s="11" t="n">
@@ -1813,10 +1813,10 @@
         <v>1.02</v>
       </c>
       <c r="AI15" s="10" t="n">
-        <v>0.59</v>
+        <v>0.57</v>
       </c>
       <c r="AJ15" s="10" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="AK15" s="10" t="n"/>
     </row>
@@ -1834,7 +1834,7 @@
         </is>
       </c>
       <c r="B17" s="8" t="n">
-        <v>5195</v>
+        <v>4907</v>
       </c>
       <c r="C17" s="9" t="n"/>
       <c r="D17" s="9" t="n"/>
@@ -1875,10 +1875,10 @@
         <v>5.43</v>
       </c>
       <c r="U17" s="10" t="n">
-        <v>3.8</v>
+        <v>3.71</v>
       </c>
       <c r="V17" s="10" t="n">
-        <v>3.11</v>
+        <v>3.02</v>
       </c>
       <c r="W17" s="10" t="n"/>
       <c r="X17" s="11" t="n">
@@ -1894,10 +1894,10 @@
         <v>13.32</v>
       </c>
       <c r="AB17" s="12" t="n">
-        <v>16.62</v>
+        <v>16.33</v>
       </c>
       <c r="AC17" s="12" t="n">
-        <v>20</v>
+        <v>20.52</v>
       </c>
       <c r="AD17" s="12" t="n"/>
       <c r="AE17" s="9" t="n">
@@ -1913,10 +1913,10 @@
         <v>0.61</v>
       </c>
       <c r="AI17" s="10" t="n">
-        <v>0.48</v>
+        <v>0.47</v>
       </c>
       <c r="AJ17" s="10" t="n">
-        <v>0.43</v>
+        <v>0.41</v>
       </c>
       <c r="AK17" s="10" t="n"/>
     </row>
@@ -1940,10 +1940,10 @@
         <v>20.62</v>
       </c>
       <c r="G18" s="15" t="n">
-        <v>13.61</v>
+        <v>12.82</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>11.1</v>
+        <v>10.46</v>
       </c>
       <c r="I18" s="15" t="n"/>
       <c r="J18" s="15" t="n">
@@ -1974,10 +1974,10 @@
         <v>4.96</v>
       </c>
       <c r="U18" s="15" t="n">
-        <v>3.05</v>
+        <v>2.85</v>
       </c>
       <c r="V18" s="15" t="n">
-        <v>2.41</v>
+        <v>2.25</v>
       </c>
       <c r="W18" s="15" t="n"/>
       <c r="X18" s="16" t="n">
@@ -1993,10 +1993,10 @@
         <v>22.59</v>
       </c>
       <c r="AB18" s="16" t="n">
-        <v>24.75</v>
+        <v>24.87</v>
       </c>
       <c r="AC18" s="16" t="n">
-        <v>24.17</v>
+        <v>24.44</v>
       </c>
       <c r="AD18" s="16" t="n"/>
       <c r="AE18" s="15" t="n">
@@ -2012,10 +2012,10 @@
         <v>2.09</v>
       </c>
       <c r="AI18" s="15" t="n">
-        <v>1.53</v>
+        <v>1.43</v>
       </c>
       <c r="AJ18" s="15" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="AK18" s="15" t="n"/>
     </row>
@@ -2065,10 +2065,10 @@
         <v>5.43</v>
       </c>
       <c r="U19" s="15" t="n">
-        <v>3.8</v>
+        <v>3.71</v>
       </c>
       <c r="V19" s="15" t="n">
-        <v>3.11</v>
+        <v>3.02</v>
       </c>
       <c r="W19" s="15" t="n"/>
       <c r="X19" s="16" t="n">
@@ -2084,10 +2084,10 @@
         <v>13.32</v>
       </c>
       <c r="AB19" s="16" t="n">
-        <v>16.62</v>
+        <v>16.33</v>
       </c>
       <c r="AC19" s="16" t="n">
-        <v>20</v>
+        <v>20.52</v>
       </c>
       <c r="AD19" s="16" t="n"/>
       <c r="AE19" s="15" t="n">
@@ -2103,10 +2103,10 @@
         <v>0.61</v>
       </c>
       <c r="AI19" s="15" t="n">
-        <v>0.48</v>
+        <v>0.47</v>
       </c>
       <c r="AJ19" s="15" t="n">
-        <v>0.43</v>
+        <v>0.41</v>
       </c>
       <c r="AK19" s="15" t="n"/>
     </row>
@@ -2130,10 +2130,10 @@
         <v>24.28</v>
       </c>
       <c r="G20" s="15" t="n">
-        <v>13.61</v>
+        <v>12.82</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>11.1</v>
+        <v>10.46</v>
       </c>
       <c r="I20" s="15" t="n"/>
       <c r="J20" s="15" t="n">
@@ -2164,10 +2164,10 @@
         <v>5.2</v>
       </c>
       <c r="U20" s="15" t="n">
-        <v>3.25</v>
+        <v>2.99</v>
       </c>
       <c r="V20" s="15" t="n">
-        <v>2.61</v>
+        <v>2.4</v>
       </c>
       <c r="W20" s="15" t="n"/>
       <c r="X20" s="16" t="n">
@@ -2186,7 +2186,7 @@
         <v>24.74</v>
       </c>
       <c r="AC20" s="16" t="n">
-        <v>23.63</v>
+        <v>24.17</v>
       </c>
       <c r="AD20" s="16" t="n"/>
       <c r="AE20" s="15" t="n">
@@ -2202,10 +2202,10 @@
         <v>2.01</v>
       </c>
       <c r="AI20" s="15" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="AJ20" s="15" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AK20" s="15" t="n"/>
     </row>
@@ -2266,7 +2266,7 @@
         </is>
       </c>
       <c r="B24" s="8" t="n">
-        <v>9485</v>
+        <v>9693</v>
       </c>
       <c r="C24" s="9" t="n">
         <v>41.88</v>
@@ -2281,10 +2281,10 @@
         <v>59.99</v>
       </c>
       <c r="G24" s="10" t="n">
-        <v>55.63</v>
+        <v>52.13</v>
       </c>
       <c r="H24" s="10" t="n">
-        <v>28.85</v>
+        <v>29.35</v>
       </c>
       <c r="I24" s="10" t="n"/>
       <c r="J24" s="9" t="n">
@@ -2315,10 +2315,10 @@
         <v>6.09</v>
       </c>
       <c r="U24" s="10" t="n">
-        <v>6.37</v>
+        <v>6.47</v>
       </c>
       <c r="V24" s="10" t="n">
-        <v>5.49</v>
+        <v>5.58</v>
       </c>
       <c r="W24" s="10" t="n"/>
       <c r="X24" s="11" t="n">
@@ -2334,10 +2334,10 @@
         <v>10.51</v>
       </c>
       <c r="AB24" s="12" t="n">
-        <v>11.95</v>
+        <v>13</v>
       </c>
       <c r="AC24" s="12" t="n">
-        <v>20.45</v>
+        <v>20.41</v>
       </c>
       <c r="AD24" s="12" t="n"/>
       <c r="AE24" s="9" t="n">
@@ -2353,10 +2353,10 @@
         <v>3.02</v>
       </c>
       <c r="AI24" s="10" t="n">
-        <v>2.37</v>
+        <v>2.43</v>
       </c>
       <c r="AJ24" s="10" t="n">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="AK24" s="10" t="n"/>
     </row>
@@ -2367,7 +2367,7 @@
         </is>
       </c>
       <c r="B25" s="8" t="n">
-        <v>41472</v>
+        <v>41082</v>
       </c>
       <c r="C25" s="9" t="n">
         <v>19.31</v>
@@ -2382,10 +2382,10 @@
         <v>34.46</v>
       </c>
       <c r="G25" s="10" t="n">
-        <v>22.44</v>
+        <v>22.4</v>
       </c>
       <c r="H25" s="10" t="n">
-        <v>18.22</v>
+        <v>18.02</v>
       </c>
       <c r="I25" s="10" t="n"/>
       <c r="J25" s="9" t="n">
@@ -2416,10 +2416,10 @@
         <v>5</v>
       </c>
       <c r="U25" s="10" t="n">
-        <v>4.74</v>
+        <v>4.7</v>
       </c>
       <c r="V25" s="10" t="n">
-        <v>3.9</v>
+        <v>3.87</v>
       </c>
       <c r="W25" s="10" t="n"/>
       <c r="X25" s="11" t="n">
@@ -2435,10 +2435,10 @@
         <v>19.14</v>
       </c>
       <c r="AB25" s="12" t="n">
-        <v>23.15</v>
+        <v>23.01</v>
       </c>
       <c r="AC25" s="12" t="n">
-        <v>23.48</v>
+        <v>23.56</v>
       </c>
       <c r="AD25" s="12" t="n"/>
       <c r="AE25" s="9" t="n">
@@ -2454,10 +2454,10 @@
         <v>1.81</v>
       </c>
       <c r="AI25" s="10" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="AJ25" s="10" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="AK25" s="10" t="n"/>
     </row>
@@ -2468,7 +2468,7 @@
         </is>
       </c>
       <c r="B26" s="8" t="n">
-        <v>11044</v>
+        <v>12399</v>
       </c>
       <c r="C26" s="9" t="n">
         <v>16.34</v>
@@ -2483,10 +2483,10 @@
         <v>36.3</v>
       </c>
       <c r="G26" s="10" t="n">
-        <v>40.52</v>
+        <v>45.66</v>
       </c>
       <c r="H26" s="10" t="n">
-        <v>28.13</v>
+        <v>31.53</v>
       </c>
       <c r="I26" s="10" t="n"/>
       <c r="J26" s="9" t="n">
@@ -2517,10 +2517,10 @@
         <v>6.43</v>
       </c>
       <c r="U26" s="10" t="n">
-        <v>8.640000000000001</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="V26" s="10" t="n">
-        <v>6.98</v>
+        <v>7.85</v>
       </c>
       <c r="W26" s="10" t="n"/>
       <c r="X26" s="11" t="n">
@@ -2536,10 +2536,10 @@
         <v>19.2</v>
       </c>
       <c r="AB26" s="12" t="n">
-        <v>23.25</v>
+        <v>23.2</v>
       </c>
       <c r="AC26" s="12" t="n">
-        <v>27.46</v>
+        <v>27.53</v>
       </c>
       <c r="AD26" s="12" t="n"/>
       <c r="AE26" s="9" t="n">
@@ -2555,10 +2555,10 @@
         <v>2.14</v>
       </c>
       <c r="AI26" s="10" t="n">
-        <v>2.87</v>
+        <v>3.23</v>
       </c>
       <c r="AJ26" s="10" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="AK26" s="10" t="n"/>
     </row>
@@ -2569,7 +2569,7 @@
         </is>
       </c>
       <c r="B27" s="8" t="n">
-        <v>9886</v>
+        <v>11547</v>
       </c>
       <c r="C27" s="9" t="n"/>
       <c r="D27" s="9" t="n">
@@ -2582,10 +2582,10 @@
         <v>41.99</v>
       </c>
       <c r="G27" s="10" t="n">
-        <v>89.69</v>
+        <v>80.54000000000001</v>
       </c>
       <c r="H27" s="10" t="n">
-        <v>30.44</v>
+        <v>35.85</v>
       </c>
       <c r="I27" s="10" t="n"/>
       <c r="J27" s="9" t="n">
@@ -2616,10 +2616,10 @@
         <v>2.1</v>
       </c>
       <c r="U27" s="10" t="n">
-        <v>2.69</v>
+        <v>3.13</v>
       </c>
       <c r="V27" s="10" t="n">
-        <v>2.58</v>
+        <v>3</v>
       </c>
       <c r="W27" s="10" t="n"/>
       <c r="X27" s="11" t="n">
@@ -2635,10 +2635,10 @@
         <v>6.6</v>
       </c>
       <c r="AB27" s="12" t="n">
-        <v>3.02</v>
+        <v>3.93</v>
       </c>
       <c r="AC27" s="12" t="n">
-        <v>8.65</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="AD27" s="12" t="n"/>
       <c r="AE27" s="9" t="n">
@@ -2654,10 +2654,10 @@
         <v>2.78</v>
       </c>
       <c r="AI27" s="10" t="n">
-        <v>2.97</v>
+        <v>3.44</v>
       </c>
       <c r="AJ27" s="10" t="n">
-        <v>2.59</v>
+        <v>3.08</v>
       </c>
       <c r="AK27" s="10" t="n"/>
     </row>
@@ -2668,7 +2668,7 @@
         </is>
       </c>
       <c r="B28" s="8" t="n">
-        <v>10100</v>
+        <v>9471</v>
       </c>
       <c r="C28" s="9" t="n">
         <v>15.67</v>
@@ -2683,10 +2683,10 @@
         <v>26.64</v>
       </c>
       <c r="G28" s="10" t="n">
-        <v>15.43</v>
+        <v>14.51</v>
       </c>
       <c r="H28" s="10" t="n">
-        <v>11.18</v>
+        <v>10.61</v>
       </c>
       <c r="I28" s="10" t="n"/>
       <c r="J28" s="9" t="n">
@@ -2717,10 +2717,10 @@
         <v>6.66</v>
       </c>
       <c r="U28" s="10" t="n">
-        <v>3.49</v>
+        <v>3.27</v>
       </c>
       <c r="V28" s="10" t="n">
-        <v>2.71</v>
+        <v>2.55</v>
       </c>
       <c r="W28" s="10" t="n"/>
       <c r="X28" s="11" t="n">
@@ -2736,10 +2736,10 @@
         <v>30.05</v>
       </c>
       <c r="AB28" s="12" t="n">
-        <v>25.21</v>
+        <v>25.17</v>
       </c>
       <c r="AC28" s="12" t="n">
-        <v>27.27</v>
+        <v>27.03</v>
       </c>
       <c r="AD28" s="12" t="n"/>
       <c r="AE28" s="9" t="n">
@@ -2755,10 +2755,10 @@
         <v>3.51</v>
       </c>
       <c r="AI28" s="10" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AJ28" s="10" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AK28" s="10" t="n"/>
     </row>
@@ -2776,7 +2776,7 @@
         </is>
       </c>
       <c r="B30" s="8" t="n">
-        <v>120040</v>
+        <v>116644</v>
       </c>
       <c r="C30" s="9" t="n">
         <v>21.56</v>
@@ -2790,12 +2790,8 @@
       <c r="F30" s="9" t="n">
         <v>22.08</v>
       </c>
-      <c r="G30" s="10" t="n">
-        <v>17.21</v>
-      </c>
-      <c r="H30" s="10" t="n">
-        <v>16.02</v>
-      </c>
+      <c r="G30" s="10" t="n"/>
+      <c r="H30" s="10" t="n"/>
       <c r="I30" s="10" t="n"/>
       <c r="J30" s="9" t="n">
         <v>15.68</v>
@@ -2825,10 +2821,10 @@
         <v>16.48</v>
       </c>
       <c r="U30" s="10" t="n">
-        <v>11.79</v>
+        <v>11.45</v>
       </c>
       <c r="V30" s="10" t="n">
-        <v>8.630000000000001</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="W30" s="10" t="n"/>
       <c r="X30" s="11" t="n">
@@ -2844,10 +2840,10 @@
         <v>76.87</v>
       </c>
       <c r="AB30" s="12" t="n">
-        <v>82.51000000000001</v>
+        <v>82.56</v>
       </c>
       <c r="AC30" s="12" t="n">
-        <v>62.21</v>
+        <v>62.25</v>
       </c>
       <c r="AD30" s="12" t="n"/>
       <c r="AE30" s="9" t="n">
@@ -2863,10 +2859,10 @@
         <v>1.48</v>
       </c>
       <c r="AI30" s="10" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AJ30" s="10" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AK30" s="10" t="n"/>
     </row>
@@ -2877,7 +2873,7 @@
         </is>
       </c>
       <c r="B31" s="8" t="n">
-        <v>73692</v>
+        <v>67906</v>
       </c>
       <c r="C31" s="9" t="n">
         <v>17.07</v>
@@ -2891,12 +2887,8 @@
       <c r="F31" s="9" t="n">
         <v>19.36</v>
       </c>
-      <c r="G31" s="10" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="H31" s="10" t="n">
-        <v>17.05</v>
-      </c>
+      <c r="G31" s="10" t="n"/>
+      <c r="H31" s="10" t="n"/>
       <c r="I31" s="10" t="n"/>
       <c r="J31" s="9" t="n">
         <v>12.31</v>
@@ -2926,10 +2918,10 @@
         <v>4.86</v>
       </c>
       <c r="U31" s="10" t="n">
-        <v>3.77</v>
+        <v>3.47</v>
       </c>
       <c r="V31" s="10" t="n">
-        <v>3.26</v>
+        <v>3.01</v>
       </c>
       <c r="W31" s="10" t="n"/>
       <c r="X31" s="11" t="n">
@@ -2945,10 +2937,10 @@
         <v>26.17</v>
       </c>
       <c r="AB31" s="12" t="n">
-        <v>22.72</v>
+        <v>22.73</v>
       </c>
       <c r="AC31" s="12" t="n">
-        <v>20.51</v>
+        <v>20.52</v>
       </c>
       <c r="AD31" s="12" t="n"/>
       <c r="AE31" s="9" t="n">
@@ -2964,10 +2956,10 @@
         <v>1.93</v>
       </c>
       <c r="AI31" s="10" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AJ31" s="10" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AK31" s="10" t="n"/>
     </row>
@@ -2978,7 +2970,7 @@
         </is>
       </c>
       <c r="B32" s="8" t="n">
-        <v>96232</v>
+        <v>89308</v>
       </c>
       <c r="C32" s="9" t="n">
         <v>20.08</v>
@@ -2992,12 +2984,8 @@
       <c r="F32" s="9" t="n">
         <v>21.62</v>
       </c>
-      <c r="G32" s="10" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="H32" s="10" t="n">
-        <v>19.12</v>
-      </c>
+      <c r="G32" s="10" t="n"/>
+      <c r="H32" s="10" t="n"/>
       <c r="I32" s="10" t="n"/>
       <c r="J32" s="9" t="n">
         <v>14.87</v>
@@ -3027,10 +3015,10 @@
         <v>3.55</v>
       </c>
       <c r="U32" s="10" t="n">
-        <v>3.38</v>
+        <v>3.14</v>
       </c>
       <c r="V32" s="10" t="n">
-        <v>3.04</v>
+        <v>2.82</v>
       </c>
       <c r="W32" s="10" t="n"/>
       <c r="X32" s="11" t="n">
@@ -3065,10 +3053,10 @@
         <v>1.73</v>
       </c>
       <c r="AI32" s="10" t="n">
-        <v>1.72</v>
+        <v>1.6</v>
       </c>
       <c r="AJ32" s="10" t="n">
-        <v>1.64</v>
+        <v>1.52</v>
       </c>
       <c r="AK32" s="10" t="n"/>
     </row>
@@ -3079,7 +3067,7 @@
         </is>
       </c>
       <c r="B33" s="8" t="n">
-        <v>265343</v>
+        <v>248904</v>
       </c>
       <c r="C33" s="9" t="n">
         <v>28.47</v>
@@ -3093,12 +3081,8 @@
       <c r="F33" s="9" t="n">
         <v>36.57</v>
       </c>
-      <c r="G33" s="10" t="n">
-        <v>27.29</v>
-      </c>
-      <c r="H33" s="10" t="n">
-        <v>25.16</v>
-      </c>
+      <c r="G33" s="10" t="n"/>
+      <c r="H33" s="10" t="n"/>
       <c r="I33" s="10" t="n"/>
       <c r="J33" s="9" t="n">
         <v>15.21</v>
@@ -3128,10 +3112,10 @@
         <v>3.77</v>
       </c>
       <c r="U33" s="10" t="n">
-        <v>3.78</v>
+        <v>3.54</v>
       </c>
       <c r="V33" s="10" t="n">
-        <v>3.51</v>
+        <v>3.29</v>
       </c>
       <c r="W33" s="10" t="n"/>
       <c r="X33" s="11" t="n">
@@ -3147,7 +3131,7 @@
         <v>10.74</v>
       </c>
       <c r="AB33" s="12" t="n">
-        <v>14.35</v>
+        <v>14.36</v>
       </c>
       <c r="AC33" s="12" t="n">
         <v>14.46</v>
@@ -3166,10 +3150,10 @@
         <v>2.78</v>
       </c>
       <c r="AI33" s="10" t="n">
-        <v>2.76</v>
+        <v>2.59</v>
       </c>
       <c r="AJ33" s="10" t="n">
-        <v>2.57</v>
+        <v>2.41</v>
       </c>
       <c r="AK33" s="10" t="n"/>
     </row>
@@ -3180,7 +3164,7 @@
         </is>
       </c>
       <c r="B34" s="8" t="n">
-        <v>10975</v>
+        <v>10582</v>
       </c>
       <c r="C34" s="9" t="n">
         <v>15.9</v>
@@ -3194,12 +3178,8 @@
       <c r="F34" s="9" t="n">
         <v>22.06</v>
       </c>
-      <c r="G34" s="10" t="n">
-        <v>15.11</v>
-      </c>
-      <c r="H34" s="10" t="n">
-        <v>13.42</v>
-      </c>
+      <c r="G34" s="10" t="n"/>
+      <c r="H34" s="10" t="n"/>
       <c r="I34" s="10" t="n"/>
       <c r="J34" s="9" t="n">
         <v>10.08</v>
@@ -3229,10 +3209,10 @@
         <v>2.63</v>
       </c>
       <c r="U34" s="10" t="n">
-        <v>1.97</v>
+        <v>1.9</v>
       </c>
       <c r="V34" s="10" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="W34" s="10" t="n"/>
       <c r="X34" s="11" t="n">
@@ -3267,10 +3247,10 @@
         <v>1.07</v>
       </c>
       <c r="AI34" s="10" t="n">
-        <v>0.82</v>
+        <v>0.79</v>
       </c>
       <c r="AJ34" s="10" t="n">
-        <v>0.77</v>
+        <v>0.75</v>
       </c>
       <c r="AK34" s="10" t="n"/>
     </row>
@@ -3288,7 +3268,7 @@
         </is>
       </c>
       <c r="B36" s="8" t="n">
-        <v>53637</v>
+        <v>50272</v>
       </c>
       <c r="C36" s="9" t="n">
         <v>17.03</v>
@@ -3333,10 +3313,10 @@
         <v>14.29</v>
       </c>
       <c r="U36" s="10" t="n">
-        <v>7.75</v>
+        <v>7.49</v>
       </c>
       <c r="V36" s="10" t="n">
-        <v>6.3</v>
+        <v>6.09</v>
       </c>
       <c r="W36" s="10" t="n"/>
       <c r="X36" s="11" t="n">
@@ -3352,10 +3332,10 @@
         <v>15.36</v>
       </c>
       <c r="AB36" s="12" t="n">
-        <v>31.17</v>
+        <v>31.09</v>
       </c>
       <c r="AC36" s="12" t="n">
-        <v>36.99</v>
+        <v>36.85</v>
       </c>
       <c r="AD36" s="12" t="n"/>
       <c r="AE36" s="9" t="n">
@@ -3371,10 +3351,10 @@
         <v>7.21</v>
       </c>
       <c r="AI36" s="10" t="n">
-        <v>3.31</v>
+        <v>3.2</v>
       </c>
       <c r="AJ36" s="10" t="n">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="AK36" s="10" t="n"/>
     </row>
@@ -3392,7 +3372,7 @@
         </is>
       </c>
       <c r="B38" s="8" t="n">
-        <v>752</v>
+        <v>745</v>
       </c>
       <c r="C38" s="9" t="n">
         <v>16.56</v>
@@ -3456,10 +3436,10 @@
         <v>17.62</v>
       </c>
       <c r="AB38" s="12" t="n">
-        <v>19.87</v>
+        <v>19.92</v>
       </c>
       <c r="AC38" s="12" t="n">
-        <v>20.57</v>
+        <v>20.58</v>
       </c>
       <c r="AD38" s="12" t="n"/>
       <c r="AE38" s="9" t="n">
@@ -3496,7 +3476,7 @@
         </is>
       </c>
       <c r="B40" s="8" t="n">
-        <v>33466</v>
+        <v>30776</v>
       </c>
       <c r="C40" s="9" t="n">
         <v>5</v>
@@ -3541,10 +3521,10 @@
         <v>2.97</v>
       </c>
       <c r="U40" s="10" t="n">
-        <v>2.75</v>
+        <v>2.61</v>
       </c>
       <c r="V40" s="10" t="n">
-        <v>2.49</v>
+        <v>2.35</v>
       </c>
       <c r="W40" s="10" t="n"/>
       <c r="X40" s="11" t="n">
@@ -3560,10 +3540,10 @@
         <v>13.2</v>
       </c>
       <c r="AB40" s="12" t="n">
-        <v>13.7</v>
+        <v>13.73</v>
       </c>
       <c r="AC40" s="12" t="n">
-        <v>14.89</v>
+        <v>14.94</v>
       </c>
       <c r="AD40" s="12" t="n"/>
       <c r="AE40" s="9" t="n">
@@ -3579,10 +3559,10 @@
         <v>1.45</v>
       </c>
       <c r="AI40" s="10" t="n">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="AJ40" s="10" t="n">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="AK40" s="10" t="n"/>
     </row>
@@ -3600,7 +3580,7 @@
         </is>
       </c>
       <c r="B42" s="8" t="n">
-        <v>31792</v>
+        <v>32858</v>
       </c>
       <c r="C42" s="9" t="n">
         <v>24.79</v>
@@ -3645,10 +3625,10 @@
         <v>6.69</v>
       </c>
       <c r="U42" s="10" t="n">
-        <v>6.16</v>
+        <v>6.6</v>
       </c>
       <c r="V42" s="10" t="n">
-        <v>5.26</v>
+        <v>5.64</v>
       </c>
       <c r="W42" s="10" t="n"/>
       <c r="X42" s="11" t="n">
@@ -3664,10 +3644,10 @@
         <v>16.02</v>
       </c>
       <c r="AB42" s="12" t="n">
-        <v>17.2</v>
+        <v>17.21</v>
       </c>
       <c r="AC42" s="12" t="n">
-        <v>18.76</v>
+        <v>18.85</v>
       </c>
       <c r="AD42" s="12" t="n"/>
       <c r="AE42" s="9" t="n">
@@ -3683,10 +3663,10 @@
         <v>3.66</v>
       </c>
       <c r="AI42" s="10" t="n">
-        <v>3.15</v>
+        <v>3.37</v>
       </c>
       <c r="AJ42" s="10" t="n">
-        <v>2.59</v>
+        <v>2.77</v>
       </c>
       <c r="AK42" s="10" t="n"/>
     </row>
@@ -3710,10 +3690,10 @@
         <v>36.3</v>
       </c>
       <c r="G43" s="15" t="n">
-        <v>40.52</v>
+        <v>45.66</v>
       </c>
       <c r="H43" s="15" t="n">
-        <v>28.13</v>
+        <v>29.35</v>
       </c>
       <c r="I43" s="15" t="n"/>
       <c r="J43" s="15" t="n">
@@ -3744,10 +3724,10 @@
         <v>6.09</v>
       </c>
       <c r="U43" s="15" t="n">
-        <v>4.74</v>
+        <v>4.7</v>
       </c>
       <c r="V43" s="15" t="n">
-        <v>3.9</v>
+        <v>3.87</v>
       </c>
       <c r="W43" s="15" t="n"/>
       <c r="X43" s="16" t="n">
@@ -3763,10 +3743,10 @@
         <v>19.14</v>
       </c>
       <c r="AB43" s="16" t="n">
-        <v>23.15</v>
+        <v>23.01</v>
       </c>
       <c r="AC43" s="16" t="n">
-        <v>23.48</v>
+        <v>23.56</v>
       </c>
       <c r="AD43" s="16" t="n"/>
       <c r="AE43" s="15" t="n">
@@ -3782,10 +3762,10 @@
         <v>2.78</v>
       </c>
       <c r="AI43" s="15" t="n">
-        <v>2.37</v>
+        <v>2.43</v>
       </c>
       <c r="AJ43" s="15" t="n">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="AK43" s="15" t="n"/>
     </row>
@@ -3808,12 +3788,8 @@
       <c r="F44" s="15" t="n">
         <v>22.06</v>
       </c>
-      <c r="G44" s="15" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="H44" s="15" t="n">
-        <v>17.05</v>
-      </c>
+      <c r="G44" s="15" t="n"/>
+      <c r="H44" s="15" t="n"/>
       <c r="I44" s="15" t="n"/>
       <c r="J44" s="15" t="n">
         <v>14.87</v>
@@ -3843,10 +3819,10 @@
         <v>3.77</v>
       </c>
       <c r="U44" s="15" t="n">
-        <v>3.77</v>
+        <v>3.47</v>
       </c>
       <c r="V44" s="15" t="n">
-        <v>3.26</v>
+        <v>3.01</v>
       </c>
       <c r="W44" s="15" t="n"/>
       <c r="X44" s="16" t="n">
@@ -3881,10 +3857,10 @@
         <v>1.73</v>
       </c>
       <c r="AI44" s="15" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AJ44" s="15" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AK44" s="15" t="n"/>
     </row>
@@ -3938,10 +3914,10 @@
         <v>14.29</v>
       </c>
       <c r="U45" s="15" t="n">
-        <v>7.75</v>
+        <v>7.49</v>
       </c>
       <c r="V45" s="15" t="n">
-        <v>6.3</v>
+        <v>6.09</v>
       </c>
       <c r="W45" s="15" t="n"/>
       <c r="X45" s="16" t="n">
@@ -3957,10 +3933,10 @@
         <v>15.36</v>
       </c>
       <c r="AB45" s="16" t="n">
-        <v>31.17</v>
+        <v>31.09</v>
       </c>
       <c r="AC45" s="16" t="n">
-        <v>36.99</v>
+        <v>36.85</v>
       </c>
       <c r="AD45" s="16" t="n"/>
       <c r="AE45" s="15" t="n">
@@ -3976,10 +3952,10 @@
         <v>7.21</v>
       </c>
       <c r="AI45" s="15" t="n">
-        <v>3.31</v>
+        <v>3.2</v>
       </c>
       <c r="AJ45" s="15" t="n">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="AK45" s="15" t="n"/>
     </row>
@@ -4052,10 +4028,10 @@
         <v>17.62</v>
       </c>
       <c r="AB46" s="16" t="n">
-        <v>19.87</v>
+        <v>19.92</v>
       </c>
       <c r="AC46" s="16" t="n">
-        <v>20.57</v>
+        <v>20.58</v>
       </c>
       <c r="AD46" s="16" t="n"/>
       <c r="AE46" s="15" t="n">
@@ -4128,10 +4104,10 @@
         <v>2.97</v>
       </c>
       <c r="U47" s="15" t="n">
-        <v>2.75</v>
+        <v>2.61</v>
       </c>
       <c r="V47" s="15" t="n">
-        <v>2.49</v>
+        <v>2.35</v>
       </c>
       <c r="W47" s="15" t="n"/>
       <c r="X47" s="16" t="n">
@@ -4147,10 +4123,10 @@
         <v>13.2</v>
       </c>
       <c r="AB47" s="16" t="n">
-        <v>13.7</v>
+        <v>13.73</v>
       </c>
       <c r="AC47" s="16" t="n">
-        <v>14.89</v>
+        <v>14.94</v>
       </c>
       <c r="AD47" s="16" t="n"/>
       <c r="AE47" s="15" t="n">
@@ -4166,10 +4142,10 @@
         <v>1.45</v>
       </c>
       <c r="AI47" s="15" t="n">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="AJ47" s="15" t="n">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="AK47" s="15" t="n"/>
     </row>
@@ -4223,10 +4199,10 @@
         <v>6.69</v>
       </c>
       <c r="U48" s="15" t="n">
-        <v>6.16</v>
+        <v>6.6</v>
       </c>
       <c r="V48" s="15" t="n">
-        <v>5.26</v>
+        <v>5.64</v>
       </c>
       <c r="W48" s="15" t="n"/>
       <c r="X48" s="16" t="n">
@@ -4242,10 +4218,10 @@
         <v>16.02</v>
       </c>
       <c r="AB48" s="16" t="n">
-        <v>17.2</v>
+        <v>17.21</v>
       </c>
       <c r="AC48" s="16" t="n">
-        <v>18.76</v>
+        <v>18.85</v>
       </c>
       <c r="AD48" s="16" t="n"/>
       <c r="AE48" s="15" t="n">
@@ -4261,10 +4237,10 @@
         <v>3.66</v>
       </c>
       <c r="AI48" s="15" t="n">
-        <v>3.15</v>
+        <v>3.37</v>
       </c>
       <c r="AJ48" s="15" t="n">
-        <v>2.59</v>
+        <v>2.77</v>
       </c>
       <c r="AK48" s="15" t="n"/>
     </row>
@@ -4288,10 +4264,10 @@
         <v>30.55</v>
       </c>
       <c r="G49" s="15" t="n">
-        <v>21.7</v>
+        <v>45.66</v>
       </c>
       <c r="H49" s="15" t="n">
-        <v>18.67</v>
+        <v>29.35</v>
       </c>
       <c r="I49" s="15" t="n"/>
       <c r="J49" s="15" t="n">
@@ -4322,10 +4298,10 @@
         <v>4.93</v>
       </c>
       <c r="U49" s="15" t="n">
-        <v>3.77</v>
+        <v>3.5</v>
       </c>
       <c r="V49" s="15" t="n">
-        <v>3.38</v>
+        <v>3.15</v>
       </c>
       <c r="W49" s="15" t="n"/>
       <c r="X49" s="16" t="n">
@@ -4341,10 +4317,10 @@
         <v>16.82</v>
       </c>
       <c r="AB49" s="16" t="n">
-        <v>18.54</v>
+        <v>18.57</v>
       </c>
       <c r="AC49" s="16" t="n">
-        <v>20.48</v>
+        <v>20.46</v>
       </c>
       <c r="AD49" s="16" t="n"/>
       <c r="AE49" s="15" t="n">
@@ -4360,10 +4336,10 @@
         <v>2.04</v>
       </c>
       <c r="AI49" s="15" t="n">
-        <v>1.86</v>
+        <v>1.79</v>
       </c>
       <c r="AJ49" s="15" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AK49" s="15" t="n"/>
     </row>
@@ -4424,7 +4400,7 @@
         </is>
       </c>
       <c r="B53" s="8" t="n">
-        <v>5097</v>
+        <v>4213</v>
       </c>
       <c r="C53" s="9" t="n">
         <v>10.61</v>
@@ -4439,10 +4415,10 @@
         <v>47.5</v>
       </c>
       <c r="G53" s="10" t="n">
-        <v>10.58</v>
+        <v>8.75</v>
       </c>
       <c r="H53" s="10" t="n">
-        <v>9.6</v>
+        <v>7.94</v>
       </c>
       <c r="I53" s="10" t="n"/>
       <c r="J53" s="9" t="n">
@@ -4473,10 +4449,10 @@
         <v>2.61</v>
       </c>
       <c r="U53" s="10" t="n">
-        <v>2.83</v>
+        <v>2.34</v>
       </c>
       <c r="V53" s="10" t="n">
-        <v>2.21</v>
+        <v>1.83</v>
       </c>
       <c r="W53" s="10" t="n"/>
       <c r="X53" s="11" t="n">
@@ -4511,10 +4487,10 @@
         <v>1.25</v>
       </c>
       <c r="AI53" s="10" t="n">
-        <v>0.72</v>
+        <v>0.6</v>
       </c>
       <c r="AJ53" s="10" t="n">
-        <v>0.66</v>
+        <v>0.54</v>
       </c>
       <c r="AK53" s="10" t="n"/>
     </row>
@@ -4525,7 +4501,7 @@
         </is>
       </c>
       <c r="B54" s="8" t="n">
-        <v>4397</v>
+        <v>3935</v>
       </c>
       <c r="C54" s="9" t="n">
         <v>5.38</v>
@@ -4540,10 +4516,10 @@
         <v>13.73</v>
       </c>
       <c r="G54" s="10" t="n">
-        <v>9.970000000000001</v>
+        <v>9.02</v>
       </c>
       <c r="H54" s="10" t="n">
-        <v>9.300000000000001</v>
+        <v>8.83</v>
       </c>
       <c r="I54" s="10" t="n"/>
       <c r="J54" s="9" t="n">
@@ -4574,10 +4550,10 @@
         <v>0.77</v>
       </c>
       <c r="U54" s="10" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="V54" s="10" t="n">
-        <v>0.74</v>
+        <v>0.66</v>
       </c>
       <c r="W54" s="10" t="n"/>
       <c r="X54" s="11" t="n">
@@ -4593,10 +4569,10 @@
         <v>5.71</v>
       </c>
       <c r="AB54" s="12" t="n">
-        <v>8</v>
+        <v>7.93</v>
       </c>
       <c r="AC54" s="12" t="n">
-        <v>8.130000000000001</v>
+        <v>7.68</v>
       </c>
       <c r="AD54" s="12" t="n"/>
       <c r="AE54" s="9" t="n">
@@ -4612,10 +4588,10 @@
         <v>0.63</v>
       </c>
       <c r="AI54" s="10" t="n">
-        <v>0.62</v>
+        <v>0.55</v>
       </c>
       <c r="AJ54" s="10" t="n">
-        <v>0.59</v>
+        <v>0.54</v>
       </c>
       <c r="AK54" s="10" t="n"/>
     </row>
@@ -4626,7 +4602,7 @@
         </is>
       </c>
       <c r="B55" s="8" t="n">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="C55" s="9" t="n">
         <v>7.23</v>
@@ -4707,7 +4683,7 @@
         </is>
       </c>
       <c r="B56" s="8" t="n">
-        <v>192</v>
+        <v>172</v>
       </c>
       <c r="C56" s="9" t="n">
         <v>5.78</v>
@@ -4722,10 +4698,10 @@
         <v>8.390000000000001</v>
       </c>
       <c r="G56" s="10" t="n">
-        <v>7.34</v>
+        <v>6.6</v>
       </c>
       <c r="H56" s="10" t="n">
-        <v>6.03</v>
+        <v>5.42</v>
       </c>
       <c r="I56" s="10" t="n"/>
       <c r="J56" s="9" t="n">
@@ -4756,10 +4732,10 @@
         <v>0.92</v>
       </c>
       <c r="U56" s="10" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="V56" s="10" t="n">
-        <v>0.7</v>
+        <v>0.63</v>
       </c>
       <c r="W56" s="10" t="n"/>
       <c r="X56" s="11" t="n">
@@ -4794,10 +4770,10 @@
         <v>0.59</v>
       </c>
       <c r="AI56" s="10" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AJ56" s="10" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AK56" s="10" t="n"/>
     </row>
@@ -4808,7 +4784,7 @@
         </is>
       </c>
       <c r="B57" s="8" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C57" s="9" t="n">
         <v>7.57</v>
@@ -4893,7 +4869,7 @@
         </is>
       </c>
       <c r="B58" s="8" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C58" s="9" t="n">
         <v>5.71</v>
@@ -4985,7 +4961,7 @@
         </is>
       </c>
       <c r="B60" s="8" t="n">
-        <v>380870</v>
+        <v>388618</v>
       </c>
       <c r="C60" s="9" t="n">
         <v>18.45</v>
@@ -4999,12 +4975,8 @@
       <c r="F60" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="G60" s="10" t="n">
-        <v>30.11</v>
-      </c>
-      <c r="H60" s="10" t="n">
-        <v>25.28</v>
-      </c>
+      <c r="G60" s="10" t="n"/>
+      <c r="H60" s="10" t="n"/>
       <c r="I60" s="10" t="n"/>
       <c r="J60" s="9" t="n">
         <v>13.46</v>
@@ -5034,10 +5006,10 @@
         <v>12.5</v>
       </c>
       <c r="U60" s="10" t="n">
-        <v>12.42</v>
+        <v>12.67</v>
       </c>
       <c r="V60" s="10" t="n">
-        <v>9.109999999999999</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="W60" s="10" t="n"/>
       <c r="X60" s="11" t="n">
@@ -5072,10 +5044,10 @@
         <v>3.94</v>
       </c>
       <c r="AI60" s="10" t="n">
-        <v>4.81</v>
+        <v>4.91</v>
       </c>
       <c r="AJ60" s="10" t="n">
-        <v>4.33</v>
+        <v>4.41</v>
       </c>
       <c r="AK60" s="10" t="n"/>
     </row>
@@ -5086,7 +5058,7 @@
         </is>
       </c>
       <c r="B61" s="8" t="n">
-        <v>182688</v>
+        <v>185233</v>
       </c>
       <c r="C61" s="9" t="n">
         <v>16.58</v>
@@ -5100,12 +5072,8 @@
       <c r="F61" s="9" t="n">
         <v>24.83</v>
       </c>
-      <c r="G61" s="10" t="n">
-        <v>37.27</v>
-      </c>
-      <c r="H61" s="10" t="n">
-        <v>29.81</v>
-      </c>
+      <c r="G61" s="10" t="n"/>
+      <c r="H61" s="10" t="n"/>
       <c r="I61" s="10" t="n"/>
       <c r="J61" s="9" t="n">
         <v>13.71</v>
@@ -5135,10 +5103,10 @@
         <v>4.81</v>
       </c>
       <c r="U61" s="10" t="n">
-        <v>6.28</v>
+        <v>6.37</v>
       </c>
       <c r="V61" s="10" t="n">
-        <v>5.53</v>
+        <v>5.61</v>
       </c>
       <c r="W61" s="10" t="n"/>
       <c r="X61" s="11" t="n">
@@ -5157,7 +5125,7 @@
         <v>17.81</v>
       </c>
       <c r="AC61" s="12" t="n">
-        <v>19.74</v>
+        <v>19.87</v>
       </c>
       <c r="AD61" s="12" t="n"/>
       <c r="AE61" s="9" t="n">
@@ -5173,10 +5141,10 @@
         <v>2.79</v>
       </c>
       <c r="AI61" s="10" t="n">
-        <v>4.44</v>
+        <v>4.5</v>
       </c>
       <c r="AJ61" s="10" t="n">
-        <v>4.1</v>
+        <v>4.14</v>
       </c>
       <c r="AK61" s="10" t="n"/>
     </row>
@@ -5187,7 +5155,7 @@
         </is>
       </c>
       <c r="B62" s="8" t="n">
-        <v>16867</v>
+        <v>21662</v>
       </c>
       <c r="C62" s="9" t="n">
         <v>10.64</v>
@@ -5201,12 +5169,8 @@
       <c r="F62" s="9" t="n">
         <v>22.45</v>
       </c>
-      <c r="G62" s="10" t="n">
-        <v>30.06</v>
-      </c>
-      <c r="H62" s="10" t="n">
-        <v>19.82</v>
-      </c>
+      <c r="G62" s="10" t="n"/>
+      <c r="H62" s="10" t="n"/>
       <c r="I62" s="10" t="n"/>
       <c r="J62" s="9" t="n">
         <v>10.23</v>
@@ -5236,10 +5200,10 @@
         <v>1.48</v>
       </c>
       <c r="U62" s="10" t="n">
-        <v>2.09</v>
+        <v>2.69</v>
       </c>
       <c r="V62" s="10" t="n">
-        <v>1.97</v>
+        <v>2.53</v>
       </c>
       <c r="W62" s="10" t="n"/>
       <c r="X62" s="11" t="n">
@@ -5274,10 +5238,10 @@
         <v>0.63</v>
       </c>
       <c r="AI62" s="10" t="n">
-        <v>0.92</v>
+        <v>1.19</v>
       </c>
       <c r="AJ62" s="10" t="n">
-        <v>0.89</v>
+        <v>1.14</v>
       </c>
       <c r="AK62" s="10" t="n"/>
     </row>
@@ -5288,7 +5252,7 @@
         </is>
       </c>
       <c r="B63" s="8" t="n">
-        <v>62409</v>
+        <v>67287</v>
       </c>
       <c r="C63" s="9" t="n">
         <v>11.71</v>
@@ -5302,12 +5266,8 @@
       <c r="F63" s="9" t="n">
         <v>20.48</v>
       </c>
-      <c r="G63" s="10" t="n">
-        <v>20.07</v>
-      </c>
-      <c r="H63" s="10" t="n">
-        <v>17.26</v>
-      </c>
+      <c r="G63" s="10" t="n"/>
+      <c r="H63" s="10" t="n"/>
       <c r="I63" s="10" t="n"/>
       <c r="J63" s="9" t="n">
         <v>6.73</v>
@@ -5337,10 +5297,10 @@
         <v>5.69</v>
       </c>
       <c r="U63" s="10" t="n">
-        <v>5.42</v>
+        <v>5.84</v>
       </c>
       <c r="V63" s="10" t="n">
-        <v>4.31</v>
+        <v>4.65</v>
       </c>
       <c r="W63" s="10" t="n"/>
       <c r="X63" s="11" t="n">
@@ -5359,7 +5319,7 @@
         <v>30.36</v>
       </c>
       <c r="AC63" s="12" t="n">
-        <v>27.82</v>
+        <v>27.83</v>
       </c>
       <c r="AD63" s="12" t="n"/>
       <c r="AE63" s="9" t="n">
@@ -5375,10 +5335,10 @@
         <v>3.17</v>
       </c>
       <c r="AI63" s="10" t="n">
-        <v>3.52</v>
+        <v>3.79</v>
       </c>
       <c r="AJ63" s="10" t="n">
-        <v>3.23</v>
+        <v>3.49</v>
       </c>
       <c r="AK63" s="10" t="n"/>
     </row>
@@ -5396,7 +5356,7 @@
         </is>
       </c>
       <c r="B65" s="8" t="n">
-        <v>41747</v>
+        <v>42820</v>
       </c>
       <c r="C65" s="9" t="n"/>
       <c r="D65" s="9" t="n">
@@ -5412,10 +5372,10 @@
         <v>14.4</v>
       </c>
       <c r="H65" s="10" t="n">
-        <v>16.21</v>
+        <v>16.92</v>
       </c>
       <c r="I65" s="10" t="n">
-        <v>14.81</v>
+        <v>15.29</v>
       </c>
       <c r="J65" s="9" t="n"/>
       <c r="K65" s="9" t="n">
@@ -5446,10 +5406,10 @@
         <v>1.54</v>
       </c>
       <c r="V65" s="10" t="n">
-        <v>1.72</v>
+        <v>1.81</v>
       </c>
       <c r="W65" s="10" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="X65" s="11" t="n"/>
       <c r="Y65" s="11" t="n">
@@ -5465,10 +5425,10 @@
         <v>11.26</v>
       </c>
       <c r="AC65" s="12" t="n">
-        <v>10.93</v>
+        <v>11.04</v>
       </c>
       <c r="AD65" s="12" t="n">
-        <v>11.27</v>
+        <v>11.49</v>
       </c>
       <c r="AE65" s="9" t="n"/>
       <c r="AF65" s="9" t="n">
@@ -5484,10 +5444,10 @@
         <v>1.31</v>
       </c>
       <c r="AJ65" s="10" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AK65" s="10" t="n">
         <v>1.47</v>
-      </c>
-      <c r="AK65" s="10" t="n">
-        <v>1.42</v>
       </c>
     </row>
     <row r="66">
@@ -5497,7 +5457,7 @@
         </is>
       </c>
       <c r="B66" s="8" t="n">
-        <v>7804</v>
+        <v>7481</v>
       </c>
       <c r="C66" s="9" t="n"/>
       <c r="D66" s="9" t="n">
@@ -5513,10 +5473,10 @@
         <v>15.32</v>
       </c>
       <c r="H66" s="10" t="n">
-        <v>13.35</v>
+        <v>13.15</v>
       </c>
       <c r="I66" s="10" t="n">
-        <v>11.41</v>
+        <v>11.24</v>
       </c>
       <c r="J66" s="9" t="n"/>
       <c r="K66" s="9" t="n">
@@ -5547,10 +5507,10 @@
         <v>1.25</v>
       </c>
       <c r="V66" s="10" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="W66" s="10" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="X66" s="11" t="n"/>
       <c r="Y66" s="11" t="n">
@@ -5585,10 +5545,10 @@
         <v>0.8</v>
       </c>
       <c r="AJ66" s="10" t="n">
-        <v>0.82</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AK66" s="10" t="n">
-        <v>0.79</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="67">
@@ -5605,7 +5565,7 @@
         </is>
       </c>
       <c r="B68" s="8" t="n">
-        <v>71495</v>
+        <v>63743</v>
       </c>
       <c r="C68" s="9" t="n">
         <v>11.71</v>
@@ -5650,10 +5610,10 @@
         <v>3.37</v>
       </c>
       <c r="U68" s="10" t="n">
-        <v>3.44</v>
+        <v>3.18</v>
       </c>
       <c r="V68" s="10" t="n">
-        <v>3.04</v>
+        <v>2.8</v>
       </c>
       <c r="W68" s="10" t="n"/>
       <c r="X68" s="11" t="n">
@@ -5669,10 +5629,10 @@
         <v>18.5</v>
       </c>
       <c r="AB68" s="12" t="n">
-        <v>23.11</v>
+        <v>23.22</v>
       </c>
       <c r="AC68" s="12" t="n">
-        <v>24.12</v>
+        <v>24.39</v>
       </c>
       <c r="AD68" s="12" t="n"/>
       <c r="AE68" s="9" t="n">
@@ -5688,10 +5648,10 @@
         <v>1.26</v>
       </c>
       <c r="AI68" s="10" t="n">
-        <v>1.39</v>
+        <v>1.28</v>
       </c>
       <c r="AJ68" s="10" t="n">
-        <v>1.28</v>
+        <v>1.17</v>
       </c>
       <c r="AK68" s="10" t="n"/>
     </row>
@@ -5709,7 +5669,7 @@
         </is>
       </c>
       <c r="B70" s="8" t="n">
-        <v>27156</v>
+        <v>23992</v>
       </c>
       <c r="C70" s="9" t="n">
         <v>31.28</v>
@@ -5724,10 +5684,10 @@
         <v>23.11</v>
       </c>
       <c r="G70" s="10" t="n">
-        <v>16.93</v>
+        <v>14.97</v>
       </c>
       <c r="H70" s="10" t="n">
-        <v>13.05</v>
+        <v>11.54</v>
       </c>
       <c r="I70" s="10" t="n"/>
       <c r="J70" s="9" t="n">
@@ -5758,10 +5718,10 @@
         <v>2.2</v>
       </c>
       <c r="U70" s="10" t="n">
-        <v>1.9</v>
+        <v>1.68</v>
       </c>
       <c r="V70" s="10" t="n">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="W70" s="10" t="n"/>
       <c r="X70" s="11" t="n">
@@ -5796,10 +5756,10 @@
         <v>2.17</v>
       </c>
       <c r="AI70" s="10" t="n">
-        <v>1.75</v>
+        <v>1.54</v>
       </c>
       <c r="AJ70" s="10" t="n">
-        <v>1.54</v>
+        <v>1.36</v>
       </c>
       <c r="AK70" s="10" t="n"/>
     </row>
@@ -5810,7 +5770,7 @@
         </is>
       </c>
       <c r="B71" s="8" t="n">
-        <v>14144</v>
+        <v>12624</v>
       </c>
       <c r="C71" s="9" t="n">
         <v>13.89</v>
@@ -5825,10 +5785,10 @@
         <v>20.71</v>
       </c>
       <c r="G71" s="10" t="n">
-        <v>12.14</v>
+        <v>10.85</v>
       </c>
       <c r="H71" s="10" t="n">
-        <v>8.94</v>
+        <v>7.99</v>
       </c>
       <c r="I71" s="10" t="n"/>
       <c r="J71" s="9" t="n">
@@ -5859,10 +5819,10 @@
         <v>2.25</v>
       </c>
       <c r="U71" s="10" t="n">
-        <v>1.51</v>
+        <v>1.35</v>
       </c>
       <c r="V71" s="10" t="n">
-        <v>1.43</v>
+        <v>1.28</v>
       </c>
       <c r="W71" s="10" t="n"/>
       <c r="X71" s="11" t="n">
@@ -5897,10 +5857,10 @@
         <v>1.35</v>
       </c>
       <c r="AI71" s="10" t="n">
-        <v>0.83</v>
+        <v>0.74</v>
       </c>
       <c r="AJ71" s="10" t="n">
-        <v>0.72</v>
+        <v>0.65</v>
       </c>
       <c r="AK71" s="10" t="n"/>
     </row>
@@ -5924,10 +5884,10 @@
         <v>8.390000000000001</v>
       </c>
       <c r="G72" s="15" t="n">
-        <v>9.970000000000001</v>
+        <v>8.75</v>
       </c>
       <c r="H72" s="15" t="n">
-        <v>9.300000000000001</v>
+        <v>7.94</v>
       </c>
       <c r="I72" s="15" t="n"/>
       <c r="J72" s="15" t="n">
@@ -5958,10 +5918,10 @@
         <v>0.66</v>
       </c>
       <c r="U72" s="15" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="V72" s="15" t="n">
-        <v>0.74</v>
+        <v>0.66</v>
       </c>
       <c r="W72" s="15" t="n"/>
       <c r="X72" s="16" t="n">
@@ -5996,10 +5956,10 @@
         <v>0.53</v>
       </c>
       <c r="AI72" s="15" t="n">
-        <v>0.62</v>
+        <v>0.55</v>
       </c>
       <c r="AJ72" s="15" t="n">
-        <v>0.59</v>
+        <v>0.54</v>
       </c>
       <c r="AK72" s="15" t="n"/>
     </row>
@@ -6022,12 +5982,8 @@
       <c r="F73" s="15" t="n">
         <v>23.64</v>
       </c>
-      <c r="G73" s="15" t="n">
-        <v>30.09</v>
-      </c>
-      <c r="H73" s="15" t="n">
-        <v>22.55</v>
-      </c>
+      <c r="G73" s="15" t="n"/>
+      <c r="H73" s="15" t="n"/>
       <c r="I73" s="15" t="n"/>
       <c r="J73" s="15" t="n">
         <v>11.85</v>
@@ -6057,10 +6013,10 @@
         <v>5.25</v>
       </c>
       <c r="U73" s="15" t="n">
-        <v>5.85</v>
+        <v>6.11</v>
       </c>
       <c r="V73" s="15" t="n">
-        <v>4.92</v>
+        <v>5.13</v>
       </c>
       <c r="W73" s="15" t="n"/>
       <c r="X73" s="16" t="n">
@@ -6079,7 +6035,7 @@
         <v>24.09</v>
       </c>
       <c r="AC73" s="16" t="n">
-        <v>23.78</v>
+        <v>23.85</v>
       </c>
       <c r="AD73" s="16" t="n"/>
       <c r="AE73" s="15" t="n">
@@ -6095,10 +6051,10 @@
         <v>2.98</v>
       </c>
       <c r="AI73" s="15" t="n">
-        <v>3.98</v>
+        <v>4.14</v>
       </c>
       <c r="AJ73" s="15" t="n">
-        <v>3.67</v>
+        <v>3.81</v>
       </c>
       <c r="AK73" s="15" t="n"/>
     </row>
@@ -6123,10 +6079,10 @@
         <v>14.86</v>
       </c>
       <c r="H74" s="15" t="n">
-        <v>14.78</v>
+        <v>15.04</v>
       </c>
       <c r="I74" s="15" t="n">
-        <v>13.11</v>
+        <v>13.27</v>
       </c>
       <c r="J74" s="15" t="n"/>
       <c r="K74" s="15" t="n">
@@ -6157,10 +6113,10 @@
         <v>1.4</v>
       </c>
       <c r="V74" s="15" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W74" s="15" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="X74" s="16" t="n"/>
       <c r="Y74" s="16" t="n">
@@ -6176,10 +6132,10 @@
         <v>9.91</v>
       </c>
       <c r="AC74" s="16" t="n">
-        <v>10.33</v>
+        <v>10.38</v>
       </c>
       <c r="AD74" s="16" t="n">
-        <v>11.04</v>
+        <v>11.16</v>
       </c>
       <c r="AE74" s="15" t="n"/>
       <c r="AF74" s="15" t="n">
@@ -6195,10 +6151,10 @@
         <v>1.06</v>
       </c>
       <c r="AJ74" s="15" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AK74" s="15" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
     </row>
     <row r="75">
@@ -6251,10 +6207,10 @@
         <v>3.37</v>
       </c>
       <c r="U75" s="15" t="n">
-        <v>3.44</v>
+        <v>3.18</v>
       </c>
       <c r="V75" s="15" t="n">
-        <v>3.04</v>
+        <v>2.8</v>
       </c>
       <c r="W75" s="15" t="n"/>
       <c r="X75" s="16" t="n">
@@ -6270,10 +6226,10 @@
         <v>18.5</v>
       </c>
       <c r="AB75" s="16" t="n">
-        <v>23.11</v>
+        <v>23.22</v>
       </c>
       <c r="AC75" s="16" t="n">
-        <v>24.12</v>
+        <v>24.39</v>
       </c>
       <c r="AD75" s="16" t="n"/>
       <c r="AE75" s="15" t="n">
@@ -6289,10 +6245,10 @@
         <v>1.26</v>
       </c>
       <c r="AI75" s="15" t="n">
-        <v>1.39</v>
+        <v>1.28</v>
       </c>
       <c r="AJ75" s="15" t="n">
-        <v>1.28</v>
+        <v>1.17</v>
       </c>
       <c r="AK75" s="15" t="n"/>
     </row>
@@ -6316,10 +6272,10 @@
         <v>21.91</v>
       </c>
       <c r="G76" s="15" t="n">
-        <v>14.54</v>
+        <v>12.91</v>
       </c>
       <c r="H76" s="15" t="n">
-        <v>11</v>
+        <v>9.77</v>
       </c>
       <c r="I76" s="15" t="n"/>
       <c r="J76" s="15" t="n">
@@ -6350,10 +6306,10 @@
         <v>2.23</v>
       </c>
       <c r="U76" s="15" t="n">
-        <v>1.71</v>
+        <v>1.52</v>
       </c>
       <c r="V76" s="15" t="n">
-        <v>1.58</v>
+        <v>1.41</v>
       </c>
       <c r="W76" s="15" t="n"/>
       <c r="X76" s="16" t="n">
@@ -6388,10 +6344,10 @@
         <v>1.76</v>
       </c>
       <c r="AI76" s="15" t="n">
-        <v>1.29</v>
+        <v>1.14</v>
       </c>
       <c r="AJ76" s="15" t="n">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="AK76" s="15" t="n"/>
     </row>
@@ -6415,13 +6371,13 @@
         <v>18.97</v>
       </c>
       <c r="G77" s="15" t="n">
-        <v>15.32</v>
+        <v>10.85</v>
       </c>
       <c r="H77" s="15" t="n">
-        <v>13.35</v>
+        <v>8.83</v>
       </c>
       <c r="I77" s="15" t="n">
-        <v>13.11</v>
+        <v>13.27</v>
       </c>
       <c r="J77" s="15" t="n">
         <v>7.18</v>
@@ -6453,13 +6409,13 @@
         <v>1.48</v>
       </c>
       <c r="U77" s="15" t="n">
-        <v>1.99</v>
+        <v>2.01</v>
       </c>
       <c r="V77" s="15" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="W77" s="15" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="X77" s="16" t="n">
         <v>15.47</v>
@@ -6480,7 +6436,7 @@
         <v>15.14</v>
       </c>
       <c r="AD77" s="16" t="n">
-        <v>11.04</v>
+        <v>11.16</v>
       </c>
       <c r="AE77" s="15" t="n">
         <v>0.64</v>
@@ -6495,13 +6451,13 @@
         <v>0.97</v>
       </c>
       <c r="AI77" s="15" t="n">
-        <v>1.11</v>
+        <v>1.23</v>
       </c>
       <c r="AJ77" s="15" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="AK77" s="15" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
     </row>
   </sheetData>
@@ -6624,7 +6580,7 @@
         </is>
       </c>
       <c r="E2" s="7" t="n">
-        <v>37480</v>
+        <v>33297</v>
       </c>
       <c r="F2" s="9" t="n"/>
       <c r="G2" s="9" t="n">
@@ -6637,10 +6593,10 @@
         <v>37.73</v>
       </c>
       <c r="J2" s="9" t="n">
-        <v>15.36</v>
+        <v>13.72</v>
       </c>
       <c r="K2" s="9" t="n">
-        <v>13.42</v>
+        <v>11.82</v>
       </c>
       <c r="L2" s="9" t="n"/>
     </row>
@@ -6666,7 +6622,7 @@
         </is>
       </c>
       <c r="E3" s="7" t="n">
-        <v>19558</v>
+        <v>17984</v>
       </c>
       <c r="F3" s="9" t="n"/>
       <c r="G3" s="9" t="n">
@@ -6679,10 +6635,10 @@
         <v>27.94</v>
       </c>
       <c r="J3" s="9" t="n">
-        <v>13.87</v>
+        <v>12.59</v>
       </c>
       <c r="K3" s="9" t="n">
-        <v>13.31</v>
+        <v>12.36</v>
       </c>
       <c r="L3" s="9" t="n"/>
     </row>
@@ -6708,7 +6664,7 @@
         </is>
       </c>
       <c r="E4" s="7" t="n">
-        <v>13630</v>
+        <v>12699</v>
       </c>
       <c r="F4" s="9" t="n"/>
       <c r="G4" s="9" t="n"/>
@@ -6719,10 +6675,10 @@
         <v>37.73</v>
       </c>
       <c r="J4" s="9" t="n">
-        <v>18.07</v>
+        <v>17.04</v>
       </c>
       <c r="K4" s="9" t="n">
-        <v>12.56</v>
+        <v>11.74</v>
       </c>
       <c r="L4" s="9" t="n"/>
     </row>
@@ -6748,7 +6704,7 @@
         </is>
       </c>
       <c r="E5" s="7" t="n">
-        <v>19273</v>
+        <v>17172</v>
       </c>
       <c r="F5" s="9" t="n"/>
       <c r="G5" s="9" t="n">
@@ -6761,10 +6717,10 @@
         <v>13.27</v>
       </c>
       <c r="J5" s="9" t="n">
-        <v>7.06</v>
+        <v>6.23</v>
       </c>
       <c r="K5" s="9" t="n">
-        <v>6.08</v>
+        <v>5.28</v>
       </c>
       <c r="L5" s="9" t="n"/>
     </row>
@@ -6790,7 +6746,7 @@
         </is>
       </c>
       <c r="E6" s="7" t="n">
-        <v>1349</v>
+        <v>1306</v>
       </c>
       <c r="F6" s="9" t="n"/>
       <c r="G6" s="9" t="n"/>
@@ -6799,10 +6755,10 @@
         <v>10.3</v>
       </c>
       <c r="J6" s="9" t="n">
-        <v>6.46</v>
+        <v>5.99</v>
       </c>
       <c r="K6" s="9" t="n">
-        <v>6.17</v>
+        <v>5.87</v>
       </c>
       <c r="L6" s="9" t="n"/>
     </row>
@@ -6828,7 +6784,7 @@
         </is>
       </c>
       <c r="E7" s="7" t="n">
-        <v>1077</v>
+        <v>1030</v>
       </c>
       <c r="F7" s="9" t="n"/>
       <c r="G7" s="9" t="n"/>
@@ -6864,7 +6820,7 @@
         </is>
       </c>
       <c r="E8" s="7" t="n">
-        <v>5195</v>
+        <v>4907</v>
       </c>
       <c r="F8" s="9" t="n"/>
       <c r="G8" s="9" t="n"/>
@@ -6900,7 +6856,7 @@
         </is>
       </c>
       <c r="E9" s="7" t="n">
-        <v>8257</v>
+        <v>7797</v>
       </c>
       <c r="F9" s="9" t="n"/>
       <c r="G9" s="9" t="n"/>
@@ -6911,10 +6867,10 @@
         <v>32.18</v>
       </c>
       <c r="J9" s="9" t="n">
-        <v>31.91</v>
+        <v>30.11</v>
       </c>
       <c r="K9" s="9" t="n">
-        <v>26.15</v>
+        <v>25.02</v>
       </c>
       <c r="L9" s="9" t="n"/>
     </row>
@@ -6940,7 +6896,7 @@
         </is>
       </c>
       <c r="E10" s="7" t="n">
-        <v>1328</v>
+        <v>1241</v>
       </c>
       <c r="F10" s="9" t="n">
         <v>14.21</v>
@@ -6955,10 +6911,10 @@
         <v>18.39</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>13.36</v>
+        <v>13.06</v>
       </c>
       <c r="K10" s="9" t="n">
-        <v>9.640000000000001</v>
+        <v>9.17</v>
       </c>
       <c r="L10" s="9" t="n"/>
     </row>
@@ -6984,7 +6940,7 @@
         </is>
       </c>
       <c r="E11" s="7" t="n">
-        <v>3129</v>
+        <v>3020</v>
       </c>
       <c r="F11" s="9" t="n"/>
       <c r="G11" s="9" t="n"/>
@@ -6995,10 +6951,10 @@
         <v>20.62</v>
       </c>
       <c r="J11" s="9" t="n">
-        <v>22.04</v>
+        <v>20.57</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>14.44</v>
+        <v>14.01</v>
       </c>
       <c r="L11" s="9" t="n"/>
     </row>
@@ -7024,7 +6980,7 @@
         </is>
       </c>
       <c r="E12" s="7" t="n">
-        <v>815</v>
+        <v>771</v>
       </c>
       <c r="F12" s="9" t="n">
         <v>23.46</v>
@@ -7037,10 +6993,10 @@
         <v>14.78</v>
       </c>
       <c r="J12" s="9" t="n">
-        <v>9.07</v>
+        <v>8.67</v>
       </c>
       <c r="K12" s="9" t="n">
-        <v>7.7</v>
+        <v>7.3</v>
       </c>
       <c r="L12" s="9" t="n"/>
     </row>
@@ -7066,7 +7022,7 @@
         </is>
       </c>
       <c r="E13" s="7" t="n">
-        <v>375</v>
+        <v>365</v>
       </c>
       <c r="F13" s="9" t="n">
         <v>37.11</v>
@@ -7081,10 +7037,10 @@
         <v>13.58</v>
       </c>
       <c r="J13" s="9" t="n">
-        <v>6.88</v>
+        <v>6.7</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>5.79</v>
+        <v>5.64</v>
       </c>
       <c r="L13" s="9" t="n"/>
     </row>
@@ -7110,7 +7066,7 @@
         </is>
       </c>
       <c r="E14" s="7" t="n">
-        <v>9485</v>
+        <v>9693</v>
       </c>
       <c r="F14" s="9" t="n">
         <v>41.88</v>
@@ -7125,10 +7081,10 @@
         <v>59.99</v>
       </c>
       <c r="J14" s="9" t="n">
-        <v>55.63</v>
+        <v>52.13</v>
       </c>
       <c r="K14" s="9" t="n">
-        <v>28.85</v>
+        <v>29.35</v>
       </c>
       <c r="L14" s="9" t="n"/>
     </row>
@@ -7154,7 +7110,7 @@
         </is>
       </c>
       <c r="E15" s="7" t="n">
-        <v>41472</v>
+        <v>41082</v>
       </c>
       <c r="F15" s="9" t="n">
         <v>19.31</v>
@@ -7169,10 +7125,10 @@
         <v>34.46</v>
       </c>
       <c r="J15" s="9" t="n">
-        <v>22.44</v>
+        <v>22.4</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>18.22</v>
+        <v>18.02</v>
       </c>
       <c r="L15" s="9" t="n"/>
     </row>
@@ -7198,7 +7154,7 @@
         </is>
       </c>
       <c r="E16" s="7" t="n">
-        <v>11044</v>
+        <v>12399</v>
       </c>
       <c r="F16" s="9" t="n">
         <v>16.34</v>
@@ -7213,10 +7169,10 @@
         <v>36.3</v>
       </c>
       <c r="J16" s="9" t="n">
-        <v>40.52</v>
+        <v>45.66</v>
       </c>
       <c r="K16" s="9" t="n">
-        <v>28.13</v>
+        <v>31.53</v>
       </c>
       <c r="L16" s="9" t="n"/>
     </row>
@@ -7242,7 +7198,7 @@
         </is>
       </c>
       <c r="E17" s="7" t="n">
-        <v>9886</v>
+        <v>11547</v>
       </c>
       <c r="F17" s="9" t="n"/>
       <c r="G17" s="9" t="n">
@@ -7255,10 +7211,10 @@
         <v>41.99</v>
       </c>
       <c r="J17" s="9" t="n">
-        <v>89.69</v>
+        <v>80.54000000000001</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>30.44</v>
+        <v>35.85</v>
       </c>
       <c r="L17" s="9" t="n"/>
     </row>
@@ -7284,7 +7240,7 @@
         </is>
       </c>
       <c r="E18" s="7" t="n">
-        <v>10100</v>
+        <v>9471</v>
       </c>
       <c r="F18" s="9" t="n">
         <v>15.67</v>
@@ -7299,10 +7255,10 @@
         <v>26.64</v>
       </c>
       <c r="J18" s="9" t="n">
-        <v>15.43</v>
+        <v>14.51</v>
       </c>
       <c r="K18" s="9" t="n">
-        <v>11.18</v>
+        <v>10.61</v>
       </c>
       <c r="L18" s="9" t="n"/>
     </row>
@@ -7328,7 +7284,7 @@
         </is>
       </c>
       <c r="E19" s="7" t="n">
-        <v>120040</v>
+        <v>116644</v>
       </c>
       <c r="F19" s="9" t="n">
         <v>21.56</v>
@@ -7342,12 +7298,8 @@
       <c r="I19" s="9" t="n">
         <v>22.08</v>
       </c>
-      <c r="J19" s="9" t="n">
-        <v>17.21</v>
-      </c>
-      <c r="K19" s="9" t="n">
-        <v>16.02</v>
-      </c>
+      <c r="J19" s="9" t="n"/>
+      <c r="K19" s="9" t="n"/>
       <c r="L19" s="9" t="n"/>
     </row>
     <row r="20">
@@ -7372,7 +7324,7 @@
         </is>
       </c>
       <c r="E20" s="7" t="n">
-        <v>73692</v>
+        <v>67906</v>
       </c>
       <c r="F20" s="9" t="n">
         <v>17.07</v>
@@ -7386,12 +7338,8 @@
       <c r="I20" s="9" t="n">
         <v>19.36</v>
       </c>
-      <c r="J20" s="9" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="K20" s="9" t="n">
-        <v>17.05</v>
-      </c>
+      <c r="J20" s="9" t="n"/>
+      <c r="K20" s="9" t="n"/>
       <c r="L20" s="9" t="n"/>
     </row>
     <row r="21">
@@ -7416,7 +7364,7 @@
         </is>
       </c>
       <c r="E21" s="7" t="n">
-        <v>96232</v>
+        <v>89308</v>
       </c>
       <c r="F21" s="9" t="n">
         <v>20.08</v>
@@ -7430,12 +7378,8 @@
       <c r="I21" s="9" t="n">
         <v>21.62</v>
       </c>
-      <c r="J21" s="9" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="K21" s="9" t="n">
-        <v>19.12</v>
-      </c>
+      <c r="J21" s="9" t="n"/>
+      <c r="K21" s="9" t="n"/>
       <c r="L21" s="9" t="n"/>
     </row>
     <row r="22">
@@ -7460,7 +7404,7 @@
         </is>
       </c>
       <c r="E22" s="7" t="n">
-        <v>265343</v>
+        <v>248904</v>
       </c>
       <c r="F22" s="9" t="n">
         <v>28.47</v>
@@ -7474,12 +7418,8 @@
       <c r="I22" s="9" t="n">
         <v>36.57</v>
       </c>
-      <c r="J22" s="9" t="n">
-        <v>27.29</v>
-      </c>
-      <c r="K22" s="9" t="n">
-        <v>25.16</v>
-      </c>
+      <c r="J22" s="9" t="n"/>
+      <c r="K22" s="9" t="n"/>
       <c r="L22" s="9" t="n"/>
     </row>
     <row r="23">
@@ -7504,7 +7444,7 @@
         </is>
       </c>
       <c r="E23" s="7" t="n">
-        <v>10975</v>
+        <v>10582</v>
       </c>
       <c r="F23" s="9" t="n">
         <v>15.9</v>
@@ -7518,12 +7458,8 @@
       <c r="I23" s="9" t="n">
         <v>22.06</v>
       </c>
-      <c r="J23" s="9" t="n">
-        <v>15.11</v>
-      </c>
-      <c r="K23" s="9" t="n">
-        <v>13.42</v>
-      </c>
+      <c r="J23" s="9" t="n"/>
+      <c r="K23" s="9" t="n"/>
       <c r="L23" s="9" t="n"/>
     </row>
     <row r="24">
@@ -7548,7 +7484,7 @@
         </is>
       </c>
       <c r="E24" s="7" t="n">
-        <v>53637</v>
+        <v>50272</v>
       </c>
       <c r="F24" s="9" t="n">
         <v>17.03</v>
@@ -7588,7 +7524,7 @@
         </is>
       </c>
       <c r="E25" s="7" t="n">
-        <v>752</v>
+        <v>745</v>
       </c>
       <c r="F25" s="9" t="n">
         <v>16.56</v>
@@ -7628,7 +7564,7 @@
         </is>
       </c>
       <c r="E26" s="7" t="n">
-        <v>33466</v>
+        <v>30776</v>
       </c>
       <c r="F26" s="9" t="n">
         <v>5</v>
@@ -7668,7 +7604,7 @@
         </is>
       </c>
       <c r="E27" s="7" t="n">
-        <v>31792</v>
+        <v>32858</v>
       </c>
       <c r="F27" s="9" t="n">
         <v>24.79</v>
@@ -7708,7 +7644,7 @@
         </is>
       </c>
       <c r="E28" s="7" t="n">
-        <v>5097</v>
+        <v>4213</v>
       </c>
       <c r="F28" s="9" t="n">
         <v>10.61</v>
@@ -7723,10 +7659,10 @@
         <v>47.5</v>
       </c>
       <c r="J28" s="9" t="n">
-        <v>10.58</v>
+        <v>8.75</v>
       </c>
       <c r="K28" s="9" t="n">
-        <v>9.6</v>
+        <v>7.94</v>
       </c>
       <c r="L28" s="9" t="n"/>
     </row>
@@ -7752,7 +7688,7 @@
         </is>
       </c>
       <c r="E29" s="7" t="n">
-        <v>4397</v>
+        <v>3935</v>
       </c>
       <c r="F29" s="9" t="n">
         <v>5.38</v>
@@ -7767,10 +7703,10 @@
         <v>13.73</v>
       </c>
       <c r="J29" s="9" t="n">
-        <v>9.970000000000001</v>
+        <v>9.02</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>9.300000000000001</v>
+        <v>8.83</v>
       </c>
       <c r="L29" s="9" t="n"/>
     </row>
@@ -7796,7 +7732,7 @@
         </is>
       </c>
       <c r="E30" s="7" t="n">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="F30" s="9" t="n">
         <v>7.23</v>
@@ -7832,7 +7768,7 @@
         </is>
       </c>
       <c r="E31" s="7" t="n">
-        <v>380870</v>
+        <v>388618</v>
       </c>
       <c r="F31" s="9" t="n">
         <v>18.45</v>
@@ -7846,12 +7782,8 @@
       <c r="I31" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="J31" s="9" t="n">
-        <v>30.11</v>
-      </c>
-      <c r="K31" s="9" t="n">
-        <v>25.28</v>
-      </c>
+      <c r="J31" s="9" t="n"/>
+      <c r="K31" s="9" t="n"/>
       <c r="L31" s="9" t="n"/>
     </row>
     <row r="32">
@@ -7876,7 +7808,7 @@
         </is>
       </c>
       <c r="E32" s="7" t="n">
-        <v>182688</v>
+        <v>185233</v>
       </c>
       <c r="F32" s="9" t="n">
         <v>16.58</v>
@@ -7890,12 +7822,8 @@
       <c r="I32" s="9" t="n">
         <v>24.83</v>
       </c>
-      <c r="J32" s="9" t="n">
-        <v>37.27</v>
-      </c>
-      <c r="K32" s="9" t="n">
-        <v>29.81</v>
-      </c>
+      <c r="J32" s="9" t="n"/>
+      <c r="K32" s="9" t="n"/>
       <c r="L32" s="9" t="n"/>
     </row>
     <row r="33">
@@ -7920,7 +7848,7 @@
         </is>
       </c>
       <c r="E33" s="7" t="n">
-        <v>16867</v>
+        <v>21662</v>
       </c>
       <c r="F33" s="9" t="n">
         <v>10.64</v>
@@ -7934,12 +7862,8 @@
       <c r="I33" s="9" t="n">
         <v>22.45</v>
       </c>
-      <c r="J33" s="9" t="n">
-        <v>30.06</v>
-      </c>
-      <c r="K33" s="9" t="n">
-        <v>19.82</v>
-      </c>
+      <c r="J33" s="9" t="n"/>
+      <c r="K33" s="9" t="n"/>
       <c r="L33" s="9" t="n"/>
     </row>
     <row r="34">
@@ -7964,7 +7888,7 @@
         </is>
       </c>
       <c r="E34" s="7" t="n">
-        <v>41747</v>
+        <v>42820</v>
       </c>
       <c r="F34" s="9" t="n"/>
       <c r="G34" s="9" t="n">
@@ -7980,10 +7904,10 @@
         <v>14.4</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>16.21</v>
+        <v>16.92</v>
       </c>
       <c r="L34" s="9" t="n">
-        <v>14.81</v>
+        <v>15.29</v>
       </c>
     </row>
     <row r="35">
@@ -8008,7 +7932,7 @@
         </is>
       </c>
       <c r="E35" s="7" t="n">
-        <v>7804</v>
+        <v>7481</v>
       </c>
       <c r="F35" s="9" t="n"/>
       <c r="G35" s="9" t="n">
@@ -8024,10 +7948,10 @@
         <v>15.32</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>13.35</v>
+        <v>13.15</v>
       </c>
       <c r="L35" s="9" t="n">
-        <v>11.41</v>
+        <v>11.24</v>
       </c>
     </row>
     <row r="36">
@@ -8052,7 +7976,7 @@
         </is>
       </c>
       <c r="E36" s="7" t="n">
-        <v>71495</v>
+        <v>63743</v>
       </c>
       <c r="F36" s="9" t="n">
         <v>11.71</v>
@@ -8092,7 +8016,7 @@
         </is>
       </c>
       <c r="E37" s="7" t="n">
-        <v>27156</v>
+        <v>23992</v>
       </c>
       <c r="F37" s="9" t="n">
         <v>31.28</v>
@@ -8107,10 +8031,10 @@
         <v>23.11</v>
       </c>
       <c r="J37" s="9" t="n">
-        <v>16.93</v>
+        <v>14.97</v>
       </c>
       <c r="K37" s="9" t="n">
-        <v>13.05</v>
+        <v>11.54</v>
       </c>
       <c r="L37" s="9" t="n"/>
     </row>
@@ -8136,7 +8060,7 @@
         </is>
       </c>
       <c r="E38" s="7" t="n">
-        <v>14144</v>
+        <v>12624</v>
       </c>
       <c r="F38" s="9" t="n">
         <v>13.89</v>
@@ -8151,10 +8075,10 @@
         <v>20.71</v>
       </c>
       <c r="J38" s="9" t="n">
-        <v>12.14</v>
+        <v>10.85</v>
       </c>
       <c r="K38" s="9" t="n">
-        <v>8.94</v>
+        <v>7.99</v>
       </c>
       <c r="L38" s="9" t="n"/>
     </row>
@@ -8180,7 +8104,7 @@
         </is>
       </c>
       <c r="E39" s="7" t="n">
-        <v>192</v>
+        <v>172</v>
       </c>
       <c r="F39" s="9" t="n">
         <v>5.78</v>
@@ -8195,10 +8119,10 @@
         <v>8.390000000000001</v>
       </c>
       <c r="J39" s="9" t="n">
-        <v>7.34</v>
+        <v>6.6</v>
       </c>
       <c r="K39" s="9" t="n">
-        <v>6.03</v>
+        <v>5.42</v>
       </c>
       <c r="L39" s="9" t="n"/>
     </row>
@@ -8224,7 +8148,7 @@
         </is>
       </c>
       <c r="E40" s="7" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F40" s="9" t="n">
         <v>7.57</v>
@@ -8264,7 +8188,7 @@
         </is>
       </c>
       <c r="E41" s="7" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F41" s="9" t="n">
         <v>5.71</v>
@@ -8304,7 +8228,7 @@
         </is>
       </c>
       <c r="E42" s="7" t="n">
-        <v>62409</v>
+        <v>67287</v>
       </c>
       <c r="F42" s="9" t="n">
         <v>11.71</v>
@@ -8318,12 +8242,8 @@
       <c r="I42" s="9" t="n">
         <v>20.48</v>
       </c>
-      <c r="J42" s="9" t="n">
-        <v>20.07</v>
-      </c>
-      <c r="K42" s="9" t="n">
-        <v>17.26</v>
-      </c>
+      <c r="J42" s="9" t="n"/>
+      <c r="K42" s="9" t="n"/>
       <c r="L42" s="9" t="n"/>
     </row>
   </sheetData>
@@ -8438,7 +8358,7 @@
         </is>
       </c>
       <c r="E2" s="7" t="n">
-        <v>37480</v>
+        <v>33297</v>
       </c>
       <c r="F2" s="9" t="n"/>
       <c r="G2" s="9" t="n">
@@ -8476,7 +8396,7 @@
         </is>
       </c>
       <c r="E3" s="7" t="n">
-        <v>19558</v>
+        <v>17984</v>
       </c>
       <c r="F3" s="9" t="n"/>
       <c r="G3" s="9" t="n">
@@ -8514,7 +8434,7 @@
         </is>
       </c>
       <c r="E4" s="7" t="n">
-        <v>13630</v>
+        <v>12699</v>
       </c>
       <c r="F4" s="9" t="n"/>
       <c r="G4" s="9" t="n">
@@ -8552,7 +8472,7 @@
         </is>
       </c>
       <c r="E5" s="7" t="n">
-        <v>19273</v>
+        <v>17172</v>
       </c>
       <c r="F5" s="9" t="n">
         <v>40.3</v>
@@ -8592,7 +8512,7 @@
         </is>
       </c>
       <c r="E6" s="7" t="n">
-        <v>1349</v>
+        <v>1306</v>
       </c>
       <c r="F6" s="9" t="n"/>
       <c r="G6" s="9" t="n"/>
@@ -8626,7 +8546,7 @@
         </is>
       </c>
       <c r="E7" s="7" t="n">
-        <v>1077</v>
+        <v>1030</v>
       </c>
       <c r="F7" s="9" t="n">
         <v>87.52</v>
@@ -8664,7 +8584,7 @@
         </is>
       </c>
       <c r="E8" s="7" t="n">
-        <v>5195</v>
+        <v>4907</v>
       </c>
       <c r="F8" s="9" t="n">
         <v>991.9299999999999</v>
@@ -8704,7 +8624,7 @@
         </is>
       </c>
       <c r="E9" s="7" t="n">
-        <v>8257</v>
+        <v>7797</v>
       </c>
       <c r="F9" s="9" t="n"/>
       <c r="G9" s="9" t="n"/>
@@ -8740,7 +8660,7 @@
         </is>
       </c>
       <c r="E10" s="7" t="n">
-        <v>1328</v>
+        <v>1241</v>
       </c>
       <c r="F10" s="9" t="n">
         <v>11.7</v>
@@ -8780,7 +8700,7 @@
         </is>
       </c>
       <c r="E11" s="7" t="n">
-        <v>3129</v>
+        <v>3020</v>
       </c>
       <c r="F11" s="9" t="n"/>
       <c r="G11" s="9" t="n">
@@ -8818,7 +8738,7 @@
         </is>
       </c>
       <c r="E12" s="7" t="n">
-        <v>815</v>
+        <v>771</v>
       </c>
       <c r="F12" s="9" t="n">
         <v>11.21</v>
@@ -8858,7 +8778,7 @@
         </is>
       </c>
       <c r="E13" s="7" t="n">
-        <v>375</v>
+        <v>365</v>
       </c>
       <c r="F13" s="9" t="n">
         <v>15.59</v>
@@ -8898,7 +8818,7 @@
         </is>
       </c>
       <c r="E14" s="7" t="n">
-        <v>9485</v>
+        <v>9693</v>
       </c>
       <c r="F14" s="9" t="n">
         <v>14.66</v>
@@ -8938,7 +8858,7 @@
         </is>
       </c>
       <c r="E15" s="7" t="n">
-        <v>41472</v>
+        <v>41082</v>
       </c>
       <c r="F15" s="9" t="n">
         <v>7.97</v>
@@ -8978,7 +8898,7 @@
         </is>
       </c>
       <c r="E16" s="7" t="n">
-        <v>11044</v>
+        <v>12399</v>
       </c>
       <c r="F16" s="9" t="n">
         <v>9.449999999999999</v>
@@ -9018,7 +8938,7 @@
         </is>
       </c>
       <c r="E17" s="7" t="n">
-        <v>9886</v>
+        <v>11547</v>
       </c>
       <c r="F17" s="9" t="n">
         <v>13.88</v>
@@ -9058,7 +8978,7 @@
         </is>
       </c>
       <c r="E18" s="7" t="n">
-        <v>10100</v>
+        <v>9471</v>
       </c>
       <c r="F18" s="9" t="n">
         <v>20.45</v>
@@ -9098,7 +9018,7 @@
         </is>
       </c>
       <c r="E19" s="7" t="n">
-        <v>120040</v>
+        <v>116644</v>
       </c>
       <c r="F19" s="9" t="n">
         <v>15.68</v>
@@ -9138,7 +9058,7 @@
         </is>
       </c>
       <c r="E20" s="7" t="n">
-        <v>73692</v>
+        <v>67906</v>
       </c>
       <c r="F20" s="9" t="n">
         <v>12.31</v>
@@ -9178,7 +9098,7 @@
         </is>
       </c>
       <c r="E21" s="7" t="n">
-        <v>96232</v>
+        <v>89308</v>
       </c>
       <c r="F21" s="9" t="n">
         <v>14.87</v>
@@ -9218,7 +9138,7 @@
         </is>
       </c>
       <c r="E22" s="7" t="n">
-        <v>265343</v>
+        <v>248904</v>
       </c>
       <c r="F22" s="9" t="n">
         <v>15.21</v>
@@ -9258,7 +9178,7 @@
         </is>
       </c>
       <c r="E23" s="7" t="n">
-        <v>10975</v>
+        <v>10582</v>
       </c>
       <c r="F23" s="9" t="n">
         <v>10.08</v>
@@ -9298,7 +9218,7 @@
         </is>
       </c>
       <c r="E24" s="7" t="n">
-        <v>53637</v>
+        <v>50272</v>
       </c>
       <c r="F24" s="9" t="n">
         <v>8.5</v>
@@ -9338,7 +9258,7 @@
         </is>
       </c>
       <c r="E25" s="7" t="n">
-        <v>752</v>
+        <v>745</v>
       </c>
       <c r="F25" s="9" t="n">
         <v>9.84</v>
@@ -9378,7 +9298,7 @@
         </is>
       </c>
       <c r="E26" s="7" t="n">
-        <v>33466</v>
+        <v>30776</v>
       </c>
       <c r="F26" s="9" t="n">
         <v>4.69</v>
@@ -9418,7 +9338,7 @@
         </is>
       </c>
       <c r="E27" s="7" t="n">
-        <v>31792</v>
+        <v>32858</v>
       </c>
       <c r="F27" s="9" t="n">
         <v>11.71</v>
@@ -9458,7 +9378,7 @@
         </is>
       </c>
       <c r="E28" s="7" t="n">
-        <v>5097</v>
+        <v>4213</v>
       </c>
       <c r="F28" s="9" t="n">
         <v>7.18</v>
@@ -9498,7 +9418,7 @@
         </is>
       </c>
       <c r="E29" s="7" t="n">
-        <v>4397</v>
+        <v>3935</v>
       </c>
       <c r="F29" s="9" t="n">
         <v>3.59</v>
@@ -9538,7 +9458,7 @@
         </is>
       </c>
       <c r="E30" s="7" t="n">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="F30" s="9" t="n">
         <v>6.74</v>
@@ -9578,7 +9498,7 @@
         </is>
       </c>
       <c r="E31" s="7" t="n">
-        <v>380870</v>
+        <v>388618</v>
       </c>
       <c r="F31" s="9" t="n">
         <v>13.46</v>
@@ -9618,7 +9538,7 @@
         </is>
       </c>
       <c r="E32" s="7" t="n">
-        <v>182688</v>
+        <v>185233</v>
       </c>
       <c r="F32" s="9" t="n">
         <v>13.71</v>
@@ -9658,7 +9578,7 @@
         </is>
       </c>
       <c r="E33" s="7" t="n">
-        <v>16867</v>
+        <v>21662</v>
       </c>
       <c r="F33" s="9" t="n">
         <v>10.23</v>
@@ -9698,7 +9618,7 @@
         </is>
       </c>
       <c r="E34" s="7" t="n">
-        <v>41747</v>
+        <v>42820</v>
       </c>
       <c r="F34" s="9" t="n"/>
       <c r="G34" s="9" t="n">
@@ -9738,7 +9658,7 @@
         </is>
       </c>
       <c r="E35" s="7" t="n">
-        <v>7804</v>
+        <v>7481</v>
       </c>
       <c r="F35" s="9" t="n"/>
       <c r="G35" s="9" t="n">
@@ -9778,7 +9698,7 @@
         </is>
       </c>
       <c r="E36" s="7" t="n">
-        <v>71495</v>
+        <v>63743</v>
       </c>
       <c r="F36" s="9" t="n">
         <v>7.78</v>
@@ -9818,7 +9738,7 @@
         </is>
       </c>
       <c r="E37" s="7" t="n">
-        <v>27156</v>
+        <v>23992</v>
       </c>
       <c r="F37" s="9" t="n">
         <v>18.39</v>
@@ -9858,7 +9778,7 @@
         </is>
       </c>
       <c r="E38" s="7" t="n">
-        <v>14144</v>
+        <v>12624</v>
       </c>
       <c r="F38" s="9" t="n">
         <v>7.78</v>
@@ -9898,7 +9818,7 @@
         </is>
       </c>
       <c r="E39" s="7" t="n">
-        <v>192</v>
+        <v>172</v>
       </c>
       <c r="F39" s="9" t="n">
         <v>3.96</v>
@@ -9938,7 +9858,7 @@
         </is>
       </c>
       <c r="E40" s="7" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F40" s="9" t="n">
         <v>2.92</v>
@@ -9978,7 +9898,7 @@
         </is>
       </c>
       <c r="E41" s="7" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F41" s="9" t="n">
         <v>3</v>
@@ -10018,7 +9938,7 @@
         </is>
       </c>
       <c r="E42" s="7" t="n">
-        <v>62409</v>
+        <v>67287</v>
       </c>
       <c r="F42" s="9" t="n">
         <v>6.73</v>
@@ -10148,7 +10068,7 @@
         </is>
       </c>
       <c r="E2" s="7" t="n">
-        <v>37480</v>
+        <v>33297</v>
       </c>
       <c r="F2" s="9" t="n">
         <v>1.95</v>
@@ -10163,10 +10083,10 @@
         <v>5.72</v>
       </c>
       <c r="J2" s="9" t="n">
-        <v>4.15</v>
+        <v>3.7</v>
       </c>
       <c r="K2" s="9" t="n">
-        <v>3.3</v>
+        <v>2.93</v>
       </c>
       <c r="L2" s="9" t="n"/>
     </row>
@@ -10192,7 +10112,7 @@
         </is>
       </c>
       <c r="E3" s="7" t="n">
-        <v>19558</v>
+        <v>17984</v>
       </c>
       <c r="F3" s="9" t="n">
         <v>2.73</v>
@@ -10207,10 +10127,10 @@
         <v>5.64</v>
       </c>
       <c r="J3" s="9" t="n">
-        <v>3.25</v>
+        <v>2.99</v>
       </c>
       <c r="K3" s="9" t="n">
-        <v>2.61</v>
+        <v>2.4</v>
       </c>
       <c r="L3" s="9" t="n"/>
     </row>
@@ -10236,7 +10156,7 @@
         </is>
       </c>
       <c r="E4" s="7" t="n">
-        <v>13630</v>
+        <v>12699</v>
       </c>
       <c r="F4" s="9" t="n">
         <v>1.21</v>
@@ -10251,10 +10171,10 @@
         <v>4.96</v>
       </c>
       <c r="J4" s="9" t="n">
-        <v>3.54</v>
+        <v>3.31</v>
       </c>
       <c r="K4" s="9" t="n">
-        <v>2.76</v>
+        <v>2.58</v>
       </c>
       <c r="L4" s="9" t="n"/>
     </row>
@@ -10280,7 +10200,7 @@
         </is>
       </c>
       <c r="E5" s="7" t="n">
-        <v>19273</v>
+        <v>17172</v>
       </c>
       <c r="F5" s="9" t="n">
         <v>0.51</v>
@@ -10295,10 +10215,10 @@
         <v>2.17</v>
       </c>
       <c r="J5" s="9" t="n">
-        <v>1.59</v>
+        <v>1.41</v>
       </c>
       <c r="K5" s="9" t="n">
-        <v>1.31</v>
+        <v>1.16</v>
       </c>
       <c r="L5" s="9" t="n"/>
     </row>
@@ -10324,7 +10244,7 @@
         </is>
       </c>
       <c r="E6" s="7" t="n">
-        <v>1349</v>
+        <v>1306</v>
       </c>
       <c r="F6" s="9" t="n"/>
       <c r="G6" s="9" t="n"/>
@@ -10333,10 +10253,10 @@
         <v>2.35</v>
       </c>
       <c r="J6" s="9" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="K6" s="9" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="L6" s="9" t="n"/>
     </row>
@@ -10362,7 +10282,7 @@
         </is>
       </c>
       <c r="E7" s="7" t="n">
-        <v>1077</v>
+        <v>1030</v>
       </c>
       <c r="F7" s="9" t="n">
         <v>0.85</v>
@@ -10402,7 +10322,7 @@
         </is>
       </c>
       <c r="E8" s="7" t="n">
-        <v>5195</v>
+        <v>4907</v>
       </c>
       <c r="F8" s="9" t="n">
         <v>1.54</v>
@@ -10417,10 +10337,10 @@
         <v>5.43</v>
       </c>
       <c r="J8" s="9" t="n">
-        <v>3.8</v>
+        <v>3.71</v>
       </c>
       <c r="K8" s="9" t="n">
-        <v>3.11</v>
+        <v>3.02</v>
       </c>
       <c r="L8" s="9" t="n"/>
     </row>
@@ -10446,7 +10366,7 @@
         </is>
       </c>
       <c r="E9" s="7" t="n">
-        <v>8257</v>
+        <v>7797</v>
       </c>
       <c r="F9" s="9" t="n"/>
       <c r="G9" s="9" t="n"/>
@@ -10457,10 +10377,10 @@
         <v>10.52</v>
       </c>
       <c r="J9" s="9" t="n">
-        <v>10.95</v>
+        <v>10.35</v>
       </c>
       <c r="K9" s="9" t="n">
-        <v>8.94</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="L9" s="9" t="n"/>
     </row>
@@ -10486,7 +10406,7 @@
         </is>
       </c>
       <c r="E10" s="7" t="n">
-        <v>1328</v>
+        <v>1241</v>
       </c>
       <c r="F10" s="9" t="n">
         <v>1.05</v>
@@ -10501,10 +10421,10 @@
         <v>6.21</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>2.86</v>
+        <v>2.7</v>
       </c>
       <c r="K10" s="9" t="n">
-        <v>2.21</v>
+        <v>2.09</v>
       </c>
       <c r="L10" s="9" t="n"/>
     </row>
@@ -10530,7 +10450,7 @@
         </is>
       </c>
       <c r="E11" s="7" t="n">
-        <v>3129</v>
+        <v>3020</v>
       </c>
       <c r="F11" s="9" t="n">
         <v>2.39</v>
@@ -10545,10 +10465,10 @@
         <v>6.44</v>
       </c>
       <c r="J11" s="9" t="n">
-        <v>5.62</v>
+        <v>5.38</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>4.05</v>
+        <v>3.89</v>
       </c>
       <c r="L11" s="9" t="n"/>
     </row>
@@ -10574,7 +10494,7 @@
         </is>
       </c>
       <c r="E12" s="7" t="n">
-        <v>815</v>
+        <v>771</v>
       </c>
       <c r="F12" s="9" t="n">
         <v>1.18</v>
@@ -10589,10 +10509,10 @@
         <v>2.59</v>
       </c>
       <c r="J12" s="9" t="n">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
       <c r="K12" s="9" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="L12" s="9" t="n"/>
     </row>
@@ -10618,7 +10538,7 @@
         </is>
       </c>
       <c r="E13" s="7" t="n">
-        <v>375</v>
+        <v>365</v>
       </c>
       <c r="F13" s="9" t="n">
         <v>2.1</v>
@@ -10633,10 +10553,10 @@
         <v>2.93</v>
       </c>
       <c r="J13" s="9" t="n">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="L13" s="9" t="n"/>
     </row>
@@ -10662,7 +10582,7 @@
         </is>
       </c>
       <c r="E14" s="7" t="n">
-        <v>9485</v>
+        <v>9693</v>
       </c>
       <c r="F14" s="9" t="n">
         <v>3.47</v>
@@ -10677,10 +10597,10 @@
         <v>6.09</v>
       </c>
       <c r="J14" s="9" t="n">
-        <v>6.37</v>
+        <v>6.47</v>
       </c>
       <c r="K14" s="9" t="n">
-        <v>5.49</v>
+        <v>5.58</v>
       </c>
       <c r="L14" s="9" t="n"/>
     </row>
@@ -10706,7 +10626,7 @@
         </is>
       </c>
       <c r="E15" s="7" t="n">
-        <v>41472</v>
+        <v>41082</v>
       </c>
       <c r="F15" s="9" t="n">
         <v>1.32</v>
@@ -10721,10 +10641,10 @@
         <v>5</v>
       </c>
       <c r="J15" s="9" t="n">
-        <v>4.74</v>
+        <v>4.7</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>3.9</v>
+        <v>3.87</v>
       </c>
       <c r="L15" s="9" t="n"/>
     </row>
@@ -10750,7 +10670,7 @@
         </is>
       </c>
       <c r="E16" s="7" t="n">
-        <v>11044</v>
+        <v>12399</v>
       </c>
       <c r="F16" s="9" t="n">
         <v>2.15</v>
@@ -10765,10 +10685,10 @@
         <v>6.43</v>
       </c>
       <c r="J16" s="9" t="n">
-        <v>8.640000000000001</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="K16" s="9" t="n">
-        <v>6.98</v>
+        <v>7.85</v>
       </c>
       <c r="L16" s="9" t="n"/>
     </row>
@@ -10794,7 +10714,7 @@
         </is>
       </c>
       <c r="E17" s="7" t="n">
-        <v>9886</v>
+        <v>11547</v>
       </c>
       <c r="F17" s="9" t="n">
         <v>0.99</v>
@@ -10809,10 +10729,10 @@
         <v>2.1</v>
       </c>
       <c r="J17" s="9" t="n">
-        <v>2.69</v>
+        <v>3.13</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>2.58</v>
+        <v>3</v>
       </c>
       <c r="L17" s="9" t="n"/>
     </row>
@@ -10838,7 +10758,7 @@
         </is>
       </c>
       <c r="E18" s="7" t="n">
-        <v>10100</v>
+        <v>9471</v>
       </c>
       <c r="F18" s="9" t="n">
         <v>2.04</v>
@@ -10853,10 +10773,10 @@
         <v>6.66</v>
       </c>
       <c r="J18" s="9" t="n">
-        <v>3.49</v>
+        <v>3.27</v>
       </c>
       <c r="K18" s="9" t="n">
-        <v>2.71</v>
+        <v>2.55</v>
       </c>
       <c r="L18" s="9" t="n"/>
     </row>
@@ -10882,7 +10802,7 @@
         </is>
       </c>
       <c r="E19" s="7" t="n">
-        <v>120040</v>
+        <v>116644</v>
       </c>
       <c r="F19" s="9" t="n">
         <v>13.34</v>
@@ -10897,10 +10817,10 @@
         <v>16.48</v>
       </c>
       <c r="J19" s="9" t="n">
-        <v>11.79</v>
+        <v>11.45</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>8.630000000000001</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="L19" s="9" t="n"/>
     </row>
@@ -10926,7 +10846,7 @@
         </is>
       </c>
       <c r="E20" s="7" t="n">
-        <v>73692</v>
+        <v>67906</v>
       </c>
       <c r="F20" s="9" t="n">
         <v>5.46</v>
@@ -10941,10 +10861,10 @@
         <v>4.86</v>
       </c>
       <c r="J20" s="9" t="n">
-        <v>3.77</v>
+        <v>3.47</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>3.26</v>
+        <v>3.01</v>
       </c>
       <c r="L20" s="9" t="n"/>
     </row>
@@ -10970,7 +10890,7 @@
         </is>
       </c>
       <c r="E21" s="7" t="n">
-        <v>96232</v>
+        <v>89308</v>
       </c>
       <c r="F21" s="9" t="n">
         <v>3.67</v>
@@ -10985,10 +10905,10 @@
         <v>3.55</v>
       </c>
       <c r="J21" s="9" t="n">
-        <v>3.38</v>
+        <v>3.14</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>3.04</v>
+        <v>2.82</v>
       </c>
       <c r="L21" s="9" t="n"/>
     </row>
@@ -11014,7 +10934,7 @@
         </is>
       </c>
       <c r="E22" s="7" t="n">
-        <v>265343</v>
+        <v>248904</v>
       </c>
       <c r="F22" s="9" t="n">
         <v>2.04</v>
@@ -11029,10 +10949,10 @@
         <v>3.77</v>
       </c>
       <c r="J22" s="9" t="n">
-        <v>3.78</v>
+        <v>3.54</v>
       </c>
       <c r="K22" s="9" t="n">
-        <v>3.51</v>
+        <v>3.29</v>
       </c>
       <c r="L22" s="9" t="n"/>
     </row>
@@ -11058,7 +10978,7 @@
         </is>
       </c>
       <c r="E23" s="7" t="n">
-        <v>10975</v>
+        <v>10582</v>
       </c>
       <c r="F23" s="9" t="n">
         <v>2.64</v>
@@ -11073,10 +10993,10 @@
         <v>2.63</v>
       </c>
       <c r="J23" s="9" t="n">
-        <v>1.97</v>
+        <v>1.9</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="L23" s="9" t="n"/>
     </row>
@@ -11102,7 +11022,7 @@
         </is>
       </c>
       <c r="E24" s="7" t="n">
-        <v>53637</v>
+        <v>50272</v>
       </c>
       <c r="F24" s="9" t="n">
         <v>2.86</v>
@@ -11117,10 +11037,10 @@
         <v>14.29</v>
       </c>
       <c r="J24" s="9" t="n">
-        <v>7.75</v>
+        <v>7.49</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>6.3</v>
+        <v>6.09</v>
       </c>
       <c r="L24" s="9" t="n"/>
     </row>
@@ -11146,7 +11066,7 @@
         </is>
       </c>
       <c r="E25" s="7" t="n">
-        <v>752</v>
+        <v>745</v>
       </c>
       <c r="F25" s="9" t="n">
         <v>2.35</v>
@@ -11190,7 +11110,7 @@
         </is>
       </c>
       <c r="E26" s="7" t="n">
-        <v>33466</v>
+        <v>30776</v>
       </c>
       <c r="F26" s="9" t="n">
         <v>0.65</v>
@@ -11205,10 +11125,10 @@
         <v>2.97</v>
       </c>
       <c r="J26" s="9" t="n">
-        <v>2.75</v>
+        <v>2.61</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>2.49</v>
+        <v>2.35</v>
       </c>
       <c r="L26" s="9" t="n"/>
     </row>
@@ -11234,7 +11154,7 @@
         </is>
       </c>
       <c r="E27" s="7" t="n">
-        <v>31792</v>
+        <v>32858</v>
       </c>
       <c r="F27" s="9" t="n">
         <v>1.85</v>
@@ -11249,10 +11169,10 @@
         <v>6.69</v>
       </c>
       <c r="J27" s="9" t="n">
-        <v>6.16</v>
+        <v>6.6</v>
       </c>
       <c r="K27" s="9" t="n">
-        <v>5.26</v>
+        <v>5.64</v>
       </c>
       <c r="L27" s="9" t="n"/>
     </row>
@@ -11278,7 +11198,7 @@
         </is>
       </c>
       <c r="E28" s="7" t="n">
-        <v>5097</v>
+        <v>4213</v>
       </c>
       <c r="F28" s="9" t="n">
         <v>0.8100000000000001</v>
@@ -11293,10 +11213,10 @@
         <v>2.61</v>
       </c>
       <c r="J28" s="9" t="n">
-        <v>2.83</v>
+        <v>2.34</v>
       </c>
       <c r="K28" s="9" t="n">
-        <v>2.21</v>
+        <v>1.83</v>
       </c>
       <c r="L28" s="9" t="n"/>
     </row>
@@ -11322,7 +11242,7 @@
         </is>
       </c>
       <c r="E29" s="7" t="n">
-        <v>4397</v>
+        <v>3935</v>
       </c>
       <c r="F29" s="9" t="n">
         <v>0.6899999999999999</v>
@@ -11337,10 +11257,10 @@
         <v>0.77</v>
       </c>
       <c r="J29" s="9" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>0.74</v>
+        <v>0.66</v>
       </c>
       <c r="L29" s="9" t="n"/>
     </row>
@@ -11366,7 +11286,7 @@
         </is>
       </c>
       <c r="E30" s="7" t="n">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="F30" s="9" t="n">
         <v>0.8100000000000001</v>
@@ -11406,7 +11326,7 @@
         </is>
       </c>
       <c r="E31" s="7" t="n">
-        <v>380870</v>
+        <v>388618</v>
       </c>
       <c r="F31" s="9" t="n">
         <v>7.79</v>
@@ -11421,10 +11341,10 @@
         <v>12.5</v>
       </c>
       <c r="J31" s="9" t="n">
-        <v>12.42</v>
+        <v>12.67</v>
       </c>
       <c r="K31" s="9" t="n">
-        <v>9.109999999999999</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="L31" s="9" t="n"/>
     </row>
@@ -11450,7 +11370,7 @@
         </is>
       </c>
       <c r="E32" s="7" t="n">
-        <v>182688</v>
+        <v>185233</v>
       </c>
       <c r="F32" s="9" t="n">
         <v>5.84</v>
@@ -11465,10 +11385,10 @@
         <v>4.81</v>
       </c>
       <c r="J32" s="9" t="n">
-        <v>6.28</v>
+        <v>6.37</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>5.53</v>
+        <v>5.61</v>
       </c>
       <c r="L32" s="9" t="n"/>
     </row>
@@ -11494,7 +11414,7 @@
         </is>
       </c>
       <c r="E33" s="7" t="n">
-        <v>16867</v>
+        <v>21662</v>
       </c>
       <c r="F33" s="9" t="n">
         <v>3.12</v>
@@ -11509,10 +11429,10 @@
         <v>1.48</v>
       </c>
       <c r="J33" s="9" t="n">
-        <v>2.09</v>
+        <v>2.69</v>
       </c>
       <c r="K33" s="9" t="n">
-        <v>1.97</v>
+        <v>2.53</v>
       </c>
       <c r="L33" s="9" t="n"/>
     </row>
@@ -11538,7 +11458,7 @@
         </is>
       </c>
       <c r="E34" s="7" t="n">
-        <v>41747</v>
+        <v>42820</v>
       </c>
       <c r="F34" s="9" t="n"/>
       <c r="G34" s="9" t="n">
@@ -11554,10 +11474,10 @@
         <v>1.54</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>1.72</v>
+        <v>1.81</v>
       </c>
       <c r="L34" s="9" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="35">
@@ -11582,7 +11502,7 @@
         </is>
       </c>
       <c r="E35" s="7" t="n">
-        <v>7804</v>
+        <v>7481</v>
       </c>
       <c r="F35" s="9" t="n"/>
       <c r="G35" s="9" t="n">
@@ -11598,10 +11518,10 @@
         <v>1.25</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="L35" s="9" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
     </row>
     <row r="36">
@@ -11626,7 +11546,7 @@
         </is>
       </c>
       <c r="E36" s="7" t="n">
-        <v>71495</v>
+        <v>63743</v>
       </c>
       <c r="F36" s="9" t="n">
         <v>2.36</v>
@@ -11641,10 +11561,10 @@
         <v>3.37</v>
       </c>
       <c r="J36" s="9" t="n">
-        <v>3.44</v>
+        <v>3.18</v>
       </c>
       <c r="K36" s="9" t="n">
-        <v>3.04</v>
+        <v>2.8</v>
       </c>
       <c r="L36" s="9" t="n"/>
     </row>
@@ -11670,7 +11590,7 @@
         </is>
       </c>
       <c r="E37" s="7" t="n">
-        <v>27156</v>
+        <v>23992</v>
       </c>
       <c r="F37" s="9" t="n">
         <v>2.06</v>
@@ -11685,10 +11605,10 @@
         <v>2.2</v>
       </c>
       <c r="J37" s="9" t="n">
-        <v>1.9</v>
+        <v>1.68</v>
       </c>
       <c r="K37" s="9" t="n">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="L37" s="9" t="n"/>
     </row>
@@ -11714,7 +11634,7 @@
         </is>
       </c>
       <c r="E38" s="7" t="n">
-        <v>14144</v>
+        <v>12624</v>
       </c>
       <c r="F38" s="9" t="n">
         <v>1.12</v>
@@ -11729,10 +11649,10 @@
         <v>2.25</v>
       </c>
       <c r="J38" s="9" t="n">
-        <v>1.51</v>
+        <v>1.35</v>
       </c>
       <c r="K38" s="9" t="n">
-        <v>1.43</v>
+        <v>1.28</v>
       </c>
       <c r="L38" s="9" t="n"/>
     </row>
@@ -11758,7 +11678,7 @@
         </is>
       </c>
       <c r="E39" s="7" t="n">
-        <v>192</v>
+        <v>172</v>
       </c>
       <c r="F39" s="9" t="n">
         <v>1.25</v>
@@ -11773,10 +11693,10 @@
         <v>0.92</v>
       </c>
       <c r="J39" s="9" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="K39" s="9" t="n">
-        <v>0.7</v>
+        <v>0.63</v>
       </c>
       <c r="L39" s="9" t="n"/>
     </row>
@@ -11802,7 +11722,7 @@
         </is>
       </c>
       <c r="E40" s="7" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F40" s="9" t="n">
         <v>0.5600000000000001</v>
@@ -11842,7 +11762,7 @@
         </is>
       </c>
       <c r="E41" s="7" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F41" s="9" t="n">
         <v>0.88</v>
@@ -11882,7 +11802,7 @@
         </is>
       </c>
       <c r="E42" s="7" t="n">
-        <v>62409</v>
+        <v>67287</v>
       </c>
       <c r="F42" s="9" t="n">
         <v>3.49</v>
@@ -11897,10 +11817,10 @@
         <v>5.69</v>
       </c>
       <c r="J42" s="9" t="n">
-        <v>5.42</v>
+        <v>5.84</v>
       </c>
       <c r="K42" s="9" t="n">
-        <v>4.31</v>
+        <v>4.65</v>
       </c>
       <c r="L42" s="9" t="n"/>
     </row>
@@ -12016,7 +11936,7 @@
         </is>
       </c>
       <c r="E2" s="7" t="n">
-        <v>37480</v>
+        <v>33297</v>
       </c>
       <c r="F2" s="11" t="n">
         <v>-6.66</v>
@@ -12031,10 +11951,10 @@
         <v>18.82</v>
       </c>
       <c r="J2" s="11" t="n">
-        <v>30.52</v>
+        <v>30.41</v>
       </c>
       <c r="K2" s="11" t="n">
-        <v>27.39</v>
+        <v>27.65</v>
       </c>
       <c r="L2" s="11" t="n"/>
     </row>
@@ -12060,7 +11980,7 @@
         </is>
       </c>
       <c r="E3" s="7" t="n">
-        <v>19558</v>
+        <v>17984</v>
       </c>
       <c r="F3" s="11" t="n">
         <v>-234.21</v>
@@ -12075,10 +11995,10 @@
         <v>22.59</v>
       </c>
       <c r="J3" s="11" t="n">
-        <v>26.58</v>
+        <v>26.9</v>
       </c>
       <c r="K3" s="11" t="n">
-        <v>21.78</v>
+        <v>21.54</v>
       </c>
       <c r="L3" s="11" t="n"/>
     </row>
@@ -12104,7 +12024,7 @@
         </is>
       </c>
       <c r="E4" s="7" t="n">
-        <v>13630</v>
+        <v>12699</v>
       </c>
       <c r="F4" s="11" t="n">
         <v>-17.23</v>
@@ -12119,7 +12039,7 @@
         <v>13.74</v>
       </c>
       <c r="J4" s="11" t="n">
-        <v>21.73</v>
+        <v>21.52</v>
       </c>
       <c r="K4" s="11" t="n">
         <v>24.71</v>
@@ -12148,7 +12068,7 @@
         </is>
       </c>
       <c r="E5" s="7" t="n">
-        <v>19273</v>
+        <v>17172</v>
       </c>
       <c r="F5" s="11" t="n">
         <v>-2.23</v>
@@ -12163,10 +12083,10 @@
         <v>17.78</v>
       </c>
       <c r="J5" s="11" t="n">
-        <v>24.77</v>
+        <v>25</v>
       </c>
       <c r="K5" s="11" t="n">
-        <v>23.63</v>
+        <v>24.17</v>
       </c>
       <c r="L5" s="11" t="n"/>
     </row>
@@ -12192,7 +12112,7 @@
         </is>
       </c>
       <c r="E6" s="7" t="n">
-        <v>1349</v>
+        <v>1306</v>
       </c>
       <c r="F6" s="11" t="n">
         <v>-7.73</v>
@@ -12207,10 +12127,10 @@
         <v>32.19</v>
       </c>
       <c r="J6" s="11" t="n">
-        <v>22.79</v>
+        <v>23.73</v>
       </c>
       <c r="K6" s="11" t="n">
-        <v>19.48</v>
+        <v>19.63</v>
       </c>
       <c r="L6" s="11" t="n"/>
     </row>
@@ -12236,7 +12156,7 @@
         </is>
       </c>
       <c r="E7" s="7" t="n">
-        <v>1077</v>
+        <v>1030</v>
       </c>
       <c r="F7" s="11" t="n">
         <v>-13.03</v>
@@ -12276,7 +12196,7 @@
         </is>
       </c>
       <c r="E8" s="7" t="n">
-        <v>5195</v>
+        <v>4907</v>
       </c>
       <c r="F8" s="11" t="n">
         <v>-52.75</v>
@@ -12291,10 +12211,10 @@
         <v>13.32</v>
       </c>
       <c r="J8" s="11" t="n">
-        <v>16.62</v>
+        <v>16.33</v>
       </c>
       <c r="K8" s="11" t="n">
-        <v>20</v>
+        <v>20.52</v>
       </c>
       <c r="L8" s="11" t="n"/>
     </row>
@@ -12320,7 +12240,7 @@
         </is>
       </c>
       <c r="E9" s="7" t="n">
-        <v>8257</v>
+        <v>7797</v>
       </c>
       <c r="F9" s="11" t="n">
         <v>57.58</v>
@@ -12335,10 +12255,10 @@
         <v>33.73</v>
       </c>
       <c r="J9" s="11" t="n">
-        <v>37.81</v>
+        <v>37.86</v>
       </c>
       <c r="K9" s="11" t="n">
-        <v>37.64</v>
+        <v>37.22</v>
       </c>
       <c r="L9" s="11" t="n"/>
     </row>
@@ -12364,7 +12284,7 @@
         </is>
       </c>
       <c r="E10" s="7" t="n">
-        <v>1328</v>
+        <v>1241</v>
       </c>
       <c r="F10" s="11" t="n">
         <v>7.36</v>
@@ -12379,10 +12299,10 @@
         <v>41.36</v>
       </c>
       <c r="J10" s="11" t="n">
-        <v>24</v>
+        <v>23.08</v>
       </c>
       <c r="K10" s="11" t="n">
-        <v>25.85</v>
+        <v>25.69</v>
       </c>
       <c r="L10" s="11" t="n"/>
     </row>
@@ -12408,7 +12328,7 @@
         </is>
       </c>
       <c r="E11" s="7" t="n">
-        <v>3129</v>
+        <v>3020</v>
       </c>
       <c r="F11" s="11" t="n">
         <v>-18.17</v>
@@ -12423,10 +12343,10 @@
         <v>36.6</v>
       </c>
       <c r="J11" s="11" t="n">
-        <v>29.23</v>
+        <v>30.11</v>
       </c>
       <c r="K11" s="11" t="n">
-        <v>32.59</v>
+        <v>32.22</v>
       </c>
       <c r="L11" s="11" t="n"/>
     </row>
@@ -12452,7 +12372,7 @@
         </is>
       </c>
       <c r="E12" s="7" t="n">
-        <v>815</v>
+        <v>771</v>
       </c>
       <c r="F12" s="11" t="n">
         <v>5.01</v>
@@ -12467,10 +12387,10 @@
         <v>19.3</v>
       </c>
       <c r="J12" s="11" t="n">
-        <v>19.11</v>
+        <v>18.94</v>
       </c>
       <c r="K12" s="11" t="n">
-        <v>19.15</v>
+        <v>19.16</v>
       </c>
       <c r="L12" s="11" t="n"/>
     </row>
@@ -12496,7 +12416,7 @@
         </is>
       </c>
       <c r="E13" s="7" t="n">
-        <v>375</v>
+        <v>365</v>
       </c>
       <c r="F13" s="11" t="n">
         <v>5.67</v>
@@ -12540,7 +12460,7 @@
         </is>
       </c>
       <c r="E14" s="7" t="n">
-        <v>9485</v>
+        <v>9693</v>
       </c>
       <c r="F14" s="11" t="n">
         <v>8.300000000000001</v>
@@ -12555,10 +12475,10 @@
         <v>10.51</v>
       </c>
       <c r="J14" s="11" t="n">
-        <v>11.95</v>
+        <v>13</v>
       </c>
       <c r="K14" s="11" t="n">
-        <v>20.45</v>
+        <v>20.41</v>
       </c>
       <c r="L14" s="11" t="n"/>
     </row>
@@ -12584,7 +12504,7 @@
         </is>
       </c>
       <c r="E15" s="7" t="n">
-        <v>41472</v>
+        <v>41082</v>
       </c>
       <c r="F15" s="11" t="n">
         <v>6.84</v>
@@ -12599,10 +12519,10 @@
         <v>19.14</v>
       </c>
       <c r="J15" s="11" t="n">
-        <v>23.15</v>
+        <v>23.01</v>
       </c>
       <c r="K15" s="11" t="n">
-        <v>23.48</v>
+        <v>23.56</v>
       </c>
       <c r="L15" s="11" t="n"/>
     </row>
@@ -12628,7 +12548,7 @@
         </is>
       </c>
       <c r="E16" s="7" t="n">
-        <v>11044</v>
+        <v>12399</v>
       </c>
       <c r="F16" s="11" t="n">
         <v>13.15</v>
@@ -12643,10 +12563,10 @@
         <v>19.2</v>
       </c>
       <c r="J16" s="11" t="n">
-        <v>23.25</v>
+        <v>23.2</v>
       </c>
       <c r="K16" s="11" t="n">
-        <v>27.46</v>
+        <v>27.53</v>
       </c>
       <c r="L16" s="11" t="n"/>
     </row>
@@ -12672,7 +12592,7 @@
         </is>
       </c>
       <c r="E17" s="7" t="n">
-        <v>9886</v>
+        <v>11547</v>
       </c>
       <c r="F17" s="11" t="n">
         <v>-3.83</v>
@@ -12687,10 +12607,10 @@
         <v>6.6</v>
       </c>
       <c r="J17" s="11" t="n">
-        <v>3.02</v>
+        <v>3.93</v>
       </c>
       <c r="K17" s="11" t="n">
-        <v>8.65</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="L17" s="11" t="n"/>
     </row>
@@ -12716,7 +12636,7 @@
         </is>
       </c>
       <c r="E18" s="7" t="n">
-        <v>10100</v>
+        <v>9471</v>
       </c>
       <c r="F18" s="11" t="n">
         <v>13.01</v>
@@ -12731,10 +12651,10 @@
         <v>30.05</v>
       </c>
       <c r="J18" s="11" t="n">
-        <v>25.21</v>
+        <v>25.17</v>
       </c>
       <c r="K18" s="11" t="n">
-        <v>27.27</v>
+        <v>27.03</v>
       </c>
       <c r="L18" s="11" t="n"/>
     </row>
@@ -12760,7 +12680,7 @@
         </is>
       </c>
       <c r="E19" s="7" t="n">
-        <v>120040</v>
+        <v>116644</v>
       </c>
       <c r="F19" s="11" t="n">
         <v>61.86</v>
@@ -12775,10 +12695,10 @@
         <v>76.87</v>
       </c>
       <c r="J19" s="11" t="n">
-        <v>82.51000000000001</v>
+        <v>82.56</v>
       </c>
       <c r="K19" s="11" t="n">
-        <v>62.21</v>
+        <v>62.25</v>
       </c>
       <c r="L19" s="11" t="n"/>
     </row>
@@ -12804,7 +12724,7 @@
         </is>
       </c>
       <c r="E20" s="7" t="n">
-        <v>73692</v>
+        <v>67906</v>
       </c>
       <c r="F20" s="11" t="n">
         <v>31.97</v>
@@ -12819,10 +12739,10 @@
         <v>26.17</v>
       </c>
       <c r="J20" s="11" t="n">
-        <v>22.72</v>
+        <v>22.73</v>
       </c>
       <c r="K20" s="11" t="n">
-        <v>20.51</v>
+        <v>20.52</v>
       </c>
       <c r="L20" s="11" t="n"/>
     </row>
@@ -12848,7 +12768,7 @@
         </is>
       </c>
       <c r="E21" s="7" t="n">
-        <v>96232</v>
+        <v>89308</v>
       </c>
       <c r="F21" s="11" t="n">
         <v>18.26</v>
@@ -12892,7 +12812,7 @@
         </is>
       </c>
       <c r="E22" s="7" t="n">
-        <v>265343</v>
+        <v>248904</v>
       </c>
       <c r="F22" s="11" t="n">
         <v>7.16</v>
@@ -12907,7 +12827,7 @@
         <v>10.74</v>
       </c>
       <c r="J22" s="11" t="n">
-        <v>14.35</v>
+        <v>14.36</v>
       </c>
       <c r="K22" s="11" t="n">
         <v>14.46</v>
@@ -12936,7 +12856,7 @@
         </is>
       </c>
       <c r="E23" s="7" t="n">
-        <v>10975</v>
+        <v>10582</v>
       </c>
       <c r="F23" s="11" t="n">
         <v>16.6</v>
@@ -12980,7 +12900,7 @@
         </is>
       </c>
       <c r="E24" s="7" t="n">
-        <v>53637</v>
+        <v>50272</v>
       </c>
       <c r="F24" s="11" t="n">
         <v>16.81</v>
@@ -12995,10 +12915,10 @@
         <v>15.36</v>
       </c>
       <c r="J24" s="11" t="n">
-        <v>31.17</v>
+        <v>31.09</v>
       </c>
       <c r="K24" s="11" t="n">
-        <v>36.99</v>
+        <v>36.85</v>
       </c>
       <c r="L24" s="11" t="n"/>
     </row>
@@ -13024,7 +12944,7 @@
         </is>
       </c>
       <c r="E25" s="7" t="n">
-        <v>752</v>
+        <v>745</v>
       </c>
       <c r="F25" s="11" t="n">
         <v>14.19</v>
@@ -13039,10 +12959,10 @@
         <v>17.62</v>
       </c>
       <c r="J25" s="11" t="n">
-        <v>19.87</v>
+        <v>19.92</v>
       </c>
       <c r="K25" s="11" t="n">
-        <v>20.57</v>
+        <v>20.58</v>
       </c>
       <c r="L25" s="11" t="n"/>
     </row>
@@ -13068,7 +12988,7 @@
         </is>
       </c>
       <c r="E26" s="7" t="n">
-        <v>33466</v>
+        <v>30776</v>
       </c>
       <c r="F26" s="11" t="n">
         <v>12.91</v>
@@ -13083,10 +13003,10 @@
         <v>13.2</v>
       </c>
       <c r="J26" s="11" t="n">
-        <v>13.7</v>
+        <v>13.73</v>
       </c>
       <c r="K26" s="11" t="n">
-        <v>14.89</v>
+        <v>14.94</v>
       </c>
       <c r="L26" s="11" t="n"/>
     </row>
@@ -13112,7 +13032,7 @@
         </is>
       </c>
       <c r="E27" s="7" t="n">
-        <v>31792</v>
+        <v>32858</v>
       </c>
       <c r="F27" s="11" t="n">
         <v>7.44</v>
@@ -13127,10 +13047,10 @@
         <v>16.02</v>
       </c>
       <c r="J27" s="11" t="n">
-        <v>17.2</v>
+        <v>17.21</v>
       </c>
       <c r="K27" s="11" t="n">
-        <v>18.76</v>
+        <v>18.85</v>
       </c>
       <c r="L27" s="11" t="n"/>
     </row>
@@ -13156,7 +13076,7 @@
         </is>
       </c>
       <c r="E28" s="7" t="n">
-        <v>5097</v>
+        <v>4213</v>
       </c>
       <c r="F28" s="11" t="n">
         <v>7.62</v>
@@ -13200,7 +13120,7 @@
         </is>
       </c>
       <c r="E29" s="7" t="n">
-        <v>4397</v>
+        <v>3935</v>
       </c>
       <c r="F29" s="11" t="n">
         <v>12.82</v>
@@ -13215,10 +13135,10 @@
         <v>5.71</v>
       </c>
       <c r="J29" s="11" t="n">
-        <v>8</v>
+        <v>7.93</v>
       </c>
       <c r="K29" s="11" t="n">
-        <v>8.130000000000001</v>
+        <v>7.68</v>
       </c>
       <c r="L29" s="11" t="n"/>
     </row>
@@ -13244,7 +13164,7 @@
         </is>
       </c>
       <c r="E30" s="7" t="n">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="F30" s="11" t="n">
         <v>11.21</v>
@@ -13284,7 +13204,7 @@
         </is>
       </c>
       <c r="E31" s="7" t="n">
-        <v>380870</v>
+        <v>388618</v>
       </c>
       <c r="F31" s="11" t="n">
         <v>42.25</v>
@@ -13328,7 +13248,7 @@
         </is>
       </c>
       <c r="E32" s="7" t="n">
-        <v>182688</v>
+        <v>185233</v>
       </c>
       <c r="F32" s="11" t="n">
         <v>35.19</v>
@@ -13346,7 +13266,7 @@
         <v>17.81</v>
       </c>
       <c r="K32" s="11" t="n">
-        <v>19.74</v>
+        <v>19.87</v>
       </c>
       <c r="L32" s="11" t="n"/>
     </row>
@@ -13372,7 +13292,7 @@
         </is>
       </c>
       <c r="E33" s="7" t="n">
-        <v>16867</v>
+        <v>21662</v>
       </c>
       <c r="F33" s="11" t="n">
         <v>29.29</v>
@@ -13416,7 +13336,7 @@
         </is>
       </c>
       <c r="E34" s="7" t="n">
-        <v>41747</v>
+        <v>42820</v>
       </c>
       <c r="F34" s="11" t="n"/>
       <c r="G34" s="11" t="n">
@@ -13432,10 +13352,10 @@
         <v>11.26</v>
       </c>
       <c r="K34" s="11" t="n">
-        <v>10.93</v>
+        <v>11.04</v>
       </c>
       <c r="L34" s="11" t="n">
-        <v>11.27</v>
+        <v>11.49</v>
       </c>
     </row>
     <row r="35">
@@ -13460,7 +13380,7 @@
         </is>
       </c>
       <c r="E35" s="7" t="n">
-        <v>7804</v>
+        <v>7481</v>
       </c>
       <c r="F35" s="11" t="n"/>
       <c r="G35" s="11" t="n">
@@ -13504,7 +13424,7 @@
         </is>
       </c>
       <c r="E36" s="7" t="n">
-        <v>71495</v>
+        <v>63743</v>
       </c>
       <c r="F36" s="11" t="n">
         <v>20.11</v>
@@ -13519,10 +13439,10 @@
         <v>18.5</v>
       </c>
       <c r="J36" s="11" t="n">
-        <v>23.11</v>
+        <v>23.22</v>
       </c>
       <c r="K36" s="11" t="n">
-        <v>24.12</v>
+        <v>24.39</v>
       </c>
       <c r="L36" s="11" t="n"/>
     </row>
@@ -13548,7 +13468,7 @@
         </is>
       </c>
       <c r="E37" s="7" t="n">
-        <v>27156</v>
+        <v>23992</v>
       </c>
       <c r="F37" s="11" t="n">
         <v>6.6</v>
@@ -13592,7 +13512,7 @@
         </is>
       </c>
       <c r="E38" s="7" t="n">
-        <v>14144</v>
+        <v>12624</v>
       </c>
       <c r="F38" s="11" t="n">
         <v>8.1</v>
@@ -13636,7 +13556,7 @@
         </is>
       </c>
       <c r="E39" s="7" t="n">
-        <v>192</v>
+        <v>172</v>
       </c>
       <c r="F39" s="11" t="n">
         <v>21.69</v>
@@ -13680,7 +13600,7 @@
         </is>
       </c>
       <c r="E40" s="7" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F40" s="11" t="n">
         <v>7.43</v>
@@ -13720,7 +13640,7 @@
         </is>
       </c>
       <c r="E41" s="7" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F41" s="11" t="n">
         <v>15.47</v>
@@ -13760,7 +13680,7 @@
         </is>
       </c>
       <c r="E42" s="7" t="n">
-        <v>62409</v>
+        <v>67287</v>
       </c>
       <c r="F42" s="11" t="n">
         <v>29.81</v>
@@ -13778,7 +13698,7 @@
         <v>30.36</v>
       </c>
       <c r="K42" s="11" t="n">
-        <v>27.82</v>
+        <v>27.83</v>
       </c>
       <c r="L42" s="11" t="n"/>
     </row>
@@ -13894,7 +13814,7 @@
         </is>
       </c>
       <c r="E2" s="7" t="n">
-        <v>37480</v>
+        <v>33297</v>
       </c>
       <c r="F2" s="9" t="n">
         <v>1.14</v>
@@ -13909,10 +13829,10 @@
         <v>3.04</v>
       </c>
       <c r="J2" s="9" t="n">
-        <v>2.01</v>
+        <v>1.79</v>
       </c>
       <c r="K2" s="9" t="n">
-        <v>1.88</v>
+        <v>1.68</v>
       </c>
       <c r="L2" s="9" t="n"/>
     </row>
@@ -13938,7 +13858,7 @@
         </is>
       </c>
       <c r="E3" s="7" t="n">
-        <v>19558</v>
+        <v>17984</v>
       </c>
       <c r="F3" s="9" t="n">
         <v>0.42</v>
@@ -13953,10 +13873,10 @@
         <v>2.72</v>
       </c>
       <c r="J3" s="9" t="n">
-        <v>1.65</v>
+        <v>1.52</v>
       </c>
       <c r="K3" s="9" t="n">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="L3" s="9" t="n"/>
     </row>
@@ -13982,7 +13902,7 @@
         </is>
       </c>
       <c r="E4" s="7" t="n">
-        <v>13630</v>
+        <v>12699</v>
       </c>
       <c r="F4" s="9" t="n">
         <v>0.73</v>
@@ -13997,10 +13917,10 @@
         <v>1.93</v>
       </c>
       <c r="J4" s="9" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="K4" s="9" t="n">
-        <v>1.24</v>
+        <v>1.15</v>
       </c>
       <c r="L4" s="9" t="n"/>
     </row>
@@ -14026,7 +13946,7 @@
         </is>
       </c>
       <c r="E5" s="7" t="n">
-        <v>19273</v>
+        <v>17172</v>
       </c>
       <c r="F5" s="9" t="n">
         <v>0.29</v>
@@ -14041,10 +13961,10 @@
         <v>0.96</v>
       </c>
       <c r="J5" s="9" t="n">
-        <v>0.74</v>
+        <v>0.66</v>
       </c>
       <c r="K5" s="9" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.62</v>
       </c>
       <c r="L5" s="9" t="n"/>
     </row>
@@ -14070,7 +13990,7 @@
         </is>
       </c>
       <c r="E6" s="7" t="n">
-        <v>1349</v>
+        <v>1306</v>
       </c>
       <c r="F6" s="9" t="n"/>
       <c r="G6" s="9" t="n"/>
@@ -14079,10 +13999,10 @@
         <v>2.09</v>
       </c>
       <c r="J6" s="9" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="K6" s="9" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="L6" s="9" t="n"/>
     </row>
@@ -14108,7 +14028,7 @@
         </is>
       </c>
       <c r="E7" s="7" t="n">
-        <v>1077</v>
+        <v>1030</v>
       </c>
       <c r="F7" s="9" t="n">
         <v>0.18</v>
@@ -14148,7 +14068,7 @@
         </is>
       </c>
       <c r="E8" s="7" t="n">
-        <v>5195</v>
+        <v>4907</v>
       </c>
       <c r="F8" s="9" t="n">
         <v>0.12</v>
@@ -14163,10 +14083,10 @@
         <v>0.61</v>
       </c>
       <c r="J8" s="9" t="n">
-        <v>0.48</v>
+        <v>0.47</v>
       </c>
       <c r="K8" s="9" t="n">
-        <v>0.43</v>
+        <v>0.41</v>
       </c>
       <c r="L8" s="9" t="n"/>
     </row>
@@ -14192,7 +14112,7 @@
         </is>
       </c>
       <c r="E9" s="7" t="n">
-        <v>8257</v>
+        <v>7797</v>
       </c>
       <c r="F9" s="9" t="n"/>
       <c r="G9" s="9" t="n"/>
@@ -14203,10 +14123,10 @@
         <v>4.38</v>
       </c>
       <c r="J9" s="9" t="n">
-        <v>4.77</v>
+        <v>4.47</v>
       </c>
       <c r="K9" s="9" t="n">
-        <v>4.14</v>
+        <v>3.93</v>
       </c>
       <c r="L9" s="9" t="n"/>
     </row>
@@ -14232,7 +14152,7 @@
         </is>
       </c>
       <c r="E10" s="7" t="n">
-        <v>1328</v>
+        <v>1241</v>
       </c>
       <c r="F10" s="9" t="n">
         <v>1.13</v>
@@ -14247,10 +14167,10 @@
         <v>7.54</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>2.93</v>
+        <v>2.74</v>
       </c>
       <c r="K10" s="9" t="n">
-        <v>2.34</v>
+        <v>2.2</v>
       </c>
       <c r="L10" s="9" t="n"/>
     </row>
@@ -14276,7 +14196,7 @@
         </is>
       </c>
       <c r="E11" s="7" t="n">
-        <v>3129</v>
+        <v>3020</v>
       </c>
       <c r="F11" s="9" t="n">
         <v>0.6899999999999999</v>
@@ -14291,10 +14211,10 @@
         <v>2.61</v>
       </c>
       <c r="J11" s="9" t="n">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>1.92</v>
+        <v>1.84</v>
       </c>
       <c r="L11" s="9" t="n"/>
     </row>
@@ -14320,7 +14240,7 @@
         </is>
       </c>
       <c r="E12" s="7" t="n">
-        <v>815</v>
+        <v>771</v>
       </c>
       <c r="F12" s="9" t="n">
         <v>1.29</v>
@@ -14335,10 +14255,10 @@
         <v>1.65</v>
       </c>
       <c r="J12" s="9" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="K12" s="9" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="L12" s="9" t="n"/>
     </row>
@@ -14364,7 +14284,7 @@
         </is>
       </c>
       <c r="E13" s="7" t="n">
-        <v>375</v>
+        <v>365</v>
       </c>
       <c r="F13" s="9" t="n">
         <v>0.72</v>
@@ -14379,10 +14299,10 @@
         <v>1.02</v>
       </c>
       <c r="J13" s="9" t="n">
-        <v>0.59</v>
+        <v>0.57</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="L13" s="9" t="n"/>
     </row>
@@ -14408,7 +14328,7 @@
         </is>
       </c>
       <c r="E14" s="7" t="n">
-        <v>9485</v>
+        <v>9693</v>
       </c>
       <c r="F14" s="9" t="n">
         <v>1.78</v>
@@ -14423,10 +14343,10 @@
         <v>3.02</v>
       </c>
       <c r="J14" s="9" t="n">
-        <v>2.37</v>
+        <v>2.43</v>
       </c>
       <c r="K14" s="9" t="n">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="L14" s="9" t="n"/>
     </row>
@@ -14452,7 +14372,7 @@
         </is>
       </c>
       <c r="E15" s="7" t="n">
-        <v>41472</v>
+        <v>41082</v>
       </c>
       <c r="F15" s="9" t="n">
         <v>0.53</v>
@@ -14467,10 +14387,10 @@
         <v>1.81</v>
       </c>
       <c r="J15" s="9" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="L15" s="9" t="n"/>
     </row>
@@ -14496,7 +14416,7 @@
         </is>
       </c>
       <c r="E16" s="7" t="n">
-        <v>11044</v>
+        <v>12399</v>
       </c>
       <c r="F16" s="9" t="n">
         <v>0.9</v>
@@ -14511,10 +14431,10 @@
         <v>2.14</v>
       </c>
       <c r="J16" s="9" t="n">
-        <v>2.87</v>
+        <v>3.23</v>
       </c>
       <c r="K16" s="9" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="L16" s="9" t="n"/>
     </row>
@@ -14540,7 +14460,7 @@
         </is>
       </c>
       <c r="E17" s="7" t="n">
-        <v>9886</v>
+        <v>11547</v>
       </c>
       <c r="F17" s="9" t="n">
         <v>0.9</v>
@@ -14555,10 +14475,10 @@
         <v>2.78</v>
       </c>
       <c r="J17" s="9" t="n">
-        <v>2.97</v>
+        <v>3.44</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>2.59</v>
+        <v>3.08</v>
       </c>
       <c r="L17" s="9" t="n"/>
     </row>
@@ -14584,7 +14504,7 @@
         </is>
       </c>
       <c r="E18" s="7" t="n">
-        <v>10100</v>
+        <v>9471</v>
       </c>
       <c r="F18" s="9" t="n">
         <v>0.98</v>
@@ -14599,10 +14519,10 @@
         <v>3.51</v>
       </c>
       <c r="J18" s="9" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="K18" s="9" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="L18" s="9" t="n"/>
     </row>
@@ -14628,7 +14548,7 @@
         </is>
       </c>
       <c r="E19" s="7" t="n">
-        <v>120040</v>
+        <v>116644</v>
       </c>
       <c r="F19" s="9" t="n">
         <v>1.87</v>
@@ -14643,10 +14563,10 @@
         <v>1.48</v>
       </c>
       <c r="J19" s="9" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="L19" s="9" t="n"/>
     </row>
@@ -14672,7 +14592,7 @@
         </is>
       </c>
       <c r="E20" s="7" t="n">
-        <v>73692</v>
+        <v>67906</v>
       </c>
       <c r="F20" s="9" t="n">
         <v>2.28</v>
@@ -14687,10 +14607,10 @@
         <v>1.93</v>
       </c>
       <c r="J20" s="9" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="L20" s="9" t="n"/>
     </row>
@@ -14716,7 +14636,7 @@
         </is>
       </c>
       <c r="E21" s="7" t="n">
-        <v>96232</v>
+        <v>89308</v>
       </c>
       <c r="F21" s="9" t="n">
         <v>1.73</v>
@@ -14731,10 +14651,10 @@
         <v>1.73</v>
       </c>
       <c r="J21" s="9" t="n">
-        <v>1.72</v>
+        <v>1.6</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>1.64</v>
+        <v>1.52</v>
       </c>
       <c r="L21" s="9" t="n"/>
     </row>
@@ -14760,7 +14680,7 @@
         </is>
       </c>
       <c r="E22" s="7" t="n">
-        <v>265343</v>
+        <v>248904</v>
       </c>
       <c r="F22" s="9" t="n">
         <v>2.21</v>
@@ -14775,10 +14695,10 @@
         <v>2.78</v>
       </c>
       <c r="J22" s="9" t="n">
-        <v>2.76</v>
+        <v>2.59</v>
       </c>
       <c r="K22" s="9" t="n">
-        <v>2.57</v>
+        <v>2.41</v>
       </c>
       <c r="L22" s="9" t="n"/>
     </row>
@@ -14804,7 +14724,7 @@
         </is>
       </c>
       <c r="E23" s="7" t="n">
-        <v>10975</v>
+        <v>10582</v>
       </c>
       <c r="F23" s="9" t="n">
         <v>0.86</v>
@@ -14819,10 +14739,10 @@
         <v>1.07</v>
       </c>
       <c r="J23" s="9" t="n">
-        <v>0.82</v>
+        <v>0.79</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>0.77</v>
+        <v>0.75</v>
       </c>
       <c r="L23" s="9" t="n"/>
     </row>
@@ -14848,7 +14768,7 @@
         </is>
       </c>
       <c r="E24" s="7" t="n">
-        <v>53637</v>
+        <v>50272</v>
       </c>
       <c r="F24" s="9" t="n">
         <v>1.26</v>
@@ -14863,10 +14783,10 @@
         <v>7.21</v>
       </c>
       <c r="J24" s="9" t="n">
-        <v>3.31</v>
+        <v>3.2</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="L24" s="9" t="n"/>
     </row>
@@ -14892,7 +14812,7 @@
         </is>
       </c>
       <c r="E25" s="7" t="n">
-        <v>752</v>
+        <v>745</v>
       </c>
       <c r="F25" s="9" t="n">
         <v>1.24</v>
@@ -14936,7 +14856,7 @@
         </is>
       </c>
       <c r="E26" s="7" t="n">
-        <v>33466</v>
+        <v>30776</v>
       </c>
       <c r="F26" s="9" t="n">
         <v>0.32</v>
@@ -14951,10 +14871,10 @@
         <v>1.45</v>
       </c>
       <c r="J26" s="9" t="n">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="L26" s="9" t="n"/>
     </row>
@@ -14980,7 +14900,7 @@
         </is>
       </c>
       <c r="E27" s="7" t="n">
-        <v>31792</v>
+        <v>32858</v>
       </c>
       <c r="F27" s="9" t="n">
         <v>1.3</v>
@@ -14995,10 +14915,10 @@
         <v>3.66</v>
       </c>
       <c r="J27" s="9" t="n">
-        <v>3.15</v>
+        <v>3.37</v>
       </c>
       <c r="K27" s="9" t="n">
-        <v>2.59</v>
+        <v>2.77</v>
       </c>
       <c r="L27" s="9" t="n"/>
     </row>
@@ -15024,7 +14944,7 @@
         </is>
       </c>
       <c r="E28" s="7" t="n">
-        <v>5097</v>
+        <v>4213</v>
       </c>
       <c r="F28" s="9" t="n">
         <v>0.34</v>
@@ -15039,10 +14959,10 @@
         <v>1.25</v>
       </c>
       <c r="J28" s="9" t="n">
-        <v>0.72</v>
+        <v>0.6</v>
       </c>
       <c r="K28" s="9" t="n">
-        <v>0.66</v>
+        <v>0.54</v>
       </c>
       <c r="L28" s="9" t="n"/>
     </row>
@@ -15068,7 +14988,7 @@
         </is>
       </c>
       <c r="E29" s="7" t="n">
-        <v>4397</v>
+        <v>3935</v>
       </c>
       <c r="F29" s="9" t="n">
         <v>0.4</v>
@@ -15083,10 +15003,10 @@
         <v>0.63</v>
       </c>
       <c r="J29" s="9" t="n">
-        <v>0.62</v>
+        <v>0.55</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>0.59</v>
+        <v>0.54</v>
       </c>
       <c r="L29" s="9" t="n"/>
     </row>
@@ -15112,7 +15032,7 @@
         </is>
       </c>
       <c r="E30" s="7" t="n">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="F30" s="9" t="n">
         <v>0.19</v>
@@ -15152,7 +15072,7 @@
         </is>
       </c>
       <c r="E31" s="7" t="n">
-        <v>380870</v>
+        <v>388618</v>
       </c>
       <c r="F31" s="9" t="n">
         <v>2.08</v>
@@ -15167,10 +15087,10 @@
         <v>3.94</v>
       </c>
       <c r="J31" s="9" t="n">
-        <v>4.81</v>
+        <v>4.91</v>
       </c>
       <c r="K31" s="9" t="n">
-        <v>4.33</v>
+        <v>4.41</v>
       </c>
       <c r="L31" s="9" t="n"/>
     </row>
@@ -15196,7 +15116,7 @@
         </is>
       </c>
       <c r="E32" s="7" t="n">
-        <v>182688</v>
+        <v>185233</v>
       </c>
       <c r="F32" s="9" t="n">
         <v>2.31</v>
@@ -15211,10 +15131,10 @@
         <v>2.79</v>
       </c>
       <c r="J32" s="9" t="n">
-        <v>4.44</v>
+        <v>4.5</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>4.1</v>
+        <v>4.14</v>
       </c>
       <c r="L32" s="9" t="n"/>
     </row>
@@ -15240,7 +15160,7 @@
         </is>
       </c>
       <c r="E33" s="7" t="n">
-        <v>16867</v>
+        <v>21662</v>
       </c>
       <c r="F33" s="9" t="n">
         <v>0.92</v>
@@ -15255,10 +15175,10 @@
         <v>0.63</v>
       </c>
       <c r="J33" s="9" t="n">
-        <v>0.92</v>
+        <v>1.19</v>
       </c>
       <c r="K33" s="9" t="n">
-        <v>0.89</v>
+        <v>1.14</v>
       </c>
       <c r="L33" s="9" t="n"/>
     </row>
@@ -15284,7 +15204,7 @@
         </is>
       </c>
       <c r="E34" s="7" t="n">
-        <v>41747</v>
+        <v>42820</v>
       </c>
       <c r="F34" s="9" t="n"/>
       <c r="G34" s="9" t="n">
@@ -15300,10 +15220,10 @@
         <v>1.31</v>
       </c>
       <c r="K34" s="9" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="L34" s="9" t="n">
         <v>1.47</v>
-      </c>
-      <c r="L34" s="9" t="n">
-        <v>1.42</v>
       </c>
     </row>
     <row r="35">
@@ -15328,7 +15248,7 @@
         </is>
       </c>
       <c r="E35" s="7" t="n">
-        <v>7804</v>
+        <v>7481</v>
       </c>
       <c r="F35" s="9" t="n"/>
       <c r="G35" s="9" t="n">
@@ -15344,10 +15264,10 @@
         <v>0.8</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>0.82</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="L35" s="9" t="n">
-        <v>0.79</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="36">
@@ -15372,7 +15292,7 @@
         </is>
       </c>
       <c r="E36" s="7" t="n">
-        <v>71495</v>
+        <v>63743</v>
       </c>
       <c r="F36" s="9" t="n">
         <v>0.8100000000000001</v>
@@ -15387,10 +15307,10 @@
         <v>1.26</v>
       </c>
       <c r="J36" s="9" t="n">
-        <v>1.39</v>
+        <v>1.28</v>
       </c>
       <c r="K36" s="9" t="n">
-        <v>1.28</v>
+        <v>1.17</v>
       </c>
       <c r="L36" s="9" t="n"/>
     </row>
@@ -15416,7 +15336,7 @@
         </is>
       </c>
       <c r="E37" s="7" t="n">
-        <v>27156</v>
+        <v>23992</v>
       </c>
       <c r="F37" s="9" t="n">
         <v>1.66</v>
@@ -15431,10 +15351,10 @@
         <v>2.17</v>
       </c>
       <c r="J37" s="9" t="n">
-        <v>1.75</v>
+        <v>1.54</v>
       </c>
       <c r="K37" s="9" t="n">
-        <v>1.54</v>
+        <v>1.36</v>
       </c>
       <c r="L37" s="9" t="n"/>
     </row>
@@ -15460,7 +15380,7 @@
         </is>
       </c>
       <c r="E38" s="7" t="n">
-        <v>14144</v>
+        <v>12624</v>
       </c>
       <c r="F38" s="9" t="n">
         <v>0.64</v>
@@ -15475,10 +15395,10 @@
         <v>1.35</v>
       </c>
       <c r="J38" s="9" t="n">
-        <v>0.83</v>
+        <v>0.74</v>
       </c>
       <c r="K38" s="9" t="n">
-        <v>0.72</v>
+        <v>0.65</v>
       </c>
       <c r="L38" s="9" t="n"/>
     </row>
@@ -15504,7 +15424,7 @@
         </is>
       </c>
       <c r="E39" s="7" t="n">
-        <v>192</v>
+        <v>172</v>
       </c>
       <c r="F39" s="9" t="n">
         <v>0.49</v>
@@ -15519,10 +15439,10 @@
         <v>0.59</v>
       </c>
       <c r="J39" s="9" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="K39" s="9" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="L39" s="9" t="n"/>
     </row>
@@ -15548,7 +15468,7 @@
         </is>
       </c>
       <c r="E40" s="7" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F40" s="9" t="n">
         <v>0.32</v>
@@ -15588,7 +15508,7 @@
         </is>
       </c>
       <c r="E41" s="7" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F41" s="9" t="n">
         <v>0.5</v>
@@ -15628,7 +15548,7 @@
         </is>
       </c>
       <c r="E42" s="7" t="n">
-        <v>62409</v>
+        <v>67287</v>
       </c>
       <c r="F42" s="9" t="n">
         <v>2.12</v>
@@ -15643,10 +15563,10 @@
         <v>3.17</v>
       </c>
       <c r="J42" s="9" t="n">
-        <v>3.52</v>
+        <v>3.79</v>
       </c>
       <c r="K42" s="9" t="n">
-        <v>3.23</v>
+        <v>3.49</v>
       </c>
       <c r="L42" s="9" t="n"/>
     </row>
@@ -16110,35 +16030,35 @@
         </is>
       </c>
       <c r="G6" s="17" t="n">
-        <v>479000</v>
+        <v>426000</v>
       </c>
       <c r="H6" s="17" t="n">
-        <v>31175.2</v>
+        <v>31055.56</v>
       </c>
       <c r="I6" s="17" t="n">
-        <v>115289.91</v>
+        <v>115189.12</v>
       </c>
       <c r="J6" s="18" t="n">
-        <v>24984976220000</v>
+        <v>25001127410000</v>
       </c>
       <c r="K6" s="18" t="n">
-        <v>3271299901206.478</v>
+        <v>3258745953990.666</v>
       </c>
       <c r="L6" s="18" t="n">
-        <v>12097690124766.46</v>
+        <v>12087113424237.14</v>
       </c>
       <c r="M6" s="17" t="n">
-        <v>15.36</v>
+        <v>13.72</v>
       </c>
       <c r="N6" s="17" t="n"/>
       <c r="O6" s="17" t="n">
-        <v>4.15</v>
+        <v>3.7</v>
       </c>
       <c r="P6" s="17" t="n">
-        <v>30.52</v>
+        <v>30.41</v>
       </c>
       <c r="Q6" s="17" t="n">
-        <v>2.01</v>
+        <v>1.79</v>
       </c>
       <c r="R6" s="17" t="inlineStr">
         <is>
@@ -16183,35 +16103,35 @@
         </is>
       </c>
       <c r="G7" s="17" t="n">
-        <v>479000</v>
+        <v>426000</v>
       </c>
       <c r="H7" s="17" t="n">
-        <v>35696.77</v>
+        <v>36045.37</v>
       </c>
       <c r="I7" s="17" t="n">
-        <v>145364.44</v>
+        <v>145557.34</v>
       </c>
       <c r="J7" s="18" t="n">
-        <v>26700164480000</v>
+        <v>26636528120000</v>
       </c>
       <c r="K7" s="18" t="n">
-        <v>3745761098939.979</v>
+        <v>3782340349158.058</v>
       </c>
       <c r="L7" s="18" t="n">
-        <v>15253493850623.39</v>
+        <v>15273735168402.8</v>
       </c>
       <c r="M7" s="17" t="n">
-        <v>13.42</v>
+        <v>11.82</v>
       </c>
       <c r="N7" s="17" t="n"/>
       <c r="O7" s="17" t="n">
-        <v>3.3</v>
+        <v>2.93</v>
       </c>
       <c r="P7" s="17" t="n">
-        <v>27.39</v>
+        <v>27.65</v>
       </c>
       <c r="Q7" s="17" t="n">
-        <v>1.88</v>
+        <v>1.68</v>
       </c>
       <c r="R7" s="17" t="inlineStr">
         <is>
@@ -16605,35 +16525,35 @@
         </is>
       </c>
       <c r="G13" s="17" t="n">
-        <v>85600</v>
+        <v>78800</v>
       </c>
       <c r="H13" s="17" t="n">
-        <v>6173.04</v>
+        <v>6260.09</v>
       </c>
       <c r="I13" s="17" t="n">
-        <v>26311.12</v>
+        <v>26398.17</v>
       </c>
       <c r="J13" s="18" t="n">
-        <v>15927238960000</v>
+        <v>15915300060000</v>
       </c>
       <c r="K13" s="18" t="n">
-        <v>1891401968679.605</v>
+        <v>1918073353572.456</v>
       </c>
       <c r="L13" s="18" t="n">
-        <v>8061653512729.605</v>
+        <v>8088324897622.456</v>
       </c>
       <c r="M13" s="17" t="n">
-        <v>13.87</v>
+        <v>12.59</v>
       </c>
       <c r="N13" s="17" t="n"/>
       <c r="O13" s="17" t="n">
-        <v>3.25</v>
+        <v>2.99</v>
       </c>
       <c r="P13" s="17" t="n">
-        <v>26.58</v>
+        <v>26.9</v>
       </c>
       <c r="Q13" s="17" t="n">
-        <v>1.65</v>
+        <v>1.52</v>
       </c>
       <c r="R13" s="17" t="inlineStr">
         <is>
@@ -16678,35 +16598,35 @@
         </is>
       </c>
       <c r="G14" s="17" t="n">
-        <v>85600</v>
+        <v>78800</v>
       </c>
       <c r="H14" s="17" t="n">
-        <v>6429.76</v>
+        <v>6373.09</v>
       </c>
       <c r="I14" s="17" t="n">
-        <v>32740.89</v>
+        <v>32771.26</v>
       </c>
       <c r="J14" s="18" t="n">
-        <v>15659930410000</v>
+        <v>15562979030000</v>
       </c>
       <c r="K14" s="18" t="n">
-        <v>1970061602673.868</v>
+        <v>1952697553211.36</v>
       </c>
       <c r="L14" s="18" t="n">
-        <v>10031715115403.47</v>
+        <v>10041022450833.82</v>
       </c>
       <c r="M14" s="17" t="n">
-        <v>13.31</v>
+        <v>12.36</v>
       </c>
       <c r="N14" s="17" t="n"/>
       <c r="O14" s="17" t="n">
-        <v>2.61</v>
+        <v>2.4</v>
       </c>
       <c r="P14" s="17" t="n">
-        <v>21.78</v>
+        <v>21.54</v>
       </c>
       <c r="Q14" s="17" t="n">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="R14" s="17" t="inlineStr">
         <is>
@@ -17098,35 +17018,35 @@
         </is>
       </c>
       <c r="G20" s="17" t="n">
-        <v>21400</v>
+        <v>19960</v>
       </c>
       <c r="H20" s="17" t="n">
-        <v>1183.96</v>
+        <v>1171.19</v>
       </c>
       <c r="I20" s="17" t="n">
-        <v>6041.35</v>
+        <v>6028.58</v>
       </c>
       <c r="J20" s="18" t="n">
-        <v>12886285050000</v>
+        <v>12851781350000</v>
       </c>
       <c r="K20" s="18" t="n">
-        <v>1011283343129.024</v>
+        <v>1000370888244.291</v>
       </c>
       <c r="L20" s="18" t="n">
-        <v>5160222652769.023</v>
+        <v>5149310197884.291</v>
       </c>
       <c r="M20" s="17" t="n">
-        <v>18.07</v>
+        <v>17.04</v>
       </c>
       <c r="N20" s="17" t="n"/>
       <c r="O20" s="17" t="n">
-        <v>3.54</v>
+        <v>3.31</v>
       </c>
       <c r="P20" s="17" t="n">
-        <v>21.73</v>
+        <v>21.52</v>
       </c>
       <c r="Q20" s="17" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="R20" s="17" t="inlineStr">
         <is>
@@ -17171,35 +17091,35 @@
         </is>
       </c>
       <c r="G21" s="17" t="n">
-        <v>21400</v>
+        <v>19960</v>
       </c>
       <c r="H21" s="17" t="n">
-        <v>1703.54</v>
+        <v>1699.61</v>
       </c>
       <c r="I21" s="17" t="n">
-        <v>7744.89</v>
+        <v>7728.18</v>
       </c>
       <c r="J21" s="18" t="n">
-        <v>14798025900000</v>
+        <v>14789024770000</v>
       </c>
       <c r="K21" s="18" t="n">
-        <v>1455080851728.347</v>
+        <v>1451720880236.928</v>
       </c>
       <c r="L21" s="18" t="n">
-        <v>6615303504497.371</v>
+        <v>6601031078121.219</v>
       </c>
       <c r="M21" s="17" t="n">
-        <v>12.56</v>
+        <v>11.74</v>
       </c>
       <c r="N21" s="17" t="n"/>
       <c r="O21" s="17" t="n">
-        <v>2.76</v>
+        <v>2.58</v>
       </c>
       <c r="P21" s="17" t="n">
         <v>24.71</v>
       </c>
       <c r="Q21" s="17" t="n">
-        <v>1.24</v>
+        <v>1.15</v>
       </c>
       <c r="R21" s="17" t="inlineStr">
         <is>
@@ -17595,35 +17515,35 @@
         </is>
       </c>
       <c r="G27" s="17" t="n">
-        <v>365500</v>
+        <v>326000</v>
       </c>
       <c r="H27" s="17" t="n">
-        <v>51760.25</v>
+        <v>52293.98</v>
       </c>
       <c r="I27" s="17" t="n">
-        <v>229984.8</v>
+        <v>230418.94</v>
       </c>
       <c r="J27" s="18" t="n">
-        <v>34925797590000</v>
+        <v>34898890079999</v>
       </c>
       <c r="K27" s="18" t="n">
-        <v>3660207210316.02</v>
+        <v>3697949729785.92</v>
       </c>
       <c r="L27" s="18" t="n">
-        <v>16263290290871.05</v>
+        <v>16293990056207.87</v>
       </c>
       <c r="M27" s="17" t="n">
-        <v>7.06</v>
+        <v>6.23</v>
       </c>
       <c r="N27" s="17" t="n"/>
       <c r="O27" s="17" t="n">
-        <v>1.59</v>
+        <v>1.41</v>
       </c>
       <c r="P27" s="17" t="n">
-        <v>24.77</v>
+        <v>25</v>
       </c>
       <c r="Q27" s="17" t="n">
-        <v>0.74</v>
+        <v>0.66</v>
       </c>
       <c r="R27" s="17" t="inlineStr">
         <is>
@@ -17668,35 +17588,35 @@
         </is>
       </c>
       <c r="G28" s="17" t="n">
-        <v>365500</v>
+        <v>326000</v>
       </c>
       <c r="H28" s="17" t="n">
-        <v>60133.68</v>
+        <v>61762.38</v>
       </c>
       <c r="I28" s="17" t="n">
-        <v>278897.54</v>
+        <v>280656.46</v>
       </c>
       <c r="J28" s="18" t="n">
-        <v>37512995060000</v>
+        <v>37153195060000</v>
       </c>
       <c r="K28" s="18" t="n">
-        <v>4252331214596.92</v>
+        <v>4367503496046.25</v>
       </c>
       <c r="L28" s="18" t="n">
-        <v>19722136500824.19</v>
+        <v>19846517399891.89</v>
       </c>
       <c r="M28" s="17" t="n">
-        <v>6.08</v>
+        <v>5.28</v>
       </c>
       <c r="N28" s="17" t="n"/>
       <c r="O28" s="17" t="n">
-        <v>1.31</v>
+        <v>1.16</v>
       </c>
       <c r="P28" s="17" t="n">
-        <v>23.63</v>
+        <v>24.17</v>
       </c>
       <c r="Q28" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.62</v>
       </c>
       <c r="R28" s="17" t="inlineStr">
         <is>
@@ -18064,35 +17984,35 @@
         </is>
       </c>
       <c r="G34" s="17" t="n">
-        <v>47300</v>
+        <v>45850</v>
       </c>
       <c r="H34" s="17" t="n">
-        <v>7317.5</v>
+        <v>7656.2</v>
       </c>
       <c r="I34" s="17" t="n">
-        <v>35650.28</v>
+        <v>35978.38</v>
       </c>
       <c r="J34" s="18" t="n">
-        <v>1338333330000</v>
+        <v>1341560000000</v>
       </c>
       <c r="K34" s="18" t="n">
-        <v>279867388060</v>
+        <v>292821413934.4</v>
       </c>
       <c r="L34" s="18" t="n">
-        <v>1363491609003.722</v>
+        <v>1376040173868.253</v>
       </c>
       <c r="M34" s="17" t="n">
-        <v>6.46</v>
+        <v>5.99</v>
       </c>
       <c r="N34" s="17" t="n"/>
       <c r="O34" s="17" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="P34" s="17" t="n">
-        <v>22.79</v>
+        <v>23.73</v>
       </c>
       <c r="Q34" s="17" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="R34" s="17" t="inlineStr">
         <is>
@@ -18137,35 +18057,35 @@
         </is>
       </c>
       <c r="G35" s="17" t="n">
-        <v>47300</v>
+        <v>45850</v>
       </c>
       <c r="H35" s="17" t="n">
-        <v>7666.2</v>
+        <v>7804.33</v>
       </c>
       <c r="I35" s="17" t="n">
-        <v>43076.52</v>
+        <v>43538.43</v>
       </c>
       <c r="J35" s="18" t="n">
-        <v>1367800000000</v>
+        <v>1372216670000</v>
       </c>
       <c r="K35" s="18" t="n">
-        <v>293203877054.4</v>
+        <v>298486973993.052</v>
       </c>
       <c r="L35" s="18" t="n">
-        <v>1647518204706.319</v>
+        <v>1665184505575.323</v>
       </c>
       <c r="M35" s="17" t="n">
-        <v>6.17</v>
+        <v>5.87</v>
       </c>
       <c r="N35" s="17" t="n"/>
       <c r="O35" s="17" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="P35" s="17" t="n">
-        <v>19.48</v>
+        <v>19.63</v>
       </c>
       <c r="Q35" s="17" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="R35" s="17" t="inlineStr">
         <is>
@@ -18557,7 +18477,7 @@
         </is>
       </c>
       <c r="G41" s="17" t="n">
-        <v>15990</v>
+        <v>15320</v>
       </c>
       <c r="H41" s="17" t="n"/>
       <c r="I41" s="17" t="n"/>
@@ -18614,7 +18534,7 @@
         </is>
       </c>
       <c r="G42" s="17" t="n">
-        <v>15990</v>
+        <v>15320</v>
       </c>
       <c r="H42" s="17" t="n"/>
       <c r="I42" s="17" t="n"/>
@@ -19021,30 +18941,30 @@
       </c>
       <c r="G48" s="17" t="n"/>
       <c r="H48" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.55</v>
       </c>
       <c r="I48" s="17" t="n">
-        <v>3.63</v>
+        <v>3.62</v>
       </c>
       <c r="J48" s="18" t="n">
-        <v>9405554850</v>
+        <v>9372494660</v>
       </c>
       <c r="K48" s="18" t="n">
-        <v>180743486.48528</v>
+        <v>177351465.4062</v>
       </c>
       <c r="L48" s="18" t="n">
-        <v>1178011486.48528</v>
+        <v>1174619465.4062</v>
       </c>
       <c r="M48" s="17" t="n"/>
       <c r="N48" s="17" t="n"/>
       <c r="O48" s="17" t="n">
-        <v>3.8</v>
+        <v>3.71</v>
       </c>
       <c r="P48" s="17" t="n">
-        <v>16.62</v>
+        <v>16.33</v>
       </c>
       <c r="Q48" s="17" t="n">
-        <v>0.48</v>
+        <v>0.47</v>
       </c>
       <c r="R48" s="17" t="inlineStr">
         <is>
@@ -19090,30 +19010,30 @@
       </c>
       <c r="G49" s="17" t="n"/>
       <c r="H49" s="17" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.83</v>
       </c>
       <c r="I49" s="17" t="n">
-        <v>4.44</v>
+        <v>4.45</v>
       </c>
       <c r="J49" s="18" t="n">
-        <v>10500143300</v>
+        <v>10522629720</v>
       </c>
       <c r="K49" s="18" t="n">
-        <v>261710964.78592</v>
+        <v>268660392.29306</v>
       </c>
       <c r="L49" s="18" t="n">
-        <v>1439722451.2712</v>
+        <v>1443279857.69926</v>
       </c>
       <c r="M49" s="17" t="n"/>
       <c r="N49" s="17" t="n"/>
       <c r="O49" s="17" t="n">
-        <v>3.11</v>
+        <v>3.02</v>
       </c>
       <c r="P49" s="17" t="n">
-        <v>20</v>
+        <v>20.52</v>
       </c>
       <c r="Q49" s="17" t="n">
-        <v>0.43</v>
+        <v>0.41</v>
       </c>
       <c r="R49" s="17" t="inlineStr">
         <is>
@@ -19491,35 +19411,35 @@
         </is>
       </c>
       <c r="G55" s="17" t="n">
-        <v>247000</v>
+        <v>233500</v>
       </c>
       <c r="H55" s="17" t="n">
-        <v>7741.59</v>
+        <v>7754.19</v>
       </c>
       <c r="I55" s="17" t="n">
-        <v>22557.28</v>
+        <v>22564.05</v>
       </c>
       <c r="J55" s="18" t="n">
-        <v>2320660330000</v>
+        <v>2340035660000</v>
       </c>
       <c r="K55" s="18" t="n">
-        <v>347065994047.99</v>
+        <v>347630913700.325</v>
       </c>
       <c r="L55" s="18" t="n">
-        <v>1011272827260.795</v>
+        <v>1011576471573.925</v>
       </c>
       <c r="M55" s="17" t="n">
-        <v>31.91</v>
+        <v>30.11</v>
       </c>
       <c r="N55" s="17" t="n"/>
       <c r="O55" s="17" t="n">
-        <v>10.95</v>
+        <v>10.35</v>
       </c>
       <c r="P55" s="17" t="n">
-        <v>37.81</v>
+        <v>37.86</v>
       </c>
       <c r="Q55" s="17" t="n">
-        <v>4.77</v>
+        <v>4.47</v>
       </c>
       <c r="R55" s="17" t="inlineStr">
         <is>
@@ -19564,35 +19484,35 @@
         </is>
       </c>
       <c r="G56" s="17" t="n">
-        <v>247000</v>
+        <v>233500</v>
       </c>
       <c r="H56" s="17" t="n">
-        <v>9447.08</v>
+        <v>9331.65</v>
       </c>
       <c r="I56" s="17" t="n">
-        <v>27635.08</v>
+        <v>27579.81</v>
       </c>
       <c r="J56" s="18" t="n">
-        <v>2675633640000</v>
+        <v>2664838750000</v>
       </c>
       <c r="K56" s="18" t="n">
-        <v>423524984095.1251</v>
+        <v>418350416915.42</v>
       </c>
       <c r="L56" s="18" t="n">
-        <v>1238917506211.924</v>
+        <v>1236439820665.963</v>
       </c>
       <c r="M56" s="17" t="n">
-        <v>26.15</v>
+        <v>25.02</v>
       </c>
       <c r="N56" s="17" t="n"/>
       <c r="O56" s="17" t="n">
-        <v>8.94</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="P56" s="17" t="n">
-        <v>37.64</v>
+        <v>37.22</v>
       </c>
       <c r="Q56" s="17" t="n">
-        <v>4.14</v>
+        <v>3.93</v>
       </c>
       <c r="R56" s="17" t="inlineStr">
         <is>
@@ -19990,35 +19910,35 @@
         </is>
       </c>
       <c r="G62" s="17" t="n">
-        <v>52500</v>
+        <v>49100</v>
       </c>
       <c r="H62" s="17" t="n">
-        <v>3930.5</v>
+        <v>3759.75</v>
       </c>
       <c r="I62" s="17" t="n">
-        <v>18343.56</v>
+        <v>18172.81</v>
       </c>
       <c r="J62" s="18" t="n">
-        <v>608766670000</v>
+        <v>607125000000</v>
       </c>
       <c r="K62" s="18" t="n">
-        <v>133328349626.5</v>
+        <v>127536258111.75</v>
       </c>
       <c r="L62" s="18" t="n">
-        <v>622240560926.5</v>
+        <v>616448469411.75</v>
       </c>
       <c r="M62" s="17" t="n">
-        <v>13.36</v>
+        <v>13.06</v>
       </c>
       <c r="N62" s="17" t="n"/>
       <c r="O62" s="17" t="n">
-        <v>2.86</v>
+        <v>2.7</v>
       </c>
       <c r="P62" s="17" t="n">
-        <v>24</v>
+        <v>23.08</v>
       </c>
       <c r="Q62" s="17" t="n">
-        <v>2.93</v>
+        <v>2.74</v>
       </c>
       <c r="R62" s="17" t="inlineStr">
         <is>
@@ -20063,35 +19983,35 @@
         </is>
       </c>
       <c r="G63" s="17" t="n">
-        <v>52500</v>
+        <v>49100</v>
       </c>
       <c r="H63" s="17" t="n">
-        <v>5446</v>
+        <v>5356.5</v>
       </c>
       <c r="I63" s="17" t="n">
-        <v>23789.56</v>
+        <v>23529.31</v>
       </c>
       <c r="J63" s="18" t="n">
-        <v>759500000000</v>
+        <v>757725000000</v>
       </c>
       <c r="K63" s="18" t="n">
-        <v>184736341958</v>
+        <v>181700370124.5</v>
       </c>
       <c r="L63" s="18" t="n">
-        <v>806976902884.5</v>
+        <v>798148839536.25</v>
       </c>
       <c r="M63" s="17" t="n">
-        <v>9.640000000000001</v>
+        <v>9.17</v>
       </c>
       <c r="N63" s="17" t="n"/>
       <c r="O63" s="17" t="n">
-        <v>2.21</v>
+        <v>2.09</v>
       </c>
       <c r="P63" s="17" t="n">
-        <v>25.85</v>
+        <v>25.69</v>
       </c>
       <c r="Q63" s="17" t="n">
-        <v>2.34</v>
+        <v>2.2</v>
       </c>
       <c r="R63" s="17" t="inlineStr">
         <is>
@@ -20483,35 +20403,35 @@
         </is>
       </c>
       <c r="G69" s="17" t="n">
-        <v>50300</v>
+        <v>48600</v>
       </c>
       <c r="H69" s="17" t="n">
-        <v>2281.89</v>
+        <v>2362.53</v>
       </c>
       <c r="I69" s="17" t="n">
-        <v>8947.75</v>
+        <v>9028.389999999999</v>
       </c>
       <c r="J69" s="18" t="n">
-        <v>1631819770000</v>
+        <v>1619261200000</v>
       </c>
       <c r="K69" s="18" t="n">
-        <v>190367860690.936</v>
+        <v>197095287490.7825</v>
       </c>
       <c r="L69" s="18" t="n">
-        <v>746470760610.936</v>
+        <v>753198187410.7825</v>
       </c>
       <c r="M69" s="17" t="n">
-        <v>22.04</v>
+        <v>20.57</v>
       </c>
       <c r="N69" s="17" t="n"/>
       <c r="O69" s="17" t="n">
-        <v>5.62</v>
+        <v>5.38</v>
       </c>
       <c r="P69" s="17" t="n">
-        <v>29.23</v>
+        <v>30.11</v>
       </c>
       <c r="Q69" s="17" t="n">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="R69" s="17" t="inlineStr">
         <is>
@@ -20556,35 +20476,35 @@
         </is>
       </c>
       <c r="G70" s="17" t="n">
-        <v>50300</v>
+        <v>48600</v>
       </c>
       <c r="H70" s="17" t="n">
-        <v>3484.13</v>
+        <v>3467.89</v>
       </c>
       <c r="I70" s="17" t="n">
-        <v>12431.88</v>
+        <v>12496.28</v>
       </c>
       <c r="J70" s="18" t="n">
-        <v>2185487500000</v>
+        <v>2203498750000</v>
       </c>
       <c r="K70" s="18" t="n">
-        <v>290665459314.871</v>
+        <v>289310895588.183</v>
       </c>
       <c r="L70" s="18" t="n">
-        <v>1037136219925.807</v>
+        <v>1042509082998.965</v>
       </c>
       <c r="M70" s="17" t="n">
-        <v>14.44</v>
+        <v>14.01</v>
       </c>
       <c r="N70" s="17" t="n"/>
       <c r="O70" s="17" t="n">
-        <v>4.05</v>
+        <v>3.89</v>
       </c>
       <c r="P70" s="17" t="n">
-        <v>32.59</v>
+        <v>32.22</v>
       </c>
       <c r="Q70" s="17" t="n">
-        <v>1.92</v>
+        <v>1.84</v>
       </c>
       <c r="R70" s="17" t="inlineStr">
         <is>
@@ -20980,35 +20900,35 @@
         </is>
       </c>
       <c r="G76" s="17" t="n">
-        <v>21700</v>
+        <v>20550</v>
       </c>
       <c r="H76" s="17" t="n">
-        <v>2393.79</v>
+        <v>2370.59</v>
       </c>
       <c r="I76" s="17" t="n">
-        <v>13534.02</v>
+        <v>13514.49</v>
       </c>
       <c r="J76" s="18" t="n">
-        <v>956157510000</v>
+        <v>946557510000</v>
       </c>
       <c r="K76" s="18" t="n">
-        <v>120569796623.7908</v>
+        <v>119401264916.5908</v>
       </c>
       <c r="L76" s="18" t="n">
-        <v>681678021001.8715</v>
+        <v>680694234169.2651</v>
       </c>
       <c r="M76" s="17" t="n">
-        <v>9.07</v>
+        <v>8.67</v>
       </c>
       <c r="N76" s="17" t="n"/>
       <c r="O76" s="17" t="n">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
       <c r="P76" s="17" t="n">
-        <v>19.11</v>
+        <v>18.94</v>
       </c>
       <c r="Q76" s="17" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="R76" s="17" t="inlineStr">
         <is>
@@ -21053,35 +20973,35 @@
         </is>
       </c>
       <c r="G77" s="17" t="n">
-        <v>21700</v>
+        <v>20550</v>
       </c>
       <c r="H77" s="17" t="n">
-        <v>2818.93</v>
+        <v>2816.13</v>
       </c>
       <c r="I77" s="17" t="n">
-        <v>15907.28</v>
+        <v>15885.39</v>
       </c>
       <c r="J77" s="18" t="n">
-        <v>1016432640000</v>
+        <v>1000192640000</v>
       </c>
       <c r="K77" s="18" t="n">
-        <v>141983281187.9196</v>
+        <v>141842251499.1196</v>
       </c>
       <c r="L77" s="18" t="n">
-        <v>801213744014.1482</v>
+        <v>800111224287.9514</v>
       </c>
       <c r="M77" s="17" t="n">
-        <v>7.7</v>
+        <v>7.3</v>
       </c>
       <c r="N77" s="17" t="n"/>
       <c r="O77" s="17" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="P77" s="17" t="n">
-        <v>19.15</v>
+        <v>19.16</v>
       </c>
       <c r="Q77" s="17" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="R77" s="17" t="inlineStr">
         <is>
@@ -21479,7 +21399,7 @@
         </is>
       </c>
       <c r="G83" s="17" t="n">
-        <v>16790</v>
+        <v>16370</v>
       </c>
       <c r="H83" s="17" t="n">
         <v>2442</v>
@@ -21497,17 +21417,17 @@
         <v>331992443278</v>
       </c>
       <c r="M83" s="17" t="n">
-        <v>6.88</v>
+        <v>6.7</v>
       </c>
       <c r="N83" s="17" t="n"/>
       <c r="O83" s="17" t="n">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="P83" s="17" t="n">
         <v>24.74</v>
       </c>
       <c r="Q83" s="17" t="n">
-        <v>0.59</v>
+        <v>0.57</v>
       </c>
       <c r="R83" s="17" t="inlineStr">
         <is>
@@ -21552,7 +21472,7 @@
         </is>
       </c>
       <c r="G84" s="17" t="n">
-        <v>16790</v>
+        <v>16370</v>
       </c>
       <c r="H84" s="17" t="n">
         <v>2901</v>
@@ -21570,17 +21490,17 @@
         <v>418828450507</v>
       </c>
       <c r="M84" s="17" t="n">
-        <v>5.79</v>
+        <v>5.64</v>
       </c>
       <c r="N84" s="17" t="n"/>
       <c r="O84" s="17" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="P84" s="17" t="n">
         <v>23.13</v>
       </c>
       <c r="Q84" s="17" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="R84" s="17" t="inlineStr">
         <is>
@@ -21978,35 +21898,35 @@
         </is>
       </c>
       <c r="G90" s="17" t="n">
-        <v>130500</v>
+        <v>133500</v>
       </c>
       <c r="H90" s="17" t="n">
-        <v>2345.72</v>
+        <v>2560.73</v>
       </c>
       <c r="I90" s="17" t="n">
-        <v>20476.64</v>
+        <v>20632.55</v>
       </c>
       <c r="J90" s="18" t="n">
-        <v>5363531540000</v>
+        <v>5345140170000</v>
       </c>
       <c r="K90" s="18" t="n">
-        <v>228649113041.826</v>
+        <v>249606972615.1071</v>
       </c>
       <c r="L90" s="18" t="n">
-        <v>1995963043226.628</v>
+        <v>2011159587203.214</v>
       </c>
       <c r="M90" s="17" t="n">
-        <v>55.63</v>
+        <v>52.13</v>
       </c>
       <c r="N90" s="17" t="n"/>
       <c r="O90" s="17" t="n">
-        <v>6.37</v>
+        <v>6.47</v>
       </c>
       <c r="P90" s="17" t="n">
-        <v>11.95</v>
+        <v>13</v>
       </c>
       <c r="Q90" s="17" t="n">
-        <v>2.37</v>
+        <v>2.43</v>
       </c>
       <c r="R90" s="17" t="inlineStr">
         <is>
@@ -22051,35 +21971,35 @@
         </is>
       </c>
       <c r="G91" s="17" t="n">
-        <v>130500</v>
+        <v>133500</v>
       </c>
       <c r="H91" s="17" t="n">
-        <v>4522.94</v>
+        <v>4548.68</v>
       </c>
       <c r="I91" s="17" t="n">
-        <v>23756.23</v>
+        <v>23930.79</v>
       </c>
       <c r="J91" s="18" t="n">
-        <v>6650915760000</v>
+        <v>6644436400000</v>
       </c>
       <c r="K91" s="18" t="n">
-        <v>440874060454.58</v>
+        <v>443383264658.974</v>
       </c>
       <c r="L91" s="18" t="n">
-        <v>2315640824462.244</v>
+        <v>2332656792407.436</v>
       </c>
       <c r="M91" s="17" t="n">
-        <v>28.85</v>
+        <v>29.35</v>
       </c>
       <c r="N91" s="17" t="n"/>
       <c r="O91" s="17" t="n">
-        <v>5.49</v>
+        <v>5.58</v>
       </c>
       <c r="P91" s="17" t="n">
-        <v>20.45</v>
+        <v>20.41</v>
       </c>
       <c r="Q91" s="17" t="n">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="R91" s="17" t="inlineStr">
         <is>
@@ -22477,35 +22397,35 @@
         </is>
       </c>
       <c r="G97" s="17" t="n">
-        <v>1081000</v>
+        <v>1072000</v>
       </c>
       <c r="H97" s="17" t="n">
-        <v>48183.27</v>
+        <v>47865.61</v>
       </c>
       <c r="I97" s="17" t="n">
-        <v>228115.29</v>
+        <v>227852.43</v>
       </c>
       <c r="J97" s="18" t="n">
-        <v>32193552050000</v>
+        <v>32295572280000</v>
       </c>
       <c r="K97" s="18" t="n">
-        <v>2478970997723.124</v>
+        <v>2462627621380.68</v>
       </c>
       <c r="L97" s="18" t="n">
-        <v>11736255268615.88</v>
+        <v>11722731124692.51</v>
       </c>
       <c r="M97" s="17" t="n">
-        <v>22.44</v>
+        <v>22.4</v>
       </c>
       <c r="N97" s="17" t="n"/>
       <c r="O97" s="17" t="n">
-        <v>4.74</v>
+        <v>4.7</v>
       </c>
       <c r="P97" s="17" t="n">
-        <v>23.15</v>
+        <v>23.01</v>
       </c>
       <c r="Q97" s="17" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="R97" s="17" t="inlineStr">
         <is>
@@ -22550,35 +22470,35 @@
         </is>
       </c>
       <c r="G98" s="17" t="n">
-        <v>1081000</v>
+        <v>1072000</v>
       </c>
       <c r="H98" s="17" t="n">
-        <v>59324.66</v>
+        <v>59474.45</v>
       </c>
       <c r="I98" s="17" t="n">
-        <v>277206.44</v>
+        <v>277067.53</v>
       </c>
       <c r="J98" s="18" t="n">
-        <v>34591886820000</v>
+        <v>34673929040000</v>
       </c>
       <c r="K98" s="18" t="n">
-        <v>3052181649716.928</v>
+        <v>3059888369466.6</v>
       </c>
       <c r="L98" s="18" t="n">
-        <v>14261935583756.64</v>
+        <v>14254788750426.12</v>
       </c>
       <c r="M98" s="17" t="n">
-        <v>18.22</v>
+        <v>18.02</v>
       </c>
       <c r="N98" s="17" t="n"/>
       <c r="O98" s="17" t="n">
-        <v>3.9</v>
+        <v>3.87</v>
       </c>
       <c r="P98" s="17" t="n">
-        <v>23.48</v>
+        <v>23.56</v>
       </c>
       <c r="Q98" s="17" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="R98" s="17" t="inlineStr">
         <is>
@@ -22976,35 +22896,35 @@
         </is>
       </c>
       <c r="G104" s="17" t="n">
-        <v>678000</v>
+        <v>762000</v>
       </c>
       <c r="H104" s="17" t="n">
-        <v>16731.12</v>
+        <v>16689.24</v>
       </c>
       <c r="I104" s="17" t="n">
-        <v>78431.64999999999</v>
+        <v>78399.19</v>
       </c>
       <c r="J104" s="18" t="n">
-        <v>5160017030000</v>
+        <v>5151126660000</v>
       </c>
       <c r="K104" s="18" t="n">
-        <v>365495499180</v>
+        <v>364580707491</v>
       </c>
       <c r="L104" s="18" t="n">
-        <v>1713358961864.5</v>
+        <v>1712649998305.525</v>
       </c>
       <c r="M104" s="17" t="n">
-        <v>40.52</v>
+        <v>45.66</v>
       </c>
       <c r="N104" s="17" t="n"/>
       <c r="O104" s="17" t="n">
-        <v>8.640000000000001</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="P104" s="17" t="n">
-        <v>23.25</v>
+        <v>23.2</v>
       </c>
       <c r="Q104" s="17" t="n">
-        <v>2.87</v>
+        <v>3.23</v>
       </c>
       <c r="R104" s="17" t="inlineStr">
         <is>
@@ -23049,35 +22969,35 @@
         </is>
       </c>
       <c r="G105" s="17" t="n">
-        <v>678000</v>
+        <v>762000</v>
       </c>
       <c r="H105" s="17" t="n">
-        <v>24106.6</v>
+        <v>24164.56</v>
       </c>
       <c r="I105" s="17" t="n">
-        <v>97114.25999999999</v>
+        <v>97126.73</v>
       </c>
       <c r="J105" s="18" t="n">
-        <v>6160377260000</v>
+        <v>6165278460000</v>
       </c>
       <c r="K105" s="18" t="n">
-        <v>526614616269</v>
+        <v>527880898030.5001</v>
       </c>
       <c r="L105" s="18" t="n">
-        <v>2121485289472.975</v>
+        <v>2121757694279.163</v>
       </c>
       <c r="M105" s="17" t="n">
-        <v>28.13</v>
+        <v>31.53</v>
       </c>
       <c r="N105" s="17" t="n"/>
       <c r="O105" s="17" t="n">
-        <v>6.98</v>
+        <v>7.85</v>
       </c>
       <c r="P105" s="17" t="n">
-        <v>27.46</v>
+        <v>27.53</v>
       </c>
       <c r="Q105" s="17" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="R105" s="17" t="inlineStr">
         <is>
@@ -23473,35 +23393,35 @@
         </is>
       </c>
       <c r="G111" s="17" t="n">
-        <v>70900</v>
+        <v>82900</v>
       </c>
       <c r="H111" s="17" t="n">
-        <v>790.5</v>
+        <v>1029.25</v>
       </c>
       <c r="I111" s="17" t="n">
-        <v>26332.55</v>
+        <v>26453.34</v>
       </c>
       <c r="J111" s="18" t="n">
-        <v>4471337600000</v>
+        <v>4503822400000</v>
       </c>
       <c r="K111" s="18" t="n">
-        <v>147818172820.5</v>
+        <v>192462813884.25</v>
       </c>
       <c r="L111" s="18" t="n">
-        <v>4924009921049.891</v>
+        <v>4946595644964.042</v>
       </c>
       <c r="M111" s="17" t="n">
-        <v>89.69</v>
+        <v>80.54000000000001</v>
       </c>
       <c r="N111" s="17" t="n"/>
       <c r="O111" s="17" t="n">
-        <v>2.69</v>
+        <v>3.13</v>
       </c>
       <c r="P111" s="17" t="n">
-        <v>3.02</v>
+        <v>3.93</v>
       </c>
       <c r="Q111" s="17" t="n">
-        <v>2.97</v>
+        <v>3.44</v>
       </c>
       <c r="R111" s="17" t="inlineStr">
         <is>
@@ -23546,35 +23466,35 @@
         </is>
       </c>
       <c r="G112" s="17" t="n">
-        <v>70900</v>
+        <v>82900</v>
       </c>
       <c r="H112" s="17" t="n">
-        <v>2329</v>
+        <v>2312.11</v>
       </c>
       <c r="I112" s="17" t="n">
-        <v>27510.79</v>
+        <v>27623.03</v>
       </c>
       <c r="J112" s="18" t="n">
-        <v>5110915690000</v>
+        <v>5031334880000</v>
       </c>
       <c r="K112" s="18" t="n">
-        <v>435507304869</v>
+        <v>432349175683.9709</v>
       </c>
       <c r="L112" s="18" t="n">
-        <v>5144333066583.118</v>
+        <v>5165321092942.562</v>
       </c>
       <c r="M112" s="17" t="n">
-        <v>30.44</v>
+        <v>35.85</v>
       </c>
       <c r="N112" s="17" t="n"/>
       <c r="O112" s="17" t="n">
-        <v>2.58</v>
+        <v>3</v>
       </c>
       <c r="P112" s="17" t="n">
-        <v>8.65</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="Q112" s="17" t="n">
-        <v>2.59</v>
+        <v>3.08</v>
       </c>
       <c r="R112" s="17" t="inlineStr">
         <is>
@@ -23972,35 +23892,35 @@
         </is>
       </c>
       <c r="G118" s="17" t="n">
-        <v>124100</v>
+        <v>116500</v>
       </c>
       <c r="H118" s="17" t="n">
-        <v>8043.6</v>
+        <v>8028.92</v>
       </c>
       <c r="I118" s="17" t="n">
-        <v>35602.36</v>
+        <v>35588.86</v>
       </c>
       <c r="J118" s="18" t="n">
-        <v>6769708300000</v>
+        <v>6783226530000</v>
       </c>
       <c r="K118" s="18" t="n">
-        <v>877897220830.5325</v>
+        <v>876294411686.681</v>
       </c>
       <c r="L118" s="18" t="n">
-        <v>3885722740488.56</v>
+        <v>3884249919156.658</v>
       </c>
       <c r="M118" s="17" t="n">
-        <v>15.43</v>
+        <v>14.51</v>
       </c>
       <c r="N118" s="17" t="n"/>
       <c r="O118" s="17" t="n">
-        <v>3.49</v>
+        <v>3.27</v>
       </c>
       <c r="P118" s="17" t="n">
-        <v>25.21</v>
+        <v>25.17</v>
       </c>
       <c r="Q118" s="17" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="R118" s="17" t="inlineStr">
         <is>
@@ -24045,35 +23965,35 @@
         </is>
       </c>
       <c r="G119" s="17" t="n">
-        <v>124100</v>
+        <v>116500</v>
       </c>
       <c r="H119" s="17" t="n">
-        <v>11099.67</v>
+        <v>10984.8</v>
       </c>
       <c r="I119" s="17" t="n">
-        <v>45801.84</v>
+        <v>45682.79</v>
       </c>
       <c r="J119" s="18" t="n">
-        <v>8088418350000</v>
+        <v>8074396330000</v>
       </c>
       <c r="K119" s="18" t="n">
-        <v>1211443217058.724</v>
+        <v>1198905932719.521</v>
       </c>
       <c r="L119" s="18" t="n">
-        <v>4998917919912.48</v>
+        <v>4985924587926.061</v>
       </c>
       <c r="M119" s="17" t="n">
-        <v>11.18</v>
+        <v>10.61</v>
       </c>
       <c r="N119" s="17" t="n"/>
       <c r="O119" s="17" t="n">
-        <v>2.71</v>
+        <v>2.55</v>
       </c>
       <c r="P119" s="17" t="n">
-        <v>27.27</v>
+        <v>27.03</v>
       </c>
       <c r="Q119" s="17" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="R119" s="17" t="inlineStr">
         <is>
@@ -24470,36 +24390,32 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G125" s="17" t="n">
-        <v>524.1900000000001</v>
-      </c>
+      <c r="G125" s="17" t="n"/>
       <c r="H125" s="17" t="n">
-        <v>30.46</v>
+        <v>30.48</v>
       </c>
       <c r="I125" s="17" t="n">
-        <v>44.48</v>
+        <v>44.49</v>
       </c>
       <c r="J125" s="18" t="n">
-        <v>80954417760</v>
+        <v>81010217760</v>
       </c>
       <c r="K125" s="18" t="n">
-        <v>6974888870</v>
+        <v>6980041370</v>
       </c>
       <c r="L125" s="18" t="n">
-        <v>10185427301.729</v>
-      </c>
-      <c r="M125" s="17" t="n">
-        <v>17.21</v>
-      </c>
+        <v>10187986548.479</v>
+      </c>
+      <c r="M125" s="17" t="n"/>
       <c r="N125" s="17" t="n"/>
       <c r="O125" s="17" t="n">
-        <v>11.79</v>
+        <v>11.45</v>
       </c>
       <c r="P125" s="17" t="n">
-        <v>82.51000000000001</v>
+        <v>82.56</v>
       </c>
       <c r="Q125" s="17" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="R125" s="17" t="inlineStr">
         <is>
@@ -24543,36 +24459,32 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G126" s="17" t="n">
-        <v>524.1900000000001</v>
-      </c>
+      <c r="G126" s="17" t="n"/>
       <c r="H126" s="17" t="n">
-        <v>32.73</v>
+        <v>32.76</v>
       </c>
       <c r="I126" s="17" t="n">
-        <v>60.73</v>
+        <v>60.76</v>
       </c>
       <c r="J126" s="18" t="n">
-        <v>85457048360</v>
+        <v>85553848360</v>
       </c>
       <c r="K126" s="18" t="n">
-        <v>7494517350</v>
+        <v>7501158350</v>
       </c>
       <c r="L126" s="18" t="n">
-        <v>13907954069.474</v>
-      </c>
-      <c r="M126" s="17" t="n">
-        <v>16.02</v>
-      </c>
+        <v>13913811900.924</v>
+      </c>
+      <c r="M126" s="17" t="n"/>
       <c r="N126" s="17" t="n"/>
       <c r="O126" s="17" t="n">
-        <v>8.630000000000001</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="P126" s="17" t="n">
-        <v>62.21</v>
+        <v>62.25</v>
       </c>
       <c r="Q126" s="17" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="R126" s="17" t="inlineStr">
         <is>
@@ -24969,36 +24881,32 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G132" s="17" t="n">
-        <v>518.97</v>
-      </c>
+      <c r="G132" s="17" t="n"/>
       <c r="H132" s="17" t="n">
-        <v>28.99</v>
+        <v>29</v>
       </c>
       <c r="I132" s="17" t="n">
-        <v>137.75</v>
+        <v>137.76</v>
       </c>
       <c r="J132" s="18" t="n">
-        <v>44056252090</v>
+        <v>44061130210</v>
       </c>
       <c r="K132" s="18" t="n">
-        <v>4116937425.38946</v>
+        <v>4118134461.73488</v>
       </c>
       <c r="L132" s="18" t="n">
-        <v>19560796522.68309</v>
-      </c>
-      <c r="M132" s="17" t="n">
-        <v>17.9</v>
-      </c>
+        <v>19561635884.5685</v>
+      </c>
+      <c r="M132" s="17" t="n"/>
       <c r="N132" s="17" t="n"/>
       <c r="O132" s="17" t="n">
-        <v>3.77</v>
+        <v>3.47</v>
       </c>
       <c r="P132" s="17" t="n">
-        <v>22.72</v>
+        <v>22.73</v>
       </c>
       <c r="Q132" s="17" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="R132" s="17" t="inlineStr">
         <is>
@@ -25042,36 +24950,32 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G133" s="17" t="n">
-        <v>518.97</v>
-      </c>
+      <c r="G133" s="17" t="n"/>
       <c r="H133" s="17" t="n">
-        <v>30.44</v>
+        <v>30.45</v>
       </c>
       <c r="I133" s="17" t="n">
-        <v>159.1</v>
+        <v>159.11</v>
       </c>
       <c r="J133" s="18" t="n">
-        <v>47011270470</v>
+        <v>46996529750</v>
       </c>
       <c r="K133" s="18" t="n">
-        <v>4322390325.44418</v>
+        <v>4324270368.29274</v>
       </c>
       <c r="L133" s="18" t="n">
-        <v>22591656618.88455</v>
-      </c>
-      <c r="M133" s="17" t="n">
-        <v>17.05</v>
-      </c>
+        <v>22593814266.81536</v>
+      </c>
+      <c r="M133" s="17" t="n"/>
       <c r="N133" s="17" t="n"/>
       <c r="O133" s="17" t="n">
-        <v>3.26</v>
+        <v>3.01</v>
       </c>
       <c r="P133" s="17" t="n">
-        <v>20.51</v>
+        <v>20.52</v>
       </c>
       <c r="Q133" s="17" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="R133" s="17" t="inlineStr">
         <is>
@@ -25468,9 +25372,7 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G139" s="17" t="n">
-        <v>355.9</v>
-      </c>
+      <c r="G139" s="17" t="n"/>
       <c r="H139" s="17" t="n">
         <v>16.99</v>
       </c>
@@ -25478,26 +25380,24 @@
         <v>105.35</v>
       </c>
       <c r="J139" s="18" t="n">
-        <v>55895186720</v>
+        <v>55892663680</v>
       </c>
       <c r="K139" s="18" t="n">
-        <v>4593657023.44618</v>
+        <v>4594803476.02434</v>
       </c>
       <c r="L139" s="18" t="n">
-        <v>28484767057.01166</v>
-      </c>
-      <c r="M139" s="17" t="n">
-        <v>20.95</v>
-      </c>
+        <v>28485481526.25837</v>
+      </c>
+      <c r="M139" s="17" t="n"/>
       <c r="N139" s="17" t="n"/>
       <c r="O139" s="17" t="n">
-        <v>3.38</v>
+        <v>3.14</v>
       </c>
       <c r="P139" s="17" t="n">
         <v>16.98</v>
       </c>
       <c r="Q139" s="17" t="n">
-        <v>1.72</v>
+        <v>1.6</v>
       </c>
       <c r="R139" s="17" t="inlineStr">
         <is>
@@ -25541,36 +25441,32 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G140" s="17" t="n">
-        <v>355.9</v>
-      </c>
+      <c r="G140" s="17" t="n"/>
       <c r="H140" s="17" t="n">
-        <v>18.61</v>
+        <v>18.62</v>
       </c>
       <c r="I140" s="17" t="n">
         <v>116.95</v>
       </c>
       <c r="J140" s="18" t="n">
-        <v>58565479680</v>
+        <v>58568178760</v>
       </c>
       <c r="K140" s="18" t="n">
-        <v>5032775399.857361</v>
+        <v>5034546452.77881</v>
       </c>
       <c r="L140" s="18" t="n">
-        <v>31621192686.20277</v>
-      </c>
-      <c r="M140" s="17" t="n">
-        <v>19.12</v>
-      </c>
+        <v>31623010875.63012</v>
+      </c>
+      <c r="M140" s="17" t="n"/>
       <c r="N140" s="17" t="n"/>
       <c r="O140" s="17" t="n">
-        <v>3.04</v>
+        <v>2.82</v>
       </c>
       <c r="P140" s="17" t="n">
         <v>16.75</v>
       </c>
       <c r="Q140" s="17" t="n">
-        <v>1.64</v>
+        <v>1.52</v>
       </c>
       <c r="R140" s="17" t="inlineStr">
         <is>
@@ -25967,9 +25863,7 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G146" s="17" t="n">
-        <v>197.68</v>
-      </c>
+      <c r="G146" s="17" t="n"/>
       <c r="H146" s="17" t="n">
         <v>7.24</v>
       </c>
@@ -25977,26 +25871,24 @@
         <v>52.32</v>
       </c>
       <c r="J146" s="18" t="n">
-        <v>96144583660</v>
+        <v>96167898590</v>
       </c>
       <c r="K146" s="18" t="n">
-        <v>9721867488.22576</v>
+        <v>9724068840.0144</v>
       </c>
       <c r="L146" s="18" t="n">
-        <v>70225512519.7807</v>
-      </c>
-      <c r="M146" s="17" t="n">
-        <v>27.29</v>
-      </c>
+        <v>70226640272.258</v>
+      </c>
+      <c r="M146" s="17" t="n"/>
       <c r="N146" s="17" t="n"/>
       <c r="O146" s="17" t="n">
-        <v>3.78</v>
+        <v>3.54</v>
       </c>
       <c r="P146" s="17" t="n">
-        <v>14.35</v>
+        <v>14.36</v>
       </c>
       <c r="Q146" s="17" t="n">
-        <v>2.76</v>
+        <v>2.59</v>
       </c>
       <c r="R146" s="17" t="inlineStr">
         <is>
@@ -26040,9 +25932,7 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G147" s="17" t="n">
-        <v>197.68</v>
-      </c>
+      <c r="G147" s="17" t="n"/>
       <c r="H147" s="17" t="n">
         <v>7.86</v>
       </c>
@@ -26050,26 +25940,24 @@
         <v>56.34</v>
       </c>
       <c r="J147" s="18" t="n">
-        <v>103174696500</v>
+        <v>103261512810</v>
       </c>
       <c r="K147" s="18" t="n">
-        <v>10544824062.38136</v>
+        <v>10546837493.89536</v>
       </c>
       <c r="L147" s="18" t="n">
-        <v>75627625676.04219</v>
-      </c>
-      <c r="M147" s="17" t="n">
-        <v>25.16</v>
-      </c>
+        <v>75629784909.44383</v>
+      </c>
+      <c r="M147" s="17" t="n"/>
       <c r="N147" s="17" t="n"/>
       <c r="O147" s="17" t="n">
-        <v>3.51</v>
+        <v>3.29</v>
       </c>
       <c r="P147" s="17" t="n">
         <v>14.46</v>
       </c>
       <c r="Q147" s="17" t="n">
-        <v>2.57</v>
+        <v>2.41</v>
       </c>
       <c r="R147" s="17" t="inlineStr">
         <is>
@@ -26466,9 +26354,7 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G153" s="17" t="n">
-        <v>279.69</v>
-      </c>
+      <c r="G153" s="17" t="n"/>
       <c r="H153" s="17" t="n">
         <v>18.51</v>
       </c>
@@ -26476,7 +26362,7 @@
         <v>141.74</v>
       </c>
       <c r="J153" s="18" t="n">
-        <v>13351488390</v>
+        <v>13351470890</v>
       </c>
       <c r="K153" s="18" t="n">
         <v>726463869.9860101</v>
@@ -26484,18 +26370,16 @@
       <c r="L153" s="18" t="n">
         <v>5561910169.971308</v>
       </c>
-      <c r="M153" s="17" t="n">
-        <v>15.11</v>
-      </c>
+      <c r="M153" s="17" t="n"/>
       <c r="N153" s="17" t="n"/>
       <c r="O153" s="17" t="n">
-        <v>1.97</v>
+        <v>1.9</v>
       </c>
       <c r="P153" s="17" t="n">
         <v>13.66</v>
       </c>
       <c r="Q153" s="17" t="n">
-        <v>0.82</v>
+        <v>0.79</v>
       </c>
       <c r="R153" s="17" t="inlineStr">
         <is>
@@ -26539,9 +26423,7 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G154" s="17" t="n">
-        <v>279.69</v>
-      </c>
+      <c r="G154" s="17" t="n"/>
       <c r="H154" s="17" t="n">
         <v>20.83</v>
       </c>
@@ -26549,7 +26431,7 @@
         <v>155.76</v>
       </c>
       <c r="J154" s="18" t="n">
-        <v>14198392090</v>
+        <v>14198402920</v>
       </c>
       <c r="K154" s="18" t="n">
         <v>817587797.0785199</v>
@@ -26557,18 +26439,16 @@
       <c r="L154" s="18" t="n">
         <v>6112146741.053395</v>
       </c>
-      <c r="M154" s="17" t="n">
-        <v>13.42</v>
-      </c>
+      <c r="M154" s="17" t="n"/>
       <c r="N154" s="17" t="n"/>
       <c r="O154" s="17" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="P154" s="17" t="n">
         <v>14.01</v>
       </c>
       <c r="Q154" s="17" t="n">
-        <v>0.77</v>
+        <v>0.75</v>
       </c>
       <c r="R154" s="17" t="inlineStr">
         <is>
@@ -26967,30 +26847,30 @@
       </c>
       <c r="G160" s="17" t="n"/>
       <c r="H160" s="17" t="n">
-        <v>37.29</v>
+        <v>37.19</v>
       </c>
       <c r="I160" s="17" t="n">
-        <v>130.05</v>
+        <v>129.99</v>
       </c>
       <c r="J160" s="18" t="n">
-        <v>13946205280</v>
+        <v>13939236840</v>
       </c>
       <c r="K160" s="18" t="n">
-        <v>1710747613.198</v>
+        <v>1706096194.3766</v>
       </c>
       <c r="L160" s="18" t="n">
-        <v>5966794691.493723</v>
+        <v>5964195943.798206</v>
       </c>
       <c r="M160" s="17" t="n"/>
       <c r="N160" s="17" t="n"/>
       <c r="O160" s="17" t="n">
-        <v>7.75</v>
+        <v>7.49</v>
       </c>
       <c r="P160" s="17" t="n">
-        <v>31.17</v>
+        <v>31.09</v>
       </c>
       <c r="Q160" s="17" t="n">
-        <v>3.31</v>
+        <v>3.2</v>
       </c>
       <c r="R160" s="17" t="inlineStr">
         <is>
@@ -27036,30 +26916,30 @@
       </c>
       <c r="G161" s="17" t="n"/>
       <c r="H161" s="17" t="n">
-        <v>53.64</v>
+        <v>53.39</v>
       </c>
       <c r="I161" s="17" t="n">
-        <v>160.02</v>
+        <v>159.82</v>
       </c>
       <c r="J161" s="18" t="n">
-        <v>18646268180</v>
+        <v>18615967290</v>
       </c>
       <c r="K161" s="18" t="n">
-        <v>2461168563.672</v>
+        <v>2449781809.6466</v>
       </c>
       <c r="L161" s="18" t="n">
-        <v>7341849568.017269</v>
+        <v>7332889040.847761</v>
       </c>
       <c r="M161" s="17" t="n"/>
       <c r="N161" s="17" t="n"/>
       <c r="O161" s="17" t="n">
-        <v>6.3</v>
+        <v>6.09</v>
       </c>
       <c r="P161" s="17" t="n">
-        <v>36.99</v>
+        <v>36.85</v>
       </c>
       <c r="Q161" s="17" t="n">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="R161" s="17" t="inlineStr">
         <is>
@@ -27464,13 +27344,13 @@
         <v>4.43</v>
       </c>
       <c r="J167" s="18" t="n">
-        <v>33180119160</v>
+        <v>33211228420</v>
       </c>
       <c r="K167" s="18" t="n">
-        <v>2458483357.5852</v>
+        <v>2465421031.64304</v>
       </c>
       <c r="L167" s="18" t="n">
-        <v>12963826163.30514</v>
+        <v>12967155553.08549</v>
       </c>
       <c r="M167" s="17" t="n"/>
       <c r="N167" s="17" t="n"/>
@@ -27478,7 +27358,7 @@
         <v>0.04</v>
       </c>
       <c r="P167" s="17" t="n">
-        <v>19.87</v>
+        <v>19.92</v>
       </c>
       <c r="Q167" s="17" t="n">
         <v>0.02</v>
@@ -27533,13 +27413,13 @@
         <v>4.89</v>
       </c>
       <c r="J168" s="18" t="n">
-        <v>36216381490</v>
+        <v>36218478880</v>
       </c>
       <c r="K168" s="18" t="n">
-        <v>2805659789.3404</v>
+        <v>2807621072.72384</v>
       </c>
       <c r="L168" s="18" t="n">
-        <v>14310262296.20959</v>
+        <v>14314532905.88567</v>
       </c>
       <c r="M168" s="17" t="n"/>
       <c r="N168" s="17" t="n"/>
@@ -27547,7 +27427,7 @@
         <v>0.04</v>
       </c>
       <c r="P168" s="17" t="n">
-        <v>20.57</v>
+        <v>20.58</v>
       </c>
       <c r="Q168" s="17" t="n">
         <v>0.02</v>
@@ -27949,30 +27829,30 @@
       </c>
       <c r="G174" s="17" t="n"/>
       <c r="H174" s="17" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="I174" s="17" t="n">
-        <v>18.18</v>
+        <v>18.19</v>
       </c>
       <c r="J174" s="18" t="n">
-        <v>22326228840</v>
+        <v>22313553850</v>
       </c>
       <c r="K174" s="18" t="n">
-        <v>1373484837.12726</v>
+        <v>1376150319.20652</v>
       </c>
       <c r="L174" s="18" t="n">
-        <v>10489986583.21887</v>
+        <v>10491791381.13474</v>
       </c>
       <c r="M174" s="17" t="n"/>
       <c r="N174" s="17" t="n"/>
       <c r="O174" s="17" t="n">
-        <v>2.75</v>
+        <v>2.61</v>
       </c>
       <c r="P174" s="17" t="n">
-        <v>13.7</v>
+        <v>13.73</v>
       </c>
       <c r="Q174" s="17" t="n">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="R174" s="17" t="inlineStr">
         <is>
@@ -28018,30 +27898,30 @@
       </c>
       <c r="G175" s="17" t="n"/>
       <c r="H175" s="17" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="I175" s="17" t="n">
-        <v>20.11</v>
+        <v>20.12</v>
       </c>
       <c r="J175" s="18" t="n">
-        <v>24733603910</v>
+        <v>24800732730</v>
       </c>
       <c r="K175" s="18" t="n">
-        <v>1644896684.43165</v>
+        <v>1650619970.62781</v>
       </c>
       <c r="L175" s="18" t="n">
-        <v>11603746128.24754</v>
+        <v>11609426163.24683</v>
       </c>
       <c r="M175" s="17" t="n"/>
       <c r="N175" s="17" t="n"/>
       <c r="O175" s="17" t="n">
-        <v>2.49</v>
+        <v>2.35</v>
       </c>
       <c r="P175" s="17" t="n">
-        <v>14.89</v>
+        <v>14.94</v>
       </c>
       <c r="Q175" s="17" t="n">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="R175" s="17" t="inlineStr">
         <is>
@@ -28440,30 +28320,30 @@
       </c>
       <c r="G181" s="17" t="n"/>
       <c r="H181" s="17" t="n">
-        <v>14.9</v>
+        <v>14.91</v>
       </c>
       <c r="I181" s="17" t="n">
         <v>92.81999999999999</v>
       </c>
       <c r="J181" s="18" t="n">
-        <v>97786114940</v>
+        <v>97917543660</v>
       </c>
       <c r="K181" s="18" t="n">
-        <v>8030719972.51368</v>
+        <v>8035732146.022079</v>
       </c>
       <c r="L181" s="18" t="n">
-        <v>50022377449.11489</v>
+        <v>50026550584.77798</v>
       </c>
       <c r="M181" s="17" t="n"/>
       <c r="N181" s="17" t="n"/>
       <c r="O181" s="17" t="n">
-        <v>6.16</v>
+        <v>6.6</v>
       </c>
       <c r="P181" s="17" t="n">
-        <v>17.2</v>
+        <v>17.21</v>
       </c>
       <c r="Q181" s="17" t="n">
-        <v>3.15</v>
+        <v>3.37</v>
       </c>
       <c r="R181" s="17" t="inlineStr">
         <is>
@@ -28509,30 +28389,30 @@
       </c>
       <c r="G182" s="17" t="n"/>
       <c r="H182" s="17" t="n">
-        <v>18.89</v>
+        <v>18.99</v>
       </c>
       <c r="I182" s="17" t="n">
-        <v>108.54</v>
+        <v>108.64</v>
       </c>
       <c r="J182" s="18" t="n">
-        <v>118685164060</v>
+        <v>119089043310</v>
       </c>
       <c r="K182" s="18" t="n">
-        <v>10181082532.89816</v>
+        <v>10235262511.6938</v>
       </c>
       <c r="L182" s="18" t="n">
-        <v>58499146766.0059</v>
+        <v>58548430152.01424</v>
       </c>
       <c r="M182" s="17" t="n"/>
       <c r="N182" s="17" t="n"/>
       <c r="O182" s="17" t="n">
-        <v>5.26</v>
+        <v>5.64</v>
       </c>
       <c r="P182" s="17" t="n">
-        <v>18.76</v>
+        <v>18.85</v>
       </c>
       <c r="Q182" s="17" t="n">
-        <v>2.59</v>
+        <v>2.77</v>
       </c>
       <c r="R182" s="17" t="inlineStr">
         <is>
@@ -28930,7 +28810,7 @@
         </is>
       </c>
       <c r="G188" s="17" t="n">
-        <v>142500</v>
+        <v>117900</v>
       </c>
       <c r="H188" s="17" t="n">
         <v>13470</v>
@@ -28948,17 +28828,17 @@
         <v>2419672871894.003</v>
       </c>
       <c r="M188" s="17" t="n">
-        <v>10.58</v>
+        <v>8.75</v>
       </c>
       <c r="N188" s="17" t="n"/>
       <c r="O188" s="17" t="n">
-        <v>2.83</v>
+        <v>2.34</v>
       </c>
       <c r="P188" s="17" t="n">
         <v>30.59</v>
       </c>
       <c r="Q188" s="17" t="n">
-        <v>0.72</v>
+        <v>0.6</v>
       </c>
       <c r="R188" s="17" t="inlineStr">
         <is>
@@ -29003,7 +28883,7 @@
         </is>
       </c>
       <c r="G189" s="17" t="n">
-        <v>142500</v>
+        <v>117900</v>
       </c>
       <c r="H189" s="17" t="n">
         <v>14842.75</v>
@@ -29012,7 +28892,7 @@
         <v>64553.49</v>
       </c>
       <c r="J189" s="18" t="n">
-        <v>10403980000000</v>
+        <v>10536725000000</v>
       </c>
       <c r="K189" s="18" t="n">
         <v>712032959482</v>
@@ -29021,17 +28901,17 @@
         <v>3096745015201.536</v>
       </c>
       <c r="M189" s="17" t="n">
-        <v>9.6</v>
+        <v>7.94</v>
       </c>
       <c r="N189" s="17" t="n"/>
       <c r="O189" s="17" t="n">
-        <v>2.21</v>
+        <v>1.83</v>
       </c>
       <c r="P189" s="17" t="n">
         <v>25.82</v>
       </c>
       <c r="Q189" s="17" t="n">
-        <v>0.66</v>
+        <v>0.54</v>
       </c>
       <c r="R189" s="17" t="inlineStr">
         <is>
@@ -29429,35 +29309,35 @@
         </is>
       </c>
       <c r="G195" s="17" t="n">
-        <v>61600</v>
+        <v>55200</v>
       </c>
       <c r="H195" s="17" t="n">
-        <v>6179.71</v>
+        <v>6119.71</v>
       </c>
       <c r="I195" s="17" t="n">
-        <v>79295.38</v>
+        <v>79254.95</v>
       </c>
       <c r="J195" s="18" t="n">
-        <v>9565166640000</v>
+        <v>9540452360000</v>
       </c>
       <c r="K195" s="18" t="n">
-        <v>591483730785.024</v>
+        <v>585740902665.024</v>
       </c>
       <c r="L195" s="18" t="n">
-        <v>7589662196632.624</v>
+        <v>7585792678930.512</v>
       </c>
       <c r="M195" s="17" t="n">
-        <v>9.970000000000001</v>
+        <v>9.02</v>
       </c>
       <c r="N195" s="17" t="n"/>
       <c r="O195" s="17" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="P195" s="17" t="n">
-        <v>8</v>
+        <v>7.93</v>
       </c>
       <c r="Q195" s="17" t="n">
-        <v>0.62</v>
+        <v>0.55</v>
       </c>
       <c r="R195" s="17" t="inlineStr">
         <is>
@@ -29502,35 +29382,35 @@
         </is>
       </c>
       <c r="G196" s="17" t="n">
-        <v>61600</v>
+        <v>55200</v>
       </c>
       <c r="H196" s="17" t="n">
-        <v>6625.59</v>
+        <v>6251.93</v>
       </c>
       <c r="I196" s="17" t="n">
-        <v>83759.7</v>
+        <v>83467.5</v>
       </c>
       <c r="J196" s="18" t="n">
-        <v>9929985100000</v>
+        <v>9875485100000</v>
       </c>
       <c r="K196" s="18" t="n">
-        <v>634160773105.6276</v>
+        <v>598395722139.2144</v>
       </c>
       <c r="L196" s="18" t="n">
-        <v>8016959738234.411</v>
+        <v>7988991728475.829</v>
       </c>
       <c r="M196" s="17" t="n">
-        <v>9.300000000000001</v>
+        <v>8.83</v>
       </c>
       <c r="N196" s="17" t="n"/>
       <c r="O196" s="17" t="n">
-        <v>0.74</v>
+        <v>0.66</v>
       </c>
       <c r="P196" s="17" t="n">
-        <v>8.130000000000001</v>
+        <v>7.68</v>
       </c>
       <c r="Q196" s="17" t="n">
-        <v>0.59</v>
+        <v>0.54</v>
       </c>
       <c r="R196" s="17" t="inlineStr">
         <is>
@@ -29924,7 +29804,7 @@
         </is>
       </c>
       <c r="G202" s="17" t="n">
-        <v>8110</v>
+        <v>7650</v>
       </c>
       <c r="H202" s="17" t="n"/>
       <c r="I202" s="17" t="n"/>
@@ -29981,7 +29861,7 @@
         </is>
       </c>
       <c r="G203" s="17" t="n">
-        <v>8110</v>
+        <v>7650</v>
       </c>
       <c r="H203" s="17" t="n"/>
       <c r="I203" s="17" t="n"/>
@@ -30390,9 +30270,7 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G209" s="17" t="n">
-        <v>818.5700000000001</v>
-      </c>
+      <c r="G209" s="17" t="n"/>
       <c r="H209" s="17" t="n">
         <v>27.19</v>
       </c>
@@ -30408,18 +30286,16 @@
       <c r="L209" s="18" t="n">
         <v>30677414343.27097</v>
       </c>
-      <c r="M209" s="17" t="n">
-        <v>30.11</v>
-      </c>
+      <c r="M209" s="17" t="n"/>
       <c r="N209" s="17" t="n"/>
       <c r="O209" s="17" t="n">
-        <v>12.42</v>
+        <v>12.67</v>
       </c>
       <c r="P209" s="17" t="n">
         <v>48.66</v>
       </c>
       <c r="Q209" s="17" t="n">
-        <v>4.81</v>
+        <v>4.91</v>
       </c>
       <c r="R209" s="17" t="inlineStr">
         <is>
@@ -30463,9 +30339,7 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G210" s="17" t="n">
-        <v>818.5700000000001</v>
-      </c>
+      <c r="G210" s="17" t="n"/>
       <c r="H210" s="17" t="n">
         <v>32.38</v>
       </c>
@@ -30481,18 +30355,16 @@
       <c r="L210" s="18" t="n">
         <v>41823834814.59047</v>
       </c>
-      <c r="M210" s="17" t="n">
-        <v>25.28</v>
-      </c>
+      <c r="M210" s="17" t="n"/>
       <c r="N210" s="17" t="n"/>
       <c r="O210" s="17" t="n">
-        <v>9.109999999999999</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="P210" s="17" t="n">
         <v>41.56</v>
       </c>
       <c r="Q210" s="17" t="n">
-        <v>4.33</v>
+        <v>4.41</v>
       </c>
       <c r="R210" s="17" t="inlineStr">
         <is>
@@ -30889,36 +30761,32 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G216" s="17" t="n">
-        <v>675.74</v>
-      </c>
+      <c r="G216" s="17" t="n"/>
       <c r="H216" s="17" t="n">
         <v>18.13</v>
       </c>
       <c r="I216" s="17" t="n">
-        <v>107.59</v>
+        <v>107.58</v>
       </c>
       <c r="J216" s="18" t="n">
-        <v>41117805710</v>
+        <v>41117790860</v>
       </c>
       <c r="K216" s="18" t="n">
-        <v>4902117812.493999</v>
+        <v>4900155056.6836</v>
       </c>
       <c r="L216" s="18" t="n">
-        <v>29086374878.3913</v>
-      </c>
-      <c r="M216" s="17" t="n">
-        <v>37.27</v>
-      </c>
+        <v>29085119107.26307</v>
+      </c>
+      <c r="M216" s="17" t="n"/>
       <c r="N216" s="17" t="n"/>
       <c r="O216" s="17" t="n">
-        <v>6.28</v>
+        <v>6.37</v>
       </c>
       <c r="P216" s="17" t="n">
         <v>17.81</v>
       </c>
       <c r="Q216" s="17" t="n">
-        <v>4.44</v>
+        <v>4.5</v>
       </c>
       <c r="R216" s="17" t="inlineStr">
         <is>
@@ -30962,36 +30830,32 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G217" s="17" t="n">
-        <v>675.74</v>
-      </c>
+      <c r="G217" s="17" t="n"/>
       <c r="H217" s="17" t="n">
-        <v>22.67</v>
+        <v>22.83</v>
       </c>
       <c r="I217" s="17" t="n">
-        <v>122.09</v>
+        <v>122.19</v>
       </c>
       <c r="J217" s="18" t="n">
-        <v>44504854240</v>
+        <v>44692285830</v>
       </c>
       <c r="K217" s="18" t="n">
-        <v>6128726646.137199</v>
+        <v>6171499042.3856</v>
       </c>
       <c r="L217" s="18" t="n">
-        <v>33007534064.01535</v>
-      </c>
-      <c r="M217" s="17" t="n">
-        <v>29.81</v>
-      </c>
+        <v>33033644071.15139</v>
+      </c>
+      <c r="M217" s="17" t="n"/>
       <c r="N217" s="17" t="n"/>
       <c r="O217" s="17" t="n">
-        <v>5.53</v>
+        <v>5.61</v>
       </c>
       <c r="P217" s="17" t="n">
-        <v>19.74</v>
+        <v>19.87</v>
       </c>
       <c r="Q217" s="17" t="n">
-        <v>4.1</v>
+        <v>4.14</v>
       </c>
       <c r="R217" s="17" t="inlineStr">
         <is>
@@ -31388,9 +31252,7 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G223" s="17" t="n">
-        <v>13.58</v>
-      </c>
+      <c r="G223" s="17" t="n"/>
       <c r="H223" s="17" t="n">
         <v>0.45</v>
       </c>
@@ -31398,7 +31260,7 @@
         <v>6.49</v>
       </c>
       <c r="J223" s="18" t="n">
-        <v>18265234810</v>
+        <v>18265223700</v>
       </c>
       <c r="K223" s="18" t="n">
         <v>561090316.16106</v>
@@ -31406,18 +31268,16 @@
       <c r="L223" s="18" t="n">
         <v>8066654189.696636</v>
       </c>
-      <c r="M223" s="17" t="n">
-        <v>30.06</v>
-      </c>
+      <c r="M223" s="17" t="n"/>
       <c r="N223" s="17" t="n"/>
       <c r="O223" s="17" t="n">
-        <v>2.09</v>
+        <v>2.69</v>
       </c>
       <c r="P223" s="17" t="n">
         <v>7.1</v>
       </c>
       <c r="Q223" s="17" t="n">
-        <v>0.92</v>
+        <v>1.19</v>
       </c>
       <c r="R223" s="17" t="inlineStr">
         <is>
@@ -31461,9 +31321,7 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G224" s="17" t="n">
-        <v>13.58</v>
-      </c>
+      <c r="G224" s="17" t="n"/>
       <c r="H224" s="17" t="n">
         <v>0.6899999999999999</v>
       </c>
@@ -31471,7 +31329,7 @@
         <v>6.91</v>
       </c>
       <c r="J224" s="18" t="n">
-        <v>19047530490</v>
+        <v>19047519380</v>
       </c>
       <c r="K224" s="18" t="n">
         <v>851013062.8700399</v>
@@ -31479,18 +31337,16 @@
       <c r="L224" s="18" t="n">
         <v>8577262027.41866</v>
       </c>
-      <c r="M224" s="17" t="n">
-        <v>19.82</v>
-      </c>
+      <c r="M224" s="17" t="n"/>
       <c r="N224" s="17" t="n"/>
       <c r="O224" s="17" t="n">
-        <v>1.97</v>
+        <v>2.53</v>
       </c>
       <c r="P224" s="17" t="n">
         <v>10.23</v>
       </c>
       <c r="Q224" s="17" t="n">
-        <v>0.89</v>
+        <v>1.14</v>
       </c>
       <c r="R224" s="17" t="inlineStr">
         <is>
@@ -31888,35 +31744,35 @@
         </is>
       </c>
       <c r="G230" s="17" t="n">
-        <v>7114</v>
+        <v>7500</v>
       </c>
       <c r="H230" s="17" t="n">
-        <v>438.93</v>
+        <v>443.3</v>
       </c>
       <c r="I230" s="17" t="n">
-        <v>4133.56</v>
+        <v>4135.92</v>
       </c>
       <c r="J230" s="18" t="n">
-        <v>4363584533599</v>
+        <v>4382561308130</v>
       </c>
       <c r="K230" s="18" t="n">
-        <v>395517352597.6937</v>
+        <v>399452699984.683</v>
       </c>
       <c r="L230" s="18" t="n">
-        <v>3724742879845.005</v>
+        <v>3726871902702.66</v>
       </c>
       <c r="M230" s="17" t="n">
-        <v>16.21</v>
+        <v>16.92</v>
       </c>
       <c r="N230" s="17" t="n"/>
       <c r="O230" s="17" t="n">
-        <v>1.72</v>
+        <v>1.81</v>
       </c>
       <c r="P230" s="17" t="n">
-        <v>10.93</v>
+        <v>11.04</v>
       </c>
       <c r="Q230" s="17" t="n">
-        <v>1.47</v>
+        <v>1.54</v>
       </c>
       <c r="R230" s="17" t="inlineStr">
         <is>
@@ -31961,35 +31817,35 @@
         </is>
       </c>
       <c r="G231" s="17" t="n">
-        <v>7114</v>
+        <v>7500</v>
       </c>
       <c r="H231" s="17" t="n">
-        <v>480.38</v>
+        <v>490.47</v>
       </c>
       <c r="I231" s="17" t="n">
-        <v>4393.44</v>
+        <v>4401.27</v>
       </c>
       <c r="J231" s="18" t="n">
-        <v>4509222796730</v>
+        <v>4599904225200</v>
       </c>
       <c r="K231" s="18" t="n">
-        <v>432866424018.5521</v>
+        <v>441958611232.6553</v>
       </c>
       <c r="L231" s="18" t="n">
-        <v>3958923606581.714</v>
+        <v>3965971502540.354</v>
       </c>
       <c r="M231" s="17" t="n">
-        <v>14.81</v>
+        <v>15.29</v>
       </c>
       <c r="N231" s="17" t="n"/>
       <c r="O231" s="17" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="P231" s="17" t="n">
-        <v>11.27</v>
+        <v>11.49</v>
       </c>
       <c r="Q231" s="17" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="R231" s="17" t="inlineStr">
         <is>
@@ -32387,7 +32243,7 @@
         </is>
       </c>
       <c r="G237" s="17" t="n">
-        <v>5633</v>
+        <v>5550</v>
       </c>
       <c r="H237" s="17" t="n">
         <v>422</v>
@@ -32405,17 +32261,17 @@
         <v>944281630158.509</v>
       </c>
       <c r="M237" s="17" t="n">
-        <v>13.35</v>
+        <v>13.15</v>
       </c>
       <c r="N237" s="17" t="n"/>
       <c r="O237" s="17" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="P237" s="17" t="n">
         <v>9.73</v>
       </c>
       <c r="Q237" s="17" t="n">
-        <v>0.82</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="R237" s="17" t="inlineStr">
         <is>
@@ -32460,7 +32316,7 @@
         </is>
       </c>
       <c r="G238" s="17" t="n">
-        <v>5633</v>
+        <v>5550</v>
       </c>
       <c r="H238" s="17" t="n">
         <v>493.57</v>
@@ -32478,17 +32334,17 @@
         <v>995878361116.4418</v>
       </c>
       <c r="M238" s="17" t="n">
-        <v>11.41</v>
+        <v>11.24</v>
       </c>
       <c r="N238" s="17" t="n"/>
       <c r="O238" s="17" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="P238" s="17" t="n">
         <v>10.82</v>
       </c>
       <c r="Q238" s="17" t="n">
-        <v>0.79</v>
+        <v>0.78</v>
       </c>
       <c r="R238" s="17" t="inlineStr">
         <is>
@@ -32887,30 +32743,30 @@
       </c>
       <c r="G244" s="17" t="n"/>
       <c r="H244" s="17" t="n">
-        <v>21.56</v>
+        <v>21.67</v>
       </c>
       <c r="I244" s="17" t="n">
-        <v>98.89</v>
+        <v>98.95</v>
       </c>
       <c r="J244" s="18" t="n">
-        <v>497752494260</v>
+        <v>500978337390</v>
       </c>
       <c r="K244" s="18" t="n">
-        <v>43848994718.00088</v>
+        <v>44061754809.5498</v>
       </c>
       <c r="L244" s="18" t="n">
-        <v>201091238350.5674</v>
+        <v>201201362967.5703</v>
       </c>
       <c r="M244" s="17" t="n"/>
       <c r="N244" s="17" t="n"/>
       <c r="O244" s="17" t="n">
-        <v>3.44</v>
+        <v>3.18</v>
       </c>
       <c r="P244" s="17" t="n">
-        <v>23.11</v>
+        <v>23.22</v>
       </c>
       <c r="Q244" s="17" t="n">
-        <v>1.39</v>
+        <v>1.28</v>
       </c>
       <c r="R244" s="17" t="inlineStr">
         <is>
@@ -32956,30 +32812,30 @@
       </c>
       <c r="G245" s="17" t="n"/>
       <c r="H245" s="17" t="n">
-        <v>25.44</v>
+        <v>25.76</v>
       </c>
       <c r="I245" s="17" t="n">
-        <v>112.06</v>
+        <v>112.28</v>
       </c>
       <c r="J245" s="18" t="n">
-        <v>541284574170</v>
+        <v>547541108220</v>
       </c>
       <c r="K245" s="18" t="n">
-        <v>51728743550.62592</v>
+        <v>52382051036.17344</v>
       </c>
       <c r="L245" s="18" t="n">
-        <v>227866034460.5091</v>
+        <v>228314311012.4322</v>
       </c>
       <c r="M245" s="17" t="n"/>
       <c r="N245" s="17" t="n"/>
       <c r="O245" s="17" t="n">
-        <v>3.04</v>
+        <v>2.8</v>
       </c>
       <c r="P245" s="17" t="n">
-        <v>24.12</v>
+        <v>24.39</v>
       </c>
       <c r="Q245" s="17" t="n">
-        <v>1.28</v>
+        <v>1.17</v>
       </c>
       <c r="R245" s="17" t="inlineStr">
         <is>
@@ -33377,7 +33233,7 @@
         </is>
       </c>
       <c r="G251" s="17" t="n">
-        <v>19.78</v>
+        <v>17.49</v>
       </c>
       <c r="H251" s="17" t="n">
         <v>1.17</v>
@@ -33386,7 +33242,7 @@
         <v>10.41</v>
       </c>
       <c r="J251" s="18" t="n">
-        <v>104038852480</v>
+        <v>104159528020</v>
       </c>
       <c r="K251" s="18" t="n">
         <v>10742983433.96895</v>
@@ -33395,17 +33251,17 @@
         <v>95703079447.24916</v>
       </c>
       <c r="M251" s="17" t="n">
-        <v>16.93</v>
+        <v>14.97</v>
       </c>
       <c r="N251" s="17" t="n"/>
       <c r="O251" s="17" t="n">
-        <v>1.9</v>
+        <v>1.68</v>
       </c>
       <c r="P251" s="17" t="n">
         <v>11.67</v>
       </c>
       <c r="Q251" s="17" t="n">
-        <v>1.75</v>
+        <v>1.54</v>
       </c>
       <c r="R251" s="17" t="inlineStr">
         <is>
@@ -33450,7 +33306,7 @@
         </is>
       </c>
       <c r="G252" s="17" t="n">
-        <v>19.78</v>
+        <v>17.49</v>
       </c>
       <c r="H252" s="17" t="n">
         <v>1.52</v>
@@ -33459,7 +33315,7 @@
         <v>11.45</v>
       </c>
       <c r="J252" s="18" t="n">
-        <v>118137033660</v>
+        <v>118277753630</v>
       </c>
       <c r="K252" s="18" t="n">
         <v>13933833873.69669</v>
@@ -33468,17 +33324,17 @@
         <v>105264476530.0565</v>
       </c>
       <c r="M252" s="17" t="n">
-        <v>13.05</v>
+        <v>11.54</v>
       </c>
       <c r="N252" s="17" t="n"/>
       <c r="O252" s="17" t="n">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="P252" s="17" t="n">
         <v>13.87</v>
       </c>
       <c r="Q252" s="17" t="n">
-        <v>1.54</v>
+        <v>1.36</v>
       </c>
       <c r="R252" s="17" t="inlineStr">
         <is>
@@ -33876,7 +33732,7 @@
         </is>
       </c>
       <c r="G258" s="17" t="n">
-        <v>8.06</v>
+        <v>7.2</v>
       </c>
       <c r="H258" s="17" t="n">
         <v>0.66</v>
@@ -33885,7 +33741,7 @@
         <v>5.35</v>
       </c>
       <c r="J258" s="18" t="n">
-        <v>114353945310</v>
+        <v>113875942040</v>
       </c>
       <c r="K258" s="18" t="n">
         <v>7802328311.90052</v>
@@ -33894,17 +33750,17 @@
         <v>62872386186.58829</v>
       </c>
       <c r="M258" s="17" t="n">
-        <v>12.14</v>
+        <v>10.85</v>
       </c>
       <c r="N258" s="17" t="n"/>
       <c r="O258" s="17" t="n">
-        <v>1.51</v>
+        <v>1.35</v>
       </c>
       <c r="P258" s="17" t="n">
         <v>12.65</v>
       </c>
       <c r="Q258" s="17" t="n">
-        <v>0.83</v>
+        <v>0.74</v>
       </c>
       <c r="R258" s="17" t="inlineStr">
         <is>
@@ -33949,7 +33805,7 @@
         </is>
       </c>
       <c r="G259" s="17" t="n">
-        <v>8.06</v>
+        <v>7.2</v>
       </c>
       <c r="H259" s="17" t="n">
         <v>0.9</v>
@@ -33958,7 +33814,7 @@
         <v>5.63</v>
       </c>
       <c r="J259" s="18" t="n">
-        <v>131317082850</v>
+        <v>130065541180</v>
       </c>
       <c r="K259" s="18" t="n">
         <v>10592366449.4025</v>
@@ -33967,17 +33823,17 @@
         <v>66146486973.8696</v>
       </c>
       <c r="M259" s="17" t="n">
-        <v>8.94</v>
+        <v>7.99</v>
       </c>
       <c r="N259" s="17" t="n"/>
       <c r="O259" s="17" t="n">
-        <v>1.43</v>
+        <v>1.28</v>
       </c>
       <c r="P259" s="17" t="n">
         <v>16.42</v>
       </c>
       <c r="Q259" s="17" t="n">
-        <v>0.72</v>
+        <v>0.65</v>
       </c>
       <c r="R259" s="17" t="inlineStr">
         <is>
@@ -34375,7 +34231,7 @@
         </is>
       </c>
       <c r="G265" s="17" t="n">
-        <v>12680</v>
+        <v>11400</v>
       </c>
       <c r="H265" s="17" t="n">
         <v>1728</v>
@@ -34393,17 +34249,17 @@
         <v>328971474869.7184</v>
       </c>
       <c r="M265" s="17" t="n">
-        <v>7.34</v>
+        <v>6.6</v>
       </c>
       <c r="N265" s="17" t="n"/>
       <c r="O265" s="17" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="P265" s="17" t="n">
         <v>11.18</v>
       </c>
       <c r="Q265" s="17" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="R265" s="17" t="inlineStr">
         <is>
@@ -34448,7 +34304,7 @@
         </is>
       </c>
       <c r="G266" s="17" t="n">
-        <v>12680</v>
+        <v>11400</v>
       </c>
       <c r="H266" s="17" t="n">
         <v>2102</v>
@@ -34466,17 +34322,17 @@
         <v>367213567791.274</v>
       </c>
       <c r="M266" s="17" t="n">
-        <v>6.03</v>
+        <v>5.42</v>
       </c>
       <c r="N266" s="17" t="n"/>
       <c r="O266" s="17" t="n">
-        <v>0.7</v>
+        <v>0.63</v>
       </c>
       <c r="P266" s="17" t="n">
         <v>12.24</v>
       </c>
       <c r="Q266" s="17" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="R266" s="17" t="inlineStr">
         <is>
@@ -34874,7 +34730,7 @@
         </is>
       </c>
       <c r="G272" s="17" t="n">
-        <v>11280</v>
+        <v>11120</v>
       </c>
       <c r="H272" s="17" t="n"/>
       <c r="I272" s="17" t="n"/>
@@ -34931,7 +34787,7 @@
         </is>
       </c>
       <c r="G273" s="17" t="n">
-        <v>11280</v>
+        <v>11120</v>
       </c>
       <c r="H273" s="17" t="n"/>
       <c r="I273" s="17" t="n"/>
@@ -35341,7 +35197,7 @@
         </is>
       </c>
       <c r="G279" s="17" t="n">
-        <v>6620</v>
+        <v>6540</v>
       </c>
       <c r="H279" s="17" t="n"/>
       <c r="I279" s="17" t="n"/>
@@ -35398,7 +35254,7 @@
         </is>
       </c>
       <c r="G280" s="17" t="n">
-        <v>6620</v>
+        <v>6540</v>
       </c>
       <c r="H280" s="17" t="n"/>
       <c r="I280" s="17" t="n"/>
@@ -35807,9 +35663,7 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G286" s="17" t="n">
-        <v>989.12</v>
-      </c>
+      <c r="G286" s="17" t="n"/>
       <c r="H286" s="17" t="n">
         <v>49.29</v>
       </c>
@@ -35817,7 +35671,7 @@
         <v>182.5</v>
       </c>
       <c r="J286" s="18" t="n">
-        <v>17746037900</v>
+        <v>17746237900</v>
       </c>
       <c r="K286" s="18" t="n">
         <v>3109809180.5109</v>
@@ -35825,18 +35679,16 @@
       <c r="L286" s="18" t="n">
         <v>11515244668.65839</v>
       </c>
-      <c r="M286" s="17" t="n">
-        <v>20.07</v>
-      </c>
+      <c r="M286" s="17" t="n"/>
       <c r="N286" s="17" t="n"/>
       <c r="O286" s="17" t="n">
-        <v>5.42</v>
+        <v>5.84</v>
       </c>
       <c r="P286" s="17" t="n">
         <v>30.36</v>
       </c>
       <c r="Q286" s="17" t="n">
-        <v>3.52</v>
+        <v>3.79</v>
       </c>
       <c r="R286" s="17" t="inlineStr">
         <is>
@@ -35880,36 +35732,32 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G287" s="17" t="n">
-        <v>989.12</v>
-      </c>
+      <c r="G287" s="17" t="n"/>
       <c r="H287" s="17" t="n">
-        <v>57.3</v>
+        <v>57.32</v>
       </c>
       <c r="I287" s="17" t="n">
-        <v>229.44</v>
+        <v>229.45</v>
       </c>
       <c r="J287" s="18" t="n">
-        <v>19300284520</v>
+        <v>19300184520</v>
       </c>
       <c r="K287" s="18" t="n">
-        <v>3615418640.7507</v>
+        <v>3616530391.7421</v>
       </c>
       <c r="L287" s="18" t="n">
-        <v>14476634041.1431</v>
-      </c>
-      <c r="M287" s="17" t="n">
-        <v>17.26</v>
-      </c>
+        <v>14477544676.36904</v>
+      </c>
+      <c r="M287" s="17" t="n"/>
       <c r="N287" s="17" t="n"/>
       <c r="O287" s="17" t="n">
-        <v>4.31</v>
+        <v>4.65</v>
       </c>
       <c r="P287" s="17" t="n">
-        <v>27.82</v>
+        <v>27.83</v>
       </c>
       <c r="Q287" s="17" t="n">
-        <v>3.23</v>
+        <v>3.49</v>
       </c>
       <c r="R287" s="17" t="inlineStr">
         <is>
@@ -36217,7 +36065,7 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>2026-09-12T08:47:20+09:00</t>
+          <t>2026-10-03T09:53:53+09:00</t>
         </is>
       </c>
     </row>

--- a/telegram_research_dashboard/static/valuation_full.xlsx
+++ b/telegram_research_dashboard/static/valuation_full.xlsx
@@ -815,10 +815,10 @@
         <v>37.73</v>
       </c>
       <c r="G5" s="10" t="n">
-        <v>11.44</v>
+        <v>11.7</v>
       </c>
       <c r="H5" s="10" t="n">
-        <v>9.84</v>
+        <v>10.05</v>
       </c>
       <c r="I5" s="10" t="n"/>
       <c r="J5" s="9" t="n"/>
@@ -847,10 +847,10 @@
         <v>5.72</v>
       </c>
       <c r="U5" s="10" t="n">
-        <v>3.06</v>
+        <v>3.07</v>
       </c>
       <c r="V5" s="10" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="W5" s="10" t="n"/>
       <c r="X5" s="11" t="n">
@@ -866,10 +866,10 @@
         <v>18.82</v>
       </c>
       <c r="AB5" s="12" t="n">
-        <v>30.13</v>
+        <v>29.54</v>
       </c>
       <c r="AC5" s="12" t="n">
-        <v>27.48</v>
+        <v>27.1</v>
       </c>
       <c r="AD5" s="12" t="n"/>
       <c r="AE5" s="9" t="n">
@@ -885,7 +885,7 @@
         <v>3.04</v>
       </c>
       <c r="AI5" s="10" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="AJ5" s="10" t="n">
         <v>1.38</v>
@@ -912,10 +912,10 @@
         <v>27.94</v>
       </c>
       <c r="G6" s="10" t="n">
+        <v>10.65</v>
+      </c>
+      <c r="H6" s="10" t="n">
         <v>10.51</v>
-      </c>
-      <c r="H6" s="10" t="n">
-        <v>10.36</v>
       </c>
       <c r="I6" s="10" t="n"/>
       <c r="J6" s="9" t="n"/>
@@ -944,10 +944,10 @@
         <v>5.64</v>
       </c>
       <c r="U6" s="10" t="n">
-        <v>2.47</v>
+        <v>2.48</v>
       </c>
       <c r="V6" s="10" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="W6" s="10" t="n"/>
       <c r="X6" s="11" t="n">
@@ -963,10 +963,10 @@
         <v>22.59</v>
       </c>
       <c r="AB6" s="12" t="n">
-        <v>26.63</v>
+        <v>26.32</v>
       </c>
       <c r="AC6" s="12" t="n">
-        <v>21.3</v>
+        <v>21.08</v>
       </c>
       <c r="AD6" s="12" t="n"/>
       <c r="AE6" s="9" t="n">
@@ -1007,10 +1007,10 @@
         <v>37.73</v>
       </c>
       <c r="G7" s="10" t="n">
-        <v>15.63</v>
+        <v>15.65</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>10.89</v>
+        <v>10.88</v>
       </c>
       <c r="I7" s="10" t="n"/>
       <c r="J7" s="9" t="n"/>
@@ -1058,10 +1058,10 @@
         <v>13.74</v>
       </c>
       <c r="AB7" s="12" t="n">
-        <v>21.61</v>
+        <v>21.59</v>
       </c>
       <c r="AC7" s="12" t="n">
-        <v>24.56</v>
+        <v>24.58</v>
       </c>
       <c r="AD7" s="12" t="n"/>
       <c r="AE7" s="9" t="n">
@@ -1077,10 +1077,10 @@
         <v>1.93</v>
       </c>
       <c r="AI7" s="10" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AJ7" s="10" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AK7" s="10" t="n"/>
     </row>
@@ -1104,10 +1104,10 @@
         <v>13.27</v>
       </c>
       <c r="G8" s="10" t="n">
-        <v>5.08</v>
+        <v>5.11</v>
       </c>
       <c r="H8" s="10" t="n">
-        <v>4.32</v>
+        <v>4.38</v>
       </c>
       <c r="I8" s="10" t="n"/>
       <c r="J8" s="9" t="n">
@@ -1157,10 +1157,10 @@
         <v>17.78</v>
       </c>
       <c r="AB8" s="12" t="n">
-        <v>24.96</v>
+        <v>24.84</v>
       </c>
       <c r="AC8" s="12" t="n">
-        <v>24.01</v>
+        <v>23.73</v>
       </c>
       <c r="AD8" s="12" t="n"/>
       <c r="AE8" s="9" t="n">
@@ -1179,7 +1179,7 @@
         <v>0.54</v>
       </c>
       <c r="AJ8" s="10" t="n">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="AK8" s="10" t="n"/>
     </row>
@@ -1357,10 +1357,10 @@
         <v>32.18</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>27.01</v>
+        <v>27.64</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>22.52</v>
+        <v>22.6</v>
       </c>
       <c r="I11" s="10" t="n"/>
       <c r="J11" s="9" t="n"/>
@@ -1383,10 +1383,10 @@
         <v>10.52</v>
       </c>
       <c r="U11" s="10" t="n">
-        <v>9.359999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="V11" s="10" t="n">
-        <v>7.65</v>
+        <v>7.68</v>
       </c>
       <c r="W11" s="10" t="n"/>
       <c r="X11" s="11" t="n">
@@ -1402,10 +1402,10 @@
         <v>33.73</v>
       </c>
       <c r="AB11" s="12" t="n">
-        <v>38.2</v>
+        <v>37.42</v>
       </c>
       <c r="AC11" s="12" t="n">
-        <v>37.37</v>
+        <v>37.39</v>
       </c>
       <c r="AD11" s="12" t="n"/>
       <c r="AE11" s="9" t="n"/>
@@ -1417,10 +1417,10 @@
         <v>4.38</v>
       </c>
       <c r="AI11" s="10" t="n">
-        <v>4.03</v>
+        <v>3.99</v>
       </c>
       <c r="AJ11" s="10" t="n">
-        <v>3.54</v>
+        <v>3.53</v>
       </c>
       <c r="AK11" s="10" t="n"/>
     </row>
@@ -1834,7 +1834,7 @@
         </is>
       </c>
       <c r="B17" s="8" t="n">
-        <v>40317</v>
+        <v>40232</v>
       </c>
       <c r="C17" s="9" t="n">
         <v>577.76</v>
@@ -1931,7 +1931,7 @@
         </is>
       </c>
       <c r="B18" s="8" t="n">
-        <v>16024</v>
+        <v>16000</v>
       </c>
       <c r="C18" s="9" t="n">
         <v>9.9</v>
@@ -1946,10 +1946,10 @@
         <v>8.640000000000001</v>
       </c>
       <c r="G18" s="10" t="n">
-        <v>9.81</v>
+        <v>9.83</v>
       </c>
       <c r="H18" s="10" t="n">
-        <v>8.83</v>
+        <v>8.85</v>
       </c>
       <c r="I18" s="10" t="n"/>
       <c r="J18" s="9" t="n">
@@ -1980,10 +1980,10 @@
         <v>2.32</v>
       </c>
       <c r="U18" s="10" t="n">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="V18" s="10" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="W18" s="10" t="n"/>
       <c r="X18" s="11" t="n">
@@ -2018,7 +2018,7 @@
         <v>2.62</v>
       </c>
       <c r="AI18" s="10" t="n">
-        <v>2.96</v>
+        <v>2.97</v>
       </c>
       <c r="AJ18" s="10" t="n">
         <v>2.59</v>
@@ -2047,10 +2047,10 @@
         <v>16.46</v>
       </c>
       <c r="G19" s="10" t="n">
-        <v>14.55</v>
+        <v>14.56</v>
       </c>
       <c r="H19" s="10" t="n">
-        <v>7.1</v>
+        <v>7.11</v>
       </c>
       <c r="I19" s="10" t="n"/>
       <c r="J19" s="9" t="n">
@@ -2084,7 +2084,7 @@
         <v>0.88</v>
       </c>
       <c r="V19" s="10" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="W19" s="10" t="n"/>
       <c r="X19" s="11" t="n">
@@ -2140,7 +2140,7 @@
         </is>
       </c>
       <c r="B21" s="8" t="n">
-        <v>80737</v>
+        <v>80657</v>
       </c>
       <c r="C21" s="9" t="n"/>
       <c r="D21" s="9" t="n">
@@ -2241,7 +2241,7 @@
         </is>
       </c>
       <c r="B22" s="8" t="n">
-        <v>12076</v>
+        <v>12064</v>
       </c>
       <c r="C22" s="9" t="n"/>
       <c r="D22" s="9" t="n">
@@ -2342,7 +2342,7 @@
         </is>
       </c>
       <c r="B23" s="8" t="n">
-        <v>16954</v>
+        <v>16937</v>
       </c>
       <c r="C23" s="9" t="n"/>
       <c r="D23" s="9" t="n">
@@ -2441,7 +2441,7 @@
         </is>
       </c>
       <c r="B24" s="8" t="n">
-        <v>2430</v>
+        <v>2428</v>
       </c>
       <c r="C24" s="9" t="n"/>
       <c r="D24" s="9" t="n">
@@ -2634,7 +2634,7 @@
         </is>
       </c>
       <c r="B27" s="8" t="n">
-        <v>5331</v>
+        <v>4553</v>
       </c>
       <c r="C27" s="9" t="n"/>
       <c r="D27" s="9" t="n"/>
@@ -2644,8 +2644,12 @@
       <c r="F27" s="9" t="n">
         <v>44.03</v>
       </c>
-      <c r="G27" s="10" t="n"/>
-      <c r="H27" s="10" t="n"/>
+      <c r="G27" s="10" t="n">
+        <v>22.92</v>
+      </c>
+      <c r="H27" s="10" t="n">
+        <v>15.24</v>
+      </c>
       <c r="I27" s="10" t="n"/>
       <c r="J27" s="9" t="n">
         <v>991.9299999999999</v>
@@ -2675,10 +2679,10 @@
         <v>5.43</v>
       </c>
       <c r="U27" s="10" t="n">
-        <v>4.04</v>
+        <v>3.46</v>
       </c>
       <c r="V27" s="10" t="n">
-        <v>3.29</v>
+        <v>2.82</v>
       </c>
       <c r="W27" s="10" t="n"/>
       <c r="X27" s="11" t="n">
@@ -2713,10 +2717,10 @@
         <v>0.61</v>
       </c>
       <c r="AI27" s="10" t="n">
-        <v>0.51</v>
+        <v>0.43</v>
       </c>
       <c r="AJ27" s="10" t="n">
-        <v>0.45</v>
+        <v>0.39</v>
       </c>
       <c r="AK27" s="10" t="n"/>
     </row>
@@ -2734,7 +2738,7 @@
         </is>
       </c>
       <c r="B29" s="8" t="n">
-        <v>10718</v>
+        <v>10674</v>
       </c>
       <c r="C29" s="9" t="n">
         <v>15.9</v>
@@ -2748,8 +2752,12 @@
       <c r="F29" s="9" t="n">
         <v>22.06</v>
       </c>
-      <c r="G29" s="10" t="n"/>
-      <c r="H29" s="10" t="n"/>
+      <c r="G29" s="10" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="H29" s="10" t="n">
+        <v>12.95</v>
+      </c>
       <c r="I29" s="10" t="n"/>
       <c r="J29" s="9" t="n">
         <v>10.08</v>
@@ -2779,7 +2787,7 @@
         <v>2.63</v>
       </c>
       <c r="U29" s="10" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="V29" s="10" t="n">
         <v>1.75</v>
@@ -2838,7 +2846,7 @@
         </is>
       </c>
       <c r="B31" s="8" t="n">
-        <v>1161</v>
+        <v>1156</v>
       </c>
       <c r="C31" s="9" t="n"/>
       <c r="D31" s="9" t="n"/>
@@ -2946,10 +2954,10 @@
         <v>20.62</v>
       </c>
       <c r="G32" s="15" t="n">
-        <v>10.75</v>
+        <v>10.82</v>
       </c>
       <c r="H32" s="15" t="n">
-        <v>9.02</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="I32" s="15" t="n"/>
       <c r="J32" s="15" t="n">
@@ -2983,7 +2991,7 @@
         <v>2.37</v>
       </c>
       <c r="V32" s="15" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="W32" s="15" t="n"/>
       <c r="X32" s="16" t="n">
@@ -2999,10 +3007,10 @@
         <v>22.59</v>
       </c>
       <c r="AB32" s="16" t="n">
-        <v>24.85</v>
+        <v>24.79</v>
       </c>
       <c r="AC32" s="16" t="n">
-        <v>24.13</v>
+        <v>23.99</v>
       </c>
       <c r="AD32" s="16" t="n"/>
       <c r="AE32" s="15" t="n">
@@ -3018,7 +3026,7 @@
         <v>2.09</v>
       </c>
       <c r="AI32" s="15" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AJ32" s="15" t="n">
         <v>1.22</v>
@@ -3048,7 +3056,7 @@
         <v>12.88</v>
       </c>
       <c r="H33" s="15" t="n">
-        <v>8.83</v>
+        <v>8.85</v>
       </c>
       <c r="I33" s="15" t="n"/>
       <c r="J33" s="15" t="n">
@@ -3238,8 +3246,12 @@
       <c r="F35" s="15" t="n">
         <v>44.03</v>
       </c>
-      <c r="G35" s="15" t="n"/>
-      <c r="H35" s="15" t="n"/>
+      <c r="G35" s="15" t="n">
+        <v>22.92</v>
+      </c>
+      <c r="H35" s="15" t="n">
+        <v>15.24</v>
+      </c>
       <c r="I35" s="15" t="n"/>
       <c r="J35" s="15" t="n">
         <v>991.9299999999999</v>
@@ -3269,10 +3281,10 @@
         <v>5.43</v>
       </c>
       <c r="U35" s="15" t="n">
-        <v>4.04</v>
+        <v>3.46</v>
       </c>
       <c r="V35" s="15" t="n">
-        <v>3.29</v>
+        <v>2.82</v>
       </c>
       <c r="W35" s="15" t="n"/>
       <c r="X35" s="16" t="n">
@@ -3307,10 +3319,10 @@
         <v>0.61</v>
       </c>
       <c r="AI35" s="15" t="n">
-        <v>0.51</v>
+        <v>0.43</v>
       </c>
       <c r="AJ35" s="15" t="n">
-        <v>0.45</v>
+        <v>0.39</v>
       </c>
       <c r="AK35" s="15" t="n"/>
     </row>
@@ -3333,8 +3345,12 @@
       <c r="F36" s="15" t="n">
         <v>22.06</v>
       </c>
-      <c r="G36" s="15" t="n"/>
-      <c r="H36" s="15" t="n"/>
+      <c r="G36" s="15" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="H36" s="15" t="n">
+        <v>12.95</v>
+      </c>
       <c r="I36" s="15" t="n"/>
       <c r="J36" s="15" t="n">
         <v>10.08</v>
@@ -3364,7 +3380,7 @@
         <v>2.63</v>
       </c>
       <c r="U36" s="15" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="V36" s="15" t="n">
         <v>1.75</v>
@@ -3522,10 +3538,10 @@
         <v>19.51</v>
       </c>
       <c r="G38" s="15" t="n">
-        <v>12.16</v>
+        <v>13.72</v>
       </c>
       <c r="H38" s="15" t="n">
-        <v>10.09</v>
+        <v>10.39</v>
       </c>
       <c r="I38" s="15" t="n">
         <v>15.74</v>
@@ -3581,10 +3597,10 @@
         <v>18.3</v>
       </c>
       <c r="AB38" s="16" t="n">
-        <v>21.61</v>
+        <v>21.59</v>
       </c>
       <c r="AC38" s="16" t="n">
-        <v>20.84</v>
+        <v>20.73</v>
       </c>
       <c r="AD38" s="16" t="n">
         <v>13.59</v>
@@ -3602,10 +3618,10 @@
         <v>1.45</v>
       </c>
       <c r="AI38" s="15" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AJ38" s="15" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AK38" s="15" t="n">
         <v>0.96</v>
@@ -3784,10 +3800,10 @@
         <v>34.46</v>
       </c>
       <c r="G43" s="10" t="n">
-        <v>19.06</v>
+        <v>19.33</v>
       </c>
       <c r="H43" s="10" t="n">
-        <v>15.19</v>
+        <v>15.37</v>
       </c>
       <c r="I43" s="10" t="n"/>
       <c r="J43" s="9" t="n">
@@ -3821,7 +3837,7 @@
         <v>3.92</v>
       </c>
       <c r="V43" s="10" t="n">
-        <v>3.23</v>
+        <v>3.24</v>
       </c>
       <c r="W43" s="10" t="n"/>
       <c r="X43" s="11" t="n">
@@ -3837,10 +3853,10 @@
         <v>19.14</v>
       </c>
       <c r="AB43" s="12" t="n">
-        <v>22.45</v>
+        <v>22.16</v>
       </c>
       <c r="AC43" s="12" t="n">
-        <v>23.3</v>
+        <v>23.09</v>
       </c>
       <c r="AD43" s="12" t="n"/>
       <c r="AE43" s="9" t="n">
@@ -4085,10 +4101,10 @@
         <v>26.64</v>
       </c>
       <c r="G46" s="10" t="n">
-        <v>12.2</v>
+        <v>12.23</v>
       </c>
       <c r="H46" s="10" t="n">
-        <v>9.41</v>
+        <v>9.48</v>
       </c>
       <c r="I46" s="10" t="n"/>
       <c r="J46" s="9" t="n">
@@ -4122,7 +4138,7 @@
         <v>2.73</v>
       </c>
       <c r="V46" s="10" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="W46" s="10" t="n"/>
       <c r="X46" s="11" t="n">
@@ -4138,10 +4154,10 @@
         <v>30.05</v>
       </c>
       <c r="AB46" s="12" t="n">
-        <v>24.93</v>
+        <v>24.88</v>
       </c>
       <c r="AC46" s="12" t="n">
-        <v>25.6</v>
+        <v>25.43</v>
       </c>
       <c r="AD46" s="12" t="n"/>
       <c r="AE46" s="9" t="n">
@@ -4157,7 +4173,7 @@
         <v>3.51</v>
       </c>
       <c r="AI46" s="10" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AJ46" s="10" t="n">
         <v>1.35</v>
@@ -4178,7 +4194,7 @@
         </is>
       </c>
       <c r="B48" s="8" t="n">
-        <v>127417</v>
+        <v>126429</v>
       </c>
       <c r="C48" s="9" t="n">
         <v>21.56</v>
@@ -4192,8 +4208,12 @@
       <c r="F48" s="9" t="n">
         <v>22.08</v>
       </c>
-      <c r="G48" s="10" t="n"/>
-      <c r="H48" s="10" t="n"/>
+      <c r="G48" s="10" t="n">
+        <v>18.15</v>
+      </c>
+      <c r="H48" s="10" t="n">
+        <v>16.87</v>
+      </c>
       <c r="I48" s="10" t="n"/>
       <c r="J48" s="9" t="n">
         <v>15.68</v>
@@ -4223,10 +4243,10 @@
         <v>16.48</v>
       </c>
       <c r="U48" s="10" t="n">
-        <v>12.51</v>
+        <v>12.42</v>
       </c>
       <c r="V48" s="10" t="n">
-        <v>9.16</v>
+        <v>9.09</v>
       </c>
       <c r="W48" s="10" t="n"/>
       <c r="X48" s="11" t="n">
@@ -4261,10 +4281,10 @@
         <v>1.48</v>
       </c>
       <c r="AI48" s="10" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AJ48" s="10" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="AK48" s="10" t="n"/>
     </row>
@@ -4275,7 +4295,7 @@
         </is>
       </c>
       <c r="B49" s="8" t="n">
-        <v>73853</v>
+        <v>73819</v>
       </c>
       <c r="C49" s="9" t="n">
         <v>17.07</v>
@@ -4289,8 +4309,12 @@
       <c r="F49" s="9" t="n">
         <v>19.36</v>
       </c>
-      <c r="G49" s="10" t="n"/>
-      <c r="H49" s="10" t="n"/>
+      <c r="G49" s="10" t="n">
+        <v>17.94</v>
+      </c>
+      <c r="H49" s="10" t="n">
+        <v>17.12</v>
+      </c>
       <c r="I49" s="10" t="n"/>
       <c r="J49" s="9" t="n">
         <v>12.31</v>
@@ -4320,7 +4344,7 @@
         <v>4.86</v>
       </c>
       <c r="U49" s="10" t="n">
-        <v>3.78</v>
+        <v>3.77</v>
       </c>
       <c r="V49" s="10" t="n">
         <v>3.27</v>
@@ -4372,7 +4396,7 @@
         </is>
       </c>
       <c r="B50" s="8" t="n">
-        <v>93134</v>
+        <v>93076</v>
       </c>
       <c r="C50" s="9" t="n">
         <v>20.08</v>
@@ -4386,8 +4410,12 @@
       <c r="F50" s="9" t="n">
         <v>21.62</v>
       </c>
-      <c r="G50" s="10" t="n"/>
-      <c r="H50" s="10" t="n"/>
+      <c r="G50" s="10" t="n">
+        <v>20.25</v>
+      </c>
+      <c r="H50" s="10" t="n">
+        <v>18.47</v>
+      </c>
       <c r="I50" s="10" t="n"/>
       <c r="J50" s="9" t="n">
         <v>14.87</v>
@@ -4420,7 +4448,7 @@
         <v>3.27</v>
       </c>
       <c r="V50" s="10" t="n">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="W50" s="10" t="n"/>
       <c r="X50" s="11" t="n">
@@ -4455,7 +4483,7 @@
         <v>1.73</v>
       </c>
       <c r="AI50" s="10" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AJ50" s="10" t="n">
         <v>1.59</v>
@@ -4469,7 +4497,7 @@
         </is>
       </c>
       <c r="B51" s="8" t="n">
-        <v>261357</v>
+        <v>260296</v>
       </c>
       <c r="C51" s="9" t="n">
         <v>28.47</v>
@@ -4483,8 +4511,12 @@
       <c r="F51" s="9" t="n">
         <v>36.57</v>
       </c>
-      <c r="G51" s="10" t="n"/>
-      <c r="H51" s="10" t="n"/>
+      <c r="G51" s="10" t="n">
+        <v>26.74</v>
+      </c>
+      <c r="H51" s="10" t="n">
+        <v>24.64</v>
+      </c>
       <c r="I51" s="10" t="n"/>
       <c r="J51" s="9" t="n">
         <v>15.21</v>
@@ -4514,10 +4546,10 @@
         <v>3.77</v>
       </c>
       <c r="U51" s="10" t="n">
-        <v>3.72</v>
+        <v>3.71</v>
       </c>
       <c r="V51" s="10" t="n">
-        <v>3.46</v>
+        <v>3.44</v>
       </c>
       <c r="W51" s="10" t="n"/>
       <c r="X51" s="11" t="n">
@@ -4552,10 +4584,10 @@
         <v>2.78</v>
       </c>
       <c r="AI51" s="10" t="n">
-        <v>2.72</v>
+        <v>2.71</v>
       </c>
       <c r="AJ51" s="10" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="AK51" s="10" t="n"/>
     </row>
@@ -4566,7 +4598,7 @@
         </is>
       </c>
       <c r="B52" s="8" t="n">
-        <v>10718</v>
+        <v>10674</v>
       </c>
       <c r="C52" s="9" t="n">
         <v>15.9</v>
@@ -4580,8 +4612,12 @@
       <c r="F52" s="9" t="n">
         <v>22.06</v>
       </c>
-      <c r="G52" s="10" t="n"/>
-      <c r="H52" s="10" t="n"/>
+      <c r="G52" s="10" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="H52" s="10" t="n">
+        <v>12.95</v>
+      </c>
       <c r="I52" s="10" t="n"/>
       <c r="J52" s="9" t="n">
         <v>10.08</v>
@@ -4611,7 +4647,7 @@
         <v>2.63</v>
       </c>
       <c r="U52" s="10" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="V52" s="10" t="n">
         <v>1.75</v>
@@ -4670,7 +4706,7 @@
         </is>
       </c>
       <c r="B54" s="8" t="n">
-        <v>57204</v>
+        <v>56088</v>
       </c>
       <c r="C54" s="9" t="n">
         <v>17.03</v>
@@ -4684,8 +4720,12 @@
       <c r="F54" s="9" t="n">
         <v>102.9</v>
       </c>
-      <c r="G54" s="10" t="n"/>
-      <c r="H54" s="10" t="n"/>
+      <c r="G54" s="10" t="n">
+        <v>29.25</v>
+      </c>
+      <c r="H54" s="10" t="n">
+        <v>20.57</v>
+      </c>
       <c r="I54" s="10" t="n"/>
       <c r="J54" s="9" t="n">
         <v>8.5</v>
@@ -4715,10 +4755,10 @@
         <v>14.29</v>
       </c>
       <c r="U54" s="10" t="n">
-        <v>8.539999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="V54" s="10" t="n">
-        <v>6.97</v>
+        <v>6.85</v>
       </c>
       <c r="W54" s="10" t="n"/>
       <c r="X54" s="11" t="n">
@@ -4753,10 +4793,10 @@
         <v>7.21</v>
       </c>
       <c r="AI54" s="10" t="n">
-        <v>3.65</v>
+        <v>3.59</v>
       </c>
       <c r="AJ54" s="10" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AK54" s="10" t="n"/>
     </row>
@@ -4774,7 +4814,7 @@
         </is>
       </c>
       <c r="B56" s="8" t="n">
-        <v>770</v>
+        <v>77068</v>
       </c>
       <c r="C56" s="9" t="n">
         <v>16.56</v>
@@ -4788,8 +4828,12 @@
       <c r="F56" s="9" t="n">
         <v>24.33</v>
       </c>
-      <c r="G56" s="10" t="n"/>
-      <c r="H56" s="10" t="n"/>
+      <c r="G56" s="10" t="n">
+        <v>23.53</v>
+      </c>
+      <c r="H56" s="10" t="n">
+        <v>20.66</v>
+      </c>
       <c r="I56" s="10" t="n"/>
       <c r="J56" s="9" t="n">
         <v>9.84</v>
@@ -4819,10 +4863,10 @@
         <v>4.26</v>
       </c>
       <c r="U56" s="10" t="n">
-        <v>0.04</v>
+        <v>4.48</v>
       </c>
       <c r="V56" s="10" t="n">
-        <v>0.04</v>
+        <v>4.06</v>
       </c>
       <c r="W56" s="10" t="n"/>
       <c r="X56" s="11" t="n">
@@ -4857,10 +4901,10 @@
         <v>1.77</v>
       </c>
       <c r="AI56" s="10" t="n">
-        <v>0.02</v>
+        <v>1.75</v>
       </c>
       <c r="AJ56" s="10" t="n">
-        <v>0.02</v>
+        <v>1.6</v>
       </c>
       <c r="AK56" s="10" t="n"/>
     </row>
@@ -4878,7 +4922,7 @@
         </is>
       </c>
       <c r="B58" s="8" t="n">
-        <v>32699</v>
+        <v>32619</v>
       </c>
       <c r="C58" s="9" t="n">
         <v>5</v>
@@ -4892,8 +4936,12 @@
       <c r="F58" s="9" t="n">
         <v>23.17</v>
       </c>
-      <c r="G58" s="10" t="n"/>
-      <c r="H58" s="10" t="n"/>
+      <c r="G58" s="10" t="n">
+        <v>21.13</v>
+      </c>
+      <c r="H58" s="10" t="n">
+        <v>17.59</v>
+      </c>
       <c r="I58" s="10" t="n"/>
       <c r="J58" s="9" t="n">
         <v>4.69</v>
@@ -4982,7 +5030,7 @@
         </is>
       </c>
       <c r="B60" s="8" t="n">
-        <v>35387</v>
+        <v>35366</v>
       </c>
       <c r="C60" s="9" t="n">
         <v>24.79</v>
@@ -4996,8 +5044,12 @@
       <c r="F60" s="9" t="n">
         <v>45.89</v>
       </c>
-      <c r="G60" s="10" t="n"/>
-      <c r="H60" s="10" t="n"/>
+      <c r="G60" s="10" t="n">
+        <v>43.52</v>
+      </c>
+      <c r="H60" s="10" t="n">
+        <v>34.15</v>
+      </c>
       <c r="I60" s="10" t="n"/>
       <c r="J60" s="9" t="n">
         <v>11.71</v>
@@ -5129,7 +5181,7 @@
         <v>3.92</v>
       </c>
       <c r="V61" s="15" t="n">
-        <v>3.23</v>
+        <v>3.24</v>
       </c>
       <c r="W61" s="15" t="n"/>
       <c r="X61" s="16" t="n">
@@ -5145,10 +5197,10 @@
         <v>19.14</v>
       </c>
       <c r="AB61" s="16" t="n">
-        <v>22.45</v>
+        <v>22.16</v>
       </c>
       <c r="AC61" s="16" t="n">
-        <v>23.3</v>
+        <v>23.09</v>
       </c>
       <c r="AD61" s="16" t="n"/>
       <c r="AE61" s="15" t="n">
@@ -5190,8 +5242,12 @@
       <c r="F62" s="15" t="n">
         <v>22.06</v>
       </c>
-      <c r="G62" s="15" t="n"/>
-      <c r="H62" s="15" t="n"/>
+      <c r="G62" s="15" t="n">
+        <v>18.15</v>
+      </c>
+      <c r="H62" s="15" t="n">
+        <v>17.12</v>
+      </c>
       <c r="I62" s="15" t="n"/>
       <c r="J62" s="15" t="n">
         <v>14.87</v>
@@ -5221,7 +5277,7 @@
         <v>3.77</v>
       </c>
       <c r="U62" s="15" t="n">
-        <v>3.72</v>
+        <v>3.71</v>
       </c>
       <c r="V62" s="15" t="n">
         <v>3.27</v>
@@ -5259,7 +5315,7 @@
         <v>1.73</v>
       </c>
       <c r="AI62" s="15" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AJ62" s="15" t="n">
         <v>1.57</v>
@@ -5285,8 +5341,12 @@
       <c r="F63" s="15" t="n">
         <v>102.9</v>
       </c>
-      <c r="G63" s="15" t="n"/>
-      <c r="H63" s="15" t="n"/>
+      <c r="G63" s="15" t="n">
+        <v>29.25</v>
+      </c>
+      <c r="H63" s="15" t="n">
+        <v>20.57</v>
+      </c>
       <c r="I63" s="15" t="n"/>
       <c r="J63" s="15" t="n">
         <v>8.5</v>
@@ -5316,10 +5376,10 @@
         <v>14.29</v>
       </c>
       <c r="U63" s="15" t="n">
-        <v>8.539999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="V63" s="15" t="n">
-        <v>6.97</v>
+        <v>6.85</v>
       </c>
       <c r="W63" s="15" t="n"/>
       <c r="X63" s="16" t="n">
@@ -5354,10 +5414,10 @@
         <v>7.21</v>
       </c>
       <c r="AI63" s="15" t="n">
-        <v>3.65</v>
+        <v>3.59</v>
       </c>
       <c r="AJ63" s="15" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AK63" s="15" t="n"/>
     </row>
@@ -5380,8 +5440,12 @@
       <c r="F64" s="15" t="n">
         <v>24.33</v>
       </c>
-      <c r="G64" s="15" t="n"/>
-      <c r="H64" s="15" t="n"/>
+      <c r="G64" s="15" t="n">
+        <v>23.53</v>
+      </c>
+      <c r="H64" s="15" t="n">
+        <v>20.66</v>
+      </c>
       <c r="I64" s="15" t="n"/>
       <c r="J64" s="15" t="n">
         <v>9.84</v>
@@ -5411,10 +5475,10 @@
         <v>4.26</v>
       </c>
       <c r="U64" s="15" t="n">
-        <v>0.04</v>
+        <v>4.48</v>
       </c>
       <c r="V64" s="15" t="n">
-        <v>0.04</v>
+        <v>4.06</v>
       </c>
       <c r="W64" s="15" t="n"/>
       <c r="X64" s="16" t="n">
@@ -5449,10 +5513,10 @@
         <v>1.77</v>
       </c>
       <c r="AI64" s="15" t="n">
-        <v>0.02</v>
+        <v>1.75</v>
       </c>
       <c r="AJ64" s="15" t="n">
-        <v>0.02</v>
+        <v>1.6</v>
       </c>
       <c r="AK64" s="15" t="n"/>
     </row>
@@ -5475,8 +5539,12 @@
       <c r="F65" s="15" t="n">
         <v>23.17</v>
       </c>
-      <c r="G65" s="15" t="n"/>
-      <c r="H65" s="15" t="n"/>
+      <c r="G65" s="15" t="n">
+        <v>21.13</v>
+      </c>
+      <c r="H65" s="15" t="n">
+        <v>17.59</v>
+      </c>
       <c r="I65" s="15" t="n"/>
       <c r="J65" s="15" t="n">
         <v>4.69</v>
@@ -5570,8 +5638,12 @@
       <c r="F66" s="15" t="n">
         <v>45.89</v>
       </c>
-      <c r="G66" s="15" t="n"/>
-      <c r="H66" s="15" t="n"/>
+      <c r="G66" s="15" t="n">
+        <v>43.52</v>
+      </c>
+      <c r="H66" s="15" t="n">
+        <v>34.15</v>
+      </c>
       <c r="I66" s="15" t="n"/>
       <c r="J66" s="15" t="n">
         <v>11.71</v>
@@ -5666,10 +5738,10 @@
         <v>30.55</v>
       </c>
       <c r="G67" s="15" t="n">
-        <v>34.97</v>
+        <v>22.33</v>
       </c>
       <c r="H67" s="15" t="n">
-        <v>23.98</v>
+        <v>19.52</v>
       </c>
       <c r="I67" s="15" t="n"/>
       <c r="J67" s="15" t="n">
@@ -5700,10 +5772,10 @@
         <v>4.93</v>
       </c>
       <c r="U67" s="15" t="n">
-        <v>3.75</v>
+        <v>3.84</v>
       </c>
       <c r="V67" s="15" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="W67" s="15" t="n"/>
       <c r="X67" s="16" t="n">
@@ -5738,10 +5810,10 @@
         <v>2.04</v>
       </c>
       <c r="AI67" s="15" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AJ67" s="15" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="AK67" s="15" t="n"/>
     </row>
@@ -6363,7 +6435,7 @@
         </is>
       </c>
       <c r="B78" s="8" t="n">
-        <v>335912</v>
+        <v>340013</v>
       </c>
       <c r="C78" s="9" t="n">
         <v>18.45</v>
@@ -6377,8 +6449,12 @@
       <c r="F78" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="G78" s="10" t="n"/>
-      <c r="H78" s="10" t="n"/>
+      <c r="G78" s="10" t="n">
+        <v>26.74</v>
+      </c>
+      <c r="H78" s="10" t="n">
+        <v>22.43</v>
+      </c>
       <c r="I78" s="10" t="n"/>
       <c r="J78" s="9" t="n">
         <v>13.46</v>
@@ -6408,10 +6484,10 @@
         <v>12.5</v>
       </c>
       <c r="U78" s="10" t="n">
-        <v>10.93</v>
+        <v>11.07</v>
       </c>
       <c r="V78" s="10" t="n">
-        <v>8.01</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="W78" s="10" t="n"/>
       <c r="X78" s="11" t="n">
@@ -6446,10 +6522,10 @@
         <v>3.94</v>
       </c>
       <c r="AI78" s="10" t="n">
-        <v>4.22</v>
+        <v>4.27</v>
       </c>
       <c r="AJ78" s="10" t="n">
-        <v>3.79</v>
+        <v>3.83</v>
       </c>
       <c r="AK78" s="10" t="n"/>
     </row>
@@ -6460,7 +6536,7 @@
         </is>
       </c>
       <c r="B79" s="8" t="n">
-        <v>173062</v>
+        <v>173528</v>
       </c>
       <c r="C79" s="9" t="n">
         <v>16.58</v>
@@ -6474,8 +6550,12 @@
       <c r="F79" s="9" t="n">
         <v>24.83</v>
       </c>
-      <c r="G79" s="10" t="n"/>
-      <c r="H79" s="10" t="n"/>
+      <c r="G79" s="10" t="n">
+        <v>35.44</v>
+      </c>
+      <c r="H79" s="10" t="n">
+        <v>27.92</v>
+      </c>
       <c r="I79" s="10" t="n"/>
       <c r="J79" s="9" t="n">
         <v>13.71</v>
@@ -6505,10 +6585,10 @@
         <v>4.81</v>
       </c>
       <c r="U79" s="10" t="n">
-        <v>5.95</v>
+        <v>5.97</v>
       </c>
       <c r="V79" s="10" t="n">
-        <v>5.23</v>
+        <v>5.25</v>
       </c>
       <c r="W79" s="10" t="n"/>
       <c r="X79" s="11" t="n">
@@ -6543,10 +6623,10 @@
         <v>2.79</v>
       </c>
       <c r="AI79" s="10" t="n">
-        <v>4.21</v>
+        <v>4.22</v>
       </c>
       <c r="AJ79" s="10" t="n">
-        <v>3.88</v>
+        <v>3.89</v>
       </c>
       <c r="AK79" s="10" t="n"/>
     </row>
@@ -6557,7 +6637,7 @@
         </is>
       </c>
       <c r="B80" s="8" t="n">
-        <v>18655</v>
+        <v>14408</v>
       </c>
       <c r="C80" s="9" t="n">
         <v>10.64</v>
@@ -6571,8 +6651,12 @@
       <c r="F80" s="9" t="n">
         <v>22.45</v>
       </c>
-      <c r="G80" s="10" t="n"/>
-      <c r="H80" s="10" t="n"/>
+      <c r="G80" s="10" t="n">
+        <v>25.76</v>
+      </c>
+      <c r="H80" s="10" t="n">
+        <v>16.79</v>
+      </c>
       <c r="I80" s="10" t="n"/>
       <c r="J80" s="9" t="n">
         <v>10.23</v>
@@ -6602,10 +6686,10 @@
         <v>1.48</v>
       </c>
       <c r="U80" s="10" t="n">
-        <v>2.31</v>
+        <v>1.79</v>
       </c>
       <c r="V80" s="10" t="n">
-        <v>2.17</v>
+        <v>1.68</v>
       </c>
       <c r="W80" s="10" t="n"/>
       <c r="X80" s="11" t="n">
@@ -6640,10 +6724,10 @@
         <v>0.63</v>
       </c>
       <c r="AI80" s="10" t="n">
-        <v>1.02</v>
+        <v>0.79</v>
       </c>
       <c r="AJ80" s="10" t="n">
-        <v>0.98</v>
+        <v>0.76</v>
       </c>
       <c r="AK80" s="10" t="n"/>
     </row>
@@ -6654,7 +6738,7 @@
         </is>
       </c>
       <c r="B81" s="8" t="n">
-        <v>64087</v>
+        <v>64966</v>
       </c>
       <c r="C81" s="9" t="n">
         <v>11.71</v>
@@ -6668,8 +6752,12 @@
       <c r="F81" s="9" t="n">
         <v>20.48</v>
       </c>
-      <c r="G81" s="10" t="n"/>
-      <c r="H81" s="10" t="n"/>
+      <c r="G81" s="10" t="n">
+        <v>20.72</v>
+      </c>
+      <c r="H81" s="10" t="n">
+        <v>17.8</v>
+      </c>
       <c r="I81" s="10" t="n"/>
       <c r="J81" s="9" t="n">
         <v>6.73</v>
@@ -6699,10 +6787,10 @@
         <v>5.69</v>
       </c>
       <c r="U81" s="10" t="n">
-        <v>5.56</v>
+        <v>5.63</v>
       </c>
       <c r="V81" s="10" t="n">
-        <v>4.41</v>
+        <v>4.47</v>
       </c>
       <c r="W81" s="10" t="n"/>
       <c r="X81" s="11" t="n">
@@ -6737,10 +6825,10 @@
         <v>3.17</v>
       </c>
       <c r="AI81" s="10" t="n">
-        <v>3.61</v>
+        <v>3.66</v>
       </c>
       <c r="AJ81" s="10" t="n">
-        <v>3.31</v>
+        <v>3.36</v>
       </c>
       <c r="AK81" s="10" t="n"/>
     </row>
@@ -6758,7 +6846,7 @@
         </is>
       </c>
       <c r="B83" s="8" t="n">
-        <v>41066</v>
+        <v>41026</v>
       </c>
       <c r="C83" s="9" t="n"/>
       <c r="D83" s="9" t="n">
@@ -6859,7 +6947,7 @@
         </is>
       </c>
       <c r="B84" s="8" t="n">
-        <v>7289</v>
+        <v>7282</v>
       </c>
       <c r="C84" s="9" t="n"/>
       <c r="D84" s="9" t="n">
@@ -6967,7 +7055,7 @@
         </is>
       </c>
       <c r="B86" s="8" t="n">
-        <v>66856</v>
+        <v>66780</v>
       </c>
       <c r="C86" s="9" t="n">
         <v>11.71</v>
@@ -6981,8 +7069,12 @@
       <c r="F86" s="9" t="n">
         <v>17.46</v>
       </c>
-      <c r="G86" s="10" t="n"/>
-      <c r="H86" s="10" t="n"/>
+      <c r="G86" s="10" t="n">
+        <v>15.08</v>
+      </c>
+      <c r="H86" s="10" t="n">
+        <v>12.62</v>
+      </c>
       <c r="I86" s="10" t="n"/>
       <c r="J86" s="9" t="n">
         <v>7.78</v>
@@ -7071,7 +7163,7 @@
         </is>
       </c>
       <c r="B88" s="8" t="n">
-        <v>24362</v>
+        <v>24311</v>
       </c>
       <c r="C88" s="9" t="n">
         <v>31.28</v>
@@ -7172,7 +7264,7 @@
         </is>
       </c>
       <c r="B89" s="8" t="n">
-        <v>12163</v>
+        <v>12138</v>
       </c>
       <c r="C89" s="9" t="n">
         <v>13.89</v>
@@ -7384,8 +7476,12 @@
       <c r="F91" s="15" t="n">
         <v>23.64</v>
       </c>
-      <c r="G91" s="15" t="n"/>
-      <c r="H91" s="15" t="n"/>
+      <c r="G91" s="15" t="n">
+        <v>26.25</v>
+      </c>
+      <c r="H91" s="15" t="n">
+        <v>20.12</v>
+      </c>
       <c r="I91" s="15" t="n"/>
       <c r="J91" s="15" t="n">
         <v>11.85</v>
@@ -7415,10 +7511,10 @@
         <v>5.25</v>
       </c>
       <c r="U91" s="15" t="n">
-        <v>5.75</v>
+        <v>5.8</v>
       </c>
       <c r="V91" s="15" t="n">
-        <v>4.82</v>
+        <v>4.86</v>
       </c>
       <c r="W91" s="15" t="n"/>
       <c r="X91" s="16" t="n">
@@ -7453,10 +7549,10 @@
         <v>2.98</v>
       </c>
       <c r="AI91" s="15" t="n">
-        <v>3.91</v>
+        <v>3.94</v>
       </c>
       <c r="AJ91" s="15" t="n">
-        <v>3.55</v>
+        <v>3.59</v>
       </c>
       <c r="AK91" s="15" t="n"/>
     </row>
@@ -7578,8 +7674,12 @@
       <c r="F93" s="15" t="n">
         <v>17.46</v>
       </c>
-      <c r="G93" s="15" t="n"/>
-      <c r="H93" s="15" t="n"/>
+      <c r="G93" s="15" t="n">
+        <v>15.08</v>
+      </c>
+      <c r="H93" s="15" t="n">
+        <v>12.62</v>
+      </c>
       <c r="I93" s="15" t="n"/>
       <c r="J93" s="15" t="n">
         <v>7.78</v>
@@ -7773,10 +7873,10 @@
         <v>18.97</v>
       </c>
       <c r="G95" s="15" t="n">
-        <v>10.41</v>
+        <v>15.11</v>
       </c>
       <c r="H95" s="15" t="n">
-        <v>8.140000000000001</v>
+        <v>12.61</v>
       </c>
       <c r="I95" s="15" t="n">
         <v>12.74</v>
@@ -7811,10 +7911,10 @@
         <v>1.48</v>
       </c>
       <c r="U95" s="15" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="V95" s="15" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="W95" s="15" t="n">
         <v>1.38</v>
@@ -7853,10 +7953,10 @@
         <v>0.97</v>
       </c>
       <c r="AI95" s="15" t="n">
-        <v>1.17</v>
+        <v>1.06</v>
       </c>
       <c r="AJ95" s="15" t="n">
-        <v>1.09</v>
+        <v>0.99</v>
       </c>
       <c r="AK95" s="15" t="n">
         <v>1.07</v>
@@ -7995,10 +8095,10 @@
         <v>37.73</v>
       </c>
       <c r="J2" s="9" t="n">
-        <v>11.44</v>
+        <v>11.7</v>
       </c>
       <c r="K2" s="9" t="n">
-        <v>9.84</v>
+        <v>10.05</v>
       </c>
       <c r="L2" s="9" t="n"/>
     </row>
@@ -8037,10 +8137,10 @@
         <v>27.94</v>
       </c>
       <c r="J3" s="9" t="n">
+        <v>10.65</v>
+      </c>
+      <c r="K3" s="9" t="n">
         <v>10.51</v>
-      </c>
-      <c r="K3" s="9" t="n">
-        <v>10.36</v>
       </c>
       <c r="L3" s="9" t="n"/>
     </row>
@@ -8077,10 +8177,10 @@
         <v>37.73</v>
       </c>
       <c r="J4" s="9" t="n">
-        <v>15.63</v>
+        <v>15.65</v>
       </c>
       <c r="K4" s="9" t="n">
-        <v>10.89</v>
+        <v>10.88</v>
       </c>
       <c r="L4" s="9" t="n"/>
     </row>
@@ -8119,10 +8219,10 @@
         <v>13.27</v>
       </c>
       <c r="J5" s="9" t="n">
-        <v>5.08</v>
+        <v>5.11</v>
       </c>
       <c r="K5" s="9" t="n">
-        <v>4.32</v>
+        <v>4.38</v>
       </c>
       <c r="L5" s="9" t="n"/>
     </row>
@@ -8222,7 +8322,7 @@
         </is>
       </c>
       <c r="E8" s="7" t="n">
-        <v>40317</v>
+        <v>40232</v>
       </c>
       <c r="F8" s="9" t="n">
         <v>577.76</v>
@@ -8266,7 +8366,7 @@
         </is>
       </c>
       <c r="E9" s="7" t="n">
-        <v>16024</v>
+        <v>16000</v>
       </c>
       <c r="F9" s="9" t="n">
         <v>9.9</v>
@@ -8281,10 +8381,10 @@
         <v>8.640000000000001</v>
       </c>
       <c r="J9" s="9" t="n">
-        <v>9.81</v>
+        <v>9.83</v>
       </c>
       <c r="K9" s="9" t="n">
-        <v>8.83</v>
+        <v>8.85</v>
       </c>
       <c r="L9" s="9" t="n"/>
     </row>
@@ -8325,10 +8425,10 @@
         <v>16.46</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>14.55</v>
+        <v>14.56</v>
       </c>
       <c r="K10" s="9" t="n">
-        <v>7.1</v>
+        <v>7.11</v>
       </c>
       <c r="L10" s="9" t="n"/>
     </row>
@@ -8354,7 +8454,7 @@
         </is>
       </c>
       <c r="E11" s="7" t="n">
-        <v>80737</v>
+        <v>80657</v>
       </c>
       <c r="F11" s="9" t="n"/>
       <c r="G11" s="9" t="n">
@@ -8398,7 +8498,7 @@
         </is>
       </c>
       <c r="E12" s="7" t="n">
-        <v>12076</v>
+        <v>12064</v>
       </c>
       <c r="F12" s="9" t="n"/>
       <c r="G12" s="9" t="n">
@@ -8442,7 +8542,7 @@
         </is>
       </c>
       <c r="E13" s="7" t="n">
-        <v>16954</v>
+        <v>16937</v>
       </c>
       <c r="F13" s="9" t="n"/>
       <c r="G13" s="9" t="n">
@@ -8484,7 +8584,7 @@
         </is>
       </c>
       <c r="E14" s="7" t="n">
-        <v>2430</v>
+        <v>2428</v>
       </c>
       <c r="F14" s="9" t="n"/>
       <c r="G14" s="9" t="n">
@@ -8568,7 +8668,7 @@
         </is>
       </c>
       <c r="E16" s="7" t="n">
-        <v>5331</v>
+        <v>4553</v>
       </c>
       <c r="F16" s="9" t="n"/>
       <c r="G16" s="9" t="n"/>
@@ -8578,8 +8678,12 @@
       <c r="I16" s="9" t="n">
         <v>44.03</v>
       </c>
-      <c r="J16" s="9" t="n"/>
-      <c r="K16" s="9" t="n"/>
+      <c r="J16" s="9" t="n">
+        <v>22.92</v>
+      </c>
+      <c r="K16" s="9" t="n">
+        <v>15.24</v>
+      </c>
       <c r="L16" s="9" t="n"/>
     </row>
     <row r="17">
@@ -8604,7 +8708,7 @@
         </is>
       </c>
       <c r="E17" s="7" t="n">
-        <v>10718</v>
+        <v>10674</v>
       </c>
       <c r="F17" s="9" t="n">
         <v>15.9</v>
@@ -8618,8 +8722,12 @@
       <c r="I17" s="9" t="n">
         <v>22.06</v>
       </c>
-      <c r="J17" s="9" t="n"/>
-      <c r="K17" s="9" t="n"/>
+      <c r="J17" s="9" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="K17" s="9" t="n">
+        <v>12.95</v>
+      </c>
       <c r="L17" s="9" t="n"/>
     </row>
     <row r="18">
@@ -8644,7 +8752,7 @@
         </is>
       </c>
       <c r="E18" s="7" t="n">
-        <v>1161</v>
+        <v>1156</v>
       </c>
       <c r="F18" s="9" t="n"/>
       <c r="G18" s="9" t="n"/>
@@ -8695,10 +8803,10 @@
         <v>32.18</v>
       </c>
       <c r="J19" s="9" t="n">
-        <v>27.01</v>
+        <v>27.64</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>22.52</v>
+        <v>22.6</v>
       </c>
       <c r="L19" s="9" t="n"/>
     </row>
@@ -8953,10 +9061,10 @@
         <v>34.46</v>
       </c>
       <c r="J25" s="9" t="n">
-        <v>19.06</v>
+        <v>19.33</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>15.19</v>
+        <v>15.37</v>
       </c>
       <c r="L25" s="9" t="n"/>
     </row>
@@ -9083,10 +9191,10 @@
         <v>26.64</v>
       </c>
       <c r="J28" s="9" t="n">
-        <v>12.2</v>
+        <v>12.23</v>
       </c>
       <c r="K28" s="9" t="n">
-        <v>9.41</v>
+        <v>9.48</v>
       </c>
       <c r="L28" s="9" t="n"/>
     </row>
@@ -9112,7 +9220,7 @@
         </is>
       </c>
       <c r="E29" s="7" t="n">
-        <v>127417</v>
+        <v>126429</v>
       </c>
       <c r="F29" s="9" t="n">
         <v>21.56</v>
@@ -9126,8 +9234,12 @@
       <c r="I29" s="9" t="n">
         <v>22.08</v>
       </c>
-      <c r="J29" s="9" t="n"/>
-      <c r="K29" s="9" t="n"/>
+      <c r="J29" s="9" t="n">
+        <v>18.15</v>
+      </c>
+      <c r="K29" s="9" t="n">
+        <v>16.87</v>
+      </c>
       <c r="L29" s="9" t="n"/>
     </row>
     <row r="30">
@@ -9152,7 +9264,7 @@
         </is>
       </c>
       <c r="E30" s="7" t="n">
-        <v>73853</v>
+        <v>73819</v>
       </c>
       <c r="F30" s="9" t="n">
         <v>17.07</v>
@@ -9166,8 +9278,12 @@
       <c r="I30" s="9" t="n">
         <v>19.36</v>
       </c>
-      <c r="J30" s="9" t="n"/>
-      <c r="K30" s="9" t="n"/>
+      <c r="J30" s="9" t="n">
+        <v>17.94</v>
+      </c>
+      <c r="K30" s="9" t="n">
+        <v>17.12</v>
+      </c>
       <c r="L30" s="9" t="n"/>
     </row>
     <row r="31">
@@ -9192,7 +9308,7 @@
         </is>
       </c>
       <c r="E31" s="7" t="n">
-        <v>93134</v>
+        <v>93076</v>
       </c>
       <c r="F31" s="9" t="n">
         <v>20.08</v>
@@ -9206,8 +9322,12 @@
       <c r="I31" s="9" t="n">
         <v>21.62</v>
       </c>
-      <c r="J31" s="9" t="n"/>
-      <c r="K31" s="9" t="n"/>
+      <c r="J31" s="9" t="n">
+        <v>20.25</v>
+      </c>
+      <c r="K31" s="9" t="n">
+        <v>18.47</v>
+      </c>
       <c r="L31" s="9" t="n"/>
     </row>
     <row r="32">
@@ -9232,7 +9352,7 @@
         </is>
       </c>
       <c r="E32" s="7" t="n">
-        <v>261357</v>
+        <v>260296</v>
       </c>
       <c r="F32" s="9" t="n">
         <v>28.47</v>
@@ -9246,8 +9366,12 @@
       <c r="I32" s="9" t="n">
         <v>36.57</v>
       </c>
-      <c r="J32" s="9" t="n"/>
-      <c r="K32" s="9" t="n"/>
+      <c r="J32" s="9" t="n">
+        <v>26.74</v>
+      </c>
+      <c r="K32" s="9" t="n">
+        <v>24.64</v>
+      </c>
       <c r="L32" s="9" t="n"/>
     </row>
     <row r="33">
@@ -9272,7 +9396,7 @@
         </is>
       </c>
       <c r="E33" s="7" t="n">
-        <v>10718</v>
+        <v>10674</v>
       </c>
       <c r="F33" s="9" t="n">
         <v>15.9</v>
@@ -9286,8 +9410,12 @@
       <c r="I33" s="9" t="n">
         <v>22.06</v>
       </c>
-      <c r="J33" s="9" t="n"/>
-      <c r="K33" s="9" t="n"/>
+      <c r="J33" s="9" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="K33" s="9" t="n">
+        <v>12.95</v>
+      </c>
       <c r="L33" s="9" t="n"/>
     </row>
     <row r="34">
@@ -9312,7 +9440,7 @@
         </is>
       </c>
       <c r="E34" s="7" t="n">
-        <v>57204</v>
+        <v>56088</v>
       </c>
       <c r="F34" s="9" t="n">
         <v>17.03</v>
@@ -9326,8 +9454,12 @@
       <c r="I34" s="9" t="n">
         <v>102.9</v>
       </c>
-      <c r="J34" s="9" t="n"/>
-      <c r="K34" s="9" t="n"/>
+      <c r="J34" s="9" t="n">
+        <v>29.25</v>
+      </c>
+      <c r="K34" s="9" t="n">
+        <v>20.57</v>
+      </c>
       <c r="L34" s="9" t="n"/>
     </row>
     <row r="35">
@@ -9352,7 +9484,7 @@
         </is>
       </c>
       <c r="E35" s="7" t="n">
-        <v>770</v>
+        <v>77068</v>
       </c>
       <c r="F35" s="9" t="n">
         <v>16.56</v>
@@ -9366,8 +9498,12 @@
       <c r="I35" s="9" t="n">
         <v>24.33</v>
       </c>
-      <c r="J35" s="9" t="n"/>
-      <c r="K35" s="9" t="n"/>
+      <c r="J35" s="9" t="n">
+        <v>23.53</v>
+      </c>
+      <c r="K35" s="9" t="n">
+        <v>20.66</v>
+      </c>
       <c r="L35" s="9" t="n"/>
     </row>
     <row r="36">
@@ -9392,7 +9528,7 @@
         </is>
       </c>
       <c r="E36" s="7" t="n">
-        <v>32699</v>
+        <v>32619</v>
       </c>
       <c r="F36" s="9" t="n">
         <v>5</v>
@@ -9406,8 +9542,12 @@
       <c r="I36" s="9" t="n">
         <v>23.17</v>
       </c>
-      <c r="J36" s="9" t="n"/>
-      <c r="K36" s="9" t="n"/>
+      <c r="J36" s="9" t="n">
+        <v>21.13</v>
+      </c>
+      <c r="K36" s="9" t="n">
+        <v>17.59</v>
+      </c>
       <c r="L36" s="9" t="n"/>
     </row>
     <row r="37">
@@ -9432,7 +9572,7 @@
         </is>
       </c>
       <c r="E37" s="7" t="n">
-        <v>35387</v>
+        <v>35366</v>
       </c>
       <c r="F37" s="9" t="n">
         <v>24.79</v>
@@ -9446,8 +9586,12 @@
       <c r="I37" s="9" t="n">
         <v>45.89</v>
       </c>
-      <c r="J37" s="9" t="n"/>
-      <c r="K37" s="9" t="n"/>
+      <c r="J37" s="9" t="n">
+        <v>43.52</v>
+      </c>
+      <c r="K37" s="9" t="n">
+        <v>34.15</v>
+      </c>
       <c r="L37" s="9" t="n"/>
     </row>
     <row r="38">
@@ -9596,7 +9740,7 @@
         </is>
       </c>
       <c r="E41" s="7" t="n">
-        <v>335912</v>
+        <v>340013</v>
       </c>
       <c r="F41" s="9" t="n">
         <v>18.45</v>
@@ -9610,8 +9754,12 @@
       <c r="I41" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="J41" s="9" t="n"/>
-      <c r="K41" s="9" t="n"/>
+      <c r="J41" s="9" t="n">
+        <v>26.74</v>
+      </c>
+      <c r="K41" s="9" t="n">
+        <v>22.43</v>
+      </c>
       <c r="L41" s="9" t="n"/>
     </row>
     <row r="42">
@@ -9636,7 +9784,7 @@
         </is>
       </c>
       <c r="E42" s="7" t="n">
-        <v>173062</v>
+        <v>173528</v>
       </c>
       <c r="F42" s="9" t="n">
         <v>16.58</v>
@@ -9650,8 +9798,12 @@
       <c r="I42" s="9" t="n">
         <v>24.83</v>
       </c>
-      <c r="J42" s="9" t="n"/>
-      <c r="K42" s="9" t="n"/>
+      <c r="J42" s="9" t="n">
+        <v>35.44</v>
+      </c>
+      <c r="K42" s="9" t="n">
+        <v>27.92</v>
+      </c>
       <c r="L42" s="9" t="n"/>
     </row>
     <row r="43">
@@ -9676,7 +9828,7 @@
         </is>
       </c>
       <c r="E43" s="7" t="n">
-        <v>18655</v>
+        <v>14408</v>
       </c>
       <c r="F43" s="9" t="n">
         <v>10.64</v>
@@ -9690,8 +9842,12 @@
       <c r="I43" s="9" t="n">
         <v>22.45</v>
       </c>
-      <c r="J43" s="9" t="n"/>
-      <c r="K43" s="9" t="n"/>
+      <c r="J43" s="9" t="n">
+        <v>25.76</v>
+      </c>
+      <c r="K43" s="9" t="n">
+        <v>16.79</v>
+      </c>
       <c r="L43" s="9" t="n"/>
     </row>
     <row r="44">
@@ -9716,7 +9872,7 @@
         </is>
       </c>
       <c r="E44" s="7" t="n">
-        <v>41066</v>
+        <v>41026</v>
       </c>
       <c r="F44" s="9" t="n"/>
       <c r="G44" s="9" t="n">
@@ -9760,7 +9916,7 @@
         </is>
       </c>
       <c r="E45" s="7" t="n">
-        <v>7289</v>
+        <v>7282</v>
       </c>
       <c r="F45" s="9" t="n"/>
       <c r="G45" s="9" t="n">
@@ -9804,7 +9960,7 @@
         </is>
       </c>
       <c r="E46" s="7" t="n">
-        <v>66856</v>
+        <v>66780</v>
       </c>
       <c r="F46" s="9" t="n">
         <v>11.71</v>
@@ -9818,8 +9974,12 @@
       <c r="I46" s="9" t="n">
         <v>17.46</v>
       </c>
-      <c r="J46" s="9" t="n"/>
-      <c r="K46" s="9" t="n"/>
+      <c r="J46" s="9" t="n">
+        <v>15.08</v>
+      </c>
+      <c r="K46" s="9" t="n">
+        <v>12.62</v>
+      </c>
       <c r="L46" s="9" t="n"/>
     </row>
     <row r="47">
@@ -9844,7 +10004,7 @@
         </is>
       </c>
       <c r="E47" s="7" t="n">
-        <v>24362</v>
+        <v>24311</v>
       </c>
       <c r="F47" s="9" t="n">
         <v>31.28</v>
@@ -9888,7 +10048,7 @@
         </is>
       </c>
       <c r="E48" s="7" t="n">
-        <v>12163</v>
+        <v>12138</v>
       </c>
       <c r="F48" s="9" t="n">
         <v>13.89</v>
@@ -10056,7 +10216,7 @@
         </is>
       </c>
       <c r="E52" s="7" t="n">
-        <v>64087</v>
+        <v>64966</v>
       </c>
       <c r="F52" s="9" t="n">
         <v>11.71</v>
@@ -10070,8 +10230,12 @@
       <c r="I52" s="9" t="n">
         <v>20.48</v>
       </c>
-      <c r="J52" s="9" t="n"/>
-      <c r="K52" s="9" t="n"/>
+      <c r="J52" s="9" t="n">
+        <v>20.72</v>
+      </c>
+      <c r="K52" s="9" t="n">
+        <v>17.8</v>
+      </c>
       <c r="L52" s="9" t="n"/>
     </row>
   </sheetData>
@@ -10412,7 +10576,7 @@
         </is>
       </c>
       <c r="E8" s="7" t="n">
-        <v>40317</v>
+        <v>40232</v>
       </c>
       <c r="F8" s="9" t="n">
         <v>13.27</v>
@@ -10452,7 +10616,7 @@
         </is>
       </c>
       <c r="E9" s="7" t="n">
-        <v>16024</v>
+        <v>16000</v>
       </c>
       <c r="F9" s="9" t="n">
         <v>5.59</v>
@@ -10532,7 +10696,7 @@
         </is>
       </c>
       <c r="E11" s="7" t="n">
-        <v>80737</v>
+        <v>80657</v>
       </c>
       <c r="F11" s="9" t="n"/>
       <c r="G11" s="9" t="n">
@@ -10572,7 +10736,7 @@
         </is>
       </c>
       <c r="E12" s="7" t="n">
-        <v>12076</v>
+        <v>12064</v>
       </c>
       <c r="F12" s="9" t="n"/>
       <c r="G12" s="9" t="n">
@@ -10612,7 +10776,7 @@
         </is>
       </c>
       <c r="E13" s="7" t="n">
-        <v>16954</v>
+        <v>16937</v>
       </c>
       <c r="F13" s="9" t="n"/>
       <c r="G13" s="9" t="n">
@@ -10652,7 +10816,7 @@
         </is>
       </c>
       <c r="E14" s="7" t="n">
-        <v>2430</v>
+        <v>2428</v>
       </c>
       <c r="F14" s="9" t="n"/>
       <c r="G14" s="9" t="n">
@@ -10732,7 +10896,7 @@
         </is>
       </c>
       <c r="E16" s="7" t="n">
-        <v>5331</v>
+        <v>4553</v>
       </c>
       <c r="F16" s="9" t="n">
         <v>991.9299999999999</v>
@@ -10772,7 +10936,7 @@
         </is>
       </c>
       <c r="E17" s="7" t="n">
-        <v>10718</v>
+        <v>10674</v>
       </c>
       <c r="F17" s="9" t="n">
         <v>10.08</v>
@@ -10812,7 +10976,7 @@
         </is>
       </c>
       <c r="E18" s="7" t="n">
-        <v>1161</v>
+        <v>1156</v>
       </c>
       <c r="F18" s="9" t="n"/>
       <c r="G18" s="9" t="n">
@@ -11244,7 +11408,7 @@
         </is>
       </c>
       <c r="E29" s="7" t="n">
-        <v>127417</v>
+        <v>126429</v>
       </c>
       <c r="F29" s="9" t="n">
         <v>15.68</v>
@@ -11284,7 +11448,7 @@
         </is>
       </c>
       <c r="E30" s="7" t="n">
-        <v>73853</v>
+        <v>73819</v>
       </c>
       <c r="F30" s="9" t="n">
         <v>12.31</v>
@@ -11324,7 +11488,7 @@
         </is>
       </c>
       <c r="E31" s="7" t="n">
-        <v>93134</v>
+        <v>93076</v>
       </c>
       <c r="F31" s="9" t="n">
         <v>14.87</v>
@@ -11364,7 +11528,7 @@
         </is>
       </c>
       <c r="E32" s="7" t="n">
-        <v>261357</v>
+        <v>260296</v>
       </c>
       <c r="F32" s="9" t="n">
         <v>15.21</v>
@@ -11404,7 +11568,7 @@
         </is>
       </c>
       <c r="E33" s="7" t="n">
-        <v>10718</v>
+        <v>10674</v>
       </c>
       <c r="F33" s="9" t="n">
         <v>10.08</v>
@@ -11444,7 +11608,7 @@
         </is>
       </c>
       <c r="E34" s="7" t="n">
-        <v>57204</v>
+        <v>56088</v>
       </c>
       <c r="F34" s="9" t="n">
         <v>8.5</v>
@@ -11484,7 +11648,7 @@
         </is>
       </c>
       <c r="E35" s="7" t="n">
-        <v>770</v>
+        <v>77068</v>
       </c>
       <c r="F35" s="9" t="n">
         <v>9.84</v>
@@ -11524,7 +11688,7 @@
         </is>
       </c>
       <c r="E36" s="7" t="n">
-        <v>32699</v>
+        <v>32619</v>
       </c>
       <c r="F36" s="9" t="n">
         <v>4.69</v>
@@ -11564,7 +11728,7 @@
         </is>
       </c>
       <c r="E37" s="7" t="n">
-        <v>35387</v>
+        <v>35366</v>
       </c>
       <c r="F37" s="9" t="n">
         <v>11.71</v>
@@ -11724,7 +11888,7 @@
         </is>
       </c>
       <c r="E41" s="7" t="n">
-        <v>335912</v>
+        <v>340013</v>
       </c>
       <c r="F41" s="9" t="n">
         <v>13.46</v>
@@ -11764,7 +11928,7 @@
         </is>
       </c>
       <c r="E42" s="7" t="n">
-        <v>173062</v>
+        <v>173528</v>
       </c>
       <c r="F42" s="9" t="n">
         <v>13.71</v>
@@ -11804,7 +11968,7 @@
         </is>
       </c>
       <c r="E43" s="7" t="n">
-        <v>18655</v>
+        <v>14408</v>
       </c>
       <c r="F43" s="9" t="n">
         <v>10.23</v>
@@ -11844,7 +12008,7 @@
         </is>
       </c>
       <c r="E44" s="7" t="n">
-        <v>41066</v>
+        <v>41026</v>
       </c>
       <c r="F44" s="9" t="n"/>
       <c r="G44" s="9" t="n">
@@ -11884,7 +12048,7 @@
         </is>
       </c>
       <c r="E45" s="7" t="n">
-        <v>7289</v>
+        <v>7282</v>
       </c>
       <c r="F45" s="9" t="n"/>
       <c r="G45" s="9" t="n">
@@ -11924,7 +12088,7 @@
         </is>
       </c>
       <c r="E46" s="7" t="n">
-        <v>66856</v>
+        <v>66780</v>
       </c>
       <c r="F46" s="9" t="n">
         <v>7.78</v>
@@ -11964,7 +12128,7 @@
         </is>
       </c>
       <c r="E47" s="7" t="n">
-        <v>24362</v>
+        <v>24311</v>
       </c>
       <c r="F47" s="9" t="n">
         <v>18.39</v>
@@ -12004,7 +12168,7 @@
         </is>
       </c>
       <c r="E48" s="7" t="n">
-        <v>12163</v>
+        <v>12138</v>
       </c>
       <c r="F48" s="9" t="n">
         <v>7.78</v>
@@ -12164,7 +12328,7 @@
         </is>
       </c>
       <c r="E52" s="7" t="n">
-        <v>64087</v>
+        <v>64966</v>
       </c>
       <c r="F52" s="9" t="n">
         <v>6.73</v>
@@ -12309,10 +12473,10 @@
         <v>5.72</v>
       </c>
       <c r="J2" s="9" t="n">
-        <v>3.06</v>
+        <v>3.07</v>
       </c>
       <c r="K2" s="9" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="L2" s="9" t="n"/>
     </row>
@@ -12353,10 +12517,10 @@
         <v>5.64</v>
       </c>
       <c r="J3" s="9" t="n">
-        <v>2.47</v>
+        <v>2.48</v>
       </c>
       <c r="K3" s="9" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="L3" s="9" t="n"/>
     </row>
@@ -12548,7 +12712,7 @@
         </is>
       </c>
       <c r="E8" s="7" t="n">
-        <v>40317</v>
+        <v>40232</v>
       </c>
       <c r="F8" s="9" t="n">
         <v>2.17</v>
@@ -12592,7 +12756,7 @@
         </is>
       </c>
       <c r="E9" s="7" t="n">
-        <v>16024</v>
+        <v>16000</v>
       </c>
       <c r="F9" s="9" t="n">
         <v>1.58</v>
@@ -12607,10 +12771,10 @@
         <v>2.32</v>
       </c>
       <c r="J9" s="9" t="n">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="K9" s="9" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="L9" s="9" t="n"/>
     </row>
@@ -12654,7 +12818,7 @@
         <v>0.88</v>
       </c>
       <c r="K10" s="9" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="L10" s="9" t="n"/>
     </row>
@@ -12680,7 +12844,7 @@
         </is>
       </c>
       <c r="E11" s="7" t="n">
-        <v>80737</v>
+        <v>80657</v>
       </c>
       <c r="F11" s="9" t="n"/>
       <c r="G11" s="9" t="n">
@@ -12724,7 +12888,7 @@
         </is>
       </c>
       <c r="E12" s="7" t="n">
-        <v>12076</v>
+        <v>12064</v>
       </c>
       <c r="F12" s="9" t="n"/>
       <c r="G12" s="9" t="n">
@@ -12768,7 +12932,7 @@
         </is>
       </c>
       <c r="E13" s="7" t="n">
-        <v>16954</v>
+        <v>16937</v>
       </c>
       <c r="F13" s="9" t="n"/>
       <c r="G13" s="9" t="n">
@@ -12812,7 +12976,7 @@
         </is>
       </c>
       <c r="E14" s="7" t="n">
-        <v>2430</v>
+        <v>2428</v>
       </c>
       <c r="F14" s="9" t="n"/>
       <c r="G14" s="9" t="n">
@@ -12896,7 +13060,7 @@
         </is>
       </c>
       <c r="E16" s="7" t="n">
-        <v>5331</v>
+        <v>4553</v>
       </c>
       <c r="F16" s="9" t="n">
         <v>1.54</v>
@@ -12911,10 +13075,10 @@
         <v>5.43</v>
       </c>
       <c r="J16" s="9" t="n">
-        <v>4.04</v>
+        <v>3.46</v>
       </c>
       <c r="K16" s="9" t="n">
-        <v>3.29</v>
+        <v>2.82</v>
       </c>
       <c r="L16" s="9" t="n"/>
     </row>
@@ -12940,7 +13104,7 @@
         </is>
       </c>
       <c r="E17" s="7" t="n">
-        <v>10718</v>
+        <v>10674</v>
       </c>
       <c r="F17" s="9" t="n">
         <v>2.64</v>
@@ -12955,7 +13119,7 @@
         <v>2.63</v>
       </c>
       <c r="J17" s="9" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="K17" s="9" t="n">
         <v>1.75</v>
@@ -12984,7 +13148,7 @@
         </is>
       </c>
       <c r="E18" s="7" t="n">
-        <v>1161</v>
+        <v>1156</v>
       </c>
       <c r="F18" s="9" t="n"/>
       <c r="G18" s="9" t="n">
@@ -13039,10 +13203,10 @@
         <v>10.52</v>
       </c>
       <c r="J19" s="9" t="n">
-        <v>9.359999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>7.65</v>
+        <v>7.68</v>
       </c>
       <c r="L19" s="9" t="n"/>
     </row>
@@ -13306,7 +13470,7 @@
         <v>3.92</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>3.23</v>
+        <v>3.24</v>
       </c>
       <c r="L25" s="9" t="n"/>
     </row>
@@ -13438,7 +13602,7 @@
         <v>2.73</v>
       </c>
       <c r="K28" s="9" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="L28" s="9" t="n"/>
     </row>
@@ -13464,7 +13628,7 @@
         </is>
       </c>
       <c r="E29" s="7" t="n">
-        <v>127417</v>
+        <v>126429</v>
       </c>
       <c r="F29" s="9" t="n">
         <v>13.34</v>
@@ -13479,10 +13643,10 @@
         <v>16.48</v>
       </c>
       <c r="J29" s="9" t="n">
-        <v>12.51</v>
+        <v>12.42</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>9.16</v>
+        <v>9.09</v>
       </c>
       <c r="L29" s="9" t="n"/>
     </row>
@@ -13508,7 +13672,7 @@
         </is>
       </c>
       <c r="E30" s="7" t="n">
-        <v>73853</v>
+        <v>73819</v>
       </c>
       <c r="F30" s="9" t="n">
         <v>5.46</v>
@@ -13523,7 +13687,7 @@
         <v>4.86</v>
       </c>
       <c r="J30" s="9" t="n">
-        <v>3.78</v>
+        <v>3.77</v>
       </c>
       <c r="K30" s="9" t="n">
         <v>3.27</v>
@@ -13552,7 +13716,7 @@
         </is>
       </c>
       <c r="E31" s="7" t="n">
-        <v>93134</v>
+        <v>93076</v>
       </c>
       <c r="F31" s="9" t="n">
         <v>3.67</v>
@@ -13570,7 +13734,7 @@
         <v>3.27</v>
       </c>
       <c r="K31" s="9" t="n">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="L31" s="9" t="n"/>
     </row>
@@ -13596,7 +13760,7 @@
         </is>
       </c>
       <c r="E32" s="7" t="n">
-        <v>261357</v>
+        <v>260296</v>
       </c>
       <c r="F32" s="9" t="n">
         <v>2.04</v>
@@ -13611,10 +13775,10 @@
         <v>3.77</v>
       </c>
       <c r="J32" s="9" t="n">
-        <v>3.72</v>
+        <v>3.71</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>3.46</v>
+        <v>3.44</v>
       </c>
       <c r="L32" s="9" t="n"/>
     </row>
@@ -13640,7 +13804,7 @@
         </is>
       </c>
       <c r="E33" s="7" t="n">
-        <v>10718</v>
+        <v>10674</v>
       </c>
       <c r="F33" s="9" t="n">
         <v>2.64</v>
@@ -13655,7 +13819,7 @@
         <v>2.63</v>
       </c>
       <c r="J33" s="9" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="K33" s="9" t="n">
         <v>1.75</v>
@@ -13684,7 +13848,7 @@
         </is>
       </c>
       <c r="E34" s="7" t="n">
-        <v>57204</v>
+        <v>56088</v>
       </c>
       <c r="F34" s="9" t="n">
         <v>2.86</v>
@@ -13699,10 +13863,10 @@
         <v>14.29</v>
       </c>
       <c r="J34" s="9" t="n">
-        <v>8.539999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>6.97</v>
+        <v>6.85</v>
       </c>
       <c r="L34" s="9" t="n"/>
     </row>
@@ -13728,7 +13892,7 @@
         </is>
       </c>
       <c r="E35" s="7" t="n">
-        <v>770</v>
+        <v>77068</v>
       </c>
       <c r="F35" s="9" t="n">
         <v>2.35</v>
@@ -13743,10 +13907,10 @@
         <v>4.26</v>
       </c>
       <c r="J35" s="9" t="n">
-        <v>0.04</v>
+        <v>4.48</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>0.04</v>
+        <v>4.06</v>
       </c>
       <c r="L35" s="9" t="n"/>
     </row>
@@ -13772,7 +13936,7 @@
         </is>
       </c>
       <c r="E36" s="7" t="n">
-        <v>32699</v>
+        <v>32619</v>
       </c>
       <c r="F36" s="9" t="n">
         <v>0.65</v>
@@ -13816,7 +13980,7 @@
         </is>
       </c>
       <c r="E37" s="7" t="n">
-        <v>35387</v>
+        <v>35366</v>
       </c>
       <c r="F37" s="9" t="n">
         <v>1.85</v>
@@ -13988,7 +14152,7 @@
         </is>
       </c>
       <c r="E41" s="7" t="n">
-        <v>335912</v>
+        <v>340013</v>
       </c>
       <c r="F41" s="9" t="n">
         <v>7.79</v>
@@ -14003,10 +14167,10 @@
         <v>12.5</v>
       </c>
       <c r="J41" s="9" t="n">
-        <v>10.93</v>
+        <v>11.07</v>
       </c>
       <c r="K41" s="9" t="n">
-        <v>8.01</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="L41" s="9" t="n"/>
     </row>
@@ -14032,7 +14196,7 @@
         </is>
       </c>
       <c r="E42" s="7" t="n">
-        <v>173062</v>
+        <v>173528</v>
       </c>
       <c r="F42" s="9" t="n">
         <v>5.84</v>
@@ -14047,10 +14211,10 @@
         <v>4.81</v>
       </c>
       <c r="J42" s="9" t="n">
-        <v>5.95</v>
+        <v>5.97</v>
       </c>
       <c r="K42" s="9" t="n">
-        <v>5.23</v>
+        <v>5.25</v>
       </c>
       <c r="L42" s="9" t="n"/>
     </row>
@@ -14076,7 +14240,7 @@
         </is>
       </c>
       <c r="E43" s="7" t="n">
-        <v>18655</v>
+        <v>14408</v>
       </c>
       <c r="F43" s="9" t="n">
         <v>3.12</v>
@@ -14091,10 +14255,10 @@
         <v>1.48</v>
       </c>
       <c r="J43" s="9" t="n">
-        <v>2.31</v>
+        <v>1.79</v>
       </c>
       <c r="K43" s="9" t="n">
-        <v>2.17</v>
+        <v>1.68</v>
       </c>
       <c r="L43" s="9" t="n"/>
     </row>
@@ -14120,7 +14284,7 @@
         </is>
       </c>
       <c r="E44" s="7" t="n">
-        <v>41066</v>
+        <v>41026</v>
       </c>
       <c r="F44" s="9" t="n"/>
       <c r="G44" s="9" t="n">
@@ -14164,7 +14328,7 @@
         </is>
       </c>
       <c r="E45" s="7" t="n">
-        <v>7289</v>
+        <v>7282</v>
       </c>
       <c r="F45" s="9" t="n"/>
       <c r="G45" s="9" t="n">
@@ -14208,7 +14372,7 @@
         </is>
       </c>
       <c r="E46" s="7" t="n">
-        <v>66856</v>
+        <v>66780</v>
       </c>
       <c r="F46" s="9" t="n">
         <v>2.36</v>
@@ -14252,7 +14416,7 @@
         </is>
       </c>
       <c r="E47" s="7" t="n">
-        <v>24362</v>
+        <v>24311</v>
       </c>
       <c r="F47" s="9" t="n">
         <v>2.06</v>
@@ -14296,7 +14460,7 @@
         </is>
       </c>
       <c r="E48" s="7" t="n">
-        <v>12163</v>
+        <v>12138</v>
       </c>
       <c r="F48" s="9" t="n">
         <v>1.12</v>
@@ -14464,7 +14628,7 @@
         </is>
       </c>
       <c r="E52" s="7" t="n">
-        <v>64087</v>
+        <v>64966</v>
       </c>
       <c r="F52" s="9" t="n">
         <v>3.49</v>
@@ -14479,10 +14643,10 @@
         <v>5.69</v>
       </c>
       <c r="J52" s="9" t="n">
-        <v>5.56</v>
+        <v>5.63</v>
       </c>
       <c r="K52" s="9" t="n">
-        <v>4.41</v>
+        <v>4.47</v>
       </c>
       <c r="L52" s="9" t="n"/>
     </row>
@@ -14613,10 +14777,10 @@
         <v>18.82</v>
       </c>
       <c r="J2" s="11" t="n">
-        <v>30.13</v>
+        <v>29.54</v>
       </c>
       <c r="K2" s="11" t="n">
-        <v>27.48</v>
+        <v>27.1</v>
       </c>
       <c r="L2" s="11" t="n"/>
     </row>
@@ -14657,10 +14821,10 @@
         <v>22.59</v>
       </c>
       <c r="J3" s="11" t="n">
-        <v>26.63</v>
+        <v>26.32</v>
       </c>
       <c r="K3" s="11" t="n">
-        <v>21.3</v>
+        <v>21.08</v>
       </c>
       <c r="L3" s="11" t="n"/>
     </row>
@@ -14701,10 +14865,10 @@
         <v>13.74</v>
       </c>
       <c r="J4" s="11" t="n">
-        <v>21.61</v>
+        <v>21.59</v>
       </c>
       <c r="K4" s="11" t="n">
-        <v>24.56</v>
+        <v>24.58</v>
       </c>
       <c r="L4" s="11" t="n"/>
     </row>
@@ -14745,10 +14909,10 @@
         <v>17.78</v>
       </c>
       <c r="J5" s="11" t="n">
-        <v>24.96</v>
+        <v>24.84</v>
       </c>
       <c r="K5" s="11" t="n">
-        <v>24.01</v>
+        <v>23.73</v>
       </c>
       <c r="L5" s="11" t="n"/>
     </row>
@@ -14858,7 +15022,7 @@
         </is>
       </c>
       <c r="E8" s="7" t="n">
-        <v>40317</v>
+        <v>40232</v>
       </c>
       <c r="F8" s="11" t="n">
         <v>0.38</v>
@@ -14902,7 +15066,7 @@
         </is>
       </c>
       <c r="E9" s="7" t="n">
-        <v>16024</v>
+        <v>16000</v>
       </c>
       <c r="F9" s="11" t="n">
         <v>15.98</v>
@@ -14990,7 +15154,7 @@
         </is>
       </c>
       <c r="E11" s="7" t="n">
-        <v>80737</v>
+        <v>80657</v>
       </c>
       <c r="F11" s="11" t="n"/>
       <c r="G11" s="11" t="n">
@@ -15034,7 +15198,7 @@
         </is>
       </c>
       <c r="E12" s="7" t="n">
-        <v>12076</v>
+        <v>12064</v>
       </c>
       <c r="F12" s="11" t="n"/>
       <c r="G12" s="11" t="n">
@@ -15078,7 +15242,7 @@
         </is>
       </c>
       <c r="E13" s="7" t="n">
-        <v>16954</v>
+        <v>16937</v>
       </c>
       <c r="F13" s="11" t="n"/>
       <c r="G13" s="11" t="n">
@@ -15122,7 +15286,7 @@
         </is>
       </c>
       <c r="E14" s="7" t="n">
-        <v>2430</v>
+        <v>2428</v>
       </c>
       <c r="F14" s="11" t="n"/>
       <c r="G14" s="11" t="n">
@@ -15206,7 +15370,7 @@
         </is>
       </c>
       <c r="E16" s="7" t="n">
-        <v>5331</v>
+        <v>4553</v>
       </c>
       <c r="F16" s="11" t="n">
         <v>-52.75</v>
@@ -15250,7 +15414,7 @@
         </is>
       </c>
       <c r="E17" s="7" t="n">
-        <v>10718</v>
+        <v>10674</v>
       </c>
       <c r="F17" s="11" t="n">
         <v>16.6</v>
@@ -15294,7 +15458,7 @@
         </is>
       </c>
       <c r="E18" s="7" t="n">
-        <v>1161</v>
+        <v>1156</v>
       </c>
       <c r="F18" s="11" t="n"/>
       <c r="G18" s="11" t="n">
@@ -15353,10 +15517,10 @@
         <v>33.73</v>
       </c>
       <c r="J19" s="11" t="n">
-        <v>38.2</v>
+        <v>37.42</v>
       </c>
       <c r="K19" s="11" t="n">
-        <v>37.37</v>
+        <v>37.39</v>
       </c>
       <c r="L19" s="11" t="n"/>
     </row>
@@ -15617,10 +15781,10 @@
         <v>19.14</v>
       </c>
       <c r="J25" s="11" t="n">
-        <v>22.45</v>
+        <v>22.16</v>
       </c>
       <c r="K25" s="11" t="n">
-        <v>23.3</v>
+        <v>23.09</v>
       </c>
       <c r="L25" s="11" t="n"/>
     </row>
@@ -15749,10 +15913,10 @@
         <v>30.05</v>
       </c>
       <c r="J28" s="11" t="n">
-        <v>24.93</v>
+        <v>24.88</v>
       </c>
       <c r="K28" s="11" t="n">
-        <v>25.6</v>
+        <v>25.43</v>
       </c>
       <c r="L28" s="11" t="n"/>
     </row>
@@ -15778,7 +15942,7 @@
         </is>
       </c>
       <c r="E29" s="7" t="n">
-        <v>127417</v>
+        <v>126429</v>
       </c>
       <c r="F29" s="11" t="n">
         <v>61.86</v>
@@ -15822,7 +15986,7 @@
         </is>
       </c>
       <c r="E30" s="7" t="n">
-        <v>73853</v>
+        <v>73819</v>
       </c>
       <c r="F30" s="11" t="n">
         <v>31.97</v>
@@ -15866,7 +16030,7 @@
         </is>
       </c>
       <c r="E31" s="7" t="n">
-        <v>93134</v>
+        <v>93076</v>
       </c>
       <c r="F31" s="11" t="n">
         <v>18.26</v>
@@ -15910,7 +16074,7 @@
         </is>
       </c>
       <c r="E32" s="7" t="n">
-        <v>261357</v>
+        <v>260296</v>
       </c>
       <c r="F32" s="11" t="n">
         <v>7.16</v>
@@ -15954,7 +16118,7 @@
         </is>
       </c>
       <c r="E33" s="7" t="n">
-        <v>10718</v>
+        <v>10674</v>
       </c>
       <c r="F33" s="11" t="n">
         <v>16.6</v>
@@ -15998,7 +16162,7 @@
         </is>
       </c>
       <c r="E34" s="7" t="n">
-        <v>57204</v>
+        <v>56088</v>
       </c>
       <c r="F34" s="11" t="n">
         <v>16.81</v>
@@ -16042,7 +16206,7 @@
         </is>
       </c>
       <c r="E35" s="7" t="n">
-        <v>770</v>
+        <v>77068</v>
       </c>
       <c r="F35" s="11" t="n">
         <v>14.19</v>
@@ -16086,7 +16250,7 @@
         </is>
       </c>
       <c r="E36" s="7" t="n">
-        <v>32699</v>
+        <v>32619</v>
       </c>
       <c r="F36" s="11" t="n">
         <v>12.91</v>
@@ -16130,7 +16294,7 @@
         </is>
       </c>
       <c r="E37" s="7" t="n">
-        <v>35387</v>
+        <v>35366</v>
       </c>
       <c r="F37" s="11" t="n">
         <v>7.44</v>
@@ -16302,7 +16466,7 @@
         </is>
       </c>
       <c r="E41" s="7" t="n">
-        <v>335912</v>
+        <v>340013</v>
       </c>
       <c r="F41" s="11" t="n">
         <v>42.25</v>
@@ -16346,7 +16510,7 @@
         </is>
       </c>
       <c r="E42" s="7" t="n">
-        <v>173062</v>
+        <v>173528</v>
       </c>
       <c r="F42" s="11" t="n">
         <v>35.19</v>
@@ -16390,7 +16554,7 @@
         </is>
       </c>
       <c r="E43" s="7" t="n">
-        <v>18655</v>
+        <v>14408</v>
       </c>
       <c r="F43" s="11" t="n">
         <v>29.29</v>
@@ -16434,7 +16598,7 @@
         </is>
       </c>
       <c r="E44" s="7" t="n">
-        <v>41066</v>
+        <v>41026</v>
       </c>
       <c r="F44" s="11" t="n"/>
       <c r="G44" s="11" t="n">
@@ -16478,7 +16642,7 @@
         </is>
       </c>
       <c r="E45" s="7" t="n">
-        <v>7289</v>
+        <v>7282</v>
       </c>
       <c r="F45" s="11" t="n"/>
       <c r="G45" s="11" t="n">
@@ -16522,7 +16686,7 @@
         </is>
       </c>
       <c r="E46" s="7" t="n">
-        <v>66856</v>
+        <v>66780</v>
       </c>
       <c r="F46" s="11" t="n">
         <v>20.11</v>
@@ -16566,7 +16730,7 @@
         </is>
       </c>
       <c r="E47" s="7" t="n">
-        <v>24362</v>
+        <v>24311</v>
       </c>
       <c r="F47" s="11" t="n">
         <v>6.6</v>
@@ -16610,7 +16774,7 @@
         </is>
       </c>
       <c r="E48" s="7" t="n">
-        <v>12163</v>
+        <v>12138</v>
       </c>
       <c r="F48" s="11" t="n">
         <v>8.1</v>
@@ -16778,7 +16942,7 @@
         </is>
       </c>
       <c r="E52" s="7" t="n">
-        <v>64087</v>
+        <v>64966</v>
       </c>
       <c r="F52" s="11" t="n">
         <v>29.81</v>
@@ -16927,7 +17091,7 @@
         <v>3.04</v>
       </c>
       <c r="J2" s="9" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="K2" s="9" t="n">
         <v>1.38</v>
@@ -17015,10 +17179,10 @@
         <v>1.93</v>
       </c>
       <c r="J4" s="9" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="K4" s="9" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="L4" s="9" t="n"/>
     </row>
@@ -17062,7 +17226,7 @@
         <v>0.54</v>
       </c>
       <c r="K5" s="9" t="n">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="L5" s="9" t="n"/>
     </row>
@@ -17166,7 +17330,7 @@
         </is>
       </c>
       <c r="E8" s="7" t="n">
-        <v>40317</v>
+        <v>40232</v>
       </c>
       <c r="F8" s="9" t="n">
         <v>1.68</v>
@@ -17206,7 +17370,7 @@
         </is>
       </c>
       <c r="E9" s="7" t="n">
-        <v>16024</v>
+        <v>16000</v>
       </c>
       <c r="F9" s="9" t="n">
         <v>1.34</v>
@@ -17221,7 +17385,7 @@
         <v>2.62</v>
       </c>
       <c r="J9" s="9" t="n">
-        <v>2.96</v>
+        <v>2.97</v>
       </c>
       <c r="K9" s="9" t="n">
         <v>2.59</v>
@@ -17294,7 +17458,7 @@
         </is>
       </c>
       <c r="E11" s="7" t="n">
-        <v>80737</v>
+        <v>80657</v>
       </c>
       <c r="F11" s="9" t="n"/>
       <c r="G11" s="9" t="n">
@@ -17338,7 +17502,7 @@
         </is>
       </c>
       <c r="E12" s="7" t="n">
-        <v>12076</v>
+        <v>12064</v>
       </c>
       <c r="F12" s="9" t="n"/>
       <c r="G12" s="9" t="n">
@@ -17382,7 +17546,7 @@
         </is>
       </c>
       <c r="E13" s="7" t="n">
-        <v>16954</v>
+        <v>16937</v>
       </c>
       <c r="F13" s="9" t="n"/>
       <c r="G13" s="9" t="n">
@@ -17426,7 +17590,7 @@
         </is>
       </c>
       <c r="E14" s="7" t="n">
-        <v>2430</v>
+        <v>2428</v>
       </c>
       <c r="F14" s="9" t="n"/>
       <c r="G14" s="9" t="n">
@@ -17510,7 +17674,7 @@
         </is>
       </c>
       <c r="E16" s="7" t="n">
-        <v>5331</v>
+        <v>4553</v>
       </c>
       <c r="F16" s="9" t="n">
         <v>0.12</v>
@@ -17525,10 +17689,10 @@
         <v>0.61</v>
       </c>
       <c r="J16" s="9" t="n">
-        <v>0.51</v>
+        <v>0.43</v>
       </c>
       <c r="K16" s="9" t="n">
-        <v>0.45</v>
+        <v>0.39</v>
       </c>
       <c r="L16" s="9" t="n"/>
     </row>
@@ -17554,7 +17718,7 @@
         </is>
       </c>
       <c r="E17" s="7" t="n">
-        <v>10718</v>
+        <v>10674</v>
       </c>
       <c r="F17" s="9" t="n">
         <v>0.86</v>
@@ -17598,7 +17762,7 @@
         </is>
       </c>
       <c r="E18" s="7" t="n">
-        <v>1161</v>
+        <v>1156</v>
       </c>
       <c r="F18" s="9" t="n"/>
       <c r="G18" s="9" t="n">
@@ -17653,10 +17817,10 @@
         <v>4.38</v>
       </c>
       <c r="J19" s="9" t="n">
-        <v>4.03</v>
+        <v>3.99</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>3.54</v>
+        <v>3.53</v>
       </c>
       <c r="L19" s="9" t="n"/>
     </row>
@@ -18049,7 +18213,7 @@
         <v>3.51</v>
       </c>
       <c r="J28" s="9" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="K28" s="9" t="n">
         <v>1.35</v>
@@ -18078,7 +18242,7 @@
         </is>
       </c>
       <c r="E29" s="7" t="n">
-        <v>127417</v>
+        <v>126429</v>
       </c>
       <c r="F29" s="9" t="n">
         <v>1.87</v>
@@ -18093,10 +18257,10 @@
         <v>1.48</v>
       </c>
       <c r="J29" s="9" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="L29" s="9" t="n"/>
     </row>
@@ -18122,7 +18286,7 @@
         </is>
       </c>
       <c r="E30" s="7" t="n">
-        <v>73853</v>
+        <v>73819</v>
       </c>
       <c r="F30" s="9" t="n">
         <v>2.28</v>
@@ -18166,7 +18330,7 @@
         </is>
       </c>
       <c r="E31" s="7" t="n">
-        <v>93134</v>
+        <v>93076</v>
       </c>
       <c r="F31" s="9" t="n">
         <v>1.73</v>
@@ -18181,7 +18345,7 @@
         <v>1.73</v>
       </c>
       <c r="J31" s="9" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="K31" s="9" t="n">
         <v>1.59</v>
@@ -18210,7 +18374,7 @@
         </is>
       </c>
       <c r="E32" s="7" t="n">
-        <v>261357</v>
+        <v>260296</v>
       </c>
       <c r="F32" s="9" t="n">
         <v>2.21</v>
@@ -18225,10 +18389,10 @@
         <v>2.78</v>
       </c>
       <c r="J32" s="9" t="n">
-        <v>2.72</v>
+        <v>2.71</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="L32" s="9" t="n"/>
     </row>
@@ -18254,7 +18418,7 @@
         </is>
       </c>
       <c r="E33" s="7" t="n">
-        <v>10718</v>
+        <v>10674</v>
       </c>
       <c r="F33" s="9" t="n">
         <v>0.86</v>
@@ -18298,7 +18462,7 @@
         </is>
       </c>
       <c r="E34" s="7" t="n">
-        <v>57204</v>
+        <v>56088</v>
       </c>
       <c r="F34" s="9" t="n">
         <v>1.26</v>
@@ -18313,10 +18477,10 @@
         <v>7.21</v>
       </c>
       <c r="J34" s="9" t="n">
-        <v>3.65</v>
+        <v>3.59</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="L34" s="9" t="n"/>
     </row>
@@ -18342,7 +18506,7 @@
         </is>
       </c>
       <c r="E35" s="7" t="n">
-        <v>770</v>
+        <v>77068</v>
       </c>
       <c r="F35" s="9" t="n">
         <v>1.24</v>
@@ -18357,10 +18521,10 @@
         <v>1.77</v>
       </c>
       <c r="J35" s="9" t="n">
-        <v>0.02</v>
+        <v>1.75</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>0.02</v>
+        <v>1.6</v>
       </c>
       <c r="L35" s="9" t="n"/>
     </row>
@@ -18386,7 +18550,7 @@
         </is>
       </c>
       <c r="E36" s="7" t="n">
-        <v>32699</v>
+        <v>32619</v>
       </c>
       <c r="F36" s="9" t="n">
         <v>0.32</v>
@@ -18430,7 +18594,7 @@
         </is>
       </c>
       <c r="E37" s="7" t="n">
-        <v>35387</v>
+        <v>35366</v>
       </c>
       <c r="F37" s="9" t="n">
         <v>1.3</v>
@@ -18602,7 +18766,7 @@
         </is>
       </c>
       <c r="E41" s="7" t="n">
-        <v>335912</v>
+        <v>340013</v>
       </c>
       <c r="F41" s="9" t="n">
         <v>2.08</v>
@@ -18617,10 +18781,10 @@
         <v>3.94</v>
       </c>
       <c r="J41" s="9" t="n">
-        <v>4.22</v>
+        <v>4.27</v>
       </c>
       <c r="K41" s="9" t="n">
-        <v>3.79</v>
+        <v>3.83</v>
       </c>
       <c r="L41" s="9" t="n"/>
     </row>
@@ -18646,7 +18810,7 @@
         </is>
       </c>
       <c r="E42" s="7" t="n">
-        <v>173062</v>
+        <v>173528</v>
       </c>
       <c r="F42" s="9" t="n">
         <v>2.31</v>
@@ -18661,10 +18825,10 @@
         <v>2.79</v>
       </c>
       <c r="J42" s="9" t="n">
-        <v>4.21</v>
+        <v>4.22</v>
       </c>
       <c r="K42" s="9" t="n">
-        <v>3.88</v>
+        <v>3.89</v>
       </c>
       <c r="L42" s="9" t="n"/>
     </row>
@@ -18690,7 +18854,7 @@
         </is>
       </c>
       <c r="E43" s="7" t="n">
-        <v>18655</v>
+        <v>14408</v>
       </c>
       <c r="F43" s="9" t="n">
         <v>0.92</v>
@@ -18705,10 +18869,10 @@
         <v>0.63</v>
       </c>
       <c r="J43" s="9" t="n">
-        <v>1.02</v>
+        <v>0.79</v>
       </c>
       <c r="K43" s="9" t="n">
-        <v>0.98</v>
+        <v>0.76</v>
       </c>
       <c r="L43" s="9" t="n"/>
     </row>
@@ -18734,7 +18898,7 @@
         </is>
       </c>
       <c r="E44" s="7" t="n">
-        <v>41066</v>
+        <v>41026</v>
       </c>
       <c r="F44" s="9" t="n"/>
       <c r="G44" s="9" t="n">
@@ -18778,7 +18942,7 @@
         </is>
       </c>
       <c r="E45" s="7" t="n">
-        <v>7289</v>
+        <v>7282</v>
       </c>
       <c r="F45" s="9" t="n"/>
       <c r="G45" s="9" t="n">
@@ -18822,7 +18986,7 @@
         </is>
       </c>
       <c r="E46" s="7" t="n">
-        <v>66856</v>
+        <v>66780</v>
       </c>
       <c r="F46" s="9" t="n">
         <v>0.8100000000000001</v>
@@ -18866,7 +19030,7 @@
         </is>
       </c>
       <c r="E47" s="7" t="n">
-        <v>24362</v>
+        <v>24311</v>
       </c>
       <c r="F47" s="9" t="n">
         <v>1.66</v>
@@ -18910,7 +19074,7 @@
         </is>
       </c>
       <c r="E48" s="7" t="n">
-        <v>12163</v>
+        <v>12138</v>
       </c>
       <c r="F48" s="9" t="n">
         <v>0.64</v>
@@ -19078,7 +19242,7 @@
         </is>
       </c>
       <c r="E52" s="7" t="n">
-        <v>64087</v>
+        <v>64966</v>
       </c>
       <c r="F52" s="9" t="n">
         <v>2.12</v>
@@ -19093,10 +19257,10 @@
         <v>3.17</v>
       </c>
       <c r="J52" s="9" t="n">
-        <v>3.61</v>
+        <v>3.66</v>
       </c>
       <c r="K52" s="9" t="n">
-        <v>3.31</v>
+        <v>3.36</v>
       </c>
       <c r="L52" s="9" t="n"/>
     </row>
@@ -19563,32 +19727,32 @@
         <v>351500</v>
       </c>
       <c r="H6" s="17" t="n">
-        <v>30719.79</v>
+        <v>30033.06</v>
       </c>
       <c r="I6" s="17" t="n">
-        <v>114906.23</v>
+        <v>114327.66</v>
       </c>
       <c r="J6" s="18" t="n">
-        <v>24876824440000</v>
+        <v>24740668320000</v>
       </c>
       <c r="K6" s="18" t="n">
-        <v>3223512781397.46</v>
+        <v>3151451982710.118</v>
       </c>
       <c r="L6" s="18" t="n">
-        <v>12057429476327.36</v>
+        <v>11996718253433.27</v>
       </c>
       <c r="M6" s="17" t="n">
-        <v>11.44</v>
+        <v>11.7</v>
       </c>
       <c r="N6" s="17" t="n"/>
       <c r="O6" s="17" t="n">
-        <v>3.06</v>
+        <v>3.07</v>
       </c>
       <c r="P6" s="17" t="n">
-        <v>30.13</v>
+        <v>29.54</v>
       </c>
       <c r="Q6" s="17" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="R6" s="17" t="inlineStr">
         <is>
@@ -19636,29 +19800,29 @@
         <v>351500</v>
       </c>
       <c r="H7" s="17" t="n">
-        <v>35705.32</v>
+        <v>34971.2</v>
       </c>
       <c r="I7" s="17" t="n">
-        <v>144987.97</v>
+        <v>143790.9</v>
       </c>
       <c r="J7" s="18" t="n">
-        <v>26797252420000</v>
+        <v>26677662210000</v>
       </c>
       <c r="K7" s="18" t="n">
-        <v>3746658693888.776</v>
+        <v>3669625340907.122</v>
       </c>
       <c r="L7" s="18" t="n">
-        <v>15213989425928.65</v>
+        <v>15088377603147.52</v>
       </c>
       <c r="M7" s="17" t="n">
-        <v>9.84</v>
+        <v>10.05</v>
       </c>
       <c r="N7" s="17" t="n"/>
       <c r="O7" s="17" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="P7" s="17" t="n">
-        <v>27.48</v>
+        <v>27.1</v>
       </c>
       <c r="Q7" s="17" t="n">
         <v>1.38</v>
@@ -20058,29 +20222,29 @@
         <v>65000</v>
       </c>
       <c r="H13" s="17" t="n">
-        <v>6186.25</v>
+        <v>6104.24</v>
       </c>
       <c r="I13" s="17" t="n">
-        <v>26324.33</v>
+        <v>26242.32</v>
       </c>
       <c r="J13" s="18" t="n">
-        <v>15831734020000</v>
+        <v>15820307080000</v>
       </c>
       <c r="K13" s="18" t="n">
-        <v>1895448249931.127</v>
+        <v>1870320739184.132</v>
       </c>
       <c r="L13" s="18" t="n">
-        <v>8065699793981.127</v>
+        <v>8040572283234.132</v>
       </c>
       <c r="M13" s="17" t="n">
-        <v>10.51</v>
+        <v>10.65</v>
       </c>
       <c r="N13" s="17" t="n"/>
       <c r="O13" s="17" t="n">
-        <v>2.47</v>
+        <v>2.48</v>
       </c>
       <c r="P13" s="17" t="n">
-        <v>26.63</v>
+        <v>26.32</v>
       </c>
       <c r="Q13" s="17" t="n">
         <v>1.26</v>
@@ -20131,29 +20295,29 @@
         <v>65000</v>
       </c>
       <c r="H14" s="17" t="n">
-        <v>6274.93</v>
+        <v>6182.11</v>
       </c>
       <c r="I14" s="17" t="n">
-        <v>32599.26</v>
+        <v>32424.43</v>
       </c>
       <c r="J14" s="18" t="n">
-        <v>15446498920000</v>
+        <v>15403595260000</v>
       </c>
       <c r="K14" s="18" t="n">
-        <v>1922622310048.97</v>
+        <v>1894180623489.071</v>
       </c>
       <c r="L14" s="18" t="n">
-        <v>9988322104030.098</v>
+        <v>9934752906723.203</v>
       </c>
       <c r="M14" s="17" t="n">
-        <v>10.36</v>
+        <v>10.51</v>
       </c>
       <c r="N14" s="17" t="n"/>
       <c r="O14" s="17" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="P14" s="17" t="n">
-        <v>21.3</v>
+        <v>21.08</v>
       </c>
       <c r="Q14" s="17" t="n">
         <v>1.29</v>
@@ -20551,32 +20715,32 @@
         <v>18400</v>
       </c>
       <c r="H20" s="17" t="n">
-        <v>1177.02</v>
+        <v>1175.69</v>
       </c>
       <c r="I20" s="17" t="n">
-        <v>6034.41</v>
+        <v>6033.08</v>
       </c>
       <c r="J20" s="18" t="n">
-        <v>12829948590000</v>
+        <v>12826981510000</v>
       </c>
       <c r="K20" s="18" t="n">
-        <v>1005352549715.528</v>
+        <v>1004215333851.666</v>
       </c>
       <c r="L20" s="18" t="n">
-        <v>5154291859355.528</v>
+        <v>5153154643491.666</v>
       </c>
       <c r="M20" s="17" t="n">
-        <v>15.63</v>
+        <v>15.65</v>
       </c>
       <c r="N20" s="17" t="n"/>
       <c r="O20" s="17" t="n">
         <v>3.05</v>
       </c>
       <c r="P20" s="17" t="n">
-        <v>21.61</v>
+        <v>21.59</v>
       </c>
       <c r="Q20" s="17" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="R20" s="17" t="inlineStr">
         <is>
@@ -20624,32 +20788,32 @@
         <v>18400</v>
       </c>
       <c r="H21" s="17" t="n">
-        <v>1689.74</v>
+        <v>1691.1</v>
       </c>
       <c r="I21" s="17" t="n">
-        <v>7724.15</v>
+        <v>7724.18</v>
       </c>
       <c r="J21" s="18" t="n">
-        <v>14766625360000</v>
+        <v>14699842200000</v>
       </c>
       <c r="K21" s="18" t="n">
-        <v>1443291098951.341</v>
+        <v>1444453939327.683</v>
       </c>
       <c r="L21" s="18" t="n">
-        <v>6597582958306.869</v>
+        <v>6597608582819.35</v>
       </c>
       <c r="M21" s="17" t="n">
-        <v>10.89</v>
+        <v>10.88</v>
       </c>
       <c r="N21" s="17" t="n"/>
       <c r="O21" s="17" t="n">
         <v>2.38</v>
       </c>
       <c r="P21" s="17" t="n">
-        <v>24.56</v>
+        <v>24.58</v>
       </c>
       <c r="Q21" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="R21" s="17" t="inlineStr">
         <is>
@@ -21048,29 +21212,29 @@
         <v>265000</v>
       </c>
       <c r="H27" s="17" t="n">
-        <v>52203.83</v>
+        <v>51904.78</v>
       </c>
       <c r="I27" s="17" t="n">
-        <v>230345.61</v>
+        <v>230102.36</v>
       </c>
       <c r="J27" s="18" t="n">
-        <v>34854796820000</v>
+        <v>34680845139999</v>
       </c>
       <c r="K27" s="18" t="n">
-        <v>3691574664462.16</v>
+        <v>3670427312931.4</v>
       </c>
       <c r="L27" s="18" t="n">
-        <v>16288804578073.52</v>
+        <v>16271603322338.4</v>
       </c>
       <c r="M27" s="17" t="n">
-        <v>5.08</v>
+        <v>5.11</v>
       </c>
       <c r="N27" s="17" t="n"/>
       <c r="O27" s="17" t="n">
         <v>1.15</v>
       </c>
       <c r="P27" s="17" t="n">
-        <v>24.96</v>
+        <v>24.84</v>
       </c>
       <c r="Q27" s="17" t="n">
         <v>0.54</v>
@@ -21121,32 +21285,32 @@
         <v>265000</v>
       </c>
       <c r="H28" s="17" t="n">
-        <v>61304.83</v>
+        <v>60438.07</v>
       </c>
       <c r="I28" s="17" t="n">
-        <v>280210.96</v>
+        <v>279262.69</v>
       </c>
       <c r="J28" s="18" t="n">
-        <v>37126069410000</v>
+        <v>37038563510000</v>
       </c>
       <c r="K28" s="18" t="n">
-        <v>4335148370662.9</v>
+        <v>4273855757964.1</v>
       </c>
       <c r="L28" s="18" t="n">
-        <v>19815014262770.72</v>
+        <v>19747957595866.4</v>
       </c>
       <c r="M28" s="17" t="n">
-        <v>4.32</v>
+        <v>4.38</v>
       </c>
       <c r="N28" s="17" t="n"/>
       <c r="O28" s="17" t="n">
         <v>0.95</v>
       </c>
       <c r="P28" s="17" t="n">
-        <v>24.01</v>
+        <v>23.73</v>
       </c>
       <c r="Q28" s="17" t="n">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="R28" s="17" t="inlineStr">
         <is>
@@ -22983,17 +23147,17 @@
         <v>38233818155.83939</v>
       </c>
       <c r="M55" s="17" t="n">
-        <v>9.81</v>
+        <v>9.83</v>
       </c>
       <c r="N55" s="17" t="n"/>
       <c r="O55" s="17" t="n">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="P55" s="17" t="n">
         <v>30.94</v>
       </c>
       <c r="Q55" s="17" t="n">
-        <v>2.96</v>
+        <v>2.97</v>
       </c>
       <c r="R55" s="17" t="inlineStr">
         <is>
@@ -23056,11 +23220,11 @@
         <v>44999698854.56541</v>
       </c>
       <c r="M56" s="17" t="n">
-        <v>8.83</v>
+        <v>8.85</v>
       </c>
       <c r="N56" s="17" t="n"/>
       <c r="O56" s="17" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="P56" s="17" t="n">
         <v>29.06</v>
@@ -23482,7 +23646,7 @@
         <v>19125837218.80924</v>
       </c>
       <c r="M62" s="17" t="n">
-        <v>14.55</v>
+        <v>14.56</v>
       </c>
       <c r="N62" s="17" t="n"/>
       <c r="O62" s="17" t="n">
@@ -23555,11 +23719,11 @@
         <v>20951974378.675</v>
       </c>
       <c r="M63" s="17" t="n">
-        <v>7.1</v>
+        <v>7.11</v>
       </c>
       <c r="N63" s="17" t="n"/>
       <c r="O63" s="17" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="P63" s="17" t="n">
         <v>11.85</v>
@@ -26419,7 +26583,9 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G104" s="17" t="n"/>
+      <c r="G104" s="17" t="n">
+        <v>12.52</v>
+      </c>
       <c r="H104" s="17" t="n">
         <v>0.55</v>
       </c>
@@ -26435,16 +26601,18 @@
       <c r="L104" s="18" t="n">
         <v>1174408680.1575</v>
       </c>
-      <c r="M104" s="17" t="n"/>
+      <c r="M104" s="17" t="n">
+        <v>22.92</v>
+      </c>
       <c r="N104" s="17" t="n"/>
       <c r="O104" s="17" t="n">
-        <v>4.04</v>
+        <v>3.46</v>
       </c>
       <c r="P104" s="17" t="n">
         <v>16.31</v>
       </c>
       <c r="Q104" s="17" t="n">
-        <v>0.51</v>
+        <v>0.43</v>
       </c>
       <c r="R104" s="17" t="inlineStr">
         <is>
@@ -26488,7 +26656,9 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G105" s="17" t="n"/>
+      <c r="G105" s="17" t="n">
+        <v>12.52</v>
+      </c>
       <c r="H105" s="17" t="n">
         <v>0.82</v>
       </c>
@@ -26504,16 +26674,18 @@
       <c r="L105" s="18" t="n">
         <v>1440753677.56484</v>
       </c>
-      <c r="M105" s="17" t="n"/>
+      <c r="M105" s="17" t="n">
+        <v>15.24</v>
+      </c>
       <c r="N105" s="17" t="n"/>
       <c r="O105" s="17" t="n">
-        <v>3.29</v>
+        <v>2.82</v>
       </c>
       <c r="P105" s="17" t="n">
         <v>20.37</v>
       </c>
       <c r="Q105" s="17" t="n">
-        <v>0.45</v>
+        <v>0.39</v>
       </c>
       <c r="R105" s="17" t="inlineStr">
         <is>
@@ -26910,7 +27082,9 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G111" s="17" t="n"/>
+      <c r="G111" s="17" t="n">
+        <v>272</v>
+      </c>
       <c r="H111" s="17" t="n">
         <v>18.5</v>
       </c>
@@ -26926,10 +27100,12 @@
       <c r="L111" s="18" t="n">
         <v>5561470755.014853</v>
       </c>
-      <c r="M111" s="17" t="n"/>
+      <c r="M111" s="17" t="n">
+        <v>14.7</v>
+      </c>
       <c r="N111" s="17" t="n"/>
       <c r="O111" s="17" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="P111" s="17" t="n">
         <v>13.65</v>
@@ -26979,7 +27155,9 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G112" s="17" t="n"/>
+      <c r="G112" s="17" t="n">
+        <v>272</v>
+      </c>
       <c r="H112" s="17" t="n">
         <v>21.01</v>
       </c>
@@ -26995,7 +27173,9 @@
       <c r="L112" s="18" t="n">
         <v>6116061130.921675</v>
       </c>
-      <c r="M112" s="17" t="n"/>
+      <c r="M112" s="17" t="n">
+        <v>12.95</v>
+      </c>
       <c r="N112" s="17" t="n"/>
       <c r="O112" s="17" t="n">
         <v>1.75</v>
@@ -27878,32 +28058,32 @@
         <v>211500</v>
       </c>
       <c r="H125" s="17" t="n">
-        <v>7831.31</v>
+        <v>7652.69</v>
       </c>
       <c r="I125" s="17" t="n">
-        <v>22605.5</v>
+        <v>22509.49</v>
       </c>
       <c r="J125" s="18" t="n">
-        <v>2354833960000</v>
+        <v>2375465460000</v>
       </c>
       <c r="K125" s="18" t="n">
-        <v>351087902773.51</v>
+        <v>343080152131.4775</v>
       </c>
       <c r="L125" s="18" t="n">
-        <v>1013434603200.762</v>
+        <v>1009130437230.669</v>
       </c>
       <c r="M125" s="17" t="n">
-        <v>27.01</v>
+        <v>27.64</v>
       </c>
       <c r="N125" s="17" t="n"/>
       <c r="O125" s="17" t="n">
-        <v>9.359999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="P125" s="17" t="n">
-        <v>38.2</v>
+        <v>37.42</v>
       </c>
       <c r="Q125" s="17" t="n">
-        <v>4.03</v>
+        <v>3.99</v>
       </c>
       <c r="R125" s="17" t="inlineStr">
         <is>
@@ -27951,32 +28131,32 @@
         <v>211500</v>
       </c>
       <c r="H126" s="17" t="n">
-        <v>9391.32</v>
+        <v>9357.49</v>
       </c>
       <c r="I126" s="17" t="n">
-        <v>27653.33</v>
+        <v>27539.14</v>
       </c>
       <c r="J126" s="18" t="n">
-        <v>2678550310000</v>
+        <v>2683070750000</v>
       </c>
       <c r="K126" s="18" t="n">
-        <v>421025368180.865</v>
+        <v>419508903443.155</v>
       </c>
       <c r="L126" s="18" t="n">
-        <v>1239735738597.977</v>
+        <v>1234616472831.365</v>
       </c>
       <c r="M126" s="17" t="n">
-        <v>22.52</v>
+        <v>22.6</v>
       </c>
       <c r="N126" s="17" t="n"/>
       <c r="O126" s="17" t="n">
-        <v>7.65</v>
+        <v>7.68</v>
       </c>
       <c r="P126" s="17" t="n">
-        <v>37.37</v>
+        <v>37.39</v>
       </c>
       <c r="Q126" s="17" t="n">
-        <v>3.54</v>
+        <v>3.53</v>
       </c>
       <c r="R126" s="17" t="inlineStr">
         <is>
@@ -30864,29 +31044,29 @@
         <v>888000</v>
       </c>
       <c r="H167" s="17" t="n">
-        <v>46578.12</v>
+        <v>45929.59</v>
       </c>
       <c r="I167" s="17" t="n">
-        <v>226787.02</v>
+        <v>226250.37</v>
       </c>
       <c r="J167" s="18" t="n">
-        <v>32220820490000</v>
+        <v>32204643850000</v>
       </c>
       <c r="K167" s="18" t="n">
-        <v>2396387666972.196</v>
+        <v>2363021738836.92</v>
       </c>
       <c r="L167" s="18" t="n">
-        <v>11667917562419.49</v>
+        <v>11640307256887.55</v>
       </c>
       <c r="M167" s="17" t="n">
-        <v>19.06</v>
+        <v>19.33</v>
       </c>
       <c r="N167" s="17" t="n"/>
       <c r="O167" s="17" t="n">
         <v>3.92</v>
       </c>
       <c r="P167" s="17" t="n">
-        <v>22.45</v>
+        <v>22.16</v>
       </c>
       <c r="Q167" s="17" t="n">
         <v>1.42</v>
@@ -30937,29 +31117,29 @@
         <v>888000</v>
       </c>
       <c r="H168" s="17" t="n">
-        <v>58466.23</v>
+        <v>57764.83</v>
       </c>
       <c r="I168" s="17" t="n">
-        <v>275167.83</v>
+        <v>274050.77</v>
       </c>
       <c r="J168" s="18" t="n">
-        <v>34622604480000</v>
+        <v>34564776120000</v>
       </c>
       <c r="K168" s="18" t="n">
-        <v>3008016878224.392</v>
+        <v>2971930595423.616</v>
       </c>
       <c r="L168" s="18" t="n">
-        <v>14157051529150.18</v>
+        <v>14099579824600.59</v>
       </c>
       <c r="M168" s="17" t="n">
-        <v>15.19</v>
+        <v>15.37</v>
       </c>
       <c r="N168" s="17" t="n"/>
       <c r="O168" s="17" t="n">
-        <v>3.23</v>
+        <v>3.24</v>
       </c>
       <c r="P168" s="17" t="n">
-        <v>23.3</v>
+        <v>23.09</v>
       </c>
       <c r="Q168" s="17" t="n">
         <v>1.32</v>
@@ -32359,32 +32539,32 @@
         <v>96900</v>
       </c>
       <c r="H188" s="17" t="n">
-        <v>7942.66</v>
+        <v>7923.99</v>
       </c>
       <c r="I188" s="17" t="n">
-        <v>35509.6</v>
+        <v>35492.44</v>
       </c>
       <c r="J188" s="18" t="n">
-        <v>6763997600000</v>
+        <v>6749053020000</v>
       </c>
       <c r="K188" s="18" t="n">
-        <v>866880234061.673</v>
+        <v>864842143624.8789</v>
       </c>
       <c r="L188" s="18" t="n">
-        <v>3875599231280.553</v>
+        <v>3873726429965.954</v>
       </c>
       <c r="M188" s="17" t="n">
-        <v>12.2</v>
+        <v>12.23</v>
       </c>
       <c r="N188" s="17" t="n"/>
       <c r="O188" s="17" t="n">
         <v>2.73</v>
       </c>
       <c r="P188" s="17" t="n">
-        <v>24.93</v>
+        <v>24.88</v>
       </c>
       <c r="Q188" s="17" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="R188" s="17" t="inlineStr">
         <is>
@@ -32432,29 +32612,29 @@
         <v>96900</v>
       </c>
       <c r="H189" s="17" t="n">
-        <v>10302.95</v>
+        <v>10218.6</v>
       </c>
       <c r="I189" s="17" t="n">
-        <v>44976.98</v>
+        <v>44882.32</v>
       </c>
       <c r="J189" s="18" t="n">
-        <v>7861624860000</v>
+        <v>7807104020000</v>
       </c>
       <c r="K189" s="18" t="n">
-        <v>1124487478522.057</v>
+        <v>1115281926390.118</v>
       </c>
       <c r="L189" s="18" t="n">
-        <v>4908890782041.396</v>
+        <v>4898558998817.525</v>
       </c>
       <c r="M189" s="17" t="n">
-        <v>9.41</v>
+        <v>9.48</v>
       </c>
       <c r="N189" s="17" t="n"/>
       <c r="O189" s="17" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="P189" s="17" t="n">
-        <v>25.6</v>
+        <v>25.43</v>
       </c>
       <c r="Q189" s="17" t="n">
         <v>1.35</v>
@@ -32854,7 +33034,9 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G195" s="17" t="n"/>
+      <c r="G195" s="17" t="n">
+        <v>552.09</v>
+      </c>
       <c r="H195" s="17" t="n">
         <v>30.42</v>
       </c>
@@ -32870,16 +33052,18 @@
       <c r="L195" s="18" t="n">
         <v>10182208950.22479</v>
       </c>
-      <c r="M195" s="17" t="n"/>
+      <c r="M195" s="17" t="n">
+        <v>18.15</v>
+      </c>
       <c r="N195" s="17" t="n"/>
       <c r="O195" s="17" t="n">
-        <v>12.51</v>
+        <v>12.42</v>
       </c>
       <c r="P195" s="17" t="n">
         <v>82.42</v>
       </c>
       <c r="Q195" s="17" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="R195" s="17" t="inlineStr">
         <is>
@@ -32923,7 +33107,9 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G196" s="17" t="n"/>
+      <c r="G196" s="17" t="n">
+        <v>552.09</v>
+      </c>
       <c r="H196" s="17" t="n">
         <v>32.73</v>
       </c>
@@ -32939,16 +33125,18 @@
       <c r="L196" s="18" t="n">
         <v>13906474418.75077</v>
       </c>
-      <c r="M196" s="17" t="n"/>
+      <c r="M196" s="17" t="n">
+        <v>16.87</v>
+      </c>
       <c r="N196" s="17" t="n"/>
       <c r="O196" s="17" t="n">
-        <v>9.16</v>
+        <v>9.09</v>
       </c>
       <c r="P196" s="17" t="n">
         <v>62.23</v>
       </c>
       <c r="Q196" s="17" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="R196" s="17" t="inlineStr">
         <is>
@@ -33345,7 +33533,9 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G202" s="17" t="n"/>
+      <c r="G202" s="17" t="n">
+        <v>519.86</v>
+      </c>
       <c r="H202" s="17" t="n">
         <v>28.98</v>
       </c>
@@ -33361,10 +33551,12 @@
       <c r="L202" s="18" t="n">
         <v>19559321914.19876</v>
       </c>
-      <c r="M202" s="17" t="n"/>
+      <c r="M202" s="17" t="n">
+        <v>17.94</v>
+      </c>
       <c r="N202" s="17" t="n"/>
       <c r="O202" s="17" t="n">
-        <v>3.78</v>
+        <v>3.77</v>
       </c>
       <c r="P202" s="17" t="n">
         <v>22.71</v>
@@ -33414,7 +33606,9 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G203" s="17" t="n"/>
+      <c r="G203" s="17" t="n">
+        <v>519.86</v>
+      </c>
       <c r="H203" s="17" t="n">
         <v>30.37</v>
       </c>
@@ -33430,7 +33624,9 @@
       <c r="L203" s="18" t="n">
         <v>22583050919.26938</v>
       </c>
-      <c r="M203" s="17" t="n"/>
+      <c r="M203" s="17" t="n">
+        <v>17.12</v>
+      </c>
       <c r="N203" s="17" t="n"/>
       <c r="O203" s="17" t="n">
         <v>3.27</v>
@@ -33836,7 +34032,9 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G209" s="17" t="n"/>
+      <c r="G209" s="17" t="n">
+        <v>344.23</v>
+      </c>
       <c r="H209" s="17" t="n">
         <v>17</v>
       </c>
@@ -33852,7 +34050,9 @@
       <c r="L209" s="18" t="n">
         <v>28484414672.91019</v>
       </c>
-      <c r="M209" s="17" t="n"/>
+      <c r="M209" s="17" t="n">
+        <v>20.25</v>
+      </c>
       <c r="N209" s="17" t="n"/>
       <c r="O209" s="17" t="n">
         <v>3.27</v>
@@ -33861,7 +34061,7 @@
         <v>16.99</v>
       </c>
       <c r="Q209" s="17" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="R209" s="17" t="inlineStr">
         <is>
@@ -33905,7 +34105,9 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G210" s="17" t="n"/>
+      <c r="G210" s="17" t="n">
+        <v>344.23</v>
+      </c>
       <c r="H210" s="17" t="n">
         <v>18.64</v>
       </c>
@@ -33921,10 +34123,12 @@
       <c r="L210" s="18" t="n">
         <v>31624169342.16605</v>
       </c>
-      <c r="M210" s="17" t="n"/>
+      <c r="M210" s="17" t="n">
+        <v>18.47</v>
+      </c>
       <c r="N210" s="17" t="n"/>
       <c r="O210" s="17" t="n">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="P210" s="17" t="n">
         <v>16.77</v>
@@ -34327,7 +34531,9 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G216" s="17" t="n"/>
+      <c r="G216" s="17" t="n">
+        <v>193.92</v>
+      </c>
       <c r="H216" s="17" t="n">
         <v>7.25</v>
       </c>
@@ -34343,16 +34549,18 @@
       <c r="L216" s="18" t="n">
         <v>70231990219.98564</v>
       </c>
-      <c r="M216" s="17" t="n"/>
+      <c r="M216" s="17" t="n">
+        <v>26.74</v>
+      </c>
       <c r="N216" s="17" t="n"/>
       <c r="O216" s="17" t="n">
-        <v>3.72</v>
+        <v>3.71</v>
       </c>
       <c r="P216" s="17" t="n">
         <v>14.37</v>
       </c>
       <c r="Q216" s="17" t="n">
-        <v>2.72</v>
+        <v>2.71</v>
       </c>
       <c r="R216" s="17" t="inlineStr">
         <is>
@@ -34396,7 +34604,9 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G217" s="17" t="n"/>
+      <c r="G217" s="17" t="n">
+        <v>193.92</v>
+      </c>
       <c r="H217" s="17" t="n">
         <v>7.87</v>
       </c>
@@ -34412,16 +34622,18 @@
       <c r="L217" s="18" t="n">
         <v>75643854309.25201</v>
       </c>
-      <c r="M217" s="17" t="n"/>
+      <c r="M217" s="17" t="n">
+        <v>24.64</v>
+      </c>
       <c r="N217" s="17" t="n"/>
       <c r="O217" s="17" t="n">
-        <v>3.46</v>
+        <v>3.44</v>
       </c>
       <c r="P217" s="17" t="n">
         <v>14.48</v>
       </c>
       <c r="Q217" s="17" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="R217" s="17" t="inlineStr">
         <is>
@@ -34818,7 +35030,9 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G223" s="17" t="n"/>
+      <c r="G223" s="17" t="n">
+        <v>272</v>
+      </c>
       <c r="H223" s="17" t="n">
         <v>18.5</v>
       </c>
@@ -34834,10 +35048,12 @@
       <c r="L223" s="18" t="n">
         <v>5561470755.014853</v>
       </c>
-      <c r="M223" s="17" t="n"/>
+      <c r="M223" s="17" t="n">
+        <v>14.7</v>
+      </c>
       <c r="N223" s="17" t="n"/>
       <c r="O223" s="17" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="P223" s="17" t="n">
         <v>13.65</v>
@@ -34887,7 +35103,9 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G224" s="17" t="n"/>
+      <c r="G224" s="17" t="n">
+        <v>272</v>
+      </c>
       <c r="H224" s="17" t="n">
         <v>21.01</v>
       </c>
@@ -34903,7 +35121,9 @@
       <c r="L224" s="18" t="n">
         <v>6116061130.921675</v>
       </c>
-      <c r="M224" s="17" t="n"/>
+      <c r="M224" s="17" t="n">
+        <v>12.95</v>
+      </c>
       <c r="N224" s="17" t="n"/>
       <c r="O224" s="17" t="n">
         <v>1.75</v>
@@ -35309,7 +35529,9 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G230" s="17" t="n"/>
+      <c r="G230" s="17" t="n">
+        <v>1090.2</v>
+      </c>
       <c r="H230" s="17" t="n">
         <v>37.27</v>
       </c>
@@ -35325,16 +35547,18 @@
       <c r="L230" s="18" t="n">
         <v>5957336206.677702</v>
       </c>
-      <c r="M230" s="17" t="n"/>
+      <c r="M230" s="17" t="n">
+        <v>29.25</v>
+      </c>
       <c r="N230" s="17" t="n"/>
       <c r="O230" s="17" t="n">
-        <v>8.539999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="P230" s="17" t="n">
         <v>31.18</v>
       </c>
       <c r="Q230" s="17" t="n">
-        <v>3.65</v>
+        <v>3.59</v>
       </c>
       <c r="R230" s="17" t="inlineStr">
         <is>
@@ -35378,7 +35602,9 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G231" s="17" t="n"/>
+      <c r="G231" s="17" t="n">
+        <v>1090.2</v>
+      </c>
       <c r="H231" s="17" t="n">
         <v>52.99</v>
       </c>
@@ -35394,16 +35620,18 @@
       <c r="L231" s="18" t="n">
         <v>7302807985.536924</v>
       </c>
-      <c r="M231" s="17" t="n"/>
+      <c r="M231" s="17" t="n">
+        <v>20.57</v>
+      </c>
       <c r="N231" s="17" t="n"/>
       <c r="O231" s="17" t="n">
-        <v>6.97</v>
+        <v>6.85</v>
       </c>
       <c r="P231" s="17" t="n">
         <v>36.67</v>
       </c>
       <c r="Q231" s="17" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="R231" s="17" t="inlineStr">
         <is>
@@ -35800,7 +36028,9 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G237" s="17" t="n"/>
+      <c r="G237" s="17" t="n">
+        <v>19.84</v>
+      </c>
       <c r="H237" s="17" t="n">
         <v>0.84</v>
       </c>
@@ -35816,16 +36046,18 @@
       <c r="L237" s="18" t="n">
         <v>12968110821.03935</v>
       </c>
-      <c r="M237" s="17" t="n"/>
+      <c r="M237" s="17" t="n">
+        <v>23.53</v>
+      </c>
       <c r="N237" s="17" t="n"/>
       <c r="O237" s="17" t="n">
-        <v>0.04</v>
+        <v>4.48</v>
       </c>
       <c r="P237" s="17" t="n">
         <v>19.94</v>
       </c>
       <c r="Q237" s="17" t="n">
-        <v>0.02</v>
+        <v>1.75</v>
       </c>
       <c r="R237" s="17" t="inlineStr">
         <is>
@@ -35869,7 +36101,9 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G238" s="17" t="n"/>
+      <c r="G238" s="17" t="n">
+        <v>19.84</v>
+      </c>
       <c r="H238" s="17" t="n">
         <v>0.96</v>
       </c>
@@ -35885,16 +36119,18 @@
       <c r="L238" s="18" t="n">
         <v>14316836787.42144</v>
       </c>
-      <c r="M238" s="17" t="n"/>
+      <c r="M238" s="17" t="n">
+        <v>20.66</v>
+      </c>
       <c r="N238" s="17" t="n"/>
       <c r="O238" s="17" t="n">
-        <v>0.04</v>
+        <v>4.06</v>
       </c>
       <c r="P238" s="17" t="n">
         <v>20.6</v>
       </c>
       <c r="Q238" s="17" t="n">
-        <v>0.02</v>
+        <v>1.6</v>
       </c>
       <c r="R238" s="17" t="inlineStr">
         <is>
@@ -36291,7 +36527,9 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G244" s="17" t="n"/>
+      <c r="G244" s="17" t="n">
+        <v>50.42</v>
+      </c>
       <c r="H244" s="17" t="n">
         <v>2.39</v>
       </c>
@@ -36307,7 +36545,9 @@
       <c r="L244" s="18" t="n">
         <v>10504026583.2873</v>
       </c>
-      <c r="M244" s="17" t="n"/>
+      <c r="M244" s="17" t="n">
+        <v>21.13</v>
+      </c>
       <c r="N244" s="17" t="n"/>
       <c r="O244" s="17" t="n">
         <v>2.77</v>
@@ -36360,7 +36600,9 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G245" s="17" t="n"/>
+      <c r="G245" s="17" t="n">
+        <v>50.42</v>
+      </c>
       <c r="H245" s="17" t="n">
         <v>2.87</v>
       </c>
@@ -36376,7 +36618,9 @@
       <c r="L245" s="18" t="n">
         <v>11638080741.73469</v>
       </c>
-      <c r="M245" s="17" t="n"/>
+      <c r="M245" s="17" t="n">
+        <v>17.59</v>
+      </c>
       <c r="N245" s="17" t="n"/>
       <c r="O245" s="17" t="n">
         <v>2.5</v>
@@ -36782,7 +37026,9 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G251" s="17" t="n"/>
+      <c r="G251" s="17" t="n">
+        <v>650.2</v>
+      </c>
       <c r="H251" s="17" t="n">
         <v>14.94</v>
       </c>
@@ -36798,7 +37044,9 @@
       <c r="L251" s="18" t="n">
         <v>50038868493.76913</v>
       </c>
-      <c r="M251" s="17" t="n"/>
+      <c r="M251" s="17" t="n">
+        <v>43.52</v>
+      </c>
       <c r="N251" s="17" t="n"/>
       <c r="O251" s="17" t="n">
         <v>7</v>
@@ -36851,7 +37099,9 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G252" s="17" t="n"/>
+      <c r="G252" s="17" t="n">
+        <v>650.2</v>
+      </c>
       <c r="H252" s="17" t="n">
         <v>19.04</v>
       </c>
@@ -36867,7 +37117,9 @@
       <c r="L252" s="18" t="n">
         <v>58579211753.7936</v>
       </c>
-      <c r="M252" s="17" t="n"/>
+      <c r="M252" s="17" t="n">
+        <v>34.15</v>
+      </c>
       <c r="N252" s="17" t="n"/>
       <c r="O252" s="17" t="n">
         <v>5.98</v>
@@ -38734,7 +38986,9 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G279" s="17" t="n"/>
+      <c r="G279" s="17" t="n">
+        <v>730.76</v>
+      </c>
       <c r="H279" s="17" t="n">
         <v>27.33</v>
       </c>
@@ -38750,16 +39004,18 @@
       <c r="L279" s="18" t="n">
         <v>30727864358.51151</v>
       </c>
-      <c r="M279" s="17" t="n"/>
+      <c r="M279" s="17" t="n">
+        <v>26.74</v>
+      </c>
       <c r="N279" s="17" t="n"/>
       <c r="O279" s="17" t="n">
-        <v>10.93</v>
+        <v>11.07</v>
       </c>
       <c r="P279" s="17" t="n">
         <v>48.86</v>
       </c>
       <c r="Q279" s="17" t="n">
-        <v>4.22</v>
+        <v>4.27</v>
       </c>
       <c r="R279" s="17" t="inlineStr">
         <is>
@@ -38803,7 +39059,9 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G280" s="17" t="n"/>
+      <c r="G280" s="17" t="n">
+        <v>730.76</v>
+      </c>
       <c r="H280" s="17" t="n">
         <v>32.59</v>
       </c>
@@ -38819,16 +39077,18 @@
       <c r="L280" s="18" t="n">
         <v>41947387673.8295</v>
       </c>
-      <c r="M280" s="17" t="n"/>
+      <c r="M280" s="17" t="n">
+        <v>22.43</v>
+      </c>
       <c r="N280" s="17" t="n"/>
       <c r="O280" s="17" t="n">
-        <v>8.01</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="P280" s="17" t="n">
         <v>41.72</v>
       </c>
       <c r="Q280" s="17" t="n">
-        <v>3.79</v>
+        <v>3.83</v>
       </c>
       <c r="R280" s="17" t="inlineStr">
         <is>
@@ -39225,7 +39485,9 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G286" s="17" t="n"/>
+      <c r="G286" s="17" t="n">
+        <v>641.86</v>
+      </c>
       <c r="H286" s="17" t="n">
         <v>18.11</v>
       </c>
@@ -39236,21 +39498,23 @@
         <v>41122105540</v>
       </c>
       <c r="K286" s="18" t="n">
-        <v>4896483675.9804</v>
+        <v>4896175474.654799</v>
       </c>
       <c r="L286" s="18" t="n">
-        <v>29082770157.96259</v>
-      </c>
-      <c r="M286" s="17" t="n"/>
+        <v>29082572970.76063</v>
+      </c>
+      <c r="M286" s="17" t="n">
+        <v>35.44</v>
+      </c>
       <c r="N286" s="17" t="n"/>
       <c r="O286" s="17" t="n">
-        <v>5.95</v>
+        <v>5.97</v>
       </c>
       <c r="P286" s="17" t="n">
         <v>17.79</v>
       </c>
       <c r="Q286" s="17" t="n">
-        <v>4.21</v>
+        <v>4.22</v>
       </c>
       <c r="R286" s="17" t="inlineStr">
         <is>
@@ -39294,7 +39558,9 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G287" s="17" t="n"/>
+      <c r="G287" s="17" t="n">
+        <v>641.86</v>
+      </c>
       <c r="H287" s="17" t="n">
         <v>22.99</v>
       </c>
@@ -39308,18 +39574,20 @@
         <v>6214658042.0512</v>
       </c>
       <c r="L287" s="18" t="n">
-        <v>33058908248.97378</v>
-      </c>
-      <c r="M287" s="17" t="n"/>
+        <v>33058711061.77183</v>
+      </c>
+      <c r="M287" s="17" t="n">
+        <v>27.92</v>
+      </c>
       <c r="N287" s="17" t="n"/>
       <c r="O287" s="17" t="n">
-        <v>5.23</v>
+        <v>5.25</v>
       </c>
       <c r="P287" s="17" t="n">
         <v>20</v>
       </c>
       <c r="Q287" s="17" t="n">
-        <v>3.88</v>
+        <v>3.89</v>
       </c>
       <c r="R287" s="17" t="inlineStr">
         <is>
@@ -39716,7 +39984,9 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G293" s="17" t="n"/>
+      <c r="G293" s="17" t="n">
+        <v>11.6</v>
+      </c>
       <c r="H293" s="17" t="n">
         <v>0.45</v>
       </c>
@@ -39732,16 +40002,18 @@
       <c r="L293" s="18" t="n">
         <v>8065566141.002792</v>
       </c>
-      <c r="M293" s="17" t="n"/>
+      <c r="M293" s="17" t="n">
+        <v>25.76</v>
+      </c>
       <c r="N293" s="17" t="n"/>
       <c r="O293" s="17" t="n">
-        <v>2.31</v>
+        <v>1.79</v>
       </c>
       <c r="P293" s="17" t="n">
         <v>7.08</v>
       </c>
       <c r="Q293" s="17" t="n">
-        <v>1.02</v>
+        <v>0.79</v>
       </c>
       <c r="R293" s="17" t="inlineStr">
         <is>
@@ -39785,7 +40057,9 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G294" s="17" t="n"/>
+      <c r="G294" s="17" t="n">
+        <v>11.6</v>
+      </c>
       <c r="H294" s="17" t="n">
         <v>0.6899999999999999</v>
       </c>
@@ -39801,16 +40075,18 @@
       <c r="L294" s="18" t="n">
         <v>8580332411.404028</v>
       </c>
-      <c r="M294" s="17" t="n"/>
+      <c r="M294" s="17" t="n">
+        <v>16.79</v>
+      </c>
       <c r="N294" s="17" t="n"/>
       <c r="O294" s="17" t="n">
-        <v>2.17</v>
+        <v>1.68</v>
       </c>
       <c r="P294" s="17" t="n">
         <v>10.31</v>
       </c>
       <c r="Q294" s="17" t="n">
-        <v>0.98</v>
+        <v>0.76</v>
       </c>
       <c r="R294" s="17" t="inlineStr">
         <is>
@@ -41205,7 +41481,9 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G314" s="17" t="n"/>
+      <c r="G314" s="17" t="n">
+        <v>325.4</v>
+      </c>
       <c r="H314" s="17" t="n">
         <v>21.57</v>
       </c>
@@ -41221,7 +41499,9 @@
       <c r="L314" s="18" t="n">
         <v>201102258179.8709</v>
       </c>
-      <c r="M314" s="17" t="n"/>
+      <c r="M314" s="17" t="n">
+        <v>15.08</v>
+      </c>
       <c r="N314" s="17" t="n"/>
       <c r="O314" s="17" t="n">
         <v>3.29</v>
@@ -41274,7 +41554,9 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G315" s="17" t="n"/>
+      <c r="G315" s="17" t="n">
+        <v>325.4</v>
+      </c>
       <c r="H315" s="17" t="n">
         <v>25.78</v>
       </c>
@@ -41290,7 +41572,9 @@
       <c r="L315" s="18" t="n">
         <v>228234046238.5371</v>
       </c>
-      <c r="M315" s="17" t="n"/>
+      <c r="M315" s="17" t="n">
+        <v>12.62</v>
+      </c>
       <c r="N315" s="17" t="n"/>
       <c r="O315" s="17" t="n">
         <v>2.9</v>
@@ -44127,7 +44411,9 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G356" s="17" t="n"/>
+      <c r="G356" s="17" t="n">
+        <v>1029.64</v>
+      </c>
       <c r="H356" s="17" t="n">
         <v>49.68</v>
       </c>
@@ -44143,16 +44429,18 @@
       <c r="L356" s="18" t="n">
         <v>11536022147.72089</v>
       </c>
-      <c r="M356" s="17" t="n"/>
+      <c r="M356" s="17" t="n">
+        <v>20.72</v>
+      </c>
       <c r="N356" s="17" t="n"/>
       <c r="O356" s="17" t="n">
-        <v>5.56</v>
+        <v>5.63</v>
       </c>
       <c r="P356" s="17" t="n">
         <v>30.58</v>
       </c>
       <c r="Q356" s="17" t="n">
-        <v>3.61</v>
+        <v>3.66</v>
       </c>
       <c r="R356" s="17" t="inlineStr">
         <is>
@@ -44196,7 +44484,9 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G357" s="17" t="n"/>
+      <c r="G357" s="17" t="n">
+        <v>1029.64</v>
+      </c>
       <c r="H357" s="17" t="n">
         <v>57.85</v>
       </c>
@@ -44212,16 +44502,18 @@
       <c r="L357" s="18" t="n">
         <v>14526020192.81969</v>
       </c>
-      <c r="M357" s="17" t="n"/>
+      <c r="M357" s="17" t="n">
+        <v>17.8</v>
+      </c>
       <c r="N357" s="17" t="n"/>
       <c r="O357" s="17" t="n">
-        <v>4.41</v>
+        <v>4.47</v>
       </c>
       <c r="P357" s="17" t="n">
         <v>28.01</v>
       </c>
       <c r="Q357" s="17" t="n">
-        <v>3.31</v>
+        <v>3.36</v>
       </c>
       <c r="R357" s="17" t="inlineStr">
         <is>
@@ -44529,7 +44821,7 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>2026-10-17T09:07:14+09:00</t>
+          <t>2026-10-19T05:55:13+09:00</t>
         </is>
       </c>
     </row>

--- a/telegram_research_dashboard/static/valuation_full.xlsx
+++ b/telegram_research_dashboard/static/valuation_full.xlsx
@@ -44821,7 +44821,7 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>2026-10-19T05:55:13+09:00</t>
+          <t>2026-10-19T06:23:49+09:00</t>
         </is>
       </c>
     </row>

--- a/telegram_research_dashboard/static/valuation_full.xlsx
+++ b/telegram_research_dashboard/static/valuation_full.xlsx
@@ -44821,7 +44821,7 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>2026-10-19T06:23:49+09:00</t>
+          <t>2026-10-19T06:32:46+09:00</t>
         </is>
       </c>
     </row>

--- a/telegram_research_dashboard/static/valuation_full.xlsx
+++ b/telegram_research_dashboard/static/valuation_full.xlsx
@@ -815,7 +815,7 @@
         <v>37.73</v>
       </c>
       <c r="G5" s="10" t="n">
-        <v>11.7</v>
+        <v>11.58</v>
       </c>
       <c r="H5" s="10" t="n">
         <v>10.05</v>
@@ -847,7 +847,7 @@
         <v>5.72</v>
       </c>
       <c r="U5" s="10" t="n">
-        <v>3.07</v>
+        <v>3.2</v>
       </c>
       <c r="V5" s="10" t="n">
         <v>2.44</v>
@@ -866,7 +866,7 @@
         <v>18.82</v>
       </c>
       <c r="AB5" s="12" t="n">
-        <v>29.54</v>
+        <v>30.55</v>
       </c>
       <c r="AC5" s="12" t="n">
         <v>27.1</v>
@@ -912,7 +912,7 @@
         <v>27.94</v>
       </c>
       <c r="G6" s="10" t="n">
-        <v>10.65</v>
+        <v>10.2</v>
       </c>
       <c r="H6" s="10" t="n">
         <v>10.51</v>
@@ -944,7 +944,7 @@
         <v>5.64</v>
       </c>
       <c r="U6" s="10" t="n">
-        <v>2.48</v>
+        <v>2.42</v>
       </c>
       <c r="V6" s="10" t="n">
         <v>2</v>
@@ -963,7 +963,7 @@
         <v>22.59</v>
       </c>
       <c r="AB6" s="12" t="n">
-        <v>26.32</v>
+        <v>27.15</v>
       </c>
       <c r="AC6" s="12" t="n">
         <v>21.08</v>
@@ -1007,7 +1007,7 @@
         <v>37.73</v>
       </c>
       <c r="G7" s="10" t="n">
-        <v>15.65</v>
+        <v>17.39</v>
       </c>
       <c r="H7" s="10" t="n">
         <v>10.88</v>
@@ -1039,7 +1039,7 @@
         <v>4.96</v>
       </c>
       <c r="U7" s="10" t="n">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="V7" s="10" t="n">
         <v>2.38</v>
@@ -1058,7 +1058,7 @@
         <v>13.74</v>
       </c>
       <c r="AB7" s="12" t="n">
-        <v>21.59</v>
+        <v>19.97</v>
       </c>
       <c r="AC7" s="12" t="n">
         <v>24.58</v>
@@ -1104,7 +1104,7 @@
         <v>13.27</v>
       </c>
       <c r="G8" s="10" t="n">
-        <v>5.11</v>
+        <v>4.73</v>
       </c>
       <c r="H8" s="10" t="n">
         <v>4.38</v>
@@ -1138,7 +1138,7 @@
         <v>2.17</v>
       </c>
       <c r="U8" s="10" t="n">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="V8" s="10" t="n">
         <v>0.95</v>
@@ -1157,7 +1157,7 @@
         <v>17.78</v>
       </c>
       <c r="AB8" s="12" t="n">
-        <v>24.84</v>
+        <v>27.86</v>
       </c>
       <c r="AC8" s="12" t="n">
         <v>23.73</v>
@@ -1199,7 +1199,7 @@
         <v>10.3</v>
       </c>
       <c r="G9" s="10" t="n">
-        <v>5.39</v>
+        <v>5.31</v>
       </c>
       <c r="H9" s="10" t="n">
         <v>5.29</v>
@@ -1221,7 +1221,7 @@
         <v>2.35</v>
       </c>
       <c r="U9" s="10" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="V9" s="10" t="n">
         <v>0.95</v>
@@ -1240,7 +1240,7 @@
         <v>32.19</v>
       </c>
       <c r="AB9" s="12" t="n">
-        <v>23.73</v>
+        <v>24.44</v>
       </c>
       <c r="AC9" s="12" t="n">
         <v>19.63</v>
@@ -1277,7 +1277,9 @@
       <c r="F10" s="9" t="n">
         <v>36.95</v>
       </c>
-      <c r="G10" s="10" t="n"/>
+      <c r="G10" s="10" t="n">
+        <v>6.37</v>
+      </c>
       <c r="H10" s="10" t="n"/>
       <c r="I10" s="10" t="n"/>
       <c r="J10" s="9" t="n">
@@ -1305,7 +1307,9 @@
       <c r="T10" s="9" t="n">
         <v>2.84</v>
       </c>
-      <c r="U10" s="10" t="n"/>
+      <c r="U10" s="10" t="n">
+        <v>1.46</v>
+      </c>
       <c r="V10" s="10" t="n"/>
       <c r="W10" s="10" t="n"/>
       <c r="X10" s="11" t="n">
@@ -1320,7 +1324,9 @@
       <c r="AA10" s="11" t="n">
         <v>10.15</v>
       </c>
-      <c r="AB10" s="12" t="n"/>
+      <c r="AB10" s="12" t="n">
+        <v>24.85</v>
+      </c>
       <c r="AC10" s="12" t="n"/>
       <c r="AD10" s="12" t="n"/>
       <c r="AE10" s="9" t="n">
@@ -1357,7 +1363,7 @@
         <v>32.18</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>27.64</v>
+        <v>27.15</v>
       </c>
       <c r="H11" s="10" t="n">
         <v>22.6</v>
@@ -1383,7 +1389,7 @@
         <v>10.52</v>
       </c>
       <c r="U11" s="10" t="n">
-        <v>9.4</v>
+        <v>9.41</v>
       </c>
       <c r="V11" s="10" t="n">
         <v>7.68</v>
@@ -1402,7 +1408,7 @@
         <v>33.73</v>
       </c>
       <c r="AB11" s="12" t="n">
-        <v>37.42</v>
+        <v>38.12</v>
       </c>
       <c r="AC11" s="12" t="n">
         <v>37.39</v>
@@ -1446,7 +1452,7 @@
         <v>18.39</v>
       </c>
       <c r="G12" s="10" t="n">
-        <v>10.98</v>
+        <v>10.88</v>
       </c>
       <c r="H12" s="10" t="n">
         <v>8.19</v>
@@ -1480,7 +1486,7 @@
         <v>6.21</v>
       </c>
       <c r="U12" s="10" t="n">
-        <v>2.26</v>
+        <v>2.66</v>
       </c>
       <c r="V12" s="10" t="n">
         <v>1.77</v>
@@ -1499,7 +1505,7 @@
         <v>41.36</v>
       </c>
       <c r="AB12" s="12" t="n">
-        <v>22.94</v>
+        <v>25.25</v>
       </c>
       <c r="AC12" s="12" t="n">
         <v>24.25</v>
@@ -1543,7 +1549,7 @@
         <v>20.62</v>
       </c>
       <c r="G13" s="10" t="n">
-        <v>16.62</v>
+        <v>16.65</v>
       </c>
       <c r="H13" s="10" t="n">
         <v>10.27</v>
@@ -1575,7 +1581,7 @@
         <v>6.44</v>
       </c>
       <c r="U13" s="10" t="n">
-        <v>4.19</v>
+        <v>4.16</v>
       </c>
       <c r="V13" s="10" t="n">
         <v>2.98</v>
@@ -1594,7 +1600,7 @@
         <v>36.6</v>
       </c>
       <c r="AB13" s="12" t="n">
-        <v>28.85</v>
+        <v>28.77</v>
       </c>
       <c r="AC13" s="12" t="n">
         <v>33.88</v>
@@ -1640,7 +1646,7 @@
         <v>14.78</v>
       </c>
       <c r="G14" s="10" t="n">
-        <v>7.51</v>
+        <v>7.77</v>
       </c>
       <c r="H14" s="10" t="n">
         <v>6.32</v>
@@ -1674,7 +1680,7 @@
         <v>2.59</v>
       </c>
       <c r="U14" s="10" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="V14" s="10" t="n">
         <v>1.12</v>
@@ -1693,7 +1699,7 @@
         <v>19.3</v>
       </c>
       <c r="AB14" s="12" t="n">
-        <v>18.94</v>
+        <v>18.68</v>
       </c>
       <c r="AC14" s="12" t="n">
         <v>19.16</v>
@@ -1741,7 +1747,7 @@
         <v>13.58</v>
       </c>
       <c r="G15" s="10" t="n">
-        <v>5.92</v>
+        <v>5.02</v>
       </c>
       <c r="H15" s="10" t="n">
         <v>4.98</v>
@@ -1775,7 +1781,7 @@
         <v>2.93</v>
       </c>
       <c r="U15" s="10" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="V15" s="10" t="n">
         <v>1.03</v>
@@ -1794,7 +1800,7 @@
         <v>24.23</v>
       </c>
       <c r="AB15" s="12" t="n">
-        <v>24.74</v>
+        <v>29.46</v>
       </c>
       <c r="AC15" s="12" t="n">
         <v>23.13</v>
@@ -2954,7 +2960,7 @@
         <v>20.62</v>
       </c>
       <c r="G32" s="15" t="n">
-        <v>10.82</v>
+        <v>10.2</v>
       </c>
       <c r="H32" s="15" t="n">
         <v>9.119999999999999</v>
@@ -2988,7 +2994,7 @@
         <v>4.96</v>
       </c>
       <c r="U32" s="15" t="n">
-        <v>2.37</v>
+        <v>2.42</v>
       </c>
       <c r="V32" s="15" t="n">
         <v>1.89</v>
@@ -3007,7 +3013,7 @@
         <v>22.59</v>
       </c>
       <c r="AB32" s="16" t="n">
-        <v>24.79</v>
+        <v>27.15</v>
       </c>
       <c r="AC32" s="16" t="n">
         <v>23.99</v>
@@ -3538,7 +3544,7 @@
         <v>19.51</v>
       </c>
       <c r="G38" s="15" t="n">
-        <v>13.72</v>
+        <v>12.88</v>
       </c>
       <c r="H38" s="15" t="n">
         <v>10.39</v>
@@ -3576,7 +3582,7 @@
         <v>2.73</v>
       </c>
       <c r="U38" s="15" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="V38" s="15" t="n">
         <v>1.87</v>
@@ -3597,7 +3603,7 @@
         <v>18.3</v>
       </c>
       <c r="AB38" s="16" t="n">
-        <v>21.59</v>
+        <v>22.2</v>
       </c>
       <c r="AC38" s="16" t="n">
         <v>20.73</v>
@@ -3699,7 +3705,7 @@
         <v>59.99</v>
       </c>
       <c r="G42" s="10" t="n">
-        <v>43.17</v>
+        <v>46.33</v>
       </c>
       <c r="H42" s="10" t="n">
         <v>24.08</v>
@@ -3733,7 +3739,7 @@
         <v>6.09</v>
       </c>
       <c r="U42" s="10" t="n">
-        <v>5.26</v>
+        <v>5.2</v>
       </c>
       <c r="V42" s="10" t="n">
         <v>4.54</v>
@@ -3752,7 +3758,7 @@
         <v>10.51</v>
       </c>
       <c r="AB42" s="12" t="n">
-        <v>12.76</v>
+        <v>11.81</v>
       </c>
       <c r="AC42" s="12" t="n">
         <v>20.25</v>
@@ -3800,7 +3806,7 @@
         <v>34.46</v>
       </c>
       <c r="G43" s="10" t="n">
-        <v>19.33</v>
+        <v>20.02</v>
       </c>
       <c r="H43" s="10" t="n">
         <v>15.37</v>
@@ -3834,7 +3840,7 @@
         <v>5</v>
       </c>
       <c r="U43" s="10" t="n">
-        <v>3.92</v>
+        <v>3.74</v>
       </c>
       <c r="V43" s="10" t="n">
         <v>3.24</v>
@@ -3853,7 +3859,7 @@
         <v>19.14</v>
       </c>
       <c r="AB43" s="12" t="n">
-        <v>22.16</v>
+        <v>20.88</v>
       </c>
       <c r="AC43" s="12" t="n">
         <v>23.09</v>
@@ -3901,7 +3907,7 @@
         <v>36.3</v>
       </c>
       <c r="G44" s="10" t="n">
-        <v>34.97</v>
+        <v>35.18</v>
       </c>
       <c r="H44" s="10" t="n">
         <v>23.98</v>
@@ -3935,7 +3941,7 @@
         <v>6.43</v>
       </c>
       <c r="U44" s="10" t="n">
-        <v>7.34</v>
+        <v>7.18</v>
       </c>
       <c r="V44" s="10" t="n">
         <v>5.93</v>
@@ -3954,7 +3960,7 @@
         <v>19.2</v>
       </c>
       <c r="AB44" s="12" t="n">
-        <v>22.85</v>
+        <v>22.12</v>
       </c>
       <c r="AC44" s="12" t="n">
         <v>27.37</v>
@@ -4000,7 +4006,7 @@
         <v>41.99</v>
       </c>
       <c r="G45" s="10" t="n">
-        <v>76.75</v>
+        <v>109.94</v>
       </c>
       <c r="H45" s="10" t="n">
         <v>34.17</v>
@@ -4034,7 +4040,7 @@
         <v>2.1</v>
       </c>
       <c r="U45" s="10" t="n">
-        <v>2.99</v>
+        <v>2.79</v>
       </c>
       <c r="V45" s="10" t="n">
         <v>2.86</v>
@@ -4053,7 +4059,7 @@
         <v>6.6</v>
       </c>
       <c r="AB45" s="12" t="n">
-        <v>3.93</v>
+        <v>2.68</v>
       </c>
       <c r="AC45" s="12" t="n">
         <v>8.550000000000001</v>
@@ -4101,7 +4107,7 @@
         <v>26.64</v>
       </c>
       <c r="G46" s="10" t="n">
-        <v>12.23</v>
+        <v>12.59</v>
       </c>
       <c r="H46" s="10" t="n">
         <v>9.48</v>
@@ -4135,7 +4141,7 @@
         <v>6.66</v>
       </c>
       <c r="U46" s="10" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="V46" s="10" t="n">
         <v>2.16</v>
@@ -4154,7 +4160,7 @@
         <v>30.05</v>
       </c>
       <c r="AB46" s="12" t="n">
-        <v>24.88</v>
+        <v>24.25</v>
       </c>
       <c r="AC46" s="12" t="n">
         <v>25.43</v>
@@ -5144,7 +5150,7 @@
         <v>36.3</v>
       </c>
       <c r="G61" s="15" t="n">
-        <v>34.97</v>
+        <v>35.18</v>
       </c>
       <c r="H61" s="15" t="n">
         <v>23.98</v>
@@ -5178,7 +5184,7 @@
         <v>6.09</v>
       </c>
       <c r="U61" s="15" t="n">
-        <v>3.92</v>
+        <v>3.74</v>
       </c>
       <c r="V61" s="15" t="n">
         <v>3.24</v>
@@ -5197,7 +5203,7 @@
         <v>19.14</v>
       </c>
       <c r="AB61" s="16" t="n">
-        <v>22.16</v>
+        <v>20.88</v>
       </c>
       <c r="AC61" s="16" t="n">
         <v>23.09</v>
@@ -5772,7 +5778,7 @@
         <v>4.93</v>
       </c>
       <c r="U67" s="15" t="n">
-        <v>3.84</v>
+        <v>3.75</v>
       </c>
       <c r="V67" s="15" t="n">
         <v>3.35</v>
@@ -5889,7 +5895,7 @@
         <v>47.5</v>
       </c>
       <c r="G71" s="10" t="n">
-        <v>7.17</v>
+        <v>7.23</v>
       </c>
       <c r="H71" s="10" t="n">
         <v>6.33</v>
@@ -5923,7 +5929,7 @@
         <v>2.61</v>
       </c>
       <c r="U71" s="10" t="n">
-        <v>1.85</v>
+        <v>0.9</v>
       </c>
       <c r="V71" s="10" t="n">
         <v>1.45</v>
@@ -5942,7 +5948,7 @@
         <v>5.74</v>
       </c>
       <c r="AB71" s="12" t="n">
-        <v>29.37</v>
+        <v>18.21</v>
       </c>
       <c r="AC71" s="12" t="n">
         <v>25.62</v>
@@ -5990,7 +5996,7 @@
         <v>13.73</v>
       </c>
       <c r="G72" s="10" t="n">
-        <v>8.32</v>
+        <v>8.75</v>
       </c>
       <c r="H72" s="10" t="n">
         <v>8.140000000000001</v>
@@ -6024,7 +6030,7 @@
         <v>0.77</v>
       </c>
       <c r="U72" s="10" t="n">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="V72" s="10" t="n">
         <v>0.61</v>
@@ -6043,7 +6049,7 @@
         <v>5.71</v>
       </c>
       <c r="AB72" s="12" t="n">
-        <v>7.93</v>
+        <v>7.49</v>
       </c>
       <c r="AC72" s="12" t="n">
         <v>7.68</v>
@@ -6172,7 +6178,7 @@
         <v>8.390000000000001</v>
       </c>
       <c r="G74" s="10" t="n">
-        <v>5.56</v>
+        <v>4.21</v>
       </c>
       <c r="H74" s="10" t="n">
         <v>4.57</v>
@@ -6206,7 +6212,7 @@
         <v>0.92</v>
       </c>
       <c r="U74" s="10" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="V74" s="10" t="n">
         <v>0.53</v>
@@ -6225,7 +6231,7 @@
         <v>11.66</v>
       </c>
       <c r="AB74" s="12" t="n">
-        <v>11.18</v>
+        <v>15.39</v>
       </c>
       <c r="AC74" s="12" t="n">
         <v>12.24</v>
@@ -7378,7 +7384,7 @@
         <v>8.390000000000001</v>
       </c>
       <c r="G90" s="15" t="n">
-        <v>7.17</v>
+        <v>7.23</v>
       </c>
       <c r="H90" s="15" t="n">
         <v>6.33</v>
@@ -7412,7 +7418,7 @@
         <v>0.66</v>
       </c>
       <c r="U90" s="15" t="n">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="V90" s="15" t="n">
         <v>0.61</v>
@@ -7431,7 +7437,7 @@
         <v>7.02</v>
       </c>
       <c r="AB90" s="16" t="n">
-        <v>11.18</v>
+        <v>15.39</v>
       </c>
       <c r="AC90" s="16" t="n">
         <v>12.24</v>
@@ -7911,7 +7917,7 @@
         <v>1.48</v>
       </c>
       <c r="U95" s="15" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="V95" s="15" t="n">
         <v>1.61</v>
@@ -7932,7 +7938,7 @@
         <v>10.49</v>
       </c>
       <c r="AB95" s="16" t="n">
-        <v>12.16</v>
+        <v>14.02</v>
       </c>
       <c r="AC95" s="16" t="n">
         <v>15.14</v>
@@ -8095,7 +8101,7 @@
         <v>37.73</v>
       </c>
       <c r="J2" s="9" t="n">
-        <v>11.7</v>
+        <v>11.58</v>
       </c>
       <c r="K2" s="9" t="n">
         <v>10.05</v>
@@ -8137,7 +8143,7 @@
         <v>27.94</v>
       </c>
       <c r="J3" s="9" t="n">
-        <v>10.65</v>
+        <v>10.2</v>
       </c>
       <c r="K3" s="9" t="n">
         <v>10.51</v>
@@ -8177,7 +8183,7 @@
         <v>37.73</v>
       </c>
       <c r="J4" s="9" t="n">
-        <v>15.65</v>
+        <v>17.39</v>
       </c>
       <c r="K4" s="9" t="n">
         <v>10.88</v>
@@ -8219,7 +8225,7 @@
         <v>13.27</v>
       </c>
       <c r="J5" s="9" t="n">
-        <v>5.11</v>
+        <v>4.73</v>
       </c>
       <c r="K5" s="9" t="n">
         <v>4.38</v>
@@ -8257,7 +8263,7 @@
         <v>10.3</v>
       </c>
       <c r="J6" s="9" t="n">
-        <v>5.39</v>
+        <v>5.31</v>
       </c>
       <c r="K6" s="9" t="n">
         <v>5.29</v>
@@ -8296,7 +8302,9 @@
       <c r="I7" s="9" t="n">
         <v>36.95</v>
       </c>
-      <c r="J7" s="9" t="n"/>
+      <c r="J7" s="9" t="n">
+        <v>6.37</v>
+      </c>
       <c r="K7" s="9" t="n"/>
       <c r="L7" s="9" t="n"/>
     </row>
@@ -8803,7 +8811,7 @@
         <v>32.18</v>
       </c>
       <c r="J19" s="9" t="n">
-        <v>27.64</v>
+        <v>27.15</v>
       </c>
       <c r="K19" s="9" t="n">
         <v>22.6</v>
@@ -8847,7 +8855,7 @@
         <v>18.39</v>
       </c>
       <c r="J20" s="9" t="n">
-        <v>10.98</v>
+        <v>10.88</v>
       </c>
       <c r="K20" s="9" t="n">
         <v>8.19</v>
@@ -8887,7 +8895,7 @@
         <v>20.62</v>
       </c>
       <c r="J21" s="9" t="n">
-        <v>16.62</v>
+        <v>16.65</v>
       </c>
       <c r="K21" s="9" t="n">
         <v>10.27</v>
@@ -8929,7 +8937,7 @@
         <v>14.78</v>
       </c>
       <c r="J22" s="9" t="n">
-        <v>7.51</v>
+        <v>7.77</v>
       </c>
       <c r="K22" s="9" t="n">
         <v>6.32</v>
@@ -8973,7 +8981,7 @@
         <v>13.58</v>
       </c>
       <c r="J23" s="9" t="n">
-        <v>5.92</v>
+        <v>5.02</v>
       </c>
       <c r="K23" s="9" t="n">
         <v>4.98</v>
@@ -9017,7 +9025,7 @@
         <v>59.99</v>
       </c>
       <c r="J24" s="9" t="n">
-        <v>43.17</v>
+        <v>46.33</v>
       </c>
       <c r="K24" s="9" t="n">
         <v>24.08</v>
@@ -9061,7 +9069,7 @@
         <v>34.46</v>
       </c>
       <c r="J25" s="9" t="n">
-        <v>19.33</v>
+        <v>20.02</v>
       </c>
       <c r="K25" s="9" t="n">
         <v>15.37</v>
@@ -9105,7 +9113,7 @@
         <v>36.3</v>
       </c>
       <c r="J26" s="9" t="n">
-        <v>34.97</v>
+        <v>35.18</v>
       </c>
       <c r="K26" s="9" t="n">
         <v>23.98</v>
@@ -9147,7 +9155,7 @@
         <v>41.99</v>
       </c>
       <c r="J27" s="9" t="n">
-        <v>76.75</v>
+        <v>109.94</v>
       </c>
       <c r="K27" s="9" t="n">
         <v>34.17</v>
@@ -9191,7 +9199,7 @@
         <v>26.64</v>
       </c>
       <c r="J28" s="9" t="n">
-        <v>12.23</v>
+        <v>12.59</v>
       </c>
       <c r="K28" s="9" t="n">
         <v>9.48</v>
@@ -9631,7 +9639,7 @@
         <v>47.5</v>
       </c>
       <c r="J38" s="9" t="n">
-        <v>7.17</v>
+        <v>7.23</v>
       </c>
       <c r="K38" s="9" t="n">
         <v>6.33</v>
@@ -9675,7 +9683,7 @@
         <v>13.73</v>
       </c>
       <c r="J39" s="9" t="n">
-        <v>8.32</v>
+        <v>8.75</v>
       </c>
       <c r="K39" s="9" t="n">
         <v>8.140000000000001</v>
@@ -10107,7 +10115,7 @@
         <v>8.390000000000001</v>
       </c>
       <c r="J49" s="9" t="n">
-        <v>5.56</v>
+        <v>4.21</v>
       </c>
       <c r="K49" s="9" t="n">
         <v>4.57</v>
@@ -12473,7 +12481,7 @@
         <v>5.72</v>
       </c>
       <c r="J2" s="9" t="n">
-        <v>3.07</v>
+        <v>3.2</v>
       </c>
       <c r="K2" s="9" t="n">
         <v>2.44</v>
@@ -12517,7 +12525,7 @@
         <v>5.64</v>
       </c>
       <c r="J3" s="9" t="n">
-        <v>2.48</v>
+        <v>2.42</v>
       </c>
       <c r="K3" s="9" t="n">
         <v>2</v>
@@ -12561,7 +12569,7 @@
         <v>4.96</v>
       </c>
       <c r="J4" s="9" t="n">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="K4" s="9" t="n">
         <v>2.38</v>
@@ -12605,7 +12613,7 @@
         <v>2.17</v>
       </c>
       <c r="J5" s="9" t="n">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="K5" s="9" t="n">
         <v>0.95</v>
@@ -12643,7 +12651,7 @@
         <v>2.35</v>
       </c>
       <c r="J6" s="9" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="K6" s="9" t="n">
         <v>0.95</v>
@@ -12686,7 +12694,9 @@
       <c r="I7" s="9" t="n">
         <v>2.84</v>
       </c>
-      <c r="J7" s="9" t="n"/>
+      <c r="J7" s="9" t="n">
+        <v>1.46</v>
+      </c>
       <c r="K7" s="9" t="n"/>
       <c r="L7" s="9" t="n"/>
     </row>
@@ -13203,7 +13213,7 @@
         <v>10.52</v>
       </c>
       <c r="J19" s="9" t="n">
-        <v>9.4</v>
+        <v>9.41</v>
       </c>
       <c r="K19" s="9" t="n">
         <v>7.68</v>
@@ -13247,7 +13257,7 @@
         <v>6.21</v>
       </c>
       <c r="J20" s="9" t="n">
-        <v>2.26</v>
+        <v>2.66</v>
       </c>
       <c r="K20" s="9" t="n">
         <v>1.77</v>
@@ -13291,7 +13301,7 @@
         <v>6.44</v>
       </c>
       <c r="J21" s="9" t="n">
-        <v>4.19</v>
+        <v>4.16</v>
       </c>
       <c r="K21" s="9" t="n">
         <v>2.98</v>
@@ -13335,7 +13345,7 @@
         <v>2.59</v>
       </c>
       <c r="J22" s="9" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="K22" s="9" t="n">
         <v>1.12</v>
@@ -13379,7 +13389,7 @@
         <v>2.93</v>
       </c>
       <c r="J23" s="9" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="K23" s="9" t="n">
         <v>1.03</v>
@@ -13423,7 +13433,7 @@
         <v>6.09</v>
       </c>
       <c r="J24" s="9" t="n">
-        <v>5.26</v>
+        <v>5.2</v>
       </c>
       <c r="K24" s="9" t="n">
         <v>4.54</v>
@@ -13467,7 +13477,7 @@
         <v>5</v>
       </c>
       <c r="J25" s="9" t="n">
-        <v>3.92</v>
+        <v>3.74</v>
       </c>
       <c r="K25" s="9" t="n">
         <v>3.24</v>
@@ -13511,7 +13521,7 @@
         <v>6.43</v>
       </c>
       <c r="J26" s="9" t="n">
-        <v>7.34</v>
+        <v>7.18</v>
       </c>
       <c r="K26" s="9" t="n">
         <v>5.93</v>
@@ -13555,7 +13565,7 @@
         <v>2.1</v>
       </c>
       <c r="J27" s="9" t="n">
-        <v>2.99</v>
+        <v>2.79</v>
       </c>
       <c r="K27" s="9" t="n">
         <v>2.86</v>
@@ -13599,7 +13609,7 @@
         <v>6.66</v>
       </c>
       <c r="J28" s="9" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="K28" s="9" t="n">
         <v>2.16</v>
@@ -14039,7 +14049,7 @@
         <v>2.61</v>
       </c>
       <c r="J38" s="9" t="n">
-        <v>1.85</v>
+        <v>0.9</v>
       </c>
       <c r="K38" s="9" t="n">
         <v>1.45</v>
@@ -14083,7 +14093,7 @@
         <v>0.77</v>
       </c>
       <c r="J39" s="9" t="n">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="K39" s="9" t="n">
         <v>0.61</v>
@@ -14519,7 +14529,7 @@
         <v>0.92</v>
       </c>
       <c r="J49" s="9" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="K49" s="9" t="n">
         <v>0.53</v>
@@ -14777,7 +14787,7 @@
         <v>18.82</v>
       </c>
       <c r="J2" s="11" t="n">
-        <v>29.54</v>
+        <v>30.55</v>
       </c>
       <c r="K2" s="11" t="n">
         <v>27.1</v>
@@ -14821,7 +14831,7 @@
         <v>22.59</v>
       </c>
       <c r="J3" s="11" t="n">
-        <v>26.32</v>
+        <v>27.15</v>
       </c>
       <c r="K3" s="11" t="n">
         <v>21.08</v>
@@ -14865,7 +14875,7 @@
         <v>13.74</v>
       </c>
       <c r="J4" s="11" t="n">
-        <v>21.59</v>
+        <v>19.97</v>
       </c>
       <c r="K4" s="11" t="n">
         <v>24.58</v>
@@ -14909,7 +14919,7 @@
         <v>17.78</v>
       </c>
       <c r="J5" s="11" t="n">
-        <v>24.84</v>
+        <v>27.86</v>
       </c>
       <c r="K5" s="11" t="n">
         <v>23.73</v>
@@ -14953,7 +14963,7 @@
         <v>32.19</v>
       </c>
       <c r="J6" s="11" t="n">
-        <v>23.73</v>
+        <v>24.44</v>
       </c>
       <c r="K6" s="11" t="n">
         <v>19.63</v>
@@ -14996,7 +15006,9 @@
       <c r="I7" s="11" t="n">
         <v>10.15</v>
       </c>
-      <c r="J7" s="11" t="n"/>
+      <c r="J7" s="11" t="n">
+        <v>24.85</v>
+      </c>
       <c r="K7" s="11" t="n"/>
       <c r="L7" s="11" t="n"/>
     </row>
@@ -15517,7 +15529,7 @@
         <v>33.73</v>
       </c>
       <c r="J19" s="11" t="n">
-        <v>37.42</v>
+        <v>38.12</v>
       </c>
       <c r="K19" s="11" t="n">
         <v>37.39</v>
@@ -15561,7 +15573,7 @@
         <v>41.36</v>
       </c>
       <c r="J20" s="11" t="n">
-        <v>22.94</v>
+        <v>25.25</v>
       </c>
       <c r="K20" s="11" t="n">
         <v>24.25</v>
@@ -15605,7 +15617,7 @@
         <v>36.6</v>
       </c>
       <c r="J21" s="11" t="n">
-        <v>28.85</v>
+        <v>28.77</v>
       </c>
       <c r="K21" s="11" t="n">
         <v>33.88</v>
@@ -15649,7 +15661,7 @@
         <v>19.3</v>
       </c>
       <c r="J22" s="11" t="n">
-        <v>18.94</v>
+        <v>18.68</v>
       </c>
       <c r="K22" s="11" t="n">
         <v>19.16</v>
@@ -15693,7 +15705,7 @@
         <v>24.23</v>
       </c>
       <c r="J23" s="11" t="n">
-        <v>24.74</v>
+        <v>29.46</v>
       </c>
       <c r="K23" s="11" t="n">
         <v>23.13</v>
@@ -15737,7 +15749,7 @@
         <v>10.51</v>
       </c>
       <c r="J24" s="11" t="n">
-        <v>12.76</v>
+        <v>11.81</v>
       </c>
       <c r="K24" s="11" t="n">
         <v>20.25</v>
@@ -15781,7 +15793,7 @@
         <v>19.14</v>
       </c>
       <c r="J25" s="11" t="n">
-        <v>22.16</v>
+        <v>20.88</v>
       </c>
       <c r="K25" s="11" t="n">
         <v>23.09</v>
@@ -15825,7 +15837,7 @@
         <v>19.2</v>
       </c>
       <c r="J26" s="11" t="n">
-        <v>22.85</v>
+        <v>22.12</v>
       </c>
       <c r="K26" s="11" t="n">
         <v>27.37</v>
@@ -15869,7 +15881,7 @@
         <v>6.6</v>
       </c>
       <c r="J27" s="11" t="n">
-        <v>3.93</v>
+        <v>2.68</v>
       </c>
       <c r="K27" s="11" t="n">
         <v>8.550000000000001</v>
@@ -15913,7 +15925,7 @@
         <v>30.05</v>
       </c>
       <c r="J28" s="11" t="n">
-        <v>24.88</v>
+        <v>24.25</v>
       </c>
       <c r="K28" s="11" t="n">
         <v>25.43</v>
@@ -16353,7 +16365,7 @@
         <v>5.74</v>
       </c>
       <c r="J38" s="11" t="n">
-        <v>29.37</v>
+        <v>18.21</v>
       </c>
       <c r="K38" s="11" t="n">
         <v>25.62</v>
@@ -16397,7 +16409,7 @@
         <v>5.71</v>
       </c>
       <c r="J39" s="11" t="n">
-        <v>7.93</v>
+        <v>7.49</v>
       </c>
       <c r="K39" s="11" t="n">
         <v>7.68</v>
@@ -16833,7 +16845,7 @@
         <v>11.66</v>
       </c>
       <c r="J49" s="11" t="n">
-        <v>11.18</v>
+        <v>15.39</v>
       </c>
       <c r="K49" s="11" t="n">
         <v>12.24</v>
@@ -19742,14 +19754,14 @@
         <v>11996718253433.27</v>
       </c>
       <c r="M6" s="17" t="n">
-        <v>11.7</v>
+        <v>11.58</v>
       </c>
       <c r="N6" s="17" t="n"/>
       <c r="O6" s="17" t="n">
-        <v>3.07</v>
+        <v>3.2</v>
       </c>
       <c r="P6" s="17" t="n">
-        <v>29.54</v>
+        <v>30.55</v>
       </c>
       <c r="Q6" s="17" t="n">
         <v>1.49</v>
@@ -20237,14 +20249,14 @@
         <v>8040572283234.132</v>
       </c>
       <c r="M13" s="17" t="n">
-        <v>10.65</v>
+        <v>10.2</v>
       </c>
       <c r="N13" s="17" t="n"/>
       <c r="O13" s="17" t="n">
-        <v>2.48</v>
+        <v>2.42</v>
       </c>
       <c r="P13" s="17" t="n">
-        <v>26.32</v>
+        <v>27.15</v>
       </c>
       <c r="Q13" s="17" t="n">
         <v>1.26</v>
@@ -20730,14 +20742,14 @@
         <v>5153154643491.666</v>
       </c>
       <c r="M20" s="17" t="n">
-        <v>15.65</v>
+        <v>17.39</v>
       </c>
       <c r="N20" s="17" t="n"/>
       <c r="O20" s="17" t="n">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="P20" s="17" t="n">
-        <v>21.59</v>
+        <v>19.97</v>
       </c>
       <c r="Q20" s="17" t="n">
         <v>1.23</v>
@@ -21227,14 +21239,14 @@
         <v>16271603322338.4</v>
       </c>
       <c r="M27" s="17" t="n">
-        <v>5.11</v>
+        <v>4.73</v>
       </c>
       <c r="N27" s="17" t="n"/>
       <c r="O27" s="17" t="n">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="P27" s="17" t="n">
-        <v>24.84</v>
+        <v>27.86</v>
       </c>
       <c r="Q27" s="17" t="n">
         <v>0.54</v>
@@ -21696,14 +21708,14 @@
         <v>1375864481019.893</v>
       </c>
       <c r="M34" s="17" t="n">
-        <v>5.39</v>
+        <v>5.31</v>
       </c>
       <c r="N34" s="17" t="n"/>
       <c r="O34" s="17" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="P34" s="17" t="n">
-        <v>23.73</v>
+        <v>24.44</v>
       </c>
       <c r="Q34" s="17" t="n">
         <v>1.18</v>
@@ -22180,10 +22192,16 @@
       </c>
       <c r="K41" s="18" t="n"/>
       <c r="L41" s="18" t="n"/>
-      <c r="M41" s="17" t="n"/>
+      <c r="M41" s="17" t="n">
+        <v>6.37</v>
+      </c>
       <c r="N41" s="17" t="n"/>
-      <c r="O41" s="17" t="n"/>
-      <c r="P41" s="17" t="n"/>
+      <c r="O41" s="17" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="P41" s="17" t="n">
+        <v>24.85</v>
+      </c>
       <c r="Q41" s="17" t="n"/>
       <c r="R41" s="17" t="inlineStr">
         <is>
@@ -28073,14 +28091,14 @@
         <v>1009130437230.669</v>
       </c>
       <c r="M125" s="17" t="n">
-        <v>27.64</v>
+        <v>27.15</v>
       </c>
       <c r="N125" s="17" t="n"/>
       <c r="O125" s="17" t="n">
-        <v>9.4</v>
+        <v>9.41</v>
       </c>
       <c r="P125" s="17" t="n">
-        <v>37.42</v>
+        <v>38.12</v>
       </c>
       <c r="Q125" s="17" t="n">
         <v>3.99</v>
@@ -28572,14 +28590,14 @@
         <v>615574991482</v>
       </c>
       <c r="M132" s="17" t="n">
-        <v>10.98</v>
+        <v>10.88</v>
       </c>
       <c r="N132" s="17" t="n"/>
       <c r="O132" s="17" t="n">
-        <v>2.26</v>
+        <v>2.66</v>
       </c>
       <c r="P132" s="17" t="n">
-        <v>22.94</v>
+        <v>25.25</v>
       </c>
       <c r="Q132" s="17" t="n">
         <v>2.34</v>
@@ -29065,14 +29083,14 @@
         <v>743585229863.8025</v>
       </c>
       <c r="M139" s="17" t="n">
-        <v>16.62</v>
+        <v>16.65</v>
       </c>
       <c r="N139" s="17" t="n"/>
       <c r="O139" s="17" t="n">
-        <v>4.19</v>
+        <v>4.16</v>
       </c>
       <c r="P139" s="17" t="n">
-        <v>28.85</v>
+        <v>28.77</v>
       </c>
       <c r="Q139" s="17" t="n">
         <v>1.98</v>
@@ -29562,14 +29580,14 @@
         <v>680694234169.2651</v>
       </c>
       <c r="M146" s="17" t="n">
-        <v>7.51</v>
+        <v>7.77</v>
       </c>
       <c r="N146" s="17" t="n"/>
       <c r="O146" s="17" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P146" s="17" t="n">
-        <v>18.94</v>
+        <v>18.68</v>
       </c>
       <c r="Q146" s="17" t="n">
         <v>0.95</v>
@@ -30061,14 +30079,14 @@
         <v>331992443278</v>
       </c>
       <c r="M153" s="17" t="n">
-        <v>5.92</v>
+        <v>5.02</v>
       </c>
       <c r="N153" s="17" t="n"/>
       <c r="O153" s="17" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="P153" s="17" t="n">
-        <v>24.74</v>
+        <v>29.46</v>
       </c>
       <c r="Q153" s="17" t="n">
         <v>0.51</v>
@@ -30560,14 +30578,14 @@
         <v>2007652633721.282</v>
       </c>
       <c r="M160" s="17" t="n">
-        <v>43.17</v>
+        <v>46.33</v>
       </c>
       <c r="N160" s="17" t="n"/>
       <c r="O160" s="17" t="n">
-        <v>5.26</v>
+        <v>5.2</v>
       </c>
       <c r="P160" s="17" t="n">
-        <v>12.76</v>
+        <v>11.81</v>
       </c>
       <c r="Q160" s="17" t="n">
         <v>1.99</v>
@@ -31059,14 +31077,14 @@
         <v>11640307256887.55</v>
       </c>
       <c r="M167" s="17" t="n">
-        <v>19.33</v>
+        <v>20.02</v>
       </c>
       <c r="N167" s="17" t="n"/>
       <c r="O167" s="17" t="n">
-        <v>3.92</v>
+        <v>3.74</v>
       </c>
       <c r="P167" s="17" t="n">
-        <v>22.16</v>
+        <v>20.88</v>
       </c>
       <c r="Q167" s="17" t="n">
         <v>1.42</v>
@@ -31558,14 +31576,14 @@
         <v>1708001170727.462</v>
       </c>
       <c r="M174" s="17" t="n">
-        <v>34.97</v>
+        <v>35.18</v>
       </c>
       <c r="N174" s="17" t="n"/>
       <c r="O174" s="17" t="n">
-        <v>7.34</v>
+        <v>7.18</v>
       </c>
       <c r="P174" s="17" t="n">
-        <v>22.85</v>
+        <v>22.12</v>
       </c>
       <c r="Q174" s="17" t="n">
         <v>2.43</v>
@@ -32055,14 +32073,14 @@
         <v>4946595644964.042</v>
       </c>
       <c r="M181" s="17" t="n">
-        <v>76.75</v>
+        <v>109.94</v>
       </c>
       <c r="N181" s="17" t="n"/>
       <c r="O181" s="17" t="n">
-        <v>2.99</v>
+        <v>2.79</v>
       </c>
       <c r="P181" s="17" t="n">
-        <v>3.93</v>
+        <v>2.68</v>
       </c>
       <c r="Q181" s="17" t="n">
         <v>3.28</v>
@@ -32554,14 +32572,14 @@
         <v>3873726429965.954</v>
       </c>
       <c r="M188" s="17" t="n">
-        <v>12.23</v>
+        <v>12.59</v>
       </c>
       <c r="N188" s="17" t="n"/>
       <c r="O188" s="17" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="P188" s="17" t="n">
-        <v>24.88</v>
+        <v>24.25</v>
       </c>
       <c r="Q188" s="17" t="n">
         <v>1.57</v>
@@ -37544,14 +37562,14 @@
         <v>2391162650434.556</v>
       </c>
       <c r="M258" s="17" t="n">
-        <v>7.17</v>
+        <v>7.23</v>
       </c>
       <c r="N258" s="17" t="n"/>
       <c r="O258" s="17" t="n">
-        <v>1.85</v>
+        <v>0.9</v>
       </c>
       <c r="P258" s="17" t="n">
-        <v>29.37</v>
+        <v>18.21</v>
       </c>
       <c r="Q258" s="17" t="n">
         <v>0.47</v>
@@ -38043,14 +38061,14 @@
         <v>7585792678930.512</v>
       </c>
       <c r="M265" s="17" t="n">
-        <v>8.32</v>
+        <v>8.75</v>
       </c>
       <c r="N265" s="17" t="n"/>
       <c r="O265" s="17" t="n">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="P265" s="17" t="n">
-        <v>7.93</v>
+        <v>7.49</v>
       </c>
       <c r="Q265" s="17" t="n">
         <v>0.51</v>
@@ -42997,14 +43015,14 @@
         <v>328971474869.7184</v>
       </c>
       <c r="M335" s="17" t="n">
-        <v>5.56</v>
+        <v>4.21</v>
       </c>
       <c r="N335" s="17" t="n"/>
       <c r="O335" s="17" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="P335" s="17" t="n">
-        <v>11.18</v>
+        <v>15.39</v>
       </c>
       <c r="Q335" s="17" t="n">
         <v>0.38</v>
@@ -44821,7 +44839,7 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>2026-10-19T06:32:46+09:00</t>
+          <t>2026-10-19T06:47:06+09:00</t>
         </is>
       </c>
     </row>

--- a/telegram_research_dashboard/static/valuation_full.xlsx
+++ b/telegram_research_dashboard/static/valuation_full.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK95"/>
+  <dimension ref="A1:AK96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2849,7 +2849,7 @@
         </is>
       </c>
       <c r="B31" s="8" t="n">
-        <v>1156</v>
+        <v>1153</v>
       </c>
       <c r="C31" s="9" t="n"/>
       <c r="D31" s="9" t="n"/>
@@ -2861,10 +2861,10 @@
       </c>
       <c r="G31" s="10" t="n"/>
       <c r="H31" s="10" t="n">
-        <v>17.47</v>
+        <v>17.3</v>
       </c>
       <c r="I31" s="10" t="n">
-        <v>15.74</v>
+        <v>15.58</v>
       </c>
       <c r="J31" s="9" t="n"/>
       <c r="K31" s="9" t="n">
@@ -2893,10 +2893,10 @@
         <v>1.39</v>
       </c>
       <c r="V31" s="10" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="W31" s="10" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="X31" s="9" t="n"/>
       <c r="Y31" s="9" t="n">
@@ -2931,10 +2931,10 @@
         <v>0.84</v>
       </c>
       <c r="AJ31" s="10" t="n">
-        <v>0.72</v>
+        <v>0.71</v>
       </c>
       <c r="AK31" s="10" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="32">
@@ -3445,10 +3445,10 @@
       </c>
       <c r="G37" s="13" t="n"/>
       <c r="H37" s="13" t="n">
-        <v>17.47</v>
+        <v>17.3</v>
       </c>
       <c r="I37" s="13" t="n">
-        <v>15.74</v>
+        <v>15.58</v>
       </c>
       <c r="J37" s="13" t="n"/>
       <c r="K37" s="13" t="n">
@@ -3477,10 +3477,10 @@
         <v>1.39</v>
       </c>
       <c r="V37" s="13" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="W37" s="13" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="X37" s="13" t="n"/>
       <c r="Y37" s="13" t="n">
@@ -3515,10 +3515,10 @@
         <v>0.84</v>
       </c>
       <c r="AJ37" s="13" t="n">
-        <v>0.72</v>
+        <v>0.71</v>
       </c>
       <c r="AK37" s="13" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="38">
@@ -3547,7 +3547,7 @@
         <v>10.39</v>
       </c>
       <c r="I38" s="13" t="n">
-        <v>15.74</v>
+        <v>15.58</v>
       </c>
       <c r="J38" s="13" t="n">
         <v>12.48</v>
@@ -5724,2244 +5724,2343 @@
     <row r="67">
       <c r="A67" s="11" t="inlineStr">
         <is>
-          <t>방산 전체 중앙값</t>
+          <t xml:space="preserve">  유럽 중앙값</t>
         </is>
       </c>
       <c r="B67" s="12" t="n"/>
       <c r="C67" s="13" t="n">
-        <v>17.07</v>
+        <v>16.8</v>
       </c>
       <c r="D67" s="13" t="n">
-        <v>18.06</v>
+        <v>20.69</v>
       </c>
       <c r="E67" s="13" t="n">
-        <v>18.02</v>
+        <v>23.63</v>
       </c>
       <c r="F67" s="13" t="n">
-        <v>30.55</v>
+        <v>35.11</v>
       </c>
       <c r="G67" s="13" t="n">
-        <v>22.33</v>
+        <v>26.39</v>
       </c>
       <c r="H67" s="13" t="n">
-        <v>19.52</v>
+        <v>20.62</v>
       </c>
       <c r="I67" s="13" t="n"/>
       <c r="J67" s="13" t="n">
-        <v>12.01</v>
+        <v>9.17</v>
       </c>
       <c r="K67" s="13" t="n">
-        <v>11.28</v>
+        <v>10.71</v>
       </c>
       <c r="L67" s="13" t="n">
-        <v>12.61</v>
+        <v>12.93</v>
       </c>
       <c r="M67" s="13" t="n">
-        <v>16.87</v>
+        <v>19.48</v>
       </c>
       <c r="N67" s="13" t="n"/>
       <c r="O67" s="13" t="n"/>
       <c r="P67" s="13" t="n"/>
       <c r="Q67" s="13" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="R67" s="13" t="n">
-        <v>2.62</v>
+        <v>2.85</v>
       </c>
       <c r="S67" s="13" t="n">
-        <v>3.08</v>
+        <v>3.21</v>
       </c>
       <c r="T67" s="13" t="n">
-        <v>4.93</v>
+        <v>5.47</v>
       </c>
       <c r="U67" s="13" t="n">
-        <v>3.75</v>
+        <v>5.74</v>
       </c>
       <c r="V67" s="13" t="n">
-        <v>3.35</v>
+        <v>5.02</v>
       </c>
       <c r="W67" s="13" t="n"/>
       <c r="X67" s="13" t="n">
-        <v>13.08</v>
+        <v>13.55</v>
       </c>
       <c r="Y67" s="13" t="n">
-        <v>16.75</v>
+        <v>14.02</v>
       </c>
       <c r="Z67" s="13" t="n">
-        <v>18.52</v>
+        <v>15.21</v>
       </c>
       <c r="AA67" s="13" t="n">
-        <v>16.82</v>
+        <v>15.69</v>
       </c>
       <c r="AB67" s="13" t="n">
         <v>18.59</v>
       </c>
       <c r="AC67" s="13" t="n">
-        <v>20.36</v>
+        <v>19.75</v>
       </c>
       <c r="AD67" s="13" t="n"/>
       <c r="AE67" s="13" t="n">
         <v>1.25</v>
       </c>
       <c r="AF67" s="13" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AG67" s="13" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AH67" s="13" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AI67" s="13" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AJ67" s="13" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AK67" s="13" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="11" t="inlineStr">
+        <is>
+          <t>방산 전체 중앙값</t>
+        </is>
+      </c>
+      <c r="B68" s="12" t="n"/>
+      <c r="C68" s="13" t="n">
+        <v>17.07</v>
+      </c>
+      <c r="D68" s="13" t="n">
+        <v>18.06</v>
+      </c>
+      <c r="E68" s="13" t="n">
+        <v>18.02</v>
+      </c>
+      <c r="F68" s="13" t="n">
+        <v>30.55</v>
+      </c>
+      <c r="G68" s="13" t="n">
+        <v>22.33</v>
+      </c>
+      <c r="H68" s="13" t="n">
+        <v>19.52</v>
+      </c>
+      <c r="I68" s="13" t="n"/>
+      <c r="J68" s="13" t="n">
+        <v>12.01</v>
+      </c>
+      <c r="K68" s="13" t="n">
+        <v>11.28</v>
+      </c>
+      <c r="L68" s="13" t="n">
+        <v>12.61</v>
+      </c>
+      <c r="M68" s="13" t="n">
+        <v>16.87</v>
+      </c>
+      <c r="N68" s="13" t="n"/>
+      <c r="O68" s="13" t="n"/>
+      <c r="P68" s="13" t="n"/>
+      <c r="Q68" s="13" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="R68" s="13" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="S68" s="13" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="T68" s="13" t="n">
+        <v>4.93</v>
+      </c>
+      <c r="U68" s="13" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="V68" s="13" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="W68" s="13" t="n"/>
+      <c r="X68" s="13" t="n">
+        <v>13.08</v>
+      </c>
+      <c r="Y68" s="13" t="n">
+        <v>16.75</v>
+      </c>
+      <c r="Z68" s="13" t="n">
+        <v>18.52</v>
+      </c>
+      <c r="AA68" s="13" t="n">
+        <v>16.82</v>
+      </c>
+      <c r="AB68" s="13" t="n">
+        <v>18.59</v>
+      </c>
+      <c r="AC68" s="13" t="n">
+        <v>20.36</v>
+      </c>
+      <c r="AD68" s="13" t="n"/>
+      <c r="AE68" s="13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF68" s="13" t="n">
         <v>1.39</v>
       </c>
-      <c r="AG67" s="13" t="n">
+      <c r="AG68" s="13" t="n">
         <v>1.48</v>
       </c>
-      <c r="AH67" s="13" t="n">
+      <c r="AH68" s="13" t="n">
         <v>2.04</v>
       </c>
-      <c r="AI67" s="13" t="n">
+      <c r="AI68" s="13" t="n">
         <v>1.71</v>
       </c>
-      <c r="AJ67" s="13" t="n">
+      <c r="AJ68" s="13" t="n">
         <v>1.59</v>
       </c>
-      <c r="AK67" s="13" t="n"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="4" t="inlineStr">
+      <c r="AK68" s="13" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="inlineStr">
         <is>
           <t>건설기계</t>
         </is>
       </c>
-      <c r="B69" s="5" t="n"/>
-      <c r="C69" s="5" t="n"/>
-      <c r="D69" s="5" t="n"/>
-      <c r="E69" s="5" t="n"/>
-      <c r="F69" s="5" t="n"/>
-      <c r="G69" s="5" t="n"/>
-      <c r="H69" s="5" t="n"/>
-      <c r="I69" s="5" t="n"/>
-      <c r="J69" s="5" t="n"/>
-      <c r="K69" s="5" t="n"/>
-      <c r="L69" s="5" t="n"/>
-      <c r="M69" s="5" t="n"/>
-      <c r="N69" s="5" t="n"/>
-      <c r="O69" s="5" t="n"/>
-      <c r="P69" s="5" t="n"/>
-      <c r="Q69" s="5" t="n"/>
-      <c r="R69" s="5" t="n"/>
-      <c r="S69" s="5" t="n"/>
-      <c r="T69" s="5" t="n"/>
-      <c r="U69" s="5" t="n"/>
-      <c r="V69" s="5" t="n"/>
-      <c r="W69" s="5" t="n"/>
-      <c r="X69" s="5" t="n"/>
-      <c r="Y69" s="5" t="n"/>
-      <c r="Z69" s="5" t="n"/>
-      <c r="AA69" s="5" t="n"/>
-      <c r="AB69" s="5" t="n"/>
-      <c r="AC69" s="5" t="n"/>
-      <c r="AD69" s="5" t="n"/>
-      <c r="AE69" s="5" t="n"/>
-      <c r="AF69" s="5" t="n"/>
-      <c r="AG69" s="5" t="n"/>
-      <c r="AH69" s="5" t="n"/>
-      <c r="AI69" s="5" t="n"/>
-      <c r="AJ69" s="5" t="n"/>
-      <c r="AK69" s="5" t="n"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="6" t="inlineStr">
+      <c r="B70" s="5" t="n"/>
+      <c r="C70" s="5" t="n"/>
+      <c r="D70" s="5" t="n"/>
+      <c r="E70" s="5" t="n"/>
+      <c r="F70" s="5" t="n"/>
+      <c r="G70" s="5" t="n"/>
+      <c r="H70" s="5" t="n"/>
+      <c r="I70" s="5" t="n"/>
+      <c r="J70" s="5" t="n"/>
+      <c r="K70" s="5" t="n"/>
+      <c r="L70" s="5" t="n"/>
+      <c r="M70" s="5" t="n"/>
+      <c r="N70" s="5" t="n"/>
+      <c r="O70" s="5" t="n"/>
+      <c r="P70" s="5" t="n"/>
+      <c r="Q70" s="5" t="n"/>
+      <c r="R70" s="5" t="n"/>
+      <c r="S70" s="5" t="n"/>
+      <c r="T70" s="5" t="n"/>
+      <c r="U70" s="5" t="n"/>
+      <c r="V70" s="5" t="n"/>
+      <c r="W70" s="5" t="n"/>
+      <c r="X70" s="5" t="n"/>
+      <c r="Y70" s="5" t="n"/>
+      <c r="Z70" s="5" t="n"/>
+      <c r="AA70" s="5" t="n"/>
+      <c r="AB70" s="5" t="n"/>
+      <c r="AC70" s="5" t="n"/>
+      <c r="AD70" s="5" t="n"/>
+      <c r="AE70" s="5" t="n"/>
+      <c r="AF70" s="5" t="n"/>
+      <c r="AG70" s="5" t="n"/>
+      <c r="AH70" s="5" t="n"/>
+      <c r="AI70" s="5" t="n"/>
+      <c r="AJ70" s="5" t="n"/>
+      <c r="AK70" s="5" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">  한국</t>
         </is>
       </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    HD건설기계</t>
-        </is>
-      </c>
-      <c r="B71" s="8" t="n">
-        <v>3295</v>
-      </c>
-      <c r="C71" s="9" t="n">
-        <v>10.61</v>
-      </c>
-      <c r="D71" s="9" t="n">
-        <v>7.05</v>
-      </c>
-      <c r="E71" s="9" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="F71" s="9" t="n">
-        <v>47.5</v>
-      </c>
-      <c r="G71" s="10" t="n">
-        <v>7.23</v>
-      </c>
-      <c r="H71" s="10" t="n">
-        <v>6.33</v>
-      </c>
-      <c r="I71" s="10" t="n"/>
-      <c r="J71" s="9" t="n">
-        <v>7.18</v>
-      </c>
-      <c r="K71" s="9" t="n">
-        <v>4.52</v>
-      </c>
-      <c r="L71" s="9" t="n">
-        <v>6.23</v>
-      </c>
-      <c r="M71" s="9" t="n">
-        <v>23.43</v>
-      </c>
-      <c r="N71" s="10" t="n"/>
-      <c r="O71" s="10" t="n"/>
-      <c r="P71" s="10" t="n"/>
-      <c r="Q71" s="9" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="R71" s="9" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="S71" s="9" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="T71" s="9" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="U71" s="10" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="V71" s="10" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="W71" s="10" t="n"/>
-      <c r="X71" s="9" t="n">
-        <v>7.62</v>
-      </c>
-      <c r="Y71" s="9" t="n">
-        <v>9.17</v>
-      </c>
-      <c r="Z71" s="9" t="n">
-        <v>6.18</v>
-      </c>
-      <c r="AA71" s="9" t="n">
-        <v>5.74</v>
-      </c>
-      <c r="AB71" s="10" t="n">
-        <v>18.21</v>
-      </c>
-      <c r="AC71" s="10" t="n">
-        <v>25.62</v>
-      </c>
-      <c r="AD71" s="10" t="n"/>
-      <c r="AE71" s="9" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="AF71" s="9" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="AG71" s="9" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="AH71" s="9" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI71" s="10" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="AJ71" s="10" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="AK71" s="10" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    두산밥캣</t>
+          <t xml:space="preserve">    HD건설기계</t>
         </is>
       </c>
       <c r="B72" s="8" t="n">
-        <v>3633</v>
+        <v>3295</v>
       </c>
       <c r="C72" s="9" t="n">
-        <v>5.38</v>
+        <v>10.61</v>
       </c>
       <c r="D72" s="9" t="n">
-        <v>5.48</v>
+        <v>7.05</v>
       </c>
       <c r="E72" s="9" t="n">
-        <v>7.35</v>
+        <v>10.3</v>
       </c>
       <c r="F72" s="9" t="n">
-        <v>13.73</v>
+        <v>47.5</v>
       </c>
       <c r="G72" s="10" t="n">
-        <v>8.75</v>
+        <v>7.23</v>
       </c>
       <c r="H72" s="10" t="n">
-        <v>8.140000000000001</v>
+        <v>6.33</v>
       </c>
       <c r="I72" s="10" t="n"/>
       <c r="J72" s="9" t="n">
-        <v>3.59</v>
+        <v>7.18</v>
       </c>
       <c r="K72" s="9" t="n">
-        <v>3.14</v>
+        <v>4.52</v>
       </c>
       <c r="L72" s="9" t="n">
-        <v>3.61</v>
+        <v>6.23</v>
       </c>
       <c r="M72" s="9" t="n">
-        <v>5.3</v>
+        <v>23.43</v>
       </c>
       <c r="N72" s="10" t="n"/>
       <c r="O72" s="10" t="n"/>
       <c r="P72" s="10" t="n"/>
       <c r="Q72" s="9" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="R72" s="9" t="n">
-        <v>0.85</v>
+        <v>0.62</v>
       </c>
       <c r="S72" s="9" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="T72" s="9" t="n">
-        <v>0.77</v>
+        <v>2.61</v>
       </c>
       <c r="U72" s="10" t="n">
-        <v>0.63</v>
+        <v>0.9</v>
       </c>
       <c r="V72" s="10" t="n">
-        <v>0.61</v>
+        <v>1.45</v>
       </c>
       <c r="W72" s="10" t="n"/>
       <c r="X72" s="9" t="n">
-        <v>12.82</v>
+        <v>7.62</v>
       </c>
       <c r="Y72" s="9" t="n">
-        <v>16.79</v>
+        <v>9.17</v>
       </c>
       <c r="Z72" s="9" t="n">
-        <v>8.77</v>
+        <v>6.18</v>
       </c>
       <c r="AA72" s="9" t="n">
-        <v>5.71</v>
+        <v>5.74</v>
       </c>
       <c r="AB72" s="10" t="n">
-        <v>7.49</v>
+        <v>18.21</v>
       </c>
       <c r="AC72" s="10" t="n">
-        <v>7.68</v>
+        <v>25.62</v>
       </c>
       <c r="AD72" s="10" t="n"/>
       <c r="AE72" s="9" t="n">
-        <v>0.4</v>
+        <v>0.34</v>
       </c>
       <c r="AF72" s="9" t="n">
-        <v>0.52</v>
+        <v>0.26</v>
       </c>
       <c r="AG72" s="9" t="n">
-        <v>0.48</v>
+        <v>0.3</v>
       </c>
       <c r="AH72" s="9" t="n">
-        <v>0.63</v>
+        <v>1.25</v>
       </c>
       <c r="AI72" s="10" t="n">
-        <v>0.51</v>
+        <v>0.47</v>
       </c>
       <c r="AJ72" s="10" t="n">
-        <v>0.49</v>
+        <v>0.42</v>
       </c>
       <c r="AK72" s="10" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    대동</t>
+          <t xml:space="preserve">    두산밥캣</t>
         </is>
       </c>
       <c r="B73" s="8" t="n">
-        <v>139</v>
+        <v>3633</v>
       </c>
       <c r="C73" s="9" t="n">
-        <v>7.23</v>
+        <v>5.38</v>
       </c>
       <c r="D73" s="9" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="E73" s="9" t="n"/>
-      <c r="F73" s="9" t="n"/>
-      <c r="G73" s="10" t="n"/>
-      <c r="H73" s="10" t="n"/>
+        <v>5.48</v>
+      </c>
+      <c r="E73" s="9" t="n">
+        <v>7.35</v>
+      </c>
+      <c r="F73" s="9" t="n">
+        <v>13.73</v>
+      </c>
+      <c r="G73" s="10" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="H73" s="10" t="n">
+        <v>8.140000000000001</v>
+      </c>
       <c r="I73" s="10" t="n"/>
       <c r="J73" s="9" t="n">
-        <v>6.74</v>
+        <v>3.59</v>
       </c>
       <c r="K73" s="9" t="n">
-        <v>9.57</v>
+        <v>3.14</v>
       </c>
       <c r="L73" s="9" t="n">
-        <v>13.34</v>
+        <v>3.61</v>
       </c>
       <c r="M73" s="9" t="n">
-        <v>14.31</v>
+        <v>5.3</v>
       </c>
       <c r="N73" s="10" t="n"/>
       <c r="O73" s="10" t="n"/>
       <c r="P73" s="10" t="n"/>
       <c r="Q73" s="9" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="R73" s="9" t="n">
-        <v>0.87</v>
+        <v>0.85</v>
       </c>
       <c r="S73" s="9" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="T73" s="9" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="U73" s="10" t="n"/>
-      <c r="V73" s="10" t="n"/>
+        <v>0.77</v>
+      </c>
+      <c r="U73" s="10" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="V73" s="10" t="n">
+        <v>0.61</v>
+      </c>
       <c r="W73" s="10" t="n"/>
       <c r="X73" s="9" t="n">
-        <v>11.21</v>
+        <v>12.82</v>
       </c>
       <c r="Y73" s="9" t="n">
-        <v>4.41</v>
+        <v>16.79</v>
       </c>
       <c r="Z73" s="9" t="n">
-        <v>-6.94</v>
+        <v>8.77</v>
       </c>
       <c r="AA73" s="9" t="n">
-        <v>-3.68</v>
-      </c>
-      <c r="AB73" s="10" t="n"/>
-      <c r="AC73" s="10" t="n"/>
+        <v>5.71</v>
+      </c>
+      <c r="AB73" s="10" t="n">
+        <v>7.49</v>
+      </c>
+      <c r="AC73" s="10" t="n">
+        <v>7.68</v>
+      </c>
       <c r="AD73" s="10" t="n"/>
       <c r="AE73" s="9" t="n">
-        <v>0.19</v>
+        <v>0.4</v>
       </c>
       <c r="AF73" s="9" t="n">
-        <v>0.28</v>
+        <v>0.52</v>
       </c>
       <c r="AG73" s="9" t="n">
-        <v>0.15</v>
+        <v>0.48</v>
       </c>
       <c r="AH73" s="9" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="AI73" s="10" t="n"/>
-      <c r="AJ73" s="10" t="n"/>
+        <v>0.63</v>
+      </c>
+      <c r="AI73" s="10" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="AJ73" s="10" t="n">
+        <v>0.49</v>
+      </c>
       <c r="AK73" s="10" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    진성티이씨</t>
+          <t xml:space="preserve">    대동</t>
         </is>
       </c>
       <c r="B74" s="8" t="n">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="C74" s="9" t="n">
-        <v>5.78</v>
+        <v>7.23</v>
       </c>
       <c r="D74" s="9" t="n">
-        <v>7.46</v>
-      </c>
-      <c r="E74" s="9" t="n">
-        <v>8.359999999999999</v>
-      </c>
-      <c r="F74" s="9" t="n">
-        <v>8.390000000000001</v>
-      </c>
-      <c r="G74" s="10" t="n">
-        <v>4.21</v>
-      </c>
-      <c r="H74" s="10" t="n">
-        <v>4.57</v>
-      </c>
+        <v>22.5</v>
+      </c>
+      <c r="E74" s="9" t="n"/>
+      <c r="F74" s="9" t="n"/>
+      <c r="G74" s="10" t="n"/>
+      <c r="H74" s="10" t="n"/>
       <c r="I74" s="10" t="n"/>
       <c r="J74" s="9" t="n">
-        <v>3.96</v>
+        <v>6.74</v>
       </c>
       <c r="K74" s="9" t="n">
-        <v>3.57</v>
+        <v>9.57</v>
       </c>
       <c r="L74" s="9" t="n">
-        <v>3.52</v>
+        <v>13.34</v>
       </c>
       <c r="M74" s="9" t="n">
-        <v>4.85</v>
+        <v>14.31</v>
       </c>
       <c r="N74" s="10" t="n"/>
       <c r="O74" s="10" t="n"/>
       <c r="P74" s="10" t="n"/>
       <c r="Q74" s="9" t="n">
-        <v>1.25</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="R74" s="9" t="n">
-        <v>0.91</v>
+        <v>0.87</v>
       </c>
       <c r="S74" s="9" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="T74" s="9" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="U74" s="10" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="V74" s="10" t="n">
-        <v>0.53</v>
-      </c>
+        <v>0.54</v>
+      </c>
+      <c r="U74" s="10" t="n"/>
+      <c r="V74" s="10" t="n"/>
       <c r="W74" s="10" t="n"/>
       <c r="X74" s="9" t="n">
-        <v>21.69</v>
+        <v>11.21</v>
       </c>
       <c r="Y74" s="9" t="n">
-        <v>12.86</v>
+        <v>4.41</v>
       </c>
       <c r="Z74" s="9" t="n">
-        <v>8.48</v>
+        <v>-6.94</v>
       </c>
       <c r="AA74" s="9" t="n">
-        <v>11.66</v>
-      </c>
-      <c r="AB74" s="10" t="n">
-        <v>15.39</v>
-      </c>
-      <c r="AC74" s="10" t="n">
-        <v>12.24</v>
-      </c>
+        <v>-3.68</v>
+      </c>
+      <c r="AB74" s="10" t="n"/>
+      <c r="AC74" s="10" t="n"/>
       <c r="AD74" s="10" t="n"/>
       <c r="AE74" s="9" t="n">
-        <v>0.49</v>
+        <v>0.19</v>
       </c>
       <c r="AF74" s="9" t="n">
-        <v>0.44</v>
+        <v>0.28</v>
       </c>
       <c r="AG74" s="9" t="n">
-        <v>0.45</v>
+        <v>0.15</v>
       </c>
       <c r="AH74" s="9" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="AI74" s="10" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="AJ74" s="10" t="n">
-        <v>0.34</v>
-      </c>
+        <v>0.18</v>
+      </c>
+      <c r="AI74" s="10" t="n"/>
+      <c r="AJ74" s="10" t="n"/>
       <c r="AK74" s="10" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    디와이파워</t>
+          <t xml:space="preserve">    진성티이씨</t>
         </is>
       </c>
       <c r="B75" s="8" t="n">
-        <v>88</v>
+        <v>145</v>
       </c>
       <c r="C75" s="9" t="n">
-        <v>7.57</v>
+        <v>5.78</v>
       </c>
       <c r="D75" s="9" t="n">
-        <v>4.95</v>
+        <v>7.46</v>
       </c>
       <c r="E75" s="9" t="n">
-        <v>5.58</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="F75" s="9" t="n">
-        <v>5.89</v>
-      </c>
-      <c r="G75" s="10" t="n"/>
-      <c r="H75" s="10" t="n"/>
+        <v>8.390000000000001</v>
+      </c>
+      <c r="G75" s="10" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="H75" s="10" t="n">
+        <v>4.57</v>
+      </c>
       <c r="I75" s="10" t="n"/>
       <c r="J75" s="9" t="n">
-        <v>2.92</v>
+        <v>3.96</v>
       </c>
       <c r="K75" s="9" t="n">
-        <v>1.93</v>
+        <v>3.57</v>
       </c>
       <c r="L75" s="9" t="n">
-        <v>1.72</v>
+        <v>3.52</v>
       </c>
       <c r="M75" s="9" t="n">
-        <v>1.95</v>
+        <v>4.85</v>
       </c>
       <c r="N75" s="10" t="n"/>
       <c r="O75" s="10" t="n"/>
       <c r="P75" s="10" t="n"/>
       <c r="Q75" s="9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="R75" s="9" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="S75" s="9" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="T75" s="9" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="U75" s="10" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="R75" s="9" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="S75" s="9" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="T75" s="9" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="U75" s="10" t="n"/>
-      <c r="V75" s="10" t="n"/>
+      <c r="V75" s="10" t="n">
+        <v>0.53</v>
+      </c>
       <c r="W75" s="10" t="n"/>
       <c r="X75" s="9" t="n">
-        <v>7.43</v>
+        <v>21.69</v>
       </c>
       <c r="Y75" s="9" t="n">
-        <v>10.9</v>
+        <v>12.86</v>
       </c>
       <c r="Z75" s="9" t="n">
-        <v>7.87</v>
+        <v>8.48</v>
       </c>
       <c r="AA75" s="9" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="AB75" s="10" t="n"/>
-      <c r="AC75" s="10" t="n"/>
+        <v>11.66</v>
+      </c>
+      <c r="AB75" s="10" t="n">
+        <v>15.39</v>
+      </c>
+      <c r="AC75" s="10" t="n">
+        <v>12.24</v>
+      </c>
       <c r="AD75" s="10" t="n"/>
       <c r="AE75" s="9" t="n">
-        <v>0.32</v>
+        <v>0.49</v>
       </c>
       <c r="AF75" s="9" t="n">
-        <v>0.32</v>
+        <v>0.44</v>
       </c>
       <c r="AG75" s="9" t="n">
-        <v>0.32</v>
+        <v>0.45</v>
       </c>
       <c r="AH75" s="9" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="AI75" s="10" t="n"/>
-      <c r="AJ75" s="10" t="n"/>
+        <v>0.59</v>
+      </c>
+      <c r="AI75" s="10" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AJ75" s="10" t="n">
+        <v>0.34</v>
+      </c>
       <c r="AK75" s="10" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    대창단조</t>
+          <t xml:space="preserve">    디와이파워</t>
         </is>
       </c>
       <c r="B76" s="8" t="n">
-        <v>118</v>
+        <v>88</v>
       </c>
       <c r="C76" s="9" t="n">
-        <v>5.71</v>
+        <v>7.57</v>
       </c>
       <c r="D76" s="9" t="n">
-        <v>4.66</v>
+        <v>4.95</v>
       </c>
       <c r="E76" s="9" t="n">
-        <v>3.74</v>
+        <v>5.58</v>
       </c>
       <c r="F76" s="9" t="n">
-        <v>5.53</v>
+        <v>5.89</v>
       </c>
       <c r="G76" s="10" t="n"/>
       <c r="H76" s="10" t="n"/>
       <c r="I76" s="10" t="n"/>
       <c r="J76" s="9" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="K76" s="9" t="n">
-        <v>2.49</v>
+        <v>1.93</v>
       </c>
       <c r="L76" s="9" t="n">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="M76" s="9" t="n">
-        <v>2.7</v>
+        <v>1.95</v>
       </c>
       <c r="N76" s="10" t="n"/>
       <c r="O76" s="10" t="n"/>
       <c r="P76" s="10" t="n"/>
       <c r="Q76" s="9" t="n">
-        <v>0.88</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="R76" s="9" t="n">
-        <v>0.59</v>
+        <v>0.52</v>
       </c>
       <c r="S76" s="9" t="n">
         <v>0.42</v>
       </c>
       <c r="T76" s="9" t="n">
-        <v>0.49</v>
+        <v>0.47</v>
       </c>
       <c r="U76" s="10" t="n"/>
       <c r="V76" s="10" t="n"/>
       <c r="W76" s="10" t="n"/>
       <c r="X76" s="9" t="n">
-        <v>15.47</v>
+        <v>7.43</v>
       </c>
       <c r="Y76" s="9" t="n">
-        <v>13.47</v>
+        <v>10.9</v>
       </c>
       <c r="Z76" s="9" t="n">
-        <v>11.86</v>
+        <v>7.87</v>
       </c>
       <c r="AA76" s="9" t="n">
-        <v>9.25</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AB76" s="10" t="n"/>
       <c r="AC76" s="10" t="n"/>
       <c r="AD76" s="10" t="n"/>
       <c r="AE76" s="9" t="n">
-        <v>0.5</v>
+        <v>0.32</v>
       </c>
       <c r="AF76" s="9" t="n">
-        <v>0.42</v>
+        <v>0.32</v>
       </c>
       <c r="AG76" s="9" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AH76" s="9" t="n">
         <v>0.39</v>
-      </c>
-      <c r="AH76" s="9" t="n">
-        <v>0.46</v>
       </c>
       <c r="AI76" s="10" t="n"/>
       <c r="AJ76" s="10" t="n"/>
       <c r="AK76" s="10" t="n"/>
     </row>
     <row r="77">
-      <c r="A77" s="6" t="inlineStr">
+      <c r="A77" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    대창단조</t>
+        </is>
+      </c>
+      <c r="B77" s="8" t="n">
+        <v>118</v>
+      </c>
+      <c r="C77" s="9" t="n">
+        <v>5.71</v>
+      </c>
+      <c r="D77" s="9" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="E77" s="9" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="F77" s="9" t="n">
+        <v>5.53</v>
+      </c>
+      <c r="G77" s="10" t="n"/>
+      <c r="H77" s="10" t="n"/>
+      <c r="I77" s="10" t="n"/>
+      <c r="J77" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="K77" s="9" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="L77" s="9" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="M77" s="9" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="N77" s="10" t="n"/>
+      <c r="O77" s="10" t="n"/>
+      <c r="P77" s="10" t="n"/>
+      <c r="Q77" s="9" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="R77" s="9" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="S77" s="9" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="T77" s="9" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="U77" s="10" t="n"/>
+      <c r="V77" s="10" t="n"/>
+      <c r="W77" s="10" t="n"/>
+      <c r="X77" s="9" t="n">
+        <v>15.47</v>
+      </c>
+      <c r="Y77" s="9" t="n">
+        <v>13.47</v>
+      </c>
+      <c r="Z77" s="9" t="n">
+        <v>11.86</v>
+      </c>
+      <c r="AA77" s="9" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="AB77" s="10" t="n"/>
+      <c r="AC77" s="10" t="n"/>
+      <c r="AD77" s="10" t="n"/>
+      <c r="AE77" s="9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AF77" s="9" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="AG77" s="9" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="AH77" s="9" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="AI77" s="10" t="n"/>
+      <c r="AJ77" s="10" t="n"/>
+      <c r="AK77" s="10" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">  미국</t>
         </is>
       </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Caterpillar</t>
-        </is>
-      </c>
-      <c r="B78" s="8" t="n">
-        <v>340013</v>
-      </c>
-      <c r="C78" s="9" t="n">
-        <v>18.45</v>
-      </c>
-      <c r="D78" s="9" t="n">
-        <v>14.29</v>
-      </c>
-      <c r="E78" s="9" t="n">
-        <v>16.07</v>
-      </c>
-      <c r="F78" s="9" t="n">
-        <v>30</v>
-      </c>
-      <c r="G78" s="10" t="n">
-        <v>26.74</v>
-      </c>
-      <c r="H78" s="10" t="n">
-        <v>22.43</v>
-      </c>
-      <c r="I78" s="10" t="n"/>
-      <c r="J78" s="9" t="n">
-        <v>13.46</v>
-      </c>
-      <c r="K78" s="9" t="n">
-        <v>11.37</v>
-      </c>
-      <c r="L78" s="9" t="n">
-        <v>12.78</v>
-      </c>
-      <c r="M78" s="9" t="n">
-        <v>20.96</v>
-      </c>
-      <c r="N78" s="10" t="n"/>
-      <c r="O78" s="10" t="n"/>
-      <c r="P78" s="10" t="n"/>
-      <c r="Q78" s="9" t="n">
-        <v>7.79</v>
-      </c>
-      <c r="R78" s="9" t="n">
-        <v>7.57</v>
-      </c>
-      <c r="S78" s="9" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="T78" s="9" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="U78" s="10" t="n">
-        <v>11.07</v>
-      </c>
-      <c r="V78" s="10" t="n">
-        <v>8.109999999999999</v>
-      </c>
-      <c r="W78" s="10" t="n"/>
-      <c r="X78" s="9" t="n">
-        <v>42.25</v>
-      </c>
-      <c r="Y78" s="9" t="n">
-        <v>58.45</v>
-      </c>
-      <c r="Z78" s="9" t="n">
-        <v>55.36</v>
-      </c>
-      <c r="AA78" s="9" t="n">
-        <v>43.54</v>
-      </c>
-      <c r="AB78" s="10" t="n">
-        <v>48.86</v>
-      </c>
-      <c r="AC78" s="10" t="n">
-        <v>41.72</v>
-      </c>
-      <c r="AD78" s="10" t="n"/>
-      <c r="AE78" s="9" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AF78" s="9" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AG78" s="9" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="AH78" s="9" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="AI78" s="10" t="n">
-        <v>4.27</v>
-      </c>
-      <c r="AJ78" s="10" t="n">
-        <v>3.83</v>
-      </c>
-      <c r="AK78" s="10" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Deere</t>
+          <t xml:space="preserve">    Caterpillar</t>
         </is>
       </c>
       <c r="B79" s="8" t="n">
-        <v>173528</v>
+        <v>340013</v>
       </c>
       <c r="C79" s="9" t="n">
-        <v>16.58</v>
+        <v>18.45</v>
       </c>
       <c r="D79" s="9" t="n">
-        <v>10.12</v>
+        <v>14.29</v>
       </c>
       <c r="E79" s="9" t="n">
-        <v>15.49</v>
+        <v>16.07</v>
       </c>
       <c r="F79" s="9" t="n">
-        <v>24.83</v>
+        <v>30</v>
       </c>
       <c r="G79" s="10" t="n">
-        <v>35.44</v>
+        <v>26.74</v>
       </c>
       <c r="H79" s="10" t="n">
-        <v>27.92</v>
+        <v>22.43</v>
       </c>
       <c r="I79" s="10" t="n"/>
       <c r="J79" s="9" t="n">
-        <v>13.71</v>
+        <v>13.46</v>
       </c>
       <c r="K79" s="9" t="n">
-        <v>9.1</v>
+        <v>11.37</v>
       </c>
       <c r="L79" s="9" t="n">
-        <v>11.46</v>
+        <v>12.78</v>
       </c>
       <c r="M79" s="9" t="n">
-        <v>15.51</v>
+        <v>20.96</v>
       </c>
       <c r="N79" s="10" t="n"/>
       <c r="O79" s="10" t="n"/>
       <c r="P79" s="10" t="n"/>
       <c r="Q79" s="9" t="n">
-        <v>5.84</v>
+        <v>7.79</v>
       </c>
       <c r="R79" s="9" t="n">
-        <v>4.72</v>
+        <v>7.57</v>
       </c>
       <c r="S79" s="9" t="n">
-        <v>4.82</v>
+        <v>8.9</v>
       </c>
       <c r="T79" s="9" t="n">
-        <v>4.81</v>
+        <v>12.5</v>
       </c>
       <c r="U79" s="10" t="n">
-        <v>5.97</v>
+        <v>11.07</v>
       </c>
       <c r="V79" s="10" t="n">
-        <v>5.25</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="W79" s="10" t="n"/>
       <c r="X79" s="9" t="n">
-        <v>35.19</v>
+        <v>42.25</v>
       </c>
       <c r="Y79" s="9" t="n">
-        <v>48.36</v>
+        <v>58.45</v>
       </c>
       <c r="Z79" s="9" t="n">
-        <v>31.82</v>
+        <v>55.36</v>
       </c>
       <c r="AA79" s="9" t="n">
-        <v>20.61</v>
+        <v>43.54</v>
       </c>
       <c r="AB79" s="10" t="n">
-        <v>17.79</v>
+        <v>48.86</v>
       </c>
       <c r="AC79" s="10" t="n">
-        <v>20</v>
+        <v>41.72</v>
       </c>
       <c r="AD79" s="10" t="n"/>
       <c r="AE79" s="9" t="n">
-        <v>2.31</v>
+        <v>2.08</v>
       </c>
       <c r="AF79" s="9" t="n">
-        <v>1.71</v>
+        <v>2.2</v>
       </c>
       <c r="AG79" s="9" t="n">
-        <v>2.18</v>
+        <v>2.68</v>
       </c>
       <c r="AH79" s="9" t="n">
-        <v>2.79</v>
+        <v>3.94</v>
       </c>
       <c r="AI79" s="10" t="n">
-        <v>4.22</v>
+        <v>4.27</v>
       </c>
       <c r="AJ79" s="10" t="n">
-        <v>3.89</v>
+        <v>3.83</v>
       </c>
       <c r="AK79" s="10" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    CNH Industrial</t>
+          <t xml:space="preserve">    Deere</t>
         </is>
       </c>
       <c r="B80" s="8" t="n">
-        <v>14408</v>
+        <v>173528</v>
       </c>
       <c r="C80" s="9" t="n">
-        <v>10.64</v>
+        <v>16.58</v>
       </c>
       <c r="D80" s="9" t="n">
-        <v>6.91</v>
+        <v>10.12</v>
       </c>
       <c r="E80" s="9" t="n">
-        <v>11.35</v>
+        <v>15.49</v>
       </c>
       <c r="F80" s="9" t="n">
-        <v>22.45</v>
+        <v>24.83</v>
       </c>
       <c r="G80" s="10" t="n">
-        <v>25.76</v>
+        <v>35.44</v>
       </c>
       <c r="H80" s="10" t="n">
-        <v>16.79</v>
+        <v>27.92</v>
       </c>
       <c r="I80" s="10" t="n"/>
       <c r="J80" s="9" t="n">
-        <v>10.23</v>
+        <v>13.71</v>
       </c>
       <c r="K80" s="9" t="n">
-        <v>8.460000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="L80" s="9" t="n">
-        <v>10.38</v>
+        <v>11.46</v>
       </c>
       <c r="M80" s="9" t="n">
-        <v>13.15</v>
+        <v>15.51</v>
       </c>
       <c r="N80" s="10" t="n"/>
       <c r="O80" s="10" t="n"/>
       <c r="P80" s="10" t="n"/>
       <c r="Q80" s="9" t="n">
-        <v>3.12</v>
+        <v>5.84</v>
       </c>
       <c r="R80" s="9" t="n">
-        <v>1.96</v>
+        <v>4.72</v>
       </c>
       <c r="S80" s="9" t="n">
-        <v>1.85</v>
+        <v>4.82</v>
       </c>
       <c r="T80" s="9" t="n">
-        <v>1.48</v>
+        <v>4.81</v>
       </c>
       <c r="U80" s="10" t="n">
-        <v>1.79</v>
+        <v>5.97</v>
       </c>
       <c r="V80" s="10" t="n">
-        <v>1.68</v>
+        <v>5.25</v>
       </c>
       <c r="W80" s="10" t="n"/>
       <c r="X80" s="9" t="n">
-        <v>29.29</v>
+        <v>35.19</v>
       </c>
       <c r="Y80" s="9" t="n">
-        <v>30.42</v>
+        <v>48.36</v>
       </c>
       <c r="Z80" s="9" t="n">
-        <v>15.89</v>
+        <v>31.82</v>
       </c>
       <c r="AA80" s="9" t="n">
-        <v>6.63</v>
+        <v>20.61</v>
       </c>
       <c r="AB80" s="10" t="n">
-        <v>7.08</v>
+        <v>17.79</v>
       </c>
       <c r="AC80" s="10" t="n">
-        <v>10.31</v>
+        <v>20</v>
       </c>
       <c r="AD80" s="10" t="n"/>
       <c r="AE80" s="9" t="n">
-        <v>0.92</v>
+        <v>2.31</v>
       </c>
       <c r="AF80" s="9" t="n">
-        <v>0.64</v>
+        <v>1.71</v>
       </c>
       <c r="AG80" s="9" t="n">
-        <v>0.71</v>
+        <v>2.18</v>
       </c>
       <c r="AH80" s="9" t="n">
-        <v>0.63</v>
+        <v>2.79</v>
       </c>
       <c r="AI80" s="10" t="n">
-        <v>0.79</v>
+        <v>4.22</v>
       </c>
       <c r="AJ80" s="10" t="n">
-        <v>0.76</v>
+        <v>3.89</v>
       </c>
       <c r="AK80" s="10" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    United Rentals</t>
+          <t xml:space="preserve">    CNH Industrial</t>
         </is>
       </c>
       <c r="B81" s="8" t="n">
-        <v>64966</v>
+        <v>14408</v>
       </c>
       <c r="C81" s="9" t="n">
-        <v>11.71</v>
+        <v>10.64</v>
       </c>
       <c r="D81" s="9" t="n">
-        <v>15.91</v>
+        <v>6.91</v>
       </c>
       <c r="E81" s="9" t="n">
-        <v>17.87</v>
+        <v>11.35</v>
       </c>
       <c r="F81" s="9" t="n">
-        <v>20.48</v>
+        <v>22.45</v>
       </c>
       <c r="G81" s="10" t="n">
-        <v>20.72</v>
+        <v>25.76</v>
       </c>
       <c r="H81" s="10" t="n">
-        <v>17.8</v>
+        <v>16.79</v>
       </c>
       <c r="I81" s="10" t="n"/>
       <c r="J81" s="9" t="n">
-        <v>6.73</v>
+        <v>10.23</v>
       </c>
       <c r="K81" s="9" t="n">
-        <v>7.68</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="L81" s="9" t="n">
-        <v>8.640000000000001</v>
+        <v>10.38</v>
       </c>
       <c r="M81" s="9" t="n">
-        <v>9.25</v>
+        <v>13.15</v>
       </c>
       <c r="N81" s="10" t="n"/>
       <c r="O81" s="10" t="n"/>
       <c r="P81" s="10" t="n"/>
       <c r="Q81" s="9" t="n">
-        <v>3.49</v>
+        <v>3.12</v>
       </c>
       <c r="R81" s="9" t="n">
-        <v>4.74</v>
+        <v>1.96</v>
       </c>
       <c r="S81" s="9" t="n">
-        <v>5.34</v>
+        <v>1.85</v>
       </c>
       <c r="T81" s="9" t="n">
-        <v>5.69</v>
+        <v>1.48</v>
       </c>
       <c r="U81" s="10" t="n">
-        <v>5.63</v>
+        <v>1.79</v>
       </c>
       <c r="V81" s="10" t="n">
-        <v>4.47</v>
+        <v>1.68</v>
       </c>
       <c r="W81" s="10" t="n"/>
       <c r="X81" s="9" t="n">
-        <v>29.81</v>
+        <v>29.29</v>
       </c>
       <c r="Y81" s="9" t="n">
-        <v>31.91</v>
+        <v>30.42</v>
       </c>
       <c r="Z81" s="9" t="n">
-        <v>30.74</v>
+        <v>15.89</v>
       </c>
       <c r="AA81" s="9" t="n">
-        <v>28.36</v>
+        <v>6.63</v>
       </c>
       <c r="AB81" s="10" t="n">
-        <v>30.58</v>
+        <v>7.08</v>
       </c>
       <c r="AC81" s="10" t="n">
-        <v>28.01</v>
+        <v>10.31</v>
       </c>
       <c r="AD81" s="10" t="n"/>
       <c r="AE81" s="9" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AF81" s="9" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="AG81" s="9" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="AH81" s="9" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="AI81" s="10" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="AJ81" s="10" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="AK81" s="10" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    United Rentals</t>
+        </is>
+      </c>
+      <c r="B82" s="8" t="n">
+        <v>64966</v>
+      </c>
+      <c r="C82" s="9" t="n">
+        <v>11.71</v>
+      </c>
+      <c r="D82" s="9" t="n">
+        <v>15.91</v>
+      </c>
+      <c r="E82" s="9" t="n">
+        <v>17.87</v>
+      </c>
+      <c r="F82" s="9" t="n">
+        <v>20.48</v>
+      </c>
+      <c r="G82" s="10" t="n">
+        <v>20.72</v>
+      </c>
+      <c r="H82" s="10" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="I82" s="10" t="n"/>
+      <c r="J82" s="9" t="n">
+        <v>6.73</v>
+      </c>
+      <c r="K82" s="9" t="n">
+        <v>7.68</v>
+      </c>
+      <c r="L82" s="9" t="n">
+        <v>8.640000000000001</v>
+      </c>
+      <c r="M82" s="9" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="N82" s="10" t="n"/>
+      <c r="O82" s="10" t="n"/>
+      <c r="P82" s="10" t="n"/>
+      <c r="Q82" s="9" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="R82" s="9" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="S82" s="9" t="n">
+        <v>5.34</v>
+      </c>
+      <c r="T82" s="9" t="n">
+        <v>5.69</v>
+      </c>
+      <c r="U82" s="10" t="n">
+        <v>5.63</v>
+      </c>
+      <c r="V82" s="10" t="n">
+        <v>4.47</v>
+      </c>
+      <c r="W82" s="10" t="n"/>
+      <c r="X82" s="9" t="n">
+        <v>29.81</v>
+      </c>
+      <c r="Y82" s="9" t="n">
+        <v>31.91</v>
+      </c>
+      <c r="Z82" s="9" t="n">
+        <v>30.74</v>
+      </c>
+      <c r="AA82" s="9" t="n">
+        <v>28.36</v>
+      </c>
+      <c r="AB82" s="10" t="n">
+        <v>30.58</v>
+      </c>
+      <c r="AC82" s="10" t="n">
+        <v>28.01</v>
+      </c>
+      <c r="AD82" s="10" t="n"/>
+      <c r="AE82" s="9" t="n">
         <v>2.12</v>
       </c>
-      <c r="AF81" s="9" t="n">
+      <c r="AF82" s="9" t="n">
         <v>2.69</v>
       </c>
-      <c r="AG81" s="9" t="n">
+      <c r="AG82" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="AH81" s="9" t="n">
+      <c r="AH82" s="9" t="n">
         <v>3.17</v>
       </c>
-      <c r="AI81" s="10" t="n">
+      <c r="AI82" s="10" t="n">
         <v>3.66</v>
       </c>
-      <c r="AJ81" s="10" t="n">
+      <c r="AJ82" s="10" t="n">
         <v>3.36</v>
       </c>
-      <c r="AK81" s="10" t="n"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="6" t="inlineStr">
+      <c r="AK82" s="10" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">  일본</t>
         </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Komatsu</t>
-        </is>
-      </c>
-      <c r="B83" s="8" t="n">
-        <v>41026</v>
-      </c>
-      <c r="C83" s="9" t="n"/>
-      <c r="D83" s="9" t="n">
-        <v>9.49</v>
-      </c>
-      <c r="E83" s="9" t="n">
-        <v>10.67</v>
-      </c>
-      <c r="F83" s="9" t="n">
-        <v>9.039999999999999</v>
-      </c>
-      <c r="G83" s="10" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="H83" s="10" t="n">
-        <v>16.11</v>
-      </c>
-      <c r="I83" s="10" t="n">
-        <v>14.56</v>
-      </c>
-      <c r="J83" s="9" t="n"/>
-      <c r="K83" s="9" t="n">
-        <v>5.96</v>
-      </c>
-      <c r="L83" s="9" t="n">
-        <v>6.43</v>
-      </c>
-      <c r="M83" s="9" t="n">
-        <v>5.83</v>
-      </c>
-      <c r="N83" s="10" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="O83" s="10" t="n"/>
-      <c r="P83" s="10" t="n"/>
-      <c r="Q83" s="9" t="n"/>
-      <c r="R83" s="9" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S83" s="9" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="T83" s="9" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="U83" s="10" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="V83" s="10" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="W83" s="10" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="X83" s="9" t="n"/>
-      <c r="Y83" s="9" t="n">
-        <v>12.85</v>
-      </c>
-      <c r="Z83" s="9" t="n">
-        <v>14.12</v>
-      </c>
-      <c r="AA83" s="9" t="n">
-        <v>14.17</v>
-      </c>
-      <c r="AB83" s="10" t="n">
-        <v>11.26</v>
-      </c>
-      <c r="AC83" s="10" t="n">
-        <v>11.13</v>
-      </c>
-      <c r="AD83" s="10" t="n">
-        <v>11.57</v>
-      </c>
-      <c r="AE83" s="9" t="n"/>
-      <c r="AF83" s="9" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="AG83" s="9" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AH83" s="9" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="AI83" s="10" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AJ83" s="10" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AK83" s="10" t="n">
-        <v>1.4</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Hitachi CM</t>
+          <t xml:space="preserve">    Komatsu</t>
         </is>
       </c>
       <c r="B84" s="8" t="n">
-        <v>7282</v>
+        <v>41026</v>
       </c>
       <c r="C84" s="9" t="n"/>
       <c r="D84" s="9" t="n">
-        <v>9.32</v>
+        <v>9.49</v>
       </c>
       <c r="E84" s="9" t="n">
-        <v>10.35</v>
+        <v>10.67</v>
       </c>
       <c r="F84" s="9" t="n">
-        <v>10.31</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="G84" s="10" t="n">
-        <v>15.32</v>
+        <v>14.4</v>
       </c>
       <c r="H84" s="10" t="n">
-        <v>12.59</v>
+        <v>16.11</v>
       </c>
       <c r="I84" s="10" t="n">
-        <v>10.92</v>
+        <v>14.56</v>
       </c>
       <c r="J84" s="9" t="n"/>
       <c r="K84" s="9" t="n">
-        <v>5.66</v>
+        <v>5.96</v>
       </c>
       <c r="L84" s="9" t="n">
-        <v>5.99</v>
+        <v>6.43</v>
       </c>
       <c r="M84" s="9" t="n">
-        <v>5.47</v>
+        <v>5.83</v>
       </c>
       <c r="N84" s="10" t="n">
-        <v>7.1</v>
+        <v>8.5</v>
       </c>
       <c r="O84" s="10" t="n"/>
       <c r="P84" s="10" t="n"/>
       <c r="Q84" s="9" t="n"/>
       <c r="R84" s="9" t="n">
-        <v>0.99</v>
+        <v>1.22</v>
       </c>
       <c r="S84" s="9" t="n">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="T84" s="9" t="n">
-        <v>1.04</v>
+        <v>1.25</v>
       </c>
       <c r="U84" s="10" t="n">
-        <v>1.25</v>
+        <v>1.54</v>
       </c>
       <c r="V84" s="10" t="n">
-        <v>1.21</v>
+        <v>1.74</v>
       </c>
       <c r="W84" s="10" t="n">
-        <v>1.13</v>
+        <v>1.63</v>
       </c>
       <c r="X84" s="9" t="n"/>
       <c r="Y84" s="9" t="n">
-        <v>10.63</v>
+        <v>12.85</v>
       </c>
       <c r="Z84" s="9" t="n">
-        <v>13.11</v>
+        <v>14.12</v>
       </c>
       <c r="AA84" s="9" t="n">
-        <v>10.36</v>
+        <v>14.17</v>
       </c>
       <c r="AB84" s="10" t="n">
-        <v>8.56</v>
+        <v>11.26</v>
       </c>
       <c r="AC84" s="10" t="n">
-        <v>9.869999999999999</v>
+        <v>11.13</v>
       </c>
       <c r="AD84" s="10" t="n">
-        <v>10.71</v>
+        <v>11.57</v>
       </c>
       <c r="AE84" s="9" t="n"/>
       <c r="AF84" s="9" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="AG84" s="9" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AH84" s="9" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="AI84" s="10" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AJ84" s="10" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AK84" s="10" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Hitachi CM</t>
+        </is>
+      </c>
+      <c r="B85" s="8" t="n">
+        <v>7282</v>
+      </c>
+      <c r="C85" s="9" t="n"/>
+      <c r="D85" s="9" t="n">
+        <v>9.32</v>
+      </c>
+      <c r="E85" s="9" t="n">
+        <v>10.35</v>
+      </c>
+      <c r="F85" s="9" t="n">
+        <v>10.31</v>
+      </c>
+      <c r="G85" s="10" t="n">
+        <v>15.32</v>
+      </c>
+      <c r="H85" s="10" t="n">
+        <v>12.59</v>
+      </c>
+      <c r="I85" s="10" t="n">
+        <v>10.92</v>
+      </c>
+      <c r="J85" s="9" t="n"/>
+      <c r="K85" s="9" t="n">
+        <v>5.66</v>
+      </c>
+      <c r="L85" s="9" t="n">
+        <v>5.99</v>
+      </c>
+      <c r="M85" s="9" t="n">
+        <v>5.47</v>
+      </c>
+      <c r="N85" s="10" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="O85" s="10" t="n"/>
+      <c r="P85" s="10" t="n"/>
+      <c r="Q85" s="9" t="n"/>
+      <c r="R85" s="9" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="S85" s="9" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="T85" s="9" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="U85" s="10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V85" s="10" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="W85" s="10" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X85" s="9" t="n"/>
+      <c r="Y85" s="9" t="n">
+        <v>10.63</v>
+      </c>
+      <c r="Z85" s="9" t="n">
+        <v>13.11</v>
+      </c>
+      <c r="AA85" s="9" t="n">
+        <v>10.36</v>
+      </c>
+      <c r="AB85" s="10" t="n">
+        <v>8.56</v>
+      </c>
+      <c r="AC85" s="10" t="n">
+        <v>9.869999999999999</v>
+      </c>
+      <c r="AD85" s="10" t="n">
+        <v>10.71</v>
+      </c>
+      <c r="AE85" s="9" t="n"/>
+      <c r="AF85" s="9" t="n">
         <v>0.52</v>
       </c>
-      <c r="AG84" s="9" t="n">
+      <c r="AG85" s="9" t="n">
         <v>0.6899999999999999</v>
       </c>
-      <c r="AH84" s="9" t="n">
+      <c r="AH85" s="9" t="n">
         <v>0.61</v>
       </c>
-      <c r="AI84" s="10" t="n">
+      <c r="AI85" s="10" t="n">
         <v>0.8</v>
       </c>
-      <c r="AJ84" s="10" t="n">
+      <c r="AJ85" s="10" t="n">
         <v>0.78</v>
       </c>
-      <c r="AK84" s="10" t="n">
+      <c r="AK85" s="10" t="n">
         <v>0.75</v>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="6" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">  스웨덴</t>
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="7" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">    Volvo</t>
         </is>
       </c>
-      <c r="B86" s="8" t="n">
+      <c r="B87" s="8" t="n">
         <v>66494</v>
       </c>
-      <c r="C86" s="9" t="n">
+      <c r="C87" s="9" t="n">
         <v>11.71</v>
       </c>
-      <c r="D86" s="9" t="n">
+      <c r="D87" s="9" t="n">
         <v>10.68</v>
       </c>
-      <c r="E86" s="9" t="n">
+      <c r="E87" s="9" t="n">
         <v>10.84</v>
       </c>
-      <c r="F86" s="9" t="n">
+      <c r="F87" s="9" t="n">
         <v>17.46</v>
       </c>
-      <c r="G86" s="10" t="n">
+      <c r="G87" s="10" t="n">
         <v>15.08</v>
       </c>
-      <c r="H86" s="10" t="n">
+      <c r="H87" s="10" t="n">
         <v>12.62</v>
       </c>
-      <c r="I86" s="10" t="n"/>
-      <c r="J86" s="9" t="n">
+      <c r="I87" s="10" t="n"/>
+      <c r="J87" s="9" t="n">
         <v>7.78</v>
       </c>
-      <c r="K86" s="9" t="n">
+      <c r="K87" s="9" t="n">
         <v>7.72</v>
       </c>
-      <c r="L86" s="9" t="n">
+      <c r="L87" s="9" t="n">
         <v>8.09</v>
       </c>
-      <c r="M86" s="9" t="n">
+      <c r="M87" s="9" t="n">
         <v>11.01</v>
       </c>
-      <c r="N86" s="10" t="n"/>
-      <c r="O86" s="10" t="n"/>
-      <c r="P86" s="10" t="n"/>
-      <c r="Q86" s="9" t="n">
+      <c r="N87" s="10" t="n"/>
+      <c r="O87" s="10" t="n"/>
+      <c r="P87" s="10" t="n"/>
+      <c r="Q87" s="9" t="n">
         <v>2.36</v>
       </c>
-      <c r="R86" s="9" t="n">
+      <c r="R87" s="9" t="n">
         <v>2.99</v>
       </c>
-      <c r="S86" s="9" t="n">
+      <c r="S87" s="9" t="n">
         <v>2.81</v>
       </c>
-      <c r="T86" s="9" t="n">
+      <c r="T87" s="9" t="n">
         <v>3.37</v>
       </c>
-      <c r="U86" s="10" t="n">
+      <c r="U87" s="10" t="n">
         <v>3.29</v>
       </c>
-      <c r="V86" s="10" t="n">
+      <c r="V87" s="10" t="n">
         <v>2.9</v>
       </c>
-      <c r="W86" s="10" t="n"/>
-      <c r="X86" s="9" t="n">
+      <c r="W87" s="10" t="n"/>
+      <c r="X87" s="9" t="n">
         <v>20.11</v>
       </c>
-      <c r="Y86" s="9" t="n">
+      <c r="Y87" s="9" t="n">
         <v>29.27</v>
       </c>
-      <c r="Z86" s="9" t="n">
+      <c r="Z87" s="9" t="n">
         <v>27.1</v>
       </c>
-      <c r="AA86" s="9" t="n">
+      <c r="AA87" s="9" t="n">
         <v>18.5</v>
       </c>
-      <c r="AB86" s="10" t="n">
+      <c r="AB87" s="10" t="n">
         <v>23.12</v>
       </c>
-      <c r="AC86" s="10" t="n">
+      <c r="AC87" s="10" t="n">
         <v>24.42</v>
       </c>
-      <c r="AD86" s="10" t="n"/>
-      <c r="AE86" s="9" t="n">
+      <c r="AD87" s="10" t="n"/>
+      <c r="AE87" s="9" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="AF86" s="9" t="n">
+      <c r="AF87" s="9" t="n">
         <v>0.96</v>
       </c>
-      <c r="AG86" s="9" t="n">
+      <c r="AG87" s="9" t="n">
         <v>1.04</v>
       </c>
-      <c r="AH86" s="9" t="n">
+      <c r="AH87" s="9" t="n">
         <v>1.26</v>
       </c>
-      <c r="AI86" s="10" t="n">
+      <c r="AI87" s="10" t="n">
         <v>1.32</v>
       </c>
-      <c r="AJ86" s="10" t="n">
+      <c r="AJ87" s="10" t="n">
         <v>1.21</v>
       </c>
-      <c r="AK86" s="10" t="n"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="6" t="inlineStr">
+      <c r="AK87" s="10" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">  중국</t>
         </is>
       </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    삼일중공업(SANY)</t>
-        </is>
-      </c>
-      <c r="B88" s="8" t="n">
-        <v>24311</v>
-      </c>
-      <c r="C88" s="9" t="n">
-        <v>31.28</v>
-      </c>
-      <c r="D88" s="9" t="n">
-        <v>25.81</v>
-      </c>
-      <c r="E88" s="9" t="n">
-        <v>23.45</v>
-      </c>
-      <c r="F88" s="9" t="n">
-        <v>23.11</v>
-      </c>
-      <c r="G88" s="10" t="n">
-        <v>15.14</v>
-      </c>
-      <c r="H88" s="10" t="n">
-        <v>11.67</v>
-      </c>
-      <c r="I88" s="10" t="n"/>
-      <c r="J88" s="9" t="n">
-        <v>18.39</v>
-      </c>
-      <c r="K88" s="9" t="n">
-        <v>14.21</v>
-      </c>
-      <c r="L88" s="9" t="n">
-        <v>12.82</v>
-      </c>
-      <c r="M88" s="9" t="n">
-        <v>12.91</v>
-      </c>
-      <c r="N88" s="10" t="n"/>
-      <c r="O88" s="10" t="n"/>
-      <c r="P88" s="10" t="n"/>
-      <c r="Q88" s="9" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="R88" s="9" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="S88" s="9" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="T88" s="9" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U88" s="10" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="V88" s="10" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="W88" s="10" t="n"/>
-      <c r="X88" s="9" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="Y88" s="9" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="Z88" s="9" t="n">
-        <v>8.51</v>
-      </c>
-      <c r="AA88" s="9" t="n">
-        <v>10.49</v>
-      </c>
-      <c r="AB88" s="10" t="n">
-        <v>11.67</v>
-      </c>
-      <c r="AC88" s="10" t="n">
-        <v>13.87</v>
-      </c>
-      <c r="AD88" s="10" t="n"/>
-      <c r="AE88" s="9" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AF88" s="9" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AG88" s="9" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AH88" s="9" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AI88" s="10" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AJ88" s="10" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AK88" s="10" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    서공기계(XCMG)</t>
+          <t xml:space="preserve">    삼일중공업(SANY)</t>
         </is>
       </c>
       <c r="B89" s="8" t="n">
-        <v>12138</v>
+        <v>24311</v>
       </c>
       <c r="C89" s="9" t="n">
-        <v>13.89</v>
+        <v>31.28</v>
       </c>
       <c r="D89" s="9" t="n">
-        <v>12.11</v>
+        <v>25.81</v>
       </c>
       <c r="E89" s="9" t="n">
-        <v>15.53</v>
+        <v>23.45</v>
       </c>
       <c r="F89" s="9" t="n">
-        <v>20.71</v>
+        <v>23.11</v>
       </c>
       <c r="G89" s="10" t="n">
-        <v>10.41</v>
+        <v>15.14</v>
       </c>
       <c r="H89" s="10" t="n">
-        <v>7.67</v>
+        <v>11.67</v>
       </c>
       <c r="I89" s="10" t="n"/>
       <c r="J89" s="9" t="n">
-        <v>7.78</v>
+        <v>18.39</v>
       </c>
       <c r="K89" s="9" t="n">
-        <v>7.57</v>
+        <v>14.21</v>
       </c>
       <c r="L89" s="9" t="n">
-        <v>9.69</v>
+        <v>12.82</v>
       </c>
       <c r="M89" s="9" t="n">
-        <v>12.29</v>
+        <v>12.91</v>
       </c>
       <c r="N89" s="10" t="n"/>
       <c r="O89" s="10" t="n"/>
       <c r="P89" s="10" t="n"/>
       <c r="Q89" s="9" t="n">
-        <v>1.12</v>
+        <v>2.06</v>
       </c>
       <c r="R89" s="9" t="n">
-        <v>1.15</v>
+        <v>1.72</v>
       </c>
       <c r="S89" s="9" t="n">
-        <v>1.57</v>
+        <v>1.94</v>
       </c>
       <c r="T89" s="9" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="U89" s="10" t="n">
-        <v>1.29</v>
+        <v>1.7</v>
       </c>
       <c r="V89" s="10" t="n">
-        <v>1.23</v>
+        <v>1.55</v>
       </c>
       <c r="W89" s="10" t="n"/>
       <c r="X89" s="9" t="n">
-        <v>8.1</v>
+        <v>6.6</v>
       </c>
       <c r="Y89" s="9" t="n">
-        <v>9.74</v>
+        <v>6.8</v>
       </c>
       <c r="Z89" s="9" t="n">
-        <v>10.43</v>
+        <v>8.51</v>
       </c>
       <c r="AA89" s="9" t="n">
-        <v>10.96</v>
+        <v>10.49</v>
       </c>
       <c r="AB89" s="10" t="n">
-        <v>12.65</v>
+        <v>11.67</v>
       </c>
       <c r="AC89" s="10" t="n">
-        <v>16.42</v>
+        <v>13.87</v>
       </c>
       <c r="AD89" s="10" t="n"/>
       <c r="AE89" s="9" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AF89" s="9" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AG89" s="9" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AH89" s="9" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AI89" s="10" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AJ89" s="10" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AK89" s="10" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    서공기계(XCMG)</t>
+        </is>
+      </c>
+      <c r="B90" s="8" t="n">
+        <v>12138</v>
+      </c>
+      <c r="C90" s="9" t="n">
+        <v>13.89</v>
+      </c>
+      <c r="D90" s="9" t="n">
+        <v>12.11</v>
+      </c>
+      <c r="E90" s="9" t="n">
+        <v>15.53</v>
+      </c>
+      <c r="F90" s="9" t="n">
+        <v>20.71</v>
+      </c>
+      <c r="G90" s="10" t="n">
+        <v>10.41</v>
+      </c>
+      <c r="H90" s="10" t="n">
+        <v>7.67</v>
+      </c>
+      <c r="I90" s="10" t="n"/>
+      <c r="J90" s="9" t="n">
+        <v>7.78</v>
+      </c>
+      <c r="K90" s="9" t="n">
+        <v>7.57</v>
+      </c>
+      <c r="L90" s="9" t="n">
+        <v>9.69</v>
+      </c>
+      <c r="M90" s="9" t="n">
+        <v>12.29</v>
+      </c>
+      <c r="N90" s="10" t="n"/>
+      <c r="O90" s="10" t="n"/>
+      <c r="P90" s="10" t="n"/>
+      <c r="Q90" s="9" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="R90" s="9" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="S90" s="9" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="T90" s="9" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U90" s="10" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V90" s="10" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="W90" s="10" t="n"/>
+      <c r="X90" s="9" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="Y90" s="9" t="n">
+        <v>9.74</v>
+      </c>
+      <c r="Z90" s="9" t="n">
+        <v>10.43</v>
+      </c>
+      <c r="AA90" s="9" t="n">
+        <v>10.96</v>
+      </c>
+      <c r="AB90" s="10" t="n">
+        <v>12.65</v>
+      </c>
+      <c r="AC90" s="10" t="n">
+        <v>16.42</v>
+      </c>
+      <c r="AD90" s="10" t="n"/>
+      <c r="AE90" s="9" t="n">
         <v>0.64</v>
       </c>
-      <c r="AF89" s="9" t="n">
+      <c r="AF90" s="9" t="n">
         <v>0.6899999999999999</v>
       </c>
-      <c r="AG89" s="9" t="n">
+      <c r="AG90" s="9" t="n">
         <v>1.01</v>
       </c>
-      <c r="AH89" s="9" t="n">
+      <c r="AH90" s="9" t="n">
         <v>1.35</v>
       </c>
-      <c r="AI89" s="10" t="n">
+      <c r="AI90" s="10" t="n">
         <v>0.71</v>
       </c>
-      <c r="AJ89" s="10" t="n">
+      <c r="AJ90" s="10" t="n">
         <v>0.62</v>
       </c>
-      <c r="AK89" s="10" t="n"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  한국 중앙값</t>
-        </is>
-      </c>
-      <c r="B90" s="12" t="n"/>
-      <c r="C90" s="13" t="n">
-        <v>6.51</v>
-      </c>
-      <c r="D90" s="13" t="n">
-        <v>6.27</v>
-      </c>
-      <c r="E90" s="13" t="n">
-        <v>7.35</v>
-      </c>
-      <c r="F90" s="13" t="n">
-        <v>8.390000000000001</v>
-      </c>
-      <c r="G90" s="13" t="n">
-        <v>7.23</v>
-      </c>
-      <c r="H90" s="13" t="n">
-        <v>6.33</v>
-      </c>
-      <c r="I90" s="13" t="n"/>
-      <c r="J90" s="13" t="n">
-        <v>3.77</v>
-      </c>
-      <c r="K90" s="13" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="L90" s="13" t="n">
-        <v>3.56</v>
-      </c>
-      <c r="M90" s="13" t="n">
-        <v>5.07</v>
-      </c>
-      <c r="N90" s="13" t="n"/>
-      <c r="O90" s="13" t="n"/>
-      <c r="P90" s="13" t="n"/>
-      <c r="Q90" s="13" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="R90" s="13" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="S90" s="13" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="T90" s="13" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="U90" s="13" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="V90" s="13" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="W90" s="13" t="n"/>
-      <c r="X90" s="13" t="n">
-        <v>12.02</v>
-      </c>
-      <c r="Y90" s="13" t="n">
-        <v>11.88</v>
-      </c>
-      <c r="Z90" s="13" t="n">
-        <v>8.18</v>
-      </c>
-      <c r="AA90" s="13" t="n">
-        <v>7.02</v>
-      </c>
-      <c r="AB90" s="13" t="n">
-        <v>15.39</v>
-      </c>
-      <c r="AC90" s="13" t="n">
-        <v>12.24</v>
-      </c>
-      <c r="AD90" s="13" t="n"/>
-      <c r="AE90" s="13" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="AF90" s="13" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="AG90" s="13" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="AH90" s="13" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="AI90" s="13" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="AJ90" s="13" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="AK90" s="13" t="n"/>
+      <c r="AK90" s="10" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">  미국 중앙값</t>
+          <t xml:space="preserve">  한국 중앙값</t>
         </is>
       </c>
       <c r="B91" s="12" t="n"/>
       <c r="C91" s="13" t="n">
-        <v>14.14</v>
+        <v>6.51</v>
       </c>
       <c r="D91" s="13" t="n">
-        <v>12.2</v>
+        <v>6.27</v>
       </c>
       <c r="E91" s="13" t="n">
-        <v>15.78</v>
+        <v>7.35</v>
       </c>
       <c r="F91" s="13" t="n">
-        <v>23.64</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="G91" s="13" t="n">
-        <v>26.25</v>
+        <v>7.23</v>
       </c>
       <c r="H91" s="13" t="n">
-        <v>20.12</v>
+        <v>6.33</v>
       </c>
       <c r="I91" s="13" t="n"/>
       <c r="J91" s="13" t="n">
-        <v>11.85</v>
+        <v>3.77</v>
       </c>
       <c r="K91" s="13" t="n">
-        <v>8.779999999999999</v>
+        <v>3.35</v>
       </c>
       <c r="L91" s="13" t="n">
-        <v>10.92</v>
+        <v>3.56</v>
       </c>
       <c r="M91" s="13" t="n">
-        <v>14.33</v>
+        <v>5.07</v>
       </c>
       <c r="N91" s="13" t="n"/>
       <c r="O91" s="13" t="n"/>
       <c r="P91" s="13" t="n"/>
       <c r="Q91" s="13" t="n">
-        <v>4.67</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="R91" s="13" t="n">
-        <v>4.73</v>
+        <v>0.73</v>
       </c>
       <c r="S91" s="13" t="n">
-        <v>5.08</v>
+        <v>0.55</v>
       </c>
       <c r="T91" s="13" t="n">
-        <v>5.25</v>
+        <v>0.66</v>
       </c>
       <c r="U91" s="13" t="n">
-        <v>5.8</v>
+        <v>0.63</v>
       </c>
       <c r="V91" s="13" t="n">
-        <v>4.86</v>
+        <v>0.61</v>
       </c>
       <c r="W91" s="13" t="n"/>
       <c r="X91" s="13" t="n">
-        <v>32.5</v>
+        <v>12.02</v>
       </c>
       <c r="Y91" s="13" t="n">
-        <v>40.13</v>
+        <v>11.88</v>
       </c>
       <c r="Z91" s="13" t="n">
-        <v>31.28</v>
+        <v>8.18</v>
       </c>
       <c r="AA91" s="13" t="n">
-        <v>24.48</v>
+        <v>7.02</v>
       </c>
       <c r="AB91" s="13" t="n">
-        <v>24.18</v>
+        <v>15.39</v>
       </c>
       <c r="AC91" s="13" t="n">
-        <v>24.01</v>
+        <v>12.24</v>
       </c>
       <c r="AD91" s="13" t="n"/>
       <c r="AE91" s="13" t="n">
-        <v>2.1</v>
+        <v>0.37</v>
       </c>
       <c r="AF91" s="13" t="n">
-        <v>1.96</v>
+        <v>0.37</v>
       </c>
       <c r="AG91" s="13" t="n">
-        <v>2.43</v>
+        <v>0.35</v>
       </c>
       <c r="AH91" s="13" t="n">
-        <v>2.98</v>
+        <v>0.53</v>
       </c>
       <c r="AI91" s="13" t="n">
-        <v>3.94</v>
+        <v>0.47</v>
       </c>
       <c r="AJ91" s="13" t="n">
-        <v>3.59</v>
+        <v>0.42</v>
       </c>
       <c r="AK91" s="13" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">  일본 중앙값</t>
+          <t xml:space="preserve">  미국 중앙값</t>
         </is>
       </c>
       <c r="B92" s="12" t="n"/>
-      <c r="C92" s="13" t="n"/>
+      <c r="C92" s="13" t="n">
+        <v>14.14</v>
+      </c>
       <c r="D92" s="13" t="n">
-        <v>9.41</v>
+        <v>12.2</v>
       </c>
       <c r="E92" s="13" t="n">
-        <v>10.51</v>
+        <v>15.78</v>
       </c>
       <c r="F92" s="13" t="n">
-        <v>9.68</v>
+        <v>23.64</v>
       </c>
       <c r="G92" s="13" t="n">
-        <v>14.86</v>
+        <v>26.25</v>
       </c>
       <c r="H92" s="13" t="n">
-        <v>14.35</v>
-      </c>
-      <c r="I92" s="13" t="n">
-        <v>12.74</v>
-      </c>
-      <c r="J92" s="13" t="n"/>
+        <v>20.12</v>
+      </c>
+      <c r="I92" s="13" t="n"/>
+      <c r="J92" s="13" t="n">
+        <v>11.85</v>
+      </c>
       <c r="K92" s="13" t="n">
-        <v>5.81</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="L92" s="13" t="n">
-        <v>6.21</v>
+        <v>10.92</v>
       </c>
       <c r="M92" s="13" t="n">
-        <v>5.65</v>
-      </c>
-      <c r="N92" s="13" t="n">
-        <v>7.8</v>
-      </c>
+        <v>14.33</v>
+      </c>
+      <c r="N92" s="13" t="n"/>
       <c r="O92" s="13" t="n"/>
       <c r="P92" s="13" t="n"/>
-      <c r="Q92" s="13" t="n"/>
+      <c r="Q92" s="13" t="n">
+        <v>4.67</v>
+      </c>
       <c r="R92" s="13" t="n">
-        <v>1.1</v>
+        <v>4.73</v>
       </c>
       <c r="S92" s="13" t="n">
-        <v>1.32</v>
+        <v>5.08</v>
       </c>
       <c r="T92" s="13" t="n">
-        <v>1.15</v>
+        <v>5.25</v>
       </c>
       <c r="U92" s="13" t="n">
-        <v>1.4</v>
+        <v>5.8</v>
       </c>
       <c r="V92" s="13" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="W92" s="13" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="X92" s="13" t="n"/>
+        <v>4.86</v>
+      </c>
+      <c r="W92" s="13" t="n"/>
+      <c r="X92" s="13" t="n">
+        <v>32.5</v>
+      </c>
       <c r="Y92" s="13" t="n">
-        <v>11.74</v>
+        <v>40.13</v>
       </c>
       <c r="Z92" s="13" t="n">
-        <v>13.61</v>
+        <v>31.28</v>
       </c>
       <c r="AA92" s="13" t="n">
-        <v>12.27</v>
+        <v>24.48</v>
       </c>
       <c r="AB92" s="13" t="n">
-        <v>9.91</v>
+        <v>24.18</v>
       </c>
       <c r="AC92" s="13" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD92" s="13" t="n">
-        <v>11.14</v>
-      </c>
-      <c r="AE92" s="13" t="n"/>
+        <v>24.01</v>
+      </c>
+      <c r="AD92" s="13" t="n"/>
+      <c r="AE92" s="13" t="n">
+        <v>2.1</v>
+      </c>
       <c r="AF92" s="13" t="n">
-        <v>0.7</v>
+        <v>1.96</v>
       </c>
       <c r="AG92" s="13" t="n">
-        <v>0.89</v>
+        <v>2.43</v>
       </c>
       <c r="AH92" s="13" t="n">
-        <v>0.79</v>
+        <v>2.98</v>
       </c>
       <c r="AI92" s="13" t="n">
-        <v>1.06</v>
+        <v>3.94</v>
       </c>
       <c r="AJ92" s="13" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AK92" s="13" t="n">
-        <v>1.07</v>
-      </c>
+        <v>3.59</v>
+      </c>
+      <c r="AK92" s="13" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">  스웨덴 중앙값</t>
+          <t xml:space="preserve">  일본 중앙값</t>
         </is>
       </c>
       <c r="B93" s="12" t="n"/>
-      <c r="C93" s="13" t="n">
-        <v>11.71</v>
-      </c>
+      <c r="C93" s="13" t="n"/>
       <c r="D93" s="13" t="n">
-        <v>10.68</v>
+        <v>9.41</v>
       </c>
       <c r="E93" s="13" t="n">
-        <v>10.84</v>
+        <v>10.51</v>
       </c>
       <c r="F93" s="13" t="n">
-        <v>17.46</v>
+        <v>9.68</v>
       </c>
       <c r="G93" s="13" t="n">
-        <v>15.08</v>
+        <v>14.86</v>
       </c>
       <c r="H93" s="13" t="n">
-        <v>12.62</v>
-      </c>
-      <c r="I93" s="13" t="n"/>
-      <c r="J93" s="13" t="n">
-        <v>7.78</v>
-      </c>
+        <v>14.35</v>
+      </c>
+      <c r="I93" s="13" t="n">
+        <v>12.74</v>
+      </c>
+      <c r="J93" s="13" t="n"/>
       <c r="K93" s="13" t="n">
-        <v>7.72</v>
+        <v>5.81</v>
       </c>
       <c r="L93" s="13" t="n">
-        <v>8.09</v>
+        <v>6.21</v>
       </c>
       <c r="M93" s="13" t="n">
-        <v>11.01</v>
-      </c>
-      <c r="N93" s="13" t="n"/>
+        <v>5.65</v>
+      </c>
+      <c r="N93" s="13" t="n">
+        <v>7.8</v>
+      </c>
       <c r="O93" s="13" t="n"/>
       <c r="P93" s="13" t="n"/>
-      <c r="Q93" s="13" t="n">
-        <v>2.36</v>
-      </c>
+      <c r="Q93" s="13" t="n"/>
       <c r="R93" s="13" t="n">
-        <v>2.99</v>
+        <v>1.1</v>
       </c>
       <c r="S93" s="13" t="n">
-        <v>2.81</v>
+        <v>1.32</v>
       </c>
       <c r="T93" s="13" t="n">
-        <v>3.37</v>
+        <v>1.15</v>
       </c>
       <c r="U93" s="13" t="n">
-        <v>3.29</v>
+        <v>1.4</v>
       </c>
       <c r="V93" s="13" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="W93" s="13" t="n"/>
-      <c r="X93" s="13" t="n">
-        <v>20.11</v>
-      </c>
+        <v>1.48</v>
+      </c>
+      <c r="W93" s="13" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X93" s="13" t="n"/>
       <c r="Y93" s="13" t="n">
-        <v>29.27</v>
+        <v>11.74</v>
       </c>
       <c r="Z93" s="13" t="n">
-        <v>27.1</v>
+        <v>13.61</v>
       </c>
       <c r="AA93" s="13" t="n">
-        <v>18.5</v>
+        <v>12.27</v>
       </c>
       <c r="AB93" s="13" t="n">
-        <v>23.12</v>
+        <v>9.91</v>
       </c>
       <c r="AC93" s="13" t="n">
-        <v>24.42</v>
-      </c>
-      <c r="AD93" s="13" t="n"/>
-      <c r="AE93" s="13" t="n">
-        <v>0.8100000000000001</v>
-      </c>
+        <v>10.5</v>
+      </c>
+      <c r="AD93" s="13" t="n">
+        <v>11.14</v>
+      </c>
+      <c r="AE93" s="13" t="n"/>
       <c r="AF93" s="13" t="n">
-        <v>0.96</v>
+        <v>0.7</v>
       </c>
       <c r="AG93" s="13" t="n">
-        <v>1.04</v>
+        <v>0.89</v>
       </c>
       <c r="AH93" s="13" t="n">
-        <v>1.26</v>
+        <v>0.79</v>
       </c>
       <c r="AI93" s="13" t="n">
-        <v>1.32</v>
+        <v>1.06</v>
       </c>
       <c r="AJ93" s="13" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AK93" s="13" t="n"/>
+        <v>1.12</v>
+      </c>
+      <c r="AK93" s="13" t="n">
+        <v>1.07</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">  중국 중앙값</t>
+          <t xml:space="preserve">  스웨덴 중앙값</t>
         </is>
       </c>
       <c r="B94" s="12" t="n"/>
       <c r="C94" s="13" t="n">
-        <v>22.59</v>
+        <v>11.71</v>
       </c>
       <c r="D94" s="13" t="n">
-        <v>18.96</v>
+        <v>10.68</v>
       </c>
       <c r="E94" s="13" t="n">
-        <v>19.49</v>
+        <v>10.84</v>
       </c>
       <c r="F94" s="13" t="n">
-        <v>21.91</v>
+        <v>17.46</v>
       </c>
       <c r="G94" s="13" t="n">
-        <v>12.78</v>
+        <v>15.08</v>
       </c>
       <c r="H94" s="13" t="n">
-        <v>9.67</v>
+        <v>12.62</v>
       </c>
       <c r="I94" s="13" t="n"/>
       <c r="J94" s="13" t="n">
-        <v>13.09</v>
+        <v>7.78</v>
       </c>
       <c r="K94" s="13" t="n">
-        <v>10.89</v>
+        <v>7.72</v>
       </c>
       <c r="L94" s="13" t="n">
-        <v>11.25</v>
+        <v>8.09</v>
       </c>
       <c r="M94" s="13" t="n">
-        <v>12.6</v>
+        <v>11.01</v>
       </c>
       <c r="N94" s="13" t="n"/>
       <c r="O94" s="13" t="n"/>
       <c r="P94" s="13" t="n"/>
       <c r="Q94" s="13" t="n">
-        <v>1.59</v>
+        <v>2.36</v>
       </c>
       <c r="R94" s="13" t="n">
-        <v>1.44</v>
+        <v>2.99</v>
       </c>
       <c r="S94" s="13" t="n">
-        <v>1.75</v>
+        <v>2.81</v>
       </c>
       <c r="T94" s="13" t="n">
-        <v>2.23</v>
+        <v>3.37</v>
       </c>
       <c r="U94" s="13" t="n">
-        <v>1.5</v>
+        <v>3.29</v>
       </c>
       <c r="V94" s="13" t="n">
-        <v>1.39</v>
+        <v>2.9</v>
       </c>
       <c r="W94" s="13" t="n"/>
       <c r="X94" s="13" t="n">
-        <v>7.35</v>
+        <v>20.11</v>
       </c>
       <c r="Y94" s="13" t="n">
-        <v>8.27</v>
+        <v>29.27</v>
       </c>
       <c r="Z94" s="13" t="n">
-        <v>9.470000000000001</v>
+        <v>27.1</v>
       </c>
       <c r="AA94" s="13" t="n">
-        <v>10.73</v>
+        <v>18.5</v>
       </c>
       <c r="AB94" s="13" t="n">
-        <v>12.16</v>
+        <v>23.12</v>
       </c>
       <c r="AC94" s="13" t="n">
-        <v>15.14</v>
+        <v>24.42</v>
       </c>
       <c r="AD94" s="13" t="n"/>
       <c r="AE94" s="13" t="n">
-        <v>1.15</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AF94" s="13" t="n">
-        <v>1.14</v>
+        <v>0.96</v>
       </c>
       <c r="AG94" s="13" t="n">
-        <v>1.4</v>
+        <v>1.04</v>
       </c>
       <c r="AH94" s="13" t="n">
-        <v>1.76</v>
+        <v>1.26</v>
       </c>
       <c r="AI94" s="13" t="n">
-        <v>1.14</v>
+        <v>1.32</v>
       </c>
       <c r="AJ94" s="13" t="n">
-        <v>1</v>
+        <v>1.21</v>
       </c>
       <c r="AK94" s="13" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="11" t="inlineStr">
         <is>
-          <t>건설기계 전체 중앙값</t>
+          <t xml:space="preserve">  중국 중앙값</t>
         </is>
       </c>
       <c r="B95" s="12" t="n"/>
       <c r="C95" s="13" t="n">
-        <v>10.64</v>
+        <v>22.59</v>
       </c>
       <c r="D95" s="13" t="n">
-        <v>9.49</v>
+        <v>18.96</v>
       </c>
       <c r="E95" s="13" t="n">
-        <v>10.75</v>
+        <v>19.49</v>
       </c>
       <c r="F95" s="13" t="n">
-        <v>18.97</v>
+        <v>21.91</v>
       </c>
       <c r="G95" s="13" t="n">
-        <v>15.11</v>
+        <v>12.78</v>
       </c>
       <c r="H95" s="13" t="n">
-        <v>12.61</v>
-      </c>
-      <c r="I95" s="13" t="n">
-        <v>12.74</v>
-      </c>
+        <v>9.67</v>
+      </c>
+      <c r="I95" s="13" t="n"/>
       <c r="J95" s="13" t="n">
-        <v>7.18</v>
+        <v>13.09</v>
       </c>
       <c r="K95" s="13" t="n">
-        <v>7.57</v>
+        <v>10.89</v>
       </c>
       <c r="L95" s="13" t="n">
-        <v>8.09</v>
+        <v>11.25</v>
       </c>
       <c r="M95" s="13" t="n">
-        <v>11.01</v>
-      </c>
-      <c r="N95" s="13" t="n">
-        <v>7.8</v>
-      </c>
+        <v>12.6</v>
+      </c>
+      <c r="N95" s="13" t="n"/>
       <c r="O95" s="13" t="n"/>
       <c r="P95" s="13" t="n"/>
       <c r="Q95" s="13" t="n">
-        <v>1.25</v>
+        <v>1.59</v>
       </c>
       <c r="R95" s="13" t="n">
-        <v>1.15</v>
+        <v>1.44</v>
       </c>
       <c r="S95" s="13" t="n">
-        <v>1.38</v>
+        <v>1.75</v>
       </c>
       <c r="T95" s="13" t="n">
-        <v>1.48</v>
+        <v>2.23</v>
       </c>
       <c r="U95" s="13" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="V95" s="13" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="W95" s="13" t="n">
-        <v>1.38</v>
-      </c>
+        <v>1.39</v>
+      </c>
+      <c r="W95" s="13" t="n"/>
       <c r="X95" s="13" t="n">
-        <v>15.47</v>
+        <v>7.35</v>
       </c>
       <c r="Y95" s="13" t="n">
-        <v>12.86</v>
+        <v>8.27</v>
       </c>
       <c r="Z95" s="13" t="n">
-        <v>11.86</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="AA95" s="13" t="n">
-        <v>10.49</v>
+        <v>10.73</v>
       </c>
       <c r="AB95" s="13" t="n">
-        <v>14.02</v>
+        <v>12.16</v>
       </c>
       <c r="AC95" s="13" t="n">
         <v>15.14</v>
       </c>
-      <c r="AD95" s="13" t="n">
+      <c r="AD95" s="13" t="n"/>
+      <c r="AE95" s="13" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AF95" s="13" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AG95" s="13" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH95" s="13" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AI95" s="13" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AJ95" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK95" s="13" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="11" t="inlineStr">
+        <is>
+          <t>건설기계 전체 중앙값</t>
+        </is>
+      </c>
+      <c r="B96" s="12" t="n"/>
+      <c r="C96" s="13" t="n">
+        <v>10.64</v>
+      </c>
+      <c r="D96" s="13" t="n">
+        <v>9.49</v>
+      </c>
+      <c r="E96" s="13" t="n">
+        <v>10.75</v>
+      </c>
+      <c r="F96" s="13" t="n">
+        <v>18.97</v>
+      </c>
+      <c r="G96" s="13" t="n">
+        <v>15.11</v>
+      </c>
+      <c r="H96" s="13" t="n">
+        <v>12.61</v>
+      </c>
+      <c r="I96" s="13" t="n">
+        <v>12.74</v>
+      </c>
+      <c r="J96" s="13" t="n">
+        <v>7.18</v>
+      </c>
+      <c r="K96" s="13" t="n">
+        <v>7.57</v>
+      </c>
+      <c r="L96" s="13" t="n">
+        <v>8.09</v>
+      </c>
+      <c r="M96" s="13" t="n">
+        <v>11.01</v>
+      </c>
+      <c r="N96" s="13" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="O96" s="13" t="n"/>
+      <c r="P96" s="13" t="n"/>
+      <c r="Q96" s="13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="R96" s="13" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="S96" s="13" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="T96" s="13" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="U96" s="13" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V96" s="13" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="W96" s="13" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X96" s="13" t="n">
+        <v>15.47</v>
+      </c>
+      <c r="Y96" s="13" t="n">
+        <v>12.86</v>
+      </c>
+      <c r="Z96" s="13" t="n">
+        <v>11.86</v>
+      </c>
+      <c r="AA96" s="13" t="n">
+        <v>10.49</v>
+      </c>
+      <c r="AB96" s="13" t="n">
+        <v>14.02</v>
+      </c>
+      <c r="AC96" s="13" t="n">
+        <v>15.14</v>
+      </c>
+      <c r="AD96" s="13" t="n">
         <v>11.14</v>
       </c>
-      <c r="AE95" s="13" t="n">
+      <c r="AE96" s="13" t="n">
         <v>0.64</v>
       </c>
-      <c r="AF95" s="13" t="n">
+      <c r="AF96" s="13" t="n">
         <v>0.64</v>
       </c>
-      <c r="AG95" s="13" t="n">
+      <c r="AG96" s="13" t="n">
         <v>0.71</v>
       </c>
-      <c r="AH95" s="13" t="n">
+      <c r="AH96" s="13" t="n">
         <v>0.97</v>
       </c>
-      <c r="AI95" s="13" t="n">
+      <c r="AI96" s="13" t="n">
         <v>1.06</v>
       </c>
-      <c r="AJ95" s="13" t="n">
+      <c r="AJ96" s="13" t="n">
         <v>0.99</v>
       </c>
-      <c r="AK95" s="13" t="n">
+      <c r="AK96" s="13" t="n">
         <v>1.07</v>
       </c>
     </row>
@@ -8757,7 +8856,7 @@
         </is>
       </c>
       <c r="E18" s="7" t="n">
-        <v>1156</v>
+        <v>1153</v>
       </c>
       <c r="F18" s="9" t="n"/>
       <c r="G18" s="9" t="n"/>
@@ -8769,10 +8868,10 @@
       </c>
       <c r="J18" s="9" t="n"/>
       <c r="K18" s="9" t="n">
-        <v>17.47</v>
+        <v>17.3</v>
       </c>
       <c r="L18" s="9" t="n">
-        <v>15.74</v>
+        <v>15.58</v>
       </c>
     </row>
     <row r="19">
@@ -10981,7 +11080,7 @@
         </is>
       </c>
       <c r="E18" s="7" t="n">
-        <v>1156</v>
+        <v>1153</v>
       </c>
       <c r="F18" s="9" t="n"/>
       <c r="G18" s="9" t="n">
@@ -13155,7 +13254,7 @@
         </is>
       </c>
       <c r="E18" s="7" t="n">
-        <v>1156</v>
+        <v>1153</v>
       </c>
       <c r="F18" s="9" t="n"/>
       <c r="G18" s="9" t="n">
@@ -13171,10 +13270,10 @@
         <v>1.39</v>
       </c>
       <c r="K18" s="9" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="L18" s="9" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="19">
@@ -15467,7 +15566,7 @@
         </is>
       </c>
       <c r="E18" s="7" t="n">
-        <v>1156</v>
+        <v>1153</v>
       </c>
       <c r="F18" s="9" t="n"/>
       <c r="G18" s="9" t="n">
@@ -17771,7 +17870,7 @@
         </is>
       </c>
       <c r="E18" s="7" t="n">
-        <v>1156</v>
+        <v>1153</v>
       </c>
       <c r="F18" s="9" t="n"/>
       <c r="G18" s="9" t="n">
@@ -17787,10 +17886,10 @@
         <v>0.84</v>
       </c>
       <c r="K18" s="9" t="n">
-        <v>0.72</v>
+        <v>0.71</v>
       </c>
       <c r="L18" s="9" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="19">
@@ -27591,7 +27690,7 @@
         </is>
       </c>
       <c r="G118" s="14" t="n">
-        <v>3.96</v>
+        <v>3.92</v>
       </c>
       <c r="H118" s="14" t="n">
         <v>0.23</v>
@@ -27609,17 +27708,17 @@
         <v>1329209800.58081</v>
       </c>
       <c r="M118" s="14" t="n">
-        <v>17.47</v>
+        <v>17.3</v>
       </c>
       <c r="N118" s="14" t="n"/>
       <c r="O118" s="14" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="P118" s="14" t="n">
         <v>7.46</v>
       </c>
       <c r="Q118" s="14" t="n">
-        <v>0.72</v>
+        <v>0.71</v>
       </c>
       <c r="R118" s="14" t="inlineStr">
         <is>
@@ -27664,7 +27763,7 @@
         </is>
       </c>
       <c r="G119" s="14" t="n">
-        <v>3.96</v>
+        <v>3.92</v>
       </c>
       <c r="H119" s="14" t="n">
         <v>0.25</v>
@@ -27682,17 +27781,17 @@
         <v>1435397636.18441</v>
       </c>
       <c r="M119" s="14" t="n">
-        <v>15.74</v>
+        <v>15.58</v>
       </c>
       <c r="N119" s="14" t="n"/>
       <c r="O119" s="14" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="P119" s="14" t="n">
         <v>7.68</v>
       </c>
       <c r="Q119" s="14" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="R119" s="14" t="inlineStr">
         <is>
@@ -44836,7 +44935,7 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>2026-10-19T07:57:27+09:00</t>
+          <t>2026-10-19T08:30:19+09:00</t>
         </is>
       </c>
     </row>

--- a/telegram_research_dashboard/static/valuation_full.xlsx
+++ b/telegram_research_dashboard/static/valuation_full.xlsx
@@ -799,7 +799,7 @@
         </is>
       </c>
       <c r="B5" s="8" t="n">
-        <v>24179</v>
+        <v>23448</v>
       </c>
       <c r="C5" s="9" t="n"/>
       <c r="D5" s="9" t="n">
@@ -815,7 +815,7 @@
         <v>10.15</v>
       </c>
       <c r="H5" s="10" t="n">
-        <v>8.76</v>
+        <v>8.49</v>
       </c>
       <c r="I5" s="10" t="n"/>
       <c r="J5" s="9" t="n"/>
@@ -847,7 +847,7 @@
         <v>2.79</v>
       </c>
       <c r="V5" s="10" t="n">
-        <v>2.13</v>
+        <v>2.06</v>
       </c>
       <c r="W5" s="10" t="n"/>
       <c r="X5" s="9" t="n">
@@ -882,10 +882,10 @@
         <v>3.04</v>
       </c>
       <c r="AI5" s="10" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AJ5" s="10" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AK5" s="10" t="n"/>
     </row>
@@ -896,7 +896,7 @@
         </is>
       </c>
       <c r="B6" s="8" t="n">
-        <v>12801</v>
+        <v>12442</v>
       </c>
       <c r="C6" s="9" t="n"/>
       <c r="D6" s="9" t="n">
@@ -912,7 +912,7 @@
         <v>8.69</v>
       </c>
       <c r="H6" s="10" t="n">
-        <v>8.949999999999999</v>
+        <v>8.69</v>
       </c>
       <c r="I6" s="10" t="n"/>
       <c r="J6" s="9" t="n"/>
@@ -944,7 +944,7 @@
         <v>2.06</v>
       </c>
       <c r="V6" s="10" t="n">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="W6" s="10" t="n"/>
       <c r="X6" s="9" t="n">
@@ -979,10 +979,10 @@
         <v>2.72</v>
       </c>
       <c r="AI6" s="10" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AJ6" s="10" t="n">
         <v>1.07</v>
-      </c>
-      <c r="AJ6" s="10" t="n">
-        <v>1.1</v>
       </c>
       <c r="AK6" s="10" t="n"/>
     </row>
@@ -993,7 +993,7 @@
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>10860</v>
+        <v>10677</v>
       </c>
       <c r="C7" s="9" t="n"/>
       <c r="D7" s="9" t="n"/>
@@ -1007,7 +1007,7 @@
         <v>15.88</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>9.949999999999999</v>
+        <v>9.77</v>
       </c>
       <c r="I7" s="10" t="n"/>
       <c r="J7" s="9" t="n"/>
@@ -1039,7 +1039,7 @@
         <v>2.78</v>
       </c>
       <c r="V7" s="10" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="W7" s="10" t="n"/>
       <c r="X7" s="9" t="n">
@@ -1074,10 +1074,10 @@
         <v>1.93</v>
       </c>
       <c r="AI7" s="10" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AJ7" s="10" t="n">
-        <v>0.98</v>
+        <v>0.96</v>
       </c>
       <c r="AK7" s="10" t="n"/>
     </row>
@@ -1088,7 +1088,7 @@
         </is>
       </c>
       <c r="B8" s="8" t="n">
-        <v>13249</v>
+        <v>13048</v>
       </c>
       <c r="C8" s="9" t="n"/>
       <c r="D8" s="9" t="n">
@@ -1104,7 +1104,7 @@
         <v>4.46</v>
       </c>
       <c r="H8" s="10" t="n">
-        <v>4.11</v>
+        <v>4.04</v>
       </c>
       <c r="I8" s="10" t="n"/>
       <c r="J8" s="9" t="n">
@@ -1138,7 +1138,7 @@
         <v>1.15</v>
       </c>
       <c r="V8" s="10" t="n">
-        <v>0.89</v>
+        <v>0.87</v>
       </c>
       <c r="W8" s="10" t="n"/>
       <c r="X8" s="9" t="n">
@@ -1173,10 +1173,10 @@
         <v>0.96</v>
       </c>
       <c r="AI8" s="10" t="n">
-        <v>0.51</v>
+        <v>0.5</v>
       </c>
       <c r="AJ8" s="10" t="n">
-        <v>0.48</v>
+        <v>0.47</v>
       </c>
       <c r="AK8" s="10" t="n"/>
     </row>
@@ -1187,7 +1187,7 @@
         </is>
       </c>
       <c r="B9" s="8" t="n">
-        <v>1071</v>
+        <v>1064</v>
       </c>
       <c r="C9" s="9" t="n"/>
       <c r="D9" s="9" t="n"/>
@@ -1199,7 +1199,7 @@
         <v>4.77</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>4.75</v>
+        <v>4.72</v>
       </c>
       <c r="I9" s="10" t="n"/>
       <c r="J9" s="9" t="n"/>
@@ -1250,7 +1250,7 @@
         <v>2.09</v>
       </c>
       <c r="AI9" s="10" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AJ9" s="10" t="n">
         <v>1.03</v>
@@ -1264,7 +1264,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>840</v>
+        <v>829</v>
       </c>
       <c r="C10" s="9" t="n"/>
       <c r="D10" s="9" t="n"/>
@@ -1349,7 +1349,7 @@
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>6655</v>
+        <v>6502</v>
       </c>
       <c r="C11" s="9" t="n"/>
       <c r="D11" s="9" t="n"/>
@@ -1363,7 +1363,7 @@
         <v>25.22</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>21</v>
+        <v>20.5</v>
       </c>
       <c r="I11" s="10" t="n"/>
       <c r="J11" s="9" t="n"/>
@@ -1389,7 +1389,7 @@
         <v>8.74</v>
       </c>
       <c r="V11" s="10" t="n">
-        <v>7.14</v>
+        <v>6.96</v>
       </c>
       <c r="W11" s="10" t="n"/>
       <c r="X11" s="9" t="n">
@@ -1420,10 +1420,10 @@
         <v>4.38</v>
       </c>
       <c r="AI11" s="10" t="n">
-        <v>3.71</v>
+        <v>3.62</v>
       </c>
       <c r="AJ11" s="10" t="n">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="AK11" s="10" t="n"/>
     </row>
@@ -1434,7 +1434,7 @@
         </is>
       </c>
       <c r="B12" s="8" t="n">
-        <v>926</v>
+        <v>913</v>
       </c>
       <c r="C12" s="9" t="n">
         <v>14.21</v>
@@ -1452,7 +1452,7 @@
         <v>9.6</v>
       </c>
       <c r="H12" s="10" t="n">
-        <v>7.22</v>
+        <v>7.11</v>
       </c>
       <c r="I12" s="10" t="n"/>
       <c r="J12" s="9" t="n">
@@ -1486,7 +1486,7 @@
         <v>2.34</v>
       </c>
       <c r="V12" s="10" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="W12" s="10" t="n"/>
       <c r="X12" s="9" t="n">
@@ -1521,10 +1521,10 @@
         <v>7.54</v>
       </c>
       <c r="AI12" s="10" t="n">
-        <v>2.06</v>
+        <v>2.03</v>
       </c>
       <c r="AJ12" s="10" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AK12" s="10" t="n"/>
     </row>
@@ -1535,7 +1535,7 @@
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>2033</v>
+        <v>1989</v>
       </c>
       <c r="C13" s="9" t="n"/>
       <c r="D13" s="9" t="n"/>
@@ -1549,7 +1549,7 @@
         <v>14.38</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>8.869999999999999</v>
+        <v>8.67</v>
       </c>
       <c r="I13" s="10" t="n"/>
       <c r="J13" s="9" t="n"/>
@@ -1581,7 +1581,7 @@
         <v>3.59</v>
       </c>
       <c r="V13" s="10" t="n">
-        <v>2.57</v>
+        <v>2.51</v>
       </c>
       <c r="W13" s="10" t="n"/>
       <c r="X13" s="9" t="n">
@@ -1616,10 +1616,10 @@
         <v>2.61</v>
       </c>
       <c r="AI13" s="10" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AJ13" s="10" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AK13" s="10" t="n"/>
     </row>
@@ -1630,7 +1630,7 @@
         </is>
       </c>
       <c r="B14" s="8" t="n">
-        <v>613</v>
+        <v>601</v>
       </c>
       <c r="C14" s="9" t="n">
         <v>23.46</v>
@@ -1646,7 +1646,7 @@
         <v>7.02</v>
       </c>
       <c r="H14" s="10" t="n">
-        <v>5.72</v>
+        <v>5.61</v>
       </c>
       <c r="I14" s="10" t="n"/>
       <c r="J14" s="9" t="n">
@@ -1680,7 +1680,7 @@
         <v>1.2</v>
       </c>
       <c r="V14" s="10" t="n">
-        <v>1.01</v>
+        <v>0.99</v>
       </c>
       <c r="W14" s="10" t="n"/>
       <c r="X14" s="9" t="n">
@@ -1715,10 +1715,10 @@
         <v>1.65</v>
       </c>
       <c r="AI14" s="10" t="n">
-        <v>0.86</v>
+        <v>0.84</v>
       </c>
       <c r="AJ14" s="10" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="AK14" s="10" t="n"/>
     </row>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="B15" s="8" t="n">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="C15" s="9" t="n">
         <v>37.11</v>
@@ -1747,7 +1747,7 @@
         <v>4.53</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>4.49</v>
+        <v>4.42</v>
       </c>
       <c r="I15" s="10" t="n"/>
       <c r="J15" s="9" t="n">
@@ -1781,7 +1781,7 @@
         <v>1.19</v>
       </c>
       <c r="V15" s="10" t="n">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="W15" s="10" t="n"/>
       <c r="X15" s="9" t="n">
@@ -1816,10 +1816,10 @@
         <v>1.02</v>
       </c>
       <c r="AI15" s="10" t="n">
-        <v>0.46</v>
+        <v>0.45</v>
       </c>
       <c r="AJ15" s="10" t="n">
-        <v>0.44</v>
+        <v>0.43</v>
       </c>
       <c r="AK15" s="10" t="n"/>
     </row>
@@ -1837,7 +1837,7 @@
         </is>
       </c>
       <c r="B17" s="8" t="n">
-        <v>39658</v>
+        <v>39556</v>
       </c>
       <c r="C17" s="9" t="n">
         <v>577.76</v>
@@ -1934,7 +1934,7 @@
         </is>
       </c>
       <c r="B18" s="8" t="n">
-        <v>15029</v>
+        <v>14877</v>
       </c>
       <c r="C18" s="9" t="n">
         <v>9.9</v>
@@ -1949,10 +1949,10 @@
         <v>8.640000000000001</v>
       </c>
       <c r="G18" s="10" t="n">
-        <v>9.17</v>
+        <v>9.08</v>
       </c>
       <c r="H18" s="10" t="n">
-        <v>8.26</v>
+        <v>8.18</v>
       </c>
       <c r="I18" s="10" t="n"/>
       <c r="J18" s="9" t="n">
@@ -1983,10 +1983,10 @@
         <v>2.32</v>
       </c>
       <c r="U18" s="10" t="n">
-        <v>2.61</v>
+        <v>2.59</v>
       </c>
       <c r="V18" s="10" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="W18" s="10" t="n"/>
       <c r="X18" s="9" t="n">
@@ -2021,10 +2021,10 @@
         <v>2.62</v>
       </c>
       <c r="AI18" s="10" t="n">
-        <v>2.77</v>
+        <v>2.74</v>
       </c>
       <c r="AJ18" s="10" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="AK18" s="10" t="n"/>
     </row>
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="B19" s="8" t="n">
-        <v>2320</v>
+        <v>2322</v>
       </c>
       <c r="C19" s="9" t="n">
         <v>13.53</v>
@@ -2050,10 +2050,10 @@
         <v>16.46</v>
       </c>
       <c r="G19" s="10" t="n">
-        <v>13.35</v>
+        <v>13.37</v>
       </c>
       <c r="H19" s="10" t="n">
-        <v>6.52</v>
+        <v>6.53</v>
       </c>
       <c r="I19" s="10" t="n"/>
       <c r="J19" s="9" t="n">
@@ -2125,7 +2125,7 @@
         <v>0.7</v>
       </c>
       <c r="AJ19" s="10" t="n">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="AK19" s="10" t="n"/>
     </row>
@@ -2143,7 +2143,7 @@
         </is>
       </c>
       <c r="B21" s="8" t="n">
-        <v>77441</v>
+        <v>75750</v>
       </c>
       <c r="C21" s="9" t="n"/>
       <c r="D21" s="9" t="n">
@@ -2159,10 +2159,10 @@
         <v>57.81</v>
       </c>
       <c r="H21" s="10" t="n">
-        <v>26.83</v>
+        <v>26.24</v>
       </c>
       <c r="I21" s="10" t="n">
-        <v>23.61</v>
+        <v>23.09</v>
       </c>
       <c r="J21" s="9" t="n"/>
       <c r="K21" s="9" t="n">
@@ -2193,10 +2193,10 @@
         <v>4.59</v>
       </c>
       <c r="V21" s="10" t="n">
-        <v>3.56</v>
+        <v>3.48</v>
       </c>
       <c r="W21" s="10" t="n">
-        <v>3.21</v>
+        <v>3.14</v>
       </c>
       <c r="X21" s="9" t="n"/>
       <c r="Y21" s="9" t="n">
@@ -2231,10 +2231,10 @@
         <v>3.25</v>
       </c>
       <c r="AJ21" s="10" t="n">
-        <v>2.17</v>
+        <v>2.12</v>
       </c>
       <c r="AK21" s="10" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="22">
@@ -2244,7 +2244,7 @@
         </is>
       </c>
       <c r="B22" s="8" t="n">
-        <v>11529</v>
+        <v>11415</v>
       </c>
       <c r="C22" s="9" t="n"/>
       <c r="D22" s="9" t="n">
@@ -2260,10 +2260,10 @@
         <v>22.39</v>
       </c>
       <c r="H22" s="10" t="n">
-        <v>15.19</v>
+        <v>15.03</v>
       </c>
       <c r="I22" s="10" t="n">
-        <v>13.27</v>
+        <v>13.14</v>
       </c>
       <c r="J22" s="9" t="n"/>
       <c r="K22" s="9" t="n">
@@ -2294,10 +2294,10 @@
         <v>2.76</v>
       </c>
       <c r="V22" s="10" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="W22" s="10" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="X22" s="9" t="n"/>
       <c r="Y22" s="9" t="n">
@@ -2335,7 +2335,7 @@
         <v>0.7</v>
       </c>
       <c r="AK22" s="10" t="n">
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="23">
@@ -2345,7 +2345,7 @@
         </is>
       </c>
       <c r="B23" s="8" t="n">
-        <v>16564</v>
+        <v>16109</v>
       </c>
       <c r="C23" s="9" t="n"/>
       <c r="D23" s="9" t="n">
@@ -2359,10 +2359,10 @@
         <v>20.66</v>
       </c>
       <c r="H23" s="10" t="n">
-        <v>13.85</v>
+        <v>13.46</v>
       </c>
       <c r="I23" s="10" t="n">
-        <v>15.85</v>
+        <v>15.41</v>
       </c>
       <c r="J23" s="9" t="n"/>
       <c r="K23" s="9" t="n">
@@ -2393,10 +2393,10 @@
         <v>5.1</v>
       </c>
       <c r="V23" s="10" t="n">
-        <v>3.19</v>
+        <v>3.1</v>
       </c>
       <c r="W23" s="10" t="n">
-        <v>2.71</v>
+        <v>2.64</v>
       </c>
       <c r="X23" s="9" t="n"/>
       <c r="Y23" s="9" t="n">
@@ -2431,10 +2431,10 @@
         <v>2.02</v>
       </c>
       <c r="AJ23" s="10" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AK23" s="10" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="24">
@@ -2444,7 +2444,7 @@
         </is>
       </c>
       <c r="B24" s="8" t="n">
-        <v>2259</v>
+        <v>2276</v>
       </c>
       <c r="C24" s="9" t="n"/>
       <c r="D24" s="9" t="n">
@@ -2460,10 +2460,10 @@
         <v>14.63</v>
       </c>
       <c r="H24" s="10" t="n">
-        <v>9.83</v>
+        <v>9.9</v>
       </c>
       <c r="I24" s="10" t="n">
-        <v>9.449999999999999</v>
+        <v>9.52</v>
       </c>
       <c r="J24" s="9" t="n"/>
       <c r="K24" s="9" t="n">
@@ -2494,10 +2494,10 @@
         <v>2.46</v>
       </c>
       <c r="V24" s="10" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W24" s="10" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="X24" s="9" t="n"/>
       <c r="Y24" s="9" t="n">
@@ -2532,7 +2532,7 @@
         <v>1.59</v>
       </c>
       <c r="AJ24" s="10" t="n">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AK24" s="10" t="n">
         <v>0.89</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="B27" s="8" t="n">
-        <v>4396</v>
+        <v>4374</v>
       </c>
       <c r="C27" s="9" t="n"/>
       <c r="D27" s="9" t="n"/>
@@ -2648,10 +2648,10 @@
         <v>44.03</v>
       </c>
       <c r="G27" s="10" t="n">
-        <v>22.09</v>
+        <v>22</v>
       </c>
       <c r="H27" s="10" t="n">
-        <v>14.69</v>
+        <v>14.63</v>
       </c>
       <c r="I27" s="10" t="n"/>
       <c r="J27" s="9" t="n">
@@ -2682,10 +2682,10 @@
         <v>5.43</v>
       </c>
       <c r="U27" s="10" t="n">
-        <v>3.33</v>
+        <v>3.32</v>
       </c>
       <c r="V27" s="10" t="n">
-        <v>2.72</v>
+        <v>2.71</v>
       </c>
       <c r="W27" s="10" t="n"/>
       <c r="X27" s="9" t="n">
@@ -2741,7 +2741,7 @@
         </is>
       </c>
       <c r="B29" s="8" t="n">
-        <v>10943</v>
+        <v>10755</v>
       </c>
       <c r="C29" s="9" t="n">
         <v>15.9</v>
@@ -2756,10 +2756,10 @@
         <v>22.06</v>
       </c>
       <c r="G29" s="10" t="n">
-        <v>15.07</v>
+        <v>14.81</v>
       </c>
       <c r="H29" s="10" t="n">
-        <v>13.27</v>
+        <v>13.04</v>
       </c>
       <c r="I29" s="10" t="n"/>
       <c r="J29" s="9" t="n">
@@ -2790,10 +2790,10 @@
         <v>2.63</v>
       </c>
       <c r="U29" s="10" t="n">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="V29" s="10" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="W29" s="10" t="n"/>
       <c r="X29" s="9" t="n">
@@ -2828,10 +2828,10 @@
         <v>1.07</v>
       </c>
       <c r="AI29" s="10" t="n">
-        <v>0.82</v>
+        <v>0.8</v>
       </c>
       <c r="AJ29" s="10" t="n">
-        <v>0.77</v>
+        <v>0.76</v>
       </c>
       <c r="AK29" s="10" t="n"/>
     </row>
@@ -2849,7 +2849,7 @@
         </is>
       </c>
       <c r="B31" s="8" t="n">
-        <v>1236</v>
+        <v>1240</v>
       </c>
       <c r="C31" s="9" t="n"/>
       <c r="D31" s="9" t="n"/>
@@ -2861,10 +2861,10 @@
       </c>
       <c r="G31" s="10" t="n"/>
       <c r="H31" s="10" t="n">
-        <v>18.35</v>
+        <v>18.42</v>
       </c>
       <c r="I31" s="10" t="n">
-        <v>16.17</v>
+        <v>16.23</v>
       </c>
       <c r="J31" s="9" t="n"/>
       <c r="K31" s="9" t="n">
@@ -2893,10 +2893,10 @@
         <v>1.39</v>
       </c>
       <c r="V31" s="10" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W31" s="10" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="X31" s="9" t="n"/>
       <c r="Y31" s="9" t="n">
@@ -2931,7 +2931,7 @@
         <v>0.84</v>
       </c>
       <c r="AJ31" s="10" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="AK31" s="10" t="n">
         <v>0.6899999999999999</v>
@@ -2960,7 +2960,7 @@
         <v>8.69</v>
       </c>
       <c r="H32" s="13" t="n">
-        <v>7.99</v>
+        <v>7.8</v>
       </c>
       <c r="I32" s="13" t="n"/>
       <c r="J32" s="13" t="n">
@@ -2994,7 +2994,7 @@
         <v>2.06</v>
       </c>
       <c r="V32" s="13" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="W32" s="13" t="n"/>
       <c r="X32" s="13" t="n">
@@ -3029,10 +3029,10 @@
         <v>2.09</v>
       </c>
       <c r="AI32" s="13" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AJ32" s="13" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AK32" s="13" t="n"/>
     </row>
@@ -3059,7 +3059,7 @@
         <v>12.64</v>
       </c>
       <c r="H33" s="13" t="n">
-        <v>8.26</v>
+        <v>8.18</v>
       </c>
       <c r="I33" s="13" t="n"/>
       <c r="J33" s="13" t="n">
@@ -3156,10 +3156,10 @@
         <v>20.66</v>
       </c>
       <c r="H34" s="13" t="n">
-        <v>14.52</v>
+        <v>14.25</v>
       </c>
       <c r="I34" s="13" t="n">
-        <v>14.56</v>
+        <v>14.28</v>
       </c>
       <c r="J34" s="13" t="n"/>
       <c r="K34" s="13" t="n">
@@ -3190,10 +3190,10 @@
         <v>2.76</v>
       </c>
       <c r="V34" s="13" t="n">
-        <v>2.53</v>
+        <v>2.48</v>
       </c>
       <c r="W34" s="13" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="X34" s="13" t="n"/>
       <c r="Y34" s="13" t="n">
@@ -3228,10 +3228,10 @@
         <v>1.59</v>
       </c>
       <c r="AJ34" s="13" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AK34" s="13" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="35">
@@ -3250,10 +3250,10 @@
         <v>44.03</v>
       </c>
       <c r="G35" s="13" t="n">
-        <v>22.09</v>
+        <v>22</v>
       </c>
       <c r="H35" s="13" t="n">
-        <v>14.69</v>
+        <v>14.63</v>
       </c>
       <c r="I35" s="13" t="n"/>
       <c r="J35" s="13" t="n">
@@ -3284,10 +3284,10 @@
         <v>5.43</v>
       </c>
       <c r="U35" s="13" t="n">
-        <v>3.33</v>
+        <v>3.32</v>
       </c>
       <c r="V35" s="13" t="n">
-        <v>2.72</v>
+        <v>2.71</v>
       </c>
       <c r="W35" s="13" t="n"/>
       <c r="X35" s="13" t="n">
@@ -3349,10 +3349,10 @@
         <v>22.06</v>
       </c>
       <c r="G36" s="13" t="n">
-        <v>15.07</v>
+        <v>14.81</v>
       </c>
       <c r="H36" s="13" t="n">
-        <v>13.27</v>
+        <v>13.04</v>
       </c>
       <c r="I36" s="13" t="n"/>
       <c r="J36" s="13" t="n">
@@ -3383,10 +3383,10 @@
         <v>2.63</v>
       </c>
       <c r="U36" s="13" t="n">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="V36" s="13" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="W36" s="13" t="n"/>
       <c r="X36" s="13" t="n">
@@ -3421,10 +3421,10 @@
         <v>1.07</v>
       </c>
       <c r="AI36" s="13" t="n">
-        <v>0.82</v>
+        <v>0.8</v>
       </c>
       <c r="AJ36" s="13" t="n">
-        <v>0.77</v>
+        <v>0.76</v>
       </c>
       <c r="AK36" s="13" t="n"/>
     </row>
@@ -3445,10 +3445,10 @@
       </c>
       <c r="G37" s="13" t="n"/>
       <c r="H37" s="13" t="n">
-        <v>18.35</v>
+        <v>18.42</v>
       </c>
       <c r="I37" s="13" t="n">
-        <v>16.17</v>
+        <v>16.23</v>
       </c>
       <c r="J37" s="13" t="n"/>
       <c r="K37" s="13" t="n">
@@ -3477,10 +3477,10 @@
         <v>1.39</v>
       </c>
       <c r="V37" s="13" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W37" s="13" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="X37" s="13" t="n"/>
       <c r="Y37" s="13" t="n">
@@ -3515,7 +3515,7 @@
         <v>0.84</v>
       </c>
       <c r="AJ37" s="13" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="AK37" s="13" t="n">
         <v>0.6899999999999999</v>
@@ -3544,10 +3544,10 @@
         <v>12.64</v>
       </c>
       <c r="H38" s="13" t="n">
-        <v>9.34</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="I38" s="13" t="n">
-        <v>15.85</v>
+        <v>15.41</v>
       </c>
       <c r="J38" s="13" t="n">
         <v>12.48</v>
@@ -3582,10 +3582,10 @@
         <v>2.2</v>
       </c>
       <c r="V38" s="13" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="W38" s="13" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="X38" s="13" t="n">
         <v>-0.93</v>
@@ -3621,10 +3621,10 @@
         <v>1.45</v>
       </c>
       <c r="AI38" s="13" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AJ38" s="13" t="n">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="AK38" s="13" t="n">
         <v>0.89</v>
@@ -3687,7 +3687,7 @@
         </is>
       </c>
       <c r="B42" s="8" t="n">
-        <v>7526</v>
+        <v>7187</v>
       </c>
       <c r="C42" s="9" t="n">
         <v>41.88</v>
@@ -3705,7 +3705,7 @@
         <v>43.97</v>
       </c>
       <c r="H42" s="10" t="n">
-        <v>22.83</v>
+        <v>21.78</v>
       </c>
       <c r="I42" s="10" t="n"/>
       <c r="J42" s="9" t="n">
@@ -3739,7 +3739,7 @@
         <v>4.9</v>
       </c>
       <c r="V42" s="10" t="n">
-        <v>4.29</v>
+        <v>4.1</v>
       </c>
       <c r="W42" s="10" t="n"/>
       <c r="X42" s="9" t="n">
@@ -3774,10 +3774,10 @@
         <v>3.02</v>
       </c>
       <c r="AI42" s="10" t="n">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="AJ42" s="10" t="n">
-        <v>1.49</v>
+        <v>1.43</v>
       </c>
       <c r="AK42" s="10" t="n"/>
     </row>
@@ -3788,7 +3788,7 @@
         </is>
       </c>
       <c r="B43" s="8" t="n">
-        <v>30784</v>
+        <v>29608</v>
       </c>
       <c r="C43" s="9" t="n">
         <v>19.31</v>
@@ -3806,7 +3806,7 @@
         <v>17.98</v>
       </c>
       <c r="H43" s="10" t="n">
-        <v>13.7</v>
+        <v>13.17</v>
       </c>
       <c r="I43" s="10" t="n"/>
       <c r="J43" s="9" t="n">
@@ -3840,7 +3840,7 @@
         <v>3.32</v>
       </c>
       <c r="V43" s="10" t="n">
-        <v>2.89</v>
+        <v>2.78</v>
       </c>
       <c r="W43" s="10" t="n"/>
       <c r="X43" s="9" t="n">
@@ -3875,10 +3875,10 @@
         <v>1.81</v>
       </c>
       <c r="AI43" s="10" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AJ43" s="10" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AK43" s="10" t="n"/>
     </row>
@@ -3889,7 +3889,7 @@
         </is>
       </c>
       <c r="B44" s="8" t="n">
-        <v>7847</v>
+        <v>7178</v>
       </c>
       <c r="C44" s="9" t="n">
         <v>16.34</v>
@@ -3907,7 +3907,7 @@
         <v>29.67</v>
       </c>
       <c r="H44" s="10" t="n">
-        <v>20.03</v>
+        <v>18.31</v>
       </c>
       <c r="I44" s="10" t="n"/>
       <c r="J44" s="9" t="n">
@@ -3941,7 +3941,7 @@
         <v>5.98</v>
       </c>
       <c r="V44" s="10" t="n">
-        <v>4.94</v>
+        <v>4.52</v>
       </c>
       <c r="W44" s="10" t="n"/>
       <c r="X44" s="9" t="n">
@@ -3976,10 +3976,10 @@
         <v>2.14</v>
       </c>
       <c r="AI44" s="10" t="n">
-        <v>2.02</v>
+        <v>1.85</v>
       </c>
       <c r="AJ44" s="10" t="n">
-        <v>1.69</v>
+        <v>1.54</v>
       </c>
       <c r="AK44" s="10" t="n"/>
     </row>
@@ -3990,7 +3990,7 @@
         </is>
       </c>
       <c r="B45" s="8" t="n">
-        <v>9366</v>
+        <v>8640</v>
       </c>
       <c r="C45" s="9" t="n"/>
       <c r="D45" s="9" t="n">
@@ -4006,7 +4006,7 @@
         <v>91.62</v>
       </c>
       <c r="H45" s="10" t="n">
-        <v>28.49</v>
+        <v>26.25</v>
       </c>
       <c r="I45" s="10" t="n"/>
       <c r="J45" s="9" t="n">
@@ -4040,7 +4040,7 @@
         <v>2.35</v>
       </c>
       <c r="V45" s="10" t="n">
-        <v>2.4</v>
+        <v>2.21</v>
       </c>
       <c r="W45" s="10" t="n"/>
       <c r="X45" s="9" t="n">
@@ -4075,10 +4075,10 @@
         <v>2.78</v>
       </c>
       <c r="AI45" s="10" t="n">
-        <v>2.76</v>
+        <v>2.55</v>
       </c>
       <c r="AJ45" s="10" t="n">
-        <v>2.52</v>
+        <v>2.32</v>
       </c>
       <c r="AK45" s="10" t="n"/>
     </row>
@@ -4089,7 +4089,7 @@
         </is>
       </c>
       <c r="B46" s="8" t="n">
-        <v>6819</v>
+        <v>6595</v>
       </c>
       <c r="C46" s="9" t="n">
         <v>15.67</v>
@@ -4107,7 +4107,7 @@
         <v>11.27</v>
       </c>
       <c r="H46" s="10" t="n">
-        <v>9.890000000000001</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="I46" s="10" t="n"/>
       <c r="J46" s="9" t="n">
@@ -4141,7 +4141,7 @@
         <v>2.37</v>
       </c>
       <c r="V46" s="10" t="n">
-        <v>1.94</v>
+        <v>1.88</v>
       </c>
       <c r="W46" s="10" t="n"/>
       <c r="X46" s="9" t="n">
@@ -4176,10 +4176,10 @@
         <v>3.51</v>
       </c>
       <c r="AI46" s="10" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AJ46" s="10" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AK46" s="10" t="n"/>
     </row>
@@ -4197,7 +4197,7 @@
         </is>
       </c>
       <c r="B48" s="8" t="n">
-        <v>135089</v>
+        <v>138357</v>
       </c>
       <c r="C48" s="9" t="n">
         <v>21.56</v>
@@ -4212,10 +4212,10 @@
         <v>22.08</v>
       </c>
       <c r="G48" s="10" t="n">
-        <v>19.28</v>
+        <v>19.73</v>
       </c>
       <c r="H48" s="10" t="n">
-        <v>17.83</v>
+        <v>18.24</v>
       </c>
       <c r="I48" s="10" t="n"/>
       <c r="J48" s="9" t="n">
@@ -4246,10 +4246,10 @@
         <v>16.48</v>
       </c>
       <c r="U48" s="10" t="n">
-        <v>13.12</v>
+        <v>13.44</v>
       </c>
       <c r="V48" s="10" t="n">
-        <v>9.539999999999999</v>
+        <v>9.77</v>
       </c>
       <c r="W48" s="10" t="n"/>
       <c r="X48" s="9" t="n">
@@ -4265,10 +4265,10 @@
         <v>76.87</v>
       </c>
       <c r="AB48" s="10" t="n">
-        <v>82.36</v>
+        <v>82.42</v>
       </c>
       <c r="AC48" s="10" t="n">
-        <v>61.96</v>
+        <v>62.03</v>
       </c>
       <c r="AD48" s="10" t="n"/>
       <c r="AE48" s="9" t="n">
@@ -4284,10 +4284,10 @@
         <v>1.48</v>
       </c>
       <c r="AI48" s="10" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AJ48" s="10" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="AK48" s="10" t="n"/>
     </row>
@@ -4298,7 +4298,7 @@
         </is>
       </c>
       <c r="B49" s="8" t="n">
-        <v>78432</v>
+        <v>78303</v>
       </c>
       <c r="C49" s="9" t="n">
         <v>17.07</v>
@@ -4313,10 +4313,10 @@
         <v>19.36</v>
       </c>
       <c r="G49" s="10" t="n">
-        <v>18.57</v>
+        <v>18.54</v>
       </c>
       <c r="H49" s="10" t="n">
-        <v>18.37</v>
+        <v>18.36</v>
       </c>
       <c r="I49" s="10" t="n"/>
       <c r="J49" s="9" t="n">
@@ -4347,10 +4347,10 @@
         <v>4.86</v>
       </c>
       <c r="U49" s="10" t="n">
-        <v>4</v>
+        <v>3.99</v>
       </c>
       <c r="V49" s="10" t="n">
-        <v>3.47</v>
+        <v>3.46</v>
       </c>
       <c r="W49" s="10" t="n"/>
       <c r="X49" s="9" t="n">
@@ -4366,10 +4366,10 @@
         <v>26.17</v>
       </c>
       <c r="AB49" s="10" t="n">
-        <v>23.28</v>
+        <v>23.27</v>
       </c>
       <c r="AC49" s="10" t="n">
-        <v>20.22</v>
+        <v>20.2</v>
       </c>
       <c r="AD49" s="10" t="n"/>
       <c r="AE49" s="9" t="n">
@@ -4399,7 +4399,7 @@
         </is>
       </c>
       <c r="B50" s="8" t="n">
-        <v>94850</v>
+        <v>94463</v>
       </c>
       <c r="C50" s="9" t="n">
         <v>20.08</v>
@@ -4414,10 +4414,10 @@
         <v>21.62</v>
       </c>
       <c r="G50" s="10" t="n">
-        <v>20.64</v>
+        <v>20.55</v>
       </c>
       <c r="H50" s="10" t="n">
-        <v>18.82</v>
+        <v>18.75</v>
       </c>
       <c r="I50" s="10" t="n"/>
       <c r="J50" s="9" t="n">
@@ -4448,10 +4448,10 @@
         <v>3.55</v>
       </c>
       <c r="U50" s="10" t="n">
-        <v>3.33</v>
+        <v>3.32</v>
       </c>
       <c r="V50" s="10" t="n">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="W50" s="10" t="n"/>
       <c r="X50" s="9" t="n">
@@ -4486,10 +4486,10 @@
         <v>1.73</v>
       </c>
       <c r="AI50" s="10" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AJ50" s="10" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AK50" s="10" t="n"/>
     </row>
@@ -4500,7 +4500,7 @@
         </is>
       </c>
       <c r="B51" s="8" t="n">
-        <v>261357</v>
+        <v>256390</v>
       </c>
       <c r="C51" s="9" t="n">
         <v>28.47</v>
@@ -4515,10 +4515,10 @@
         <v>36.57</v>
       </c>
       <c r="G51" s="10" t="n">
-        <v>25.59</v>
+        <v>25.03</v>
       </c>
       <c r="H51" s="10" t="n">
-        <v>24.26</v>
+        <v>23.78</v>
       </c>
       <c r="I51" s="10" t="n"/>
       <c r="J51" s="9" t="n">
@@ -4549,10 +4549,10 @@
         <v>3.77</v>
       </c>
       <c r="U51" s="10" t="n">
-        <v>3.69</v>
+        <v>3.62</v>
       </c>
       <c r="V51" s="10" t="n">
-        <v>3.41</v>
+        <v>3.35</v>
       </c>
       <c r="W51" s="10" t="n"/>
       <c r="X51" s="9" t="n">
@@ -4568,7 +4568,7 @@
         <v>10.74</v>
       </c>
       <c r="AB51" s="10" t="n">
-        <v>15.02</v>
+        <v>15.06</v>
       </c>
       <c r="AC51" s="10" t="n">
         <v>14.62</v>
@@ -4587,10 +4587,10 @@
         <v>2.78</v>
       </c>
       <c r="AI51" s="10" t="n">
-        <v>2.69</v>
+        <v>2.64</v>
       </c>
       <c r="AJ51" s="10" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AK51" s="10" t="n"/>
     </row>
@@ -4601,7 +4601,7 @@
         </is>
       </c>
       <c r="B52" s="8" t="n">
-        <v>10943</v>
+        <v>10755</v>
       </c>
       <c r="C52" s="9" t="n">
         <v>15.9</v>
@@ -4616,10 +4616,10 @@
         <v>22.06</v>
       </c>
       <c r="G52" s="10" t="n">
-        <v>15.07</v>
+        <v>14.81</v>
       </c>
       <c r="H52" s="10" t="n">
-        <v>13.27</v>
+        <v>13.04</v>
       </c>
       <c r="I52" s="10" t="n"/>
       <c r="J52" s="9" t="n">
@@ -4650,10 +4650,10 @@
         <v>2.63</v>
       </c>
       <c r="U52" s="10" t="n">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="V52" s="10" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="W52" s="10" t="n"/>
       <c r="X52" s="9" t="n">
@@ -4688,10 +4688,10 @@
         <v>1.07</v>
       </c>
       <c r="AI52" s="10" t="n">
-        <v>0.82</v>
+        <v>0.8</v>
       </c>
       <c r="AJ52" s="10" t="n">
-        <v>0.77</v>
+        <v>0.76</v>
       </c>
       <c r="AK52" s="10" t="n"/>
     </row>
@@ -4709,7 +4709,7 @@
         </is>
       </c>
       <c r="B54" s="8" t="n">
-        <v>52319</v>
+        <v>52463</v>
       </c>
       <c r="C54" s="9" t="n">
         <v>17.03</v>
@@ -4724,10 +4724,10 @@
         <v>102.9</v>
       </c>
       <c r="G54" s="10" t="n">
-        <v>27.23</v>
+        <v>27.34</v>
       </c>
       <c r="H54" s="10" t="n">
-        <v>19.15</v>
+        <v>19.23</v>
       </c>
       <c r="I54" s="10" t="n"/>
       <c r="J54" s="9" t="n">
@@ -4758,10 +4758,10 @@
         <v>14.29</v>
       </c>
       <c r="U54" s="10" t="n">
-        <v>7.82</v>
+        <v>7.85</v>
       </c>
       <c r="V54" s="10" t="n">
-        <v>6.38</v>
+        <v>6.4</v>
       </c>
       <c r="W54" s="10" t="n"/>
       <c r="X54" s="9" t="n">
@@ -4796,10 +4796,10 @@
         <v>7.21</v>
       </c>
       <c r="AI54" s="10" t="n">
-        <v>3.34</v>
+        <v>3.36</v>
       </c>
       <c r="AJ54" s="10" t="n">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="AK54" s="10" t="n"/>
     </row>
@@ -4817,7 +4817,7 @@
         </is>
       </c>
       <c r="B56" s="8" t="n">
-        <v>75701</v>
+        <v>75806</v>
       </c>
       <c r="C56" s="9" t="n">
         <v>16.56</v>
@@ -4832,10 +4832,10 @@
         <v>24.33</v>
       </c>
       <c r="G56" s="10" t="n">
-        <v>22.93</v>
+        <v>22.94</v>
       </c>
       <c r="H56" s="10" t="n">
-        <v>20.16</v>
+        <v>20.18</v>
       </c>
       <c r="I56" s="10" t="n"/>
       <c r="J56" s="9" t="n">
@@ -4925,7 +4925,7 @@
         </is>
       </c>
       <c r="B58" s="8" t="n">
-        <v>31323</v>
+        <v>31374</v>
       </c>
       <c r="C58" s="9" t="n">
         <v>5</v>
@@ -4940,10 +4940,10 @@
         <v>23.17</v>
       </c>
       <c r="G58" s="10" t="n">
-        <v>20.06</v>
+        <v>20.12</v>
       </c>
       <c r="H58" s="10" t="n">
-        <v>16.73</v>
+        <v>16.78</v>
       </c>
       <c r="I58" s="10" t="n"/>
       <c r="J58" s="9" t="n">
@@ -4974,10 +4974,10 @@
         <v>2.97</v>
       </c>
       <c r="U58" s="10" t="n">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="V58" s="10" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="W58" s="10" t="n"/>
       <c r="X58" s="9" t="n">
@@ -5033,7 +5033,7 @@
         </is>
       </c>
       <c r="B60" s="8" t="n">
-        <v>34602</v>
+        <v>35175</v>
       </c>
       <c r="C60" s="9" t="n">
         <v>24.79</v>
@@ -5048,10 +5048,10 @@
         <v>45.89</v>
       </c>
       <c r="G60" s="10" t="n">
-        <v>42.49</v>
+        <v>41.65</v>
       </c>
       <c r="H60" s="10" t="n">
-        <v>33.35</v>
+        <v>33.96</v>
       </c>
       <c r="I60" s="10" t="n"/>
       <c r="J60" s="9" t="n">
@@ -5082,10 +5082,10 @@
         <v>6.69</v>
       </c>
       <c r="U60" s="10" t="n">
-        <v>6.84</v>
+        <v>6.93</v>
       </c>
       <c r="V60" s="10" t="n">
-        <v>5.84</v>
+        <v>5.93</v>
       </c>
       <c r="W60" s="10" t="n"/>
       <c r="X60" s="9" t="n">
@@ -5101,10 +5101,10 @@
         <v>16.02</v>
       </c>
       <c r="AB60" s="10" t="n">
-        <v>17.25</v>
+        <v>17.88</v>
       </c>
       <c r="AC60" s="10" t="n">
-        <v>18.89</v>
+        <v>18.82</v>
       </c>
       <c r="AD60" s="10" t="n"/>
       <c r="AE60" s="9" t="n">
@@ -5120,10 +5120,10 @@
         <v>3.66</v>
       </c>
       <c r="AI60" s="10" t="n">
-        <v>3.49</v>
+        <v>3.57</v>
       </c>
       <c r="AJ60" s="10" t="n">
-        <v>2.87</v>
+        <v>2.93</v>
       </c>
       <c r="AK60" s="10" t="n"/>
     </row>
@@ -5150,7 +5150,7 @@
         <v>29.67</v>
       </c>
       <c r="H61" s="13" t="n">
-        <v>20.03</v>
+        <v>18.31</v>
       </c>
       <c r="I61" s="13" t="n"/>
       <c r="J61" s="13" t="n">
@@ -5184,7 +5184,7 @@
         <v>3.32</v>
       </c>
       <c r="V61" s="13" t="n">
-        <v>2.89</v>
+        <v>2.78</v>
       </c>
       <c r="W61" s="13" t="n"/>
       <c r="X61" s="13" t="n">
@@ -5219,10 +5219,10 @@
         <v>2.78</v>
       </c>
       <c r="AI61" s="13" t="n">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="AJ61" s="13" t="n">
-        <v>1.49</v>
+        <v>1.43</v>
       </c>
       <c r="AK61" s="13" t="n"/>
     </row>
@@ -5246,10 +5246,10 @@
         <v>22.06</v>
       </c>
       <c r="G62" s="13" t="n">
-        <v>19.28</v>
+        <v>19.73</v>
       </c>
       <c r="H62" s="13" t="n">
-        <v>18.37</v>
+        <v>18.36</v>
       </c>
       <c r="I62" s="13" t="n"/>
       <c r="J62" s="13" t="n">
@@ -5280,10 +5280,10 @@
         <v>3.77</v>
       </c>
       <c r="U62" s="13" t="n">
-        <v>3.69</v>
+        <v>3.62</v>
       </c>
       <c r="V62" s="13" t="n">
-        <v>3.41</v>
+        <v>3.35</v>
       </c>
       <c r="W62" s="13" t="n"/>
       <c r="X62" s="13" t="n">
@@ -5321,7 +5321,7 @@
         <v>1.7</v>
       </c>
       <c r="AJ62" s="13" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AK62" s="13" t="n"/>
     </row>
@@ -5345,10 +5345,10 @@
         <v>102.9</v>
       </c>
       <c r="G63" s="13" t="n">
-        <v>27.23</v>
+        <v>27.34</v>
       </c>
       <c r="H63" s="13" t="n">
-        <v>19.15</v>
+        <v>19.23</v>
       </c>
       <c r="I63" s="13" t="n"/>
       <c r="J63" s="13" t="n">
@@ -5379,10 +5379,10 @@
         <v>14.29</v>
       </c>
       <c r="U63" s="13" t="n">
-        <v>7.82</v>
+        <v>7.85</v>
       </c>
       <c r="V63" s="13" t="n">
-        <v>6.38</v>
+        <v>6.4</v>
       </c>
       <c r="W63" s="13" t="n"/>
       <c r="X63" s="13" t="n">
@@ -5417,10 +5417,10 @@
         <v>7.21</v>
       </c>
       <c r="AI63" s="13" t="n">
-        <v>3.34</v>
+        <v>3.36</v>
       </c>
       <c r="AJ63" s="13" t="n">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="AK63" s="13" t="n"/>
     </row>
@@ -5444,10 +5444,10 @@
         <v>24.33</v>
       </c>
       <c r="G64" s="13" t="n">
-        <v>22.93</v>
+        <v>22.94</v>
       </c>
       <c r="H64" s="13" t="n">
-        <v>20.16</v>
+        <v>20.18</v>
       </c>
       <c r="I64" s="13" t="n"/>
       <c r="J64" s="13" t="n">
@@ -5543,10 +5543,10 @@
         <v>23.17</v>
       </c>
       <c r="G65" s="13" t="n">
-        <v>20.06</v>
+        <v>20.12</v>
       </c>
       <c r="H65" s="13" t="n">
-        <v>16.73</v>
+        <v>16.78</v>
       </c>
       <c r="I65" s="13" t="n"/>
       <c r="J65" s="13" t="n">
@@ -5577,10 +5577,10 @@
         <v>2.97</v>
       </c>
       <c r="U65" s="13" t="n">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="V65" s="13" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="W65" s="13" t="n"/>
       <c r="X65" s="13" t="n">
@@ -5642,10 +5642,10 @@
         <v>45.89</v>
       </c>
       <c r="G66" s="13" t="n">
-        <v>42.49</v>
+        <v>41.65</v>
       </c>
       <c r="H66" s="13" t="n">
-        <v>33.35</v>
+        <v>33.96</v>
       </c>
       <c r="I66" s="13" t="n"/>
       <c r="J66" s="13" t="n">
@@ -5676,10 +5676,10 @@
         <v>6.69</v>
       </c>
       <c r="U66" s="13" t="n">
-        <v>6.84</v>
+        <v>6.93</v>
       </c>
       <c r="V66" s="13" t="n">
-        <v>5.84</v>
+        <v>5.93</v>
       </c>
       <c r="W66" s="13" t="n"/>
       <c r="X66" s="13" t="n">
@@ -5695,10 +5695,10 @@
         <v>16.02</v>
       </c>
       <c r="AB66" s="13" t="n">
-        <v>17.25</v>
+        <v>17.88</v>
       </c>
       <c r="AC66" s="13" t="n">
-        <v>18.89</v>
+        <v>18.82</v>
       </c>
       <c r="AD66" s="13" t="n"/>
       <c r="AE66" s="13" t="n">
@@ -5714,10 +5714,10 @@
         <v>3.66</v>
       </c>
       <c r="AI66" s="13" t="n">
-        <v>3.49</v>
+        <v>3.57</v>
       </c>
       <c r="AJ66" s="13" t="n">
-        <v>2.87</v>
+        <v>2.93</v>
       </c>
       <c r="AK66" s="13" t="n"/>
     </row>
@@ -5741,10 +5741,10 @@
         <v>35.11</v>
       </c>
       <c r="G67" s="13" t="n">
-        <v>25.08</v>
+        <v>25.14</v>
       </c>
       <c r="H67" s="13" t="n">
-        <v>19.66</v>
+        <v>19.7</v>
       </c>
       <c r="I67" s="13" t="n"/>
       <c r="J67" s="13" t="n">
@@ -5775,10 +5775,10 @@
         <v>5.47</v>
       </c>
       <c r="U67" s="13" t="n">
-        <v>5.6</v>
+        <v>5.64</v>
       </c>
       <c r="V67" s="13" t="n">
-        <v>4.89</v>
+        <v>4.94</v>
       </c>
       <c r="W67" s="13" t="n"/>
       <c r="X67" s="13" t="n">
@@ -5794,10 +5794,10 @@
         <v>15.69</v>
       </c>
       <c r="AB67" s="13" t="n">
-        <v>18.59</v>
+        <v>18.9</v>
       </c>
       <c r="AC67" s="13" t="n">
-        <v>19.72</v>
+        <v>19.69</v>
       </c>
       <c r="AD67" s="13" t="n"/>
       <c r="AE67" s="13" t="n">
@@ -5813,7 +5813,7 @@
         <v>2.71</v>
       </c>
       <c r="AI67" s="13" t="n">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="AJ67" s="13" t="n">
         <v>2.04</v>
@@ -5840,10 +5840,10 @@
         <v>30.55</v>
       </c>
       <c r="G68" s="13" t="n">
-        <v>21.79</v>
+        <v>21.75</v>
       </c>
       <c r="H68" s="13" t="n">
-        <v>18.98</v>
+        <v>18.55</v>
       </c>
       <c r="I68" s="13" t="n"/>
       <c r="J68" s="13" t="n">
@@ -5874,10 +5874,10 @@
         <v>4.93</v>
       </c>
       <c r="U68" s="13" t="n">
-        <v>3.84</v>
+        <v>3.81</v>
       </c>
       <c r="V68" s="13" t="n">
-        <v>3.44</v>
+        <v>3.41</v>
       </c>
       <c r="W68" s="13" t="n"/>
       <c r="X68" s="13" t="n">
@@ -5893,7 +5893,7 @@
         <v>16.82</v>
       </c>
       <c r="AB68" s="13" t="n">
-        <v>18.59</v>
+        <v>18.9</v>
       </c>
       <c r="AC68" s="13" t="n">
         <v>20.2</v>
@@ -5915,7 +5915,7 @@
         <v>1.74</v>
       </c>
       <c r="AJ68" s="13" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="AK68" s="13" t="n"/>
     </row>
@@ -5976,7 +5976,7 @@
         </is>
       </c>
       <c r="B72" s="8" t="n">
-        <v>3236</v>
+        <v>3142</v>
       </c>
       <c r="C72" s="9" t="n">
         <v>10.61</v>
@@ -5994,7 +5994,7 @@
         <v>7.01</v>
       </c>
       <c r="H72" s="10" t="n">
-        <v>6.14</v>
+        <v>5.95</v>
       </c>
       <c r="I72" s="10" t="n"/>
       <c r="J72" s="9" t="n">
@@ -6028,7 +6028,7 @@
         <v>0.87</v>
       </c>
       <c r="V72" s="10" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W72" s="10" t="n"/>
       <c r="X72" s="9" t="n">
@@ -6063,10 +6063,10 @@
         <v>1.25</v>
       </c>
       <c r="AI72" s="10" t="n">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="AJ72" s="10" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="AK72" s="10" t="n"/>
     </row>
@@ -6077,7 +6077,7 @@
         </is>
       </c>
       <c r="B73" s="8" t="n">
-        <v>3572</v>
+        <v>3514</v>
       </c>
       <c r="C73" s="9" t="n">
         <v>5.38</v>
@@ -6095,7 +6095,7 @@
         <v>8.460000000000001</v>
       </c>
       <c r="H73" s="10" t="n">
-        <v>7.9</v>
+        <v>7.77</v>
       </c>
       <c r="I73" s="10" t="n"/>
       <c r="J73" s="9" t="n">
@@ -6129,7 +6129,7 @@
         <v>0.61</v>
       </c>
       <c r="V73" s="10" t="n">
-        <v>0.59</v>
+        <v>0.58</v>
       </c>
       <c r="W73" s="10" t="n"/>
       <c r="X73" s="9" t="n">
@@ -6164,10 +6164,10 @@
         <v>0.63</v>
       </c>
       <c r="AI73" s="10" t="n">
-        <v>0.5</v>
+        <v>0.49</v>
       </c>
       <c r="AJ73" s="10" t="n">
-        <v>0.48</v>
+        <v>0.47</v>
       </c>
       <c r="AK73" s="10" t="n"/>
     </row>
@@ -6178,7 +6178,7 @@
         </is>
       </c>
       <c r="B74" s="8" t="n">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="C74" s="9" t="n">
         <v>7.23</v>
@@ -6259,7 +6259,7 @@
         </is>
       </c>
       <c r="B75" s="8" t="n">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C75" s="9" t="n">
         <v>5.78</v>
@@ -6277,7 +6277,7 @@
         <v>4.02</v>
       </c>
       <c r="H75" s="10" t="n">
-        <v>4.37</v>
+        <v>4.27</v>
       </c>
       <c r="I75" s="10" t="n"/>
       <c r="J75" s="9" t="n">
@@ -6311,7 +6311,7 @@
         <v>0.54</v>
       </c>
       <c r="V75" s="10" t="n">
-        <v>0.51</v>
+        <v>0.5</v>
       </c>
       <c r="W75" s="10" t="n"/>
       <c r="X75" s="9" t="n">
@@ -6346,10 +6346,10 @@
         <v>0.59</v>
       </c>
       <c r="AI75" s="10" t="n">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="AJ75" s="10" t="n">
-        <v>0.32</v>
+        <v>0.31</v>
       </c>
       <c r="AK75" s="10" t="n"/>
     </row>
@@ -6360,7 +6360,7 @@
         </is>
       </c>
       <c r="B76" s="8" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C76" s="9" t="n">
         <v>7.57</v>
@@ -6537,7 +6537,7 @@
         </is>
       </c>
       <c r="B79" s="8" t="n">
-        <v>327586</v>
+        <v>319652</v>
       </c>
       <c r="C79" s="9" t="n">
         <v>18.45</v>
@@ -6552,10 +6552,10 @@
         <v>30</v>
       </c>
       <c r="G79" s="10" t="n">
-        <v>25.76</v>
+        <v>25.14</v>
       </c>
       <c r="H79" s="10" t="n">
-        <v>21.61</v>
+        <v>21.08</v>
       </c>
       <c r="I79" s="10" t="n"/>
       <c r="J79" s="9" t="n">
@@ -6586,10 +6586,10 @@
         <v>12.5</v>
       </c>
       <c r="U79" s="10" t="n">
-        <v>10.66</v>
+        <v>10.4</v>
       </c>
       <c r="V79" s="10" t="n">
-        <v>7.81</v>
+        <v>7.62</v>
       </c>
       <c r="W79" s="10" t="n"/>
       <c r="X79" s="9" t="n">
@@ -6624,10 +6624,10 @@
         <v>3.94</v>
       </c>
       <c r="AI79" s="10" t="n">
-        <v>4.12</v>
+        <v>4.02</v>
       </c>
       <c r="AJ79" s="10" t="n">
-        <v>3.69</v>
+        <v>3.61</v>
       </c>
       <c r="AK79" s="10" t="n"/>
     </row>
@@ -6638,7 +6638,7 @@
         </is>
       </c>
       <c r="B80" s="8" t="n">
-        <v>174004</v>
+        <v>174688</v>
       </c>
       <c r="C80" s="9" t="n">
         <v>16.58</v>
@@ -6653,10 +6653,10 @@
         <v>24.83</v>
       </c>
       <c r="G80" s="10" t="n">
-        <v>35.53</v>
+        <v>35.67</v>
       </c>
       <c r="H80" s="10" t="n">
-        <v>27.99</v>
+        <v>28.1</v>
       </c>
       <c r="I80" s="10" t="n"/>
       <c r="J80" s="9" t="n">
@@ -6687,10 +6687,10 @@
         <v>4.81</v>
       </c>
       <c r="U80" s="10" t="n">
-        <v>5.98</v>
+        <v>6.01</v>
       </c>
       <c r="V80" s="10" t="n">
-        <v>5.26</v>
+        <v>5.28</v>
       </c>
       <c r="W80" s="10" t="n"/>
       <c r="X80" s="9" t="n">
@@ -6725,10 +6725,10 @@
         <v>2.79</v>
       </c>
       <c r="AI80" s="10" t="n">
-        <v>4.23</v>
+        <v>4.25</v>
       </c>
       <c r="AJ80" s="10" t="n">
-        <v>3.9</v>
+        <v>3.91</v>
       </c>
       <c r="AK80" s="10" t="n"/>
     </row>
@@ -6739,7 +6739,7 @@
         </is>
       </c>
       <c r="B81" s="8" t="n">
-        <v>14383</v>
+        <v>14271</v>
       </c>
       <c r="C81" s="9" t="n">
         <v>10.64</v>
@@ -6754,10 +6754,10 @@
         <v>22.45</v>
       </c>
       <c r="G81" s="10" t="n">
-        <v>25.68</v>
+        <v>25.48</v>
       </c>
       <c r="H81" s="10" t="n">
-        <v>16.84</v>
+        <v>16.71</v>
       </c>
       <c r="I81" s="10" t="n"/>
       <c r="J81" s="9" t="n">
@@ -6788,10 +6788,10 @@
         <v>1.48</v>
       </c>
       <c r="U81" s="10" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="V81" s="10" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="W81" s="10" t="n"/>
       <c r="X81" s="9" t="n">
@@ -6826,7 +6826,7 @@
         <v>0.63</v>
       </c>
       <c r="AI81" s="10" t="n">
-        <v>0.79</v>
+        <v>0.78</v>
       </c>
       <c r="AJ81" s="10" t="n">
         <v>0.75</v>
@@ -6840,7 +6840,7 @@
         </is>
       </c>
       <c r="B82" s="8" t="n">
-        <v>70101</v>
+        <v>69335</v>
       </c>
       <c r="C82" s="9" t="n">
         <v>11.71</v>
@@ -6855,10 +6855,10 @@
         <v>20.48</v>
       </c>
       <c r="G82" s="10" t="n">
-        <v>21.43</v>
+        <v>21.2</v>
       </c>
       <c r="H82" s="10" t="n">
-        <v>18.24</v>
+        <v>18.04</v>
       </c>
       <c r="I82" s="10" t="n"/>
       <c r="J82" s="9" t="n">
@@ -6889,10 +6889,10 @@
         <v>5.69</v>
       </c>
       <c r="U82" s="10" t="n">
-        <v>6</v>
+        <v>5.93</v>
       </c>
       <c r="V82" s="10" t="n">
-        <v>4.71</v>
+        <v>4.66</v>
       </c>
       <c r="W82" s="10" t="n"/>
       <c r="X82" s="9" t="n">
@@ -6927,10 +6927,10 @@
         <v>3.17</v>
       </c>
       <c r="AI82" s="10" t="n">
-        <v>3.88</v>
+        <v>3.84</v>
       </c>
       <c r="AJ82" s="10" t="n">
-        <v>3.52</v>
+        <v>3.49</v>
       </c>
       <c r="AK82" s="10" t="n"/>
     </row>
@@ -6948,7 +6948,7 @@
         </is>
       </c>
       <c r="B84" s="8" t="n">
-        <v>38546</v>
+        <v>38449</v>
       </c>
       <c r="C84" s="9" t="n"/>
       <c r="D84" s="9" t="n">
@@ -6964,10 +6964,10 @@
         <v>14.4</v>
       </c>
       <c r="H84" s="10" t="n">
-        <v>15.01</v>
+        <v>14.97</v>
       </c>
       <c r="I84" s="10" t="n">
-        <v>13.57</v>
+        <v>13.53</v>
       </c>
       <c r="J84" s="9" t="n"/>
       <c r="K84" s="9" t="n">
@@ -7039,7 +7039,7 @@
         <v>1.36</v>
       </c>
       <c r="AK84" s="10" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="85">
@@ -7049,7 +7049,7 @@
         </is>
       </c>
       <c r="B85" s="8" t="n">
-        <v>7107</v>
+        <v>7160</v>
       </c>
       <c r="C85" s="9" t="n"/>
       <c r="D85" s="9" t="n">
@@ -7065,10 +7065,10 @@
         <v>15.32</v>
       </c>
       <c r="H85" s="10" t="n">
-        <v>12.18</v>
+        <v>12.27</v>
       </c>
       <c r="I85" s="10" t="n">
-        <v>10.56</v>
+        <v>10.64</v>
       </c>
       <c r="J85" s="9" t="n"/>
       <c r="K85" s="9" t="n">
@@ -7099,10 +7099,10 @@
         <v>1.25</v>
       </c>
       <c r="V85" s="10" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W85" s="10" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X85" s="9" t="n"/>
       <c r="Y85" s="9" t="n">
@@ -7137,10 +7137,10 @@
         <v>0.8</v>
       </c>
       <c r="AJ85" s="10" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="AK85" s="10" t="n">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="86">
@@ -7157,7 +7157,7 @@
         </is>
       </c>
       <c r="B87" s="8" t="n">
-        <v>63992</v>
+        <v>63165</v>
       </c>
       <c r="C87" s="9" t="n">
         <v>11.71</v>
@@ -7172,10 +7172,10 @@
         <v>17.46</v>
       </c>
       <c r="G87" s="10" t="n">
-        <v>14.29</v>
+        <v>14.13</v>
       </c>
       <c r="H87" s="10" t="n">
-        <v>12.14</v>
+        <v>12</v>
       </c>
       <c r="I87" s="10" t="n"/>
       <c r="J87" s="9" t="n">
@@ -7206,10 +7206,10 @@
         <v>3.37</v>
       </c>
       <c r="U87" s="10" t="n">
-        <v>3.14</v>
+        <v>3.08</v>
       </c>
       <c r="V87" s="10" t="n">
-        <v>2.77</v>
+        <v>2.7</v>
       </c>
       <c r="W87" s="10" t="n"/>
       <c r="X87" s="9" t="n">
@@ -7225,10 +7225,10 @@
         <v>18.5</v>
       </c>
       <c r="AB87" s="10" t="n">
-        <v>23.32</v>
+        <v>23.21</v>
       </c>
       <c r="AC87" s="10" t="n">
-        <v>24.27</v>
+        <v>23.96</v>
       </c>
       <c r="AD87" s="10" t="n"/>
       <c r="AE87" s="9" t="n">
@@ -7244,10 +7244,10 @@
         <v>1.26</v>
       </c>
       <c r="AI87" s="10" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AJ87" s="10" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AK87" s="10" t="n"/>
     </row>
@@ -7265,7 +7265,7 @@
         </is>
       </c>
       <c r="B89" s="8" t="n">
-        <v>25291</v>
+        <v>25225</v>
       </c>
       <c r="C89" s="9" t="n">
         <v>31.28</v>
@@ -7366,7 +7366,7 @@
         </is>
       </c>
       <c r="B90" s="8" t="n">
-        <v>12599</v>
+        <v>12566</v>
       </c>
       <c r="C90" s="9" t="n">
         <v>13.89</v>
@@ -7483,7 +7483,7 @@
         <v>7.01</v>
       </c>
       <c r="H91" s="13" t="n">
-        <v>6.14</v>
+        <v>5.95</v>
       </c>
       <c r="I91" s="13" t="n"/>
       <c r="J91" s="13" t="n">
@@ -7517,7 +7517,7 @@
         <v>0.61</v>
       </c>
       <c r="V91" s="13" t="n">
-        <v>0.59</v>
+        <v>0.58</v>
       </c>
       <c r="W91" s="13" t="n"/>
       <c r="X91" s="13" t="n">
@@ -7552,10 +7552,10 @@
         <v>0.53</v>
       </c>
       <c r="AI91" s="13" t="n">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="AJ91" s="13" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="AK91" s="13" t="n"/>
     </row>
@@ -7579,10 +7579,10 @@
         <v>23.64</v>
       </c>
       <c r="G92" s="13" t="n">
-        <v>25.72</v>
+        <v>25.31</v>
       </c>
       <c r="H92" s="13" t="n">
-        <v>19.92</v>
+        <v>19.56</v>
       </c>
       <c r="I92" s="13" t="n"/>
       <c r="J92" s="13" t="n">
@@ -7613,10 +7613,10 @@
         <v>5.25</v>
       </c>
       <c r="U92" s="13" t="n">
-        <v>5.99</v>
+        <v>5.97</v>
       </c>
       <c r="V92" s="13" t="n">
-        <v>4.98</v>
+        <v>4.97</v>
       </c>
       <c r="W92" s="13" t="n"/>
       <c r="X92" s="13" t="n">
@@ -7651,10 +7651,10 @@
         <v>2.98</v>
       </c>
       <c r="AI92" s="13" t="n">
-        <v>4</v>
+        <v>3.93</v>
       </c>
       <c r="AJ92" s="13" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="AK92" s="13" t="n"/>
     </row>
@@ -7679,10 +7679,10 @@
         <v>14.86</v>
       </c>
       <c r="H93" s="13" t="n">
-        <v>13.59</v>
+        <v>13.62</v>
       </c>
       <c r="I93" s="13" t="n">
-        <v>12.07</v>
+        <v>12.09</v>
       </c>
       <c r="J93" s="13" t="n"/>
       <c r="K93" s="13" t="n">
@@ -7777,10 +7777,10 @@
         <v>17.46</v>
       </c>
       <c r="G94" s="13" t="n">
-        <v>14.29</v>
+        <v>14.13</v>
       </c>
       <c r="H94" s="13" t="n">
-        <v>12.14</v>
+        <v>12</v>
       </c>
       <c r="I94" s="13" t="n"/>
       <c r="J94" s="13" t="n">
@@ -7811,10 +7811,10 @@
         <v>3.37</v>
       </c>
       <c r="U94" s="13" t="n">
-        <v>3.14</v>
+        <v>3.08</v>
       </c>
       <c r="V94" s="13" t="n">
-        <v>2.77</v>
+        <v>2.7</v>
       </c>
       <c r="W94" s="13" t="n"/>
       <c r="X94" s="13" t="n">
@@ -7830,10 +7830,10 @@
         <v>18.5</v>
       </c>
       <c r="AB94" s="13" t="n">
-        <v>23.32</v>
+        <v>23.21</v>
       </c>
       <c r="AC94" s="13" t="n">
-        <v>24.27</v>
+        <v>23.96</v>
       </c>
       <c r="AD94" s="13" t="n"/>
       <c r="AE94" s="13" t="n">
@@ -7849,10 +7849,10 @@
         <v>1.26</v>
       </c>
       <c r="AI94" s="13" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AJ94" s="13" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AK94" s="13" t="n"/>
     </row>
@@ -7978,10 +7978,10 @@
         <v>14.86</v>
       </c>
       <c r="H96" s="13" t="n">
-        <v>12.16</v>
+        <v>12.18</v>
       </c>
       <c r="I96" s="13" t="n">
-        <v>12.07</v>
+        <v>12.09</v>
       </c>
       <c r="J96" s="13" t="n">
         <v>7.18</v>
@@ -8055,7 +8055,7 @@
         <v>0.97</v>
       </c>
       <c r="AI96" s="13" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AJ96" s="13" t="n">
         <v>0.95</v>
@@ -8184,7 +8184,7 @@
         </is>
       </c>
       <c r="E2" s="7" t="n">
-        <v>24179</v>
+        <v>23448</v>
       </c>
       <c r="F2" s="9" t="n"/>
       <c r="G2" s="9" t="n">
@@ -8200,7 +8200,7 @@
         <v>10.15</v>
       </c>
       <c r="K2" s="9" t="n">
-        <v>8.76</v>
+        <v>8.49</v>
       </c>
       <c r="L2" s="9" t="n"/>
     </row>
@@ -8226,7 +8226,7 @@
         </is>
       </c>
       <c r="E3" s="7" t="n">
-        <v>12801</v>
+        <v>12442</v>
       </c>
       <c r="F3" s="9" t="n"/>
       <c r="G3" s="9" t="n">
@@ -8242,7 +8242,7 @@
         <v>8.69</v>
       </c>
       <c r="K3" s="9" t="n">
-        <v>8.949999999999999</v>
+        <v>8.69</v>
       </c>
       <c r="L3" s="9" t="n"/>
     </row>
@@ -8268,7 +8268,7 @@
         </is>
       </c>
       <c r="E4" s="7" t="n">
-        <v>10860</v>
+        <v>10677</v>
       </c>
       <c r="F4" s="9" t="n"/>
       <c r="G4" s="9" t="n"/>
@@ -8282,7 +8282,7 @@
         <v>15.88</v>
       </c>
       <c r="K4" s="9" t="n">
-        <v>9.949999999999999</v>
+        <v>9.77</v>
       </c>
       <c r="L4" s="9" t="n"/>
     </row>
@@ -8308,7 +8308,7 @@
         </is>
       </c>
       <c r="E5" s="7" t="n">
-        <v>13249</v>
+        <v>13048</v>
       </c>
       <c r="F5" s="9" t="n"/>
       <c r="G5" s="9" t="n">
@@ -8324,7 +8324,7 @@
         <v>4.46</v>
       </c>
       <c r="K5" s="9" t="n">
-        <v>4.11</v>
+        <v>4.04</v>
       </c>
       <c r="L5" s="9" t="n"/>
     </row>
@@ -8350,7 +8350,7 @@
         </is>
       </c>
       <c r="E6" s="7" t="n">
-        <v>1071</v>
+        <v>1064</v>
       </c>
       <c r="F6" s="9" t="n"/>
       <c r="G6" s="9" t="n"/>
@@ -8362,7 +8362,7 @@
         <v>4.77</v>
       </c>
       <c r="K6" s="9" t="n">
-        <v>4.75</v>
+        <v>4.72</v>
       </c>
       <c r="L6" s="9" t="n"/>
     </row>
@@ -8388,7 +8388,7 @@
         </is>
       </c>
       <c r="E7" s="7" t="n">
-        <v>840</v>
+        <v>829</v>
       </c>
       <c r="F7" s="9" t="n"/>
       <c r="G7" s="9" t="n"/>
@@ -8426,7 +8426,7 @@
         </is>
       </c>
       <c r="E8" s="7" t="n">
-        <v>39658</v>
+        <v>39556</v>
       </c>
       <c r="F8" s="9" t="n">
         <v>577.76</v>
@@ -8470,7 +8470,7 @@
         </is>
       </c>
       <c r="E9" s="7" t="n">
-        <v>15029</v>
+        <v>14877</v>
       </c>
       <c r="F9" s="9" t="n">
         <v>9.9</v>
@@ -8485,10 +8485,10 @@
         <v>8.640000000000001</v>
       </c>
       <c r="J9" s="9" t="n">
-        <v>9.17</v>
+        <v>9.08</v>
       </c>
       <c r="K9" s="9" t="n">
-        <v>8.26</v>
+        <v>8.18</v>
       </c>
       <c r="L9" s="9" t="n"/>
     </row>
@@ -8514,7 +8514,7 @@
         </is>
       </c>
       <c r="E10" s="7" t="n">
-        <v>2320</v>
+        <v>2322</v>
       </c>
       <c r="F10" s="9" t="n">
         <v>13.53</v>
@@ -8529,10 +8529,10 @@
         <v>16.46</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>13.35</v>
+        <v>13.37</v>
       </c>
       <c r="K10" s="9" t="n">
-        <v>6.52</v>
+        <v>6.53</v>
       </c>
       <c r="L10" s="9" t="n"/>
     </row>
@@ -8558,7 +8558,7 @@
         </is>
       </c>
       <c r="E11" s="7" t="n">
-        <v>77441</v>
+        <v>75750</v>
       </c>
       <c r="F11" s="9" t="n"/>
       <c r="G11" s="9" t="n">
@@ -8574,10 +8574,10 @@
         <v>57.81</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>26.83</v>
+        <v>26.24</v>
       </c>
       <c r="L11" s="9" t="n">
-        <v>23.61</v>
+        <v>23.09</v>
       </c>
     </row>
     <row r="12">
@@ -8602,7 +8602,7 @@
         </is>
       </c>
       <c r="E12" s="7" t="n">
-        <v>11529</v>
+        <v>11415</v>
       </c>
       <c r="F12" s="9" t="n"/>
       <c r="G12" s="9" t="n">
@@ -8618,10 +8618,10 @@
         <v>22.39</v>
       </c>
       <c r="K12" s="9" t="n">
-        <v>15.19</v>
+        <v>15.03</v>
       </c>
       <c r="L12" s="9" t="n">
-        <v>13.27</v>
+        <v>13.14</v>
       </c>
     </row>
     <row r="13">
@@ -8646,7 +8646,7 @@
         </is>
       </c>
       <c r="E13" s="7" t="n">
-        <v>16564</v>
+        <v>16109</v>
       </c>
       <c r="F13" s="9" t="n"/>
       <c r="G13" s="9" t="n">
@@ -8660,10 +8660,10 @@
         <v>20.66</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>13.85</v>
+        <v>13.46</v>
       </c>
       <c r="L13" s="9" t="n">
-        <v>15.85</v>
+        <v>15.41</v>
       </c>
     </row>
     <row r="14">
@@ -8688,7 +8688,7 @@
         </is>
       </c>
       <c r="E14" s="7" t="n">
-        <v>2259</v>
+        <v>2276</v>
       </c>
       <c r="F14" s="9" t="n"/>
       <c r="G14" s="9" t="n">
@@ -8704,10 +8704,10 @@
         <v>14.63</v>
       </c>
       <c r="K14" s="9" t="n">
-        <v>9.83</v>
+        <v>9.9</v>
       </c>
       <c r="L14" s="9" t="n">
-        <v>9.449999999999999</v>
+        <v>9.52</v>
       </c>
     </row>
     <row r="15">
@@ -8772,7 +8772,7 @@
         </is>
       </c>
       <c r="E16" s="7" t="n">
-        <v>4396</v>
+        <v>4374</v>
       </c>
       <c r="F16" s="9" t="n"/>
       <c r="G16" s="9" t="n"/>
@@ -8783,10 +8783,10 @@
         <v>44.03</v>
       </c>
       <c r="J16" s="9" t="n">
-        <v>22.09</v>
+        <v>22</v>
       </c>
       <c r="K16" s="9" t="n">
-        <v>14.69</v>
+        <v>14.63</v>
       </c>
       <c r="L16" s="9" t="n"/>
     </row>
@@ -8812,7 +8812,7 @@
         </is>
       </c>
       <c r="E17" s="7" t="n">
-        <v>10943</v>
+        <v>10755</v>
       </c>
       <c r="F17" s="9" t="n">
         <v>15.9</v>
@@ -8827,10 +8827,10 @@
         <v>22.06</v>
       </c>
       <c r="J17" s="9" t="n">
-        <v>15.07</v>
+        <v>14.81</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>13.27</v>
+        <v>13.04</v>
       </c>
       <c r="L17" s="9" t="n"/>
     </row>
@@ -8856,7 +8856,7 @@
         </is>
       </c>
       <c r="E18" s="7" t="n">
-        <v>1236</v>
+        <v>1240</v>
       </c>
       <c r="F18" s="9" t="n"/>
       <c r="G18" s="9" t="n"/>
@@ -8868,10 +8868,10 @@
       </c>
       <c r="J18" s="9" t="n"/>
       <c r="K18" s="9" t="n">
-        <v>18.35</v>
+        <v>18.42</v>
       </c>
       <c r="L18" s="9" t="n">
-        <v>16.17</v>
+        <v>16.23</v>
       </c>
     </row>
     <row r="19">
@@ -8896,7 +8896,7 @@
         </is>
       </c>
       <c r="E19" s="7" t="n">
-        <v>6655</v>
+        <v>6502</v>
       </c>
       <c r="F19" s="9" t="n"/>
       <c r="G19" s="9" t="n"/>
@@ -8910,7 +8910,7 @@
         <v>25.22</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>21</v>
+        <v>20.5</v>
       </c>
       <c r="L19" s="9" t="n"/>
     </row>
@@ -8936,7 +8936,7 @@
         </is>
       </c>
       <c r="E20" s="7" t="n">
-        <v>926</v>
+        <v>913</v>
       </c>
       <c r="F20" s="9" t="n">
         <v>14.21</v>
@@ -8954,7 +8954,7 @@
         <v>9.6</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>7.22</v>
+        <v>7.11</v>
       </c>
       <c r="L20" s="9" t="n"/>
     </row>
@@ -8980,7 +8980,7 @@
         </is>
       </c>
       <c r="E21" s="7" t="n">
-        <v>2033</v>
+        <v>1989</v>
       </c>
       <c r="F21" s="9" t="n"/>
       <c r="G21" s="9" t="n"/>
@@ -8994,7 +8994,7 @@
         <v>14.38</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>8.869999999999999</v>
+        <v>8.67</v>
       </c>
       <c r="L21" s="9" t="n"/>
     </row>
@@ -9020,7 +9020,7 @@
         </is>
       </c>
       <c r="E22" s="7" t="n">
-        <v>613</v>
+        <v>601</v>
       </c>
       <c r="F22" s="9" t="n">
         <v>23.46</v>
@@ -9036,7 +9036,7 @@
         <v>7.02</v>
       </c>
       <c r="K22" s="9" t="n">
-        <v>5.72</v>
+        <v>5.61</v>
       </c>
       <c r="L22" s="9" t="n"/>
     </row>
@@ -9062,7 +9062,7 @@
         </is>
       </c>
       <c r="E23" s="7" t="n">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="F23" s="9" t="n">
         <v>37.11</v>
@@ -9080,7 +9080,7 @@
         <v>4.53</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>4.49</v>
+        <v>4.42</v>
       </c>
       <c r="L23" s="9" t="n"/>
     </row>
@@ -9106,7 +9106,7 @@
         </is>
       </c>
       <c r="E24" s="7" t="n">
-        <v>7526</v>
+        <v>7187</v>
       </c>
       <c r="F24" s="9" t="n">
         <v>41.88</v>
@@ -9124,7 +9124,7 @@
         <v>43.97</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>22.83</v>
+        <v>21.78</v>
       </c>
       <c r="L24" s="9" t="n"/>
     </row>
@@ -9150,7 +9150,7 @@
         </is>
       </c>
       <c r="E25" s="7" t="n">
-        <v>30784</v>
+        <v>29608</v>
       </c>
       <c r="F25" s="9" t="n">
         <v>19.31</v>
@@ -9168,7 +9168,7 @@
         <v>17.98</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>13.7</v>
+        <v>13.17</v>
       </c>
       <c r="L25" s="9" t="n"/>
     </row>
@@ -9194,7 +9194,7 @@
         </is>
       </c>
       <c r="E26" s="7" t="n">
-        <v>7847</v>
+        <v>7178</v>
       </c>
       <c r="F26" s="9" t="n">
         <v>16.34</v>
@@ -9212,7 +9212,7 @@
         <v>29.67</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>20.03</v>
+        <v>18.31</v>
       </c>
       <c r="L26" s="9" t="n"/>
     </row>
@@ -9238,7 +9238,7 @@
         </is>
       </c>
       <c r="E27" s="7" t="n">
-        <v>9366</v>
+        <v>8640</v>
       </c>
       <c r="F27" s="9" t="n"/>
       <c r="G27" s="9" t="n">
@@ -9254,7 +9254,7 @@
         <v>91.62</v>
       </c>
       <c r="K27" s="9" t="n">
-        <v>28.49</v>
+        <v>26.25</v>
       </c>
       <c r="L27" s="9" t="n"/>
     </row>
@@ -9280,7 +9280,7 @@
         </is>
       </c>
       <c r="E28" s="7" t="n">
-        <v>6819</v>
+        <v>6595</v>
       </c>
       <c r="F28" s="9" t="n">
         <v>15.67</v>
@@ -9298,7 +9298,7 @@
         <v>11.27</v>
       </c>
       <c r="K28" s="9" t="n">
-        <v>9.890000000000001</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="L28" s="9" t="n"/>
     </row>
@@ -9324,7 +9324,7 @@
         </is>
       </c>
       <c r="E29" s="7" t="n">
-        <v>135089</v>
+        <v>138357</v>
       </c>
       <c r="F29" s="9" t="n">
         <v>21.56</v>
@@ -9339,10 +9339,10 @@
         <v>22.08</v>
       </c>
       <c r="J29" s="9" t="n">
-        <v>19.28</v>
+        <v>19.73</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>17.83</v>
+        <v>18.24</v>
       </c>
       <c r="L29" s="9" t="n"/>
     </row>
@@ -9368,7 +9368,7 @@
         </is>
       </c>
       <c r="E30" s="7" t="n">
-        <v>78432</v>
+        <v>78303</v>
       </c>
       <c r="F30" s="9" t="n">
         <v>17.07</v>
@@ -9383,10 +9383,10 @@
         <v>19.36</v>
       </c>
       <c r="J30" s="9" t="n">
-        <v>18.57</v>
+        <v>18.54</v>
       </c>
       <c r="K30" s="9" t="n">
-        <v>18.37</v>
+        <v>18.36</v>
       </c>
       <c r="L30" s="9" t="n"/>
     </row>
@@ -9412,7 +9412,7 @@
         </is>
       </c>
       <c r="E31" s="7" t="n">
-        <v>94850</v>
+        <v>94463</v>
       </c>
       <c r="F31" s="9" t="n">
         <v>20.08</v>
@@ -9427,10 +9427,10 @@
         <v>21.62</v>
       </c>
       <c r="J31" s="9" t="n">
-        <v>20.64</v>
+        <v>20.55</v>
       </c>
       <c r="K31" s="9" t="n">
-        <v>18.82</v>
+        <v>18.75</v>
       </c>
       <c r="L31" s="9" t="n"/>
     </row>
@@ -9456,7 +9456,7 @@
         </is>
       </c>
       <c r="E32" s="7" t="n">
-        <v>261357</v>
+        <v>256390</v>
       </c>
       <c r="F32" s="9" t="n">
         <v>28.47</v>
@@ -9471,10 +9471,10 @@
         <v>36.57</v>
       </c>
       <c r="J32" s="9" t="n">
-        <v>25.59</v>
+        <v>25.03</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>24.26</v>
+        <v>23.78</v>
       </c>
       <c r="L32" s="9" t="n"/>
     </row>
@@ -9500,7 +9500,7 @@
         </is>
       </c>
       <c r="E33" s="7" t="n">
-        <v>10943</v>
+        <v>10755</v>
       </c>
       <c r="F33" s="9" t="n">
         <v>15.9</v>
@@ -9515,10 +9515,10 @@
         <v>22.06</v>
       </c>
       <c r="J33" s="9" t="n">
-        <v>15.07</v>
+        <v>14.81</v>
       </c>
       <c r="K33" s="9" t="n">
-        <v>13.27</v>
+        <v>13.04</v>
       </c>
       <c r="L33" s="9" t="n"/>
     </row>
@@ -9544,7 +9544,7 @@
         </is>
       </c>
       <c r="E34" s="7" t="n">
-        <v>52319</v>
+        <v>52463</v>
       </c>
       <c r="F34" s="9" t="n">
         <v>17.03</v>
@@ -9559,10 +9559,10 @@
         <v>102.9</v>
       </c>
       <c r="J34" s="9" t="n">
-        <v>27.23</v>
+        <v>27.34</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>19.15</v>
+        <v>19.23</v>
       </c>
       <c r="L34" s="9" t="n"/>
     </row>
@@ -9588,7 +9588,7 @@
         </is>
       </c>
       <c r="E35" s="7" t="n">
-        <v>75701</v>
+        <v>75806</v>
       </c>
       <c r="F35" s="9" t="n">
         <v>16.56</v>
@@ -9603,10 +9603,10 @@
         <v>24.33</v>
       </c>
       <c r="J35" s="9" t="n">
-        <v>22.93</v>
+        <v>22.94</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>20.16</v>
+        <v>20.18</v>
       </c>
       <c r="L35" s="9" t="n"/>
     </row>
@@ -9632,7 +9632,7 @@
         </is>
       </c>
       <c r="E36" s="7" t="n">
-        <v>31323</v>
+        <v>31374</v>
       </c>
       <c r="F36" s="9" t="n">
         <v>5</v>
@@ -9647,10 +9647,10 @@
         <v>23.17</v>
       </c>
       <c r="J36" s="9" t="n">
-        <v>20.06</v>
+        <v>20.12</v>
       </c>
       <c r="K36" s="9" t="n">
-        <v>16.73</v>
+        <v>16.78</v>
       </c>
       <c r="L36" s="9" t="n"/>
     </row>
@@ -9676,7 +9676,7 @@
         </is>
       </c>
       <c r="E37" s="7" t="n">
-        <v>34602</v>
+        <v>35175</v>
       </c>
       <c r="F37" s="9" t="n">
         <v>24.79</v>
@@ -9691,10 +9691,10 @@
         <v>45.89</v>
       </c>
       <c r="J37" s="9" t="n">
-        <v>42.49</v>
+        <v>41.65</v>
       </c>
       <c r="K37" s="9" t="n">
-        <v>33.35</v>
+        <v>33.96</v>
       </c>
       <c r="L37" s="9" t="n"/>
     </row>
@@ -9720,7 +9720,7 @@
         </is>
       </c>
       <c r="E38" s="7" t="n">
-        <v>3236</v>
+        <v>3142</v>
       </c>
       <c r="F38" s="9" t="n">
         <v>10.61</v>
@@ -9738,7 +9738,7 @@
         <v>7.01</v>
       </c>
       <c r="K38" s="9" t="n">
-        <v>6.14</v>
+        <v>5.95</v>
       </c>
       <c r="L38" s="9" t="n"/>
     </row>
@@ -9764,7 +9764,7 @@
         </is>
       </c>
       <c r="E39" s="7" t="n">
-        <v>3572</v>
+        <v>3514</v>
       </c>
       <c r="F39" s="9" t="n">
         <v>5.38</v>
@@ -9782,7 +9782,7 @@
         <v>8.460000000000001</v>
       </c>
       <c r="K39" s="9" t="n">
-        <v>7.9</v>
+        <v>7.77</v>
       </c>
       <c r="L39" s="9" t="n"/>
     </row>
@@ -9808,7 +9808,7 @@
         </is>
       </c>
       <c r="E40" s="7" t="n">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="F40" s="9" t="n">
         <v>7.23</v>
@@ -9844,7 +9844,7 @@
         </is>
       </c>
       <c r="E41" s="7" t="n">
-        <v>327586</v>
+        <v>319652</v>
       </c>
       <c r="F41" s="9" t="n">
         <v>18.45</v>
@@ -9859,10 +9859,10 @@
         <v>30</v>
       </c>
       <c r="J41" s="9" t="n">
-        <v>25.76</v>
+        <v>25.14</v>
       </c>
       <c r="K41" s="9" t="n">
-        <v>21.61</v>
+        <v>21.08</v>
       </c>
       <c r="L41" s="9" t="n"/>
     </row>
@@ -9888,7 +9888,7 @@
         </is>
       </c>
       <c r="E42" s="7" t="n">
-        <v>174004</v>
+        <v>174688</v>
       </c>
       <c r="F42" s="9" t="n">
         <v>16.58</v>
@@ -9903,10 +9903,10 @@
         <v>24.83</v>
       </c>
       <c r="J42" s="9" t="n">
-        <v>35.53</v>
+        <v>35.67</v>
       </c>
       <c r="K42" s="9" t="n">
-        <v>27.99</v>
+        <v>28.1</v>
       </c>
       <c r="L42" s="9" t="n"/>
     </row>
@@ -9932,7 +9932,7 @@
         </is>
       </c>
       <c r="E43" s="7" t="n">
-        <v>14383</v>
+        <v>14271</v>
       </c>
       <c r="F43" s="9" t="n">
         <v>10.64</v>
@@ -9947,10 +9947,10 @@
         <v>22.45</v>
       </c>
       <c r="J43" s="9" t="n">
-        <v>25.68</v>
+        <v>25.48</v>
       </c>
       <c r="K43" s="9" t="n">
-        <v>16.84</v>
+        <v>16.71</v>
       </c>
       <c r="L43" s="9" t="n"/>
     </row>
@@ -9976,7 +9976,7 @@
         </is>
       </c>
       <c r="E44" s="7" t="n">
-        <v>38546</v>
+        <v>38449</v>
       </c>
       <c r="F44" s="9" t="n"/>
       <c r="G44" s="9" t="n">
@@ -9992,10 +9992,10 @@
         <v>14.4</v>
       </c>
       <c r="K44" s="9" t="n">
-        <v>15.01</v>
+        <v>14.97</v>
       </c>
       <c r="L44" s="9" t="n">
-        <v>13.57</v>
+        <v>13.53</v>
       </c>
     </row>
     <row r="45">
@@ -10020,7 +10020,7 @@
         </is>
       </c>
       <c r="E45" s="7" t="n">
-        <v>7107</v>
+        <v>7160</v>
       </c>
       <c r="F45" s="9" t="n"/>
       <c r="G45" s="9" t="n">
@@ -10036,10 +10036,10 @@
         <v>15.32</v>
       </c>
       <c r="K45" s="9" t="n">
-        <v>12.18</v>
+        <v>12.27</v>
       </c>
       <c r="L45" s="9" t="n">
-        <v>10.56</v>
+        <v>10.64</v>
       </c>
     </row>
     <row r="46">
@@ -10064,7 +10064,7 @@
         </is>
       </c>
       <c r="E46" s="7" t="n">
-        <v>63992</v>
+        <v>63165</v>
       </c>
       <c r="F46" s="9" t="n">
         <v>11.71</v>
@@ -10079,10 +10079,10 @@
         <v>17.46</v>
       </c>
       <c r="J46" s="9" t="n">
-        <v>14.29</v>
+        <v>14.13</v>
       </c>
       <c r="K46" s="9" t="n">
-        <v>12.14</v>
+        <v>12</v>
       </c>
       <c r="L46" s="9" t="n"/>
     </row>
@@ -10108,7 +10108,7 @@
         </is>
       </c>
       <c r="E47" s="7" t="n">
-        <v>25291</v>
+        <v>25225</v>
       </c>
       <c r="F47" s="9" t="n">
         <v>31.28</v>
@@ -10152,7 +10152,7 @@
         </is>
       </c>
       <c r="E48" s="7" t="n">
-        <v>12599</v>
+        <v>12566</v>
       </c>
       <c r="F48" s="9" t="n">
         <v>13.89</v>
@@ -10196,7 +10196,7 @@
         </is>
       </c>
       <c r="E49" s="7" t="n">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="F49" s="9" t="n">
         <v>5.78</v>
@@ -10214,7 +10214,7 @@
         <v>4.02</v>
       </c>
       <c r="K49" s="9" t="n">
-        <v>4.37</v>
+        <v>4.27</v>
       </c>
       <c r="L49" s="9" t="n"/>
     </row>
@@ -10240,7 +10240,7 @@
         </is>
       </c>
       <c r="E50" s="7" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F50" s="9" t="n">
         <v>7.57</v>
@@ -10320,7 +10320,7 @@
         </is>
       </c>
       <c r="E52" s="7" t="n">
-        <v>70101</v>
+        <v>69335</v>
       </c>
       <c r="F52" s="9" t="n">
         <v>11.71</v>
@@ -10335,10 +10335,10 @@
         <v>20.48</v>
       </c>
       <c r="J52" s="9" t="n">
-        <v>21.43</v>
+        <v>21.2</v>
       </c>
       <c r="K52" s="9" t="n">
-        <v>18.24</v>
+        <v>18.04</v>
       </c>
       <c r="L52" s="9" t="n"/>
     </row>
@@ -10454,7 +10454,7 @@
         </is>
       </c>
       <c r="E2" s="7" t="n">
-        <v>24179</v>
+        <v>23448</v>
       </c>
       <c r="F2" s="9" t="n"/>
       <c r="G2" s="9" t="n">
@@ -10492,7 +10492,7 @@
         </is>
       </c>
       <c r="E3" s="7" t="n">
-        <v>12801</v>
+        <v>12442</v>
       </c>
       <c r="F3" s="9" t="n"/>
       <c r="G3" s="9" t="n">
@@ -10530,7 +10530,7 @@
         </is>
       </c>
       <c r="E4" s="7" t="n">
-        <v>10860</v>
+        <v>10677</v>
       </c>
       <c r="F4" s="9" t="n"/>
       <c r="G4" s="9" t="n">
@@ -10568,7 +10568,7 @@
         </is>
       </c>
       <c r="E5" s="7" t="n">
-        <v>13249</v>
+        <v>13048</v>
       </c>
       <c r="F5" s="9" t="n">
         <v>40.3</v>
@@ -10608,7 +10608,7 @@
         </is>
       </c>
       <c r="E6" s="7" t="n">
-        <v>1071</v>
+        <v>1064</v>
       </c>
       <c r="F6" s="9" t="n"/>
       <c r="G6" s="9" t="n"/>
@@ -10642,7 +10642,7 @@
         </is>
       </c>
       <c r="E7" s="7" t="n">
-        <v>840</v>
+        <v>829</v>
       </c>
       <c r="F7" s="9" t="n">
         <v>87.52</v>
@@ -10680,7 +10680,7 @@
         </is>
       </c>
       <c r="E8" s="7" t="n">
-        <v>39658</v>
+        <v>39556</v>
       </c>
       <c r="F8" s="9" t="n">
         <v>13.27</v>
@@ -10720,7 +10720,7 @@
         </is>
       </c>
       <c r="E9" s="7" t="n">
-        <v>15029</v>
+        <v>14877</v>
       </c>
       <c r="F9" s="9" t="n">
         <v>5.59</v>
@@ -10760,7 +10760,7 @@
         </is>
       </c>
       <c r="E10" s="7" t="n">
-        <v>2320</v>
+        <v>2322</v>
       </c>
       <c r="F10" s="9" t="n">
         <v>0.93</v>
@@ -10800,7 +10800,7 @@
         </is>
       </c>
       <c r="E11" s="7" t="n">
-        <v>77441</v>
+        <v>75750</v>
       </c>
       <c r="F11" s="9" t="n"/>
       <c r="G11" s="9" t="n">
@@ -10840,7 +10840,7 @@
         </is>
       </c>
       <c r="E12" s="7" t="n">
-        <v>11529</v>
+        <v>11415</v>
       </c>
       <c r="F12" s="9" t="n"/>
       <c r="G12" s="9" t="n">
@@ -10880,7 +10880,7 @@
         </is>
       </c>
       <c r="E13" s="7" t="n">
-        <v>16564</v>
+        <v>16109</v>
       </c>
       <c r="F13" s="9" t="n"/>
       <c r="G13" s="9" t="n">
@@ -10920,7 +10920,7 @@
         </is>
       </c>
       <c r="E14" s="7" t="n">
-        <v>2259</v>
+        <v>2276</v>
       </c>
       <c r="F14" s="9" t="n"/>
       <c r="G14" s="9" t="n">
@@ -11000,7 +11000,7 @@
         </is>
       </c>
       <c r="E16" s="7" t="n">
-        <v>4396</v>
+        <v>4374</v>
       </c>
       <c r="F16" s="9" t="n">
         <v>991.9299999999999</v>
@@ -11040,7 +11040,7 @@
         </is>
       </c>
       <c r="E17" s="7" t="n">
-        <v>10943</v>
+        <v>10755</v>
       </c>
       <c r="F17" s="9" t="n">
         <v>10.08</v>
@@ -11080,7 +11080,7 @@
         </is>
       </c>
       <c r="E18" s="7" t="n">
-        <v>1236</v>
+        <v>1240</v>
       </c>
       <c r="F18" s="9" t="n"/>
       <c r="G18" s="9" t="n">
@@ -11118,7 +11118,7 @@
         </is>
       </c>
       <c r="E19" s="7" t="n">
-        <v>6655</v>
+        <v>6502</v>
       </c>
       <c r="F19" s="9" t="n"/>
       <c r="G19" s="9" t="n"/>
@@ -11154,7 +11154,7 @@
         </is>
       </c>
       <c r="E20" s="7" t="n">
-        <v>926</v>
+        <v>913</v>
       </c>
       <c r="F20" s="9" t="n">
         <v>11.7</v>
@@ -11194,7 +11194,7 @@
         </is>
       </c>
       <c r="E21" s="7" t="n">
-        <v>2033</v>
+        <v>1989</v>
       </c>
       <c r="F21" s="9" t="n"/>
       <c r="G21" s="9" t="n">
@@ -11232,7 +11232,7 @@
         </is>
       </c>
       <c r="E22" s="7" t="n">
-        <v>613</v>
+        <v>601</v>
       </c>
       <c r="F22" s="9" t="n">
         <v>11.21</v>
@@ -11272,7 +11272,7 @@
         </is>
       </c>
       <c r="E23" s="7" t="n">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="F23" s="9" t="n">
         <v>15.59</v>
@@ -11312,7 +11312,7 @@
         </is>
       </c>
       <c r="E24" s="7" t="n">
-        <v>7526</v>
+        <v>7187</v>
       </c>
       <c r="F24" s="9" t="n">
         <v>14.66</v>
@@ -11352,7 +11352,7 @@
         </is>
       </c>
       <c r="E25" s="7" t="n">
-        <v>30784</v>
+        <v>29608</v>
       </c>
       <c r="F25" s="9" t="n">
         <v>7.97</v>
@@ -11392,7 +11392,7 @@
         </is>
       </c>
       <c r="E26" s="7" t="n">
-        <v>7847</v>
+        <v>7178</v>
       </c>
       <c r="F26" s="9" t="n">
         <v>9.449999999999999</v>
@@ -11432,7 +11432,7 @@
         </is>
       </c>
       <c r="E27" s="7" t="n">
-        <v>9366</v>
+        <v>8640</v>
       </c>
       <c r="F27" s="9" t="n">
         <v>13.88</v>
@@ -11472,7 +11472,7 @@
         </is>
       </c>
       <c r="E28" s="7" t="n">
-        <v>6819</v>
+        <v>6595</v>
       </c>
       <c r="F28" s="9" t="n">
         <v>20.45</v>
@@ -11512,7 +11512,7 @@
         </is>
       </c>
       <c r="E29" s="7" t="n">
-        <v>135089</v>
+        <v>138357</v>
       </c>
       <c r="F29" s="9" t="n">
         <v>15.68</v>
@@ -11552,7 +11552,7 @@
         </is>
       </c>
       <c r="E30" s="7" t="n">
-        <v>78432</v>
+        <v>78303</v>
       </c>
       <c r="F30" s="9" t="n">
         <v>12.31</v>
@@ -11592,7 +11592,7 @@
         </is>
       </c>
       <c r="E31" s="7" t="n">
-        <v>94850</v>
+        <v>94463</v>
       </c>
       <c r="F31" s="9" t="n">
         <v>14.87</v>
@@ -11632,7 +11632,7 @@
         </is>
       </c>
       <c r="E32" s="7" t="n">
-        <v>261357</v>
+        <v>256390</v>
       </c>
       <c r="F32" s="9" t="n">
         <v>15.21</v>
@@ -11672,7 +11672,7 @@
         </is>
       </c>
       <c r="E33" s="7" t="n">
-        <v>10943</v>
+        <v>10755</v>
       </c>
       <c r="F33" s="9" t="n">
         <v>10.08</v>
@@ -11712,7 +11712,7 @@
         </is>
       </c>
       <c r="E34" s="7" t="n">
-        <v>52319</v>
+        <v>52463</v>
       </c>
       <c r="F34" s="9" t="n">
         <v>8.5</v>
@@ -11752,7 +11752,7 @@
         </is>
       </c>
       <c r="E35" s="7" t="n">
-        <v>75701</v>
+        <v>75806</v>
       </c>
       <c r="F35" s="9" t="n">
         <v>9.84</v>
@@ -11792,7 +11792,7 @@
         </is>
       </c>
       <c r="E36" s="7" t="n">
-        <v>31323</v>
+        <v>31374</v>
       </c>
       <c r="F36" s="9" t="n">
         <v>4.69</v>
@@ -11832,7 +11832,7 @@
         </is>
       </c>
       <c r="E37" s="7" t="n">
-        <v>34602</v>
+        <v>35175</v>
       </c>
       <c r="F37" s="9" t="n">
         <v>11.71</v>
@@ -11872,7 +11872,7 @@
         </is>
       </c>
       <c r="E38" s="7" t="n">
-        <v>3236</v>
+        <v>3142</v>
       </c>
       <c r="F38" s="9" t="n">
         <v>7.18</v>
@@ -11912,7 +11912,7 @@
         </is>
       </c>
       <c r="E39" s="7" t="n">
-        <v>3572</v>
+        <v>3514</v>
       </c>
       <c r="F39" s="9" t="n">
         <v>3.59</v>
@@ -11952,7 +11952,7 @@
         </is>
       </c>
       <c r="E40" s="7" t="n">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="F40" s="9" t="n">
         <v>6.74</v>
@@ -11992,7 +11992,7 @@
         </is>
       </c>
       <c r="E41" s="7" t="n">
-        <v>327586</v>
+        <v>319652</v>
       </c>
       <c r="F41" s="9" t="n">
         <v>13.46</v>
@@ -12032,7 +12032,7 @@
         </is>
       </c>
       <c r="E42" s="7" t="n">
-        <v>174004</v>
+        <v>174688</v>
       </c>
       <c r="F42" s="9" t="n">
         <v>13.71</v>
@@ -12072,7 +12072,7 @@
         </is>
       </c>
       <c r="E43" s="7" t="n">
-        <v>14383</v>
+        <v>14271</v>
       </c>
       <c r="F43" s="9" t="n">
         <v>10.23</v>
@@ -12112,7 +12112,7 @@
         </is>
       </c>
       <c r="E44" s="7" t="n">
-        <v>38546</v>
+        <v>38449</v>
       </c>
       <c r="F44" s="9" t="n"/>
       <c r="G44" s="9" t="n">
@@ -12152,7 +12152,7 @@
         </is>
       </c>
       <c r="E45" s="7" t="n">
-        <v>7107</v>
+        <v>7160</v>
       </c>
       <c r="F45" s="9" t="n"/>
       <c r="G45" s="9" t="n">
@@ -12192,7 +12192,7 @@
         </is>
       </c>
       <c r="E46" s="7" t="n">
-        <v>63992</v>
+        <v>63165</v>
       </c>
       <c r="F46" s="9" t="n">
         <v>7.78</v>
@@ -12232,7 +12232,7 @@
         </is>
       </c>
       <c r="E47" s="7" t="n">
-        <v>25291</v>
+        <v>25225</v>
       </c>
       <c r="F47" s="9" t="n">
         <v>18.39</v>
@@ -12272,7 +12272,7 @@
         </is>
       </c>
       <c r="E48" s="7" t="n">
-        <v>12599</v>
+        <v>12566</v>
       </c>
       <c r="F48" s="9" t="n">
         <v>7.78</v>
@@ -12312,7 +12312,7 @@
         </is>
       </c>
       <c r="E49" s="7" t="n">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="F49" s="9" t="n">
         <v>3.96</v>
@@ -12352,7 +12352,7 @@
         </is>
       </c>
       <c r="E50" s="7" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F50" s="9" t="n">
         <v>2.92</v>
@@ -12432,7 +12432,7 @@
         </is>
       </c>
       <c r="E52" s="7" t="n">
-        <v>70101</v>
+        <v>69335</v>
       </c>
       <c r="F52" s="9" t="n">
         <v>6.73</v>
@@ -12562,7 +12562,7 @@
         </is>
       </c>
       <c r="E2" s="7" t="n">
-        <v>24179</v>
+        <v>23448</v>
       </c>
       <c r="F2" s="9" t="n">
         <v>1.95</v>
@@ -12580,7 +12580,7 @@
         <v>2.79</v>
       </c>
       <c r="K2" s="9" t="n">
-        <v>2.13</v>
+        <v>2.06</v>
       </c>
       <c r="L2" s="9" t="n"/>
     </row>
@@ -12606,7 +12606,7 @@
         </is>
       </c>
       <c r="E3" s="7" t="n">
-        <v>12801</v>
+        <v>12442</v>
       </c>
       <c r="F3" s="9" t="n">
         <v>2.73</v>
@@ -12624,7 +12624,7 @@
         <v>2.06</v>
       </c>
       <c r="K3" s="9" t="n">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="L3" s="9" t="n"/>
     </row>
@@ -12650,7 +12650,7 @@
         </is>
       </c>
       <c r="E4" s="7" t="n">
-        <v>10860</v>
+        <v>10677</v>
       </c>
       <c r="F4" s="9" t="n">
         <v>1.21</v>
@@ -12668,7 +12668,7 @@
         <v>2.78</v>
       </c>
       <c r="K4" s="9" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="L4" s="9" t="n"/>
     </row>
@@ -12694,7 +12694,7 @@
         </is>
       </c>
       <c r="E5" s="7" t="n">
-        <v>13249</v>
+        <v>13048</v>
       </c>
       <c r="F5" s="9" t="n">
         <v>0.51</v>
@@ -12712,7 +12712,7 @@
         <v>1.15</v>
       </c>
       <c r="K5" s="9" t="n">
-        <v>0.89</v>
+        <v>0.87</v>
       </c>
       <c r="L5" s="9" t="n"/>
     </row>
@@ -12738,7 +12738,7 @@
         </is>
       </c>
       <c r="E6" s="7" t="n">
-        <v>1071</v>
+        <v>1064</v>
       </c>
       <c r="F6" s="9" t="n"/>
       <c r="G6" s="9" t="n"/>
@@ -12776,7 +12776,7 @@
         </is>
       </c>
       <c r="E7" s="7" t="n">
-        <v>840</v>
+        <v>829</v>
       </c>
       <c r="F7" s="9" t="n">
         <v>0.85</v>
@@ -12818,7 +12818,7 @@
         </is>
       </c>
       <c r="E8" s="7" t="n">
-        <v>39658</v>
+        <v>39556</v>
       </c>
       <c r="F8" s="9" t="n">
         <v>2.17</v>
@@ -12862,7 +12862,7 @@
         </is>
       </c>
       <c r="E9" s="7" t="n">
-        <v>15029</v>
+        <v>14877</v>
       </c>
       <c r="F9" s="9" t="n">
         <v>1.58</v>
@@ -12877,10 +12877,10 @@
         <v>2.32</v>
       </c>
       <c r="J9" s="9" t="n">
-        <v>2.61</v>
+        <v>2.59</v>
       </c>
       <c r="K9" s="9" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="L9" s="9" t="n"/>
     </row>
@@ -12906,7 +12906,7 @@
         </is>
       </c>
       <c r="E10" s="7" t="n">
-        <v>2320</v>
+        <v>2322</v>
       </c>
       <c r="F10" s="9" t="n">
         <v>0.6</v>
@@ -12950,7 +12950,7 @@
         </is>
       </c>
       <c r="E11" s="7" t="n">
-        <v>77441</v>
+        <v>75750</v>
       </c>
       <c r="F11" s="9" t="n"/>
       <c r="G11" s="9" t="n">
@@ -12966,10 +12966,10 @@
         <v>4.59</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>3.56</v>
+        <v>3.48</v>
       </c>
       <c r="L11" s="9" t="n">
-        <v>3.21</v>
+        <v>3.14</v>
       </c>
     </row>
     <row r="12">
@@ -12994,7 +12994,7 @@
         </is>
       </c>
       <c r="E12" s="7" t="n">
-        <v>11529</v>
+        <v>11415</v>
       </c>
       <c r="F12" s="9" t="n"/>
       <c r="G12" s="9" t="n">
@@ -13010,10 +13010,10 @@
         <v>2.76</v>
       </c>
       <c r="K12" s="9" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="L12" s="9" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="13">
@@ -13038,7 +13038,7 @@
         </is>
       </c>
       <c r="E13" s="7" t="n">
-        <v>16564</v>
+        <v>16109</v>
       </c>
       <c r="F13" s="9" t="n"/>
       <c r="G13" s="9" t="n">
@@ -13054,10 +13054,10 @@
         <v>5.1</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>3.19</v>
+        <v>3.1</v>
       </c>
       <c r="L13" s="9" t="n">
-        <v>2.71</v>
+        <v>2.64</v>
       </c>
     </row>
     <row r="14">
@@ -13082,7 +13082,7 @@
         </is>
       </c>
       <c r="E14" s="7" t="n">
-        <v>2259</v>
+        <v>2276</v>
       </c>
       <c r="F14" s="9" t="n"/>
       <c r="G14" s="9" t="n">
@@ -13098,10 +13098,10 @@
         <v>2.46</v>
       </c>
       <c r="K14" s="9" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="L14" s="9" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="15">
@@ -13166,7 +13166,7 @@
         </is>
       </c>
       <c r="E16" s="7" t="n">
-        <v>4396</v>
+        <v>4374</v>
       </c>
       <c r="F16" s="9" t="n">
         <v>1.54</v>
@@ -13181,10 +13181,10 @@
         <v>5.43</v>
       </c>
       <c r="J16" s="9" t="n">
-        <v>3.33</v>
+        <v>3.32</v>
       </c>
       <c r="K16" s="9" t="n">
-        <v>2.72</v>
+        <v>2.71</v>
       </c>
       <c r="L16" s="9" t="n"/>
     </row>
@@ -13210,7 +13210,7 @@
         </is>
       </c>
       <c r="E17" s="7" t="n">
-        <v>10943</v>
+        <v>10755</v>
       </c>
       <c r="F17" s="9" t="n">
         <v>2.64</v>
@@ -13225,10 +13225,10 @@
         <v>2.63</v>
       </c>
       <c r="J17" s="9" t="n">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="L17" s="9" t="n"/>
     </row>
@@ -13254,7 +13254,7 @@
         </is>
       </c>
       <c r="E18" s="7" t="n">
-        <v>1236</v>
+        <v>1240</v>
       </c>
       <c r="F18" s="9" t="n"/>
       <c r="G18" s="9" t="n">
@@ -13270,10 +13270,10 @@
         <v>1.39</v>
       </c>
       <c r="K18" s="9" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="L18" s="9" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="19">
@@ -13298,7 +13298,7 @@
         </is>
       </c>
       <c r="E19" s="7" t="n">
-        <v>6655</v>
+        <v>6502</v>
       </c>
       <c r="F19" s="9" t="n"/>
       <c r="G19" s="9" t="n"/>
@@ -13312,7 +13312,7 @@
         <v>8.74</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>7.14</v>
+        <v>6.96</v>
       </c>
       <c r="L19" s="9" t="n"/>
     </row>
@@ -13338,7 +13338,7 @@
         </is>
       </c>
       <c r="E20" s="7" t="n">
-        <v>926</v>
+        <v>913</v>
       </c>
       <c r="F20" s="9" t="n">
         <v>1.05</v>
@@ -13356,7 +13356,7 @@
         <v>2.34</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="L20" s="9" t="n"/>
     </row>
@@ -13382,7 +13382,7 @@
         </is>
       </c>
       <c r="E21" s="7" t="n">
-        <v>2033</v>
+        <v>1989</v>
       </c>
       <c r="F21" s="9" t="n">
         <v>2.39</v>
@@ -13400,7 +13400,7 @@
         <v>3.59</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>2.57</v>
+        <v>2.51</v>
       </c>
       <c r="L21" s="9" t="n"/>
     </row>
@@ -13426,7 +13426,7 @@
         </is>
       </c>
       <c r="E22" s="7" t="n">
-        <v>613</v>
+        <v>601</v>
       </c>
       <c r="F22" s="9" t="n">
         <v>1.18</v>
@@ -13444,7 +13444,7 @@
         <v>1.2</v>
       </c>
       <c r="K22" s="9" t="n">
-        <v>1.01</v>
+        <v>0.99</v>
       </c>
       <c r="L22" s="9" t="n"/>
     </row>
@@ -13470,7 +13470,7 @@
         </is>
       </c>
       <c r="E23" s="7" t="n">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="F23" s="9" t="n">
         <v>2.1</v>
@@ -13488,7 +13488,7 @@
         <v>1.19</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="L23" s="9" t="n"/>
     </row>
@@ -13514,7 +13514,7 @@
         </is>
       </c>
       <c r="E24" s="7" t="n">
-        <v>7526</v>
+        <v>7187</v>
       </c>
       <c r="F24" s="9" t="n">
         <v>3.47</v>
@@ -13532,7 +13532,7 @@
         <v>4.9</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>4.29</v>
+        <v>4.1</v>
       </c>
       <c r="L24" s="9" t="n"/>
     </row>
@@ -13558,7 +13558,7 @@
         </is>
       </c>
       <c r="E25" s="7" t="n">
-        <v>30784</v>
+        <v>29608</v>
       </c>
       <c r="F25" s="9" t="n">
         <v>1.32</v>
@@ -13576,7 +13576,7 @@
         <v>3.32</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>2.89</v>
+        <v>2.78</v>
       </c>
       <c r="L25" s="9" t="n"/>
     </row>
@@ -13602,7 +13602,7 @@
         </is>
       </c>
       <c r="E26" s="7" t="n">
-        <v>7847</v>
+        <v>7178</v>
       </c>
       <c r="F26" s="9" t="n">
         <v>2.15</v>
@@ -13620,7 +13620,7 @@
         <v>5.98</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>4.94</v>
+        <v>4.52</v>
       </c>
       <c r="L26" s="9" t="n"/>
     </row>
@@ -13646,7 +13646,7 @@
         </is>
       </c>
       <c r="E27" s="7" t="n">
-        <v>9366</v>
+        <v>8640</v>
       </c>
       <c r="F27" s="9" t="n">
         <v>0.99</v>
@@ -13664,7 +13664,7 @@
         <v>2.35</v>
       </c>
       <c r="K27" s="9" t="n">
-        <v>2.4</v>
+        <v>2.21</v>
       </c>
       <c r="L27" s="9" t="n"/>
     </row>
@@ -13690,7 +13690,7 @@
         </is>
       </c>
       <c r="E28" s="7" t="n">
-        <v>6819</v>
+        <v>6595</v>
       </c>
       <c r="F28" s="9" t="n">
         <v>2.04</v>
@@ -13708,7 +13708,7 @@
         <v>2.37</v>
       </c>
       <c r="K28" s="9" t="n">
-        <v>1.94</v>
+        <v>1.88</v>
       </c>
       <c r="L28" s="9" t="n"/>
     </row>
@@ -13734,7 +13734,7 @@
         </is>
       </c>
       <c r="E29" s="7" t="n">
-        <v>135089</v>
+        <v>138357</v>
       </c>
       <c r="F29" s="9" t="n">
         <v>13.34</v>
@@ -13749,10 +13749,10 @@
         <v>16.48</v>
       </c>
       <c r="J29" s="9" t="n">
-        <v>13.12</v>
+        <v>13.44</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>9.539999999999999</v>
+        <v>9.77</v>
       </c>
       <c r="L29" s="9" t="n"/>
     </row>
@@ -13778,7 +13778,7 @@
         </is>
       </c>
       <c r="E30" s="7" t="n">
-        <v>78432</v>
+        <v>78303</v>
       </c>
       <c r="F30" s="9" t="n">
         <v>5.46</v>
@@ -13793,10 +13793,10 @@
         <v>4.86</v>
       </c>
       <c r="J30" s="9" t="n">
-        <v>4</v>
+        <v>3.99</v>
       </c>
       <c r="K30" s="9" t="n">
-        <v>3.47</v>
+        <v>3.46</v>
       </c>
       <c r="L30" s="9" t="n"/>
     </row>
@@ -13822,7 +13822,7 @@
         </is>
       </c>
       <c r="E31" s="7" t="n">
-        <v>94850</v>
+        <v>94463</v>
       </c>
       <c r="F31" s="9" t="n">
         <v>3.67</v>
@@ -13837,10 +13837,10 @@
         <v>3.55</v>
       </c>
       <c r="J31" s="9" t="n">
-        <v>3.33</v>
+        <v>3.32</v>
       </c>
       <c r="K31" s="9" t="n">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="L31" s="9" t="n"/>
     </row>
@@ -13866,7 +13866,7 @@
         </is>
       </c>
       <c r="E32" s="7" t="n">
-        <v>261357</v>
+        <v>256390</v>
       </c>
       <c r="F32" s="9" t="n">
         <v>2.04</v>
@@ -13881,10 +13881,10 @@
         <v>3.77</v>
       </c>
       <c r="J32" s="9" t="n">
-        <v>3.69</v>
+        <v>3.62</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>3.41</v>
+        <v>3.35</v>
       </c>
       <c r="L32" s="9" t="n"/>
     </row>
@@ -13910,7 +13910,7 @@
         </is>
       </c>
       <c r="E33" s="7" t="n">
-        <v>10943</v>
+        <v>10755</v>
       </c>
       <c r="F33" s="9" t="n">
         <v>2.64</v>
@@ -13925,10 +13925,10 @@
         <v>2.63</v>
       </c>
       <c r="J33" s="9" t="n">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="K33" s="9" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="L33" s="9" t="n"/>
     </row>
@@ -13954,7 +13954,7 @@
         </is>
       </c>
       <c r="E34" s="7" t="n">
-        <v>52319</v>
+        <v>52463</v>
       </c>
       <c r="F34" s="9" t="n">
         <v>2.86</v>
@@ -13969,10 +13969,10 @@
         <v>14.29</v>
       </c>
       <c r="J34" s="9" t="n">
-        <v>7.82</v>
+        <v>7.85</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>6.38</v>
+        <v>6.4</v>
       </c>
       <c r="L34" s="9" t="n"/>
     </row>
@@ -13998,7 +13998,7 @@
         </is>
       </c>
       <c r="E35" s="7" t="n">
-        <v>75701</v>
+        <v>75806</v>
       </c>
       <c r="F35" s="9" t="n">
         <v>2.35</v>
@@ -14042,7 +14042,7 @@
         </is>
       </c>
       <c r="E36" s="7" t="n">
-        <v>31323</v>
+        <v>31374</v>
       </c>
       <c r="F36" s="9" t="n">
         <v>0.65</v>
@@ -14057,10 +14057,10 @@
         <v>2.97</v>
       </c>
       <c r="J36" s="9" t="n">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="K36" s="9" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="L36" s="9" t="n"/>
     </row>
@@ -14086,7 +14086,7 @@
         </is>
       </c>
       <c r="E37" s="7" t="n">
-        <v>34602</v>
+        <v>35175</v>
       </c>
       <c r="F37" s="9" t="n">
         <v>1.85</v>
@@ -14101,10 +14101,10 @@
         <v>6.69</v>
       </c>
       <c r="J37" s="9" t="n">
-        <v>6.84</v>
+        <v>6.93</v>
       </c>
       <c r="K37" s="9" t="n">
-        <v>5.84</v>
+        <v>5.93</v>
       </c>
       <c r="L37" s="9" t="n"/>
     </row>
@@ -14130,7 +14130,7 @@
         </is>
       </c>
       <c r="E38" s="7" t="n">
-        <v>3236</v>
+        <v>3142</v>
       </c>
       <c r="F38" s="9" t="n">
         <v>0.8100000000000001</v>
@@ -14148,7 +14148,7 @@
         <v>0.87</v>
       </c>
       <c r="K38" s="9" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="L38" s="9" t="n"/>
     </row>
@@ -14174,7 +14174,7 @@
         </is>
       </c>
       <c r="E39" s="7" t="n">
-        <v>3572</v>
+        <v>3514</v>
       </c>
       <c r="F39" s="9" t="n">
         <v>0.6899999999999999</v>
@@ -14192,7 +14192,7 @@
         <v>0.61</v>
       </c>
       <c r="K39" s="9" t="n">
-        <v>0.59</v>
+        <v>0.58</v>
       </c>
       <c r="L39" s="9" t="n"/>
     </row>
@@ -14218,7 +14218,7 @@
         </is>
       </c>
       <c r="E40" s="7" t="n">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="F40" s="9" t="n">
         <v>0.8100000000000001</v>
@@ -14258,7 +14258,7 @@
         </is>
       </c>
       <c r="E41" s="7" t="n">
-        <v>327586</v>
+        <v>319652</v>
       </c>
       <c r="F41" s="9" t="n">
         <v>7.79</v>
@@ -14273,10 +14273,10 @@
         <v>12.5</v>
       </c>
       <c r="J41" s="9" t="n">
-        <v>10.66</v>
+        <v>10.4</v>
       </c>
       <c r="K41" s="9" t="n">
-        <v>7.81</v>
+        <v>7.62</v>
       </c>
       <c r="L41" s="9" t="n"/>
     </row>
@@ -14302,7 +14302,7 @@
         </is>
       </c>
       <c r="E42" s="7" t="n">
-        <v>174004</v>
+        <v>174688</v>
       </c>
       <c r="F42" s="9" t="n">
         <v>5.84</v>
@@ -14317,10 +14317,10 @@
         <v>4.81</v>
       </c>
       <c r="J42" s="9" t="n">
-        <v>5.98</v>
+        <v>6.01</v>
       </c>
       <c r="K42" s="9" t="n">
-        <v>5.26</v>
+        <v>5.28</v>
       </c>
       <c r="L42" s="9" t="n"/>
     </row>
@@ -14346,7 +14346,7 @@
         </is>
       </c>
       <c r="E43" s="7" t="n">
-        <v>14383</v>
+        <v>14271</v>
       </c>
       <c r="F43" s="9" t="n">
         <v>3.12</v>
@@ -14361,10 +14361,10 @@
         <v>1.48</v>
       </c>
       <c r="J43" s="9" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="K43" s="9" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="L43" s="9" t="n"/>
     </row>
@@ -14390,7 +14390,7 @@
         </is>
       </c>
       <c r="E44" s="7" t="n">
-        <v>38546</v>
+        <v>38449</v>
       </c>
       <c r="F44" s="9" t="n"/>
       <c r="G44" s="9" t="n">
@@ -14434,7 +14434,7 @@
         </is>
       </c>
       <c r="E45" s="7" t="n">
-        <v>7107</v>
+        <v>7160</v>
       </c>
       <c r="F45" s="9" t="n"/>
       <c r="G45" s="9" t="n">
@@ -14450,10 +14450,10 @@
         <v>1.25</v>
       </c>
       <c r="K45" s="9" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="L45" s="9" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
     </row>
     <row r="46">
@@ -14478,7 +14478,7 @@
         </is>
       </c>
       <c r="E46" s="7" t="n">
-        <v>63992</v>
+        <v>63165</v>
       </c>
       <c r="F46" s="9" t="n">
         <v>2.36</v>
@@ -14493,10 +14493,10 @@
         <v>3.37</v>
       </c>
       <c r="J46" s="9" t="n">
-        <v>3.14</v>
+        <v>3.08</v>
       </c>
       <c r="K46" s="9" t="n">
-        <v>2.77</v>
+        <v>2.7</v>
       </c>
       <c r="L46" s="9" t="n"/>
     </row>
@@ -14522,7 +14522,7 @@
         </is>
       </c>
       <c r="E47" s="7" t="n">
-        <v>25291</v>
+        <v>25225</v>
       </c>
       <c r="F47" s="9" t="n">
         <v>2.06</v>
@@ -14566,7 +14566,7 @@
         </is>
       </c>
       <c r="E48" s="7" t="n">
-        <v>12599</v>
+        <v>12566</v>
       </c>
       <c r="F48" s="9" t="n">
         <v>1.12</v>
@@ -14610,7 +14610,7 @@
         </is>
       </c>
       <c r="E49" s="7" t="n">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="F49" s="9" t="n">
         <v>1.25</v>
@@ -14628,7 +14628,7 @@
         <v>0.54</v>
       </c>
       <c r="K49" s="9" t="n">
-        <v>0.51</v>
+        <v>0.5</v>
       </c>
       <c r="L49" s="9" t="n"/>
     </row>
@@ -14654,7 +14654,7 @@
         </is>
       </c>
       <c r="E50" s="7" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F50" s="9" t="n">
         <v>0.5600000000000001</v>
@@ -14734,7 +14734,7 @@
         </is>
       </c>
       <c r="E52" s="7" t="n">
-        <v>70101</v>
+        <v>69335</v>
       </c>
       <c r="F52" s="9" t="n">
         <v>3.49</v>
@@ -14749,10 +14749,10 @@
         <v>5.69</v>
       </c>
       <c r="J52" s="9" t="n">
-        <v>6</v>
+        <v>5.93</v>
       </c>
       <c r="K52" s="9" t="n">
-        <v>4.71</v>
+        <v>4.66</v>
       </c>
       <c r="L52" s="9" t="n"/>
     </row>
@@ -14868,7 +14868,7 @@
         </is>
       </c>
       <c r="E2" s="7" t="n">
-        <v>24179</v>
+        <v>23448</v>
       </c>
       <c r="F2" s="9" t="n">
         <v>-6.66</v>
@@ -14912,7 +14912,7 @@
         </is>
       </c>
       <c r="E3" s="7" t="n">
-        <v>12801</v>
+        <v>12442</v>
       </c>
       <c r="F3" s="9" t="n">
         <v>-234.21</v>
@@ -14956,7 +14956,7 @@
         </is>
       </c>
       <c r="E4" s="7" t="n">
-        <v>10860</v>
+        <v>10677</v>
       </c>
       <c r="F4" s="9" t="n">
         <v>-17.23</v>
@@ -15000,7 +15000,7 @@
         </is>
       </c>
       <c r="E5" s="7" t="n">
-        <v>13249</v>
+        <v>13048</v>
       </c>
       <c r="F5" s="9" t="n">
         <v>-2.23</v>
@@ -15044,7 +15044,7 @@
         </is>
       </c>
       <c r="E6" s="7" t="n">
-        <v>1071</v>
+        <v>1064</v>
       </c>
       <c r="F6" s="9" t="n">
         <v>-7.73</v>
@@ -15088,7 +15088,7 @@
         </is>
       </c>
       <c r="E7" s="7" t="n">
-        <v>840</v>
+        <v>829</v>
       </c>
       <c r="F7" s="9" t="n">
         <v>-13.03</v>
@@ -15130,7 +15130,7 @@
         </is>
       </c>
       <c r="E8" s="7" t="n">
-        <v>39658</v>
+        <v>39556</v>
       </c>
       <c r="F8" s="9" t="n">
         <v>0.38</v>
@@ -15174,7 +15174,7 @@
         </is>
       </c>
       <c r="E9" s="7" t="n">
-        <v>15029</v>
+        <v>14877</v>
       </c>
       <c r="F9" s="9" t="n">
         <v>15.98</v>
@@ -15218,7 +15218,7 @@
         </is>
       </c>
       <c r="E10" s="7" t="n">
-        <v>2320</v>
+        <v>2322</v>
       </c>
       <c r="F10" s="9" t="n">
         <v>4.42</v>
@@ -15262,7 +15262,7 @@
         </is>
       </c>
       <c r="E11" s="7" t="n">
-        <v>77441</v>
+        <v>75750</v>
       </c>
       <c r="F11" s="9" t="n"/>
       <c r="G11" s="9" t="n">
@@ -15306,7 +15306,7 @@
         </is>
       </c>
       <c r="E12" s="7" t="n">
-        <v>11529</v>
+        <v>11415</v>
       </c>
       <c r="F12" s="9" t="n"/>
       <c r="G12" s="9" t="n">
@@ -15350,7 +15350,7 @@
         </is>
       </c>
       <c r="E13" s="7" t="n">
-        <v>16564</v>
+        <v>16109</v>
       </c>
       <c r="F13" s="9" t="n"/>
       <c r="G13" s="9" t="n">
@@ -15394,7 +15394,7 @@
         </is>
       </c>
       <c r="E14" s="7" t="n">
-        <v>2259</v>
+        <v>2276</v>
       </c>
       <c r="F14" s="9" t="n"/>
       <c r="G14" s="9" t="n">
@@ -15478,7 +15478,7 @@
         </is>
       </c>
       <c r="E16" s="7" t="n">
-        <v>4396</v>
+        <v>4374</v>
       </c>
       <c r="F16" s="9" t="n">
         <v>-52.75</v>
@@ -15522,7 +15522,7 @@
         </is>
       </c>
       <c r="E17" s="7" t="n">
-        <v>10943</v>
+        <v>10755</v>
       </c>
       <c r="F17" s="9" t="n">
         <v>16.6</v>
@@ -15566,7 +15566,7 @@
         </is>
       </c>
       <c r="E18" s="7" t="n">
-        <v>1236</v>
+        <v>1240</v>
       </c>
       <c r="F18" s="9" t="n"/>
       <c r="G18" s="9" t="n">
@@ -15610,7 +15610,7 @@
         </is>
       </c>
       <c r="E19" s="7" t="n">
-        <v>6655</v>
+        <v>6502</v>
       </c>
       <c r="F19" s="9" t="n">
         <v>57.58</v>
@@ -15654,7 +15654,7 @@
         </is>
       </c>
       <c r="E20" s="7" t="n">
-        <v>926</v>
+        <v>913</v>
       </c>
       <c r="F20" s="9" t="n">
         <v>7.36</v>
@@ -15698,7 +15698,7 @@
         </is>
       </c>
       <c r="E21" s="7" t="n">
-        <v>2033</v>
+        <v>1989</v>
       </c>
       <c r="F21" s="9" t="n">
         <v>-18.17</v>
@@ -15742,7 +15742,7 @@
         </is>
       </c>
       <c r="E22" s="7" t="n">
-        <v>613</v>
+        <v>601</v>
       </c>
       <c r="F22" s="9" t="n">
         <v>5.01</v>
@@ -15786,7 +15786,7 @@
         </is>
       </c>
       <c r="E23" s="7" t="n">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="F23" s="9" t="n">
         <v>5.67</v>
@@ -15830,7 +15830,7 @@
         </is>
       </c>
       <c r="E24" s="7" t="n">
-        <v>7526</v>
+        <v>7187</v>
       </c>
       <c r="F24" s="9" t="n">
         <v>8.300000000000001</v>
@@ -15874,7 +15874,7 @@
         </is>
       </c>
       <c r="E25" s="7" t="n">
-        <v>30784</v>
+        <v>29608</v>
       </c>
       <c r="F25" s="9" t="n">
         <v>6.84</v>
@@ -15918,7 +15918,7 @@
         </is>
       </c>
       <c r="E26" s="7" t="n">
-        <v>7847</v>
+        <v>7178</v>
       </c>
       <c r="F26" s="9" t="n">
         <v>13.15</v>
@@ -15962,7 +15962,7 @@
         </is>
       </c>
       <c r="E27" s="7" t="n">
-        <v>9366</v>
+        <v>8640</v>
       </c>
       <c r="F27" s="9" t="n">
         <v>-3.83</v>
@@ -16006,7 +16006,7 @@
         </is>
       </c>
       <c r="E28" s="7" t="n">
-        <v>6819</v>
+        <v>6595</v>
       </c>
       <c r="F28" s="9" t="n">
         <v>13.01</v>
@@ -16050,7 +16050,7 @@
         </is>
       </c>
       <c r="E29" s="7" t="n">
-        <v>135089</v>
+        <v>138357</v>
       </c>
       <c r="F29" s="9" t="n">
         <v>61.86</v>
@@ -16065,10 +16065,10 @@
         <v>76.87</v>
       </c>
       <c r="J29" s="9" t="n">
-        <v>82.36</v>
+        <v>82.42</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>61.96</v>
+        <v>62.03</v>
       </c>
       <c r="L29" s="9" t="n"/>
     </row>
@@ -16094,7 +16094,7 @@
         </is>
       </c>
       <c r="E30" s="7" t="n">
-        <v>78432</v>
+        <v>78303</v>
       </c>
       <c r="F30" s="9" t="n">
         <v>31.97</v>
@@ -16109,10 +16109,10 @@
         <v>26.17</v>
       </c>
       <c r="J30" s="9" t="n">
-        <v>23.28</v>
+        <v>23.27</v>
       </c>
       <c r="K30" s="9" t="n">
-        <v>20.22</v>
+        <v>20.2</v>
       </c>
       <c r="L30" s="9" t="n"/>
     </row>
@@ -16138,7 +16138,7 @@
         </is>
       </c>
       <c r="E31" s="7" t="n">
-        <v>94850</v>
+        <v>94463</v>
       </c>
       <c r="F31" s="9" t="n">
         <v>18.26</v>
@@ -16182,7 +16182,7 @@
         </is>
       </c>
       <c r="E32" s="7" t="n">
-        <v>261357</v>
+        <v>256390</v>
       </c>
       <c r="F32" s="9" t="n">
         <v>7.16</v>
@@ -16197,7 +16197,7 @@
         <v>10.74</v>
       </c>
       <c r="J32" s="9" t="n">
-        <v>15.02</v>
+        <v>15.06</v>
       </c>
       <c r="K32" s="9" t="n">
         <v>14.62</v>
@@ -16226,7 +16226,7 @@
         </is>
       </c>
       <c r="E33" s="7" t="n">
-        <v>10943</v>
+        <v>10755</v>
       </c>
       <c r="F33" s="9" t="n">
         <v>16.6</v>
@@ -16270,7 +16270,7 @@
         </is>
       </c>
       <c r="E34" s="7" t="n">
-        <v>52319</v>
+        <v>52463</v>
       </c>
       <c r="F34" s="9" t="n">
         <v>16.81</v>
@@ -16314,7 +16314,7 @@
         </is>
       </c>
       <c r="E35" s="7" t="n">
-        <v>75701</v>
+        <v>75806</v>
       </c>
       <c r="F35" s="9" t="n">
         <v>14.19</v>
@@ -16358,7 +16358,7 @@
         </is>
       </c>
       <c r="E36" s="7" t="n">
-        <v>31323</v>
+        <v>31374</v>
       </c>
       <c r="F36" s="9" t="n">
         <v>12.91</v>
@@ -16402,7 +16402,7 @@
         </is>
       </c>
       <c r="E37" s="7" t="n">
-        <v>34602</v>
+        <v>35175</v>
       </c>
       <c r="F37" s="9" t="n">
         <v>7.44</v>
@@ -16417,10 +16417,10 @@
         <v>16.02</v>
       </c>
       <c r="J37" s="9" t="n">
-        <v>17.25</v>
+        <v>17.88</v>
       </c>
       <c r="K37" s="9" t="n">
-        <v>18.89</v>
+        <v>18.82</v>
       </c>
       <c r="L37" s="9" t="n"/>
     </row>
@@ -16446,7 +16446,7 @@
         </is>
       </c>
       <c r="E38" s="7" t="n">
-        <v>3236</v>
+        <v>3142</v>
       </c>
       <c r="F38" s="9" t="n">
         <v>7.62</v>
@@ -16490,7 +16490,7 @@
         </is>
       </c>
       <c r="E39" s="7" t="n">
-        <v>3572</v>
+        <v>3514</v>
       </c>
       <c r="F39" s="9" t="n">
         <v>12.82</v>
@@ -16534,7 +16534,7 @@
         </is>
       </c>
       <c r="E40" s="7" t="n">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="F40" s="9" t="n">
         <v>11.21</v>
@@ -16574,7 +16574,7 @@
         </is>
       </c>
       <c r="E41" s="7" t="n">
-        <v>327586</v>
+        <v>319652</v>
       </c>
       <c r="F41" s="9" t="n">
         <v>42.25</v>
@@ -16618,7 +16618,7 @@
         </is>
       </c>
       <c r="E42" s="7" t="n">
-        <v>174004</v>
+        <v>174688</v>
       </c>
       <c r="F42" s="9" t="n">
         <v>35.19</v>
@@ -16662,7 +16662,7 @@
         </is>
       </c>
       <c r="E43" s="7" t="n">
-        <v>14383</v>
+        <v>14271</v>
       </c>
       <c r="F43" s="9" t="n">
         <v>29.29</v>
@@ -16706,7 +16706,7 @@
         </is>
       </c>
       <c r="E44" s="7" t="n">
-        <v>38546</v>
+        <v>38449</v>
       </c>
       <c r="F44" s="9" t="n"/>
       <c r="G44" s="9" t="n">
@@ -16750,7 +16750,7 @@
         </is>
       </c>
       <c r="E45" s="7" t="n">
-        <v>7107</v>
+        <v>7160</v>
       </c>
       <c r="F45" s="9" t="n"/>
       <c r="G45" s="9" t="n">
@@ -16794,7 +16794,7 @@
         </is>
       </c>
       <c r="E46" s="7" t="n">
-        <v>63992</v>
+        <v>63165</v>
       </c>
       <c r="F46" s="9" t="n">
         <v>20.11</v>
@@ -16809,10 +16809,10 @@
         <v>18.5</v>
       </c>
       <c r="J46" s="9" t="n">
-        <v>23.32</v>
+        <v>23.21</v>
       </c>
       <c r="K46" s="9" t="n">
-        <v>24.27</v>
+        <v>23.96</v>
       </c>
       <c r="L46" s="9" t="n"/>
     </row>
@@ -16838,7 +16838,7 @@
         </is>
       </c>
       <c r="E47" s="7" t="n">
-        <v>25291</v>
+        <v>25225</v>
       </c>
       <c r="F47" s="9" t="n">
         <v>6.6</v>
@@ -16882,7 +16882,7 @@
         </is>
       </c>
       <c r="E48" s="7" t="n">
-        <v>12599</v>
+        <v>12566</v>
       </c>
       <c r="F48" s="9" t="n">
         <v>8.1</v>
@@ -16926,7 +16926,7 @@
         </is>
       </c>
       <c r="E49" s="7" t="n">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="F49" s="9" t="n">
         <v>21.69</v>
@@ -16970,7 +16970,7 @@
         </is>
       </c>
       <c r="E50" s="7" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F50" s="9" t="n">
         <v>7.43</v>
@@ -17050,7 +17050,7 @@
         </is>
       </c>
       <c r="E52" s="7" t="n">
-        <v>70101</v>
+        <v>69335</v>
       </c>
       <c r="F52" s="9" t="n">
         <v>29.81</v>
@@ -17184,7 +17184,7 @@
         </is>
       </c>
       <c r="E2" s="7" t="n">
-        <v>24179</v>
+        <v>23448</v>
       </c>
       <c r="F2" s="9" t="n">
         <v>1.14</v>
@@ -17199,10 +17199,10 @@
         <v>3.04</v>
       </c>
       <c r="J2" s="9" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="K2" s="9" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="L2" s="9" t="n"/>
     </row>
@@ -17228,7 +17228,7 @@
         </is>
       </c>
       <c r="E3" s="7" t="n">
-        <v>12801</v>
+        <v>12442</v>
       </c>
       <c r="F3" s="9" t="n">
         <v>0.42</v>
@@ -17243,10 +17243,10 @@
         <v>2.72</v>
       </c>
       <c r="J3" s="9" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="K3" s="9" t="n">
         <v>1.07</v>
-      </c>
-      <c r="K3" s="9" t="n">
-        <v>1.1</v>
       </c>
       <c r="L3" s="9" t="n"/>
     </row>
@@ -17272,7 +17272,7 @@
         </is>
       </c>
       <c r="E4" s="7" t="n">
-        <v>10860</v>
+        <v>10677</v>
       </c>
       <c r="F4" s="9" t="n">
         <v>0.73</v>
@@ -17287,10 +17287,10 @@
         <v>1.93</v>
       </c>
       <c r="J4" s="9" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="K4" s="9" t="n">
-        <v>0.98</v>
+        <v>0.96</v>
       </c>
       <c r="L4" s="9" t="n"/>
     </row>
@@ -17316,7 +17316,7 @@
         </is>
       </c>
       <c r="E5" s="7" t="n">
-        <v>13249</v>
+        <v>13048</v>
       </c>
       <c r="F5" s="9" t="n">
         <v>0.29</v>
@@ -17331,10 +17331,10 @@
         <v>0.96</v>
       </c>
       <c r="J5" s="9" t="n">
-        <v>0.51</v>
+        <v>0.5</v>
       </c>
       <c r="K5" s="9" t="n">
-        <v>0.48</v>
+        <v>0.47</v>
       </c>
       <c r="L5" s="9" t="n"/>
     </row>
@@ -17360,7 +17360,7 @@
         </is>
       </c>
       <c r="E6" s="7" t="n">
-        <v>1071</v>
+        <v>1064</v>
       </c>
       <c r="F6" s="9" t="n"/>
       <c r="G6" s="9" t="n"/>
@@ -17369,7 +17369,7 @@
         <v>2.09</v>
       </c>
       <c r="J6" s="9" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="K6" s="9" t="n">
         <v>1.03</v>
@@ -17398,7 +17398,7 @@
         </is>
       </c>
       <c r="E7" s="7" t="n">
-        <v>840</v>
+        <v>829</v>
       </c>
       <c r="F7" s="9" t="n">
         <v>0.18</v>
@@ -17438,7 +17438,7 @@
         </is>
       </c>
       <c r="E8" s="7" t="n">
-        <v>39658</v>
+        <v>39556</v>
       </c>
       <c r="F8" s="9" t="n">
         <v>1.68</v>
@@ -17478,7 +17478,7 @@
         </is>
       </c>
       <c r="E9" s="7" t="n">
-        <v>15029</v>
+        <v>14877</v>
       </c>
       <c r="F9" s="9" t="n">
         <v>1.34</v>
@@ -17493,10 +17493,10 @@
         <v>2.62</v>
       </c>
       <c r="J9" s="9" t="n">
-        <v>2.77</v>
+        <v>2.74</v>
       </c>
       <c r="K9" s="9" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="L9" s="9" t="n"/>
     </row>
@@ -17522,7 +17522,7 @@
         </is>
       </c>
       <c r="E10" s="7" t="n">
-        <v>2320</v>
+        <v>2322</v>
       </c>
       <c r="F10" s="9" t="n">
         <v>0.73</v>
@@ -17540,7 +17540,7 @@
         <v>0.7</v>
       </c>
       <c r="K10" s="9" t="n">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="L10" s="9" t="n"/>
     </row>
@@ -17566,7 +17566,7 @@
         </is>
       </c>
       <c r="E11" s="7" t="n">
-        <v>77441</v>
+        <v>75750</v>
       </c>
       <c r="F11" s="9" t="n"/>
       <c r="G11" s="9" t="n">
@@ -17582,10 +17582,10 @@
         <v>3.25</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>2.17</v>
+        <v>2.12</v>
       </c>
       <c r="L11" s="9" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="12">
@@ -17610,7 +17610,7 @@
         </is>
       </c>
       <c r="E12" s="7" t="n">
-        <v>11529</v>
+        <v>11415</v>
       </c>
       <c r="F12" s="9" t="n"/>
       <c r="G12" s="9" t="n">
@@ -17629,7 +17629,7 @@
         <v>0.7</v>
       </c>
       <c r="L12" s="9" t="n">
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="13">
@@ -17654,7 +17654,7 @@
         </is>
       </c>
       <c r="E13" s="7" t="n">
-        <v>16564</v>
+        <v>16109</v>
       </c>
       <c r="F13" s="9" t="n"/>
       <c r="G13" s="9" t="n">
@@ -17670,10 +17670,10 @@
         <v>2.02</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="L13" s="9" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="14">
@@ -17698,7 +17698,7 @@
         </is>
       </c>
       <c r="E14" s="7" t="n">
-        <v>2259</v>
+        <v>2276</v>
       </c>
       <c r="F14" s="9" t="n"/>
       <c r="G14" s="9" t="n">
@@ -17714,7 +17714,7 @@
         <v>1.59</v>
       </c>
       <c r="K14" s="9" t="n">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="L14" s="9" t="n">
         <v>0.89</v>
@@ -17782,7 +17782,7 @@
         </is>
       </c>
       <c r="E16" s="7" t="n">
-        <v>4396</v>
+        <v>4374</v>
       </c>
       <c r="F16" s="9" t="n">
         <v>0.12</v>
@@ -17826,7 +17826,7 @@
         </is>
       </c>
       <c r="E17" s="7" t="n">
-        <v>10943</v>
+        <v>10755</v>
       </c>
       <c r="F17" s="9" t="n">
         <v>0.86</v>
@@ -17841,10 +17841,10 @@
         <v>1.07</v>
       </c>
       <c r="J17" s="9" t="n">
-        <v>0.82</v>
+        <v>0.8</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>0.77</v>
+        <v>0.76</v>
       </c>
       <c r="L17" s="9" t="n"/>
     </row>
@@ -17870,7 +17870,7 @@
         </is>
       </c>
       <c r="E18" s="7" t="n">
-        <v>1236</v>
+        <v>1240</v>
       </c>
       <c r="F18" s="9" t="n"/>
       <c r="G18" s="9" t="n">
@@ -17886,7 +17886,7 @@
         <v>0.84</v>
       </c>
       <c r="K18" s="9" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="L18" s="9" t="n">
         <v>0.6899999999999999</v>
@@ -17914,7 +17914,7 @@
         </is>
       </c>
       <c r="E19" s="7" t="n">
-        <v>6655</v>
+        <v>6502</v>
       </c>
       <c r="F19" s="9" t="n"/>
       <c r="G19" s="9" t="n"/>
@@ -17925,10 +17925,10 @@
         <v>4.38</v>
       </c>
       <c r="J19" s="9" t="n">
-        <v>3.71</v>
+        <v>3.62</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="L19" s="9" t="n"/>
     </row>
@@ -17954,7 +17954,7 @@
         </is>
       </c>
       <c r="E20" s="7" t="n">
-        <v>926</v>
+        <v>913</v>
       </c>
       <c r="F20" s="9" t="n">
         <v>1.13</v>
@@ -17969,10 +17969,10 @@
         <v>7.54</v>
       </c>
       <c r="J20" s="9" t="n">
-        <v>2.06</v>
+        <v>2.03</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="L20" s="9" t="n"/>
     </row>
@@ -17998,7 +17998,7 @@
         </is>
       </c>
       <c r="E21" s="7" t="n">
-        <v>2033</v>
+        <v>1989</v>
       </c>
       <c r="F21" s="9" t="n">
         <v>0.6899999999999999</v>
@@ -18013,10 +18013,10 @@
         <v>2.61</v>
       </c>
       <c r="J21" s="9" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="L21" s="9" t="n"/>
     </row>
@@ -18042,7 +18042,7 @@
         </is>
       </c>
       <c r="E22" s="7" t="n">
-        <v>613</v>
+        <v>601</v>
       </c>
       <c r="F22" s="9" t="n">
         <v>1.29</v>
@@ -18057,10 +18057,10 @@
         <v>1.65</v>
       </c>
       <c r="J22" s="9" t="n">
-        <v>0.86</v>
+        <v>0.84</v>
       </c>
       <c r="K22" s="9" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="L22" s="9" t="n"/>
     </row>
@@ -18086,7 +18086,7 @@
         </is>
       </c>
       <c r="E23" s="7" t="n">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="F23" s="9" t="n">
         <v>0.72</v>
@@ -18101,10 +18101,10 @@
         <v>1.02</v>
       </c>
       <c r="J23" s="9" t="n">
-        <v>0.46</v>
+        <v>0.45</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>0.44</v>
+        <v>0.43</v>
       </c>
       <c r="L23" s="9" t="n"/>
     </row>
@@ -18130,7 +18130,7 @@
         </is>
       </c>
       <c r="E24" s="7" t="n">
-        <v>7526</v>
+        <v>7187</v>
       </c>
       <c r="F24" s="9" t="n">
         <v>1.78</v>
@@ -18145,10 +18145,10 @@
         <v>3.02</v>
       </c>
       <c r="J24" s="9" t="n">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>1.49</v>
+        <v>1.43</v>
       </c>
       <c r="L24" s="9" t="n"/>
     </row>
@@ -18174,7 +18174,7 @@
         </is>
       </c>
       <c r="E25" s="7" t="n">
-        <v>30784</v>
+        <v>29608</v>
       </c>
       <c r="F25" s="9" t="n">
         <v>0.53</v>
@@ -18189,10 +18189,10 @@
         <v>1.81</v>
       </c>
       <c r="J25" s="9" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="L25" s="9" t="n"/>
     </row>
@@ -18218,7 +18218,7 @@
         </is>
       </c>
       <c r="E26" s="7" t="n">
-        <v>7847</v>
+        <v>7178</v>
       </c>
       <c r="F26" s="9" t="n">
         <v>0.9</v>
@@ -18233,10 +18233,10 @@
         <v>2.14</v>
       </c>
       <c r="J26" s="9" t="n">
-        <v>2.02</v>
+        <v>1.85</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>1.69</v>
+        <v>1.54</v>
       </c>
       <c r="L26" s="9" t="n"/>
     </row>
@@ -18262,7 +18262,7 @@
         </is>
       </c>
       <c r="E27" s="7" t="n">
-        <v>9366</v>
+        <v>8640</v>
       </c>
       <c r="F27" s="9" t="n">
         <v>0.9</v>
@@ -18277,10 +18277,10 @@
         <v>2.78</v>
       </c>
       <c r="J27" s="9" t="n">
-        <v>2.76</v>
+        <v>2.55</v>
       </c>
       <c r="K27" s="9" t="n">
-        <v>2.52</v>
+        <v>2.32</v>
       </c>
       <c r="L27" s="9" t="n"/>
     </row>
@@ -18306,7 +18306,7 @@
         </is>
       </c>
       <c r="E28" s="7" t="n">
-        <v>6819</v>
+        <v>6595</v>
       </c>
       <c r="F28" s="9" t="n">
         <v>0.98</v>
@@ -18321,10 +18321,10 @@
         <v>3.51</v>
       </c>
       <c r="J28" s="9" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="K28" s="9" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="L28" s="9" t="n"/>
     </row>
@@ -18350,7 +18350,7 @@
         </is>
       </c>
       <c r="E29" s="7" t="n">
-        <v>135089</v>
+        <v>138357</v>
       </c>
       <c r="F29" s="9" t="n">
         <v>1.87</v>
@@ -18365,10 +18365,10 @@
         <v>1.48</v>
       </c>
       <c r="J29" s="9" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="L29" s="9" t="n"/>
     </row>
@@ -18394,7 +18394,7 @@
         </is>
       </c>
       <c r="E30" s="7" t="n">
-        <v>78432</v>
+        <v>78303</v>
       </c>
       <c r="F30" s="9" t="n">
         <v>2.28</v>
@@ -18438,7 +18438,7 @@
         </is>
       </c>
       <c r="E31" s="7" t="n">
-        <v>94850</v>
+        <v>94463</v>
       </c>
       <c r="F31" s="9" t="n">
         <v>1.73</v>
@@ -18453,10 +18453,10 @@
         <v>1.73</v>
       </c>
       <c r="J31" s="9" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="K31" s="9" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="L31" s="9" t="n"/>
     </row>
@@ -18482,7 +18482,7 @@
         </is>
       </c>
       <c r="E32" s="7" t="n">
-        <v>261357</v>
+        <v>256390</v>
       </c>
       <c r="F32" s="9" t="n">
         <v>2.21</v>
@@ -18497,10 +18497,10 @@
         <v>2.78</v>
       </c>
       <c r="J32" s="9" t="n">
-        <v>2.69</v>
+        <v>2.64</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="L32" s="9" t="n"/>
     </row>
@@ -18526,7 +18526,7 @@
         </is>
       </c>
       <c r="E33" s="7" t="n">
-        <v>10943</v>
+        <v>10755</v>
       </c>
       <c r="F33" s="9" t="n">
         <v>0.86</v>
@@ -18541,10 +18541,10 @@
         <v>1.07</v>
       </c>
       <c r="J33" s="9" t="n">
-        <v>0.82</v>
+        <v>0.8</v>
       </c>
       <c r="K33" s="9" t="n">
-        <v>0.77</v>
+        <v>0.76</v>
       </c>
       <c r="L33" s="9" t="n"/>
     </row>
@@ -18570,7 +18570,7 @@
         </is>
       </c>
       <c r="E34" s="7" t="n">
-        <v>52319</v>
+        <v>52463</v>
       </c>
       <c r="F34" s="9" t="n">
         <v>1.26</v>
@@ -18585,10 +18585,10 @@
         <v>7.21</v>
       </c>
       <c r="J34" s="9" t="n">
-        <v>3.34</v>
+        <v>3.36</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="L34" s="9" t="n"/>
     </row>
@@ -18614,7 +18614,7 @@
         </is>
       </c>
       <c r="E35" s="7" t="n">
-        <v>75701</v>
+        <v>75806</v>
       </c>
       <c r="F35" s="9" t="n">
         <v>1.24</v>
@@ -18658,7 +18658,7 @@
         </is>
       </c>
       <c r="E36" s="7" t="n">
-        <v>31323</v>
+        <v>31374</v>
       </c>
       <c r="F36" s="9" t="n">
         <v>0.32</v>
@@ -18702,7 +18702,7 @@
         </is>
       </c>
       <c r="E37" s="7" t="n">
-        <v>34602</v>
+        <v>35175</v>
       </c>
       <c r="F37" s="9" t="n">
         <v>1.3</v>
@@ -18717,10 +18717,10 @@
         <v>3.66</v>
       </c>
       <c r="J37" s="9" t="n">
-        <v>3.49</v>
+        <v>3.57</v>
       </c>
       <c r="K37" s="9" t="n">
-        <v>2.87</v>
+        <v>2.93</v>
       </c>
       <c r="L37" s="9" t="n"/>
     </row>
@@ -18746,7 +18746,7 @@
         </is>
       </c>
       <c r="E38" s="7" t="n">
-        <v>3236</v>
+        <v>3142</v>
       </c>
       <c r="F38" s="9" t="n">
         <v>0.34</v>
@@ -18761,10 +18761,10 @@
         <v>1.25</v>
       </c>
       <c r="J38" s="9" t="n">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="K38" s="9" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="L38" s="9" t="n"/>
     </row>
@@ -18790,7 +18790,7 @@
         </is>
       </c>
       <c r="E39" s="7" t="n">
-        <v>3572</v>
+        <v>3514</v>
       </c>
       <c r="F39" s="9" t="n">
         <v>0.4</v>
@@ -18805,10 +18805,10 @@
         <v>0.63</v>
       </c>
       <c r="J39" s="9" t="n">
-        <v>0.5</v>
+        <v>0.49</v>
       </c>
       <c r="K39" s="9" t="n">
-        <v>0.48</v>
+        <v>0.47</v>
       </c>
       <c r="L39" s="9" t="n"/>
     </row>
@@ -18834,7 +18834,7 @@
         </is>
       </c>
       <c r="E40" s="7" t="n">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="F40" s="9" t="n">
         <v>0.19</v>
@@ -18874,7 +18874,7 @@
         </is>
       </c>
       <c r="E41" s="7" t="n">
-        <v>327586</v>
+        <v>319652</v>
       </c>
       <c r="F41" s="9" t="n">
         <v>2.08</v>
@@ -18889,10 +18889,10 @@
         <v>3.94</v>
       </c>
       <c r="J41" s="9" t="n">
-        <v>4.12</v>
+        <v>4.02</v>
       </c>
       <c r="K41" s="9" t="n">
-        <v>3.69</v>
+        <v>3.61</v>
       </c>
       <c r="L41" s="9" t="n"/>
     </row>
@@ -18918,7 +18918,7 @@
         </is>
       </c>
       <c r="E42" s="7" t="n">
-        <v>174004</v>
+        <v>174688</v>
       </c>
       <c r="F42" s="9" t="n">
         <v>2.31</v>
@@ -18933,10 +18933,10 @@
         <v>2.79</v>
       </c>
       <c r="J42" s="9" t="n">
-        <v>4.23</v>
+        <v>4.25</v>
       </c>
       <c r="K42" s="9" t="n">
-        <v>3.9</v>
+        <v>3.91</v>
       </c>
       <c r="L42" s="9" t="n"/>
     </row>
@@ -18962,7 +18962,7 @@
         </is>
       </c>
       <c r="E43" s="7" t="n">
-        <v>14383</v>
+        <v>14271</v>
       </c>
       <c r="F43" s="9" t="n">
         <v>0.92</v>
@@ -18977,7 +18977,7 @@
         <v>0.63</v>
       </c>
       <c r="J43" s="9" t="n">
-        <v>0.79</v>
+        <v>0.78</v>
       </c>
       <c r="K43" s="9" t="n">
         <v>0.75</v>
@@ -19006,7 +19006,7 @@
         </is>
       </c>
       <c r="E44" s="7" t="n">
-        <v>38546</v>
+        <v>38449</v>
       </c>
       <c r="F44" s="9" t="n"/>
       <c r="G44" s="9" t="n">
@@ -19025,7 +19025,7 @@
         <v>1.36</v>
       </c>
       <c r="L44" s="9" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="45">
@@ -19050,7 +19050,7 @@
         </is>
       </c>
       <c r="E45" s="7" t="n">
-        <v>7107</v>
+        <v>7160</v>
       </c>
       <c r="F45" s="9" t="n"/>
       <c r="G45" s="9" t="n">
@@ -19066,10 +19066,10 @@
         <v>0.8</v>
       </c>
       <c r="K45" s="9" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="L45" s="9" t="n">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="46">
@@ -19094,7 +19094,7 @@
         </is>
       </c>
       <c r="E46" s="7" t="n">
-        <v>63992</v>
+        <v>63165</v>
       </c>
       <c r="F46" s="9" t="n">
         <v>0.8100000000000001</v>
@@ -19109,10 +19109,10 @@
         <v>1.26</v>
       </c>
       <c r="J46" s="9" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="K46" s="9" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="L46" s="9" t="n"/>
     </row>
@@ -19138,7 +19138,7 @@
         </is>
       </c>
       <c r="E47" s="7" t="n">
-        <v>25291</v>
+        <v>25225</v>
       </c>
       <c r="F47" s="9" t="n">
         <v>1.66</v>
@@ -19182,7 +19182,7 @@
         </is>
       </c>
       <c r="E48" s="7" t="n">
-        <v>12599</v>
+        <v>12566</v>
       </c>
       <c r="F48" s="9" t="n">
         <v>0.64</v>
@@ -19226,7 +19226,7 @@
         </is>
       </c>
       <c r="E49" s="7" t="n">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="F49" s="9" t="n">
         <v>0.49</v>
@@ -19241,10 +19241,10 @@
         <v>0.59</v>
       </c>
       <c r="J49" s="9" t="n">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="K49" s="9" t="n">
-        <v>0.32</v>
+        <v>0.31</v>
       </c>
       <c r="L49" s="9" t="n"/>
     </row>
@@ -19270,7 +19270,7 @@
         </is>
       </c>
       <c r="E50" s="7" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F50" s="9" t="n">
         <v>0.32</v>
@@ -19350,7 +19350,7 @@
         </is>
       </c>
       <c r="E52" s="7" t="n">
-        <v>70101</v>
+        <v>69335</v>
       </c>
       <c r="F52" s="9" t="n">
         <v>2.12</v>
@@ -19365,10 +19365,10 @@
         <v>3.17</v>
       </c>
       <c r="J52" s="9" t="n">
-        <v>3.88</v>
+        <v>3.84</v>
       </c>
       <c r="K52" s="9" t="n">
-        <v>3.52</v>
+        <v>3.49</v>
       </c>
       <c r="L52" s="9" t="n"/>
     </row>
@@ -19832,7 +19832,7 @@
         </is>
       </c>
       <c r="G6" s="14" t="n">
-        <v>305000</v>
+        <v>295500</v>
       </c>
       <c r="H6" s="14" t="n">
         <v>29839.46</v>
@@ -19860,7 +19860,7 @@
         <v>30.27</v>
       </c>
       <c r="Q6" s="14" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="R6" s="14" t="inlineStr">
         <is>
@@ -19905,7 +19905,7 @@
         </is>
       </c>
       <c r="G7" s="14" t="n">
-        <v>305000</v>
+        <v>295500</v>
       </c>
       <c r="H7" s="14" t="n">
         <v>34806.34</v>
@@ -19923,17 +19923,17 @@
         <v>15056687726226.81</v>
       </c>
       <c r="M7" s="14" t="n">
-        <v>8.76</v>
+        <v>8.49</v>
       </c>
       <c r="N7" s="14" t="n"/>
       <c r="O7" s="14" t="n">
-        <v>2.13</v>
+        <v>2.06</v>
       </c>
       <c r="P7" s="14" t="n">
         <v>27.02</v>
       </c>
       <c r="Q7" s="14" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="R7" s="14" t="inlineStr">
         <is>
@@ -20327,7 +20327,7 @@
         </is>
       </c>
       <c r="G13" s="14" t="n">
-        <v>55300</v>
+        <v>53700</v>
       </c>
       <c r="H13" s="14" t="n">
         <v>6104.24</v>
@@ -20355,7 +20355,7 @@
         <v>27.12</v>
       </c>
       <c r="Q13" s="14" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="R13" s="14" t="inlineStr">
         <is>
@@ -20400,7 +20400,7 @@
         </is>
       </c>
       <c r="G14" s="14" t="n">
-        <v>55300</v>
+        <v>53700</v>
       </c>
       <c r="H14" s="14" t="n">
         <v>6182.11</v>
@@ -20418,17 +20418,17 @@
         <v>9934752906723.203</v>
       </c>
       <c r="M14" s="14" t="n">
-        <v>8.949999999999999</v>
+        <v>8.69</v>
       </c>
       <c r="N14" s="14" t="n"/>
       <c r="O14" s="14" t="n">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="P14" s="14" t="n">
         <v>21.08</v>
       </c>
       <c r="Q14" s="14" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="R14" s="14" t="inlineStr">
         <is>
@@ -20820,7 +20820,7 @@
         </is>
       </c>
       <c r="G20" s="14" t="n">
-        <v>16830</v>
+        <v>16530</v>
       </c>
       <c r="H20" s="14" t="n">
         <v>1175.69</v>
@@ -20848,7 +20848,7 @@
         <v>20</v>
       </c>
       <c r="Q20" s="14" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="R20" s="14" t="inlineStr">
         <is>
@@ -20893,7 +20893,7 @@
         </is>
       </c>
       <c r="G21" s="14" t="n">
-        <v>16830</v>
+        <v>16530</v>
       </c>
       <c r="H21" s="14" t="n">
         <v>1691.1</v>
@@ -20911,17 +20911,17 @@
         <v>6597608582819.35</v>
       </c>
       <c r="M21" s="14" t="n">
-        <v>9.949999999999999</v>
+        <v>9.77</v>
       </c>
       <c r="N21" s="14" t="n"/>
       <c r="O21" s="14" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="P21" s="14" t="n">
         <v>24.58</v>
       </c>
       <c r="Q21" s="14" t="n">
-        <v>0.98</v>
+        <v>0.96</v>
       </c>
       <c r="R21" s="14" t="inlineStr">
         <is>
@@ -21317,7 +21317,7 @@
         </is>
       </c>
       <c r="G27" s="14" t="n">
-        <v>248000</v>
+        <v>244000</v>
       </c>
       <c r="H27" s="14" t="n">
         <v>51923.58</v>
@@ -21345,7 +21345,7 @@
         <v>27.62</v>
       </c>
       <c r="Q27" s="14" t="n">
-        <v>0.51</v>
+        <v>0.5</v>
       </c>
       <c r="R27" s="14" t="inlineStr">
         <is>
@@ -21390,7 +21390,7 @@
         </is>
       </c>
       <c r="G28" s="14" t="n">
-        <v>248000</v>
+        <v>244000</v>
       </c>
       <c r="H28" s="14" t="n">
         <v>60335.65</v>
@@ -21408,17 +21408,17 @@
         <v>19743148063746.41</v>
       </c>
       <c r="M28" s="14" t="n">
-        <v>4.11</v>
+        <v>4.04</v>
       </c>
       <c r="N28" s="14" t="n"/>
       <c r="O28" s="14" t="n">
-        <v>0.89</v>
+        <v>0.87</v>
       </c>
       <c r="P28" s="14" t="n">
         <v>23.69</v>
       </c>
       <c r="Q28" s="14" t="n">
-        <v>0.48</v>
+        <v>0.47</v>
       </c>
       <c r="R28" s="14" t="inlineStr">
         <is>
@@ -21786,7 +21786,7 @@
         </is>
       </c>
       <c r="G34" s="14" t="n">
-        <v>37050</v>
+        <v>36800</v>
       </c>
       <c r="H34" s="14" t="n">
         <v>7656.2</v>
@@ -21814,7 +21814,7 @@
         <v>24.44</v>
       </c>
       <c r="Q34" s="14" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="R34" s="14" t="inlineStr">
         <is>
@@ -21859,7 +21859,7 @@
         </is>
       </c>
       <c r="G35" s="14" t="n">
-        <v>37050</v>
+        <v>36800</v>
       </c>
       <c r="H35" s="14" t="n">
         <v>7804.33</v>
@@ -21877,7 +21877,7 @@
         <v>1664829720542.566</v>
       </c>
       <c r="M35" s="14" t="n">
-        <v>4.75</v>
+        <v>4.72</v>
       </c>
       <c r="N35" s="14" t="n"/>
       <c r="O35" s="14" t="n">
@@ -22279,7 +22279,7 @@
         </is>
       </c>
       <c r="G41" s="14" t="n">
-        <v>12320</v>
+        <v>12140</v>
       </c>
       <c r="H41" s="14" t="n"/>
       <c r="I41" s="14" t="n"/>
@@ -22342,7 +22342,7 @@
         </is>
       </c>
       <c r="G42" s="14" t="n">
-        <v>12320</v>
+        <v>12140</v>
       </c>
       <c r="H42" s="14" t="n"/>
       <c r="I42" s="14" t="n"/>
@@ -23243,7 +23243,7 @@
         </is>
       </c>
       <c r="G55" s="14" t="n">
-        <v>4.88</v>
+        <v>4.83</v>
       </c>
       <c r="H55" s="14" t="n">
         <v>2.77</v>
@@ -23261,17 +23261,17 @@
         <v>38233818155.83939</v>
       </c>
       <c r="M55" s="14" t="n">
-        <v>9.17</v>
+        <v>9.08</v>
       </c>
       <c r="N55" s="14" t="n"/>
       <c r="O55" s="14" t="n">
-        <v>2.61</v>
+        <v>2.59</v>
       </c>
       <c r="P55" s="14" t="n">
         <v>30.94</v>
       </c>
       <c r="Q55" s="14" t="n">
-        <v>2.77</v>
+        <v>2.74</v>
       </c>
       <c r="R55" s="14" t="inlineStr">
         <is>
@@ -23316,7 +23316,7 @@
         </is>
       </c>
       <c r="G56" s="14" t="n">
-        <v>4.88</v>
+        <v>4.83</v>
       </c>
       <c r="H56" s="14" t="n">
         <v>3.07</v>
@@ -23334,17 +23334,17 @@
         <v>44999698854.56541</v>
       </c>
       <c r="M56" s="14" t="n">
-        <v>8.26</v>
+        <v>8.18</v>
       </c>
       <c r="N56" s="14" t="n"/>
       <c r="O56" s="14" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="P56" s="14" t="n">
         <v>29.06</v>
       </c>
       <c r="Q56" s="14" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="R56" s="14" t="inlineStr">
         <is>
@@ -23760,7 +23760,7 @@
         <v>19125837218.80924</v>
       </c>
       <c r="M62" s="14" t="n">
-        <v>13.35</v>
+        <v>13.37</v>
       </c>
       <c r="N62" s="14" t="n"/>
       <c r="O62" s="14" t="n">
@@ -23833,7 +23833,7 @@
         <v>20951974378.675</v>
       </c>
       <c r="M63" s="14" t="n">
-        <v>6.52</v>
+        <v>6.53</v>
       </c>
       <c r="N63" s="14" t="n"/>
       <c r="O63" s="14" t="n">
@@ -23843,7 +23843,7 @@
         <v>11.85</v>
       </c>
       <c r="Q63" s="14" t="n">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="R63" s="14" t="inlineStr">
         <is>
@@ -24241,7 +24241,7 @@
         </is>
       </c>
       <c r="G69" s="14" t="n">
-        <v>3614</v>
+        <v>3534</v>
       </c>
       <c r="H69" s="14" t="n">
         <v>134.68</v>
@@ -24259,17 +24259,17 @@
         <v>3414081930273.525</v>
       </c>
       <c r="M69" s="14" t="n">
-        <v>26.83</v>
+        <v>26.24</v>
       </c>
       <c r="N69" s="14" t="n"/>
       <c r="O69" s="14" t="n">
-        <v>3.56</v>
+        <v>3.48</v>
       </c>
       <c r="P69" s="14" t="n">
         <v>13.92</v>
       </c>
       <c r="Q69" s="14" t="n">
-        <v>2.17</v>
+        <v>2.12</v>
       </c>
       <c r="R69" s="14" t="inlineStr">
         <is>
@@ -24314,7 +24314,7 @@
         </is>
       </c>
       <c r="G70" s="14" t="n">
-        <v>3614</v>
+        <v>3534</v>
       </c>
       <c r="H70" s="14" t="n">
         <v>153.07</v>
@@ -24332,17 +24332,17 @@
         <v>3784052023498.018</v>
       </c>
       <c r="M70" s="14" t="n">
-        <v>23.61</v>
+        <v>23.09</v>
       </c>
       <c r="N70" s="14" t="n"/>
       <c r="O70" s="14" t="n">
-        <v>3.21</v>
+        <v>3.14</v>
       </c>
       <c r="P70" s="14" t="n">
         <v>14.29</v>
       </c>
       <c r="Q70" s="14" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="R70" s="14" t="inlineStr">
         <is>
@@ -24740,7 +24740,7 @@
         </is>
       </c>
       <c r="G76" s="14" t="n">
-        <v>2163</v>
+        <v>2141</v>
       </c>
       <c r="H76" s="14" t="n">
         <v>142.43</v>
@@ -24758,11 +24758,11 @@
         <v>968719416048.4681</v>
       </c>
       <c r="M76" s="14" t="n">
-        <v>15.19</v>
+        <v>15.03</v>
       </c>
       <c r="N76" s="14" t="n"/>
       <c r="O76" s="14" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="P76" s="14" t="n">
         <v>12.89</v>
@@ -24813,7 +24813,7 @@
         </is>
       </c>
       <c r="G77" s="14" t="n">
-        <v>2163</v>
+        <v>2141</v>
       </c>
       <c r="H77" s="14" t="n">
         <v>162.98</v>
@@ -24831,17 +24831,17 @@
         <v>1072390237896.21</v>
       </c>
       <c r="M77" s="14" t="n">
-        <v>13.27</v>
+        <v>13.14</v>
       </c>
       <c r="N77" s="14" t="n"/>
       <c r="O77" s="14" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="P77" s="14" t="n">
         <v>13.35</v>
       </c>
       <c r="Q77" s="14" t="n">
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="R77" s="14" t="inlineStr">
         <is>
@@ -25237,7 +25237,7 @@
         </is>
       </c>
       <c r="G83" s="14" t="n">
-        <v>2450</v>
+        <v>2382</v>
       </c>
       <c r="H83" s="14" t="n">
         <v>176.91</v>
@@ -25255,17 +25255,17 @@
         <v>815093716660.2814</v>
       </c>
       <c r="M83" s="14" t="n">
-        <v>13.85</v>
+        <v>13.46</v>
       </c>
       <c r="N83" s="14" t="n"/>
       <c r="O83" s="14" t="n">
-        <v>3.19</v>
+        <v>3.1</v>
       </c>
       <c r="P83" s="14" t="n">
         <v>25.56</v>
       </c>
       <c r="Q83" s="14" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="R83" s="14" t="inlineStr">
         <is>
@@ -25310,7 +25310,7 @@
         </is>
       </c>
       <c r="G84" s="14" t="n">
-        <v>2450</v>
+        <v>2382</v>
       </c>
       <c r="H84" s="14" t="n">
         <v>154.53</v>
@@ -25328,17 +25328,17 @@
         <v>957348937809.2065</v>
       </c>
       <c r="M84" s="14" t="n">
-        <v>15.85</v>
+        <v>15.41</v>
       </c>
       <c r="N84" s="14" t="n"/>
       <c r="O84" s="14" t="n">
-        <v>2.71</v>
+        <v>2.64</v>
       </c>
       <c r="P84" s="14" t="n">
         <v>18.49</v>
       </c>
       <c r="Q84" s="14" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="R84" s="14" t="inlineStr">
         <is>
@@ -25736,7 +25736,7 @@
         </is>
       </c>
       <c r="G90" s="14" t="n">
-        <v>3511</v>
+        <v>3536</v>
       </c>
       <c r="H90" s="14" t="n">
         <v>357.21</v>
@@ -25754,17 +25754,17 @@
         <v>259885320112.1904</v>
       </c>
       <c r="M90" s="14" t="n">
-        <v>9.83</v>
+        <v>9.9</v>
       </c>
       <c r="N90" s="14" t="n"/>
       <c r="O90" s="14" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P90" s="14" t="n">
         <v>14.74</v>
       </c>
       <c r="Q90" s="14" t="n">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="R90" s="14" t="inlineStr">
         <is>
@@ -25809,7 +25809,7 @@
         </is>
       </c>
       <c r="G91" s="14" t="n">
-        <v>3511</v>
+        <v>3536</v>
       </c>
       <c r="H91" s="14" t="n">
         <v>371.62</v>
@@ -25827,11 +25827,11 @@
         <v>291908147365.1342</v>
       </c>
       <c r="M91" s="14" t="n">
-        <v>9.449999999999999</v>
+        <v>9.52</v>
       </c>
       <c r="N91" s="14" t="n"/>
       <c r="O91" s="14" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P91" s="14" t="n">
         <v>13.59</v>
@@ -26235,7 +26235,7 @@
         </is>
       </c>
       <c r="G97" s="14" t="n">
-        <v>10400</v>
+        <v>10340</v>
       </c>
       <c r="H97" s="14" t="n"/>
       <c r="I97" s="14" t="n"/>
@@ -26292,7 +26292,7 @@
         </is>
       </c>
       <c r="G98" s="14" t="n">
-        <v>10400</v>
+        <v>10340</v>
       </c>
       <c r="H98" s="14" t="n"/>
       <c r="I98" s="14" t="n"/>
@@ -26698,7 +26698,7 @@
         </is>
       </c>
       <c r="G104" s="14" t="n">
-        <v>12.06</v>
+        <v>12.02</v>
       </c>
       <c r="H104" s="14" t="n">
         <v>0.55</v>
@@ -26716,11 +26716,11 @@
         <v>1174408680.1575</v>
       </c>
       <c r="M104" s="14" t="n">
-        <v>22.09</v>
+        <v>22</v>
       </c>
       <c r="N104" s="14" t="n"/>
       <c r="O104" s="14" t="n">
-        <v>3.33</v>
+        <v>3.32</v>
       </c>
       <c r="P104" s="14" t="n">
         <v>16.31</v>
@@ -26771,7 +26771,7 @@
         </is>
       </c>
       <c r="G105" s="14" t="n">
-        <v>12.06</v>
+        <v>12.02</v>
       </c>
       <c r="H105" s="14" t="n">
         <v>0.82</v>
@@ -26789,11 +26789,11 @@
         <v>1440753677.56484</v>
       </c>
       <c r="M105" s="14" t="n">
-        <v>14.69</v>
+        <v>14.63</v>
       </c>
       <c r="N105" s="14" t="n"/>
       <c r="O105" s="14" t="n">
-        <v>2.72</v>
+        <v>2.71</v>
       </c>
       <c r="P105" s="14" t="n">
         <v>20.37</v>
@@ -27197,7 +27197,7 @@
         </is>
       </c>
       <c r="G111" s="14" t="n">
-        <v>278.86</v>
+        <v>274.08</v>
       </c>
       <c r="H111" s="14" t="n">
         <v>18.5</v>
@@ -27215,17 +27215,17 @@
         <v>5561470755.014853</v>
       </c>
       <c r="M111" s="14" t="n">
-        <v>15.07</v>
+        <v>14.81</v>
       </c>
       <c r="N111" s="14" t="n"/>
       <c r="O111" s="14" t="n">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="P111" s="14" t="n">
         <v>13.65</v>
       </c>
       <c r="Q111" s="14" t="n">
-        <v>0.82</v>
+        <v>0.8</v>
       </c>
       <c r="R111" s="14" t="inlineStr">
         <is>
@@ -27270,7 +27270,7 @@
         </is>
       </c>
       <c r="G112" s="14" t="n">
-        <v>278.86</v>
+        <v>274.08</v>
       </c>
       <c r="H112" s="14" t="n">
         <v>21.01</v>
@@ -27288,17 +27288,17 @@
         <v>6116222709.314589</v>
       </c>
       <c r="M112" s="14" t="n">
-        <v>13.27</v>
+        <v>13.04</v>
       </c>
       <c r="N112" s="14" t="n"/>
       <c r="O112" s="14" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="P112" s="14" t="n">
         <v>14.12</v>
       </c>
       <c r="Q112" s="14" t="n">
-        <v>0.77</v>
+        <v>0.76</v>
       </c>
       <c r="R112" s="14" t="inlineStr">
         <is>
@@ -27690,7 +27690,7 @@
         </is>
       </c>
       <c r="G118" s="14" t="n">
-        <v>4.16</v>
+        <v>4.18</v>
       </c>
       <c r="H118" s="14" t="n">
         <v>0.23</v>
@@ -27708,17 +27708,17 @@
         <v>1329243564.59849</v>
       </c>
       <c r="M118" s="14" t="n">
-        <v>18.35</v>
+        <v>18.42</v>
       </c>
       <c r="N118" s="14" t="n"/>
       <c r="O118" s="14" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P118" s="14" t="n">
         <v>7.47</v>
       </c>
       <c r="Q118" s="14" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="R118" s="14" t="inlineStr">
         <is>
@@ -27763,7 +27763,7 @@
         </is>
       </c>
       <c r="G119" s="14" t="n">
-        <v>4.16</v>
+        <v>4.18</v>
       </c>
       <c r="H119" s="14" t="n">
         <v>0.26</v>
@@ -27781,11 +27781,11 @@
         <v>1437828645.45737</v>
       </c>
       <c r="M119" s="14" t="n">
-        <v>16.17</v>
+        <v>16.23</v>
       </c>
       <c r="N119" s="14" t="n"/>
       <c r="O119" s="14" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P119" s="14" t="n">
         <v>7.85</v>
@@ -28169,7 +28169,7 @@
         </is>
       </c>
       <c r="G125" s="14" t="n">
-        <v>196500</v>
+        <v>191800</v>
       </c>
       <c r="H125" s="14" t="n">
         <v>7652.69</v>
@@ -28197,7 +28197,7 @@
         <v>38.12</v>
       </c>
       <c r="Q125" s="14" t="n">
-        <v>3.71</v>
+        <v>3.62</v>
       </c>
       <c r="R125" s="14" t="inlineStr">
         <is>
@@ -28242,7 +28242,7 @@
         </is>
       </c>
       <c r="G126" s="14" t="n">
-        <v>196500</v>
+        <v>191800</v>
       </c>
       <c r="H126" s="14" t="n">
         <v>9357.49</v>
@@ -28260,17 +28260,17 @@
         <v>1234616472831.365</v>
       </c>
       <c r="M126" s="14" t="n">
-        <v>21</v>
+        <v>20.5</v>
       </c>
       <c r="N126" s="14" t="n"/>
       <c r="O126" s="14" t="n">
-        <v>7.14</v>
+        <v>6.96</v>
       </c>
       <c r="P126" s="14" t="n">
         <v>37.39</v>
       </c>
       <c r="Q126" s="14" t="n">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="R126" s="14" t="inlineStr">
         <is>
@@ -28668,7 +28668,7 @@
         </is>
       </c>
       <c r="G132" s="14" t="n">
-        <v>36150</v>
+        <v>35600</v>
       </c>
       <c r="H132" s="14" t="n">
         <v>3734</v>
@@ -28696,7 +28696,7 @@
         <v>25.25</v>
       </c>
       <c r="Q132" s="14" t="n">
-        <v>2.06</v>
+        <v>2.03</v>
       </c>
       <c r="R132" s="14" t="inlineStr">
         <is>
@@ -28741,7 +28741,7 @@
         </is>
       </c>
       <c r="G133" s="14" t="n">
-        <v>36150</v>
+        <v>35600</v>
       </c>
       <c r="H133" s="14" t="n">
         <v>5008</v>
@@ -28759,17 +28759,17 @@
         <v>785453728266</v>
       </c>
       <c r="M133" s="14" t="n">
-        <v>7.22</v>
+        <v>7.11</v>
       </c>
       <c r="N133" s="14" t="n"/>
       <c r="O133" s="14" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="P133" s="14" t="n">
         <v>24.25</v>
       </c>
       <c r="Q133" s="14" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="R133" s="14" t="inlineStr">
         <is>
@@ -29161,7 +29161,7 @@
         </is>
       </c>
       <c r="G139" s="14" t="n">
-        <v>32250</v>
+        <v>31525</v>
       </c>
       <c r="H139" s="14" t="n">
         <v>2247.3</v>
@@ -29189,7 +29189,7 @@
         <v>28.77</v>
       </c>
       <c r="Q139" s="14" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="R139" s="14" t="inlineStr">
         <is>
@@ -29234,7 +29234,7 @@
         </is>
       </c>
       <c r="G140" s="14" t="n">
-        <v>32250</v>
+        <v>31525</v>
       </c>
       <c r="H140" s="14" t="n">
         <v>3635.11</v>
@@ -29252,17 +29252,17 @@
         <v>1046846601812.56</v>
       </c>
       <c r="M140" s="14" t="n">
-        <v>8.869999999999999</v>
+        <v>8.67</v>
       </c>
       <c r="N140" s="14" t="n"/>
       <c r="O140" s="14" t="n">
-        <v>2.57</v>
+        <v>2.51</v>
       </c>
       <c r="P140" s="14" t="n">
         <v>33.88</v>
       </c>
       <c r="Q140" s="14" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="R140" s="14" t="inlineStr">
         <is>
@@ -29658,7 +29658,7 @@
         </is>
       </c>
       <c r="G146" s="14" t="n">
-        <v>16100</v>
+        <v>15790</v>
       </c>
       <c r="H146" s="14" t="n">
         <v>2370.59</v>
@@ -29686,7 +29686,7 @@
         <v>18.68</v>
       </c>
       <c r="Q146" s="14" t="n">
-        <v>0.86</v>
+        <v>0.84</v>
       </c>
       <c r="R146" s="14" t="inlineStr">
         <is>
@@ -29731,7 +29731,7 @@
         </is>
       </c>
       <c r="G147" s="14" t="n">
-        <v>16100</v>
+        <v>15790</v>
       </c>
       <c r="H147" s="14" t="n">
         <v>2816.13</v>
@@ -29749,17 +29749,17 @@
         <v>800111224287.9514</v>
       </c>
       <c r="M147" s="14" t="n">
-        <v>5.72</v>
+        <v>5.61</v>
       </c>
       <c r="N147" s="14" t="n"/>
       <c r="O147" s="14" t="n">
-        <v>1.01</v>
+        <v>0.99</v>
       </c>
       <c r="P147" s="14" t="n">
         <v>19.16</v>
       </c>
       <c r="Q147" s="14" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="R147" s="14" t="inlineStr">
         <is>
@@ -30157,7 +30157,7 @@
         </is>
       </c>
       <c r="G153" s="14" t="n">
-        <v>13030</v>
+        <v>12830</v>
       </c>
       <c r="H153" s="14" t="n">
         <v>2442</v>
@@ -30185,7 +30185,7 @@
         <v>29.46</v>
       </c>
       <c r="Q153" s="14" t="n">
-        <v>0.46</v>
+        <v>0.45</v>
       </c>
       <c r="R153" s="14" t="inlineStr">
         <is>
@@ -30230,7 +30230,7 @@
         </is>
       </c>
       <c r="G154" s="14" t="n">
-        <v>13030</v>
+        <v>12830</v>
       </c>
       <c r="H154" s="14" t="n">
         <v>2901</v>
@@ -30248,17 +30248,17 @@
         <v>418828450507</v>
       </c>
       <c r="M154" s="14" t="n">
-        <v>4.49</v>
+        <v>4.42</v>
       </c>
       <c r="N154" s="14" t="n"/>
       <c r="O154" s="14" t="n">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="P154" s="14" t="n">
         <v>23.13</v>
       </c>
       <c r="Q154" s="14" t="n">
-        <v>0.44</v>
+        <v>0.43</v>
       </c>
       <c r="R154" s="14" t="inlineStr">
         <is>
@@ -30656,7 +30656,7 @@
         </is>
       </c>
       <c r="G160" s="14" t="n">
-        <v>102200</v>
+        <v>97500</v>
       </c>
       <c r="H160" s="14" t="n">
         <v>2449.48</v>
@@ -30684,7 +30684,7 @@
         <v>11.73</v>
       </c>
       <c r="Q160" s="14" t="n">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="R160" s="14" t="inlineStr">
         <is>
@@ -30729,7 +30729,7 @@
         </is>
       </c>
       <c r="G161" s="14" t="n">
-        <v>102200</v>
+        <v>97500</v>
       </c>
       <c r="H161" s="14" t="n">
         <v>4476.83</v>
@@ -30747,17 +30747,17 @@
         <v>2319715367260.464</v>
       </c>
       <c r="M161" s="14" t="n">
-        <v>22.83</v>
+        <v>21.78</v>
       </c>
       <c r="N161" s="14" t="n"/>
       <c r="O161" s="14" t="n">
-        <v>4.29</v>
+        <v>4.1</v>
       </c>
       <c r="P161" s="14" t="n">
         <v>20.19</v>
       </c>
       <c r="Q161" s="14" t="n">
-        <v>1.49</v>
+        <v>1.43</v>
       </c>
       <c r="R161" s="14" t="inlineStr">
         <is>
@@ -31155,7 +31155,7 @@
         </is>
       </c>
       <c r="G167" s="14" t="n">
-        <v>792000</v>
+        <v>761000</v>
       </c>
       <c r="H167" s="14" t="n">
         <v>46056.24</v>
@@ -31183,7 +31183,7 @@
         <v>20.69</v>
       </c>
       <c r="Q167" s="14" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="R167" s="14" t="inlineStr">
         <is>
@@ -31228,7 +31228,7 @@
         </is>
       </c>
       <c r="G168" s="14" t="n">
-        <v>792000</v>
+        <v>761000</v>
       </c>
       <c r="H168" s="14" t="n">
         <v>57796.36</v>
@@ -31246,17 +31246,17 @@
         <v>14106313861667.52</v>
       </c>
       <c r="M168" s="14" t="n">
-        <v>13.7</v>
+        <v>13.17</v>
       </c>
       <c r="N168" s="14" t="n"/>
       <c r="O168" s="14" t="n">
-        <v>2.89</v>
+        <v>2.78</v>
       </c>
       <c r="P168" s="14" t="n">
         <v>23.09</v>
       </c>
       <c r="Q168" s="14" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="R168" s="14" t="inlineStr">
         <is>
@@ -31654,7 +31654,7 @@
         </is>
       </c>
       <c r="G174" s="14" t="n">
-        <v>475500</v>
+        <v>434500</v>
       </c>
       <c r="H174" s="14" t="n">
         <v>15952.36</v>
@@ -31682,7 +31682,7 @@
         <v>21.8</v>
       </c>
       <c r="Q174" s="14" t="n">
-        <v>2.02</v>
+        <v>1.85</v>
       </c>
       <c r="R174" s="14" t="inlineStr">
         <is>
@@ -31727,7 +31727,7 @@
         </is>
       </c>
       <c r="G175" s="14" t="n">
-        <v>475500</v>
+        <v>434500</v>
       </c>
       <c r="H175" s="14" t="n">
         <v>23734.43</v>
@@ -31745,17 +31745,17 @@
         <v>2102000083957.019</v>
       </c>
       <c r="M175" s="14" t="n">
-        <v>20.03</v>
+        <v>18.31</v>
       </c>
       <c r="N175" s="14" t="n"/>
       <c r="O175" s="14" t="n">
-        <v>4.94</v>
+        <v>4.52</v>
       </c>
       <c r="P175" s="14" t="n">
         <v>27.27</v>
       </c>
       <c r="Q175" s="14" t="n">
-        <v>1.69</v>
+        <v>1.54</v>
       </c>
       <c r="R175" s="14" t="inlineStr">
         <is>
@@ -32151,7 +32151,7 @@
         </is>
       </c>
       <c r="G181" s="14" t="n">
-        <v>66300</v>
+        <v>61100</v>
       </c>
       <c r="H181" s="14" t="n">
         <v>1076.43</v>
@@ -32179,7 +32179,7 @@
         <v>2.7</v>
       </c>
       <c r="Q181" s="14" t="n">
-        <v>2.76</v>
+        <v>2.55</v>
       </c>
       <c r="R181" s="14" t="inlineStr">
         <is>
@@ -32224,7 +32224,7 @@
         </is>
       </c>
       <c r="G182" s="14" t="n">
-        <v>66300</v>
+        <v>61100</v>
       </c>
       <c r="H182" s="14" t="n">
         <v>2327.22</v>
@@ -32242,17 +32242,17 @@
         <v>5171213701216.773</v>
       </c>
       <c r="M182" s="14" t="n">
-        <v>28.49</v>
+        <v>26.25</v>
       </c>
       <c r="N182" s="14" t="n"/>
       <c r="O182" s="14" t="n">
-        <v>2.4</v>
+        <v>2.21</v>
       </c>
       <c r="P182" s="14" t="n">
         <v>8.6</v>
       </c>
       <c r="Q182" s="14" t="n">
-        <v>2.52</v>
+        <v>2.32</v>
       </c>
       <c r="R182" s="14" t="inlineStr">
         <is>
@@ -32650,7 +32650,7 @@
         </is>
       </c>
       <c r="G188" s="14" t="n">
-        <v>82700</v>
+        <v>79900</v>
       </c>
       <c r="H188" s="14" t="n">
         <v>7274.68</v>
@@ -32678,7 +32678,7 @@
         <v>23.27</v>
       </c>
       <c r="Q188" s="14" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="R188" s="14" t="inlineStr">
         <is>
@@ -32723,7 +32723,7 @@
         </is>
       </c>
       <c r="G189" s="14" t="n">
-        <v>82700</v>
+        <v>79900</v>
       </c>
       <c r="H189" s="14" t="n">
         <v>8364.940000000001</v>
@@ -32741,17 +32741,17 @@
         <v>4647533368918.296</v>
       </c>
       <c r="M189" s="14" t="n">
-        <v>9.890000000000001</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="N189" s="14" t="n"/>
       <c r="O189" s="14" t="n">
-        <v>1.94</v>
+        <v>1.88</v>
       </c>
       <c r="P189" s="14" t="n">
         <v>21.59</v>
       </c>
       <c r="Q189" s="14" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="R189" s="14" t="inlineStr">
         <is>
@@ -33149,35 +33149,35 @@
         </is>
       </c>
       <c r="G195" s="14" t="n">
-        <v>589.91</v>
+        <v>604.1799999999999</v>
       </c>
       <c r="H195" s="14" t="n">
-        <v>30.6</v>
+        <v>30.62</v>
       </c>
       <c r="I195" s="14" t="n">
-        <v>44.95</v>
+        <v>44.96</v>
       </c>
       <c r="J195" s="15" t="n">
-        <v>81203646650</v>
+        <v>81206789500</v>
       </c>
       <c r="K195" s="15" t="n">
-        <v>7006788570</v>
+        <v>7012813560</v>
       </c>
       <c r="L195" s="15" t="n">
-        <v>10293761491.843</v>
+        <v>10296833634.244</v>
       </c>
       <c r="M195" s="14" t="n">
-        <v>19.28</v>
+        <v>19.73</v>
       </c>
       <c r="N195" s="14" t="n"/>
       <c r="O195" s="14" t="n">
-        <v>13.12</v>
+        <v>13.44</v>
       </c>
       <c r="P195" s="14" t="n">
-        <v>82.36</v>
+        <v>82.42</v>
       </c>
       <c r="Q195" s="14" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="R195" s="14" t="inlineStr">
         <is>
@@ -33222,35 +33222,35 @@
         </is>
       </c>
       <c r="G196" s="14" t="n">
-        <v>589.91</v>
+        <v>604.1799999999999</v>
       </c>
       <c r="H196" s="14" t="n">
-        <v>33.08</v>
+        <v>33.13</v>
       </c>
       <c r="I196" s="14" t="n">
-        <v>61.82</v>
+        <v>61.86</v>
       </c>
       <c r="J196" s="15" t="n">
-        <v>86538592170</v>
+        <v>86590442170</v>
       </c>
       <c r="K196" s="15" t="n">
-        <v>7574534529.999999</v>
+        <v>7586557030</v>
       </c>
       <c r="L196" s="15" t="n">
-        <v>14156016648.69</v>
+        <v>14165219063.841</v>
       </c>
       <c r="M196" s="14" t="n">
-        <v>17.83</v>
+        <v>18.24</v>
       </c>
       <c r="N196" s="14" t="n"/>
       <c r="O196" s="14" t="n">
-        <v>9.539999999999999</v>
+        <v>9.77</v>
       </c>
       <c r="P196" s="14" t="n">
-        <v>61.96</v>
+        <v>62.03</v>
       </c>
       <c r="Q196" s="14" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="R196" s="14" t="inlineStr">
         <is>
@@ -33648,32 +33648,32 @@
         </is>
       </c>
       <c r="G202" s="14" t="n">
-        <v>552.35</v>
+        <v>551.4400000000001</v>
       </c>
       <c r="H202" s="14" t="n">
         <v>29.75</v>
       </c>
       <c r="I202" s="14" t="n">
-        <v>138.2</v>
+        <v>138.19</v>
       </c>
       <c r="J202" s="15" t="n">
-        <v>44057240810</v>
+        <v>44053074150</v>
       </c>
       <c r="K202" s="15" t="n">
-        <v>4224176546.24214</v>
+        <v>4223815873.36938</v>
       </c>
       <c r="L202" s="15" t="n">
-        <v>19623320064.58626</v>
+        <v>19623068242.7865</v>
       </c>
       <c r="M202" s="14" t="n">
-        <v>18.57</v>
+        <v>18.54</v>
       </c>
       <c r="N202" s="14" t="n"/>
       <c r="O202" s="14" t="n">
-        <v>4</v>
+        <v>3.99</v>
       </c>
       <c r="P202" s="14" t="n">
-        <v>23.28</v>
+        <v>23.27</v>
       </c>
       <c r="Q202" s="14" t="n">
         <v>1.78</v>
@@ -33721,32 +33721,32 @@
         </is>
       </c>
       <c r="G203" s="14" t="n">
-        <v>552.35</v>
+        <v>551.4400000000001</v>
       </c>
       <c r="H203" s="14" t="n">
-        <v>30.07</v>
+        <v>30.03</v>
       </c>
       <c r="I203" s="14" t="n">
-        <v>159.19</v>
+        <v>159.16</v>
       </c>
       <c r="J203" s="15" t="n">
-        <v>46860987480</v>
+        <v>46880306230</v>
       </c>
       <c r="K203" s="15" t="n">
-        <v>4269196756.59984</v>
+        <v>4264462570.15188</v>
       </c>
       <c r="L203" s="15" t="n">
-        <v>22604073240.04427</v>
+        <v>22600516009.26654</v>
       </c>
       <c r="M203" s="14" t="n">
-        <v>18.37</v>
+        <v>18.36</v>
       </c>
       <c r="N203" s="14" t="n"/>
       <c r="O203" s="14" t="n">
-        <v>3.47</v>
+        <v>3.46</v>
       </c>
       <c r="P203" s="14" t="n">
-        <v>20.22</v>
+        <v>20.2</v>
       </c>
       <c r="Q203" s="14" t="n">
         <v>1.67</v>
@@ -34147,7 +34147,7 @@
         </is>
       </c>
       <c r="G209" s="14" t="n">
-        <v>350.79</v>
+        <v>349.36</v>
       </c>
       <c r="H209" s="14" t="n">
         <v>17</v>
@@ -34165,17 +34165,17 @@
         <v>28485068164.94001</v>
       </c>
       <c r="M209" s="14" t="n">
-        <v>20.64</v>
+        <v>20.55</v>
       </c>
       <c r="N209" s="14" t="n"/>
       <c r="O209" s="14" t="n">
-        <v>3.33</v>
+        <v>3.32</v>
       </c>
       <c r="P209" s="14" t="n">
         <v>16.99</v>
       </c>
       <c r="Q209" s="14" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="R209" s="14" t="inlineStr">
         <is>
@@ -34220,7 +34220,7 @@
         </is>
       </c>
       <c r="G210" s="14" t="n">
-        <v>350.79</v>
+        <v>349.36</v>
       </c>
       <c r="H210" s="14" t="n">
         <v>18.64</v>
@@ -34238,17 +34238,17 @@
         <v>31623829122.08868</v>
       </c>
       <c r="M210" s="14" t="n">
-        <v>18.82</v>
+        <v>18.75</v>
       </c>
       <c r="N210" s="14" t="n"/>
       <c r="O210" s="14" t="n">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="P210" s="14" t="n">
         <v>16.77</v>
       </c>
       <c r="Q210" s="14" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="R210" s="14" t="inlineStr">
         <is>
@@ -34646,35 +34646,35 @@
         </is>
       </c>
       <c r="G216" s="14" t="n">
-        <v>194.71</v>
+        <v>191.01</v>
       </c>
       <c r="H216" s="14" t="n">
-        <v>7.61</v>
+        <v>7.63</v>
       </c>
       <c r="I216" s="14" t="n">
-        <v>52.73</v>
+        <v>52.74</v>
       </c>
       <c r="J216" s="15" t="n">
-        <v>97261865160</v>
+        <v>97292341360</v>
       </c>
       <c r="K216" s="15" t="n">
-        <v>10213064240.3812</v>
+        <v>10242245574.45744</v>
       </c>
       <c r="L216" s="15" t="n">
-        <v>70775374286.16641</v>
+        <v>70791175978.56871</v>
       </c>
       <c r="M216" s="14" t="n">
-        <v>25.59</v>
+        <v>25.03</v>
       </c>
       <c r="N216" s="14" t="n"/>
       <c r="O216" s="14" t="n">
-        <v>3.69</v>
+        <v>3.62</v>
       </c>
       <c r="P216" s="14" t="n">
-        <v>15.02</v>
+        <v>15.06</v>
       </c>
       <c r="Q216" s="14" t="n">
-        <v>2.69</v>
+        <v>2.64</v>
       </c>
       <c r="R216" s="14" t="inlineStr">
         <is>
@@ -34719,35 +34719,35 @@
         </is>
       </c>
       <c r="G217" s="14" t="n">
-        <v>194.71</v>
+        <v>191.01</v>
       </c>
       <c r="H217" s="14" t="n">
         <v>8.029999999999999</v>
       </c>
       <c r="I217" s="14" t="n">
-        <v>57.07</v>
+        <v>57.09</v>
       </c>
       <c r="J217" s="15" t="n">
-        <v>104744928720</v>
+        <v>104778262050</v>
       </c>
       <c r="K217" s="15" t="n">
-        <v>10773992837.30484</v>
+        <v>10779831788.69544</v>
       </c>
       <c r="L217" s="15" t="n">
-        <v>76609491407.56699</v>
+        <v>76628454892.14729</v>
       </c>
       <c r="M217" s="14" t="n">
-        <v>24.26</v>
+        <v>23.78</v>
       </c>
       <c r="N217" s="14" t="n"/>
       <c r="O217" s="14" t="n">
-        <v>3.41</v>
+        <v>3.35</v>
       </c>
       <c r="P217" s="14" t="n">
         <v>14.62</v>
       </c>
       <c r="Q217" s="14" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="R217" s="14" t="inlineStr">
         <is>
@@ -35145,7 +35145,7 @@
         </is>
       </c>
       <c r="G223" s="14" t="n">
-        <v>278.86</v>
+        <v>274.08</v>
       </c>
       <c r="H223" s="14" t="n">
         <v>18.5</v>
@@ -35163,17 +35163,17 @@
         <v>5561470755.014853</v>
       </c>
       <c r="M223" s="14" t="n">
-        <v>15.07</v>
+        <v>14.81</v>
       </c>
       <c r="N223" s="14" t="n"/>
       <c r="O223" s="14" t="n">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="P223" s="14" t="n">
         <v>13.65</v>
       </c>
       <c r="Q223" s="14" t="n">
-        <v>0.82</v>
+        <v>0.8</v>
       </c>
       <c r="R223" s="14" t="inlineStr">
         <is>
@@ -35218,7 +35218,7 @@
         </is>
       </c>
       <c r="G224" s="14" t="n">
-        <v>278.86</v>
+        <v>274.08</v>
       </c>
       <c r="H224" s="14" t="n">
         <v>21.01</v>
@@ -35236,17 +35236,17 @@
         <v>6116222709.314589</v>
       </c>
       <c r="M224" s="14" t="n">
-        <v>13.27</v>
+        <v>13.04</v>
       </c>
       <c r="N224" s="14" t="n"/>
       <c r="O224" s="14" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="P224" s="14" t="n">
         <v>14.12</v>
       </c>
       <c r="Q224" s="14" t="n">
-        <v>0.77</v>
+        <v>0.76</v>
       </c>
       <c r="R224" s="14" t="inlineStr">
         <is>
@@ -35644,7 +35644,7 @@
         </is>
       </c>
       <c r="G230" s="14" t="n">
-        <v>1015</v>
+        <v>1019</v>
       </c>
       <c r="H230" s="14" t="n">
         <v>37.27</v>
@@ -35662,17 +35662,17 @@
         <v>5957336206.677702</v>
       </c>
       <c r="M230" s="14" t="n">
-        <v>27.23</v>
+        <v>27.34</v>
       </c>
       <c r="N230" s="14" t="n"/>
       <c r="O230" s="14" t="n">
-        <v>7.82</v>
+        <v>7.85</v>
       </c>
       <c r="P230" s="14" t="n">
         <v>31.18</v>
       </c>
       <c r="Q230" s="14" t="n">
-        <v>3.34</v>
+        <v>3.36</v>
       </c>
       <c r="R230" s="14" t="inlineStr">
         <is>
@@ -35717,7 +35717,7 @@
         </is>
       </c>
       <c r="G231" s="14" t="n">
-        <v>1015</v>
+        <v>1019</v>
       </c>
       <c r="H231" s="14" t="n">
         <v>52.99</v>
@@ -35735,17 +35735,17 @@
         <v>7302807985.536924</v>
       </c>
       <c r="M231" s="14" t="n">
-        <v>19.15</v>
+        <v>19.23</v>
       </c>
       <c r="N231" s="14" t="n"/>
       <c r="O231" s="14" t="n">
-        <v>6.38</v>
+        <v>6.4</v>
       </c>
       <c r="P231" s="14" t="n">
         <v>36.67</v>
       </c>
       <c r="Q231" s="14" t="n">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="R231" s="14" t="inlineStr">
         <is>
@@ -36143,7 +36143,7 @@
         </is>
       </c>
       <c r="G237" s="14" t="n">
-        <v>19.3</v>
+        <v>19.32</v>
       </c>
       <c r="H237" s="14" t="n">
         <v>0.84</v>
@@ -36161,7 +36161,7 @@
         <v>12966958880.27147</v>
       </c>
       <c r="M237" s="14" t="n">
-        <v>22.93</v>
+        <v>22.94</v>
       </c>
       <c r="N237" s="14" t="n"/>
       <c r="O237" s="14" t="n">
@@ -36216,7 +36216,7 @@
         </is>
       </c>
       <c r="G238" s="14" t="n">
-        <v>19.3</v>
+        <v>19.32</v>
       </c>
       <c r="H238" s="14" t="n">
         <v>0.96</v>
@@ -36234,7 +36234,7 @@
         <v>14312018303.47772</v>
       </c>
       <c r="M238" s="14" t="n">
-        <v>20.16</v>
+        <v>20.18</v>
       </c>
       <c r="N238" s="14" t="n"/>
       <c r="O238" s="14" t="n">
@@ -36642,7 +36642,7 @@
         </is>
       </c>
       <c r="G244" s="14" t="n">
-        <v>48.33</v>
+        <v>48.46</v>
       </c>
       <c r="H244" s="14" t="n">
         <v>2.41</v>
@@ -36660,11 +36660,11 @@
         <v>10512752480.55845</v>
       </c>
       <c r="M244" s="14" t="n">
-        <v>20.06</v>
+        <v>20.12</v>
       </c>
       <c r="N244" s="14" t="n"/>
       <c r="O244" s="14" t="n">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="P244" s="14" t="n">
         <v>13.85</v>
@@ -36715,7 +36715,7 @@
         </is>
       </c>
       <c r="G245" s="14" t="n">
-        <v>48.33</v>
+        <v>48.46</v>
       </c>
       <c r="H245" s="14" t="n">
         <v>2.89</v>
@@ -36733,11 +36733,11 @@
         <v>11655069739.36822</v>
       </c>
       <c r="M245" s="14" t="n">
-        <v>16.73</v>
+        <v>16.78</v>
       </c>
       <c r="N245" s="14" t="n"/>
       <c r="O245" s="14" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="P245" s="14" t="n">
         <v>15.03</v>
@@ -37141,35 +37141,35 @@
         </is>
       </c>
       <c r="G251" s="14" t="n">
-        <v>634.9</v>
+        <v>646.5</v>
       </c>
       <c r="H251" s="14" t="n">
-        <v>14.94</v>
+        <v>15.52</v>
       </c>
       <c r="I251" s="14" t="n">
-        <v>92.84999999999999</v>
+        <v>93.26000000000001</v>
       </c>
       <c r="J251" s="15" t="n">
-        <v>97930140070</v>
+        <v>97586015830</v>
       </c>
       <c r="K251" s="15" t="n">
-        <v>8052460948.7856</v>
+        <v>8365603225.515241</v>
       </c>
       <c r="L251" s="15" t="n">
-        <v>50038868493.76913</v>
+        <v>50260209789.75896</v>
       </c>
       <c r="M251" s="14" t="n">
-        <v>42.49</v>
+        <v>41.65</v>
       </c>
       <c r="N251" s="14" t="n"/>
       <c r="O251" s="14" t="n">
-        <v>6.84</v>
+        <v>6.93</v>
       </c>
       <c r="P251" s="14" t="n">
-        <v>17.25</v>
+        <v>17.88</v>
       </c>
       <c r="Q251" s="14" t="n">
-        <v>3.49</v>
+        <v>3.57</v>
       </c>
       <c r="R251" s="14" t="inlineStr">
         <is>
@@ -37214,13 +37214,13 @@
         </is>
       </c>
       <c r="G252" s="14" t="n">
-        <v>634.9</v>
+        <v>646.5</v>
       </c>
       <c r="H252" s="14" t="n">
         <v>19.04</v>
       </c>
       <c r="I252" s="14" t="n">
-        <v>108.69</v>
+        <v>109.01</v>
       </c>
       <c r="J252" s="15" t="n">
         <v>119097442780</v>
@@ -37229,20 +37229,20 @@
         <v>10259903003.39316</v>
       </c>
       <c r="L252" s="15" t="n">
-        <v>58579211753.7936</v>
+        <v>58752331505.66748</v>
       </c>
       <c r="M252" s="14" t="n">
-        <v>33.35</v>
+        <v>33.96</v>
       </c>
       <c r="N252" s="14" t="n"/>
       <c r="O252" s="14" t="n">
-        <v>5.84</v>
+        <v>5.93</v>
       </c>
       <c r="P252" s="14" t="n">
-        <v>18.89</v>
+        <v>18.82</v>
       </c>
       <c r="Q252" s="14" t="n">
-        <v>2.87</v>
+        <v>2.93</v>
       </c>
       <c r="R252" s="14" t="inlineStr">
         <is>
@@ -37640,7 +37640,7 @@
         </is>
       </c>
       <c r="G258" s="14" t="n">
-        <v>89300</v>
+        <v>86600</v>
       </c>
       <c r="H258" s="14" t="n">
         <v>12845</v>
@@ -37668,7 +37668,7 @@
         <v>18.21</v>
       </c>
       <c r="Q258" s="14" t="n">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="R258" s="14" t="inlineStr">
         <is>
@@ -37713,7 +37713,7 @@
         </is>
       </c>
       <c r="G259" s="14" t="n">
-        <v>89300</v>
+        <v>86600</v>
       </c>
       <c r="H259" s="14" t="n">
         <v>14544.8</v>
@@ -37731,17 +37731,17 @@
         <v>3054643400967.941</v>
       </c>
       <c r="M259" s="14" t="n">
-        <v>6.14</v>
+        <v>5.95</v>
       </c>
       <c r="N259" s="14" t="n"/>
       <c r="O259" s="14" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="P259" s="14" t="n">
         <v>25.62</v>
       </c>
       <c r="Q259" s="14" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="R259" s="14" t="inlineStr">
         <is>
@@ -38139,7 +38139,7 @@
         </is>
       </c>
       <c r="G265" s="14" t="n">
-        <v>49400</v>
+        <v>48550</v>
       </c>
       <c r="H265" s="14" t="n">
         <v>6119.71</v>
@@ -38167,7 +38167,7 @@
         <v>7.51</v>
       </c>
       <c r="Q265" s="14" t="n">
-        <v>0.5</v>
+        <v>0.49</v>
       </c>
       <c r="R265" s="14" t="inlineStr">
         <is>
@@ -38212,7 +38212,7 @@
         </is>
       </c>
       <c r="G266" s="14" t="n">
-        <v>49400</v>
+        <v>48550</v>
       </c>
       <c r="H266" s="14" t="n">
         <v>6251.93</v>
@@ -38230,17 +38230,17 @@
         <v>7988991728475.829</v>
       </c>
       <c r="M266" s="14" t="n">
-        <v>7.9</v>
+        <v>7.77</v>
       </c>
       <c r="N266" s="14" t="n"/>
       <c r="O266" s="14" t="n">
-        <v>0.59</v>
+        <v>0.58</v>
       </c>
       <c r="P266" s="14" t="n">
         <v>7.68</v>
       </c>
       <c r="Q266" s="14" t="n">
-        <v>0.48</v>
+        <v>0.47</v>
       </c>
       <c r="R266" s="14" t="inlineStr">
         <is>
@@ -38634,7 +38634,7 @@
         </is>
       </c>
       <c r="G272" s="14" t="n">
-        <v>7160</v>
+        <v>6960</v>
       </c>
       <c r="H272" s="14" t="n"/>
       <c r="I272" s="14" t="n"/>
@@ -38691,7 +38691,7 @@
         </is>
       </c>
       <c r="G273" s="14" t="n">
-        <v>7160</v>
+        <v>6960</v>
       </c>
       <c r="H273" s="14" t="n"/>
       <c r="I273" s="14" t="n"/>
@@ -39101,7 +39101,7 @@
         </is>
       </c>
       <c r="G279" s="14" t="n">
-        <v>704.05</v>
+        <v>687</v>
       </c>
       <c r="H279" s="14" t="n">
         <v>27.33</v>
@@ -39119,17 +39119,17 @@
         <v>30727864358.51151</v>
       </c>
       <c r="M279" s="14" t="n">
-        <v>25.76</v>
+        <v>25.14</v>
       </c>
       <c r="N279" s="14" t="n"/>
       <c r="O279" s="14" t="n">
-        <v>10.66</v>
+        <v>10.4</v>
       </c>
       <c r="P279" s="14" t="n">
         <v>48.86</v>
       </c>
       <c r="Q279" s="14" t="n">
-        <v>4.12</v>
+        <v>4.02</v>
       </c>
       <c r="R279" s="14" t="inlineStr">
         <is>
@@ -39174,7 +39174,7 @@
         </is>
       </c>
       <c r="G280" s="14" t="n">
-        <v>704.05</v>
+        <v>687</v>
       </c>
       <c r="H280" s="14" t="n">
         <v>32.59</v>
@@ -39192,17 +39192,17 @@
         <v>41947387673.8295</v>
       </c>
       <c r="M280" s="14" t="n">
-        <v>21.61</v>
+        <v>21.08</v>
       </c>
       <c r="N280" s="14" t="n"/>
       <c r="O280" s="14" t="n">
-        <v>7.81</v>
+        <v>7.62</v>
       </c>
       <c r="P280" s="14" t="n">
         <v>41.72</v>
       </c>
       <c r="Q280" s="14" t="n">
-        <v>3.69</v>
+        <v>3.61</v>
       </c>
       <c r="R280" s="14" t="inlineStr">
         <is>
@@ -39600,7 +39600,7 @@
         </is>
       </c>
       <c r="G286" s="14" t="n">
-        <v>643.62</v>
+        <v>646.15</v>
       </c>
       <c r="H286" s="14" t="n">
         <v>18.11</v>
@@ -39618,17 +39618,17 @@
         <v>29083067668.47782</v>
       </c>
       <c r="M286" s="14" t="n">
-        <v>35.53</v>
+        <v>35.67</v>
       </c>
       <c r="N286" s="14" t="n"/>
       <c r="O286" s="14" t="n">
-        <v>5.98</v>
+        <v>6.01</v>
       </c>
       <c r="P286" s="14" t="n">
         <v>17.8</v>
       </c>
       <c r="Q286" s="14" t="n">
-        <v>4.23</v>
+        <v>4.25</v>
       </c>
       <c r="R286" s="14" t="inlineStr">
         <is>
@@ -39673,7 +39673,7 @@
         </is>
       </c>
       <c r="G287" s="14" t="n">
-        <v>643.62</v>
+        <v>646.15</v>
       </c>
       <c r="H287" s="14" t="n">
         <v>22.99</v>
@@ -39691,17 +39691,17 @@
         <v>33060029102.54279</v>
       </c>
       <c r="M287" s="14" t="n">
-        <v>27.99</v>
+        <v>28.1</v>
       </c>
       <c r="N287" s="14" t="n"/>
       <c r="O287" s="14" t="n">
-        <v>5.26</v>
+        <v>5.28</v>
       </c>
       <c r="P287" s="14" t="n">
         <v>20.01</v>
       </c>
       <c r="Q287" s="14" t="n">
-        <v>3.9</v>
+        <v>3.91</v>
       </c>
       <c r="R287" s="14" t="inlineStr">
         <is>
@@ -40099,7 +40099,7 @@
         </is>
       </c>
       <c r="G293" s="14" t="n">
-        <v>11.58</v>
+        <v>11.49</v>
       </c>
       <c r="H293" s="14" t="n">
         <v>0.45</v>
@@ -40117,17 +40117,17 @@
         <v>8066043093.854888</v>
       </c>
       <c r="M293" s="14" t="n">
-        <v>25.68</v>
+        <v>25.48</v>
       </c>
       <c r="N293" s="14" t="n"/>
       <c r="O293" s="14" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="P293" s="14" t="n">
         <v>7.09</v>
       </c>
       <c r="Q293" s="14" t="n">
-        <v>0.79</v>
+        <v>0.78</v>
       </c>
       <c r="R293" s="14" t="inlineStr">
         <is>
@@ -40172,7 +40172,7 @@
         </is>
       </c>
       <c r="G294" s="14" t="n">
-        <v>11.58</v>
+        <v>11.49</v>
       </c>
       <c r="H294" s="14" t="n">
         <v>0.6899999999999999</v>
@@ -40190,11 +40190,11 @@
         <v>8578521481.043726</v>
       </c>
       <c r="M294" s="14" t="n">
-        <v>16.84</v>
+        <v>16.71</v>
       </c>
       <c r="N294" s="14" t="n"/>
       <c r="O294" s="14" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="P294" s="14" t="n">
         <v>10.26</v>
@@ -40598,7 +40598,7 @@
         </is>
       </c>
       <c r="G300" s="14" t="n">
-        <v>6708</v>
+        <v>6689</v>
       </c>
       <c r="H300" s="14" t="n">
         <v>446.97</v>
@@ -40616,7 +40616,7 @@
         <v>3728663618702.116</v>
       </c>
       <c r="M300" s="14" t="n">
-        <v>15.01</v>
+        <v>14.97</v>
       </c>
       <c r="N300" s="14" t="n"/>
       <c r="O300" s="14" t="n">
@@ -40671,7 +40671,7 @@
         </is>
       </c>
       <c r="G301" s="14" t="n">
-        <v>6708</v>
+        <v>6689</v>
       </c>
       <c r="H301" s="14" t="n">
         <v>494.41</v>
@@ -40689,7 +40689,7 @@
         <v>3969683662208.616</v>
       </c>
       <c r="M301" s="14" t="n">
-        <v>13.57</v>
+        <v>13.53</v>
       </c>
       <c r="N301" s="14" t="n"/>
       <c r="O301" s="14" t="n">
@@ -40699,7 +40699,7 @@
         <v>11.57</v>
       </c>
       <c r="Q301" s="14" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="R301" s="14" t="inlineStr">
         <is>
@@ -41097,7 +41097,7 @@
         </is>
       </c>
       <c r="G307" s="14" t="n">
-        <v>5239</v>
+        <v>5276</v>
       </c>
       <c r="H307" s="14" t="n">
         <v>429.98</v>
@@ -41115,17 +41115,17 @@
         <v>953778299859.0259</v>
       </c>
       <c r="M307" s="14" t="n">
-        <v>12.18</v>
+        <v>12.27</v>
       </c>
       <c r="N307" s="14" t="n"/>
       <c r="O307" s="14" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="P307" s="14" t="n">
         <v>9.869999999999999</v>
       </c>
       <c r="Q307" s="14" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="R307" s="14" t="inlineStr">
         <is>
@@ -41170,7 +41170,7 @@
         </is>
       </c>
       <c r="G308" s="14" t="n">
-        <v>5239</v>
+        <v>5276</v>
       </c>
       <c r="H308" s="14" t="n">
         <v>495.89</v>
@@ -41188,17 +41188,17 @@
         <v>1015608764702.593</v>
       </c>
       <c r="M308" s="14" t="n">
-        <v>10.56</v>
+        <v>10.64</v>
       </c>
       <c r="N308" s="14" t="n"/>
       <c r="O308" s="14" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="P308" s="14" t="n">
         <v>10.71</v>
       </c>
       <c r="Q308" s="14" t="n">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="R308" s="14" t="inlineStr">
         <is>
@@ -41596,35 +41596,35 @@
         </is>
       </c>
       <c r="G314" s="14" t="n">
-        <v>311.2</v>
+        <v>307.7</v>
       </c>
       <c r="H314" s="14" t="n">
         <v>21.77</v>
       </c>
       <c r="I314" s="14" t="n">
-        <v>99</v>
+        <v>99.87</v>
       </c>
       <c r="J314" s="15" t="n">
-        <v>499952956410</v>
+        <v>500856064990</v>
       </c>
       <c r="K314" s="15" t="n">
         <v>44278012438.6832</v>
       </c>
       <c r="L314" s="15" t="n">
-        <v>201313297909.9221</v>
+        <v>203071136332.0782</v>
       </c>
       <c r="M314" s="14" t="n">
-        <v>14.29</v>
+        <v>14.13</v>
       </c>
       <c r="N314" s="14" t="n"/>
       <c r="O314" s="14" t="n">
-        <v>3.14</v>
+        <v>3.08</v>
       </c>
       <c r="P314" s="14" t="n">
-        <v>23.32</v>
+        <v>23.21</v>
       </c>
       <c r="Q314" s="14" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="R314" s="14" t="inlineStr">
         <is>
@@ -41669,13 +41669,13 @@
         </is>
       </c>
       <c r="G315" s="14" t="n">
-        <v>311.2</v>
+        <v>307.7</v>
       </c>
       <c r="H315" s="14" t="n">
         <v>25.64</v>
       </c>
       <c r="I315" s="14" t="n">
-        <v>112.27</v>
+        <v>114.15</v>
       </c>
       <c r="J315" s="15" t="n">
         <v>546677979470</v>
@@ -41684,20 +41684,20 @@
         <v>52139378864.46888</v>
       </c>
       <c r="L315" s="15" t="n">
-        <v>228300638845.9898</v>
+        <v>232128412173.2467</v>
       </c>
       <c r="M315" s="14" t="n">
-        <v>12.14</v>
+        <v>12</v>
       </c>
       <c r="N315" s="14" t="n"/>
       <c r="O315" s="14" t="n">
-        <v>2.77</v>
+        <v>2.7</v>
       </c>
       <c r="P315" s="14" t="n">
-        <v>24.27</v>
+        <v>23.96</v>
       </c>
       <c r="Q315" s="14" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="R315" s="14" t="inlineStr">
         <is>
@@ -43093,7 +43093,7 @@
         </is>
       </c>
       <c r="G335" s="14" t="n">
-        <v>9180</v>
+        <v>8970</v>
       </c>
       <c r="H335" s="14" t="n">
         <v>1728</v>
@@ -43121,7 +43121,7 @@
         <v>15.39</v>
       </c>
       <c r="Q335" s="14" t="n">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="R335" s="14" t="inlineStr">
         <is>
@@ -43166,7 +43166,7 @@
         </is>
       </c>
       <c r="G336" s="14" t="n">
-        <v>9180</v>
+        <v>8970</v>
       </c>
       <c r="H336" s="14" t="n">
         <v>2102</v>
@@ -43184,17 +43184,17 @@
         <v>367213567791.274</v>
       </c>
       <c r="M336" s="14" t="n">
-        <v>4.37</v>
+        <v>4.27</v>
       </c>
       <c r="N336" s="14" t="n"/>
       <c r="O336" s="14" t="n">
-        <v>0.51</v>
+        <v>0.5</v>
       </c>
       <c r="P336" s="14" t="n">
         <v>12.24</v>
       </c>
       <c r="Q336" s="14" t="n">
-        <v>0.32</v>
+        <v>0.31</v>
       </c>
       <c r="R336" s="14" t="inlineStr">
         <is>
@@ -43592,7 +43592,7 @@
         </is>
       </c>
       <c r="G342" s="14" t="n">
-        <v>10490</v>
+        <v>10350</v>
       </c>
       <c r="H342" s="14" t="n"/>
       <c r="I342" s="14" t="n"/>
@@ -43649,7 +43649,7 @@
         </is>
       </c>
       <c r="G343" s="14" t="n">
-        <v>10490</v>
+        <v>10350</v>
       </c>
       <c r="H343" s="14" t="n"/>
       <c r="I343" s="14" t="n"/>
@@ -44059,7 +44059,7 @@
         </is>
       </c>
       <c r="G349" s="14" t="n">
-        <v>6100</v>
+        <v>6070</v>
       </c>
       <c r="H349" s="14" t="n"/>
       <c r="I349" s="14" t="n"/>
@@ -44116,7 +44116,7 @@
         </is>
       </c>
       <c r="G350" s="14" t="n">
-        <v>6100</v>
+        <v>6070</v>
       </c>
       <c r="H350" s="14" t="n"/>
       <c r="I350" s="14" t="n"/>
@@ -44526,7 +44526,7 @@
         </is>
       </c>
       <c r="G356" s="14" t="n">
-        <v>1111.02</v>
+        <v>1098.88</v>
       </c>
       <c r="H356" s="14" t="n">
         <v>51.84</v>
@@ -44535,7 +44535,7 @@
         <v>185.19</v>
       </c>
       <c r="J356" s="15" t="n">
-        <v>18089144740</v>
+        <v>18066663440</v>
       </c>
       <c r="K356" s="15" t="n">
         <v>3270834512.6688</v>
@@ -44544,17 +44544,17 @@
         <v>11684428030.06309</v>
       </c>
       <c r="M356" s="14" t="n">
-        <v>21.43</v>
+        <v>21.2</v>
       </c>
       <c r="N356" s="14" t="n"/>
       <c r="O356" s="14" t="n">
-        <v>6</v>
+        <v>5.93</v>
       </c>
       <c r="P356" s="14" t="n">
         <v>31.68</v>
       </c>
       <c r="Q356" s="14" t="n">
-        <v>3.88</v>
+        <v>3.84</v>
       </c>
       <c r="R356" s="14" t="inlineStr">
         <is>
@@ -44599,7 +44599,7 @@
         </is>
       </c>
       <c r="G357" s="14" t="n">
-        <v>1111.02</v>
+        <v>1098.88</v>
       </c>
       <c r="H357" s="14" t="n">
         <v>60.91</v>
@@ -44617,17 +44617,17 @@
         <v>14876412692.75734</v>
       </c>
       <c r="M357" s="14" t="n">
-        <v>18.24</v>
+        <v>18.04</v>
       </c>
       <c r="N357" s="14" t="n"/>
       <c r="O357" s="14" t="n">
-        <v>4.71</v>
+        <v>4.66</v>
       </c>
       <c r="P357" s="14" t="n">
         <v>28.94</v>
       </c>
       <c r="Q357" s="14" t="n">
-        <v>3.52</v>
+        <v>3.49</v>
       </c>
       <c r="R357" s="14" t="inlineStr">
         <is>
@@ -44935,7 +44935,7 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>2026-10-24T09:12:40+09:00</t>
+          <t>2026-10-26T10:22:15+09:00</t>
         </is>
       </c>
     </row>

--- a/telegram_research_dashboard/static/valuation_full.xlsx
+++ b/telegram_research_dashboard/static/valuation_full.xlsx
@@ -799,7 +799,7 @@
         </is>
       </c>
       <c r="B5" s="8" t="n">
-        <v>23448</v>
+        <v>22941</v>
       </c>
       <c r="C5" s="9" t="n"/>
       <c r="D5" s="9" t="n">
@@ -815,7 +815,7 @@
         <v>10.15</v>
       </c>
       <c r="H5" s="10" t="n">
-        <v>8.49</v>
+        <v>8.32</v>
       </c>
       <c r="I5" s="10" t="n"/>
       <c r="J5" s="9" t="n"/>
@@ -847,7 +847,7 @@
         <v>2.79</v>
       </c>
       <c r="V5" s="10" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="W5" s="10" t="n"/>
       <c r="X5" s="9" t="n">
@@ -882,10 +882,10 @@
         <v>3.04</v>
       </c>
       <c r="AI5" s="10" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="AJ5" s="10" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AK5" s="10" t="n"/>
     </row>
@@ -896,7 +896,7 @@
         </is>
       </c>
       <c r="B6" s="8" t="n">
-        <v>12442</v>
+        <v>12263</v>
       </c>
       <c r="C6" s="9" t="n"/>
       <c r="D6" s="9" t="n">
@@ -912,7 +912,7 @@
         <v>8.69</v>
       </c>
       <c r="H6" s="10" t="n">
-        <v>8.69</v>
+        <v>8.57</v>
       </c>
       <c r="I6" s="10" t="n"/>
       <c r="J6" s="9" t="n"/>
@@ -944,7 +944,7 @@
         <v>2.06</v>
       </c>
       <c r="V6" s="10" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="W6" s="10" t="n"/>
       <c r="X6" s="9" t="n">
@@ -979,10 +979,10 @@
         <v>2.72</v>
       </c>
       <c r="AI6" s="10" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AJ6" s="10" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AK6" s="10" t="n"/>
     </row>
@@ -993,7 +993,7 @@
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>10677</v>
+        <v>10514</v>
       </c>
       <c r="C7" s="9" t="n"/>
       <c r="D7" s="9" t="n"/>
@@ -1007,7 +1007,7 @@
         <v>15.88</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>9.77</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="I7" s="10" t="n"/>
       <c r="J7" s="9" t="n"/>
@@ -1039,7 +1039,7 @@
         <v>2.78</v>
       </c>
       <c r="V7" s="10" t="n">
-        <v>2.14</v>
+        <v>2.11</v>
       </c>
       <c r="W7" s="10" t="n"/>
       <c r="X7" s="9" t="n">
@@ -1074,10 +1074,10 @@
         <v>1.93</v>
       </c>
       <c r="AI7" s="10" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AJ7" s="10" t="n">
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
       <c r="AK7" s="10" t="n"/>
     </row>
@@ -1088,7 +1088,7 @@
         </is>
       </c>
       <c r="B8" s="8" t="n">
-        <v>13048</v>
+        <v>12977</v>
       </c>
       <c r="C8" s="9" t="n"/>
       <c r="D8" s="9" t="n">
@@ -1104,7 +1104,7 @@
         <v>4.46</v>
       </c>
       <c r="H8" s="10" t="n">
-        <v>4.04</v>
+        <v>4.03</v>
       </c>
       <c r="I8" s="10" t="n"/>
       <c r="J8" s="9" t="n">
@@ -1187,7 +1187,7 @@
         </is>
       </c>
       <c r="B9" s="8" t="n">
-        <v>1064</v>
+        <v>1048</v>
       </c>
       <c r="C9" s="9" t="n"/>
       <c r="D9" s="9" t="n"/>
@@ -1199,7 +1199,7 @@
         <v>4.77</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>4.72</v>
+        <v>4.65</v>
       </c>
       <c r="I9" s="10" t="n"/>
       <c r="J9" s="9" t="n"/>
@@ -1221,7 +1221,7 @@
         <v>1.06</v>
       </c>
       <c r="V9" s="10" t="n">
-        <v>0.85</v>
+        <v>0.83</v>
       </c>
       <c r="W9" s="10" t="n"/>
       <c r="X9" s="9" t="n">
@@ -1250,10 +1250,10 @@
         <v>2.09</v>
       </c>
       <c r="AI9" s="10" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AJ9" s="10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AK9" s="10" t="n"/>
     </row>
@@ -1264,7 +1264,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>829</v>
+        <v>817</v>
       </c>
       <c r="C10" s="9" t="n"/>
       <c r="D10" s="9" t="n"/>
@@ -1349,7 +1349,7 @@
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>6502</v>
+        <v>5742</v>
       </c>
       <c r="C11" s="9" t="n"/>
       <c r="D11" s="9" t="n"/>
@@ -1363,7 +1363,7 @@
         <v>25.22</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>20.5</v>
+        <v>18.12</v>
       </c>
       <c r="I11" s="10" t="n"/>
       <c r="J11" s="9" t="n"/>
@@ -1389,7 +1389,7 @@
         <v>8.74</v>
       </c>
       <c r="V11" s="10" t="n">
-        <v>6.96</v>
+        <v>6.16</v>
       </c>
       <c r="W11" s="10" t="n"/>
       <c r="X11" s="9" t="n">
@@ -1420,10 +1420,10 @@
         <v>4.38</v>
       </c>
       <c r="AI11" s="10" t="n">
-        <v>3.62</v>
+        <v>3.2</v>
       </c>
       <c r="AJ11" s="10" t="n">
-        <v>3.2</v>
+        <v>2.83</v>
       </c>
       <c r="AK11" s="10" t="n"/>
     </row>
@@ -1434,7 +1434,7 @@
         </is>
       </c>
       <c r="B12" s="8" t="n">
-        <v>913</v>
+        <v>895</v>
       </c>
       <c r="C12" s="9" t="n">
         <v>14.21</v>
@@ -1452,7 +1452,7 @@
         <v>9.6</v>
       </c>
       <c r="H12" s="10" t="n">
-        <v>7.11</v>
+        <v>6.98</v>
       </c>
       <c r="I12" s="10" t="n"/>
       <c r="J12" s="9" t="n">
@@ -1486,7 +1486,7 @@
         <v>2.34</v>
       </c>
       <c r="V12" s="10" t="n">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="W12" s="10" t="n"/>
       <c r="X12" s="9" t="n">
@@ -1521,10 +1521,10 @@
         <v>7.54</v>
       </c>
       <c r="AI12" s="10" t="n">
-        <v>2.03</v>
+        <v>1.99</v>
       </c>
       <c r="AJ12" s="10" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="AK12" s="10" t="n"/>
     </row>
@@ -1535,7 +1535,7 @@
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>1989</v>
+        <v>1956</v>
       </c>
       <c r="C13" s="9" t="n"/>
       <c r="D13" s="9" t="n"/>
@@ -1549,7 +1549,7 @@
         <v>14.38</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>8.67</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="I13" s="10" t="n"/>
       <c r="J13" s="9" t="n"/>
@@ -1581,7 +1581,7 @@
         <v>3.59</v>
       </c>
       <c r="V13" s="10" t="n">
-        <v>2.51</v>
+        <v>2.47</v>
       </c>
       <c r="W13" s="10" t="n"/>
       <c r="X13" s="9" t="n">
@@ -1616,10 +1616,10 @@
         <v>2.61</v>
       </c>
       <c r="AI13" s="10" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AJ13" s="10" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AK13" s="10" t="n"/>
     </row>
@@ -1630,7 +1630,7 @@
         </is>
       </c>
       <c r="B14" s="8" t="n">
-        <v>601</v>
+        <v>591</v>
       </c>
       <c r="C14" s="9" t="n">
         <v>23.46</v>
@@ -1646,7 +1646,7 @@
         <v>7.02</v>
       </c>
       <c r="H14" s="10" t="n">
-        <v>5.61</v>
+        <v>5.51</v>
       </c>
       <c r="I14" s="10" t="n"/>
       <c r="J14" s="9" t="n">
@@ -1680,7 +1680,7 @@
         <v>1.2</v>
       </c>
       <c r="V14" s="10" t="n">
-        <v>0.99</v>
+        <v>0.98</v>
       </c>
       <c r="W14" s="10" t="n"/>
       <c r="X14" s="9" t="n">
@@ -1715,10 +1715,10 @@
         <v>1.65</v>
       </c>
       <c r="AI14" s="10" t="n">
-        <v>0.84</v>
+        <v>0.83</v>
       </c>
       <c r="AJ14" s="10" t="n">
-        <v>0.8</v>
+        <v>0.78</v>
       </c>
       <c r="AK14" s="10" t="n"/>
     </row>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="B15" s="8" t="n">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="C15" s="9" t="n">
         <v>37.11</v>
@@ -1747,7 +1747,7 @@
         <v>4.53</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>4.42</v>
+        <v>4.32</v>
       </c>
       <c r="I15" s="10" t="n"/>
       <c r="J15" s="9" t="n">
@@ -1781,7 +1781,7 @@
         <v>1.19</v>
       </c>
       <c r="V15" s="10" t="n">
-        <v>0.92</v>
+        <v>0.9</v>
       </c>
       <c r="W15" s="10" t="n"/>
       <c r="X15" s="9" t="n">
@@ -1816,10 +1816,10 @@
         <v>1.02</v>
       </c>
       <c r="AI15" s="10" t="n">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="AJ15" s="10" t="n">
-        <v>0.43</v>
+        <v>0.42</v>
       </c>
       <c r="AK15" s="10" t="n"/>
     </row>
@@ -1837,7 +1837,7 @@
         </is>
       </c>
       <c r="B17" s="8" t="n">
-        <v>39556</v>
+        <v>39698</v>
       </c>
       <c r="C17" s="9" t="n">
         <v>577.76</v>
@@ -1852,10 +1852,10 @@
         <v>31.89</v>
       </c>
       <c r="G17" s="10" t="n">
-        <v>12.64</v>
+        <v>12.67</v>
       </c>
       <c r="H17" s="10" t="n">
-        <v>9.720000000000001</v>
+        <v>9.74</v>
       </c>
       <c r="I17" s="10" t="n"/>
       <c r="J17" s="9" t="n">
@@ -1923,7 +1923,7 @@
         <v>1.42</v>
       </c>
       <c r="AJ17" s="10" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AK17" s="10" t="n"/>
     </row>
@@ -1934,7 +1934,7 @@
         </is>
       </c>
       <c r="B18" s="8" t="n">
-        <v>14877</v>
+        <v>14859</v>
       </c>
       <c r="C18" s="9" t="n">
         <v>9.9</v>
@@ -1949,10 +1949,10 @@
         <v>8.640000000000001</v>
       </c>
       <c r="G18" s="10" t="n">
-        <v>9.08</v>
+        <v>9.1</v>
       </c>
       <c r="H18" s="10" t="n">
-        <v>8.18</v>
+        <v>8.19</v>
       </c>
       <c r="I18" s="10" t="n"/>
       <c r="J18" s="9" t="n">
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="B19" s="8" t="n">
-        <v>2322</v>
+        <v>2299</v>
       </c>
       <c r="C19" s="9" t="n">
         <v>13.53</v>
@@ -2050,10 +2050,10 @@
         <v>16.46</v>
       </c>
       <c r="G19" s="10" t="n">
-        <v>13.37</v>
+        <v>13.22</v>
       </c>
       <c r="H19" s="10" t="n">
-        <v>6.53</v>
+        <v>6.45</v>
       </c>
       <c r="I19" s="10" t="n"/>
       <c r="J19" s="9" t="n">
@@ -2084,10 +2084,10 @@
         <v>0.91</v>
       </c>
       <c r="U19" s="10" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="V19" s="10" t="n">
-        <v>0.74</v>
+        <v>0.73</v>
       </c>
       <c r="W19" s="10" t="n"/>
       <c r="X19" s="9" t="n">
@@ -2122,10 +2122,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="AI19" s="10" t="n">
-        <v>0.7</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AJ19" s="10" t="n">
-        <v>0.54</v>
+        <v>0.53</v>
       </c>
       <c r="AK19" s="10" t="n"/>
     </row>
@@ -2143,7 +2143,7 @@
         </is>
       </c>
       <c r="B21" s="8" t="n">
-        <v>75750</v>
+        <v>74777</v>
       </c>
       <c r="C21" s="9" t="n"/>
       <c r="D21" s="9" t="n">
@@ -2159,10 +2159,10 @@
         <v>57.81</v>
       </c>
       <c r="H21" s="10" t="n">
-        <v>26.24</v>
+        <v>25.99</v>
       </c>
       <c r="I21" s="10" t="n">
-        <v>23.09</v>
+        <v>22.87</v>
       </c>
       <c r="J21" s="9" t="n"/>
       <c r="K21" s="9" t="n">
@@ -2193,10 +2193,10 @@
         <v>4.59</v>
       </c>
       <c r="V21" s="10" t="n">
-        <v>3.48</v>
+        <v>3.44</v>
       </c>
       <c r="W21" s="10" t="n">
-        <v>3.14</v>
+        <v>3.11</v>
       </c>
       <c r="X21" s="9" t="n"/>
       <c r="Y21" s="9" t="n">
@@ -2231,10 +2231,10 @@
         <v>3.25</v>
       </c>
       <c r="AJ21" s="10" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AK21" s="10" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
     </row>
     <row r="22">
@@ -2244,7 +2244,7 @@
         </is>
       </c>
       <c r="B22" s="8" t="n">
-        <v>11415</v>
+        <v>11392</v>
       </c>
       <c r="C22" s="9" t="n"/>
       <c r="D22" s="9" t="n">
@@ -2260,10 +2260,10 @@
         <v>22.39</v>
       </c>
       <c r="H22" s="10" t="n">
-        <v>15.03</v>
+        <v>15.05</v>
       </c>
       <c r="I22" s="10" t="n">
-        <v>13.14</v>
+        <v>13.15</v>
       </c>
       <c r="J22" s="9" t="n"/>
       <c r="K22" s="9" t="n">
@@ -2345,7 +2345,7 @@
         </is>
       </c>
       <c r="B23" s="8" t="n">
-        <v>16109</v>
+        <v>16127</v>
       </c>
       <c r="C23" s="9" t="n"/>
       <c r="D23" s="9" t="n">
@@ -2359,10 +2359,10 @@
         <v>20.66</v>
       </c>
       <c r="H23" s="10" t="n">
-        <v>13.46</v>
+        <v>13.52</v>
       </c>
       <c r="I23" s="10" t="n">
-        <v>15.41</v>
+        <v>15.48</v>
       </c>
       <c r="J23" s="9" t="n"/>
       <c r="K23" s="9" t="n">
@@ -2393,10 +2393,10 @@
         <v>5.1</v>
       </c>
       <c r="V23" s="10" t="n">
-        <v>3.1</v>
+        <v>3.11</v>
       </c>
       <c r="W23" s="10" t="n">
-        <v>2.64</v>
+        <v>2.65</v>
       </c>
       <c r="X23" s="9" t="n"/>
       <c r="Y23" s="9" t="n">
@@ -2434,7 +2434,7 @@
         <v>1.36</v>
       </c>
       <c r="AK23" s="10" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="24">
@@ -2444,7 +2444,7 @@
         </is>
       </c>
       <c r="B24" s="8" t="n">
-        <v>2276</v>
+        <v>2250</v>
       </c>
       <c r="C24" s="9" t="n"/>
       <c r="D24" s="9" t="n">
@@ -2460,10 +2460,10 @@
         <v>14.63</v>
       </c>
       <c r="H24" s="10" t="n">
-        <v>9.9</v>
+        <v>9.82</v>
       </c>
       <c r="I24" s="10" t="n">
-        <v>9.52</v>
+        <v>9.44</v>
       </c>
       <c r="J24" s="9" t="n"/>
       <c r="K24" s="9" t="n">
@@ -2494,10 +2494,10 @@
         <v>2.46</v>
       </c>
       <c r="V24" s="10" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W24" s="10" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="X24" s="9" t="n"/>
       <c r="Y24" s="9" t="n">
@@ -2532,7 +2532,7 @@
         <v>1.59</v>
       </c>
       <c r="AJ24" s="10" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.93</v>
       </c>
       <c r="AK24" s="10" t="n">
         <v>0.89</v>
@@ -2545,7 +2545,7 @@
         </is>
       </c>
       <c r="B25" s="8" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C25" s="9" t="n"/>
       <c r="D25" s="9" t="n">
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="B27" s="8" t="n">
-        <v>4374</v>
+        <v>4427</v>
       </c>
       <c r="C27" s="9" t="n"/>
       <c r="D27" s="9" t="n"/>
@@ -2648,10 +2648,10 @@
         <v>44.03</v>
       </c>
       <c r="G27" s="10" t="n">
-        <v>22</v>
+        <v>22.28</v>
       </c>
       <c r="H27" s="10" t="n">
-        <v>14.63</v>
+        <v>14.82</v>
       </c>
       <c r="I27" s="10" t="n"/>
       <c r="J27" s="9" t="n">
@@ -2682,10 +2682,10 @@
         <v>5.43</v>
       </c>
       <c r="U27" s="10" t="n">
-        <v>3.32</v>
+        <v>3.36</v>
       </c>
       <c r="V27" s="10" t="n">
-        <v>2.71</v>
+        <v>2.74</v>
       </c>
       <c r="W27" s="10" t="n"/>
       <c r="X27" s="9" t="n">
@@ -2723,7 +2723,7 @@
         <v>0.42</v>
       </c>
       <c r="AJ27" s="10" t="n">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="AK27" s="10" t="n"/>
     </row>
@@ -2849,7 +2849,7 @@
         </is>
       </c>
       <c r="B31" s="8" t="n">
-        <v>1240</v>
+        <v>1242</v>
       </c>
       <c r="C31" s="9" t="n"/>
       <c r="D31" s="9" t="n"/>
@@ -2861,10 +2861,10 @@
       </c>
       <c r="G31" s="10" t="n"/>
       <c r="H31" s="10" t="n">
-        <v>18.42</v>
+        <v>18.44</v>
       </c>
       <c r="I31" s="10" t="n">
-        <v>16.23</v>
+        <v>16.25</v>
       </c>
       <c r="J31" s="9" t="n"/>
       <c r="K31" s="9" t="n">
@@ -2960,7 +2960,7 @@
         <v>8.69</v>
       </c>
       <c r="H32" s="13" t="n">
-        <v>7.8</v>
+        <v>7.65</v>
       </c>
       <c r="I32" s="13" t="n"/>
       <c r="J32" s="13" t="n">
@@ -2994,7 +2994,7 @@
         <v>2.06</v>
       </c>
       <c r="V32" s="13" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="W32" s="13" t="n"/>
       <c r="X32" s="13" t="n">
@@ -3029,10 +3029,10 @@
         <v>2.09</v>
       </c>
       <c r="AI32" s="13" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AJ32" s="13" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AK32" s="13" t="n"/>
     </row>
@@ -3056,10 +3056,10 @@
         <v>16.46</v>
       </c>
       <c r="G33" s="13" t="n">
-        <v>12.64</v>
+        <v>12.67</v>
       </c>
       <c r="H33" s="13" t="n">
-        <v>8.18</v>
+        <v>8.19</v>
       </c>
       <c r="I33" s="13" t="n"/>
       <c r="J33" s="13" t="n">
@@ -3131,7 +3131,7 @@
         <v>1.42</v>
       </c>
       <c r="AJ33" s="13" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AK33" s="13" t="n"/>
     </row>
@@ -3156,10 +3156,10 @@
         <v>20.66</v>
       </c>
       <c r="H34" s="13" t="n">
-        <v>14.25</v>
+        <v>14.29</v>
       </c>
       <c r="I34" s="13" t="n">
-        <v>14.28</v>
+        <v>14.32</v>
       </c>
       <c r="J34" s="13" t="n"/>
       <c r="K34" s="13" t="n">
@@ -3231,7 +3231,7 @@
         <v>1.15</v>
       </c>
       <c r="AK34" s="13" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
     </row>
     <row r="35">
@@ -3250,10 +3250,10 @@
         <v>44.03</v>
       </c>
       <c r="G35" s="13" t="n">
-        <v>22</v>
+        <v>22.28</v>
       </c>
       <c r="H35" s="13" t="n">
-        <v>14.63</v>
+        <v>14.82</v>
       </c>
       <c r="I35" s="13" t="n"/>
       <c r="J35" s="13" t="n">
@@ -3284,10 +3284,10 @@
         <v>5.43</v>
       </c>
       <c r="U35" s="13" t="n">
-        <v>3.32</v>
+        <v>3.36</v>
       </c>
       <c r="V35" s="13" t="n">
-        <v>2.71</v>
+        <v>2.74</v>
       </c>
       <c r="W35" s="13" t="n"/>
       <c r="X35" s="13" t="n">
@@ -3325,7 +3325,7 @@
         <v>0.42</v>
       </c>
       <c r="AJ35" s="13" t="n">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="AK35" s="13" t="n"/>
     </row>
@@ -3445,10 +3445,10 @@
       </c>
       <c r="G37" s="13" t="n"/>
       <c r="H37" s="13" t="n">
-        <v>18.42</v>
+        <v>18.44</v>
       </c>
       <c r="I37" s="13" t="n">
-        <v>16.23</v>
+        <v>16.25</v>
       </c>
       <c r="J37" s="13" t="n"/>
       <c r="K37" s="13" t="n">
@@ -3541,13 +3541,13 @@
         <v>19.51</v>
       </c>
       <c r="G38" s="13" t="n">
-        <v>12.64</v>
+        <v>12.67</v>
       </c>
       <c r="H38" s="13" t="n">
-        <v>9.210000000000001</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="I38" s="13" t="n">
-        <v>15.41</v>
+        <v>15.48</v>
       </c>
       <c r="J38" s="13" t="n">
         <v>12.48</v>
@@ -3582,7 +3582,7 @@
         <v>2.2</v>
       </c>
       <c r="V38" s="13" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="W38" s="13" t="n">
         <v>1.67</v>
@@ -3624,7 +3624,7 @@
         <v>1.05</v>
       </c>
       <c r="AJ38" s="13" t="n">
-        <v>0.99</v>
+        <v>0.98</v>
       </c>
       <c r="AK38" s="13" t="n">
         <v>0.89</v>
@@ -3687,7 +3687,7 @@
         </is>
       </c>
       <c r="B42" s="8" t="n">
-        <v>7187</v>
+        <v>7199</v>
       </c>
       <c r="C42" s="9" t="n">
         <v>41.88</v>
@@ -3705,7 +3705,7 @@
         <v>43.97</v>
       </c>
       <c r="H42" s="10" t="n">
-        <v>21.78</v>
+        <v>21.85</v>
       </c>
       <c r="I42" s="10" t="n"/>
       <c r="J42" s="9" t="n">
@@ -3739,7 +3739,7 @@
         <v>4.9</v>
       </c>
       <c r="V42" s="10" t="n">
-        <v>4.1</v>
+        <v>4.11</v>
       </c>
       <c r="W42" s="10" t="n"/>
       <c r="X42" s="9" t="n">
@@ -3788,7 +3788,7 @@
         </is>
       </c>
       <c r="B43" s="8" t="n">
-        <v>29608</v>
+        <v>29529</v>
       </c>
       <c r="C43" s="9" t="n">
         <v>19.31</v>
@@ -3806,7 +3806,7 @@
         <v>17.98</v>
       </c>
       <c r="H43" s="10" t="n">
-        <v>13.17</v>
+        <v>13.15</v>
       </c>
       <c r="I43" s="10" t="n"/>
       <c r="J43" s="9" t="n">
@@ -3840,7 +3840,7 @@
         <v>3.32</v>
       </c>
       <c r="V43" s="10" t="n">
-        <v>2.78</v>
+        <v>2.77</v>
       </c>
       <c r="W43" s="10" t="n"/>
       <c r="X43" s="9" t="n">
@@ -3875,7 +3875,7 @@
         <v>1.81</v>
       </c>
       <c r="AI43" s="10" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AJ43" s="10" t="n">
         <v>1.13</v>
@@ -3889,7 +3889,7 @@
         </is>
       </c>
       <c r="B44" s="8" t="n">
-        <v>7178</v>
+        <v>7077</v>
       </c>
       <c r="C44" s="9" t="n">
         <v>16.34</v>
@@ -3907,7 +3907,7 @@
         <v>29.67</v>
       </c>
       <c r="H44" s="10" t="n">
-        <v>18.31</v>
+        <v>18.08</v>
       </c>
       <c r="I44" s="10" t="n"/>
       <c r="J44" s="9" t="n">
@@ -3941,7 +3941,7 @@
         <v>5.98</v>
       </c>
       <c r="V44" s="10" t="n">
-        <v>4.52</v>
+        <v>4.46</v>
       </c>
       <c r="W44" s="10" t="n"/>
       <c r="X44" s="9" t="n">
@@ -3976,10 +3976,10 @@
         <v>2.14</v>
       </c>
       <c r="AI44" s="10" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AJ44" s="10" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="AK44" s="10" t="n"/>
     </row>
@@ -3990,7 +3990,7 @@
         </is>
       </c>
       <c r="B45" s="8" t="n">
-        <v>8640</v>
+        <v>8995</v>
       </c>
       <c r="C45" s="9" t="n"/>
       <c r="D45" s="9" t="n">
@@ -4006,7 +4006,7 @@
         <v>91.62</v>
       </c>
       <c r="H45" s="10" t="n">
-        <v>26.25</v>
+        <v>27.37</v>
       </c>
       <c r="I45" s="10" t="n"/>
       <c r="J45" s="9" t="n">
@@ -4040,7 +4040,7 @@
         <v>2.35</v>
       </c>
       <c r="V45" s="10" t="n">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="W45" s="10" t="n"/>
       <c r="X45" s="9" t="n">
@@ -4075,10 +4075,10 @@
         <v>2.78</v>
       </c>
       <c r="AI45" s="10" t="n">
-        <v>2.55</v>
+        <v>2.65</v>
       </c>
       <c r="AJ45" s="10" t="n">
-        <v>2.32</v>
+        <v>2.42</v>
       </c>
       <c r="AK45" s="10" t="n"/>
     </row>
@@ -4089,7 +4089,7 @@
         </is>
       </c>
       <c r="B46" s="8" t="n">
-        <v>6595</v>
+        <v>6520</v>
       </c>
       <c r="C46" s="9" t="n">
         <v>15.67</v>
@@ -4107,7 +4107,7 @@
         <v>11.27</v>
       </c>
       <c r="H46" s="10" t="n">
-        <v>9.550000000000001</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="I46" s="10" t="n"/>
       <c r="J46" s="9" t="n">
@@ -4141,7 +4141,7 @@
         <v>2.37</v>
       </c>
       <c r="V46" s="10" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="W46" s="10" t="n"/>
       <c r="X46" s="9" t="n">
@@ -4176,10 +4176,10 @@
         <v>3.51</v>
       </c>
       <c r="AI46" s="10" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AJ46" s="10" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AK46" s="10" t="n"/>
     </row>
@@ -4212,10 +4212,10 @@
         <v>22.08</v>
       </c>
       <c r="G48" s="10" t="n">
-        <v>19.73</v>
+        <v>19.74</v>
       </c>
       <c r="H48" s="10" t="n">
-        <v>18.24</v>
+        <v>18.19</v>
       </c>
       <c r="I48" s="10" t="n"/>
       <c r="J48" s="9" t="n">
@@ -4249,7 +4249,7 @@
         <v>13.44</v>
       </c>
       <c r="V48" s="10" t="n">
-        <v>9.77</v>
+        <v>9.76</v>
       </c>
       <c r="W48" s="10" t="n"/>
       <c r="X48" s="9" t="n">
@@ -4265,10 +4265,10 @@
         <v>76.87</v>
       </c>
       <c r="AB48" s="10" t="n">
-        <v>82.42</v>
+        <v>82.38</v>
       </c>
       <c r="AC48" s="10" t="n">
-        <v>62.03</v>
+        <v>62.19</v>
       </c>
       <c r="AD48" s="10" t="n"/>
       <c r="AE48" s="9" t="n">
@@ -4287,7 +4287,7 @@
         <v>1.7</v>
       </c>
       <c r="AJ48" s="10" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AK48" s="10" t="n"/>
     </row>
@@ -4313,10 +4313,10 @@
         <v>19.36</v>
       </c>
       <c r="G49" s="10" t="n">
-        <v>18.54</v>
+        <v>18.52</v>
       </c>
       <c r="H49" s="10" t="n">
-        <v>18.36</v>
+        <v>18.38</v>
       </c>
       <c r="I49" s="10" t="n"/>
       <c r="J49" s="9" t="n">
@@ -4366,10 +4366,10 @@
         <v>26.17</v>
       </c>
       <c r="AB49" s="10" t="n">
-        <v>23.27</v>
+        <v>23.29</v>
       </c>
       <c r="AC49" s="10" t="n">
-        <v>20.2</v>
+        <v>20.18</v>
       </c>
       <c r="AD49" s="10" t="n"/>
       <c r="AE49" s="9" t="n">
@@ -4515,7 +4515,7 @@
         <v>36.57</v>
       </c>
       <c r="G51" s="10" t="n">
-        <v>25.03</v>
+        <v>24.98</v>
       </c>
       <c r="H51" s="10" t="n">
         <v>23.78</v>
@@ -4568,10 +4568,10 @@
         <v>10.74</v>
       </c>
       <c r="AB51" s="10" t="n">
-        <v>15.06</v>
+        <v>15.09</v>
       </c>
       <c r="AC51" s="10" t="n">
-        <v>14.62</v>
+        <v>14.63</v>
       </c>
       <c r="AD51" s="10" t="n"/>
       <c r="AE51" s="9" t="n">
@@ -4587,7 +4587,7 @@
         <v>2.78</v>
       </c>
       <c r="AI51" s="10" t="n">
-        <v>2.64</v>
+        <v>2.63</v>
       </c>
       <c r="AJ51" s="10" t="n">
         <v>2.45</v>
@@ -4709,7 +4709,7 @@
         </is>
       </c>
       <c r="B54" s="8" t="n">
-        <v>52463</v>
+        <v>53060</v>
       </c>
       <c r="C54" s="9" t="n">
         <v>17.03</v>
@@ -4724,10 +4724,10 @@
         <v>102.9</v>
       </c>
       <c r="G54" s="10" t="n">
-        <v>27.34</v>
+        <v>27.66</v>
       </c>
       <c r="H54" s="10" t="n">
-        <v>19.23</v>
+        <v>19.46</v>
       </c>
       <c r="I54" s="10" t="n"/>
       <c r="J54" s="9" t="n">
@@ -4758,10 +4758,10 @@
         <v>14.29</v>
       </c>
       <c r="U54" s="10" t="n">
-        <v>7.85</v>
+        <v>7.94</v>
       </c>
       <c r="V54" s="10" t="n">
-        <v>6.4</v>
+        <v>6.48</v>
       </c>
       <c r="W54" s="10" t="n"/>
       <c r="X54" s="9" t="n">
@@ -4796,10 +4796,10 @@
         <v>7.21</v>
       </c>
       <c r="AI54" s="10" t="n">
-        <v>3.36</v>
+        <v>3.4</v>
       </c>
       <c r="AJ54" s="10" t="n">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="AK54" s="10" t="n"/>
     </row>
@@ -4817,7 +4817,7 @@
         </is>
       </c>
       <c r="B56" s="8" t="n">
-        <v>75806</v>
+        <v>76652</v>
       </c>
       <c r="C56" s="9" t="n">
         <v>16.56</v>
@@ -4832,10 +4832,10 @@
         <v>24.33</v>
       </c>
       <c r="G56" s="10" t="n">
-        <v>22.94</v>
+        <v>23.29</v>
       </c>
       <c r="H56" s="10" t="n">
-        <v>20.18</v>
+        <v>20.48</v>
       </c>
       <c r="I56" s="10" t="n"/>
       <c r="J56" s="9" t="n">
@@ -4866,10 +4866,10 @@
         <v>4.26</v>
       </c>
       <c r="U56" s="10" t="n">
-        <v>4.36</v>
+        <v>4.43</v>
       </c>
       <c r="V56" s="10" t="n">
-        <v>3.95</v>
+        <v>4.01</v>
       </c>
       <c r="W56" s="10" t="n"/>
       <c r="X56" s="9" t="n">
@@ -4904,10 +4904,10 @@
         <v>1.77</v>
       </c>
       <c r="AI56" s="10" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AJ56" s="10" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="AK56" s="10" t="n"/>
     </row>
@@ -4925,7 +4925,7 @@
         </is>
       </c>
       <c r="B58" s="8" t="n">
-        <v>31374</v>
+        <v>31646</v>
       </c>
       <c r="C58" s="9" t="n">
         <v>5</v>
@@ -4940,10 +4940,10 @@
         <v>23.17</v>
       </c>
       <c r="G58" s="10" t="n">
-        <v>20.12</v>
+        <v>20.3</v>
       </c>
       <c r="H58" s="10" t="n">
-        <v>16.78</v>
+        <v>16.93</v>
       </c>
       <c r="I58" s="10" t="n"/>
       <c r="J58" s="9" t="n">
@@ -4974,10 +4974,10 @@
         <v>2.97</v>
       </c>
       <c r="U58" s="10" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="V58" s="10" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="W58" s="10" t="n"/>
       <c r="X58" s="9" t="n">
@@ -5012,10 +5012,10 @@
         <v>1.45</v>
       </c>
       <c r="AI58" s="10" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AJ58" s="10" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AK58" s="10" t="n"/>
     </row>
@@ -5033,7 +5033,7 @@
         </is>
       </c>
       <c r="B60" s="8" t="n">
-        <v>35175</v>
+        <v>35082</v>
       </c>
       <c r="C60" s="9" t="n">
         <v>24.79</v>
@@ -5048,10 +5048,10 @@
         <v>45.89</v>
       </c>
       <c r="G60" s="10" t="n">
-        <v>41.65</v>
+        <v>41.54</v>
       </c>
       <c r="H60" s="10" t="n">
-        <v>33.96</v>
+        <v>33.87</v>
       </c>
       <c r="I60" s="10" t="n"/>
       <c r="J60" s="9" t="n">
@@ -5082,10 +5082,10 @@
         <v>6.69</v>
       </c>
       <c r="U60" s="10" t="n">
-        <v>6.93</v>
+        <v>6.91</v>
       </c>
       <c r="V60" s="10" t="n">
-        <v>5.93</v>
+        <v>5.91</v>
       </c>
       <c r="W60" s="10" t="n"/>
       <c r="X60" s="9" t="n">
@@ -5120,10 +5120,10 @@
         <v>3.66</v>
       </c>
       <c r="AI60" s="10" t="n">
-        <v>3.57</v>
+        <v>3.56</v>
       </c>
       <c r="AJ60" s="10" t="n">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="AK60" s="10" t="n"/>
     </row>
@@ -5150,7 +5150,7 @@
         <v>29.67</v>
       </c>
       <c r="H61" s="13" t="n">
-        <v>18.31</v>
+        <v>18.08</v>
       </c>
       <c r="I61" s="13" t="n"/>
       <c r="J61" s="13" t="n">
@@ -5184,7 +5184,7 @@
         <v>3.32</v>
       </c>
       <c r="V61" s="13" t="n">
-        <v>2.78</v>
+        <v>2.77</v>
       </c>
       <c r="W61" s="13" t="n"/>
       <c r="X61" s="13" t="n">
@@ -5246,10 +5246,10 @@
         <v>22.06</v>
       </c>
       <c r="G62" s="13" t="n">
-        <v>19.73</v>
+        <v>19.74</v>
       </c>
       <c r="H62" s="13" t="n">
-        <v>18.36</v>
+        <v>18.38</v>
       </c>
       <c r="I62" s="13" t="n"/>
       <c r="J62" s="13" t="n">
@@ -5345,10 +5345,10 @@
         <v>102.9</v>
       </c>
       <c r="G63" s="13" t="n">
-        <v>27.34</v>
+        <v>27.66</v>
       </c>
       <c r="H63" s="13" t="n">
-        <v>19.23</v>
+        <v>19.46</v>
       </c>
       <c r="I63" s="13" t="n"/>
       <c r="J63" s="13" t="n">
@@ -5379,10 +5379,10 @@
         <v>14.29</v>
       </c>
       <c r="U63" s="13" t="n">
-        <v>7.85</v>
+        <v>7.94</v>
       </c>
       <c r="V63" s="13" t="n">
-        <v>6.4</v>
+        <v>6.48</v>
       </c>
       <c r="W63" s="13" t="n"/>
       <c r="X63" s="13" t="n">
@@ -5417,10 +5417,10 @@
         <v>7.21</v>
       </c>
       <c r="AI63" s="13" t="n">
-        <v>3.36</v>
+        <v>3.4</v>
       </c>
       <c r="AJ63" s="13" t="n">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="AK63" s="13" t="n"/>
     </row>
@@ -5444,10 +5444,10 @@
         <v>24.33</v>
       </c>
       <c r="G64" s="13" t="n">
-        <v>22.94</v>
+        <v>23.29</v>
       </c>
       <c r="H64" s="13" t="n">
-        <v>20.18</v>
+        <v>20.48</v>
       </c>
       <c r="I64" s="13" t="n"/>
       <c r="J64" s="13" t="n">
@@ -5478,10 +5478,10 @@
         <v>4.26</v>
       </c>
       <c r="U64" s="13" t="n">
-        <v>4.36</v>
+        <v>4.43</v>
       </c>
       <c r="V64" s="13" t="n">
-        <v>3.95</v>
+        <v>4.01</v>
       </c>
       <c r="W64" s="13" t="n"/>
       <c r="X64" s="13" t="n">
@@ -5516,10 +5516,10 @@
         <v>1.77</v>
       </c>
       <c r="AI64" s="13" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AJ64" s="13" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="AK64" s="13" t="n"/>
     </row>
@@ -5543,10 +5543,10 @@
         <v>23.17</v>
       </c>
       <c r="G65" s="13" t="n">
-        <v>20.12</v>
+        <v>20.3</v>
       </c>
       <c r="H65" s="13" t="n">
-        <v>16.78</v>
+        <v>16.93</v>
       </c>
       <c r="I65" s="13" t="n"/>
       <c r="J65" s="13" t="n">
@@ -5577,10 +5577,10 @@
         <v>2.97</v>
       </c>
       <c r="U65" s="13" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="V65" s="13" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="W65" s="13" t="n"/>
       <c r="X65" s="13" t="n">
@@ -5615,10 +5615,10 @@
         <v>1.45</v>
       </c>
       <c r="AI65" s="13" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AJ65" s="13" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AK65" s="13" t="n"/>
     </row>
@@ -5642,10 +5642,10 @@
         <v>45.89</v>
       </c>
       <c r="G66" s="13" t="n">
-        <v>41.65</v>
+        <v>41.54</v>
       </c>
       <c r="H66" s="13" t="n">
-        <v>33.96</v>
+        <v>33.87</v>
       </c>
       <c r="I66" s="13" t="n"/>
       <c r="J66" s="13" t="n">
@@ -5676,10 +5676,10 @@
         <v>6.69</v>
       </c>
       <c r="U66" s="13" t="n">
-        <v>6.93</v>
+        <v>6.91</v>
       </c>
       <c r="V66" s="13" t="n">
-        <v>5.93</v>
+        <v>5.91</v>
       </c>
       <c r="W66" s="13" t="n"/>
       <c r="X66" s="13" t="n">
@@ -5714,10 +5714,10 @@
         <v>3.66</v>
       </c>
       <c r="AI66" s="13" t="n">
-        <v>3.57</v>
+        <v>3.56</v>
       </c>
       <c r="AJ66" s="13" t="n">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="AK66" s="13" t="n"/>
     </row>
@@ -5741,10 +5741,10 @@
         <v>35.11</v>
       </c>
       <c r="G67" s="13" t="n">
-        <v>25.14</v>
+        <v>25.48</v>
       </c>
       <c r="H67" s="13" t="n">
-        <v>19.7</v>
+        <v>19.97</v>
       </c>
       <c r="I67" s="13" t="n"/>
       <c r="J67" s="13" t="n">
@@ -5775,10 +5775,10 @@
         <v>5.47</v>
       </c>
       <c r="U67" s="13" t="n">
-        <v>5.64</v>
+        <v>5.67</v>
       </c>
       <c r="V67" s="13" t="n">
-        <v>4.94</v>
+        <v>4.96</v>
       </c>
       <c r="W67" s="13" t="n"/>
       <c r="X67" s="13" t="n">
@@ -5813,10 +5813,10 @@
         <v>2.71</v>
       </c>
       <c r="AI67" s="13" t="n">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="AJ67" s="13" t="n">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="AK67" s="13" t="n"/>
     </row>
@@ -5840,10 +5840,10 @@
         <v>30.55</v>
       </c>
       <c r="G68" s="13" t="n">
-        <v>21.75</v>
+        <v>21.92</v>
       </c>
       <c r="H68" s="13" t="n">
-        <v>18.55</v>
+        <v>18.56</v>
       </c>
       <c r="I68" s="13" t="n"/>
       <c r="J68" s="13" t="n">
@@ -5896,7 +5896,7 @@
         <v>18.9</v>
       </c>
       <c r="AC68" s="13" t="n">
-        <v>20.2</v>
+        <v>20.19</v>
       </c>
       <c r="AD68" s="13" t="n"/>
       <c r="AE68" s="13" t="n">
@@ -5912,7 +5912,7 @@
         <v>2.04</v>
       </c>
       <c r="AI68" s="13" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AJ68" s="13" t="n">
         <v>1.58</v>
@@ -5976,7 +5976,7 @@
         </is>
       </c>
       <c r="B72" s="8" t="n">
-        <v>3142</v>
+        <v>2934</v>
       </c>
       <c r="C72" s="9" t="n">
         <v>10.61</v>
@@ -5994,7 +5994,7 @@
         <v>7.01</v>
       </c>
       <c r="H72" s="10" t="n">
-        <v>5.95</v>
+        <v>5.57</v>
       </c>
       <c r="I72" s="10" t="n"/>
       <c r="J72" s="9" t="n">
@@ -6028,7 +6028,7 @@
         <v>0.87</v>
       </c>
       <c r="V72" s="10" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="W72" s="10" t="n"/>
       <c r="X72" s="9" t="n">
@@ -6063,10 +6063,10 @@
         <v>1.25</v>
       </c>
       <c r="AI72" s="10" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="AJ72" s="10" t="n">
-        <v>0.4</v>
+        <v>0.37</v>
       </c>
       <c r="AK72" s="10" t="n"/>
     </row>
@@ -6077,7 +6077,7 @@
         </is>
       </c>
       <c r="B73" s="8" t="n">
-        <v>3514</v>
+        <v>3509</v>
       </c>
       <c r="C73" s="9" t="n">
         <v>5.38</v>
@@ -6259,7 +6259,7 @@
         </is>
       </c>
       <c r="B75" s="8" t="n">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C75" s="9" t="n">
         <v>5.78</v>
@@ -6277,7 +6277,7 @@
         <v>4.02</v>
       </c>
       <c r="H75" s="10" t="n">
-        <v>4.27</v>
+        <v>4.22</v>
       </c>
       <c r="I75" s="10" t="n"/>
       <c r="J75" s="9" t="n">
@@ -6311,7 +6311,7 @@
         <v>0.54</v>
       </c>
       <c r="V75" s="10" t="n">
-        <v>0.5</v>
+        <v>0.49</v>
       </c>
       <c r="W75" s="10" t="n"/>
       <c r="X75" s="9" t="n">
@@ -6445,7 +6445,7 @@
         </is>
       </c>
       <c r="B77" s="8" t="n">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C77" s="9" t="n">
         <v>5.71</v>
@@ -6948,7 +6948,7 @@
         </is>
       </c>
       <c r="B84" s="8" t="n">
-        <v>38449</v>
+        <v>38576</v>
       </c>
       <c r="C84" s="9" t="n"/>
       <c r="D84" s="9" t="n">
@@ -6964,10 +6964,10 @@
         <v>14.4</v>
       </c>
       <c r="H84" s="10" t="n">
-        <v>14.97</v>
+        <v>15.06</v>
       </c>
       <c r="I84" s="10" t="n">
-        <v>13.53</v>
+        <v>13.62</v>
       </c>
       <c r="J84" s="9" t="n"/>
       <c r="K84" s="9" t="n">
@@ -6998,10 +6998,10 @@
         <v>1.54</v>
       </c>
       <c r="V84" s="10" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="W84" s="10" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="X84" s="9" t="n"/>
       <c r="Y84" s="9" t="n">
@@ -7036,10 +7036,10 @@
         <v>1.31</v>
       </c>
       <c r="AJ84" s="10" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AK84" s="10" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
     </row>
     <row r="85">
@@ -7049,7 +7049,7 @@
         </is>
       </c>
       <c r="B85" s="8" t="n">
-        <v>7160</v>
+        <v>7093</v>
       </c>
       <c r="C85" s="9" t="n"/>
       <c r="D85" s="9" t="n">
@@ -7065,10 +7065,10 @@
         <v>15.32</v>
       </c>
       <c r="H85" s="10" t="n">
-        <v>12.27</v>
+        <v>12.2</v>
       </c>
       <c r="I85" s="10" t="n">
-        <v>10.64</v>
+        <v>10.57</v>
       </c>
       <c r="J85" s="9" t="n"/>
       <c r="K85" s="9" t="n">
@@ -7099,10 +7099,10 @@
         <v>1.25</v>
       </c>
       <c r="V85" s="10" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="W85" s="10" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X85" s="9" t="n"/>
       <c r="Y85" s="9" t="n">
@@ -7137,10 +7137,10 @@
         <v>0.8</v>
       </c>
       <c r="AJ85" s="10" t="n">
-        <v>0.76</v>
+        <v>0.75</v>
       </c>
       <c r="AK85" s="10" t="n">
-        <v>0.73</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="86">
@@ -7157,7 +7157,7 @@
         </is>
       </c>
       <c r="B87" s="8" t="n">
-        <v>63165</v>
+        <v>63699</v>
       </c>
       <c r="C87" s="9" t="n">
         <v>11.71</v>
@@ -7172,10 +7172,10 @@
         <v>17.46</v>
       </c>
       <c r="G87" s="10" t="n">
-        <v>14.13</v>
+        <v>14.28</v>
       </c>
       <c r="H87" s="10" t="n">
-        <v>12</v>
+        <v>12.13</v>
       </c>
       <c r="I87" s="10" t="n"/>
       <c r="J87" s="9" t="n">
@@ -7206,10 +7206,10 @@
         <v>3.37</v>
       </c>
       <c r="U87" s="10" t="n">
-        <v>3.08</v>
+        <v>3.11</v>
       </c>
       <c r="V87" s="10" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="W87" s="10" t="n"/>
       <c r="X87" s="9" t="n">
@@ -7225,10 +7225,10 @@
         <v>18.5</v>
       </c>
       <c r="AB87" s="10" t="n">
-        <v>23.21</v>
+        <v>23.17</v>
       </c>
       <c r="AC87" s="10" t="n">
-        <v>23.96</v>
+        <v>23.92</v>
       </c>
       <c r="AD87" s="10" t="n"/>
       <c r="AE87" s="9" t="n">
@@ -7244,10 +7244,10 @@
         <v>1.26</v>
       </c>
       <c r="AI87" s="10" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AJ87" s="10" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AK87" s="10" t="n"/>
     </row>
@@ -7265,7 +7265,7 @@
         </is>
       </c>
       <c r="B89" s="8" t="n">
-        <v>25225</v>
+        <v>25197</v>
       </c>
       <c r="C89" s="9" t="n">
         <v>31.28</v>
@@ -7280,10 +7280,10 @@
         <v>23.11</v>
       </c>
       <c r="G89" s="10" t="n">
-        <v>15.68</v>
+        <v>15.64</v>
       </c>
       <c r="H89" s="10" t="n">
-        <v>12.09</v>
+        <v>12.06</v>
       </c>
       <c r="I89" s="10" t="n"/>
       <c r="J89" s="9" t="n">
@@ -7352,7 +7352,7 @@
         <v>2.17</v>
       </c>
       <c r="AI89" s="10" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AJ89" s="10" t="n">
         <v>1.42</v>
@@ -7366,7 +7366,7 @@
         </is>
       </c>
       <c r="B90" s="8" t="n">
-        <v>12566</v>
+        <v>12551</v>
       </c>
       <c r="C90" s="9" t="n">
         <v>13.89</v>
@@ -7381,10 +7381,10 @@
         <v>20.71</v>
       </c>
       <c r="G90" s="10" t="n">
-        <v>10.76</v>
+        <v>10.73</v>
       </c>
       <c r="H90" s="10" t="n">
-        <v>7.92</v>
+        <v>7.9</v>
       </c>
       <c r="I90" s="10" t="n"/>
       <c r="J90" s="9" t="n">
@@ -7453,7 +7453,7 @@
         <v>1.35</v>
       </c>
       <c r="AI90" s="10" t="n">
-        <v>0.74</v>
+        <v>0.73</v>
       </c>
       <c r="AJ90" s="10" t="n">
         <v>0.64</v>
@@ -7483,7 +7483,7 @@
         <v>7.01</v>
       </c>
       <c r="H91" s="13" t="n">
-        <v>5.95</v>
+        <v>5.57</v>
       </c>
       <c r="I91" s="13" t="n"/>
       <c r="J91" s="13" t="n">
@@ -7552,10 +7552,10 @@
         <v>0.53</v>
       </c>
       <c r="AI91" s="13" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="AJ91" s="13" t="n">
-        <v>0.4</v>
+        <v>0.37</v>
       </c>
       <c r="AK91" s="13" t="n"/>
     </row>
@@ -7679,7 +7679,7 @@
         <v>14.86</v>
       </c>
       <c r="H93" s="13" t="n">
-        <v>13.62</v>
+        <v>13.63</v>
       </c>
       <c r="I93" s="13" t="n">
         <v>12.09</v>
@@ -7777,10 +7777,10 @@
         <v>17.46</v>
       </c>
       <c r="G94" s="13" t="n">
-        <v>14.13</v>
+        <v>14.28</v>
       </c>
       <c r="H94" s="13" t="n">
-        <v>12</v>
+        <v>12.13</v>
       </c>
       <c r="I94" s="13" t="n"/>
       <c r="J94" s="13" t="n">
@@ -7811,10 +7811,10 @@
         <v>3.37</v>
       </c>
       <c r="U94" s="13" t="n">
-        <v>3.08</v>
+        <v>3.11</v>
       </c>
       <c r="V94" s="13" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="W94" s="13" t="n"/>
       <c r="X94" s="13" t="n">
@@ -7830,10 +7830,10 @@
         <v>18.5</v>
       </c>
       <c r="AB94" s="13" t="n">
-        <v>23.21</v>
+        <v>23.17</v>
       </c>
       <c r="AC94" s="13" t="n">
-        <v>23.96</v>
+        <v>23.92</v>
       </c>
       <c r="AD94" s="13" t="n"/>
       <c r="AE94" s="13" t="n">
@@ -7849,10 +7849,10 @@
         <v>1.26</v>
       </c>
       <c r="AI94" s="13" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AJ94" s="13" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AK94" s="13" t="n"/>
     </row>
@@ -7876,10 +7876,10 @@
         <v>21.91</v>
       </c>
       <c r="G95" s="13" t="n">
-        <v>13.22</v>
+        <v>13.19</v>
       </c>
       <c r="H95" s="13" t="n">
-        <v>10</v>
+        <v>9.98</v>
       </c>
       <c r="I95" s="13" t="n"/>
       <c r="J95" s="13" t="n">
@@ -7948,7 +7948,7 @@
         <v>1.76</v>
       </c>
       <c r="AI95" s="13" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AJ95" s="13" t="n">
         <v>1.03</v>
@@ -7978,7 +7978,7 @@
         <v>14.86</v>
       </c>
       <c r="H96" s="13" t="n">
-        <v>12.18</v>
+        <v>12.16</v>
       </c>
       <c r="I96" s="13" t="n">
         <v>12.09</v>
@@ -8055,7 +8055,7 @@
         <v>0.97</v>
       </c>
       <c r="AI96" s="13" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AJ96" s="13" t="n">
         <v>0.95</v>
@@ -8184,7 +8184,7 @@
         </is>
       </c>
       <c r="E2" s="7" t="n">
-        <v>23448</v>
+        <v>22941</v>
       </c>
       <c r="F2" s="9" t="n"/>
       <c r="G2" s="9" t="n">
@@ -8200,7 +8200,7 @@
         <v>10.15</v>
       </c>
       <c r="K2" s="9" t="n">
-        <v>8.49</v>
+        <v>8.32</v>
       </c>
       <c r="L2" s="9" t="n"/>
     </row>
@@ -8226,7 +8226,7 @@
         </is>
       </c>
       <c r="E3" s="7" t="n">
-        <v>12442</v>
+        <v>12263</v>
       </c>
       <c r="F3" s="9" t="n"/>
       <c r="G3" s="9" t="n">
@@ -8242,7 +8242,7 @@
         <v>8.69</v>
       </c>
       <c r="K3" s="9" t="n">
-        <v>8.69</v>
+        <v>8.57</v>
       </c>
       <c r="L3" s="9" t="n"/>
     </row>
@@ -8268,7 +8268,7 @@
         </is>
       </c>
       <c r="E4" s="7" t="n">
-        <v>10677</v>
+        <v>10514</v>
       </c>
       <c r="F4" s="9" t="n"/>
       <c r="G4" s="9" t="n"/>
@@ -8282,7 +8282,7 @@
         <v>15.88</v>
       </c>
       <c r="K4" s="9" t="n">
-        <v>9.77</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="L4" s="9" t="n"/>
     </row>
@@ -8308,7 +8308,7 @@
         </is>
       </c>
       <c r="E5" s="7" t="n">
-        <v>13048</v>
+        <v>12977</v>
       </c>
       <c r="F5" s="9" t="n"/>
       <c r="G5" s="9" t="n">
@@ -8324,7 +8324,7 @@
         <v>4.46</v>
       </c>
       <c r="K5" s="9" t="n">
-        <v>4.04</v>
+        <v>4.03</v>
       </c>
       <c r="L5" s="9" t="n"/>
     </row>
@@ -8350,7 +8350,7 @@
         </is>
       </c>
       <c r="E6" s="7" t="n">
-        <v>1064</v>
+        <v>1048</v>
       </c>
       <c r="F6" s="9" t="n"/>
       <c r="G6" s="9" t="n"/>
@@ -8362,7 +8362,7 @@
         <v>4.77</v>
       </c>
       <c r="K6" s="9" t="n">
-        <v>4.72</v>
+        <v>4.65</v>
       </c>
       <c r="L6" s="9" t="n"/>
     </row>
@@ -8388,7 +8388,7 @@
         </is>
       </c>
       <c r="E7" s="7" t="n">
-        <v>829</v>
+        <v>817</v>
       </c>
       <c r="F7" s="9" t="n"/>
       <c r="G7" s="9" t="n"/>
@@ -8426,7 +8426,7 @@
         </is>
       </c>
       <c r="E8" s="7" t="n">
-        <v>39556</v>
+        <v>39698</v>
       </c>
       <c r="F8" s="9" t="n">
         <v>577.76</v>
@@ -8441,10 +8441,10 @@
         <v>31.89</v>
       </c>
       <c r="J8" s="9" t="n">
-        <v>12.64</v>
+        <v>12.67</v>
       </c>
       <c r="K8" s="9" t="n">
-        <v>9.720000000000001</v>
+        <v>9.74</v>
       </c>
       <c r="L8" s="9" t="n"/>
     </row>
@@ -8470,7 +8470,7 @@
         </is>
       </c>
       <c r="E9" s="7" t="n">
-        <v>14877</v>
+        <v>14859</v>
       </c>
       <c r="F9" s="9" t="n">
         <v>9.9</v>
@@ -8485,10 +8485,10 @@
         <v>8.640000000000001</v>
       </c>
       <c r="J9" s="9" t="n">
-        <v>9.08</v>
+        <v>9.1</v>
       </c>
       <c r="K9" s="9" t="n">
-        <v>8.18</v>
+        <v>8.19</v>
       </c>
       <c r="L9" s="9" t="n"/>
     </row>
@@ -8514,7 +8514,7 @@
         </is>
       </c>
       <c r="E10" s="7" t="n">
-        <v>2322</v>
+        <v>2299</v>
       </c>
       <c r="F10" s="9" t="n">
         <v>13.53</v>
@@ -8529,10 +8529,10 @@
         <v>16.46</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>13.37</v>
+        <v>13.22</v>
       </c>
       <c r="K10" s="9" t="n">
-        <v>6.53</v>
+        <v>6.45</v>
       </c>
       <c r="L10" s="9" t="n"/>
     </row>
@@ -8558,7 +8558,7 @@
         </is>
       </c>
       <c r="E11" s="7" t="n">
-        <v>75750</v>
+        <v>74777</v>
       </c>
       <c r="F11" s="9" t="n"/>
       <c r="G11" s="9" t="n">
@@ -8574,10 +8574,10 @@
         <v>57.81</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>26.24</v>
+        <v>25.99</v>
       </c>
       <c r="L11" s="9" t="n">
-        <v>23.09</v>
+        <v>22.87</v>
       </c>
     </row>
     <row r="12">
@@ -8602,7 +8602,7 @@
         </is>
       </c>
       <c r="E12" s="7" t="n">
-        <v>11415</v>
+        <v>11392</v>
       </c>
       <c r="F12" s="9" t="n"/>
       <c r="G12" s="9" t="n">
@@ -8618,10 +8618,10 @@
         <v>22.39</v>
       </c>
       <c r="K12" s="9" t="n">
-        <v>15.03</v>
+        <v>15.05</v>
       </c>
       <c r="L12" s="9" t="n">
-        <v>13.14</v>
+        <v>13.15</v>
       </c>
     </row>
     <row r="13">
@@ -8646,7 +8646,7 @@
         </is>
       </c>
       <c r="E13" s="7" t="n">
-        <v>16109</v>
+        <v>16127</v>
       </c>
       <c r="F13" s="9" t="n"/>
       <c r="G13" s="9" t="n">
@@ -8660,10 +8660,10 @@
         <v>20.66</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>13.46</v>
+        <v>13.52</v>
       </c>
       <c r="L13" s="9" t="n">
-        <v>15.41</v>
+        <v>15.48</v>
       </c>
     </row>
     <row r="14">
@@ -8688,7 +8688,7 @@
         </is>
       </c>
       <c r="E14" s="7" t="n">
-        <v>2276</v>
+        <v>2250</v>
       </c>
       <c r="F14" s="9" t="n"/>
       <c r="G14" s="9" t="n">
@@ -8704,10 +8704,10 @@
         <v>14.63</v>
       </c>
       <c r="K14" s="9" t="n">
-        <v>9.9</v>
+        <v>9.82</v>
       </c>
       <c r="L14" s="9" t="n">
-        <v>9.52</v>
+        <v>9.44</v>
       </c>
     </row>
     <row r="15">
@@ -8732,7 +8732,7 @@
         </is>
       </c>
       <c r="E15" s="7" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F15" s="9" t="n"/>
       <c r="G15" s="9" t="n">
@@ -8772,7 +8772,7 @@
         </is>
       </c>
       <c r="E16" s="7" t="n">
-        <v>4374</v>
+        <v>4427</v>
       </c>
       <c r="F16" s="9" t="n"/>
       <c r="G16" s="9" t="n"/>
@@ -8783,10 +8783,10 @@
         <v>44.03</v>
       </c>
       <c r="J16" s="9" t="n">
-        <v>22</v>
+        <v>22.28</v>
       </c>
       <c r="K16" s="9" t="n">
-        <v>14.63</v>
+        <v>14.82</v>
       </c>
       <c r="L16" s="9" t="n"/>
     </row>
@@ -8856,7 +8856,7 @@
         </is>
       </c>
       <c r="E18" s="7" t="n">
-        <v>1240</v>
+        <v>1242</v>
       </c>
       <c r="F18" s="9" t="n"/>
       <c r="G18" s="9" t="n"/>
@@ -8868,10 +8868,10 @@
       </c>
       <c r="J18" s="9" t="n"/>
       <c r="K18" s="9" t="n">
-        <v>18.42</v>
+        <v>18.44</v>
       </c>
       <c r="L18" s="9" t="n">
-        <v>16.23</v>
+        <v>16.25</v>
       </c>
     </row>
     <row r="19">
@@ -8896,7 +8896,7 @@
         </is>
       </c>
       <c r="E19" s="7" t="n">
-        <v>6502</v>
+        <v>5742</v>
       </c>
       <c r="F19" s="9" t="n"/>
       <c r="G19" s="9" t="n"/>
@@ -8910,7 +8910,7 @@
         <v>25.22</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>20.5</v>
+        <v>18.12</v>
       </c>
       <c r="L19" s="9" t="n"/>
     </row>
@@ -8936,7 +8936,7 @@
         </is>
       </c>
       <c r="E20" s="7" t="n">
-        <v>913</v>
+        <v>895</v>
       </c>
       <c r="F20" s="9" t="n">
         <v>14.21</v>
@@ -8954,7 +8954,7 @@
         <v>9.6</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>7.11</v>
+        <v>6.98</v>
       </c>
       <c r="L20" s="9" t="n"/>
     </row>
@@ -8980,7 +8980,7 @@
         </is>
       </c>
       <c r="E21" s="7" t="n">
-        <v>1989</v>
+        <v>1956</v>
       </c>
       <c r="F21" s="9" t="n"/>
       <c r="G21" s="9" t="n"/>
@@ -8994,7 +8994,7 @@
         <v>14.38</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>8.67</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="L21" s="9" t="n"/>
     </row>
@@ -9020,7 +9020,7 @@
         </is>
       </c>
       <c r="E22" s="7" t="n">
-        <v>601</v>
+        <v>591</v>
       </c>
       <c r="F22" s="9" t="n">
         <v>23.46</v>
@@ -9036,7 +9036,7 @@
         <v>7.02</v>
       </c>
       <c r="K22" s="9" t="n">
-        <v>5.61</v>
+        <v>5.51</v>
       </c>
       <c r="L22" s="9" t="n"/>
     </row>
@@ -9062,7 +9062,7 @@
         </is>
       </c>
       <c r="E23" s="7" t="n">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="F23" s="9" t="n">
         <v>37.11</v>
@@ -9080,7 +9080,7 @@
         <v>4.53</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>4.42</v>
+        <v>4.32</v>
       </c>
       <c r="L23" s="9" t="n"/>
     </row>
@@ -9106,7 +9106,7 @@
         </is>
       </c>
       <c r="E24" s="7" t="n">
-        <v>7187</v>
+        <v>7199</v>
       </c>
       <c r="F24" s="9" t="n">
         <v>41.88</v>
@@ -9124,7 +9124,7 @@
         <v>43.97</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>21.78</v>
+        <v>21.85</v>
       </c>
       <c r="L24" s="9" t="n"/>
     </row>
@@ -9150,7 +9150,7 @@
         </is>
       </c>
       <c r="E25" s="7" t="n">
-        <v>29608</v>
+        <v>29529</v>
       </c>
       <c r="F25" s="9" t="n">
         <v>19.31</v>
@@ -9168,7 +9168,7 @@
         <v>17.98</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>13.17</v>
+        <v>13.15</v>
       </c>
       <c r="L25" s="9" t="n"/>
     </row>
@@ -9194,7 +9194,7 @@
         </is>
       </c>
       <c r="E26" s="7" t="n">
-        <v>7178</v>
+        <v>7077</v>
       </c>
       <c r="F26" s="9" t="n">
         <v>16.34</v>
@@ -9212,7 +9212,7 @@
         <v>29.67</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>18.31</v>
+        <v>18.08</v>
       </c>
       <c r="L26" s="9" t="n"/>
     </row>
@@ -9238,7 +9238,7 @@
         </is>
       </c>
       <c r="E27" s="7" t="n">
-        <v>8640</v>
+        <v>8995</v>
       </c>
       <c r="F27" s="9" t="n"/>
       <c r="G27" s="9" t="n">
@@ -9254,7 +9254,7 @@
         <v>91.62</v>
       </c>
       <c r="K27" s="9" t="n">
-        <v>26.25</v>
+        <v>27.37</v>
       </c>
       <c r="L27" s="9" t="n"/>
     </row>
@@ -9280,7 +9280,7 @@
         </is>
       </c>
       <c r="E28" s="7" t="n">
-        <v>6595</v>
+        <v>6520</v>
       </c>
       <c r="F28" s="9" t="n">
         <v>15.67</v>
@@ -9298,7 +9298,7 @@
         <v>11.27</v>
       </c>
       <c r="K28" s="9" t="n">
-        <v>9.550000000000001</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="L28" s="9" t="n"/>
     </row>
@@ -9339,10 +9339,10 @@
         <v>22.08</v>
       </c>
       <c r="J29" s="9" t="n">
-        <v>19.73</v>
+        <v>19.74</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>18.24</v>
+        <v>18.19</v>
       </c>
       <c r="L29" s="9" t="n"/>
     </row>
@@ -9383,10 +9383,10 @@
         <v>19.36</v>
       </c>
       <c r="J30" s="9" t="n">
-        <v>18.54</v>
+        <v>18.52</v>
       </c>
       <c r="K30" s="9" t="n">
-        <v>18.36</v>
+        <v>18.38</v>
       </c>
       <c r="L30" s="9" t="n"/>
     </row>
@@ -9471,7 +9471,7 @@
         <v>36.57</v>
       </c>
       <c r="J32" s="9" t="n">
-        <v>25.03</v>
+        <v>24.98</v>
       </c>
       <c r="K32" s="9" t="n">
         <v>23.78</v>
@@ -9544,7 +9544,7 @@
         </is>
       </c>
       <c r="E34" s="7" t="n">
-        <v>52463</v>
+        <v>53060</v>
       </c>
       <c r="F34" s="9" t="n">
         <v>17.03</v>
@@ -9559,10 +9559,10 @@
         <v>102.9</v>
       </c>
       <c r="J34" s="9" t="n">
-        <v>27.34</v>
+        <v>27.66</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>19.23</v>
+        <v>19.46</v>
       </c>
       <c r="L34" s="9" t="n"/>
     </row>
@@ -9588,7 +9588,7 @@
         </is>
       </c>
       <c r="E35" s="7" t="n">
-        <v>75806</v>
+        <v>76652</v>
       </c>
       <c r="F35" s="9" t="n">
         <v>16.56</v>
@@ -9603,10 +9603,10 @@
         <v>24.33</v>
       </c>
       <c r="J35" s="9" t="n">
-        <v>22.94</v>
+        <v>23.29</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>20.18</v>
+        <v>20.48</v>
       </c>
       <c r="L35" s="9" t="n"/>
     </row>
@@ -9632,7 +9632,7 @@
         </is>
       </c>
       <c r="E36" s="7" t="n">
-        <v>31374</v>
+        <v>31646</v>
       </c>
       <c r="F36" s="9" t="n">
         <v>5</v>
@@ -9647,10 +9647,10 @@
         <v>23.17</v>
       </c>
       <c r="J36" s="9" t="n">
-        <v>20.12</v>
+        <v>20.3</v>
       </c>
       <c r="K36" s="9" t="n">
-        <v>16.78</v>
+        <v>16.93</v>
       </c>
       <c r="L36" s="9" t="n"/>
     </row>
@@ -9676,7 +9676,7 @@
         </is>
       </c>
       <c r="E37" s="7" t="n">
-        <v>35175</v>
+        <v>35082</v>
       </c>
       <c r="F37" s="9" t="n">
         <v>24.79</v>
@@ -9691,10 +9691,10 @@
         <v>45.89</v>
       </c>
       <c r="J37" s="9" t="n">
-        <v>41.65</v>
+        <v>41.54</v>
       </c>
       <c r="K37" s="9" t="n">
-        <v>33.96</v>
+        <v>33.87</v>
       </c>
       <c r="L37" s="9" t="n"/>
     </row>
@@ -9720,7 +9720,7 @@
         </is>
       </c>
       <c r="E38" s="7" t="n">
-        <v>3142</v>
+        <v>2934</v>
       </c>
       <c r="F38" s="9" t="n">
         <v>10.61</v>
@@ -9738,7 +9738,7 @@
         <v>7.01</v>
       </c>
       <c r="K38" s="9" t="n">
-        <v>5.95</v>
+        <v>5.57</v>
       </c>
       <c r="L38" s="9" t="n"/>
     </row>
@@ -9764,7 +9764,7 @@
         </is>
       </c>
       <c r="E39" s="7" t="n">
-        <v>3514</v>
+        <v>3509</v>
       </c>
       <c r="F39" s="9" t="n">
         <v>5.38</v>
@@ -9976,7 +9976,7 @@
         </is>
       </c>
       <c r="E44" s="7" t="n">
-        <v>38449</v>
+        <v>38576</v>
       </c>
       <c r="F44" s="9" t="n"/>
       <c r="G44" s="9" t="n">
@@ -9992,10 +9992,10 @@
         <v>14.4</v>
       </c>
       <c r="K44" s="9" t="n">
-        <v>14.97</v>
+        <v>15.06</v>
       </c>
       <c r="L44" s="9" t="n">
-        <v>13.53</v>
+        <v>13.62</v>
       </c>
     </row>
     <row r="45">
@@ -10020,7 +10020,7 @@
         </is>
       </c>
       <c r="E45" s="7" t="n">
-        <v>7160</v>
+        <v>7093</v>
       </c>
       <c r="F45" s="9" t="n"/>
       <c r="G45" s="9" t="n">
@@ -10036,10 +10036,10 @@
         <v>15.32</v>
       </c>
       <c r="K45" s="9" t="n">
-        <v>12.27</v>
+        <v>12.2</v>
       </c>
       <c r="L45" s="9" t="n">
-        <v>10.64</v>
+        <v>10.57</v>
       </c>
     </row>
     <row r="46">
@@ -10064,7 +10064,7 @@
         </is>
       </c>
       <c r="E46" s="7" t="n">
-        <v>63165</v>
+        <v>63699</v>
       </c>
       <c r="F46" s="9" t="n">
         <v>11.71</v>
@@ -10079,10 +10079,10 @@
         <v>17.46</v>
       </c>
       <c r="J46" s="9" t="n">
-        <v>14.13</v>
+        <v>14.28</v>
       </c>
       <c r="K46" s="9" t="n">
-        <v>12</v>
+        <v>12.13</v>
       </c>
       <c r="L46" s="9" t="n"/>
     </row>
@@ -10108,7 +10108,7 @@
         </is>
       </c>
       <c r="E47" s="7" t="n">
-        <v>25225</v>
+        <v>25197</v>
       </c>
       <c r="F47" s="9" t="n">
         <v>31.28</v>
@@ -10123,10 +10123,10 @@
         <v>23.11</v>
       </c>
       <c r="J47" s="9" t="n">
-        <v>15.68</v>
+        <v>15.64</v>
       </c>
       <c r="K47" s="9" t="n">
-        <v>12.09</v>
+        <v>12.06</v>
       </c>
       <c r="L47" s="9" t="n"/>
     </row>
@@ -10152,7 +10152,7 @@
         </is>
       </c>
       <c r="E48" s="7" t="n">
-        <v>12566</v>
+        <v>12551</v>
       </c>
       <c r="F48" s="9" t="n">
         <v>13.89</v>
@@ -10167,10 +10167,10 @@
         <v>20.71</v>
       </c>
       <c r="J48" s="9" t="n">
-        <v>10.76</v>
+        <v>10.73</v>
       </c>
       <c r="K48" s="9" t="n">
-        <v>7.92</v>
+        <v>7.9</v>
       </c>
       <c r="L48" s="9" t="n"/>
     </row>
@@ -10196,7 +10196,7 @@
         </is>
       </c>
       <c r="E49" s="7" t="n">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="F49" s="9" t="n">
         <v>5.78</v>
@@ -10214,7 +10214,7 @@
         <v>4.02</v>
       </c>
       <c r="K49" s="9" t="n">
-        <v>4.27</v>
+        <v>4.22</v>
       </c>
       <c r="L49" s="9" t="n"/>
     </row>
@@ -10280,7 +10280,7 @@
         </is>
       </c>
       <c r="E51" s="7" t="n">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="F51" s="9" t="n">
         <v>5.71</v>
@@ -10454,7 +10454,7 @@
         </is>
       </c>
       <c r="E2" s="7" t="n">
-        <v>23448</v>
+        <v>22941</v>
       </c>
       <c r="F2" s="9" t="n"/>
       <c r="G2" s="9" t="n">
@@ -10492,7 +10492,7 @@
         </is>
       </c>
       <c r="E3" s="7" t="n">
-        <v>12442</v>
+        <v>12263</v>
       </c>
       <c r="F3" s="9" t="n"/>
       <c r="G3" s="9" t="n">
@@ -10530,7 +10530,7 @@
         </is>
       </c>
       <c r="E4" s="7" t="n">
-        <v>10677</v>
+        <v>10514</v>
       </c>
       <c r="F4" s="9" t="n"/>
       <c r="G4" s="9" t="n">
@@ -10568,7 +10568,7 @@
         </is>
       </c>
       <c r="E5" s="7" t="n">
-        <v>13048</v>
+        <v>12977</v>
       </c>
       <c r="F5" s="9" t="n">
         <v>40.3</v>
@@ -10608,7 +10608,7 @@
         </is>
       </c>
       <c r="E6" s="7" t="n">
-        <v>1064</v>
+        <v>1048</v>
       </c>
       <c r="F6" s="9" t="n"/>
       <c r="G6" s="9" t="n"/>
@@ -10642,7 +10642,7 @@
         </is>
       </c>
       <c r="E7" s="7" t="n">
-        <v>829</v>
+        <v>817</v>
       </c>
       <c r="F7" s="9" t="n">
         <v>87.52</v>
@@ -10680,7 +10680,7 @@
         </is>
       </c>
       <c r="E8" s="7" t="n">
-        <v>39556</v>
+        <v>39698</v>
       </c>
       <c r="F8" s="9" t="n">
         <v>13.27</v>
@@ -10720,7 +10720,7 @@
         </is>
       </c>
       <c r="E9" s="7" t="n">
-        <v>14877</v>
+        <v>14859</v>
       </c>
       <c r="F9" s="9" t="n">
         <v>5.59</v>
@@ -10760,7 +10760,7 @@
         </is>
       </c>
       <c r="E10" s="7" t="n">
-        <v>2322</v>
+        <v>2299</v>
       </c>
       <c r="F10" s="9" t="n">
         <v>0.93</v>
@@ -10800,7 +10800,7 @@
         </is>
       </c>
       <c r="E11" s="7" t="n">
-        <v>75750</v>
+        <v>74777</v>
       </c>
       <c r="F11" s="9" t="n"/>
       <c r="G11" s="9" t="n">
@@ -10840,7 +10840,7 @@
         </is>
       </c>
       <c r="E12" s="7" t="n">
-        <v>11415</v>
+        <v>11392</v>
       </c>
       <c r="F12" s="9" t="n"/>
       <c r="G12" s="9" t="n">
@@ -10880,7 +10880,7 @@
         </is>
       </c>
       <c r="E13" s="7" t="n">
-        <v>16109</v>
+        <v>16127</v>
       </c>
       <c r="F13" s="9" t="n"/>
       <c r="G13" s="9" t="n">
@@ -10920,7 +10920,7 @@
         </is>
       </c>
       <c r="E14" s="7" t="n">
-        <v>2276</v>
+        <v>2250</v>
       </c>
       <c r="F14" s="9" t="n"/>
       <c r="G14" s="9" t="n">
@@ -10960,7 +10960,7 @@
         </is>
       </c>
       <c r="E15" s="7" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F15" s="9" t="n"/>
       <c r="G15" s="9" t="n">
@@ -11000,7 +11000,7 @@
         </is>
       </c>
       <c r="E16" s="7" t="n">
-        <v>4374</v>
+        <v>4427</v>
       </c>
       <c r="F16" s="9" t="n">
         <v>991.9299999999999</v>
@@ -11080,7 +11080,7 @@
         </is>
       </c>
       <c r="E18" s="7" t="n">
-        <v>1240</v>
+        <v>1242</v>
       </c>
       <c r="F18" s="9" t="n"/>
       <c r="G18" s="9" t="n">
@@ -11118,7 +11118,7 @@
         </is>
       </c>
       <c r="E19" s="7" t="n">
-        <v>6502</v>
+        <v>5742</v>
       </c>
       <c r="F19" s="9" t="n"/>
       <c r="G19" s="9" t="n"/>
@@ -11154,7 +11154,7 @@
         </is>
       </c>
       <c r="E20" s="7" t="n">
-        <v>913</v>
+        <v>895</v>
       </c>
       <c r="F20" s="9" t="n">
         <v>11.7</v>
@@ -11194,7 +11194,7 @@
         </is>
       </c>
       <c r="E21" s="7" t="n">
-        <v>1989</v>
+        <v>1956</v>
       </c>
       <c r="F21" s="9" t="n"/>
       <c r="G21" s="9" t="n">
@@ -11232,7 +11232,7 @@
         </is>
       </c>
       <c r="E22" s="7" t="n">
-        <v>601</v>
+        <v>591</v>
       </c>
       <c r="F22" s="9" t="n">
         <v>11.21</v>
@@ -11272,7 +11272,7 @@
         </is>
       </c>
       <c r="E23" s="7" t="n">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="F23" s="9" t="n">
         <v>15.59</v>
@@ -11312,7 +11312,7 @@
         </is>
       </c>
       <c r="E24" s="7" t="n">
-        <v>7187</v>
+        <v>7199</v>
       </c>
       <c r="F24" s="9" t="n">
         <v>14.66</v>
@@ -11352,7 +11352,7 @@
         </is>
       </c>
       <c r="E25" s="7" t="n">
-        <v>29608</v>
+        <v>29529</v>
       </c>
       <c r="F25" s="9" t="n">
         <v>7.97</v>
@@ -11392,7 +11392,7 @@
         </is>
       </c>
       <c r="E26" s="7" t="n">
-        <v>7178</v>
+        <v>7077</v>
       </c>
       <c r="F26" s="9" t="n">
         <v>9.449999999999999</v>
@@ -11432,7 +11432,7 @@
         </is>
       </c>
       <c r="E27" s="7" t="n">
-        <v>8640</v>
+        <v>8995</v>
       </c>
       <c r="F27" s="9" t="n">
         <v>13.88</v>
@@ -11472,7 +11472,7 @@
         </is>
       </c>
       <c r="E28" s="7" t="n">
-        <v>6595</v>
+        <v>6520</v>
       </c>
       <c r="F28" s="9" t="n">
         <v>20.45</v>
@@ -11712,7 +11712,7 @@
         </is>
       </c>
       <c r="E34" s="7" t="n">
-        <v>52463</v>
+        <v>53060</v>
       </c>
       <c r="F34" s="9" t="n">
         <v>8.5</v>
@@ -11752,7 +11752,7 @@
         </is>
       </c>
       <c r="E35" s="7" t="n">
-        <v>75806</v>
+        <v>76652</v>
       </c>
       <c r="F35" s="9" t="n">
         <v>9.84</v>
@@ -11792,7 +11792,7 @@
         </is>
       </c>
       <c r="E36" s="7" t="n">
-        <v>31374</v>
+        <v>31646</v>
       </c>
       <c r="F36" s="9" t="n">
         <v>4.69</v>
@@ -11832,7 +11832,7 @@
         </is>
       </c>
       <c r="E37" s="7" t="n">
-        <v>35175</v>
+        <v>35082</v>
       </c>
       <c r="F37" s="9" t="n">
         <v>11.71</v>
@@ -11872,7 +11872,7 @@
         </is>
       </c>
       <c r="E38" s="7" t="n">
-        <v>3142</v>
+        <v>2934</v>
       </c>
       <c r="F38" s="9" t="n">
         <v>7.18</v>
@@ -11912,7 +11912,7 @@
         </is>
       </c>
       <c r="E39" s="7" t="n">
-        <v>3514</v>
+        <v>3509</v>
       </c>
       <c r="F39" s="9" t="n">
         <v>3.59</v>
@@ -12112,7 +12112,7 @@
         </is>
       </c>
       <c r="E44" s="7" t="n">
-        <v>38449</v>
+        <v>38576</v>
       </c>
       <c r="F44" s="9" t="n"/>
       <c r="G44" s="9" t="n">
@@ -12152,7 +12152,7 @@
         </is>
       </c>
       <c r="E45" s="7" t="n">
-        <v>7160</v>
+        <v>7093</v>
       </c>
       <c r="F45" s="9" t="n"/>
       <c r="G45" s="9" t="n">
@@ -12192,7 +12192,7 @@
         </is>
       </c>
       <c r="E46" s="7" t="n">
-        <v>63165</v>
+        <v>63699</v>
       </c>
       <c r="F46" s="9" t="n">
         <v>7.78</v>
@@ -12232,7 +12232,7 @@
         </is>
       </c>
       <c r="E47" s="7" t="n">
-        <v>25225</v>
+        <v>25197</v>
       </c>
       <c r="F47" s="9" t="n">
         <v>18.39</v>
@@ -12272,7 +12272,7 @@
         </is>
       </c>
       <c r="E48" s="7" t="n">
-        <v>12566</v>
+        <v>12551</v>
       </c>
       <c r="F48" s="9" t="n">
         <v>7.78</v>
@@ -12312,7 +12312,7 @@
         </is>
       </c>
       <c r="E49" s="7" t="n">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="F49" s="9" t="n">
         <v>3.96</v>
@@ -12392,7 +12392,7 @@
         </is>
       </c>
       <c r="E51" s="7" t="n">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="F51" s="9" t="n">
         <v>3</v>
@@ -12562,7 +12562,7 @@
         </is>
       </c>
       <c r="E2" s="7" t="n">
-        <v>23448</v>
+        <v>22941</v>
       </c>
       <c r="F2" s="9" t="n">
         <v>1.95</v>
@@ -12580,7 +12580,7 @@
         <v>2.79</v>
       </c>
       <c r="K2" s="9" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="L2" s="9" t="n"/>
     </row>
@@ -12606,7 +12606,7 @@
         </is>
       </c>
       <c r="E3" s="7" t="n">
-        <v>12442</v>
+        <v>12263</v>
       </c>
       <c r="F3" s="9" t="n">
         <v>2.73</v>
@@ -12624,7 +12624,7 @@
         <v>2.06</v>
       </c>
       <c r="K3" s="9" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="L3" s="9" t="n"/>
     </row>
@@ -12650,7 +12650,7 @@
         </is>
       </c>
       <c r="E4" s="7" t="n">
-        <v>10677</v>
+        <v>10514</v>
       </c>
       <c r="F4" s="9" t="n">
         <v>1.21</v>
@@ -12668,7 +12668,7 @@
         <v>2.78</v>
       </c>
       <c r="K4" s="9" t="n">
-        <v>2.14</v>
+        <v>2.11</v>
       </c>
       <c r="L4" s="9" t="n"/>
     </row>
@@ -12694,7 +12694,7 @@
         </is>
       </c>
       <c r="E5" s="7" t="n">
-        <v>13048</v>
+        <v>12977</v>
       </c>
       <c r="F5" s="9" t="n">
         <v>0.51</v>
@@ -12738,7 +12738,7 @@
         </is>
       </c>
       <c r="E6" s="7" t="n">
-        <v>1064</v>
+        <v>1048</v>
       </c>
       <c r="F6" s="9" t="n"/>
       <c r="G6" s="9" t="n"/>
@@ -12750,7 +12750,7 @@
         <v>1.06</v>
       </c>
       <c r="K6" s="9" t="n">
-        <v>0.85</v>
+        <v>0.83</v>
       </c>
       <c r="L6" s="9" t="n"/>
     </row>
@@ -12776,7 +12776,7 @@
         </is>
       </c>
       <c r="E7" s="7" t="n">
-        <v>829</v>
+        <v>817</v>
       </c>
       <c r="F7" s="9" t="n">
         <v>0.85</v>
@@ -12818,7 +12818,7 @@
         </is>
       </c>
       <c r="E8" s="7" t="n">
-        <v>39556</v>
+        <v>39698</v>
       </c>
       <c r="F8" s="9" t="n">
         <v>2.17</v>
@@ -12862,7 +12862,7 @@
         </is>
       </c>
       <c r="E9" s="7" t="n">
-        <v>14877</v>
+        <v>14859</v>
       </c>
       <c r="F9" s="9" t="n">
         <v>1.58</v>
@@ -12906,7 +12906,7 @@
         </is>
       </c>
       <c r="E10" s="7" t="n">
-        <v>2322</v>
+        <v>2299</v>
       </c>
       <c r="F10" s="9" t="n">
         <v>0.6</v>
@@ -12921,10 +12921,10 @@
         <v>0.91</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="K10" s="9" t="n">
-        <v>0.74</v>
+        <v>0.73</v>
       </c>
       <c r="L10" s="9" t="n"/>
     </row>
@@ -12950,7 +12950,7 @@
         </is>
       </c>
       <c r="E11" s="7" t="n">
-        <v>75750</v>
+        <v>74777</v>
       </c>
       <c r="F11" s="9" t="n"/>
       <c r="G11" s="9" t="n">
@@ -12966,10 +12966,10 @@
         <v>4.59</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>3.48</v>
+        <v>3.44</v>
       </c>
       <c r="L11" s="9" t="n">
-        <v>3.14</v>
+        <v>3.11</v>
       </c>
     </row>
     <row r="12">
@@ -12994,7 +12994,7 @@
         </is>
       </c>
       <c r="E12" s="7" t="n">
-        <v>11415</v>
+        <v>11392</v>
       </c>
       <c r="F12" s="9" t="n"/>
       <c r="G12" s="9" t="n">
@@ -13038,7 +13038,7 @@
         </is>
       </c>
       <c r="E13" s="7" t="n">
-        <v>16109</v>
+        <v>16127</v>
       </c>
       <c r="F13" s="9" t="n"/>
       <c r="G13" s="9" t="n">
@@ -13054,10 +13054,10 @@
         <v>5.1</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>3.1</v>
+        <v>3.11</v>
       </c>
       <c r="L13" s="9" t="n">
-        <v>2.64</v>
+        <v>2.65</v>
       </c>
     </row>
     <row r="14">
@@ -13082,7 +13082,7 @@
         </is>
       </c>
       <c r="E14" s="7" t="n">
-        <v>2276</v>
+        <v>2250</v>
       </c>
       <c r="F14" s="9" t="n"/>
       <c r="G14" s="9" t="n">
@@ -13098,10 +13098,10 @@
         <v>2.46</v>
       </c>
       <c r="K14" s="9" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="L14" s="9" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="15">
@@ -13126,7 +13126,7 @@
         </is>
       </c>
       <c r="E15" s="7" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F15" s="9" t="n"/>
       <c r="G15" s="9" t="n">
@@ -13166,7 +13166,7 @@
         </is>
       </c>
       <c r="E16" s="7" t="n">
-        <v>4374</v>
+        <v>4427</v>
       </c>
       <c r="F16" s="9" t="n">
         <v>1.54</v>
@@ -13181,10 +13181,10 @@
         <v>5.43</v>
       </c>
       <c r="J16" s="9" t="n">
-        <v>3.32</v>
+        <v>3.36</v>
       </c>
       <c r="K16" s="9" t="n">
-        <v>2.71</v>
+        <v>2.74</v>
       </c>
       <c r="L16" s="9" t="n"/>
     </row>
@@ -13254,7 +13254,7 @@
         </is>
       </c>
       <c r="E18" s="7" t="n">
-        <v>1240</v>
+        <v>1242</v>
       </c>
       <c r="F18" s="9" t="n"/>
       <c r="G18" s="9" t="n">
@@ -13298,7 +13298,7 @@
         </is>
       </c>
       <c r="E19" s="7" t="n">
-        <v>6502</v>
+        <v>5742</v>
       </c>
       <c r="F19" s="9" t="n"/>
       <c r="G19" s="9" t="n"/>
@@ -13312,7 +13312,7 @@
         <v>8.74</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>6.96</v>
+        <v>6.16</v>
       </c>
       <c r="L19" s="9" t="n"/>
     </row>
@@ -13338,7 +13338,7 @@
         </is>
       </c>
       <c r="E20" s="7" t="n">
-        <v>913</v>
+        <v>895</v>
       </c>
       <c r="F20" s="9" t="n">
         <v>1.05</v>
@@ -13356,7 +13356,7 @@
         <v>2.34</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="L20" s="9" t="n"/>
     </row>
@@ -13382,7 +13382,7 @@
         </is>
       </c>
       <c r="E21" s="7" t="n">
-        <v>1989</v>
+        <v>1956</v>
       </c>
       <c r="F21" s="9" t="n">
         <v>2.39</v>
@@ -13400,7 +13400,7 @@
         <v>3.59</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>2.51</v>
+        <v>2.47</v>
       </c>
       <c r="L21" s="9" t="n"/>
     </row>
@@ -13426,7 +13426,7 @@
         </is>
       </c>
       <c r="E22" s="7" t="n">
-        <v>601</v>
+        <v>591</v>
       </c>
       <c r="F22" s="9" t="n">
         <v>1.18</v>
@@ -13444,7 +13444,7 @@
         <v>1.2</v>
       </c>
       <c r="K22" s="9" t="n">
-        <v>0.99</v>
+        <v>0.98</v>
       </c>
       <c r="L22" s="9" t="n"/>
     </row>
@@ -13470,7 +13470,7 @@
         </is>
       </c>
       <c r="E23" s="7" t="n">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="F23" s="9" t="n">
         <v>2.1</v>
@@ -13488,7 +13488,7 @@
         <v>1.19</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>0.92</v>
+        <v>0.9</v>
       </c>
       <c r="L23" s="9" t="n"/>
     </row>
@@ -13514,7 +13514,7 @@
         </is>
       </c>
       <c r="E24" s="7" t="n">
-        <v>7187</v>
+        <v>7199</v>
       </c>
       <c r="F24" s="9" t="n">
         <v>3.47</v>
@@ -13532,7 +13532,7 @@
         <v>4.9</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>4.1</v>
+        <v>4.11</v>
       </c>
       <c r="L24" s="9" t="n"/>
     </row>
@@ -13558,7 +13558,7 @@
         </is>
       </c>
       <c r="E25" s="7" t="n">
-        <v>29608</v>
+        <v>29529</v>
       </c>
       <c r="F25" s="9" t="n">
         <v>1.32</v>
@@ -13576,7 +13576,7 @@
         <v>3.32</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>2.78</v>
+        <v>2.77</v>
       </c>
       <c r="L25" s="9" t="n"/>
     </row>
@@ -13602,7 +13602,7 @@
         </is>
       </c>
       <c r="E26" s="7" t="n">
-        <v>7178</v>
+        <v>7077</v>
       </c>
       <c r="F26" s="9" t="n">
         <v>2.15</v>
@@ -13620,7 +13620,7 @@
         <v>5.98</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>4.52</v>
+        <v>4.46</v>
       </c>
       <c r="L26" s="9" t="n"/>
     </row>
@@ -13646,7 +13646,7 @@
         </is>
       </c>
       <c r="E27" s="7" t="n">
-        <v>8640</v>
+        <v>8995</v>
       </c>
       <c r="F27" s="9" t="n">
         <v>0.99</v>
@@ -13664,7 +13664,7 @@
         <v>2.35</v>
       </c>
       <c r="K27" s="9" t="n">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="L27" s="9" t="n"/>
     </row>
@@ -13690,7 +13690,7 @@
         </is>
       </c>
       <c r="E28" s="7" t="n">
-        <v>6595</v>
+        <v>6520</v>
       </c>
       <c r="F28" s="9" t="n">
         <v>2.04</v>
@@ -13708,7 +13708,7 @@
         <v>2.37</v>
       </c>
       <c r="K28" s="9" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="L28" s="9" t="n"/>
     </row>
@@ -13752,7 +13752,7 @@
         <v>13.44</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>9.77</v>
+        <v>9.76</v>
       </c>
       <c r="L29" s="9" t="n"/>
     </row>
@@ -13954,7 +13954,7 @@
         </is>
       </c>
       <c r="E34" s="7" t="n">
-        <v>52463</v>
+        <v>53060</v>
       </c>
       <c r="F34" s="9" t="n">
         <v>2.86</v>
@@ -13969,10 +13969,10 @@
         <v>14.29</v>
       </c>
       <c r="J34" s="9" t="n">
-        <v>7.85</v>
+        <v>7.94</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>6.4</v>
+        <v>6.48</v>
       </c>
       <c r="L34" s="9" t="n"/>
     </row>
@@ -13998,7 +13998,7 @@
         </is>
       </c>
       <c r="E35" s="7" t="n">
-        <v>75806</v>
+        <v>76652</v>
       </c>
       <c r="F35" s="9" t="n">
         <v>2.35</v>
@@ -14013,10 +14013,10 @@
         <v>4.26</v>
       </c>
       <c r="J35" s="9" t="n">
-        <v>4.36</v>
+        <v>4.43</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>3.95</v>
+        <v>4.01</v>
       </c>
       <c r="L35" s="9" t="n"/>
     </row>
@@ -14042,7 +14042,7 @@
         </is>
       </c>
       <c r="E36" s="7" t="n">
-        <v>31374</v>
+        <v>31646</v>
       </c>
       <c r="F36" s="9" t="n">
         <v>0.65</v>
@@ -14057,10 +14057,10 @@
         <v>2.97</v>
       </c>
       <c r="J36" s="9" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="K36" s="9" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="L36" s="9" t="n"/>
     </row>
@@ -14086,7 +14086,7 @@
         </is>
       </c>
       <c r="E37" s="7" t="n">
-        <v>35175</v>
+        <v>35082</v>
       </c>
       <c r="F37" s="9" t="n">
         <v>1.85</v>
@@ -14101,10 +14101,10 @@
         <v>6.69</v>
       </c>
       <c r="J37" s="9" t="n">
-        <v>6.93</v>
+        <v>6.91</v>
       </c>
       <c r="K37" s="9" t="n">
-        <v>5.93</v>
+        <v>5.91</v>
       </c>
       <c r="L37" s="9" t="n"/>
     </row>
@@ -14130,7 +14130,7 @@
         </is>
       </c>
       <c r="E38" s="7" t="n">
-        <v>3142</v>
+        <v>2934</v>
       </c>
       <c r="F38" s="9" t="n">
         <v>0.8100000000000001</v>
@@ -14148,7 +14148,7 @@
         <v>0.87</v>
       </c>
       <c r="K38" s="9" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="L38" s="9" t="n"/>
     </row>
@@ -14174,7 +14174,7 @@
         </is>
       </c>
       <c r="E39" s="7" t="n">
-        <v>3514</v>
+        <v>3509</v>
       </c>
       <c r="F39" s="9" t="n">
         <v>0.6899999999999999</v>
@@ -14390,7 +14390,7 @@
         </is>
       </c>
       <c r="E44" s="7" t="n">
-        <v>38449</v>
+        <v>38576</v>
       </c>
       <c r="F44" s="9" t="n"/>
       <c r="G44" s="9" t="n">
@@ -14406,10 +14406,10 @@
         <v>1.54</v>
       </c>
       <c r="K44" s="9" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="L44" s="9" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
     </row>
     <row r="45">
@@ -14434,7 +14434,7 @@
         </is>
       </c>
       <c r="E45" s="7" t="n">
-        <v>7160</v>
+        <v>7093</v>
       </c>
       <c r="F45" s="9" t="n"/>
       <c r="G45" s="9" t="n">
@@ -14450,10 +14450,10 @@
         <v>1.25</v>
       </c>
       <c r="K45" s="9" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="L45" s="9" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="46">
@@ -14478,7 +14478,7 @@
         </is>
       </c>
       <c r="E46" s="7" t="n">
-        <v>63165</v>
+        <v>63699</v>
       </c>
       <c r="F46" s="9" t="n">
         <v>2.36</v>
@@ -14493,10 +14493,10 @@
         <v>3.37</v>
       </c>
       <c r="J46" s="9" t="n">
-        <v>3.08</v>
+        <v>3.11</v>
       </c>
       <c r="K46" s="9" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="L46" s="9" t="n"/>
     </row>
@@ -14522,7 +14522,7 @@
         </is>
       </c>
       <c r="E47" s="7" t="n">
-        <v>25225</v>
+        <v>25197</v>
       </c>
       <c r="F47" s="9" t="n">
         <v>2.06</v>
@@ -14566,7 +14566,7 @@
         </is>
       </c>
       <c r="E48" s="7" t="n">
-        <v>12566</v>
+        <v>12551</v>
       </c>
       <c r="F48" s="9" t="n">
         <v>1.12</v>
@@ -14610,7 +14610,7 @@
         </is>
       </c>
       <c r="E49" s="7" t="n">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="F49" s="9" t="n">
         <v>1.25</v>
@@ -14628,7 +14628,7 @@
         <v>0.54</v>
       </c>
       <c r="K49" s="9" t="n">
-        <v>0.5</v>
+        <v>0.49</v>
       </c>
       <c r="L49" s="9" t="n"/>
     </row>
@@ -14694,7 +14694,7 @@
         </is>
       </c>
       <c r="E51" s="7" t="n">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="F51" s="9" t="n">
         <v>0.88</v>
@@ -14868,7 +14868,7 @@
         </is>
       </c>
       <c r="E2" s="7" t="n">
-        <v>23448</v>
+        <v>22941</v>
       </c>
       <c r="F2" s="9" t="n">
         <v>-6.66</v>
@@ -14912,7 +14912,7 @@
         </is>
       </c>
       <c r="E3" s="7" t="n">
-        <v>12442</v>
+        <v>12263</v>
       </c>
       <c r="F3" s="9" t="n">
         <v>-234.21</v>
@@ -14956,7 +14956,7 @@
         </is>
       </c>
       <c r="E4" s="7" t="n">
-        <v>10677</v>
+        <v>10514</v>
       </c>
       <c r="F4" s="9" t="n">
         <v>-17.23</v>
@@ -15000,7 +15000,7 @@
         </is>
       </c>
       <c r="E5" s="7" t="n">
-        <v>13048</v>
+        <v>12977</v>
       </c>
       <c r="F5" s="9" t="n">
         <v>-2.23</v>
@@ -15044,7 +15044,7 @@
         </is>
       </c>
       <c r="E6" s="7" t="n">
-        <v>1064</v>
+        <v>1048</v>
       </c>
       <c r="F6" s="9" t="n">
         <v>-7.73</v>
@@ -15088,7 +15088,7 @@
         </is>
       </c>
       <c r="E7" s="7" t="n">
-        <v>829</v>
+        <v>817</v>
       </c>
       <c r="F7" s="9" t="n">
         <v>-13.03</v>
@@ -15130,7 +15130,7 @@
         </is>
       </c>
       <c r="E8" s="7" t="n">
-        <v>39556</v>
+        <v>39698</v>
       </c>
       <c r="F8" s="9" t="n">
         <v>0.38</v>
@@ -15174,7 +15174,7 @@
         </is>
       </c>
       <c r="E9" s="7" t="n">
-        <v>14877</v>
+        <v>14859</v>
       </c>
       <c r="F9" s="9" t="n">
         <v>15.98</v>
@@ -15218,7 +15218,7 @@
         </is>
       </c>
       <c r="E10" s="7" t="n">
-        <v>2322</v>
+        <v>2299</v>
       </c>
       <c r="F10" s="9" t="n">
         <v>4.42</v>
@@ -15262,7 +15262,7 @@
         </is>
       </c>
       <c r="E11" s="7" t="n">
-        <v>75750</v>
+        <v>74777</v>
       </c>
       <c r="F11" s="9" t="n"/>
       <c r="G11" s="9" t="n">
@@ -15306,7 +15306,7 @@
         </is>
       </c>
       <c r="E12" s="7" t="n">
-        <v>11415</v>
+        <v>11392</v>
       </c>
       <c r="F12" s="9" t="n"/>
       <c r="G12" s="9" t="n">
@@ -15350,7 +15350,7 @@
         </is>
       </c>
       <c r="E13" s="7" t="n">
-        <v>16109</v>
+        <v>16127</v>
       </c>
       <c r="F13" s="9" t="n"/>
       <c r="G13" s="9" t="n">
@@ -15394,7 +15394,7 @@
         </is>
       </c>
       <c r="E14" s="7" t="n">
-        <v>2276</v>
+        <v>2250</v>
       </c>
       <c r="F14" s="9" t="n"/>
       <c r="G14" s="9" t="n">
@@ -15438,7 +15438,7 @@
         </is>
       </c>
       <c r="E15" s="7" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F15" s="9" t="n"/>
       <c r="G15" s="9" t="n">
@@ -15478,7 +15478,7 @@
         </is>
       </c>
       <c r="E16" s="7" t="n">
-        <v>4374</v>
+        <v>4427</v>
       </c>
       <c r="F16" s="9" t="n">
         <v>-52.75</v>
@@ -15566,7 +15566,7 @@
         </is>
       </c>
       <c r="E18" s="7" t="n">
-        <v>1240</v>
+        <v>1242</v>
       </c>
       <c r="F18" s="9" t="n"/>
       <c r="G18" s="9" t="n">
@@ -15610,7 +15610,7 @@
         </is>
       </c>
       <c r="E19" s="7" t="n">
-        <v>6502</v>
+        <v>5742</v>
       </c>
       <c r="F19" s="9" t="n">
         <v>57.58</v>
@@ -15654,7 +15654,7 @@
         </is>
       </c>
       <c r="E20" s="7" t="n">
-        <v>913</v>
+        <v>895</v>
       </c>
       <c r="F20" s="9" t="n">
         <v>7.36</v>
@@ -15698,7 +15698,7 @@
         </is>
       </c>
       <c r="E21" s="7" t="n">
-        <v>1989</v>
+        <v>1956</v>
       </c>
       <c r="F21" s="9" t="n">
         <v>-18.17</v>
@@ -15742,7 +15742,7 @@
         </is>
       </c>
       <c r="E22" s="7" t="n">
-        <v>601</v>
+        <v>591</v>
       </c>
       <c r="F22" s="9" t="n">
         <v>5.01</v>
@@ -15786,7 +15786,7 @@
         </is>
       </c>
       <c r="E23" s="7" t="n">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="F23" s="9" t="n">
         <v>5.67</v>
@@ -15830,7 +15830,7 @@
         </is>
       </c>
       <c r="E24" s="7" t="n">
-        <v>7187</v>
+        <v>7199</v>
       </c>
       <c r="F24" s="9" t="n">
         <v>8.300000000000001</v>
@@ -15874,7 +15874,7 @@
         </is>
       </c>
       <c r="E25" s="7" t="n">
-        <v>29608</v>
+        <v>29529</v>
       </c>
       <c r="F25" s="9" t="n">
         <v>6.84</v>
@@ -15918,7 +15918,7 @@
         </is>
       </c>
       <c r="E26" s="7" t="n">
-        <v>7178</v>
+        <v>7077</v>
       </c>
       <c r="F26" s="9" t="n">
         <v>13.15</v>
@@ -15962,7 +15962,7 @@
         </is>
       </c>
       <c r="E27" s="7" t="n">
-        <v>8640</v>
+        <v>8995</v>
       </c>
       <c r="F27" s="9" t="n">
         <v>-3.83</v>
@@ -16006,7 +16006,7 @@
         </is>
       </c>
       <c r="E28" s="7" t="n">
-        <v>6595</v>
+        <v>6520</v>
       </c>
       <c r="F28" s="9" t="n">
         <v>13.01</v>
@@ -16065,10 +16065,10 @@
         <v>76.87</v>
       </c>
       <c r="J29" s="9" t="n">
-        <v>82.42</v>
+        <v>82.38</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>62.03</v>
+        <v>62.19</v>
       </c>
       <c r="L29" s="9" t="n"/>
     </row>
@@ -16109,10 +16109,10 @@
         <v>26.17</v>
       </c>
       <c r="J30" s="9" t="n">
-        <v>23.27</v>
+        <v>23.29</v>
       </c>
       <c r="K30" s="9" t="n">
-        <v>20.2</v>
+        <v>20.18</v>
       </c>
       <c r="L30" s="9" t="n"/>
     </row>
@@ -16197,10 +16197,10 @@
         <v>10.74</v>
       </c>
       <c r="J32" s="9" t="n">
-        <v>15.06</v>
+        <v>15.09</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>14.62</v>
+        <v>14.63</v>
       </c>
       <c r="L32" s="9" t="n"/>
     </row>
@@ -16270,7 +16270,7 @@
         </is>
       </c>
       <c r="E34" s="7" t="n">
-        <v>52463</v>
+        <v>53060</v>
       </c>
       <c r="F34" s="9" t="n">
         <v>16.81</v>
@@ -16314,7 +16314,7 @@
         </is>
       </c>
       <c r="E35" s="7" t="n">
-        <v>75806</v>
+        <v>76652</v>
       </c>
       <c r="F35" s="9" t="n">
         <v>14.19</v>
@@ -16358,7 +16358,7 @@
         </is>
       </c>
       <c r="E36" s="7" t="n">
-        <v>31374</v>
+        <v>31646</v>
       </c>
       <c r="F36" s="9" t="n">
         <v>12.91</v>
@@ -16402,7 +16402,7 @@
         </is>
       </c>
       <c r="E37" s="7" t="n">
-        <v>35175</v>
+        <v>35082</v>
       </c>
       <c r="F37" s="9" t="n">
         <v>7.44</v>
@@ -16446,7 +16446,7 @@
         </is>
       </c>
       <c r="E38" s="7" t="n">
-        <v>3142</v>
+        <v>2934</v>
       </c>
       <c r="F38" s="9" t="n">
         <v>7.62</v>
@@ -16490,7 +16490,7 @@
         </is>
       </c>
       <c r="E39" s="7" t="n">
-        <v>3514</v>
+        <v>3509</v>
       </c>
       <c r="F39" s="9" t="n">
         <v>12.82</v>
@@ -16706,7 +16706,7 @@
         </is>
       </c>
       <c r="E44" s="7" t="n">
-        <v>38449</v>
+        <v>38576</v>
       </c>
       <c r="F44" s="9" t="n"/>
       <c r="G44" s="9" t="n">
@@ -16750,7 +16750,7 @@
         </is>
       </c>
       <c r="E45" s="7" t="n">
-        <v>7160</v>
+        <v>7093</v>
       </c>
       <c r="F45" s="9" t="n"/>
       <c r="G45" s="9" t="n">
@@ -16794,7 +16794,7 @@
         </is>
       </c>
       <c r="E46" s="7" t="n">
-        <v>63165</v>
+        <v>63699</v>
       </c>
       <c r="F46" s="9" t="n">
         <v>20.11</v>
@@ -16809,10 +16809,10 @@
         <v>18.5</v>
       </c>
       <c r="J46" s="9" t="n">
-        <v>23.21</v>
+        <v>23.17</v>
       </c>
       <c r="K46" s="9" t="n">
-        <v>23.96</v>
+        <v>23.92</v>
       </c>
       <c r="L46" s="9" t="n"/>
     </row>
@@ -16838,7 +16838,7 @@
         </is>
       </c>
       <c r="E47" s="7" t="n">
-        <v>25225</v>
+        <v>25197</v>
       </c>
       <c r="F47" s="9" t="n">
         <v>6.6</v>
@@ -16882,7 +16882,7 @@
         </is>
       </c>
       <c r="E48" s="7" t="n">
-        <v>12566</v>
+        <v>12551</v>
       </c>
       <c r="F48" s="9" t="n">
         <v>8.1</v>
@@ -16926,7 +16926,7 @@
         </is>
       </c>
       <c r="E49" s="7" t="n">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="F49" s="9" t="n">
         <v>21.69</v>
@@ -17010,7 +17010,7 @@
         </is>
       </c>
       <c r="E51" s="7" t="n">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="F51" s="9" t="n">
         <v>15.47</v>
@@ -17184,7 +17184,7 @@
         </is>
       </c>
       <c r="E2" s="7" t="n">
-        <v>23448</v>
+        <v>22941</v>
       </c>
       <c r="F2" s="9" t="n">
         <v>1.14</v>
@@ -17199,10 +17199,10 @@
         <v>3.04</v>
       </c>
       <c r="J2" s="9" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="K2" s="9" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="L2" s="9" t="n"/>
     </row>
@@ -17228,7 +17228,7 @@
         </is>
       </c>
       <c r="E3" s="7" t="n">
-        <v>12442</v>
+        <v>12263</v>
       </c>
       <c r="F3" s="9" t="n">
         <v>0.42</v>
@@ -17243,10 +17243,10 @@
         <v>2.72</v>
       </c>
       <c r="J3" s="9" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="K3" s="9" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="L3" s="9" t="n"/>
     </row>
@@ -17272,7 +17272,7 @@
         </is>
       </c>
       <c r="E4" s="7" t="n">
-        <v>10677</v>
+        <v>10514</v>
       </c>
       <c r="F4" s="9" t="n">
         <v>0.73</v>
@@ -17287,10 +17287,10 @@
         <v>1.93</v>
       </c>
       <c r="J4" s="9" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="K4" s="9" t="n">
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
       <c r="L4" s="9" t="n"/>
     </row>
@@ -17316,7 +17316,7 @@
         </is>
       </c>
       <c r="E5" s="7" t="n">
-        <v>13048</v>
+        <v>12977</v>
       </c>
       <c r="F5" s="9" t="n">
         <v>0.29</v>
@@ -17360,7 +17360,7 @@
         </is>
       </c>
       <c r="E6" s="7" t="n">
-        <v>1064</v>
+        <v>1048</v>
       </c>
       <c r="F6" s="9" t="n"/>
       <c r="G6" s="9" t="n"/>
@@ -17369,10 +17369,10 @@
         <v>2.09</v>
       </c>
       <c r="J6" s="9" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="K6" s="9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="L6" s="9" t="n"/>
     </row>
@@ -17398,7 +17398,7 @@
         </is>
       </c>
       <c r="E7" s="7" t="n">
-        <v>829</v>
+        <v>817</v>
       </c>
       <c r="F7" s="9" t="n">
         <v>0.18</v>
@@ -17438,7 +17438,7 @@
         </is>
       </c>
       <c r="E8" s="7" t="n">
-        <v>39556</v>
+        <v>39698</v>
       </c>
       <c r="F8" s="9" t="n">
         <v>1.68</v>
@@ -17452,7 +17452,7 @@
         <v>1.42</v>
       </c>
       <c r="K8" s="9" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="L8" s="9" t="n"/>
     </row>
@@ -17478,7 +17478,7 @@
         </is>
       </c>
       <c r="E9" s="7" t="n">
-        <v>14877</v>
+        <v>14859</v>
       </c>
       <c r="F9" s="9" t="n">
         <v>1.34</v>
@@ -17522,7 +17522,7 @@
         </is>
       </c>
       <c r="E10" s="7" t="n">
-        <v>2322</v>
+        <v>2299</v>
       </c>
       <c r="F10" s="9" t="n">
         <v>0.73</v>
@@ -17537,10 +17537,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>0.7</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="K10" s="9" t="n">
-        <v>0.54</v>
+        <v>0.53</v>
       </c>
       <c r="L10" s="9" t="n"/>
     </row>
@@ -17566,7 +17566,7 @@
         </is>
       </c>
       <c r="E11" s="7" t="n">
-        <v>75750</v>
+        <v>74777</v>
       </c>
       <c r="F11" s="9" t="n"/>
       <c r="G11" s="9" t="n">
@@ -17582,10 +17582,10 @@
         <v>3.25</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="L11" s="9" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
     </row>
     <row r="12">
@@ -17610,7 +17610,7 @@
         </is>
       </c>
       <c r="E12" s="7" t="n">
-        <v>11415</v>
+        <v>11392</v>
       </c>
       <c r="F12" s="9" t="n"/>
       <c r="G12" s="9" t="n">
@@ -17654,7 +17654,7 @@
         </is>
       </c>
       <c r="E13" s="7" t="n">
-        <v>16109</v>
+        <v>16127</v>
       </c>
       <c r="F13" s="9" t="n"/>
       <c r="G13" s="9" t="n">
@@ -17673,7 +17673,7 @@
         <v>1.36</v>
       </c>
       <c r="L13" s="9" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="14">
@@ -17698,7 +17698,7 @@
         </is>
       </c>
       <c r="E14" s="7" t="n">
-        <v>2276</v>
+        <v>2250</v>
       </c>
       <c r="F14" s="9" t="n"/>
       <c r="G14" s="9" t="n">
@@ -17714,7 +17714,7 @@
         <v>1.59</v>
       </c>
       <c r="K14" s="9" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.93</v>
       </c>
       <c r="L14" s="9" t="n">
         <v>0.89</v>
@@ -17742,7 +17742,7 @@
         </is>
       </c>
       <c r="E15" s="7" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F15" s="9" t="n"/>
       <c r="G15" s="9" t="n">
@@ -17782,7 +17782,7 @@
         </is>
       </c>
       <c r="E16" s="7" t="n">
-        <v>4374</v>
+        <v>4427</v>
       </c>
       <c r="F16" s="9" t="n">
         <v>0.12</v>
@@ -17800,7 +17800,7 @@
         <v>0.42</v>
       </c>
       <c r="K16" s="9" t="n">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="L16" s="9" t="n"/>
     </row>
@@ -17870,7 +17870,7 @@
         </is>
       </c>
       <c r="E18" s="7" t="n">
-        <v>1240</v>
+        <v>1242</v>
       </c>
       <c r="F18" s="9" t="n"/>
       <c r="G18" s="9" t="n">
@@ -17914,7 +17914,7 @@
         </is>
       </c>
       <c r="E19" s="7" t="n">
-        <v>6502</v>
+        <v>5742</v>
       </c>
       <c r="F19" s="9" t="n"/>
       <c r="G19" s="9" t="n"/>
@@ -17925,10 +17925,10 @@
         <v>4.38</v>
       </c>
       <c r="J19" s="9" t="n">
-        <v>3.62</v>
+        <v>3.2</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>3.2</v>
+        <v>2.83</v>
       </c>
       <c r="L19" s="9" t="n"/>
     </row>
@@ -17954,7 +17954,7 @@
         </is>
       </c>
       <c r="E20" s="7" t="n">
-        <v>913</v>
+        <v>895</v>
       </c>
       <c r="F20" s="9" t="n">
         <v>1.13</v>
@@ -17969,10 +17969,10 @@
         <v>7.54</v>
       </c>
       <c r="J20" s="9" t="n">
-        <v>2.03</v>
+        <v>1.99</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="L20" s="9" t="n"/>
     </row>
@@ -17998,7 +17998,7 @@
         </is>
       </c>
       <c r="E21" s="7" t="n">
-        <v>1989</v>
+        <v>1956</v>
       </c>
       <c r="F21" s="9" t="n">
         <v>0.6899999999999999</v>
@@ -18013,10 +18013,10 @@
         <v>2.61</v>
       </c>
       <c r="J21" s="9" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="L21" s="9" t="n"/>
     </row>
@@ -18042,7 +18042,7 @@
         </is>
       </c>
       <c r="E22" s="7" t="n">
-        <v>601</v>
+        <v>591</v>
       </c>
       <c r="F22" s="9" t="n">
         <v>1.29</v>
@@ -18057,10 +18057,10 @@
         <v>1.65</v>
       </c>
       <c r="J22" s="9" t="n">
-        <v>0.84</v>
+        <v>0.83</v>
       </c>
       <c r="K22" s="9" t="n">
-        <v>0.8</v>
+        <v>0.78</v>
       </c>
       <c r="L22" s="9" t="n"/>
     </row>
@@ -18086,7 +18086,7 @@
         </is>
       </c>
       <c r="E23" s="7" t="n">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="F23" s="9" t="n">
         <v>0.72</v>
@@ -18101,10 +18101,10 @@
         <v>1.02</v>
       </c>
       <c r="J23" s="9" t="n">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>0.43</v>
+        <v>0.42</v>
       </c>
       <c r="L23" s="9" t="n"/>
     </row>
@@ -18130,7 +18130,7 @@
         </is>
       </c>
       <c r="E24" s="7" t="n">
-        <v>7187</v>
+        <v>7199</v>
       </c>
       <c r="F24" s="9" t="n">
         <v>1.78</v>
@@ -18174,7 +18174,7 @@
         </is>
       </c>
       <c r="E25" s="7" t="n">
-        <v>29608</v>
+        <v>29529</v>
       </c>
       <c r="F25" s="9" t="n">
         <v>0.53</v>
@@ -18189,7 +18189,7 @@
         <v>1.81</v>
       </c>
       <c r="J25" s="9" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="K25" s="9" t="n">
         <v>1.13</v>
@@ -18218,7 +18218,7 @@
         </is>
       </c>
       <c r="E26" s="7" t="n">
-        <v>7178</v>
+        <v>7077</v>
       </c>
       <c r="F26" s="9" t="n">
         <v>0.9</v>
@@ -18233,10 +18233,10 @@
         <v>2.14</v>
       </c>
       <c r="J26" s="9" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="L26" s="9" t="n"/>
     </row>
@@ -18262,7 +18262,7 @@
         </is>
       </c>
       <c r="E27" s="7" t="n">
-        <v>8640</v>
+        <v>8995</v>
       </c>
       <c r="F27" s="9" t="n">
         <v>0.9</v>
@@ -18277,10 +18277,10 @@
         <v>2.78</v>
       </c>
       <c r="J27" s="9" t="n">
-        <v>2.55</v>
+        <v>2.65</v>
       </c>
       <c r="K27" s="9" t="n">
-        <v>2.32</v>
+        <v>2.42</v>
       </c>
       <c r="L27" s="9" t="n"/>
     </row>
@@ -18306,7 +18306,7 @@
         </is>
       </c>
       <c r="E28" s="7" t="n">
-        <v>6595</v>
+        <v>6520</v>
       </c>
       <c r="F28" s="9" t="n">
         <v>0.98</v>
@@ -18321,10 +18321,10 @@
         <v>3.51</v>
       </c>
       <c r="J28" s="9" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="K28" s="9" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="L28" s="9" t="n"/>
     </row>
@@ -18368,7 +18368,7 @@
         <v>1.7</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="L29" s="9" t="n"/>
     </row>
@@ -18497,7 +18497,7 @@
         <v>2.78</v>
       </c>
       <c r="J32" s="9" t="n">
-        <v>2.64</v>
+        <v>2.63</v>
       </c>
       <c r="K32" s="9" t="n">
         <v>2.45</v>
@@ -18570,7 +18570,7 @@
         </is>
       </c>
       <c r="E34" s="7" t="n">
-        <v>52463</v>
+        <v>53060</v>
       </c>
       <c r="F34" s="9" t="n">
         <v>1.26</v>
@@ -18585,10 +18585,10 @@
         <v>7.21</v>
       </c>
       <c r="J34" s="9" t="n">
-        <v>3.36</v>
+        <v>3.4</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="L34" s="9" t="n"/>
     </row>
@@ -18614,7 +18614,7 @@
         </is>
       </c>
       <c r="E35" s="7" t="n">
-        <v>75806</v>
+        <v>76652</v>
       </c>
       <c r="F35" s="9" t="n">
         <v>1.24</v>
@@ -18629,10 +18629,10 @@
         <v>1.77</v>
       </c>
       <c r="J35" s="9" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="L35" s="9" t="n"/>
     </row>
@@ -18658,7 +18658,7 @@
         </is>
       </c>
       <c r="E36" s="7" t="n">
-        <v>31374</v>
+        <v>31646</v>
       </c>
       <c r="F36" s="9" t="n">
         <v>0.32</v>
@@ -18673,10 +18673,10 @@
         <v>1.45</v>
       </c>
       <c r="J36" s="9" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="K36" s="9" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="L36" s="9" t="n"/>
     </row>
@@ -18702,7 +18702,7 @@
         </is>
       </c>
       <c r="E37" s="7" t="n">
-        <v>35175</v>
+        <v>35082</v>
       </c>
       <c r="F37" s="9" t="n">
         <v>1.3</v>
@@ -18717,10 +18717,10 @@
         <v>3.66</v>
       </c>
       <c r="J37" s="9" t="n">
-        <v>3.57</v>
+        <v>3.56</v>
       </c>
       <c r="K37" s="9" t="n">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="L37" s="9" t="n"/>
     </row>
@@ -18746,7 +18746,7 @@
         </is>
       </c>
       <c r="E38" s="7" t="n">
-        <v>3142</v>
+        <v>2934</v>
       </c>
       <c r="F38" s="9" t="n">
         <v>0.34</v>
@@ -18761,10 +18761,10 @@
         <v>1.25</v>
       </c>
       <c r="J38" s="9" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="K38" s="9" t="n">
-        <v>0.4</v>
+        <v>0.37</v>
       </c>
       <c r="L38" s="9" t="n"/>
     </row>
@@ -18790,7 +18790,7 @@
         </is>
       </c>
       <c r="E39" s="7" t="n">
-        <v>3514</v>
+        <v>3509</v>
       </c>
       <c r="F39" s="9" t="n">
         <v>0.4</v>
@@ -19006,7 +19006,7 @@
         </is>
       </c>
       <c r="E44" s="7" t="n">
-        <v>38449</v>
+        <v>38576</v>
       </c>
       <c r="F44" s="9" t="n"/>
       <c r="G44" s="9" t="n">
@@ -19022,10 +19022,10 @@
         <v>1.31</v>
       </c>
       <c r="K44" s="9" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="L44" s="9" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
     </row>
     <row r="45">
@@ -19050,7 +19050,7 @@
         </is>
       </c>
       <c r="E45" s="7" t="n">
-        <v>7160</v>
+        <v>7093</v>
       </c>
       <c r="F45" s="9" t="n"/>
       <c r="G45" s="9" t="n">
@@ -19066,10 +19066,10 @@
         <v>0.8</v>
       </c>
       <c r="K45" s="9" t="n">
-        <v>0.76</v>
+        <v>0.75</v>
       </c>
       <c r="L45" s="9" t="n">
-        <v>0.73</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="46">
@@ -19094,7 +19094,7 @@
         </is>
       </c>
       <c r="E46" s="7" t="n">
-        <v>63165</v>
+        <v>63699</v>
       </c>
       <c r="F46" s="9" t="n">
         <v>0.8100000000000001</v>
@@ -19109,10 +19109,10 @@
         <v>1.26</v>
       </c>
       <c r="J46" s="9" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="K46" s="9" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="L46" s="9" t="n"/>
     </row>
@@ -19138,7 +19138,7 @@
         </is>
       </c>
       <c r="E47" s="7" t="n">
-        <v>25225</v>
+        <v>25197</v>
       </c>
       <c r="F47" s="9" t="n">
         <v>1.66</v>
@@ -19153,7 +19153,7 @@
         <v>2.17</v>
       </c>
       <c r="J47" s="9" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="K47" s="9" t="n">
         <v>1.42</v>
@@ -19182,7 +19182,7 @@
         </is>
       </c>
       <c r="E48" s="7" t="n">
-        <v>12566</v>
+        <v>12551</v>
       </c>
       <c r="F48" s="9" t="n">
         <v>0.64</v>
@@ -19197,7 +19197,7 @@
         <v>1.35</v>
       </c>
       <c r="J48" s="9" t="n">
-        <v>0.74</v>
+        <v>0.73</v>
       </c>
       <c r="K48" s="9" t="n">
         <v>0.64</v>
@@ -19226,7 +19226,7 @@
         </is>
       </c>
       <c r="E49" s="7" t="n">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="F49" s="9" t="n">
         <v>0.49</v>
@@ -19310,7 +19310,7 @@
         </is>
       </c>
       <c r="E51" s="7" t="n">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="F51" s="9" t="n">
         <v>0.5</v>
@@ -19832,7 +19832,7 @@
         </is>
       </c>
       <c r="G6" s="14" t="n">
-        <v>295500</v>
+        <v>289500</v>
       </c>
       <c r="H6" s="14" t="n">
         <v>29839.46</v>
@@ -19860,7 +19860,7 @@
         <v>30.27</v>
       </c>
       <c r="Q6" s="14" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="R6" s="14" t="inlineStr">
         <is>
@@ -19905,7 +19905,7 @@
         </is>
       </c>
       <c r="G7" s="14" t="n">
-        <v>295500</v>
+        <v>289500</v>
       </c>
       <c r="H7" s="14" t="n">
         <v>34806.34</v>
@@ -19923,17 +19923,17 @@
         <v>15056687726226.81</v>
       </c>
       <c r="M7" s="14" t="n">
-        <v>8.49</v>
+        <v>8.32</v>
       </c>
       <c r="N7" s="14" t="n"/>
       <c r="O7" s="14" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="P7" s="14" t="n">
         <v>27.02</v>
       </c>
       <c r="Q7" s="14" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="R7" s="14" t="inlineStr">
         <is>
@@ -20327,7 +20327,7 @@
         </is>
       </c>
       <c r="G13" s="14" t="n">
-        <v>53700</v>
+        <v>53000</v>
       </c>
       <c r="H13" s="14" t="n">
         <v>6104.24</v>
@@ -20355,7 +20355,7 @@
         <v>27.12</v>
       </c>
       <c r="Q13" s="14" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="R13" s="14" t="inlineStr">
         <is>
@@ -20400,7 +20400,7 @@
         </is>
       </c>
       <c r="G14" s="14" t="n">
-        <v>53700</v>
+        <v>53000</v>
       </c>
       <c r="H14" s="14" t="n">
         <v>6182.11</v>
@@ -20418,17 +20418,17 @@
         <v>9934752906723.203</v>
       </c>
       <c r="M14" s="14" t="n">
-        <v>8.69</v>
+        <v>8.57</v>
       </c>
       <c r="N14" s="14" t="n"/>
       <c r="O14" s="14" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="P14" s="14" t="n">
         <v>21.08</v>
       </c>
       <c r="Q14" s="14" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="R14" s="14" t="inlineStr">
         <is>
@@ -20820,7 +20820,7 @@
         </is>
       </c>
       <c r="G20" s="14" t="n">
-        <v>16530</v>
+        <v>16300</v>
       </c>
       <c r="H20" s="14" t="n">
         <v>1175.69</v>
@@ -20848,7 +20848,7 @@
         <v>20</v>
       </c>
       <c r="Q20" s="14" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="R20" s="14" t="inlineStr">
         <is>
@@ -20893,7 +20893,7 @@
         </is>
       </c>
       <c r="G21" s="14" t="n">
-        <v>16530</v>
+        <v>16300</v>
       </c>
       <c r="H21" s="14" t="n">
         <v>1691.1</v>
@@ -20911,17 +20911,17 @@
         <v>6597608582819.35</v>
       </c>
       <c r="M21" s="14" t="n">
-        <v>9.77</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="N21" s="14" t="n"/>
       <c r="O21" s="14" t="n">
-        <v>2.14</v>
+        <v>2.11</v>
       </c>
       <c r="P21" s="14" t="n">
         <v>24.58</v>
       </c>
       <c r="Q21" s="14" t="n">
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
       <c r="R21" s="14" t="inlineStr">
         <is>
@@ -21317,7 +21317,7 @@
         </is>
       </c>
       <c r="G27" s="14" t="n">
-        <v>244000</v>
+        <v>243000</v>
       </c>
       <c r="H27" s="14" t="n">
         <v>51923.58</v>
@@ -21390,7 +21390,7 @@
         </is>
       </c>
       <c r="G28" s="14" t="n">
-        <v>244000</v>
+        <v>243000</v>
       </c>
       <c r="H28" s="14" t="n">
         <v>60335.65</v>
@@ -21408,7 +21408,7 @@
         <v>19743148063746.41</v>
       </c>
       <c r="M28" s="14" t="n">
-        <v>4.04</v>
+        <v>4.03</v>
       </c>
       <c r="N28" s="14" t="n"/>
       <c r="O28" s="14" t="n">
@@ -21786,7 +21786,7 @@
         </is>
       </c>
       <c r="G34" s="14" t="n">
-        <v>36800</v>
+        <v>36300</v>
       </c>
       <c r="H34" s="14" t="n">
         <v>7656.2</v>
@@ -21814,7 +21814,7 @@
         <v>24.44</v>
       </c>
       <c r="Q34" s="14" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="R34" s="14" t="inlineStr">
         <is>
@@ -21859,7 +21859,7 @@
         </is>
       </c>
       <c r="G35" s="14" t="n">
-        <v>36800</v>
+        <v>36300</v>
       </c>
       <c r="H35" s="14" t="n">
         <v>7804.33</v>
@@ -21877,17 +21877,17 @@
         <v>1664829720542.566</v>
       </c>
       <c r="M35" s="14" t="n">
-        <v>4.72</v>
+        <v>4.65</v>
       </c>
       <c r="N35" s="14" t="n"/>
       <c r="O35" s="14" t="n">
-        <v>0.85</v>
+        <v>0.83</v>
       </c>
       <c r="P35" s="14" t="n">
         <v>19.63</v>
       </c>
       <c r="Q35" s="14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="R35" s="14" t="inlineStr">
         <is>
@@ -22279,7 +22279,7 @@
         </is>
       </c>
       <c r="G41" s="14" t="n">
-        <v>12140</v>
+        <v>11980</v>
       </c>
       <c r="H41" s="14" t="n"/>
       <c r="I41" s="14" t="n"/>
@@ -22342,7 +22342,7 @@
         </is>
       </c>
       <c r="G42" s="14" t="n">
-        <v>12140</v>
+        <v>11980</v>
       </c>
       <c r="H42" s="14" t="n"/>
       <c r="I42" s="14" t="n"/>
@@ -22744,7 +22744,7 @@
         </is>
       </c>
       <c r="G48" s="14" t="n">
-        <v>35.1</v>
+        <v>35.17</v>
       </c>
       <c r="H48" s="14" t="n">
         <v>2.78</v>
@@ -22762,7 +22762,7 @@
         <v>164311447690.6485</v>
       </c>
       <c r="M48" s="14" t="n">
-        <v>12.64</v>
+        <v>12.67</v>
       </c>
       <c r="N48" s="14" t="n"/>
       <c r="O48" s="14" t="n">
@@ -22817,7 +22817,7 @@
         </is>
       </c>
       <c r="G49" s="14" t="n">
-        <v>35.1</v>
+        <v>35.17</v>
       </c>
       <c r="H49" s="14" t="n">
         <v>3.61</v>
@@ -22835,7 +22835,7 @@
         <v>191476156060.4519</v>
       </c>
       <c r="M49" s="14" t="n">
-        <v>9.720000000000001</v>
+        <v>9.74</v>
       </c>
       <c r="N49" s="14" t="n"/>
       <c r="O49" s="14" t="n">
@@ -22845,7 +22845,7 @@
         <v>15.27</v>
       </c>
       <c r="Q49" s="14" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="R49" s="14" t="inlineStr">
         <is>
@@ -23261,7 +23261,7 @@
         <v>38233818155.83939</v>
       </c>
       <c r="M55" s="14" t="n">
-        <v>9.08</v>
+        <v>9.1</v>
       </c>
       <c r="N55" s="14" t="n"/>
       <c r="O55" s="14" t="n">
@@ -23334,7 +23334,7 @@
         <v>44999698854.56541</v>
       </c>
       <c r="M56" s="14" t="n">
-        <v>8.18</v>
+        <v>8.19</v>
       </c>
       <c r="N56" s="14" t="n"/>
       <c r="O56" s="14" t="n">
@@ -23742,7 +23742,7 @@
         </is>
       </c>
       <c r="G62" s="14" t="n">
-        <v>12.87</v>
+        <v>12.76</v>
       </c>
       <c r="H62" s="14" t="n">
         <v>0.82</v>
@@ -23760,17 +23760,17 @@
         <v>19125837218.80924</v>
       </c>
       <c r="M62" s="14" t="n">
-        <v>13.37</v>
+        <v>13.22</v>
       </c>
       <c r="N62" s="14" t="n"/>
       <c r="O62" s="14" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="P62" s="14" t="n">
         <v>6.2</v>
       </c>
       <c r="Q62" s="14" t="n">
-        <v>0.7</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="R62" s="14" t="inlineStr">
         <is>
@@ -23815,7 +23815,7 @@
         </is>
       </c>
       <c r="G63" s="14" t="n">
-        <v>12.87</v>
+        <v>12.76</v>
       </c>
       <c r="H63" s="14" t="n">
         <v>1.68</v>
@@ -23833,17 +23833,17 @@
         <v>20951974378.675</v>
       </c>
       <c r="M63" s="14" t="n">
-        <v>6.53</v>
+        <v>6.45</v>
       </c>
       <c r="N63" s="14" t="n"/>
       <c r="O63" s="14" t="n">
-        <v>0.74</v>
+        <v>0.73</v>
       </c>
       <c r="P63" s="14" t="n">
         <v>11.85</v>
       </c>
       <c r="Q63" s="14" t="n">
-        <v>0.54</v>
+        <v>0.53</v>
       </c>
       <c r="R63" s="14" t="inlineStr">
         <is>
@@ -24241,7 +24241,7 @@
         </is>
       </c>
       <c r="G69" s="14" t="n">
-        <v>3534</v>
+        <v>3500</v>
       </c>
       <c r="H69" s="14" t="n">
         <v>134.68</v>
@@ -24259,17 +24259,17 @@
         <v>3414081930273.525</v>
       </c>
       <c r="M69" s="14" t="n">
-        <v>26.24</v>
+        <v>25.99</v>
       </c>
       <c r="N69" s="14" t="n"/>
       <c r="O69" s="14" t="n">
-        <v>3.48</v>
+        <v>3.44</v>
       </c>
       <c r="P69" s="14" t="n">
         <v>13.92</v>
       </c>
       <c r="Q69" s="14" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="R69" s="14" t="inlineStr">
         <is>
@@ -24314,7 +24314,7 @@
         </is>
       </c>
       <c r="G70" s="14" t="n">
-        <v>3534</v>
+        <v>3500</v>
       </c>
       <c r="H70" s="14" t="n">
         <v>153.07</v>
@@ -24332,17 +24332,17 @@
         <v>3784052023498.018</v>
       </c>
       <c r="M70" s="14" t="n">
-        <v>23.09</v>
+        <v>22.87</v>
       </c>
       <c r="N70" s="14" t="n"/>
       <c r="O70" s="14" t="n">
-        <v>3.14</v>
+        <v>3.11</v>
       </c>
       <c r="P70" s="14" t="n">
         <v>14.29</v>
       </c>
       <c r="Q70" s="14" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="R70" s="14" t="inlineStr">
         <is>
@@ -24740,7 +24740,7 @@
         </is>
       </c>
       <c r="G76" s="14" t="n">
-        <v>2141</v>
+        <v>2143.5</v>
       </c>
       <c r="H76" s="14" t="n">
         <v>142.43</v>
@@ -24758,7 +24758,7 @@
         <v>968719416048.4681</v>
       </c>
       <c r="M76" s="14" t="n">
-        <v>15.03</v>
+        <v>15.05</v>
       </c>
       <c r="N76" s="14" t="n"/>
       <c r="O76" s="14" t="n">
@@ -24813,7 +24813,7 @@
         </is>
       </c>
       <c r="G77" s="14" t="n">
-        <v>2141</v>
+        <v>2143.5</v>
       </c>
       <c r="H77" s="14" t="n">
         <v>162.98</v>
@@ -24831,7 +24831,7 @@
         <v>1072390237896.21</v>
       </c>
       <c r="M77" s="14" t="n">
-        <v>13.14</v>
+        <v>13.15</v>
       </c>
       <c r="N77" s="14" t="n"/>
       <c r="O77" s="14" t="n">
@@ -25237,7 +25237,7 @@
         </is>
       </c>
       <c r="G83" s="14" t="n">
-        <v>2382</v>
+        <v>2392.5</v>
       </c>
       <c r="H83" s="14" t="n">
         <v>176.91</v>
@@ -25255,11 +25255,11 @@
         <v>815093716660.2814</v>
       </c>
       <c r="M83" s="14" t="n">
-        <v>13.46</v>
+        <v>13.52</v>
       </c>
       <c r="N83" s="14" t="n"/>
       <c r="O83" s="14" t="n">
-        <v>3.1</v>
+        <v>3.11</v>
       </c>
       <c r="P83" s="14" t="n">
         <v>25.56</v>
@@ -25310,7 +25310,7 @@
         </is>
       </c>
       <c r="G84" s="14" t="n">
-        <v>2382</v>
+        <v>2392.5</v>
       </c>
       <c r="H84" s="14" t="n">
         <v>154.53</v>
@@ -25328,17 +25328,17 @@
         <v>957348937809.2065</v>
       </c>
       <c r="M84" s="14" t="n">
-        <v>15.41</v>
+        <v>15.48</v>
       </c>
       <c r="N84" s="14" t="n"/>
       <c r="O84" s="14" t="n">
-        <v>2.64</v>
+        <v>2.65</v>
       </c>
       <c r="P84" s="14" t="n">
         <v>18.49</v>
       </c>
       <c r="Q84" s="14" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="R84" s="14" t="inlineStr">
         <is>
@@ -25736,7 +25736,7 @@
         </is>
       </c>
       <c r="G90" s="14" t="n">
-        <v>3536</v>
+        <v>3507</v>
       </c>
       <c r="H90" s="14" t="n">
         <v>357.21</v>
@@ -25754,17 +25754,17 @@
         <v>259885320112.1904</v>
       </c>
       <c r="M90" s="14" t="n">
-        <v>9.9</v>
+        <v>9.82</v>
       </c>
       <c r="N90" s="14" t="n"/>
       <c r="O90" s="14" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="P90" s="14" t="n">
         <v>14.74</v>
       </c>
       <c r="Q90" s="14" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.93</v>
       </c>
       <c r="R90" s="14" t="inlineStr">
         <is>
@@ -25809,7 +25809,7 @@
         </is>
       </c>
       <c r="G91" s="14" t="n">
-        <v>3536</v>
+        <v>3507</v>
       </c>
       <c r="H91" s="14" t="n">
         <v>371.62</v>
@@ -25827,11 +25827,11 @@
         <v>291908147365.1342</v>
       </c>
       <c r="M91" s="14" t="n">
-        <v>9.52</v>
+        <v>9.44</v>
       </c>
       <c r="N91" s="14" t="n"/>
       <c r="O91" s="14" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="P91" s="14" t="n">
         <v>13.59</v>
@@ -26235,7 +26235,7 @@
         </is>
       </c>
       <c r="G97" s="14" t="n">
-        <v>10340</v>
+        <v>10460</v>
       </c>
       <c r="H97" s="14" t="n"/>
       <c r="I97" s="14" t="n"/>
@@ -26292,7 +26292,7 @@
         </is>
       </c>
       <c r="G98" s="14" t="n">
-        <v>10340</v>
+        <v>10460</v>
       </c>
       <c r="H98" s="14" t="n"/>
       <c r="I98" s="14" t="n"/>
@@ -26698,7 +26698,7 @@
         </is>
       </c>
       <c r="G104" s="14" t="n">
-        <v>12.02</v>
+        <v>12.17</v>
       </c>
       <c r="H104" s="14" t="n">
         <v>0.55</v>
@@ -26716,11 +26716,11 @@
         <v>1174408680.1575</v>
       </c>
       <c r="M104" s="14" t="n">
-        <v>22</v>
+        <v>22.28</v>
       </c>
       <c r="N104" s="14" t="n"/>
       <c r="O104" s="14" t="n">
-        <v>3.32</v>
+        <v>3.36</v>
       </c>
       <c r="P104" s="14" t="n">
         <v>16.31</v>
@@ -26771,7 +26771,7 @@
         </is>
       </c>
       <c r="G105" s="14" t="n">
-        <v>12.02</v>
+        <v>12.17</v>
       </c>
       <c r="H105" s="14" t="n">
         <v>0.82</v>
@@ -26789,17 +26789,17 @@
         <v>1440753677.56484</v>
       </c>
       <c r="M105" s="14" t="n">
-        <v>14.63</v>
+        <v>14.82</v>
       </c>
       <c r="N105" s="14" t="n"/>
       <c r="O105" s="14" t="n">
-        <v>2.71</v>
+        <v>2.74</v>
       </c>
       <c r="P105" s="14" t="n">
         <v>20.37</v>
       </c>
       <c r="Q105" s="14" t="n">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="R105" s="14" t="inlineStr">
         <is>
@@ -27708,7 +27708,7 @@
         <v>1329243564.59849</v>
       </c>
       <c r="M118" s="14" t="n">
-        <v>18.42</v>
+        <v>18.44</v>
       </c>
       <c r="N118" s="14" t="n"/>
       <c r="O118" s="14" t="n">
@@ -27781,7 +27781,7 @@
         <v>1437828645.45737</v>
       </c>
       <c r="M119" s="14" t="n">
-        <v>16.23</v>
+        <v>16.25</v>
       </c>
       <c r="N119" s="14" t="n"/>
       <c r="O119" s="14" t="n">
@@ -28169,7 +28169,7 @@
         </is>
       </c>
       <c r="G125" s="14" t="n">
-        <v>191800</v>
+        <v>169600</v>
       </c>
       <c r="H125" s="14" t="n">
         <v>7652.69</v>
@@ -28197,7 +28197,7 @@
         <v>38.12</v>
       </c>
       <c r="Q125" s="14" t="n">
-        <v>3.62</v>
+        <v>3.2</v>
       </c>
       <c r="R125" s="14" t="inlineStr">
         <is>
@@ -28242,7 +28242,7 @@
         </is>
       </c>
       <c r="G126" s="14" t="n">
-        <v>191800</v>
+        <v>169600</v>
       </c>
       <c r="H126" s="14" t="n">
         <v>9357.49</v>
@@ -28260,17 +28260,17 @@
         <v>1234616472831.365</v>
       </c>
       <c r="M126" s="14" t="n">
-        <v>20.5</v>
+        <v>18.12</v>
       </c>
       <c r="N126" s="14" t="n"/>
       <c r="O126" s="14" t="n">
-        <v>6.96</v>
+        <v>6.16</v>
       </c>
       <c r="P126" s="14" t="n">
         <v>37.39</v>
       </c>
       <c r="Q126" s="14" t="n">
-        <v>3.2</v>
+        <v>2.83</v>
       </c>
       <c r="R126" s="14" t="inlineStr">
         <is>
@@ -28668,7 +28668,7 @@
         </is>
       </c>
       <c r="G132" s="14" t="n">
-        <v>35600</v>
+        <v>34950</v>
       </c>
       <c r="H132" s="14" t="n">
         <v>3734</v>
@@ -28696,7 +28696,7 @@
         <v>25.25</v>
       </c>
       <c r="Q132" s="14" t="n">
-        <v>2.03</v>
+        <v>1.99</v>
       </c>
       <c r="R132" s="14" t="inlineStr">
         <is>
@@ -28741,7 +28741,7 @@
         </is>
       </c>
       <c r="G133" s="14" t="n">
-        <v>35600</v>
+        <v>34950</v>
       </c>
       <c r="H133" s="14" t="n">
         <v>5008</v>
@@ -28759,17 +28759,17 @@
         <v>785453728266</v>
       </c>
       <c r="M133" s="14" t="n">
-        <v>7.11</v>
+        <v>6.98</v>
       </c>
       <c r="N133" s="14" t="n"/>
       <c r="O133" s="14" t="n">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="P133" s="14" t="n">
         <v>24.25</v>
       </c>
       <c r="Q133" s="14" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="R133" s="14" t="inlineStr">
         <is>
@@ -29161,7 +29161,7 @@
         </is>
       </c>
       <c r="G139" s="14" t="n">
-        <v>31525</v>
+        <v>31050</v>
       </c>
       <c r="H139" s="14" t="n">
         <v>2247.3</v>
@@ -29189,7 +29189,7 @@
         <v>28.77</v>
       </c>
       <c r="Q139" s="14" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="R139" s="14" t="inlineStr">
         <is>
@@ -29234,7 +29234,7 @@
         </is>
       </c>
       <c r="G140" s="14" t="n">
-        <v>31525</v>
+        <v>31050</v>
       </c>
       <c r="H140" s="14" t="n">
         <v>3635.11</v>
@@ -29252,17 +29252,17 @@
         <v>1046846601812.56</v>
       </c>
       <c r="M140" s="14" t="n">
-        <v>8.67</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="N140" s="14" t="n"/>
       <c r="O140" s="14" t="n">
-        <v>2.51</v>
+        <v>2.47</v>
       </c>
       <c r="P140" s="14" t="n">
         <v>33.88</v>
       </c>
       <c r="Q140" s="14" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="R140" s="14" t="inlineStr">
         <is>
@@ -29658,7 +29658,7 @@
         </is>
       </c>
       <c r="G146" s="14" t="n">
-        <v>15790</v>
+        <v>15530</v>
       </c>
       <c r="H146" s="14" t="n">
         <v>2370.59</v>
@@ -29686,7 +29686,7 @@
         <v>18.68</v>
       </c>
       <c r="Q146" s="14" t="n">
-        <v>0.84</v>
+        <v>0.83</v>
       </c>
       <c r="R146" s="14" t="inlineStr">
         <is>
@@ -29731,7 +29731,7 @@
         </is>
       </c>
       <c r="G147" s="14" t="n">
-        <v>15790</v>
+        <v>15530</v>
       </c>
       <c r="H147" s="14" t="n">
         <v>2816.13</v>
@@ -29749,17 +29749,17 @@
         <v>800111224287.9514</v>
       </c>
       <c r="M147" s="14" t="n">
-        <v>5.61</v>
+        <v>5.51</v>
       </c>
       <c r="N147" s="14" t="n"/>
       <c r="O147" s="14" t="n">
-        <v>0.99</v>
+        <v>0.98</v>
       </c>
       <c r="P147" s="14" t="n">
         <v>19.16</v>
       </c>
       <c r="Q147" s="14" t="n">
-        <v>0.8</v>
+        <v>0.78</v>
       </c>
       <c r="R147" s="14" t="inlineStr">
         <is>
@@ -30157,7 +30157,7 @@
         </is>
       </c>
       <c r="G153" s="14" t="n">
-        <v>12830</v>
+        <v>12530</v>
       </c>
       <c r="H153" s="14" t="n">
         <v>2442</v>
@@ -30185,7 +30185,7 @@
         <v>29.46</v>
       </c>
       <c r="Q153" s="14" t="n">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="R153" s="14" t="inlineStr">
         <is>
@@ -30230,7 +30230,7 @@
         </is>
       </c>
       <c r="G154" s="14" t="n">
-        <v>12830</v>
+        <v>12530</v>
       </c>
       <c r="H154" s="14" t="n">
         <v>2901</v>
@@ -30248,17 +30248,17 @@
         <v>418828450507</v>
       </c>
       <c r="M154" s="14" t="n">
-        <v>4.42</v>
+        <v>4.32</v>
       </c>
       <c r="N154" s="14" t="n"/>
       <c r="O154" s="14" t="n">
-        <v>0.92</v>
+        <v>0.9</v>
       </c>
       <c r="P154" s="14" t="n">
         <v>23.13</v>
       </c>
       <c r="Q154" s="14" t="n">
-        <v>0.43</v>
+        <v>0.42</v>
       </c>
       <c r="R154" s="14" t="inlineStr">
         <is>
@@ -30656,7 +30656,7 @@
         </is>
       </c>
       <c r="G160" s="14" t="n">
-        <v>97500</v>
+        <v>97800</v>
       </c>
       <c r="H160" s="14" t="n">
         <v>2449.48</v>
@@ -30729,7 +30729,7 @@
         </is>
       </c>
       <c r="G161" s="14" t="n">
-        <v>97500</v>
+        <v>97800</v>
       </c>
       <c r="H161" s="14" t="n">
         <v>4476.83</v>
@@ -30747,11 +30747,11 @@
         <v>2319715367260.464</v>
       </c>
       <c r="M161" s="14" t="n">
-        <v>21.78</v>
+        <v>21.85</v>
       </c>
       <c r="N161" s="14" t="n"/>
       <c r="O161" s="14" t="n">
-        <v>4.1</v>
+        <v>4.11</v>
       </c>
       <c r="P161" s="14" t="n">
         <v>20.19</v>
@@ -31155,7 +31155,7 @@
         </is>
       </c>
       <c r="G167" s="14" t="n">
-        <v>761000</v>
+        <v>760000</v>
       </c>
       <c r="H167" s="14" t="n">
         <v>46056.24</v>
@@ -31183,7 +31183,7 @@
         <v>20.69</v>
       </c>
       <c r="Q167" s="14" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="R167" s="14" t="inlineStr">
         <is>
@@ -31228,7 +31228,7 @@
         </is>
       </c>
       <c r="G168" s="14" t="n">
-        <v>761000</v>
+        <v>760000</v>
       </c>
       <c r="H168" s="14" t="n">
         <v>57796.36</v>
@@ -31246,11 +31246,11 @@
         <v>14106313861667.52</v>
       </c>
       <c r="M168" s="14" t="n">
-        <v>13.17</v>
+        <v>13.15</v>
       </c>
       <c r="N168" s="14" t="n"/>
       <c r="O168" s="14" t="n">
-        <v>2.78</v>
+        <v>2.77</v>
       </c>
       <c r="P168" s="14" t="n">
         <v>23.09</v>
@@ -31654,7 +31654,7 @@
         </is>
       </c>
       <c r="G174" s="14" t="n">
-        <v>434500</v>
+        <v>429000</v>
       </c>
       <c r="H174" s="14" t="n">
         <v>15952.36</v>
@@ -31682,7 +31682,7 @@
         <v>21.8</v>
       </c>
       <c r="Q174" s="14" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="R174" s="14" t="inlineStr">
         <is>
@@ -31727,7 +31727,7 @@
         </is>
       </c>
       <c r="G175" s="14" t="n">
-        <v>434500</v>
+        <v>429000</v>
       </c>
       <c r="H175" s="14" t="n">
         <v>23734.43</v>
@@ -31745,17 +31745,17 @@
         <v>2102000083957.019</v>
       </c>
       <c r="M175" s="14" t="n">
-        <v>18.31</v>
+        <v>18.08</v>
       </c>
       <c r="N175" s="14" t="n"/>
       <c r="O175" s="14" t="n">
-        <v>4.52</v>
+        <v>4.46</v>
       </c>
       <c r="P175" s="14" t="n">
         <v>27.27</v>
       </c>
       <c r="Q175" s="14" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="R175" s="14" t="inlineStr">
         <is>
@@ -32151,7 +32151,7 @@
         </is>
       </c>
       <c r="G181" s="14" t="n">
-        <v>61100</v>
+        <v>63700</v>
       </c>
       <c r="H181" s="14" t="n">
         <v>1076.43</v>
@@ -32179,7 +32179,7 @@
         <v>2.7</v>
       </c>
       <c r="Q181" s="14" t="n">
-        <v>2.55</v>
+        <v>2.65</v>
       </c>
       <c r="R181" s="14" t="inlineStr">
         <is>
@@ -32224,7 +32224,7 @@
         </is>
       </c>
       <c r="G182" s="14" t="n">
-        <v>61100</v>
+        <v>63700</v>
       </c>
       <c r="H182" s="14" t="n">
         <v>2327.22</v>
@@ -32242,17 +32242,17 @@
         <v>5171213701216.773</v>
       </c>
       <c r="M182" s="14" t="n">
-        <v>26.25</v>
+        <v>27.37</v>
       </c>
       <c r="N182" s="14" t="n"/>
       <c r="O182" s="14" t="n">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="P182" s="14" t="n">
         <v>8.6</v>
       </c>
       <c r="Q182" s="14" t="n">
-        <v>2.32</v>
+        <v>2.42</v>
       </c>
       <c r="R182" s="14" t="inlineStr">
         <is>
@@ -32650,7 +32650,7 @@
         </is>
       </c>
       <c r="G188" s="14" t="n">
-        <v>79900</v>
+        <v>79100</v>
       </c>
       <c r="H188" s="14" t="n">
         <v>7274.68</v>
@@ -32678,7 +32678,7 @@
         <v>23.27</v>
       </c>
       <c r="Q188" s="14" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="R188" s="14" t="inlineStr">
         <is>
@@ -32723,7 +32723,7 @@
         </is>
       </c>
       <c r="G189" s="14" t="n">
-        <v>79900</v>
+        <v>79100</v>
       </c>
       <c r="H189" s="14" t="n">
         <v>8364.940000000001</v>
@@ -32741,17 +32741,17 @@
         <v>4647533368918.296</v>
       </c>
       <c r="M189" s="14" t="n">
-        <v>9.550000000000001</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="N189" s="14" t="n"/>
       <c r="O189" s="14" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="P189" s="14" t="n">
         <v>21.59</v>
       </c>
       <c r="Q189" s="14" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="R189" s="14" t="inlineStr">
         <is>
@@ -33152,29 +33152,29 @@
         <v>604.1799999999999</v>
       </c>
       <c r="H195" s="14" t="n">
-        <v>30.62</v>
+        <v>30.61</v>
       </c>
       <c r="I195" s="14" t="n">
         <v>44.96</v>
       </c>
       <c r="J195" s="15" t="n">
-        <v>81206789500</v>
+        <v>81282888230</v>
       </c>
       <c r="K195" s="15" t="n">
-        <v>7012813560</v>
+        <v>7008925140</v>
       </c>
       <c r="L195" s="15" t="n">
-        <v>10296833634.244</v>
+        <v>10294850928.886</v>
       </c>
       <c r="M195" s="14" t="n">
-        <v>19.73</v>
+        <v>19.74</v>
       </c>
       <c r="N195" s="14" t="n"/>
       <c r="O195" s="14" t="n">
         <v>13.44</v>
       </c>
       <c r="P195" s="14" t="n">
-        <v>82.42</v>
+        <v>82.38</v>
       </c>
       <c r="Q195" s="14" t="n">
         <v>1.7</v>
@@ -33225,32 +33225,32 @@
         <v>604.1799999999999</v>
       </c>
       <c r="H196" s="14" t="n">
-        <v>33.13</v>
+        <v>33.22</v>
       </c>
       <c r="I196" s="14" t="n">
-        <v>61.86</v>
+        <v>61.9</v>
       </c>
       <c r="J196" s="15" t="n">
-        <v>86590442170</v>
+        <v>86882575210</v>
       </c>
       <c r="K196" s="15" t="n">
-        <v>7586557030</v>
+        <v>7608279970.000001</v>
       </c>
       <c r="L196" s="15" t="n">
-        <v>14165219063.841</v>
+        <v>14174312885.589</v>
       </c>
       <c r="M196" s="14" t="n">
-        <v>18.24</v>
+        <v>18.19</v>
       </c>
       <c r="N196" s="14" t="n"/>
       <c r="O196" s="14" t="n">
-        <v>9.77</v>
+        <v>9.76</v>
       </c>
       <c r="P196" s="14" t="n">
-        <v>62.03</v>
+        <v>62.19</v>
       </c>
       <c r="Q196" s="14" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="R196" s="14" t="inlineStr">
         <is>
@@ -33651,29 +33651,29 @@
         <v>551.4400000000001</v>
       </c>
       <c r="H202" s="14" t="n">
-        <v>29.75</v>
+        <v>29.77</v>
       </c>
       <c r="I202" s="14" t="n">
-        <v>138.19</v>
+        <v>138.21</v>
       </c>
       <c r="J202" s="15" t="n">
-        <v>44053074150</v>
+        <v>44052615810</v>
       </c>
       <c r="K202" s="15" t="n">
-        <v>4223815873.36938</v>
+        <v>4227111628.24212</v>
       </c>
       <c r="L202" s="15" t="n">
-        <v>19623068242.7865</v>
+        <v>19625369338.83865</v>
       </c>
       <c r="M202" s="14" t="n">
-        <v>18.54</v>
+        <v>18.52</v>
       </c>
       <c r="N202" s="14" t="n"/>
       <c r="O202" s="14" t="n">
         <v>3.99</v>
       </c>
       <c r="P202" s="14" t="n">
-        <v>23.27</v>
+        <v>23.29</v>
       </c>
       <c r="Q202" s="14" t="n">
         <v>1.78</v>
@@ -33724,29 +33724,29 @@
         <v>551.4400000000001</v>
       </c>
       <c r="H203" s="14" t="n">
-        <v>30.03</v>
+        <v>30.01</v>
       </c>
       <c r="I203" s="14" t="n">
         <v>159.16</v>
       </c>
       <c r="J203" s="15" t="n">
-        <v>46880306230</v>
+        <v>46888033500</v>
       </c>
       <c r="K203" s="15" t="n">
-        <v>4264462570.15188</v>
+        <v>4261267633.28688</v>
       </c>
       <c r="L203" s="15" t="n">
-        <v>22600516009.26654</v>
+        <v>22600586400.39954</v>
       </c>
       <c r="M203" s="14" t="n">
-        <v>18.36</v>
+        <v>18.38</v>
       </c>
       <c r="N203" s="14" t="n"/>
       <c r="O203" s="14" t="n">
         <v>3.46</v>
       </c>
       <c r="P203" s="14" t="n">
-        <v>20.2</v>
+        <v>20.18</v>
       </c>
       <c r="Q203" s="14" t="n">
         <v>1.67</v>
@@ -34649,32 +34649,32 @@
         <v>191.01</v>
       </c>
       <c r="H216" s="14" t="n">
-        <v>7.63</v>
+        <v>7.65</v>
       </c>
       <c r="I216" s="14" t="n">
-        <v>52.74</v>
+        <v>52.75</v>
       </c>
       <c r="J216" s="15" t="n">
-        <v>97292341360</v>
+        <v>97349303260</v>
       </c>
       <c r="K216" s="15" t="n">
-        <v>10242245574.45744</v>
+        <v>10263842983.16428</v>
       </c>
       <c r="L216" s="15" t="n">
-        <v>70791175978.56871</v>
+        <v>70802870975.38345</v>
       </c>
       <c r="M216" s="14" t="n">
-        <v>25.03</v>
+        <v>24.98</v>
       </c>
       <c r="N216" s="14" t="n"/>
       <c r="O216" s="14" t="n">
         <v>3.62</v>
       </c>
       <c r="P216" s="14" t="n">
-        <v>15.06</v>
+        <v>15.09</v>
       </c>
       <c r="Q216" s="14" t="n">
-        <v>2.64</v>
+        <v>2.63</v>
       </c>
       <c r="R216" s="14" t="inlineStr">
         <is>
@@ -34725,16 +34725,16 @@
         <v>8.029999999999999</v>
       </c>
       <c r="I217" s="14" t="n">
-        <v>57.09</v>
+        <v>57.1</v>
       </c>
       <c r="J217" s="15" t="n">
-        <v>104778262050</v>
+        <v>104852081100</v>
       </c>
       <c r="K217" s="15" t="n">
-        <v>10779831788.69544</v>
+        <v>10782757975.82912</v>
       </c>
       <c r="L217" s="15" t="n">
-        <v>76628454892.14729</v>
+        <v>76641734419.29492</v>
       </c>
       <c r="M217" s="14" t="n">
         <v>23.78</v>
@@ -34744,7 +34744,7 @@
         <v>3.35</v>
       </c>
       <c r="P217" s="14" t="n">
-        <v>14.62</v>
+        <v>14.63</v>
       </c>
       <c r="Q217" s="14" t="n">
         <v>2.45</v>
@@ -35644,7 +35644,7 @@
         </is>
       </c>
       <c r="G230" s="14" t="n">
-        <v>1019</v>
+        <v>1031</v>
       </c>
       <c r="H230" s="14" t="n">
         <v>37.27</v>
@@ -35662,17 +35662,17 @@
         <v>5957336206.677702</v>
       </c>
       <c r="M230" s="14" t="n">
-        <v>27.34</v>
+        <v>27.66</v>
       </c>
       <c r="N230" s="14" t="n"/>
       <c r="O230" s="14" t="n">
-        <v>7.85</v>
+        <v>7.94</v>
       </c>
       <c r="P230" s="14" t="n">
         <v>31.18</v>
       </c>
       <c r="Q230" s="14" t="n">
-        <v>3.36</v>
+        <v>3.4</v>
       </c>
       <c r="R230" s="14" t="inlineStr">
         <is>
@@ -35717,7 +35717,7 @@
         </is>
       </c>
       <c r="G231" s="14" t="n">
-        <v>1019</v>
+        <v>1031</v>
       </c>
       <c r="H231" s="14" t="n">
         <v>52.99</v>
@@ -35735,17 +35735,17 @@
         <v>7302807985.536924</v>
       </c>
       <c r="M231" s="14" t="n">
-        <v>19.23</v>
+        <v>19.46</v>
       </c>
       <c r="N231" s="14" t="n"/>
       <c r="O231" s="14" t="n">
-        <v>6.4</v>
+        <v>6.48</v>
       </c>
       <c r="P231" s="14" t="n">
         <v>36.67</v>
       </c>
       <c r="Q231" s="14" t="n">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="R231" s="14" t="inlineStr">
         <is>
@@ -36143,7 +36143,7 @@
         </is>
       </c>
       <c r="G237" s="14" t="n">
-        <v>19.32</v>
+        <v>19.61</v>
       </c>
       <c r="H237" s="14" t="n">
         <v>0.84</v>
@@ -36161,17 +36161,17 @@
         <v>12966958880.27147</v>
       </c>
       <c r="M237" s="14" t="n">
-        <v>22.94</v>
+        <v>23.29</v>
       </c>
       <c r="N237" s="14" t="n"/>
       <c r="O237" s="14" t="n">
-        <v>4.36</v>
+        <v>4.43</v>
       </c>
       <c r="P237" s="14" t="n">
         <v>19.92</v>
       </c>
       <c r="Q237" s="14" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="R237" s="14" t="inlineStr">
         <is>
@@ -36216,7 +36216,7 @@
         </is>
       </c>
       <c r="G238" s="14" t="n">
-        <v>19.32</v>
+        <v>19.61</v>
       </c>
       <c r="H238" s="14" t="n">
         <v>0.96</v>
@@ -36234,17 +36234,17 @@
         <v>14312018303.47772</v>
       </c>
       <c r="M238" s="14" t="n">
-        <v>20.18</v>
+        <v>20.48</v>
       </c>
       <c r="N238" s="14" t="n"/>
       <c r="O238" s="14" t="n">
-        <v>3.95</v>
+        <v>4.01</v>
       </c>
       <c r="P238" s="14" t="n">
         <v>20.55</v>
       </c>
       <c r="Q238" s="14" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="R238" s="14" t="inlineStr">
         <is>
@@ -36642,7 +36642,7 @@
         </is>
       </c>
       <c r="G244" s="14" t="n">
-        <v>48.46</v>
+        <v>48.9</v>
       </c>
       <c r="H244" s="14" t="n">
         <v>2.41</v>
@@ -36660,17 +36660,17 @@
         <v>10512752480.55845</v>
       </c>
       <c r="M244" s="14" t="n">
-        <v>20.12</v>
+        <v>20.3</v>
       </c>
       <c r="N244" s="14" t="n"/>
       <c r="O244" s="14" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="P244" s="14" t="n">
         <v>13.85</v>
       </c>
       <c r="Q244" s="14" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="R244" s="14" t="inlineStr">
         <is>
@@ -36715,7 +36715,7 @@
         </is>
       </c>
       <c r="G245" s="14" t="n">
-        <v>48.46</v>
+        <v>48.9</v>
       </c>
       <c r="H245" s="14" t="n">
         <v>2.89</v>
@@ -36733,17 +36733,17 @@
         <v>11655069739.36822</v>
       </c>
       <c r="M245" s="14" t="n">
-        <v>16.78</v>
+        <v>16.93</v>
       </c>
       <c r="N245" s="14" t="n"/>
       <c r="O245" s="14" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="P245" s="14" t="n">
         <v>15.03</v>
       </c>
       <c r="Q245" s="14" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="R245" s="14" t="inlineStr">
         <is>
@@ -37141,7 +37141,7 @@
         </is>
       </c>
       <c r="G251" s="14" t="n">
-        <v>646.5</v>
+        <v>644.8</v>
       </c>
       <c r="H251" s="14" t="n">
         <v>15.52</v>
@@ -37159,17 +37159,17 @@
         <v>50260209789.75896</v>
       </c>
       <c r="M251" s="14" t="n">
-        <v>41.65</v>
+        <v>41.54</v>
       </c>
       <c r="N251" s="14" t="n"/>
       <c r="O251" s="14" t="n">
-        <v>6.93</v>
+        <v>6.91</v>
       </c>
       <c r="P251" s="14" t="n">
         <v>17.88</v>
       </c>
       <c r="Q251" s="14" t="n">
-        <v>3.57</v>
+        <v>3.56</v>
       </c>
       <c r="R251" s="14" t="inlineStr">
         <is>
@@ -37214,7 +37214,7 @@
         </is>
       </c>
       <c r="G252" s="14" t="n">
-        <v>646.5</v>
+        <v>644.8</v>
       </c>
       <c r="H252" s="14" t="n">
         <v>19.04</v>
@@ -37232,17 +37232,17 @@
         <v>58752331505.66748</v>
       </c>
       <c r="M252" s="14" t="n">
-        <v>33.96</v>
+        <v>33.87</v>
       </c>
       <c r="N252" s="14" t="n"/>
       <c r="O252" s="14" t="n">
-        <v>5.93</v>
+        <v>5.91</v>
       </c>
       <c r="P252" s="14" t="n">
         <v>18.82</v>
       </c>
       <c r="Q252" s="14" t="n">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="R252" s="14" t="inlineStr">
         <is>
@@ -37640,7 +37640,7 @@
         </is>
       </c>
       <c r="G258" s="14" t="n">
-        <v>86600</v>
+        <v>81000</v>
       </c>
       <c r="H258" s="14" t="n">
         <v>12845</v>
@@ -37668,7 +37668,7 @@
         <v>18.21</v>
       </c>
       <c r="Q258" s="14" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="R258" s="14" t="inlineStr">
         <is>
@@ -37713,7 +37713,7 @@
         </is>
       </c>
       <c r="G259" s="14" t="n">
-        <v>86600</v>
+        <v>81000</v>
       </c>
       <c r="H259" s="14" t="n">
         <v>14544.8</v>
@@ -37731,17 +37731,17 @@
         <v>3054643400967.941</v>
       </c>
       <c r="M259" s="14" t="n">
-        <v>5.95</v>
+        <v>5.57</v>
       </c>
       <c r="N259" s="14" t="n"/>
       <c r="O259" s="14" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="P259" s="14" t="n">
         <v>25.62</v>
       </c>
       <c r="Q259" s="14" t="n">
-        <v>0.4</v>
+        <v>0.37</v>
       </c>
       <c r="R259" s="14" t="inlineStr">
         <is>
@@ -38634,7 +38634,7 @@
         </is>
       </c>
       <c r="G272" s="14" t="n">
-        <v>6960</v>
+        <v>6940</v>
       </c>
       <c r="H272" s="14" t="n"/>
       <c r="I272" s="14" t="n"/>
@@ -38691,7 +38691,7 @@
         </is>
       </c>
       <c r="G273" s="14" t="n">
-        <v>6960</v>
+        <v>6940</v>
       </c>
       <c r="H273" s="14" t="n"/>
       <c r="I273" s="14" t="n"/>
@@ -40598,7 +40598,7 @@
         </is>
       </c>
       <c r="G300" s="14" t="n">
-        <v>6689</v>
+        <v>6733</v>
       </c>
       <c r="H300" s="14" t="n">
         <v>446.97</v>
@@ -40616,17 +40616,17 @@
         <v>3728663618702.116</v>
       </c>
       <c r="M300" s="14" t="n">
-        <v>14.97</v>
+        <v>15.06</v>
       </c>
       <c r="N300" s="14" t="n"/>
       <c r="O300" s="14" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="P300" s="14" t="n">
         <v>11.13</v>
       </c>
       <c r="Q300" s="14" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="R300" s="14" t="inlineStr">
         <is>
@@ -40671,7 +40671,7 @@
         </is>
       </c>
       <c r="G301" s="14" t="n">
-        <v>6689</v>
+        <v>6733</v>
       </c>
       <c r="H301" s="14" t="n">
         <v>494.41</v>
@@ -40689,17 +40689,17 @@
         <v>3969683662208.616</v>
       </c>
       <c r="M301" s="14" t="n">
-        <v>13.53</v>
+        <v>13.62</v>
       </c>
       <c r="N301" s="14" t="n"/>
       <c r="O301" s="14" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="P301" s="14" t="n">
         <v>11.57</v>
       </c>
       <c r="Q301" s="14" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="R301" s="14" t="inlineStr">
         <is>
@@ -41097,7 +41097,7 @@
         </is>
       </c>
       <c r="G307" s="14" t="n">
-        <v>5276</v>
+        <v>5244</v>
       </c>
       <c r="H307" s="14" t="n">
         <v>429.98</v>
@@ -41115,17 +41115,17 @@
         <v>953778299859.0259</v>
       </c>
       <c r="M307" s="14" t="n">
-        <v>12.27</v>
+        <v>12.2</v>
       </c>
       <c r="N307" s="14" t="n"/>
       <c r="O307" s="14" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="P307" s="14" t="n">
         <v>9.869999999999999</v>
       </c>
       <c r="Q307" s="14" t="n">
-        <v>0.76</v>
+        <v>0.75</v>
       </c>
       <c r="R307" s="14" t="inlineStr">
         <is>
@@ -41170,7 +41170,7 @@
         </is>
       </c>
       <c r="G308" s="14" t="n">
-        <v>5276</v>
+        <v>5244</v>
       </c>
       <c r="H308" s="14" t="n">
         <v>495.89</v>
@@ -41188,17 +41188,17 @@
         <v>1015608764702.593</v>
       </c>
       <c r="M308" s="14" t="n">
-        <v>10.64</v>
+        <v>10.57</v>
       </c>
       <c r="N308" s="14" t="n"/>
       <c r="O308" s="14" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="P308" s="14" t="n">
         <v>10.71</v>
       </c>
       <c r="Q308" s="14" t="n">
-        <v>0.73</v>
+        <v>0.72</v>
       </c>
       <c r="R308" s="14" t="inlineStr">
         <is>
@@ -41596,35 +41596,35 @@
         </is>
       </c>
       <c r="G314" s="14" t="n">
-        <v>307.7</v>
+        <v>310.3</v>
       </c>
       <c r="H314" s="14" t="n">
-        <v>21.77</v>
+        <v>21.73</v>
       </c>
       <c r="I314" s="14" t="n">
-        <v>99.87</v>
+        <v>99.84</v>
       </c>
       <c r="J314" s="15" t="n">
-        <v>500856064990</v>
+        <v>500306856210</v>
       </c>
       <c r="K314" s="15" t="n">
-        <v>44278012438.6832</v>
+        <v>44195616960.23952</v>
       </c>
       <c r="L314" s="15" t="n">
-        <v>203071136332.0782</v>
+        <v>203025217331.9415</v>
       </c>
       <c r="M314" s="14" t="n">
-        <v>14.13</v>
+        <v>14.28</v>
       </c>
       <c r="N314" s="14" t="n"/>
       <c r="O314" s="14" t="n">
-        <v>3.08</v>
+        <v>3.11</v>
       </c>
       <c r="P314" s="14" t="n">
-        <v>23.21</v>
+        <v>23.17</v>
       </c>
       <c r="Q314" s="14" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="R314" s="14" t="inlineStr">
         <is>
@@ -41669,35 +41669,35 @@
         </is>
       </c>
       <c r="G315" s="14" t="n">
-        <v>307.7</v>
+        <v>310.3</v>
       </c>
       <c r="H315" s="14" t="n">
-        <v>25.64</v>
+        <v>25.59</v>
       </c>
       <c r="I315" s="14" t="n">
-        <v>114.15</v>
+        <v>114.1</v>
       </c>
       <c r="J315" s="15" t="n">
-        <v>546677979470</v>
+        <v>545791718110</v>
       </c>
       <c r="K315" s="15" t="n">
-        <v>52139378864.46888</v>
+        <v>52026115583.39008</v>
       </c>
       <c r="L315" s="15" t="n">
-        <v>232128412173.2467</v>
+        <v>232019371546.5648</v>
       </c>
       <c r="M315" s="14" t="n">
-        <v>12</v>
+        <v>12.13</v>
       </c>
       <c r="N315" s="14" t="n"/>
       <c r="O315" s="14" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="P315" s="14" t="n">
-        <v>23.96</v>
+        <v>23.92</v>
       </c>
       <c r="Q315" s="14" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="R315" s="14" t="inlineStr">
         <is>
@@ -42095,7 +42095,7 @@
         </is>
       </c>
       <c r="G321" s="14" t="n">
-        <v>18.32</v>
+        <v>18.27</v>
       </c>
       <c r="H321" s="14" t="n">
         <v>1.17</v>
@@ -42113,7 +42113,7 @@
         <v>95703079447.24916</v>
       </c>
       <c r="M321" s="14" t="n">
-        <v>15.68</v>
+        <v>15.64</v>
       </c>
       <c r="N321" s="14" t="n"/>
       <c r="O321" s="14" t="n">
@@ -42123,7 +42123,7 @@
         <v>11.67</v>
       </c>
       <c r="Q321" s="14" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="R321" s="14" t="inlineStr">
         <is>
@@ -42168,7 +42168,7 @@
         </is>
       </c>
       <c r="G322" s="14" t="n">
-        <v>18.32</v>
+        <v>18.27</v>
       </c>
       <c r="H322" s="14" t="n">
         <v>1.52</v>
@@ -42186,7 +42186,7 @@
         <v>105264476530.0565</v>
       </c>
       <c r="M322" s="14" t="n">
-        <v>12.09</v>
+        <v>12.06</v>
       </c>
       <c r="N322" s="14" t="n"/>
       <c r="O322" s="14" t="n">
@@ -42594,7 +42594,7 @@
         </is>
       </c>
       <c r="G328" s="14" t="n">
-        <v>7.14</v>
+        <v>7.12</v>
       </c>
       <c r="H328" s="14" t="n">
         <v>0.66</v>
@@ -42612,7 +42612,7 @@
         <v>62872386186.58829</v>
       </c>
       <c r="M328" s="14" t="n">
-        <v>10.76</v>
+        <v>10.73</v>
       </c>
       <c r="N328" s="14" t="n"/>
       <c r="O328" s="14" t="n">
@@ -42622,7 +42622,7 @@
         <v>12.65</v>
       </c>
       <c r="Q328" s="14" t="n">
-        <v>0.74</v>
+        <v>0.73</v>
       </c>
       <c r="R328" s="14" t="inlineStr">
         <is>
@@ -42667,7 +42667,7 @@
         </is>
       </c>
       <c r="G329" s="14" t="n">
-        <v>7.14</v>
+        <v>7.12</v>
       </c>
       <c r="H329" s="14" t="n">
         <v>0.9</v>
@@ -42685,7 +42685,7 @@
         <v>66146486973.8696</v>
       </c>
       <c r="M329" s="14" t="n">
-        <v>7.92</v>
+        <v>7.9</v>
       </c>
       <c r="N329" s="14" t="n"/>
       <c r="O329" s="14" t="n">
@@ -43093,7 +43093,7 @@
         </is>
       </c>
       <c r="G335" s="14" t="n">
-        <v>8970</v>
+        <v>8860</v>
       </c>
       <c r="H335" s="14" t="n">
         <v>1728</v>
@@ -43166,7 +43166,7 @@
         </is>
       </c>
       <c r="G336" s="14" t="n">
-        <v>8970</v>
+        <v>8860</v>
       </c>
       <c r="H336" s="14" t="n">
         <v>2102</v>
@@ -43184,11 +43184,11 @@
         <v>367213567791.274</v>
       </c>
       <c r="M336" s="14" t="n">
-        <v>4.27</v>
+        <v>4.22</v>
       </c>
       <c r="N336" s="14" t="n"/>
       <c r="O336" s="14" t="n">
-        <v>0.5</v>
+        <v>0.49</v>
       </c>
       <c r="P336" s="14" t="n">
         <v>12.24</v>
@@ -43592,7 +43592,7 @@
         </is>
       </c>
       <c r="G342" s="14" t="n">
-        <v>10350</v>
+        <v>10370</v>
       </c>
       <c r="H342" s="14" t="n"/>
       <c r="I342" s="14" t="n"/>
@@ -43649,7 +43649,7 @@
         </is>
       </c>
       <c r="G343" s="14" t="n">
-        <v>10350</v>
+        <v>10370</v>
       </c>
       <c r="H343" s="14" t="n"/>
       <c r="I343" s="14" t="n"/>
@@ -44059,7 +44059,7 @@
         </is>
       </c>
       <c r="G349" s="14" t="n">
-        <v>6070</v>
+        <v>5950</v>
       </c>
       <c r="H349" s="14" t="n"/>
       <c r="I349" s="14" t="n"/>
@@ -44116,7 +44116,7 @@
         </is>
       </c>
       <c r="G350" s="14" t="n">
-        <v>6070</v>
+        <v>5950</v>
       </c>
       <c r="H350" s="14" t="n"/>
       <c r="I350" s="14" t="n"/>
@@ -44935,7 +44935,7 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>2026-10-26T10:22:15+09:00</t>
+          <t>2026-10-26T18:25:00+09:00</t>
         </is>
       </c>
     </row>
